--- a/dev_stuffs/3匠魂.xlsx
+++ b/dev_stuffs/3匠魂.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\12044\Documents\EX\PCL\.minecraft\versions\Palmon\dev_stuffs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\Palmon\dev_stuffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103BEB71-1919-475E-A4EB-15EE9F4A9F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0523A407-1592-4B98-9E7E-A90FFB3AFDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="690" yWindow="1950" windowWidth="19200" windowHeight="11260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7860" yWindow="4515" windowWidth="23940" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="阶段1" sheetId="1" r:id="rId1"/>
@@ -25,21 +25,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="140">
   <si>
     <t>材料名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -162,14 +153,6 @@
   </si>
   <si>
     <t>材料词条</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>词条1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>词条1a</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -708,7 +691,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -741,28 +724,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="4" applyBorder="1" applyAlignment="1">
@@ -790,6 +761,45 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1076,111 +1086,131 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:M68"/>
-  <sheetFormatPr defaultColWidth="16.58203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:M68"/>
+  <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="16.58203125" style="2"/>
+    <col min="1" max="16384" width="16.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:13" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1">
-        <v>1</v>
-      </c>
-      <c r="L5" s="1">
-        <v>1</v>
-      </c>
-      <c r="M5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="1" t="s">
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1">
-        <v>2</v>
-      </c>
-      <c r="I6" s="1">
-        <v>2</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="K6" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
@@ -1189,11 +1219,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:13" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="B7" s="20" t="s">
+    <row r="7" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -1230,9 +1260,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:13" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="22"/>
-      <c r="B8" s="20"/>
+    <row r="8" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="18"/>
+      <c r="B8" s="16"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
@@ -1249,10 +1279,10 @@
         <v>450</v>
       </c>
       <c r="H8" s="3">
-        <v>450</v>
+        <v>750</v>
       </c>
       <c r="I8" s="3">
-        <v>750</v>
+        <v>850</v>
       </c>
       <c r="J8" s="3">
         <v>650</v>
@@ -1267,9 +1297,9 @@
         <v>800</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
-      <c r="B9" s="20"/>
+    <row r="9" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="18"/>
+      <c r="B9" s="16"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
@@ -1304,9 +1334,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="22"/>
-      <c r="B10" s="20"/>
+    <row r="10" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="18"/>
+      <c r="B10" s="16"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -1314,7 +1344,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>27</v>
@@ -1323,53 +1353,53 @@
         <v>27</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>27</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="22"/>
-      <c r="B11" s="20" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="18"/>
+      <c r="B11" s="16" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:13" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
-      <c r="B12" s="20"/>
+    <row r="12" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="18"/>
+      <c r="B12" s="16"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:13" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="22"/>
-      <c r="B13" s="20"/>
+    <row r="13" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="18"/>
+      <c r="B13" s="16"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="22"/>
-    </row>
-    <row r="15" spans="1:13" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
-      <c r="B15" s="26" t="s">
+    <row r="14" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="18"/>
+    </row>
+    <row r="15" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="18"/>
+      <c r="B15" s="22" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -1382,7 +1412,7 @@
         <v>0.1</v>
       </c>
       <c r="F15" s="3">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G15" s="3">
         <v>-0.1</v>
@@ -1406,9 +1436,9 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="16" spans="1:13" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="22"/>
-      <c r="B16" s="27"/>
+    <row r="16" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="18"/>
+      <c r="B16" s="23"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
@@ -1419,7 +1449,7 @@
         <v>0.15</v>
       </c>
       <c r="F16" s="3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="3">
         <v>0.2</v>
@@ -1443,9 +1473,9 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="17" spans="1:13" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="22"/>
-      <c r="B17" s="27"/>
+    <row r="17" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="18"/>
+      <c r="B17" s="23"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
@@ -1480,9 +1510,9 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="18" spans="1:13" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="22"/>
-      <c r="B18" s="28"/>
+    <row r="18" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="18"/>
+      <c r="B18" s="24"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
@@ -1517,17 +1547,17 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
     </row>
-    <row r="20" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="B20" s="23" t="s">
+    <row r="20" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="B20" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -1564,16 +1594,56 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="19"/>
-      <c r="B21" s="23"/>
+    <row r="21" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="32"/>
+      <c r="B21" s="19"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="19"/>
-      <c r="B22" s="23"/>
+      <c r="D21" s="4">
+        <f>0.7*D26</f>
+        <v>420</v>
+      </c>
+      <c r="E21" s="4">
+        <f t="shared" ref="E21:M21" si="0">0.7*E26</f>
+        <v>454.99999999999994</v>
+      </c>
+      <c r="F21" s="4">
+        <f t="shared" si="0"/>
+        <v>385</v>
+      </c>
+      <c r="G21" s="4">
+        <f t="shared" si="0"/>
+        <v>315</v>
+      </c>
+      <c r="H21" s="4">
+        <f t="shared" si="0"/>
+        <v>525</v>
+      </c>
+      <c r="I21" s="4">
+        <f t="shared" si="0"/>
+        <v>595</v>
+      </c>
+      <c r="J21" s="4">
+        <f t="shared" si="0"/>
+        <v>454.99999999999994</v>
+      </c>
+      <c r="K21" s="4">
+        <f t="shared" si="0"/>
+        <v>454.99999999999994</v>
+      </c>
+      <c r="L21" s="4">
+        <f t="shared" si="0"/>
+        <v>175</v>
+      </c>
+      <c r="M21" s="4">
+        <f t="shared" si="0"/>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="32"/>
+      <c r="B22" s="19"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
@@ -1608,23 +1678,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="19"/>
-      <c r="B23" s="23"/>
+    <row r="23" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="32"/>
+      <c r="B23" s="19"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="19"/>
+    <row r="24" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="32"/>
       <c r="B24" s="10"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
-    <row r="25" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="19"/>
-      <c r="B25" s="23" t="s">
+    <row r="25" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="32"/>
+      <c r="B25" s="19" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="4" t="s">
@@ -1661,16 +1731,56 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="19"/>
-      <c r="B26" s="23"/>
+    <row r="26" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="32"/>
+      <c r="B26" s="19"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="19"/>
-      <c r="B27" s="23"/>
+      <c r="D26" s="4">
+        <f t="shared" ref="D26:M26" si="1">D8</f>
+        <v>600</v>
+      </c>
+      <c r="E26" s="4">
+        <f t="shared" si="1"/>
+        <v>650</v>
+      </c>
+      <c r="F26" s="4">
+        <f t="shared" si="1"/>
+        <v>550</v>
+      </c>
+      <c r="G26" s="4">
+        <f t="shared" si="1"/>
+        <v>450</v>
+      </c>
+      <c r="H26" s="4">
+        <f t="shared" si="1"/>
+        <v>750</v>
+      </c>
+      <c r="I26" s="4">
+        <f t="shared" si="1"/>
+        <v>850</v>
+      </c>
+      <c r="J26" s="4">
+        <f t="shared" si="1"/>
+        <v>650</v>
+      </c>
+      <c r="K26" s="4">
+        <f t="shared" si="1"/>
+        <v>650</v>
+      </c>
+      <c r="L26" s="4">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="M26" s="4">
+        <f t="shared" si="1"/>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="32"/>
+      <c r="B27" s="19"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
@@ -1705,23 +1815,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="19"/>
-      <c r="B28" s="23"/>
+    <row r="28" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="32"/>
+      <c r="B28" s="19"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="19"/>
+    <row r="29" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="32"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
-    <row r="30" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="19"/>
-      <c r="B30" s="15" t="s">
+    <row r="30" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="32"/>
+      <c r="B30" s="25" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -1758,16 +1868,56 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="19"/>
-      <c r="B31" s="16"/>
+    <row r="31" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="32"/>
+      <c r="B31" s="26"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="19"/>
-      <c r="B32" s="16"/>
+      <c r="D31" s="4">
+        <f>0.9*D26</f>
+        <v>540</v>
+      </c>
+      <c r="E31" s="4">
+        <f t="shared" ref="E31:M31" si="2">0.9*E26</f>
+        <v>585</v>
+      </c>
+      <c r="F31" s="4">
+        <f t="shared" si="2"/>
+        <v>495</v>
+      </c>
+      <c r="G31" s="4">
+        <f t="shared" si="2"/>
+        <v>405</v>
+      </c>
+      <c r="H31" s="4">
+        <f t="shared" si="2"/>
+        <v>675</v>
+      </c>
+      <c r="I31" s="4">
+        <f t="shared" si="2"/>
+        <v>765</v>
+      </c>
+      <c r="J31" s="4">
+        <f t="shared" si="2"/>
+        <v>585</v>
+      </c>
+      <c r="K31" s="4">
+        <f t="shared" si="2"/>
+        <v>585</v>
+      </c>
+      <c r="L31" s="4">
+        <f t="shared" si="2"/>
+        <v>225</v>
+      </c>
+      <c r="M31" s="4">
+        <f t="shared" si="2"/>
+        <v>720</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="32"/>
+      <c r="B32" s="26"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
@@ -1802,23 +1952,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="19"/>
-      <c r="B33" s="17"/>
+    <row r="33" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="32"/>
+      <c r="B33" s="27"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="19"/>
+    <row r="34" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="32"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="19"/>
-      <c r="B35" s="15" t="s">
+    <row r="35" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="32"/>
+      <c r="B35" s="25" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -1855,16 +2005,56 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="19"/>
-      <c r="B36" s="16"/>
+    <row r="36" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="32"/>
+      <c r="B36" s="26"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="19"/>
-      <c r="B37" s="16"/>
+      <c r="D36" s="4">
+        <f>0.6*D26</f>
+        <v>360</v>
+      </c>
+      <c r="E36" s="4">
+        <f t="shared" ref="E36:M36" si="3">0.6*E26</f>
+        <v>390</v>
+      </c>
+      <c r="F36" s="4">
+        <f t="shared" si="3"/>
+        <v>330</v>
+      </c>
+      <c r="G36" s="4">
+        <f t="shared" si="3"/>
+        <v>270</v>
+      </c>
+      <c r="H36" s="4">
+        <f t="shared" si="3"/>
+        <v>450</v>
+      </c>
+      <c r="I36" s="4">
+        <f t="shared" si="3"/>
+        <v>510</v>
+      </c>
+      <c r="J36" s="4">
+        <f t="shared" si="3"/>
+        <v>390</v>
+      </c>
+      <c r="K36" s="4">
+        <f t="shared" si="3"/>
+        <v>390</v>
+      </c>
+      <c r="L36" s="4">
+        <f t="shared" si="3"/>
+        <v>150</v>
+      </c>
+      <c r="M36" s="4">
+        <f t="shared" si="3"/>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="32"/>
+      <c r="B37" s="26"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
@@ -1899,32 +2089,72 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="19"/>
-      <c r="B38" s="17"/>
+    <row r="38" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="32"/>
+      <c r="B38" s="27"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="19"/>
+    <row r="39" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="32"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="19"/>
-      <c r="B40" s="15" t="s">
+    <row r="40" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="32"/>
+      <c r="B40" s="25" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="19"/>
-      <c r="B41" s="16"/>
+      <c r="D40" s="4">
+        <f>0.9*D26</f>
+        <v>540</v>
+      </c>
+      <c r="E40" s="4">
+        <f t="shared" ref="E40:M40" si="4">0.9*E26</f>
+        <v>585</v>
+      </c>
+      <c r="F40" s="4">
+        <f t="shared" si="4"/>
+        <v>495</v>
+      </c>
+      <c r="G40" s="4">
+        <f t="shared" si="4"/>
+        <v>405</v>
+      </c>
+      <c r="H40" s="4">
+        <f t="shared" si="4"/>
+        <v>675</v>
+      </c>
+      <c r="I40" s="4">
+        <f t="shared" si="4"/>
+        <v>765</v>
+      </c>
+      <c r="J40" s="4">
+        <f t="shared" si="4"/>
+        <v>585</v>
+      </c>
+      <c r="K40" s="4">
+        <f t="shared" si="4"/>
+        <v>585</v>
+      </c>
+      <c r="L40" s="4">
+        <f t="shared" si="4"/>
+        <v>225</v>
+      </c>
+      <c r="M40" s="4">
+        <f t="shared" si="4"/>
+        <v>720</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="32"/>
+      <c r="B41" s="26"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
@@ -1959,49 +2189,49 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="19"/>
-      <c r="B42" s="17"/>
+    <row r="42" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="32"/>
+      <c r="B42" s="27"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="19"/>
-    </row>
-    <row r="44" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="19"/>
-      <c r="B44" s="15" t="s">
+    <row r="43" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="32"/>
+    </row>
+    <row r="44" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="32"/>
+      <c r="B44" s="25" t="s">
         <v>30</v>
       </c>
       <c r="C44" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="19"/>
-      <c r="B45" s="16"/>
+    <row r="45" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="32"/>
+      <c r="B45" s="26"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="19"/>
-      <c r="B46" s="17"/>
+    <row r="46" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="32"/>
+      <c r="B46" s="27"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="19"/>
+    <row r="47" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="32"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
     </row>
-    <row r="48" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="19"/>
-      <c r="B48" s="15" t="s">
+    <row r="48" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="32"/>
+      <c r="B48" s="25" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="4" t="s">
@@ -2016,19 +2246,19 @@
         <v>11</v>
       </c>
       <c r="F48" s="4">
-        <f t="shared" ref="F48:M48" si="0">F20+F25+F30+F35</f>
+        <f t="shared" ref="F48:M48" si="5">F20+F25+F30+F35</f>
         <v>10</v>
       </c>
       <c r="G48" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="H48" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="I48" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="J48" s="4">
@@ -2036,23 +2266,23 @@
         <v>15</v>
       </c>
       <c r="K48" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="L48" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="M48" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="19"/>
-      <c r="B49" s="16"/>
+    <row r="49" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="32"/>
+      <c r="B49" s="26"/>
       <c r="C49" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D49" s="4">
         <f>D22+D27+D32+D37+D41</f>
@@ -2063,19 +2293,19 @@
         <v>5</v>
       </c>
       <c r="F49" s="4">
-        <f t="shared" ref="F49:M49" si="1">F22+F27+F32+F37+F41</f>
+        <f t="shared" ref="F49:M49" si="6">F22+F27+F32+F37+F41</f>
         <v>5</v>
       </c>
       <c r="G49" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="H49" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="I49" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="J49" s="4">
@@ -2083,23 +2313,23 @@
         <v>5</v>
       </c>
       <c r="K49" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="L49" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="M49" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:13" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="19"/>
-      <c r="B50" s="17"/>
+    <row r="50" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="32"/>
+      <c r="B50" s="27"/>
       <c r="C50" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D50" s="4">
         <f>D48*(1+D49*0.02)</f>
@@ -2110,19 +2340,19 @@
         <v>12.100000000000001</v>
       </c>
       <c r="F50" s="4">
-        <f t="shared" ref="F50:M50" si="2">F48*(1+F49*0.02)</f>
+        <f t="shared" ref="F50:M50" si="7">F48*(1+F49*0.02)</f>
         <v>11</v>
       </c>
       <c r="G50" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="H50" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>12.100000000000001</v>
       </c>
       <c r="I50" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>14.3</v>
       </c>
       <c r="J50" s="4">
@@ -2130,111 +2360,111 @@
         <v>16.5</v>
       </c>
       <c r="K50" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>16.5</v>
       </c>
       <c r="L50" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>16.5</v>
       </c>
       <c r="M50" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
     </row>
-    <row r="52" spans="1:13" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="B52" s="21" t="s">
+    <row r="52" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="B52" s="17" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:13" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="21"/>
-      <c r="B53" s="21"/>
+    <row r="53" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="17"/>
+      <c r="B53" s="17"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:13" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="21"/>
-      <c r="B54" s="21"/>
+    <row r="54" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="17"/>
+      <c r="B54" s="17"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:13" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="21"/>
-      <c r="B55" s="21"/>
+    <row r="55" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="17"/>
+      <c r="B55" s="17"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:13" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="21"/>
-      <c r="B56" s="21" t="s">
+    <row r="56" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="17"/>
+      <c r="B56" s="17" t="s">
         <v>30</v>
       </c>
       <c r="C56" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:13" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="21"/>
-      <c r="B57" s="24"/>
+    <row r="57" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="17"/>
+      <c r="B57" s="20"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:13" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="21"/>
-      <c r="B58" s="25"/>
+    <row r="58" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="17"/>
+      <c r="B58" s="21"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="21"/>
+    <row r="59" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="17"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
     </row>
-    <row r="60" spans="1:13" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="21"/>
-      <c r="B60" s="21" t="s">
+    <row r="60" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="17"/>
+      <c r="B60" s="17" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:13" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="21"/>
-      <c r="B61" s="24"/>
+    <row r="61" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="17"/>
+      <c r="B61" s="20"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:13" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="21"/>
-      <c r="B62" s="25"/>
+    <row r="62" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="17"/>
+      <c r="B62" s="21"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:12" s="6" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="12" t="s">
+    <row r="65" spans="1:12" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="28" t="s">
         <v>26</v>
       </c>
       <c r="B65" s="6" t="s">
@@ -2271,85 +2501,85 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:12" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
+    <row r="66" spans="1:12" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="29"/>
       <c r="B66" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D66" s="4">
+        <v>1</v>
+      </c>
+      <c r="E66" s="4">
+        <v>1</v>
+      </c>
+      <c r="F66" s="4">
+        <v>1</v>
+      </c>
+      <c r="G66" s="4">
+        <v>1</v>
+      </c>
+      <c r="H66" s="4">
+        <v>1</v>
+      </c>
+      <c r="I66" s="4">
+        <v>1</v>
+      </c>
+      <c r="J66" s="4">
+        <v>1</v>
+      </c>
+      <c r="K66" s="4">
+        <v>1</v>
+      </c>
+      <c r="L66" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="29"/>
+      <c r="B67" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D67" s="4">
+        <v>1</v>
+      </c>
+      <c r="E67" s="4">
+        <v>1</v>
+      </c>
+      <c r="F67" s="4">
+        <v>1</v>
+      </c>
+      <c r="G67" s="4">
+        <v>1</v>
+      </c>
+      <c r="H67" s="4">
+        <v>1</v>
+      </c>
+      <c r="I67" s="4">
+        <v>1</v>
+      </c>
+      <c r="J67" s="4">
+        <v>1</v>
+      </c>
+      <c r="K67" s="4">
+        <v>1</v>
+      </c>
+      <c r="L67" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="30"/>
+      <c r="B68" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C66" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D66" s="4">
-        <v>1</v>
-      </c>
-      <c r="E66" s="4">
-        <v>1</v>
-      </c>
-      <c r="F66" s="4">
-        <v>1</v>
-      </c>
-      <c r="G66" s="4">
-        <v>1</v>
-      </c>
-      <c r="H66" s="4">
-        <v>1</v>
-      </c>
-      <c r="I66" s="4">
-        <v>1</v>
-      </c>
-      <c r="J66" s="4">
-        <v>1</v>
-      </c>
-      <c r="K66" s="4">
-        <v>1</v>
-      </c>
-      <c r="L66" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="4" t="s">
+      <c r="C68" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D67" s="4">
-        <v>1</v>
-      </c>
-      <c r="E67" s="4">
-        <v>1</v>
-      </c>
-      <c r="F67" s="4">
-        <v>1</v>
-      </c>
-      <c r="G67" s="4">
-        <v>1</v>
-      </c>
-      <c r="H67" s="4">
-        <v>1</v>
-      </c>
-      <c r="I67" s="4">
-        <v>1</v>
-      </c>
-      <c r="J67" s="4">
-        <v>1</v>
-      </c>
-      <c r="K67" s="4">
-        <v>1</v>
-      </c>
-      <c r="L67" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="14"/>
-      <c r="B68" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>138</v>
       </c>
       <c r="D68" s="5">
         <v>0</v>
@@ -2381,7 +2611,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B48:B50"/>
     <mergeCell ref="A65:A68"/>
     <mergeCell ref="B44:B46"/>
     <mergeCell ref="A20:A50"/>
@@ -2398,6 +2627,7 @@
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="B35:B38"/>
     <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B48:B50"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2407,78 +2637,78 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228FD55C-7A05-4B85-B3F0-CE35E1F4B422}">
-  <dimension ref="A1:Q68"/>
-  <sheetFormatPr defaultColWidth="16.58203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q67"/>
+  <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="16.58203125" style="2"/>
+    <col min="1" max="3" width="16.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="2"/>
     </row>
-    <row r="4" spans="1:17" s="11" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="P4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" s="11" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:17" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -2523,11 +2753,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="11" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -2557,7 +2787,7 @@
         <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N6" s="1">
         <v>3</v>
@@ -2572,163 +2802,618 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="B7" s="20" t="s">
+    <row r="7" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="22"/>
-      <c r="B8" s="20"/>
+        <v>17</v>
+      </c>
+      <c r="E7" s="3">
+        <v>18</v>
+      </c>
+      <c r="F7" s="3">
+        <v>13</v>
+      </c>
+      <c r="G7" s="3">
+        <v>14</v>
+      </c>
+      <c r="H7" s="3">
+        <v>20</v>
+      </c>
+      <c r="I7" s="3">
+        <v>19</v>
+      </c>
+      <c r="J7" s="3">
+        <v>21</v>
+      </c>
+      <c r="K7" s="3">
+        <v>23</v>
+      </c>
+      <c r="L7" s="3">
+        <v>23</v>
+      </c>
+      <c r="M7" s="3">
+        <v>25</v>
+      </c>
+      <c r="N7" s="3">
+        <v>24</v>
+      </c>
+      <c r="O7" s="3">
+        <v>28</v>
+      </c>
+      <c r="P7" s="3">
+        <v>32</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="18"/>
+      <c r="B8" s="16"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="3">
+        <v>200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>250</v>
+      </c>
+      <c r="F8" s="3">
+        <v>250</v>
+      </c>
+      <c r="G8" s="3">
+        <v>200</v>
+      </c>
+      <c r="H8" s="3">
+        <v>500</v>
+      </c>
+      <c r="I8" s="3">
+        <v>300</v>
+      </c>
+      <c r="J8" s="3">
+        <v>450</v>
+      </c>
+      <c r="K8" s="3">
+        <v>600</v>
+      </c>
+      <c r="L8" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
-      <c r="B9" s="20"/>
+      <c r="M8" s="3">
+        <v>900</v>
+      </c>
+      <c r="N8" s="3">
+        <v>800</v>
+      </c>
+      <c r="O8" s="3">
+        <v>800</v>
+      </c>
+      <c r="P8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="18"/>
+      <c r="B9" s="16"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="3">
+        <v>6</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6</v>
+      </c>
+      <c r="F9" s="3">
+        <v>6</v>
+      </c>
+      <c r="G9" s="3">
+        <v>6</v>
+      </c>
+      <c r="H9" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="22"/>
-      <c r="B10" s="20"/>
+      <c r="I9" s="3">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
+        <v>9</v>
+      </c>
+      <c r="L9" s="3">
+        <v>8</v>
+      </c>
+      <c r="M9" s="3">
+        <v>10</v>
+      </c>
+      <c r="N9" s="3">
+        <v>9</v>
+      </c>
+      <c r="O9" s="3">
+        <v>10</v>
+      </c>
+      <c r="P9" s="3">
+        <v>8</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="18"/>
+      <c r="B10" s="16"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="22"/>
-      <c r="B11" s="20" t="s">
+      <c r="E10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="18"/>
+      <c r="B11" s="16" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
-      <c r="B12" s="20"/>
+    </row>
+    <row r="12" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="18"/>
+      <c r="B12" s="16"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="22"/>
-      <c r="B13" s="20"/>
+    <row r="13" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="18"/>
+      <c r="B13" s="16"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="22"/>
-    </row>
-    <row r="15" spans="1:17" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
-      <c r="B15" s="26" t="s">
+    <row r="14" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="18"/>
+    </row>
+    <row r="15" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="18"/>
+      <c r="B15" s="22" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="22"/>
-      <c r="B16" s="27"/>
+      <c r="D15" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E15" s="3">
+        <v>-0.3</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>-0.2</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="18"/>
+      <c r="B16" s="23"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="22"/>
-      <c r="B17" s="27"/>
+      <c r="D16" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="I16" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="K16" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="L16" s="3">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="N16" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="O16" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="P16" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="18"/>
+      <c r="B17" s="23"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="22"/>
-      <c r="B18" s="28"/>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="L17" s="3">
+        <v>-0.2</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="P17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="18"/>
+      <c r="B18" s="24"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
     </row>
-    <row r="20" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="B20" s="23" t="s">
+    <row r="20" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B20" s="34" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E20" s="4">
+        <v>3</v>
+      </c>
+      <c r="F20" s="4">
+        <v>4</v>
+      </c>
+      <c r="G20" s="4">
+        <v>3</v>
+      </c>
+      <c r="H20" s="4">
+        <v>4</v>
+      </c>
+      <c r="I20" s="4">
+        <v>4</v>
+      </c>
+      <c r="J20" s="4">
+        <v>3</v>
+      </c>
+      <c r="K20" s="4">
+        <v>4</v>
+      </c>
+      <c r="L20" s="4">
+        <v>4</v>
+      </c>
+      <c r="M20" s="4">
+        <v>5</v>
+      </c>
+      <c r="N20" s="4">
+        <v>4</v>
+      </c>
+      <c r="O20" s="4">
+        <v>5</v>
+      </c>
+      <c r="P20" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="19"/>
-      <c r="B21" s="23"/>
+      <c r="B21" s="34"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D21" s="4">
+        <f>0.7*D26</f>
+        <v>140</v>
+      </c>
+      <c r="E21" s="4">
+        <f t="shared" ref="E21:Q21" si="0">0.7*E26</f>
+        <v>175</v>
+      </c>
+      <c r="F21" s="4">
+        <f t="shared" si="0"/>
+        <v>175</v>
+      </c>
+      <c r="G21" s="4">
+        <f t="shared" si="0"/>
+        <v>140</v>
+      </c>
+      <c r="H21" s="4">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="I21" s="4">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="J21" s="4">
+        <f t="shared" si="0"/>
+        <v>315</v>
+      </c>
+      <c r="K21" s="4">
+        <f t="shared" si="0"/>
+        <v>420</v>
+      </c>
+      <c r="L21" s="4">
+        <f t="shared" si="0"/>
+        <v>280</v>
+      </c>
+      <c r="M21" s="4">
+        <f t="shared" si="0"/>
+        <v>630</v>
+      </c>
+      <c r="N21" s="4">
+        <f t="shared" si="0"/>
+        <v>560</v>
+      </c>
+      <c r="O21" s="4">
+        <f t="shared" si="0"/>
+        <v>560</v>
+      </c>
+      <c r="P21" s="4">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="Q21" s="4">
+        <f t="shared" si="0"/>
+        <v>489.99999999999994</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="19"/>
-      <c r="B22" s="23"/>
+      <c r="B22" s="34"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D22" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E22" s="4">
+        <v>1</v>
+      </c>
+      <c r="F22" s="4">
+        <v>1</v>
+      </c>
+      <c r="G22" s="4">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4">
+        <v>1</v>
+      </c>
+      <c r="I22" s="4">
+        <v>2</v>
+      </c>
+      <c r="J22" s="4">
+        <v>1</v>
+      </c>
+      <c r="K22" s="4">
+        <v>2</v>
+      </c>
+      <c r="L22" s="4">
+        <v>2</v>
+      </c>
+      <c r="M22" s="4">
+        <v>2</v>
+      </c>
+      <c r="N22" s="4">
+        <v>2</v>
+      </c>
+      <c r="O22" s="4">
+        <v>2</v>
+      </c>
+      <c r="P22" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="19"/>
-      <c r="B23" s="23"/>
+      <c r="B23" s="34"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="19"/>
-      <c r="B24" s="10"/>
+      <c r="B24" s="12"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
-    <row r="25" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="19"/>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="34" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="4" t="s">
@@ -2737,81 +3422,352 @@
       <c r="D25" s="4">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E25" s="4">
+        <v>4</v>
+      </c>
+      <c r="F25" s="4">
+        <v>4</v>
+      </c>
+      <c r="G25" s="4">
+        <v>4</v>
+      </c>
+      <c r="H25" s="4">
+        <v>6</v>
+      </c>
+      <c r="I25" s="4">
+        <v>5</v>
+      </c>
+      <c r="J25" s="4">
+        <v>6</v>
+      </c>
+      <c r="K25" s="4">
+        <v>6</v>
+      </c>
+      <c r="L25" s="4">
+        <v>6</v>
+      </c>
+      <c r="M25" s="4">
+        <v>7</v>
+      </c>
+      <c r="N25" s="4">
+        <v>6</v>
+      </c>
+      <c r="O25" s="4">
+        <v>7</v>
+      </c>
+      <c r="P25" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q25" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="19"/>
-      <c r="B26" s="23"/>
+      <c r="B26" s="34"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D26" s="4">
+        <f t="shared" ref="D26:Q26" si="1">D8</f>
+        <v>200</v>
+      </c>
+      <c r="E26" s="4">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="F26" s="4">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="G26" s="4">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="H26" s="4">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="I26" s="4">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="J26" s="4">
+        <f t="shared" si="1"/>
+        <v>450</v>
+      </c>
+      <c r="K26" s="4">
+        <f t="shared" si="1"/>
+        <v>600</v>
+      </c>
+      <c r="L26" s="4">
+        <f t="shared" si="1"/>
+        <v>400</v>
+      </c>
+      <c r="M26" s="4">
+        <f t="shared" si="1"/>
+        <v>900</v>
+      </c>
+      <c r="N26" s="4">
+        <f t="shared" si="1"/>
+        <v>800</v>
+      </c>
+      <c r="O26" s="4">
+        <f t="shared" si="1"/>
+        <v>800</v>
+      </c>
+      <c r="P26" s="4">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="Q26" s="4">
+        <f t="shared" si="1"/>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="19"/>
-      <c r="B27" s="23"/>
+      <c r="B27" s="34"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D27" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E27" s="4">
+        <v>1</v>
+      </c>
+      <c r="F27" s="4">
+        <v>1</v>
+      </c>
+      <c r="G27" s="4">
+        <v>1</v>
+      </c>
+      <c r="H27" s="4">
+        <v>1</v>
+      </c>
+      <c r="I27" s="4">
+        <v>1</v>
+      </c>
+      <c r="J27" s="4">
+        <v>1</v>
+      </c>
+      <c r="K27" s="4">
+        <v>2</v>
+      </c>
+      <c r="L27" s="4">
+        <v>2</v>
+      </c>
+      <c r="M27" s="4">
+        <v>2</v>
+      </c>
+      <c r="N27" s="4">
+        <v>2</v>
+      </c>
+      <c r="O27" s="4">
+        <v>2</v>
+      </c>
+      <c r="P27" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="19"/>
-      <c r="B28" s="23"/>
+      <c r="B28" s="34"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="19"/>
-      <c r="B29" s="9"/>
+      <c r="B29" s="13"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
-    <row r="30" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="19"/>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D30" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E30" s="4">
+        <v>4</v>
+      </c>
+      <c r="F30" s="4">
+        <v>4</v>
+      </c>
+      <c r="G30" s="4">
+        <v>4</v>
+      </c>
+      <c r="H30" s="4">
+        <v>5</v>
+      </c>
+      <c r="I30" s="4">
+        <v>4</v>
+      </c>
+      <c r="J30" s="4">
+        <v>5</v>
+      </c>
+      <c r="K30" s="4">
+        <v>5</v>
+      </c>
+      <c r="L30" s="4">
+        <v>5</v>
+      </c>
+      <c r="M30" s="4">
+        <v>6</v>
+      </c>
+      <c r="N30" s="4">
+        <v>5</v>
+      </c>
+      <c r="O30" s="4">
+        <v>6</v>
+      </c>
+      <c r="P30" s="4">
+        <v>6</v>
+      </c>
+      <c r="Q30" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="19"/>
+      <c r="B31" s="36"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D31" s="4">
+        <f>0.9*D26</f>
+        <v>180</v>
+      </c>
+      <c r="E31" s="4">
+        <f t="shared" ref="E31:Q31" si="2">0.9*E26</f>
+        <v>225</v>
+      </c>
+      <c r="F31" s="4">
+        <f t="shared" si="2"/>
+        <v>225</v>
+      </c>
+      <c r="G31" s="4">
+        <f t="shared" si="2"/>
+        <v>180</v>
+      </c>
+      <c r="H31" s="4">
+        <f t="shared" si="2"/>
+        <v>450</v>
+      </c>
+      <c r="I31" s="4">
+        <f t="shared" si="2"/>
+        <v>270</v>
+      </c>
+      <c r="J31" s="4">
+        <f t="shared" si="2"/>
+        <v>405</v>
+      </c>
+      <c r="K31" s="4">
+        <f t="shared" si="2"/>
+        <v>540</v>
+      </c>
+      <c r="L31" s="4">
+        <f t="shared" si="2"/>
+        <v>360</v>
+      </c>
+      <c r="M31" s="4">
+        <f t="shared" si="2"/>
+        <v>810</v>
+      </c>
+      <c r="N31" s="4">
+        <f t="shared" si="2"/>
+        <v>720</v>
+      </c>
+      <c r="O31" s="4">
+        <f t="shared" si="2"/>
+        <v>720</v>
+      </c>
+      <c r="P31" s="4">
+        <f t="shared" si="2"/>
+        <v>900</v>
+      </c>
+      <c r="Q31" s="4">
+        <f t="shared" si="2"/>
+        <v>630</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="19"/>
+      <c r="B32" s="36"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D32" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E32" s="4">
+        <v>1</v>
+      </c>
+      <c r="F32" s="4">
+        <v>1</v>
+      </c>
+      <c r="G32" s="4">
+        <v>1</v>
+      </c>
+      <c r="H32" s="4">
+        <v>1</v>
+      </c>
+      <c r="I32" s="4">
+        <v>1</v>
+      </c>
+      <c r="J32" s="4">
+        <v>1</v>
+      </c>
+      <c r="K32" s="4">
+        <v>2</v>
+      </c>
+      <c r="L32" s="4">
+        <v>2</v>
+      </c>
+      <c r="M32" s="4">
+        <v>2</v>
+      </c>
+      <c r="N32" s="4">
+        <v>2</v>
+      </c>
+      <c r="O32" s="4">
+        <v>2</v>
+      </c>
+      <c r="P32" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q32" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="19"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="19"/>
-      <c r="B34" s="1"/>
+      <c r="B34" s="14"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="19"/>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="35" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -2820,287 +3776,1742 @@
       <c r="D35" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E35" s="4">
+        <v>2</v>
+      </c>
+      <c r="F35" s="4">
+        <v>2</v>
+      </c>
+      <c r="G35" s="4">
+        <v>3</v>
+      </c>
+      <c r="H35" s="4">
+        <v>3</v>
+      </c>
+      <c r="I35" s="4">
+        <v>3</v>
+      </c>
+      <c r="J35" s="4">
+        <v>2</v>
+      </c>
+      <c r="K35" s="4">
+        <v>3</v>
+      </c>
+      <c r="L35" s="4">
+        <v>3</v>
+      </c>
+      <c r="M35" s="4">
+        <v>4</v>
+      </c>
+      <c r="N35" s="4">
+        <v>3</v>
+      </c>
+      <c r="O35" s="4">
+        <v>4</v>
+      </c>
+      <c r="P35" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="19"/>
+      <c r="B36" s="36"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>0.6*D26</f>
+        <v>120</v>
+      </c>
+      <c r="E36" s="4">
+        <f t="shared" ref="E36:Q36" si="3">0.6*E26</f>
+        <v>150</v>
+      </c>
+      <c r="F36" s="4">
+        <f t="shared" si="3"/>
+        <v>150</v>
+      </c>
+      <c r="G36" s="4">
+        <f t="shared" si="3"/>
+        <v>120</v>
+      </c>
+      <c r="H36" s="4">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="I36" s="4">
+        <f t="shared" si="3"/>
+        <v>180</v>
+      </c>
+      <c r="J36" s="4">
+        <f t="shared" si="3"/>
+        <v>270</v>
+      </c>
+      <c r="K36" s="4">
+        <f t="shared" si="3"/>
+        <v>360</v>
+      </c>
+      <c r="L36" s="4">
+        <f t="shared" si="3"/>
+        <v>240</v>
+      </c>
+      <c r="M36" s="4">
+        <f t="shared" si="3"/>
+        <v>540</v>
+      </c>
+      <c r="N36" s="4">
+        <f t="shared" si="3"/>
+        <v>480</v>
+      </c>
+      <c r="O36" s="4">
+        <f t="shared" si="3"/>
+        <v>480</v>
+      </c>
+      <c r="P36" s="4">
+        <f t="shared" si="3"/>
+        <v>600</v>
+      </c>
+      <c r="Q36" s="4">
+        <f t="shared" si="3"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="19"/>
+      <c r="B37" s="36"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D37" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E37" s="4">
+        <v>1</v>
+      </c>
+      <c r="F37" s="4">
+        <v>1</v>
+      </c>
+      <c r="G37" s="4">
+        <v>1</v>
+      </c>
+      <c r="H37" s="4">
+        <v>1</v>
+      </c>
+      <c r="I37" s="4">
+        <v>2</v>
+      </c>
+      <c r="J37" s="4">
+        <v>1</v>
+      </c>
+      <c r="K37" s="4">
+        <v>2</v>
+      </c>
+      <c r="L37" s="4">
+        <v>2</v>
+      </c>
+      <c r="M37" s="4">
+        <v>2</v>
+      </c>
+      <c r="N37" s="4">
+        <v>2</v>
+      </c>
+      <c r="O37" s="4">
+        <v>2</v>
+      </c>
+      <c r="P37" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q37" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="19"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="19"/>
-      <c r="B39" s="1"/>
+      <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="19"/>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="35" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D40" s="4">
+        <f>0.9*D26</f>
+        <v>180</v>
+      </c>
+      <c r="E40" s="4">
+        <f t="shared" ref="E40:Q40" si="4">0.9*E26</f>
+        <v>225</v>
+      </c>
+      <c r="F40" s="4">
+        <f t="shared" si="4"/>
+        <v>225</v>
+      </c>
+      <c r="G40" s="4">
+        <f t="shared" si="4"/>
+        <v>180</v>
+      </c>
+      <c r="H40" s="4">
+        <f t="shared" si="4"/>
+        <v>450</v>
+      </c>
+      <c r="I40" s="4">
+        <f t="shared" si="4"/>
+        <v>270</v>
+      </c>
+      <c r="J40" s="4">
+        <f t="shared" si="4"/>
+        <v>405</v>
+      </c>
+      <c r="K40" s="4">
+        <f t="shared" si="4"/>
+        <v>540</v>
+      </c>
+      <c r="L40" s="4">
+        <f t="shared" si="4"/>
+        <v>360</v>
+      </c>
+      <c r="M40" s="4">
+        <f t="shared" si="4"/>
+        <v>810</v>
+      </c>
+      <c r="N40" s="4">
+        <f t="shared" si="4"/>
+        <v>720</v>
+      </c>
+      <c r="O40" s="4">
+        <f t="shared" si="4"/>
+        <v>720</v>
+      </c>
+      <c r="P40" s="4">
+        <f t="shared" si="4"/>
+        <v>900</v>
+      </c>
+      <c r="Q40" s="4">
+        <f t="shared" si="4"/>
+        <v>630</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="19"/>
+      <c r="B41" s="36"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D41" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E41" s="4">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4">
+        <v>1</v>
+      </c>
+      <c r="G41" s="4">
+        <v>1</v>
+      </c>
+      <c r="H41" s="4">
+        <v>1</v>
+      </c>
+      <c r="I41" s="4">
+        <v>1</v>
+      </c>
+      <c r="J41" s="4">
+        <v>1</v>
+      </c>
+      <c r="K41" s="4">
+        <v>2</v>
+      </c>
+      <c r="L41" s="4">
+        <v>2</v>
+      </c>
+      <c r="M41" s="4">
+        <v>2</v>
+      </c>
+      <c r="N41" s="4">
+        <v>2</v>
+      </c>
+      <c r="O41" s="4">
+        <v>2</v>
+      </c>
+      <c r="P41" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q41" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="19"/>
+      <c r="B42" s="37"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="19"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
     </row>
-    <row r="44" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="19"/>
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C44" s="4">
         <v>1</v>
       </c>
-      <c r="D44" s="4">
-        <f>D20+D25+D30+D35</f>
-        <v>11</v>
-      </c>
-      <c r="E44" s="4">
-        <f>E20+E25+E30+E35</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="19"/>
-      <c r="B45" s="16"/>
+      <c r="B45" s="36"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
-      <c r="D45" s="4">
-        <f>D22+D27+D32+D37+D41</f>
-        <v>5</v>
-      </c>
-      <c r="E45" s="4">
-        <f>E22+E27+E32+E37+E41</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="19"/>
-      <c r="B46" s="17"/>
+      <c r="B46" s="37"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
-      <c r="D46" s="4">
-        <f>D44*(1+D45*0.02)</f>
-        <v>12.100000000000001</v>
-      </c>
-      <c r="E46" s="4">
-        <f>E44*(1+E45*0.02)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="19"/>
-      <c r="B47" s="7"/>
+      <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
-    <row r="48" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="19"/>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="35" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D48" s="4">
+        <f t="shared" ref="D48:Q48" si="5">D20+D25+D30+D35</f>
+        <v>13</v>
+      </c>
+      <c r="E48" s="4">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="F48" s="4">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="G48" s="4">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="H48" s="4">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="I48" s="4">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="J48" s="4">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="K48" s="4">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="L48" s="4">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="M48" s="4">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
+      <c r="N48" s="4">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="O48" s="4">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
+      <c r="P48" s="4">
+        <f t="shared" si="5"/>
+        <v>23</v>
+      </c>
+      <c r="Q48" s="4">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="19"/>
-      <c r="B49" s="4"/>
+      <c r="B49" s="36"/>
       <c r="C49" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+      <c r="D49" s="4">
+        <f t="shared" ref="D49:Q49" si="6">D22+D27+D32+D37+D41</f>
+        <v>5</v>
+      </c>
+      <c r="E49" s="4">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="F49" s="4">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="G49" s="4">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="H49" s="4">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="I49" s="4">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="J49" s="4">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="K49" s="4">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="L49" s="4">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="M49" s="4">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="N49" s="4">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="O49" s="4">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="P49" s="4">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="Q49" s="4">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="19"/>
-      <c r="B50" s="4"/>
+      <c r="B50" s="37"/>
       <c r="C50" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+      <c r="D50" s="4">
+        <f>D48*(1+D49*0.02)</f>
+        <v>14.3</v>
+      </c>
+      <c r="E50" s="4">
+        <f>E48*(1+E49*0.02)</f>
+        <v>14.3</v>
+      </c>
+      <c r="F50" s="4">
+        <f t="shared" ref="F50:M50" si="7">F48*(1+F49*0.02)</f>
+        <v>15.400000000000002</v>
+      </c>
+      <c r="G50" s="4">
+        <f t="shared" si="7"/>
+        <v>15.400000000000002</v>
+      </c>
+      <c r="H50" s="4">
+        <f t="shared" si="7"/>
+        <v>19.8</v>
+      </c>
+      <c r="I50" s="4">
+        <f t="shared" si="7"/>
+        <v>18.240000000000002</v>
+      </c>
+      <c r="J50" s="4">
+        <f t="shared" si="7"/>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="K50" s="4">
+        <f t="shared" si="7"/>
+        <v>21.599999999999998</v>
+      </c>
+      <c r="L50" s="4">
+        <f t="shared" si="7"/>
+        <v>21.599999999999998</v>
+      </c>
+      <c r="M50" s="4">
+        <f t="shared" si="7"/>
+        <v>26.4</v>
+      </c>
+      <c r="N50" s="4">
+        <f t="shared" ref="N50" si="8">N48*(1+N49*0.02)</f>
+        <v>21.599999999999998</v>
+      </c>
+      <c r="O50" s="4">
+        <f t="shared" ref="O50" si="9">O48*(1+O49*0.02)</f>
+        <v>26.4</v>
+      </c>
+      <c r="P50" s="4">
+        <f t="shared" ref="P50" si="10">P48*(1+P49*0.02)</f>
+        <v>28.52</v>
+      </c>
+      <c r="Q50" s="4">
+        <f t="shared" ref="Q50" si="11">Q48*(1+Q49*0.02)</f>
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
     </row>
-    <row r="52" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="B52" s="21" t="s">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="B52" s="33" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="21"/>
-      <c r="B53" s="21"/>
+    </row>
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="20"/>
+      <c r="B53" s="20"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="21"/>
-      <c r="B54" s="21"/>
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="20"/>
+      <c r="B54" s="20"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="21"/>
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="20"/>
       <c r="B55" s="21"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-    </row>
-    <row r="56" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="21"/>
-      <c r="B56" s="21" t="s">
+    </row>
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="20"/>
+      <c r="B56" s="33" t="s">
         <v>30</v>
       </c>
       <c r="C56" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="21"/>
-      <c r="B57" s="24"/>
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="20"/>
+      <c r="B57" s="20"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="21"/>
-      <c r="B58" s="25"/>
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="20"/>
+      <c r="B58" s="21"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="21"/>
+    <row r="59" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="20"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
-    </row>
-    <row r="60" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="21"/>
-      <c r="B60" s="21" t="s">
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+    </row>
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="20"/>
+      <c r="B60" s="33" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-    </row>
-    <row r="61" spans="1:5" s="6" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="21"/>
-      <c r="B61" s="24"/>
+    </row>
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="20"/>
+      <c r="B61" s="20"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="21"/>
-      <c r="B62" s="25"/>
+      <c r="B62" s="21"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-    </row>
-    <row r="64" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-    </row>
-    <row r="65" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="12" t="s">
+    <row r="63" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B64" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C64" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
+      <c r="D64" s="6">
+        <v>1</v>
+      </c>
+      <c r="E64" s="6">
+        <v>1</v>
+      </c>
+      <c r="F64" s="6">
+        <v>1</v>
+      </c>
+      <c r="G64" s="6">
+        <v>1</v>
+      </c>
+      <c r="H64" s="6">
+        <v>1</v>
+      </c>
+      <c r="I64" s="6">
+        <v>1</v>
+      </c>
+      <c r="J64" s="6">
+        <v>1</v>
+      </c>
+      <c r="K64" s="6">
+        <v>1</v>
+      </c>
+      <c r="L64" s="6">
+        <v>1</v>
+      </c>
+      <c r="M64" s="6">
+        <v>1</v>
+      </c>
+      <c r="N64" s="6">
+        <v>1</v>
+      </c>
+      <c r="O64" s="6">
+        <v>1</v>
+      </c>
+      <c r="P64" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="29"/>
+      <c r="B65" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F65" s="4">
+        <v>1</v>
+      </c>
+      <c r="G65" s="4">
+        <v>1</v>
+      </c>
+      <c r="H65" s="4">
+        <v>1</v>
+      </c>
+      <c r="I65" s="4">
+        <v>1</v>
+      </c>
+      <c r="J65" s="4">
+        <v>1</v>
+      </c>
+      <c r="K65" s="4">
+        <v>1</v>
+      </c>
+      <c r="L65" s="4">
+        <v>0</v>
+      </c>
+      <c r="M65" s="4">
+        <v>1</v>
+      </c>
+      <c r="N65" s="4">
+        <v>1</v>
+      </c>
+      <c r="O65" s="4">
+        <v>1</v>
+      </c>
+      <c r="P65" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="29"/>
       <c r="B66" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F66" s="4">
+        <v>1</v>
+      </c>
+      <c r="G66" s="4">
+        <v>1</v>
+      </c>
+      <c r="H66" s="4">
+        <v>1</v>
+      </c>
+      <c r="I66" s="4">
+        <v>1</v>
+      </c>
+      <c r="J66" s="4">
+        <v>1</v>
+      </c>
+      <c r="K66" s="4">
+        <v>1</v>
+      </c>
+      <c r="L66" s="4">
+        <v>0</v>
+      </c>
+      <c r="M66" s="4">
+        <v>1</v>
+      </c>
+      <c r="N66" s="4">
+        <v>1</v>
+      </c>
+      <c r="O66" s="4">
+        <v>1</v>
+      </c>
+      <c r="P66" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q66" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="30"/>
+      <c r="B67" s="5" t="s">
         <v>135</v>
       </c>
+      <c r="C67" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A64:A67"/>
+    <mergeCell ref="A7:A18"/>
+    <mergeCell ref="B60:B62"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="A20:A50"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="A52:A62"/>
+    <mergeCell ref="B52:B55"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="B48:B50"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15BE3A64-1223-4346-9F98-17294D0E7928}">
+  <dimension ref="A1:AF67"/>
+  <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="3" width="16.625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:32" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D5" s="1">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1">
+        <v>3</v>
+      </c>
+      <c r="H5" s="1">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1">
+        <v>3</v>
+      </c>
+      <c r="J5" s="1">
+        <v>3</v>
+      </c>
+      <c r="K5" s="1">
+        <v>3</v>
+      </c>
+      <c r="L5" s="1">
+        <v>3</v>
+      </c>
+      <c r="M5" s="1">
+        <v>3</v>
+      </c>
+      <c r="N5" s="1">
+        <v>3</v>
+      </c>
+      <c r="O5" s="1">
+        <v>3</v>
+      </c>
+      <c r="P5" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>3</v>
+      </c>
+      <c r="R5" s="1">
+        <v>3</v>
+      </c>
+      <c r="S5" s="1">
+        <v>3</v>
+      </c>
+      <c r="T5" s="1">
+        <v>3</v>
+      </c>
+      <c r="U5" s="1">
+        <v>3</v>
+      </c>
+      <c r="V5" s="1">
+        <v>3</v>
+      </c>
+      <c r="W5" s="1">
+        <v>3</v>
+      </c>
+      <c r="X5" s="1">
+        <v>3</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>3</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>3</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>3</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>3</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>3</v>
+      </c>
+      <c r="AF5" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1">
+        <v>2</v>
+      </c>
+      <c r="L6" s="1">
+        <v>2</v>
+      </c>
+      <c r="M6" s="1">
+        <v>2</v>
+      </c>
+      <c r="N6" s="1">
+        <v>2</v>
+      </c>
+      <c r="O6" s="1">
+        <v>2</v>
+      </c>
+      <c r="P6" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>2</v>
+      </c>
+      <c r="R6" s="1">
+        <v>3</v>
+      </c>
+      <c r="S6" s="1">
+        <v>3</v>
+      </c>
+      <c r="T6" s="1">
+        <v>3</v>
+      </c>
+      <c r="U6" s="1">
+        <v>3</v>
+      </c>
+      <c r="V6" s="1">
+        <v>4</v>
+      </c>
+      <c r="W6" s="1">
+        <v>4</v>
+      </c>
+      <c r="X6" s="1">
+        <v>4</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>6</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>6</v>
+      </c>
+      <c r="AF6" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="18"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="18"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="18"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="18"/>
+      <c r="B11" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="18"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="18"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="18"/>
+    </row>
+    <row r="15" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="18"/>
+      <c r="B15" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="18"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="18"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="18"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+    </row>
+    <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="19"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="19"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="19"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="19"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+    </row>
+    <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="19"/>
+      <c r="B25" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="19"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="19"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="19"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="19"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+    </row>
+    <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="19"/>
+      <c r="B30" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="19"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="19"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="19"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="19"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="19"/>
+      <c r="B35" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="19"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="19"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="19"/>
+      <c r="B38" s="37"/>
+      <c r="C38" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="19"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+    </row>
+    <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="19"/>
+      <c r="B40" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="19"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="19"/>
+      <c r="B42" s="37"/>
+      <c r="C42" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="19"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+    </row>
+    <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="19"/>
+      <c r="B44" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="19"/>
+      <c r="B45" s="36"/>
+      <c r="C45" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="19"/>
+      <c r="B46" s="37"/>
+      <c r="C46" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="19"/>
+      <c r="B47" s="15"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+    </row>
+    <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="19"/>
+      <c r="B48" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D48" s="4">
+        <f t="shared" ref="D48:Q48" si="0">D20+D25+D30+D35</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="19"/>
+      <c r="B49" s="36"/>
+      <c r="C49" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D49" s="4">
+        <f t="shared" ref="D49:Q49" si="1">D22+D27+D32+D37+D41</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="19"/>
+      <c r="B50" s="37"/>
+      <c r="C50" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D50" s="4">
+        <f>D48*(1+D49*0.02)</f>
+        <v>0</v>
+      </c>
+      <c r="E50" s="4">
+        <f>E48*(1+E49*0.02)</f>
+        <v>0</v>
+      </c>
+      <c r="F50" s="4">
+        <f t="shared" ref="F50:Q50" si="2">F48*(1+F49*0.02)</f>
+        <v>0</v>
+      </c>
+      <c r="G50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="2"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+    </row>
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="B52" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="20"/>
+      <c r="B53" s="20"/>
+      <c r="C53" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="20"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="20"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="20"/>
+      <c r="B56" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="20"/>
+      <c r="B57" s="20"/>
+      <c r="C57" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="20"/>
+      <c r="B58" s="21"/>
+      <c r="C58" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="20"/>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+    </row>
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="20"/>
+      <c r="B60" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="20"/>
+      <c r="B61" s="20"/>
+      <c r="C61" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="21"/>
+      <c r="B62" s="21"/>
+      <c r="C62" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="29"/>
+      <c r="B65" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="29"/>
+      <c r="B66" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="C66" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C67" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="14"/>
-      <c r="B68" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>138</v>
+    </row>
+    <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="30"/>
+      <c r="B67" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A65:A68"/>
+  <mergeCells count="17">
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A64:A67"/>
     <mergeCell ref="A7:A18"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B7:B10"/>
@@ -3113,225 +5524,119 @@
     <mergeCell ref="A52:A62"/>
     <mergeCell ref="B52:B55"/>
     <mergeCell ref="B60:B62"/>
+    <mergeCell ref="B30:B33"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15BE3A64-1223-4346-9F98-17294D0E7928}">
-  <dimension ref="A1:AF68"/>
-  <sheetFormatPr defaultColWidth="16.58203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.3"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C5AF949-03E5-4E6E-B7CB-0D2F8A5AE350}">
+  <dimension ref="A1:Q67"/>
+  <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="16.58203125" style="2"/>
+    <col min="1" max="3" width="16.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:32" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:32" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="2"/>
     </row>
-    <row r="4" spans="1:32" s="11" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC4" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AD4" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AE4" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AF4" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" s="11" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D5" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M5" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N5" s="1">
-        <v>3</v>
-      </c>
-      <c r="O5" s="1">
-        <v>3</v>
-      </c>
-      <c r="P5" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>3</v>
-      </c>
-      <c r="R5" s="1">
-        <v>3</v>
-      </c>
-      <c r="S5" s="1">
-        <v>3</v>
-      </c>
-      <c r="T5" s="1">
-        <v>3</v>
-      </c>
-      <c r="U5" s="1">
-        <v>3</v>
-      </c>
-      <c r="V5" s="1">
-        <v>3</v>
-      </c>
-      <c r="W5" s="1">
-        <v>3</v>
-      </c>
-      <c r="X5" s="1">
-        <v>3</v>
-      </c>
-      <c r="Y5" s="1">
-        <v>3</v>
-      </c>
-      <c r="Z5" s="1">
-        <v>3</v>
-      </c>
-      <c r="AA5" s="1">
-        <v>3</v>
-      </c>
-      <c r="AB5" s="1">
-        <v>3</v>
-      </c>
-      <c r="AC5" s="1">
-        <v>3</v>
-      </c>
-      <c r="AD5" s="1">
-        <v>3</v>
-      </c>
-      <c r="AE5" s="1">
-        <v>3</v>
-      </c>
-      <c r="AF5" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" s="11" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -3340,124 +5645,70 @@
         <v>1</v>
       </c>
       <c r="F6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K6" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L6" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M6" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N6" s="1">
-        <v>2</v>
-      </c>
-      <c r="O6" s="1">
-        <v>2</v>
-      </c>
-      <c r="P6" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>2</v>
-      </c>
-      <c r="R6" s="1">
-        <v>3</v>
-      </c>
-      <c r="S6" s="1">
-        <v>3</v>
-      </c>
-      <c r="T6" s="1">
-        <v>3</v>
-      </c>
-      <c r="U6" s="1">
-        <v>3</v>
-      </c>
-      <c r="V6" s="1">
-        <v>4</v>
-      </c>
-      <c r="W6" s="1">
-        <v>4</v>
-      </c>
-      <c r="X6" s="1">
-        <v>4</v>
-      </c>
-      <c r="Y6" s="1">
         <v>5</v>
       </c>
-      <c r="Z6" s="1">
-        <v>5</v>
-      </c>
-      <c r="AA6" s="1">
-        <v>5</v>
-      </c>
-      <c r="AB6" s="1">
-        <v>5</v>
-      </c>
-      <c r="AC6" s="1">
-        <v>5</v>
-      </c>
-      <c r="AD6" s="1">
-        <v>6</v>
-      </c>
-      <c r="AE6" s="1">
-        <v>6</v>
-      </c>
-      <c r="AF6" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="B7" s="20" t="s">
+    </row>
+    <row r="7" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="22"/>
-      <c r="B8" s="20"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="18"/>
+      <c r="B8" s="16"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="3">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
-      <c r="B9" s="20"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="18"/>
+      <c r="B9" s="16"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="22"/>
-      <c r="B10" s="20"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="18"/>
+      <c r="B10" s="16"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -3465,491 +5716,614 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:32" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="22"/>
-      <c r="B11" s="20" t="s">
+    <row r="11" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="18"/>
+      <c r="B11" s="16" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
-      <c r="B12" s="20"/>
+    </row>
+    <row r="12" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="18"/>
+      <c r="B12" s="16"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:32" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="22"/>
-      <c r="B13" s="20"/>
+    <row r="13" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="18"/>
+      <c r="B13" s="16"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:32" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="22"/>
-    </row>
-    <row r="15" spans="1:32" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
-      <c r="B15" s="26" t="s">
+    <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="18"/>
+    </row>
+    <row r="15" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="18"/>
+      <c r="B15" s="22" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="22"/>
-      <c r="B16" s="27"/>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="18"/>
+      <c r="B16" s="23"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="22"/>
-      <c r="B17" s="27"/>
+      <c r="D16" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="18"/>
+      <c r="B17" s="23"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="22"/>
-      <c r="B18" s="28"/>
+      <c r="D17" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="18"/>
+      <c r="B18" s="24"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
     </row>
-    <row r="20" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="B20" s="23" t="s">
+    <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B20" s="34" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="19"/>
-      <c r="B21" s="23"/>
+      <c r="B21" s="34"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="19"/>
-      <c r="B22" s="23"/>
+      <c r="B22" s="34"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="19"/>
-      <c r="B23" s="23"/>
+      <c r="B23" s="34"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="19"/>
-      <c r="B24" s="10"/>
+      <c r="B24" s="12"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
-    <row r="25" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="19"/>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="34" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="19"/>
-      <c r="B26" s="23"/>
+      <c r="B26" s="34"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="19"/>
-      <c r="B27" s="23"/>
+      <c r="B27" s="34"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="19"/>
-      <c r="B28" s="23"/>
+      <c r="B28" s="34"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="19"/>
-      <c r="B29" s="9"/>
+      <c r="B29" s="13"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
-    <row r="30" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="19"/>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="19"/>
+      <c r="B31" s="36"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="19"/>
+      <c r="B32" s="36"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="19"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="19"/>
-      <c r="B34" s="1"/>
+      <c r="B34" s="14"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="19"/>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="35" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="19"/>
+      <c r="B36" s="36"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="19"/>
+      <c r="B37" s="36"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D37" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="19"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="19"/>
-      <c r="B39" s="1"/>
+      <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="19"/>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="35" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="19"/>
+      <c r="B41" s="36"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D41" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="19"/>
+      <c r="B42" s="37"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="19"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
     </row>
-    <row r="44" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="19"/>
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C44" s="4">
         <v>1</v>
       </c>
-      <c r="D44" s="4">
-        <f>D20+D25+D30+D35</f>
-        <v>11</v>
-      </c>
-      <c r="E44" s="4">
-        <f>E20+E25+E30+E35</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="19"/>
-      <c r="B45" s="16"/>
+      <c r="B45" s="36"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
-      <c r="D45" s="4">
-        <f>D22+D27+D32+D37+D41</f>
-        <v>5</v>
-      </c>
-      <c r="E45" s="4">
-        <f>E22+E27+E32+E37+E41</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="19"/>
-      <c r="B46" s="17"/>
+      <c r="B46" s="37"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
-      <c r="D46" s="4">
-        <f>D44*(1+D45*0.02)</f>
-        <v>12.100000000000001</v>
-      </c>
-      <c r="E46" s="4">
-        <f>E44*(1+E45*0.02)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="19"/>
-      <c r="B47" s="7"/>
+      <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
-    <row r="48" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="19"/>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="35" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D48" s="4">
+        <f t="shared" ref="D48:Q48" si="0">D20+D25+D30+D35</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="19"/>
-      <c r="B49" s="4"/>
+      <c r="B49" s="36"/>
       <c r="C49" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+      <c r="D49" s="4">
+        <f t="shared" ref="D49:Q49" si="1">D22+D27+D32+D37+D41</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="19"/>
-      <c r="B50" s="4"/>
+      <c r="B50" s="37"/>
       <c r="C50" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+      <c r="D50" s="4">
+        <f>D48*(1+D49*0.02)</f>
+        <v>0</v>
+      </c>
+      <c r="E50" s="4">
+        <f>E48*(1+E49*0.02)</f>
+        <v>0</v>
+      </c>
+      <c r="F50" s="4">
+        <f t="shared" ref="F50:Q50" si="2">F48*(1+F49*0.02)</f>
+        <v>0</v>
+      </c>
+      <c r="G50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
     </row>
-    <row r="52" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="B52" s="21" t="s">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="B52" s="33" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="21"/>
-      <c r="B53" s="21"/>
+    </row>
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="20"/>
+      <c r="B53" s="20"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="21"/>
-      <c r="B54" s="21"/>
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="20"/>
+      <c r="B54" s="20"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="21"/>
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="20"/>
       <c r="B55" s="21"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-    </row>
-    <row r="56" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="21"/>
-      <c r="B56" s="21" t="s">
+    </row>
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="20"/>
+      <c r="B56" s="33" t="s">
         <v>30</v>
       </c>
       <c r="C56" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="21"/>
-      <c r="B57" s="24"/>
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="20"/>
+      <c r="B57" s="20"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="21"/>
-      <c r="B58" s="25"/>
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="20"/>
+      <c r="B58" s="21"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="21"/>
+    <row r="59" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="20"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
-    </row>
-    <row r="60" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="21"/>
-      <c r="B60" s="21" t="s">
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+    </row>
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="20"/>
+      <c r="B60" s="33" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-    </row>
-    <row r="61" spans="1:5" s="6" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="21"/>
-      <c r="B61" s="24"/>
+    </row>
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="20"/>
+      <c r="B61" s="20"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="21"/>
-      <c r="B62" s="25"/>
+      <c r="B62" s="21"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-    </row>
-    <row r="64" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-    </row>
-    <row r="65" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="12" t="s">
+    <row r="63" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B64" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C64" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
+    <row r="65" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="29"/>
+      <c r="B65" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="29"/>
       <c r="B66" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="30"/>
+      <c r="B67" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C66" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="4" t="s">
+      <c r="C67" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C67" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="14"/>
-      <c r="B68" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>138</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A65:A68"/>
+  <mergeCells count="17">
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A64:A67"/>
     <mergeCell ref="A7:A18"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B7:B10"/>
@@ -3962,117 +6336,193 @@
     <mergeCell ref="A52:A62"/>
     <mergeCell ref="B52:B55"/>
     <mergeCell ref="B60:B62"/>
+    <mergeCell ref="B30:B33"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C5AF949-03E5-4E6E-B7CB-0D2F8A5AE350}">
-  <dimension ref="A1:N68"/>
-  <sheetFormatPr defaultColWidth="16.58203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.3"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB9C480B-7650-4DE9-B7AF-42C282E029C5}">
+  <dimension ref="A1:AB67"/>
+  <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="16.58203125" style="2"/>
+    <col min="1" max="3" width="16.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="2"/>
     </row>
-    <row r="4" spans="1:14" s="11" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" s="11" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AB4" s="1"/>
+    </row>
+    <row r="5" spans="1:28" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D5" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K5" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L5" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M5" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N5" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" s="11" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="O5" s="1">
+        <v>5</v>
+      </c>
+      <c r="P5" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>5</v>
+      </c>
+      <c r="R5" s="1">
+        <v>5</v>
+      </c>
+      <c r="S5" s="1">
+        <v>5</v>
+      </c>
+      <c r="T5" s="1">
+        <v>5</v>
+      </c>
+      <c r="U5" s="1">
+        <v>5</v>
+      </c>
+      <c r="V5" s="1">
+        <v>5</v>
+      </c>
+      <c r="W5" s="1">
+        <v>5</v>
+      </c>
+      <c r="X5" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>5</v>
+      </c>
+      <c r="AB5" s="1"/>
+    </row>
+    <row r="6" spans="1:28" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -4081,70 +6531,107 @@
         <v>1</v>
       </c>
       <c r="F6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6" s="1">
+        <v>2</v>
+      </c>
+      <c r="K6" s="1">
+        <v>2</v>
+      </c>
+      <c r="L6" s="1">
+        <v>2</v>
+      </c>
+      <c r="M6" s="1">
+        <v>3</v>
+      </c>
+      <c r="N6" s="1">
+        <v>3</v>
+      </c>
+      <c r="O6" s="1">
+        <v>3</v>
+      </c>
+      <c r="P6" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>3</v>
+      </c>
+      <c r="R6" s="1">
         <v>4</v>
       </c>
-      <c r="K6" s="1">
-        <v>4</v>
-      </c>
-      <c r="L6" s="1">
+      <c r="S6" s="1">
         <v>5</v>
       </c>
-      <c r="M6" s="1">
+      <c r="T6" s="1">
         <v>5</v>
       </c>
-      <c r="N6" s="1">
+      <c r="U6" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="B7" s="20" t="s">
+      <c r="V6" s="1">
+        <v>5</v>
+      </c>
+      <c r="W6" s="1">
+        <v>6</v>
+      </c>
+      <c r="X6" s="1">
+        <v>6</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>6</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>6</v>
+      </c>
+      <c r="AB6" s="1"/>
+    </row>
+    <row r="7" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="22"/>
-      <c r="B8" s="20"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="18"/>
+      <c r="B8" s="16"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="3">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
-      <c r="B9" s="20"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="18"/>
+      <c r="B9" s="16"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="22"/>
-      <c r="B10" s="20"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="18"/>
+      <c r="B10" s="16"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -4152,491 +6639,614 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:14" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="22"/>
-      <c r="B11" s="20" t="s">
+    <row r="11" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="18"/>
+      <c r="B11" s="16" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
-      <c r="B12" s="20"/>
+    </row>
+    <row r="12" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="18"/>
+      <c r="B12" s="16"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:14" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="22"/>
-      <c r="B13" s="20"/>
+    <row r="13" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="18"/>
+      <c r="B13" s="16"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:14" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="22"/>
-    </row>
-    <row r="15" spans="1:14" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
-      <c r="B15" s="26" t="s">
+    <row r="14" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="18"/>
+    </row>
+    <row r="15" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="18"/>
+      <c r="B15" s="22" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="22"/>
-      <c r="B16" s="27"/>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="18"/>
+      <c r="B16" s="23"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="22"/>
-      <c r="B17" s="27"/>
+      <c r="D16" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="18"/>
+      <c r="B17" s="23"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="22"/>
-      <c r="B18" s="28"/>
+      <c r="D17" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="18"/>
+      <c r="B18" s="24"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
     </row>
-    <row r="20" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="B20" s="23" t="s">
+    <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B20" s="34" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="19"/>
-      <c r="B21" s="23"/>
+      <c r="B21" s="34"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="19"/>
-      <c r="B22" s="23"/>
+      <c r="B22" s="34"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="19"/>
-      <c r="B23" s="23"/>
+      <c r="B23" s="34"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="19"/>
-      <c r="B24" s="10"/>
+      <c r="B24" s="12"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
-    <row r="25" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="19"/>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="34" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="19"/>
-      <c r="B26" s="23"/>
+      <c r="B26" s="34"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="19"/>
-      <c r="B27" s="23"/>
+      <c r="B27" s="34"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="19"/>
-      <c r="B28" s="23"/>
+      <c r="B28" s="34"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="19"/>
-      <c r="B29" s="9"/>
+      <c r="B29" s="13"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
-    <row r="30" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="19"/>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="19"/>
+      <c r="B31" s="36"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="19"/>
+      <c r="B32" s="36"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="19"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="19"/>
-      <c r="B34" s="1"/>
+      <c r="B34" s="14"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="19"/>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="35" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="19"/>
+      <c r="B36" s="36"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="19"/>
+      <c r="B37" s="36"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D37" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="19"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="19"/>
-      <c r="B39" s="1"/>
+      <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="19"/>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="35" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="19"/>
+      <c r="B41" s="36"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D41" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="19"/>
+      <c r="B42" s="37"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="19"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
     </row>
-    <row r="44" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="19"/>
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C44" s="4">
         <v>1</v>
       </c>
-      <c r="D44" s="4">
-        <f>D20+D25+D30+D35</f>
-        <v>11</v>
-      </c>
-      <c r="E44" s="4">
-        <f>E20+E25+E30+E35</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="19"/>
-      <c r="B45" s="16"/>
+      <c r="B45" s="36"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
-      <c r="D45" s="4">
-        <f>D22+D27+D32+D37+D41</f>
-        <v>5</v>
-      </c>
-      <c r="E45" s="4">
-        <f>E22+E27+E32+E37+E41</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="19"/>
-      <c r="B46" s="17"/>
+      <c r="B46" s="37"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
-      <c r="D46" s="4">
-        <f>D44*(1+D45*0.02)</f>
-        <v>12.100000000000001</v>
-      </c>
-      <c r="E46" s="4">
-        <f>E44*(1+E45*0.02)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="19"/>
-      <c r="B47" s="7"/>
+      <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
-    <row r="48" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="19"/>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="35" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D48" s="4">
+        <f t="shared" ref="D48:Q48" si="0">D20+D25+D30+D35</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="19"/>
-      <c r="B49" s="4"/>
+      <c r="B49" s="36"/>
       <c r="C49" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+      <c r="D49" s="4">
+        <f t="shared" ref="D49:Q49" si="1">D22+D27+D32+D37+D41</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="19"/>
-      <c r="B50" s="4"/>
+      <c r="B50" s="37"/>
       <c r="C50" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+      <c r="D50" s="4">
+        <f>D48*(1+D49*0.02)</f>
+        <v>0</v>
+      </c>
+      <c r="E50" s="4">
+        <f>E48*(1+E49*0.02)</f>
+        <v>0</v>
+      </c>
+      <c r="F50" s="4">
+        <f t="shared" ref="F50:Q50" si="2">F48*(1+F49*0.02)</f>
+        <v>0</v>
+      </c>
+      <c r="G50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
     </row>
-    <row r="52" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="B52" s="21" t="s">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="B52" s="33" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="21"/>
-      <c r="B53" s="21"/>
+    </row>
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="20"/>
+      <c r="B53" s="20"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="21"/>
-      <c r="B54" s="21"/>
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="20"/>
+      <c r="B54" s="20"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="21"/>
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="20"/>
       <c r="B55" s="21"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-    </row>
-    <row r="56" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="21"/>
-      <c r="B56" s="21" t="s">
+    </row>
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="20"/>
+      <c r="B56" s="33" t="s">
         <v>30</v>
       </c>
       <c r="C56" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="21"/>
-      <c r="B57" s="24"/>
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="20"/>
+      <c r="B57" s="20"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="21"/>
-      <c r="B58" s="25"/>
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="20"/>
+      <c r="B58" s="21"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="21"/>
+    <row r="59" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="20"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
-    </row>
-    <row r="60" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="21"/>
-      <c r="B60" s="21" t="s">
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+    </row>
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="20"/>
+      <c r="B60" s="33" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-    </row>
-    <row r="61" spans="1:5" s="6" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="21"/>
-      <c r="B61" s="24"/>
+    </row>
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="20"/>
+      <c r="B61" s="20"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="21"/>
-      <c r="B62" s="25"/>
+      <c r="B62" s="21"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-    </row>
-    <row r="64" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-    </row>
-    <row r="65" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="12" t="s">
+    <row r="63" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B64" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C64" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
+    <row r="65" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="29"/>
+      <c r="B65" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="29"/>
       <c r="B66" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="30"/>
+      <c r="B67" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C66" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="4" t="s">
+      <c r="C67" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C67" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="14"/>
-      <c r="B68" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>138</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A65:A68"/>
+  <mergeCells count="17">
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A64:A67"/>
     <mergeCell ref="A7:A18"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B7:B10"/>
@@ -4649,191 +7259,95 @@
     <mergeCell ref="A52:A62"/>
     <mergeCell ref="B52:B55"/>
     <mergeCell ref="B60:B62"/>
+    <mergeCell ref="B30:B33"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB9C480B-7650-4DE9-B7AF-42C282E029C5}">
-  <dimension ref="A1:AB68"/>
-  <sheetFormatPr defaultColWidth="16.58203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.3"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21A46B60-4F3A-4D99-AC29-6361CD3DE12A}">
+  <dimension ref="A1:Q67"/>
+  <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="16.58203125" style="2"/>
+    <col min="1" max="3" width="16.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="2"/>
     </row>
-    <row r="4" spans="1:28" s="11" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AB4" s="1"/>
-    </row>
-    <row r="5" spans="1:28" s="11" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D5" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J5" s="1">
-        <v>5</v>
-      </c>
-      <c r="K5" s="1">
-        <v>5</v>
-      </c>
-      <c r="L5" s="1">
-        <v>5</v>
-      </c>
-      <c r="M5" s="1">
-        <v>5</v>
-      </c>
-      <c r="N5" s="1">
-        <v>5</v>
-      </c>
-      <c r="O5" s="1">
-        <v>5</v>
-      </c>
-      <c r="P5" s="1">
-        <v>5</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>5</v>
-      </c>
-      <c r="R5" s="1">
-        <v>5</v>
-      </c>
-      <c r="S5" s="1">
-        <v>5</v>
-      </c>
-      <c r="T5" s="1">
-        <v>5</v>
-      </c>
-      <c r="U5" s="1">
-        <v>5</v>
-      </c>
-      <c r="V5" s="1">
-        <v>5</v>
-      </c>
-      <c r="W5" s="1">
-        <v>5</v>
-      </c>
-      <c r="X5" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y5" s="1">
-        <v>5</v>
-      </c>
-      <c r="Z5" s="1">
-        <v>5</v>
-      </c>
-      <c r="AB5" s="1"/>
-    </row>
-    <row r="6" spans="1:28" s="11" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -4842,13 +7356,13 @@
         <v>1</v>
       </c>
       <c r="F6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" s="1">
         <v>1</v>
@@ -4856,93 +7370,44 @@
       <c r="J6" s="1">
         <v>2</v>
       </c>
-      <c r="K6" s="1">
-        <v>2</v>
-      </c>
-      <c r="L6" s="1">
-        <v>2</v>
-      </c>
-      <c r="M6" s="1">
-        <v>3</v>
-      </c>
-      <c r="N6" s="1">
-        <v>3</v>
-      </c>
-      <c r="O6" s="1">
-        <v>3</v>
-      </c>
-      <c r="P6" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>3</v>
-      </c>
-      <c r="R6" s="1">
-        <v>4</v>
-      </c>
-      <c r="S6" s="1">
-        <v>5</v>
-      </c>
-      <c r="T6" s="1">
-        <v>5</v>
-      </c>
-      <c r="U6" s="1">
-        <v>5</v>
-      </c>
-      <c r="V6" s="1">
-        <v>5</v>
-      </c>
-      <c r="W6" s="1">
-        <v>6</v>
-      </c>
-      <c r="X6" s="1">
-        <v>6</v>
-      </c>
-      <c r="Y6" s="1">
-        <v>6</v>
-      </c>
-      <c r="Z6" s="1">
-        <v>6</v>
-      </c>
-      <c r="AB6" s="1"/>
-    </row>
-    <row r="7" spans="1:28" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="B7" s="20" t="s">
+    </row>
+    <row r="7" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="22"/>
-      <c r="B8" s="20"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="18"/>
+      <c r="B8" s="16"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="3">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
-      <c r="B9" s="20"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="18"/>
+      <c r="B9" s="16"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="22"/>
-      <c r="B10" s="20"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="18"/>
+      <c r="B10" s="16"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -4950,491 +7415,614 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:28" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="22"/>
-      <c r="B11" s="20" t="s">
+    <row r="11" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="18"/>
+      <c r="B11" s="16" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
-      <c r="B12" s="20"/>
+    </row>
+    <row r="12" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="18"/>
+      <c r="B12" s="16"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:28" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="22"/>
-      <c r="B13" s="20"/>
+    <row r="13" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="18"/>
+      <c r="B13" s="16"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:28" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="22"/>
-    </row>
-    <row r="15" spans="1:28" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
-      <c r="B15" s="26" t="s">
+    <row r="14" spans="1:10" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="18"/>
+    </row>
+    <row r="15" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="18"/>
+      <c r="B15" s="22" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="22"/>
-      <c r="B16" s="27"/>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="18"/>
+      <c r="B16" s="23"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="22"/>
-      <c r="B17" s="27"/>
+      <c r="D16" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="18"/>
+      <c r="B17" s="23"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="22"/>
-      <c r="B18" s="28"/>
+      <c r="D17" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="18"/>
+      <c r="B18" s="24"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
     </row>
-    <row r="20" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="B20" s="23" t="s">
+    <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B20" s="34" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="19"/>
-      <c r="B21" s="23"/>
+      <c r="B21" s="34"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="19"/>
-      <c r="B22" s="23"/>
+      <c r="B22" s="34"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="19"/>
-      <c r="B23" s="23"/>
+      <c r="B23" s="34"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="19"/>
-      <c r="B24" s="10"/>
+      <c r="B24" s="12"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
-    <row r="25" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="19"/>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="34" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="19"/>
-      <c r="B26" s="23"/>
+      <c r="B26" s="34"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="19"/>
-      <c r="B27" s="23"/>
+      <c r="B27" s="34"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="19"/>
-      <c r="B28" s="23"/>
+      <c r="B28" s="34"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="19"/>
-      <c r="B29" s="9"/>
+      <c r="B29" s="13"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
-    <row r="30" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="19"/>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="19"/>
+      <c r="B31" s="36"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="19"/>
+      <c r="B32" s="36"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="19"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="19"/>
-      <c r="B34" s="1"/>
+      <c r="B34" s="14"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="19"/>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="35" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="19"/>
+      <c r="B36" s="36"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="19"/>
+      <c r="B37" s="36"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D37" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="19"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="19"/>
-      <c r="B39" s="1"/>
+      <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="19"/>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="35" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="19"/>
+      <c r="B41" s="36"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D41" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="19"/>
+      <c r="B42" s="37"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="19"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
     </row>
-    <row r="44" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="19"/>
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C44" s="4">
         <v>1</v>
       </c>
-      <c r="D44" s="4">
-        <f>D20+D25+D30+D35</f>
-        <v>11</v>
-      </c>
-      <c r="E44" s="4">
-        <f>E20+E25+E30+E35</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="19"/>
-      <c r="B45" s="16"/>
+      <c r="B45" s="36"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
-      <c r="D45" s="4">
-        <f>D22+D27+D32+D37+D41</f>
-        <v>5</v>
-      </c>
-      <c r="E45" s="4">
-        <f>E22+E27+E32+E37+E41</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="19"/>
-      <c r="B46" s="17"/>
+      <c r="B46" s="37"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
-      <c r="D46" s="4">
-        <f>D44*(1+D45*0.02)</f>
-        <v>12.100000000000001</v>
-      </c>
-      <c r="E46" s="4">
-        <f>E44*(1+E45*0.02)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="19"/>
-      <c r="B47" s="7"/>
+      <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
-    <row r="48" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="19"/>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="35" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D48" s="4">
+        <f t="shared" ref="D48:Q48" si="0">D20+D25+D30+D35</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="19"/>
-      <c r="B49" s="4"/>
+      <c r="B49" s="36"/>
       <c r="C49" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+      <c r="D49" s="4">
+        <f t="shared" ref="D49:Q49" si="1">D22+D27+D32+D37+D41</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="19"/>
-      <c r="B50" s="4"/>
+      <c r="B50" s="37"/>
       <c r="C50" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+      <c r="D50" s="4">
+        <f>D48*(1+D49*0.02)</f>
+        <v>0</v>
+      </c>
+      <c r="E50" s="4">
+        <f>E48*(1+E49*0.02)</f>
+        <v>0</v>
+      </c>
+      <c r="F50" s="4">
+        <f t="shared" ref="F50:Q50" si="2">F48*(1+F49*0.02)</f>
+        <v>0</v>
+      </c>
+      <c r="G50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
     </row>
-    <row r="52" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="B52" s="21" t="s">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="B52" s="33" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="21"/>
-      <c r="B53" s="21"/>
+    </row>
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="20"/>
+      <c r="B53" s="20"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="21"/>
-      <c r="B54" s="21"/>
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="20"/>
+      <c r="B54" s="20"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="21"/>
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="20"/>
       <c r="B55" s="21"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-    </row>
-    <row r="56" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="21"/>
-      <c r="B56" s="21" t="s">
+    </row>
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="20"/>
+      <c r="B56" s="33" t="s">
         <v>30</v>
       </c>
       <c r="C56" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="21"/>
-      <c r="B57" s="24"/>
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="20"/>
+      <c r="B57" s="20"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="21"/>
-      <c r="B58" s="25"/>
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="20"/>
+      <c r="B58" s="21"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="21"/>
+    <row r="59" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="20"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
-    </row>
-    <row r="60" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="21"/>
-      <c r="B60" s="21" t="s">
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+    </row>
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="20"/>
+      <c r="B60" s="33" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-    </row>
-    <row r="61" spans="1:5" s="6" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="21"/>
-      <c r="B61" s="24"/>
+    </row>
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="20"/>
+      <c r="B61" s="20"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="21"/>
-      <c r="B62" s="25"/>
+      <c r="B62" s="21"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-    </row>
-    <row r="64" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-    </row>
-    <row r="65" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="12" t="s">
+    <row r="63" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B64" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C64" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
+    <row r="65" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="29"/>
+      <c r="B65" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="29"/>
       <c r="B66" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="30"/>
+      <c r="B67" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C66" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="4" t="s">
+      <c r="C67" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C67" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="14"/>
-      <c r="B68" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>138</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A65:A68"/>
+  <mergeCells count="17">
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A64:A67"/>
     <mergeCell ref="A7:A18"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B7:B10"/>
@@ -5447,659 +8035,10 @@
     <mergeCell ref="A52:A62"/>
     <mergeCell ref="B52:B55"/>
     <mergeCell ref="B60:B62"/>
+    <mergeCell ref="B30:B33"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21A46B60-4F3A-4D99-AC29-6361CD3DE12A}">
-  <dimension ref="A1:J68"/>
-  <sheetFormatPr defaultColWidth="16.58203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="3" width="16.58203125" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-    </row>
-    <row r="2" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" s="11" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="11" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D5" s="1">
-        <v>6</v>
-      </c>
-      <c r="E5" s="1">
-        <v>6</v>
-      </c>
-      <c r="F5" s="1">
-        <v>6</v>
-      </c>
-      <c r="G5" s="1">
-        <v>6</v>
-      </c>
-      <c r="H5" s="1">
-        <v>6</v>
-      </c>
-      <c r="I5" s="1">
-        <v>7</v>
-      </c>
-      <c r="J5" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="11" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <v>2</v>
-      </c>
-      <c r="G6" s="1">
-        <v>2</v>
-      </c>
-      <c r="H6" s="1">
-        <v>3</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1</v>
-      </c>
-      <c r="J6" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="22"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="3">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="22"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="22"/>
-      <c r="B11" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="3">
-        <v>1</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="22"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="22"/>
-    </row>
-    <row r="15" spans="1:10" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
-      <c r="B15" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="22"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="22"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="22"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-    </row>
-    <row r="20" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="19"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="19"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="19"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="19"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-    </row>
-    <row r="25" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="19"/>
-      <c r="B25" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="19"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="19"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="19"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="19"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-    </row>
-    <row r="30" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="19"/>
-      <c r="B30" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="19"/>
-      <c r="C31" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="19"/>
-      <c r="C32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D32" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="19"/>
-      <c r="C33" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="19"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="19"/>
-      <c r="B35" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="19"/>
-      <c r="C36" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="19"/>
-      <c r="C37" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D37" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="19"/>
-      <c r="C38" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="19"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-    </row>
-    <row r="40" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="19"/>
-      <c r="B40" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="19"/>
-      <c r="C41" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D41" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="19"/>
-      <c r="C42" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="19"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-    </row>
-    <row r="44" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="19"/>
-      <c r="B44" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C44" s="4">
-        <v>1</v>
-      </c>
-      <c r="D44" s="4">
-        <f>D20+D25+D30+D35</f>
-        <v>11</v>
-      </c>
-      <c r="E44" s="4">
-        <f>E20+E25+E30+E35</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="19"/>
-      <c r="B45" s="16"/>
-      <c r="C45" s="4">
-        <v>2</v>
-      </c>
-      <c r="D45" s="4">
-        <f>D22+D27+D32+D37+D41</f>
-        <v>5</v>
-      </c>
-      <c r="E45" s="4">
-        <f>E22+E27+E32+E37+E41</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="19"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="4">
-        <v>3</v>
-      </c>
-      <c r="D46" s="4">
-        <f>D44*(1+D45*0.02)</f>
-        <v>12.100000000000001</v>
-      </c>
-      <c r="E46" s="4">
-        <f>E44*(1+E45*0.02)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="19"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-    </row>
-    <row r="48" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="19"/>
-      <c r="B48" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="19"/>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="19"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="2"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-    </row>
-    <row r="52" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="B52" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="21"/>
-      <c r="B53" s="21"/>
-      <c r="C53" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="21"/>
-      <c r="B54" s="21"/>
-      <c r="C54" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="21"/>
-      <c r="B55" s="21"/>
-      <c r="C55" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-    </row>
-    <row r="56" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="21"/>
-      <c r="B56" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="C56" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="21"/>
-      <c r="B57" s="24"/>
-      <c r="C57" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="21"/>
-      <c r="B58" s="25"/>
-      <c r="C58" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="21"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-    </row>
-    <row r="60" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="21"/>
-      <c r="B60" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-    </row>
-    <row r="61" spans="1:5" s="6" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="21"/>
-      <c r="B61" s="24"/>
-      <c r="C61" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="21"/>
-      <c r="B62" s="25"/>
-      <c r="C62" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" s="4" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-    </row>
-    <row r="64" spans="1:5" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-    </row>
-    <row r="65" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
-      <c r="B66" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="14"/>
-      <c r="B68" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>138</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A65:A68"/>
-    <mergeCell ref="A7:A18"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="A20:A50"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="A52:A62"/>
-    <mergeCell ref="B52:B55"/>
-    <mergeCell ref="B60:B62"/>
-  </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/dev_stuffs/3匠魂.xlsx
+++ b/dev_stuffs/3匠魂.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\Palmon\dev_stuffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0523A407-1592-4B98-9E7E-A90FFB3AFDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CFBC585-03CD-42C1-A412-2C6A19A2C44B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7860" yWindow="4515" windowWidth="23940" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13035" yWindow="5265" windowWidth="23940" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="阶段1" sheetId="1" r:id="rId1"/>
     <sheet name="阶段2" sheetId="2" r:id="rId2"/>
     <sheet name="阶段3" sheetId="8" r:id="rId3"/>
-    <sheet name="阶段4" sheetId="9" r:id="rId4"/>
-    <sheet name="阶段5" sheetId="10" r:id="rId5"/>
-    <sheet name="阶段EX" sheetId="11" r:id="rId6"/>
+    <sheet name="阶段3追加" sheetId="12" r:id="rId4"/>
+    <sheet name="阶段4" sheetId="9" r:id="rId5"/>
+    <sheet name="阶段5" sheetId="10" r:id="rId6"/>
+    <sheet name="阶段EX" sheetId="11" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="171">
   <si>
     <t>材料名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -222,9 +223,6 @@
     <t>Beta框架</t>
   </si>
   <si>
-    <t>合金巨兽锭</t>
-  </si>
-  <si>
     <t>泰拉*</t>
   </si>
   <si>
@@ -493,6 +491,111 @@
   <si>
     <t>下界合金</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>'kubejs:virtual_gold_ingot'</t>
+  </si>
+  <si>
+    <t>'kubejs:alpha_framework'</t>
+  </si>
+  <si>
+    <t>'#forge:ingots/iesnium'</t>
+  </si>
+  <si>
+    <t>'#forge:ingots/hop_graphite'</t>
+  </si>
+  <si>
+    <t>'cataclysm:black_steel_nugget'</t>
+  </si>
+  <si>
+    <t>'occultism:iesnium_nugget'</t>
+  </si>
+  <si>
+    <t>'tfc:powder/graphite'</t>
+  </si>
+  <si>
+    <t>leftover</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>#forge:ingots/black_steel'</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>精炼钢</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>精炼M钢</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚合物</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>'tinkers_things:hematite_block'</t>
+  </si>
+  <si>
+    <t>'tinkers_things:hematite'</t>
+  </si>
+  <si>
+    <t>'#forge:ingots/dawnstone'</t>
+  </si>
+  <si>
+    <t>'#forge:gems/fluix'</t>
+  </si>
+  <si>
+    <t>null</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>'tinkers_advanced:blaze_netherite'</t>
+  </si>
+  <si>
+    <t>'#forge:ingots/manyullyn'</t>
+  </si>
+  <si>
+    <t>'kubejs:beta_framework'</t>
+  </si>
+  <si>
+    <t>'kubejs:ancient_netherite'</t>
+  </si>
+  <si>
+    <t>远古下界合金</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>'#forge:ingots/terrasteel'</t>
+  </si>
+  <si>
+    <t>'malum:blazing_quartz'</t>
+  </si>
+  <si>
+    <t>'malum:blazing_quartz_fragment'</t>
+  </si>
+  <si>
+    <t>embers:ember_crystal'</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>'embers:ember_shard'</t>
+  </si>
+  <si>
+    <t>'#botania:livingwood_logs'</t>
+  </si>
+  <si>
+    <t>'botania:livingrock'</t>
+  </si>
+  <si>
+    <t>'#forge:ingots/manasteel'</t>
+  </si>
+  <si>
+    <t>'#forge:gems/certus_quartz'</t>
   </si>
 </sst>
 </file>
@@ -691,7 +794,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -736,6 +839,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -763,36 +893,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -800,6 +900,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1086,7 +1192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:M68"/>
+  <dimension ref="A2:M70"/>
   <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="16.625" style="2"/>
@@ -1151,1483 +1257,1535 @@
     </row>
     <row r="5" spans="1:13" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1">
-        <v>1</v>
-      </c>
-      <c r="L5" s="1">
-        <v>1</v>
-      </c>
-      <c r="M5" s="1">
-        <v>1</v>
+        <v>139</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C8" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>2</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1">
-        <v>2</v>
-      </c>
-      <c r="I6" s="1">
-        <v>2</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="L6" s="1">
-        <v>3</v>
-      </c>
-      <c r="M6" s="1">
+      <c r="K8" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="L8" s="1">
+        <v>3</v>
+      </c>
+      <c r="M8" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="18" t="s">
+    <row r="9" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="3">
+        <v>10</v>
+      </c>
+      <c r="E9" s="3">
+        <v>13</v>
+      </c>
+      <c r="F9" s="3">
+        <v>11</v>
+      </c>
+      <c r="G9" s="3">
+        <v>9</v>
+      </c>
+      <c r="H9" s="3">
+        <v>17</v>
+      </c>
+      <c r="I9" s="3">
+        <v>15</v>
+      </c>
+      <c r="J9" s="3">
+        <v>18</v>
+      </c>
+      <c r="K9" s="3">
+        <v>18</v>
+      </c>
+      <c r="L9" s="3">
+        <v>22</v>
+      </c>
+      <c r="M9" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="27"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="3">
+        <v>600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>650</v>
+      </c>
+      <c r="F10" s="3">
+        <v>550</v>
+      </c>
+      <c r="G10" s="3">
+        <v>450</v>
+      </c>
+      <c r="H10" s="3">
+        <v>750</v>
+      </c>
+      <c r="I10" s="3">
+        <v>850</v>
+      </c>
+      <c r="J10" s="3">
+        <v>650</v>
+      </c>
+      <c r="K10" s="3">
+        <v>650</v>
+      </c>
+      <c r="L10" s="3">
+        <v>250</v>
+      </c>
+      <c r="M10" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="27"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="3">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3">
+        <v>7</v>
+      </c>
+      <c r="F11" s="3">
+        <v>8</v>
+      </c>
+      <c r="G11" s="3">
+        <v>6</v>
+      </c>
+      <c r="H11" s="3">
+        <v>7</v>
+      </c>
+      <c r="I11" s="3">
+        <v>8</v>
+      </c>
+      <c r="J11" s="3">
+        <v>9</v>
+      </c>
+      <c r="K11" s="3">
+        <v>9</v>
+      </c>
+      <c r="L11" s="3">
+        <v>7</v>
+      </c>
+      <c r="M11" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="27"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B7" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="3">
-        <v>10</v>
-      </c>
-      <c r="E7" s="3">
-        <v>13</v>
-      </c>
-      <c r="F7" s="3">
-        <v>11</v>
-      </c>
-      <c r="G7" s="3">
-        <v>9</v>
-      </c>
-      <c r="H7" s="3">
-        <v>17</v>
-      </c>
-      <c r="I7" s="3">
-        <v>15</v>
-      </c>
-      <c r="J7" s="3">
-        <v>18</v>
-      </c>
-      <c r="K7" s="3">
-        <v>18</v>
-      </c>
-      <c r="L7" s="3">
-        <v>20</v>
-      </c>
-      <c r="M7" s="3">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="3">
-        <v>600</v>
-      </c>
-      <c r="E8" s="3">
-        <v>650</v>
-      </c>
-      <c r="F8" s="3">
-        <v>550</v>
-      </c>
-      <c r="G8" s="3">
-        <v>450</v>
-      </c>
-      <c r="H8" s="3">
-        <v>750</v>
-      </c>
-      <c r="I8" s="3">
-        <v>850</v>
-      </c>
-      <c r="J8" s="3">
-        <v>650</v>
-      </c>
-      <c r="K8" s="3">
-        <v>650</v>
-      </c>
-      <c r="L8" s="3">
-        <v>250</v>
-      </c>
-      <c r="M8" s="3">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="18"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3">
-        <v>7</v>
-      </c>
-      <c r="E9" s="3">
-        <v>7</v>
-      </c>
-      <c r="F9" s="3">
-        <v>8</v>
-      </c>
-      <c r="G9" s="3">
-        <v>6</v>
-      </c>
-      <c r="H9" s="3">
-        <v>7</v>
-      </c>
-      <c r="I9" s="3">
-        <v>8</v>
-      </c>
-      <c r="J9" s="3">
-        <v>9</v>
-      </c>
-      <c r="K9" s="3">
-        <v>9</v>
-      </c>
-      <c r="L9" s="3">
-        <v>7</v>
-      </c>
-      <c r="M9" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="18"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="16" t="s">
+      <c r="M12" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="27"/>
+      <c r="B13" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="18"/>
-      <c r="B13" s="16"/>
       <c r="C13" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="18"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="27"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="15" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="18"/>
-      <c r="B15" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
+      <c r="A15" s="27"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="27"/>
+    </row>
+    <row r="17" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="27"/>
+      <c r="B17" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
         <v>0.1</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F17" s="3">
         <v>0.3</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G17" s="3">
         <v>-0.1</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H17" s="3">
         <v>-0.1</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I17" s="3">
         <v>0.3</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="J17" s="3">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
         <v>0.1</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L17" s="3">
         <v>-0.1</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M17" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="16" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="18"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="3">
+    <row r="18" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="27"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="3">
         <v>0.2</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E18" s="3">
         <v>0.15</v>
       </c>
-      <c r="F16" s="3">
-        <v>0</v>
-      </c>
-      <c r="G16" s="3">
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
         <v>0.2</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H18" s="3">
         <v>0.25</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I18" s="3">
         <v>0.15</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J18" s="3">
         <v>0.3</v>
-      </c>
-      <c r="K16" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="L16" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="M16" s="3">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="18"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="3">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="H17" s="3">
-        <v>0</v>
-      </c>
-      <c r="I17" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="J17" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="K17" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="L17" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="M17" s="3">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="18"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E18" s="3">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="I18" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="J18" s="3">
-        <v>0.1</v>
       </c>
       <c r="K18" s="3">
         <v>0.25</v>
       </c>
       <c r="L18" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="27"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
         <v>0.1</v>
       </c>
-      <c r="M18" s="3">
+      <c r="J19" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="K19" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="L19" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="M19" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="27"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="M20" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-    </row>
-    <row r="20" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="B20" s="19" t="s">
+    <row r="21" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+    </row>
+    <row r="22" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C22" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="4">
-        <v>2</v>
-      </c>
-      <c r="E20" s="4">
-        <v>2</v>
-      </c>
-      <c r="F20" s="4">
-        <v>2</v>
-      </c>
-      <c r="G20" s="4">
-        <v>1</v>
-      </c>
-      <c r="H20" s="4">
-        <v>2</v>
-      </c>
-      <c r="I20" s="4">
-        <v>3</v>
-      </c>
-      <c r="J20" s="4">
-        <v>3</v>
-      </c>
-      <c r="K20" s="4">
-        <v>3</v>
-      </c>
-      <c r="L20" s="4">
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
+      <c r="E22" s="4">
+        <v>2</v>
+      </c>
+      <c r="F22" s="4">
+        <v>2</v>
+      </c>
+      <c r="G22" s="4">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4">
+        <v>2</v>
+      </c>
+      <c r="I22" s="4">
+        <v>3</v>
+      </c>
+      <c r="J22" s="4">
+        <v>3</v>
+      </c>
+      <c r="K22" s="4">
+        <v>3</v>
+      </c>
+      <c r="L22" s="4">
         <v>4</v>
       </c>
-      <c r="M20" s="4">
+      <c r="M22" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="32"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="4" t="s">
+    <row r="23" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="24"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="4">
-        <f>0.7*D26</f>
+      <c r="D23" s="4">
+        <f>0.7*D28</f>
         <v>420</v>
       </c>
-      <c r="E21" s="4">
-        <f t="shared" ref="E21:M21" si="0">0.7*E26</f>
+      <c r="E23" s="4">
+        <f t="shared" ref="E23:M23" si="0">0.7*E28</f>
         <v>454.99999999999994</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F23" s="4">
         <f t="shared" si="0"/>
         <v>385</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G23" s="4">
         <f t="shared" si="0"/>
         <v>315</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H23" s="4">
         <f t="shared" si="0"/>
         <v>525</v>
       </c>
-      <c r="I21" s="4">
+      <c r="I23" s="4">
         <f t="shared" si="0"/>
         <v>595</v>
       </c>
-      <c r="J21" s="4">
+      <c r="J23" s="4">
         <f t="shared" si="0"/>
         <v>454.99999999999994</v>
       </c>
-      <c r="K21" s="4">
+      <c r="K23" s="4">
         <f t="shared" si="0"/>
         <v>454.99999999999994</v>
       </c>
-      <c r="L21" s="4">
+      <c r="L23" s="4">
         <f t="shared" si="0"/>
         <v>175</v>
       </c>
-      <c r="M21" s="4">
+      <c r="M23" s="4">
         <f t="shared" si="0"/>
         <v>560</v>
       </c>
     </row>
-    <row r="22" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="32"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="4" t="s">
+    <row r="24" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="24"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="4">
-        <v>1</v>
-      </c>
-      <c r="E22" s="4">
-        <v>1</v>
-      </c>
-      <c r="F22" s="4">
-        <v>1</v>
-      </c>
-      <c r="G22" s="4">
-        <v>1</v>
-      </c>
-      <c r="H22" s="4">
-        <v>1</v>
-      </c>
-      <c r="I22" s="4">
-        <v>1</v>
-      </c>
-      <c r="J22" s="4">
-        <v>1</v>
-      </c>
-      <c r="K22" s="4">
-        <v>1</v>
-      </c>
-      <c r="L22" s="4">
-        <v>1</v>
-      </c>
-      <c r="M22" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="32"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="4" t="s">
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="4">
+        <v>1</v>
+      </c>
+      <c r="F24" s="4">
+        <v>1</v>
+      </c>
+      <c r="G24" s="4">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4">
+        <v>1</v>
+      </c>
+      <c r="I24" s="4">
+        <v>1</v>
+      </c>
+      <c r="J24" s="4">
+        <v>1</v>
+      </c>
+      <c r="K24" s="4">
+        <v>1</v>
+      </c>
+      <c r="L24" s="4">
+        <v>1</v>
+      </c>
+      <c r="M24" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="24"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="32"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-    </row>
-    <row r="25" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="32"/>
-      <c r="B25" s="19" t="s">
+    <row r="26" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="24"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+    </row>
+    <row r="27" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="24"/>
+      <c r="B27" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C27" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="4">
-        <v>3</v>
-      </c>
-      <c r="E25" s="4">
+      <c r="D27" s="4">
+        <v>3</v>
+      </c>
+      <c r="E27" s="4">
         <v>4</v>
       </c>
-      <c r="F25" s="4">
-        <v>3</v>
-      </c>
-      <c r="G25" s="4">
-        <v>3</v>
-      </c>
-      <c r="H25" s="4">
+      <c r="F27" s="4">
+        <v>3</v>
+      </c>
+      <c r="G27" s="4">
+        <v>3</v>
+      </c>
+      <c r="H27" s="4">
         <v>4</v>
       </c>
-      <c r="I25" s="4">
+      <c r="I27" s="4">
         <v>4</v>
       </c>
-      <c r="J25" s="4">
+      <c r="J27" s="4">
         <v>4</v>
       </c>
-      <c r="K25" s="4">
+      <c r="K27" s="4">
         <v>5</v>
       </c>
-      <c r="L25" s="4">
+      <c r="L27" s="4">
         <v>5</v>
       </c>
-      <c r="M25" s="4">
+      <c r="M27" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="32"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="4" t="s">
+    <row r="28" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="24"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="4">
-        <f t="shared" ref="D26:M26" si="1">D8</f>
+      <c r="D28" s="4">
+        <f t="shared" ref="D28:M28" si="1">D10</f>
         <v>600</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E28" s="4">
         <f t="shared" si="1"/>
         <v>650</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F28" s="4">
         <f t="shared" si="1"/>
         <v>550</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G28" s="4">
         <f t="shared" si="1"/>
         <v>450</v>
       </c>
-      <c r="H26" s="4">
+      <c r="H28" s="4">
         <f t="shared" si="1"/>
         <v>750</v>
       </c>
-      <c r="I26" s="4">
+      <c r="I28" s="4">
         <f t="shared" si="1"/>
         <v>850</v>
       </c>
-      <c r="J26" s="4">
+      <c r="J28" s="4">
         <f t="shared" si="1"/>
         <v>650</v>
       </c>
-      <c r="K26" s="4">
+      <c r="K28" s="4">
         <f t="shared" si="1"/>
         <v>650</v>
       </c>
-      <c r="L26" s="4">
+      <c r="L28" s="4">
         <f t="shared" si="1"/>
         <v>250</v>
       </c>
-      <c r="M26" s="4">
+      <c r="M28" s="4">
         <f t="shared" si="1"/>
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="32"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="4" t="s">
+    <row r="29" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="24"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-      <c r="E27" s="4">
-        <v>1</v>
-      </c>
-      <c r="F27" s="4">
-        <v>1</v>
-      </c>
-      <c r="G27" s="4">
-        <v>1</v>
-      </c>
-      <c r="H27" s="4">
-        <v>1</v>
-      </c>
-      <c r="I27" s="4">
-        <v>1</v>
-      </c>
-      <c r="J27" s="4">
-        <v>1</v>
-      </c>
-      <c r="K27" s="4">
-        <v>1</v>
-      </c>
-      <c r="L27" s="4">
-        <v>1</v>
-      </c>
-      <c r="M27" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="32"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="4" t="s">
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="4">
+        <v>1</v>
+      </c>
+      <c r="F29" s="4">
+        <v>1</v>
+      </c>
+      <c r="G29" s="4">
+        <v>1</v>
+      </c>
+      <c r="H29" s="4">
+        <v>1</v>
+      </c>
+      <c r="I29" s="4">
+        <v>1</v>
+      </c>
+      <c r="J29" s="4">
+        <v>1</v>
+      </c>
+      <c r="K29" s="4">
+        <v>1</v>
+      </c>
+      <c r="L29" s="4">
+        <v>1</v>
+      </c>
+      <c r="M29" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="24"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="32"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-    </row>
-    <row r="30" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="32"/>
-      <c r="B30" s="25" t="s">
+    <row r="31" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="24"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+    </row>
+    <row r="32" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="24"/>
+      <c r="B32" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C32" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="4">
-        <v>3</v>
-      </c>
-      <c r="E30" s="4">
-        <v>3</v>
-      </c>
-      <c r="F30" s="4">
-        <v>3</v>
-      </c>
-      <c r="G30" s="4">
-        <v>3</v>
-      </c>
-      <c r="H30" s="4">
-        <v>3</v>
-      </c>
-      <c r="I30" s="4">
+      <c r="D32" s="4">
+        <v>3</v>
+      </c>
+      <c r="E32" s="4">
+        <v>3</v>
+      </c>
+      <c r="F32" s="4">
+        <v>3</v>
+      </c>
+      <c r="G32" s="4">
+        <v>3</v>
+      </c>
+      <c r="H32" s="4">
+        <v>3</v>
+      </c>
+      <c r="I32" s="4">
         <v>4</v>
       </c>
-      <c r="J30" s="4">
+      <c r="J32" s="4">
         <v>5</v>
       </c>
-      <c r="K30" s="4">
+      <c r="K32" s="4">
         <v>4</v>
       </c>
-      <c r="L30" s="4">
+      <c r="L32" s="4">
         <v>4</v>
       </c>
-      <c r="M30" s="4">
+      <c r="M32" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="32"/>
-      <c r="B31" s="26"/>
-      <c r="C31" s="4" t="s">
+    <row r="33" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="24"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="4">
-        <f>0.9*D26</f>
+      <c r="D33" s="4">
+        <f>0.9*D28</f>
         <v>540</v>
       </c>
-      <c r="E31" s="4">
-        <f t="shared" ref="E31:M31" si="2">0.9*E26</f>
+      <c r="E33" s="4">
+        <f t="shared" ref="E33:M33" si="2">0.9*E28</f>
         <v>585</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F33" s="4">
         <f t="shared" si="2"/>
         <v>495</v>
       </c>
-      <c r="G31" s="4">
+      <c r="G33" s="4">
         <f t="shared" si="2"/>
         <v>405</v>
       </c>
-      <c r="H31" s="4">
+      <c r="H33" s="4">
         <f t="shared" si="2"/>
         <v>675</v>
       </c>
-      <c r="I31" s="4">
+      <c r="I33" s="4">
         <f t="shared" si="2"/>
         <v>765</v>
       </c>
-      <c r="J31" s="4">
+      <c r="J33" s="4">
         <f t="shared" si="2"/>
         <v>585</v>
       </c>
-      <c r="K31" s="4">
+      <c r="K33" s="4">
         <f t="shared" si="2"/>
         <v>585</v>
       </c>
-      <c r="L31" s="4">
+      <c r="L33" s="4">
         <f t="shared" si="2"/>
         <v>225</v>
       </c>
-      <c r="M31" s="4">
+      <c r="M33" s="4">
         <f t="shared" si="2"/>
         <v>720</v>
       </c>
     </row>
-    <row r="32" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="32"/>
-      <c r="B32" s="26"/>
-      <c r="C32" s="4" t="s">
+    <row r="34" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="24"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="4">
-        <v>1</v>
-      </c>
-      <c r="E32" s="4">
-        <v>1</v>
-      </c>
-      <c r="F32" s="4">
-        <v>1</v>
-      </c>
-      <c r="G32" s="4">
-        <v>1</v>
-      </c>
-      <c r="H32" s="4">
-        <v>1</v>
-      </c>
-      <c r="I32" s="4">
-        <v>1</v>
-      </c>
-      <c r="J32" s="4">
-        <v>1</v>
-      </c>
-      <c r="K32" s="4">
-        <v>1</v>
-      </c>
-      <c r="L32" s="4">
-        <v>1</v>
-      </c>
-      <c r="M32" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="32"/>
-      <c r="B33" s="27"/>
-      <c r="C33" s="4" t="s">
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+      <c r="E34" s="4">
+        <v>1</v>
+      </c>
+      <c r="F34" s="4">
+        <v>1</v>
+      </c>
+      <c r="G34" s="4">
+        <v>1</v>
+      </c>
+      <c r="H34" s="4">
+        <v>1</v>
+      </c>
+      <c r="I34" s="4">
+        <v>1</v>
+      </c>
+      <c r="J34" s="4">
+        <v>1</v>
+      </c>
+      <c r="K34" s="4">
+        <v>1</v>
+      </c>
+      <c r="L34" s="4">
+        <v>1</v>
+      </c>
+      <c r="M34" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="24"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="32"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="32"/>
-      <c r="B35" s="25" t="s">
+    <row r="36" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="24"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="24"/>
+      <c r="B37" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C37" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="4">
-        <v>2</v>
-      </c>
-      <c r="E35" s="4">
-        <v>2</v>
-      </c>
-      <c r="F35" s="4">
-        <v>2</v>
-      </c>
-      <c r="G35" s="4">
-        <v>1</v>
-      </c>
-      <c r="H35" s="4">
-        <v>2</v>
-      </c>
-      <c r="I35" s="4">
-        <v>2</v>
-      </c>
-      <c r="J35" s="4">
-        <v>3</v>
-      </c>
-      <c r="K35" s="4">
-        <v>3</v>
-      </c>
-      <c r="L35" s="4">
-        <v>2</v>
-      </c>
-      <c r="M35" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="32"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="4" t="s">
+      <c r="D37" s="4">
+        <v>2</v>
+      </c>
+      <c r="E37" s="4">
+        <v>2</v>
+      </c>
+      <c r="F37" s="4">
+        <v>2</v>
+      </c>
+      <c r="G37" s="4">
+        <v>1</v>
+      </c>
+      <c r="H37" s="4">
+        <v>2</v>
+      </c>
+      <c r="I37" s="4">
+        <v>2</v>
+      </c>
+      <c r="J37" s="4">
+        <v>3</v>
+      </c>
+      <c r="K37" s="4">
+        <v>3</v>
+      </c>
+      <c r="L37" s="4">
+        <v>2</v>
+      </c>
+      <c r="M37" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="24"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D36" s="4">
-        <f>0.6*D26</f>
+      <c r="D38" s="4">
+        <f>0.6*D28</f>
         <v>360</v>
       </c>
-      <c r="E36" s="4">
-        <f t="shared" ref="E36:M36" si="3">0.6*E26</f>
+      <c r="E38" s="4">
+        <f t="shared" ref="E38:M38" si="3">0.6*E28</f>
         <v>390</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F38" s="4">
         <f t="shared" si="3"/>
         <v>330</v>
       </c>
-      <c r="G36" s="4">
+      <c r="G38" s="4">
         <f t="shared" si="3"/>
         <v>270</v>
       </c>
-      <c r="H36" s="4">
+      <c r="H38" s="4">
         <f t="shared" si="3"/>
         <v>450</v>
       </c>
-      <c r="I36" s="4">
+      <c r="I38" s="4">
         <f t="shared" si="3"/>
         <v>510</v>
       </c>
-      <c r="J36" s="4">
+      <c r="J38" s="4">
         <f t="shared" si="3"/>
         <v>390</v>
       </c>
-      <c r="K36" s="4">
+      <c r="K38" s="4">
         <f t="shared" si="3"/>
         <v>390</v>
       </c>
-      <c r="L36" s="4">
+      <c r="L38" s="4">
         <f t="shared" si="3"/>
         <v>150</v>
       </c>
-      <c r="M36" s="4">
+      <c r="M38" s="4">
         <f t="shared" si="3"/>
         <v>480</v>
       </c>
     </row>
-    <row r="37" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="32"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="4" t="s">
+    <row r="39" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="24"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D37" s="4">
-        <v>1</v>
-      </c>
-      <c r="E37" s="4">
-        <v>1</v>
-      </c>
-      <c r="F37" s="4">
-        <v>1</v>
-      </c>
-      <c r="G37" s="4">
-        <v>1</v>
-      </c>
-      <c r="H37" s="4">
-        <v>1</v>
-      </c>
-      <c r="I37" s="4">
-        <v>1</v>
-      </c>
-      <c r="J37" s="4">
-        <v>1</v>
-      </c>
-      <c r="K37" s="4">
-        <v>1</v>
-      </c>
-      <c r="L37" s="4">
-        <v>1</v>
-      </c>
-      <c r="M37" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="32"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="4" t="s">
+      <c r="D39" s="4">
+        <v>1</v>
+      </c>
+      <c r="E39" s="4">
+        <v>1</v>
+      </c>
+      <c r="F39" s="4">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4">
+        <v>1</v>
+      </c>
+      <c r="H39" s="4">
+        <v>1</v>
+      </c>
+      <c r="I39" s="4">
+        <v>1</v>
+      </c>
+      <c r="J39" s="4">
+        <v>1</v>
+      </c>
+      <c r="K39" s="4">
+        <v>1</v>
+      </c>
+      <c r="L39" s="4">
+        <v>1</v>
+      </c>
+      <c r="M39" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="24"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="32"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-    </row>
-    <row r="40" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="32"/>
-      <c r="B40" s="25" t="s">
+    <row r="41" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="24"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+    </row>
+    <row r="42" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="24"/>
+      <c r="B42" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C42" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D40" s="4">
-        <f>0.9*D26</f>
+      <c r="D42" s="4">
+        <f>0.9*D28</f>
         <v>540</v>
       </c>
-      <c r="E40" s="4">
-        <f t="shared" ref="E40:M40" si="4">0.9*E26</f>
+      <c r="E42" s="4">
+        <f t="shared" ref="E42:M42" si="4">0.9*E28</f>
         <v>585</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F42" s="4">
         <f t="shared" si="4"/>
         <v>495</v>
       </c>
-      <c r="G40" s="4">
+      <c r="G42" s="4">
         <f t="shared" si="4"/>
         <v>405</v>
       </c>
-      <c r="H40" s="4">
+      <c r="H42" s="4">
         <f t="shared" si="4"/>
         <v>675</v>
       </c>
-      <c r="I40" s="4">
+      <c r="I42" s="4">
         <f t="shared" si="4"/>
         <v>765</v>
       </c>
-      <c r="J40" s="4">
+      <c r="J42" s="4">
         <f t="shared" si="4"/>
         <v>585</v>
       </c>
-      <c r="K40" s="4">
+      <c r="K42" s="4">
         <f t="shared" si="4"/>
         <v>585</v>
       </c>
-      <c r="L40" s="4">
+      <c r="L42" s="4">
         <f t="shared" si="4"/>
         <v>225</v>
       </c>
-      <c r="M40" s="4">
+      <c r="M42" s="4">
         <f t="shared" si="4"/>
         <v>720</v>
       </c>
     </row>
-    <row r="41" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="32"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="4" t="s">
+    <row r="43" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="24"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D41" s="4">
-        <v>1</v>
-      </c>
-      <c r="E41" s="4">
-        <v>1</v>
-      </c>
-      <c r="F41" s="4">
-        <v>1</v>
-      </c>
-      <c r="G41" s="4">
-        <v>1</v>
-      </c>
-      <c r="H41" s="4">
-        <v>1</v>
-      </c>
-      <c r="I41" s="4">
-        <v>1</v>
-      </c>
-      <c r="J41" s="4">
-        <v>1</v>
-      </c>
-      <c r="K41" s="4">
-        <v>1</v>
-      </c>
-      <c r="L41" s="4">
-        <v>1</v>
-      </c>
-      <c r="M41" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="32"/>
-      <c r="B42" s="27"/>
-      <c r="C42" s="4" t="s">
+      <c r="D43" s="4">
+        <v>1</v>
+      </c>
+      <c r="E43" s="4">
+        <v>1</v>
+      </c>
+      <c r="F43" s="4">
+        <v>1</v>
+      </c>
+      <c r="G43" s="4">
+        <v>1</v>
+      </c>
+      <c r="H43" s="4">
+        <v>1</v>
+      </c>
+      <c r="I43" s="4">
+        <v>1</v>
+      </c>
+      <c r="J43" s="4">
+        <v>1</v>
+      </c>
+      <c r="K43" s="4">
+        <v>1</v>
+      </c>
+      <c r="L43" s="4">
+        <v>1</v>
+      </c>
+      <c r="M43" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="24"/>
+      <c r="B44" s="19"/>
+      <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="32"/>
-    </row>
-    <row r="44" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="32"/>
-      <c r="B44" s="25" t="s">
+    <row r="45" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="24"/>
+    </row>
+    <row r="46" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="24"/>
+      <c r="B46" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C44" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="32"/>
-      <c r="B45" s="26"/>
-      <c r="C45" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="32"/>
-      <c r="B46" s="27"/>
       <c r="C46" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="32"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="24"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="4">
+        <v>2</v>
+      </c>
     </row>
     <row r="48" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="32"/>
-      <c r="B48" s="25" t="s">
+      <c r="A48" s="24"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="24"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+    </row>
+    <row r="50" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="24"/>
+      <c r="B50" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C50" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D48" s="4">
-        <f>D20+D25+D30+D35</f>
+      <c r="D50" s="4">
+        <f>D22+D27+D32+D37</f>
         <v>10</v>
       </c>
-      <c r="E48" s="4">
-        <f>E20+E25+E30+E35</f>
+      <c r="E50" s="4">
+        <f>E22+E27+E32+E37</f>
         <v>11</v>
       </c>
-      <c r="F48" s="4">
-        <f t="shared" ref="F48:M48" si="5">F20+F25+F30+F35</f>
+      <c r="F50" s="4">
+        <f t="shared" ref="F50:M50" si="5">F22+F27+F32+F37</f>
         <v>10</v>
       </c>
-      <c r="G48" s="4">
+      <c r="G50" s="4">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="H48" s="4">
+      <c r="H50" s="4">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="I48" s="4">
+      <c r="I50" s="4">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="J48" s="4">
-        <f>J20+J25+J30+J35</f>
+      <c r="J50" s="4">
+        <f>J22+J27+J32+J37</f>
         <v>15</v>
       </c>
-      <c r="K48" s="4">
+      <c r="K50" s="4">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="L48" s="4">
+      <c r="L50" s="4">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="M48" s="4">
+      <c r="M50" s="4">
         <f t="shared" si="5"/>
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="32"/>
-      <c r="B49" s="26"/>
-      <c r="C49" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D49" s="4">
-        <f>D22+D27+D32+D37+D41</f>
+    <row r="51" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="24"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D51" s="4">
+        <f>D24+D29+D34+D39+D43</f>
         <v>5</v>
       </c>
-      <c r="E49" s="4">
-        <f>E22+E27+E32+E37+E41</f>
+      <c r="E51" s="4">
+        <f>E24+E29+E34+E39+E43</f>
         <v>5</v>
       </c>
-      <c r="F49" s="4">
-        <f t="shared" ref="F49:M49" si="6">F22+F27+F32+F37+F41</f>
+      <c r="F51" s="4">
+        <f t="shared" ref="F51:M51" si="6">F24+F29+F34+F39+F43</f>
         <v>5</v>
       </c>
-      <c r="G49" s="4">
+      <c r="G51" s="4">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="H49" s="4">
+      <c r="H51" s="4">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="I49" s="4">
+      <c r="I51" s="4">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="J49" s="4">
-        <f>J22+J27+J32+J37+J41</f>
+      <c r="J51" s="4">
+        <f>J24+J29+J34+J39+J43</f>
         <v>5</v>
       </c>
-      <c r="K49" s="4">
+      <c r="K51" s="4">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L49" s="4">
+      <c r="L51" s="4">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="M49" s="4">
+      <c r="M51" s="4">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="32"/>
-      <c r="B50" s="27"/>
-      <c r="C50" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D50" s="4">
-        <f>D48*(1+D49*0.02)</f>
+    <row r="52" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="24"/>
+      <c r="B52" s="19"/>
+      <c r="C52" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D52" s="4">
+        <f>D50*(1+D51*0.02)</f>
         <v>11</v>
       </c>
-      <c r="E50" s="4">
-        <f>E48*(1+E49*0.02)</f>
+      <c r="E52" s="4">
+        <f>E50*(1+E51*0.02)</f>
         <v>12.100000000000001</v>
       </c>
-      <c r="F50" s="4">
-        <f t="shared" ref="F50:M50" si="7">F48*(1+F49*0.02)</f>
+      <c r="F52" s="4">
+        <f t="shared" ref="F52:M52" si="7">F50*(1+F51*0.02)</f>
         <v>11</v>
       </c>
-      <c r="G50" s="4">
+      <c r="G52" s="4">
         <f t="shared" si="7"/>
         <v>8.8000000000000007</v>
       </c>
-      <c r="H50" s="4">
+      <c r="H52" s="4">
         <f t="shared" si="7"/>
         <v>12.100000000000001</v>
       </c>
-      <c r="I50" s="4">
+      <c r="I52" s="4">
         <f t="shared" si="7"/>
         <v>14.3</v>
       </c>
-      <c r="J50" s="4">
-        <f>J48*(1+J49*0.02)</f>
+      <c r="J52" s="4">
+        <f>J50*(1+J51*0.02)</f>
         <v>16.5</v>
       </c>
-      <c r="K50" s="4">
+      <c r="K52" s="4">
         <f t="shared" si="7"/>
         <v>16.5</v>
       </c>
-      <c r="L50" s="4">
+      <c r="L52" s="4">
         <f t="shared" si="7"/>
         <v>16.5</v>
       </c>
-      <c r="M50" s="4">
+      <c r="M52" s="4">
         <f t="shared" si="7"/>
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-    </row>
-    <row r="52" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="B52" s="17" t="s">
+    <row r="53" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+    </row>
+    <row r="54" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="B54" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C54" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="17"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="5" t="s">
+    <row r="55" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="26"/>
+      <c r="B55" s="26"/>
+      <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="17"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="5" t="s">
+    <row r="56" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="26"/>
+      <c r="B56" s="26"/>
+      <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="17"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="5" t="s">
+    <row r="57" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="26"/>
+      <c r="B57" s="26"/>
+      <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="17"/>
-      <c r="B56" s="17" t="s">
+    <row r="58" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="26"/>
+      <c r="B58" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C56" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="17"/>
-      <c r="B57" s="20"/>
-      <c r="C57" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="17"/>
-      <c r="B58" s="21"/>
       <c r="C58" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="17"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="26"/>
+      <c r="B59" s="29"/>
+      <c r="C59" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="60" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="17"/>
-      <c r="B60" s="17" t="s">
+      <c r="A60" s="26"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="26"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+    </row>
+    <row r="62" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="26"/>
+      <c r="B62" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="17"/>
-      <c r="B61" s="20"/>
-      <c r="C61" s="5" t="s">
+      <c r="C62" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="26"/>
+      <c r="B63" s="29"/>
+      <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="17"/>
-      <c r="B62" s="21"/>
-      <c r="C62" s="5" t="s">
+    <row r="64" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="26"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:12" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="28" t="s">
+    <row r="67" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B67" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C67" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D65" s="6">
-        <v>1</v>
-      </c>
-      <c r="E65" s="6">
-        <v>1</v>
-      </c>
-      <c r="F65" s="6">
-        <v>1</v>
-      </c>
-      <c r="G65" s="6">
-        <v>1</v>
-      </c>
-      <c r="H65" s="6">
-        <v>1</v>
-      </c>
-      <c r="I65" s="6">
-        <v>1</v>
-      </c>
-      <c r="J65" s="6">
-        <v>1</v>
-      </c>
-      <c r="K65" s="6">
-        <v>1</v>
-      </c>
-      <c r="L65" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="29"/>
-      <c r="B66" s="4" t="s">
+      <c r="D67" s="6">
+        <v>1</v>
+      </c>
+      <c r="E67" s="6">
+        <v>1</v>
+      </c>
+      <c r="F67" s="6">
+        <v>1</v>
+      </c>
+      <c r="G67" s="6">
+        <v>1</v>
+      </c>
+      <c r="H67" s="6">
+        <v>1</v>
+      </c>
+      <c r="I67" s="6">
+        <v>1</v>
+      </c>
+      <c r="J67" s="6">
+        <v>1</v>
+      </c>
+      <c r="K67" s="6">
+        <v>1</v>
+      </c>
+      <c r="L67" s="6">
+        <v>0</v>
+      </c>
+      <c r="M67" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="21"/>
+      <c r="B68" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D68" s="4">
+        <v>1</v>
+      </c>
+      <c r="E68" s="4">
+        <v>1</v>
+      </c>
+      <c r="F68" s="4">
+        <v>1</v>
+      </c>
+      <c r="G68" s="4">
+        <v>1</v>
+      </c>
+      <c r="H68" s="4">
+        <v>1</v>
+      </c>
+      <c r="I68" s="4">
+        <v>1</v>
+      </c>
+      <c r="J68" s="4">
+        <v>1</v>
+      </c>
+      <c r="K68" s="4">
+        <v>1</v>
+      </c>
+      <c r="L68" s="4">
+        <v>0</v>
+      </c>
+      <c r="M68" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="21"/>
+      <c r="B69" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C66" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D66" s="4">
-        <v>1</v>
-      </c>
-      <c r="E66" s="4">
-        <v>1</v>
-      </c>
-      <c r="F66" s="4">
-        <v>1</v>
-      </c>
-      <c r="G66" s="4">
-        <v>1</v>
-      </c>
-      <c r="H66" s="4">
-        <v>1</v>
-      </c>
-      <c r="I66" s="4">
-        <v>1</v>
-      </c>
-      <c r="J66" s="4">
-        <v>1</v>
-      </c>
-      <c r="K66" s="4">
-        <v>1</v>
-      </c>
-      <c r="L66" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="29"/>
-      <c r="B67" s="4" t="s">
+      <c r="C69" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D69" s="4">
+        <v>1</v>
+      </c>
+      <c r="E69" s="4">
+        <v>1</v>
+      </c>
+      <c r="F69" s="4">
+        <v>1</v>
+      </c>
+      <c r="G69" s="4">
+        <v>1</v>
+      </c>
+      <c r="H69" s="4">
+        <v>1</v>
+      </c>
+      <c r="I69" s="4">
+        <v>1</v>
+      </c>
+      <c r="J69" s="4">
+        <v>1</v>
+      </c>
+      <c r="K69" s="4">
+        <v>1</v>
+      </c>
+      <c r="L69" s="4">
+        <v>0</v>
+      </c>
+      <c r="M69" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="22"/>
+      <c r="B70" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C67" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D67" s="4">
-        <v>1</v>
-      </c>
-      <c r="E67" s="4">
-        <v>1</v>
-      </c>
-      <c r="F67" s="4">
-        <v>1</v>
-      </c>
-      <c r="G67" s="4">
-        <v>1</v>
-      </c>
-      <c r="H67" s="4">
-        <v>1</v>
-      </c>
-      <c r="I67" s="4">
-        <v>1</v>
-      </c>
-      <c r="J67" s="4">
-        <v>1</v>
-      </c>
-      <c r="K67" s="4">
-        <v>1</v>
-      </c>
-      <c r="L67" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="30"/>
-      <c r="B68" s="5" t="s">
+      <c r="C70" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C68" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D68" s="5">
-        <v>0</v>
-      </c>
-      <c r="E68" s="5">
-        <v>0</v>
-      </c>
-      <c r="F68" s="5">
-        <v>0</v>
-      </c>
-      <c r="G68" s="5">
-        <v>0</v>
-      </c>
-      <c r="H68" s="5">
-        <v>0</v>
-      </c>
-      <c r="I68" s="5">
-        <v>0</v>
-      </c>
-      <c r="J68" s="5">
-        <v>0</v>
-      </c>
-      <c r="K68" s="5">
-        <v>1</v>
-      </c>
-      <c r="L68" s="5">
+      <c r="D70" s="5">
+        <v>0</v>
+      </c>
+      <c r="E70" s="5">
+        <v>0</v>
+      </c>
+      <c r="F70" s="5">
+        <v>0</v>
+      </c>
+      <c r="G70" s="5">
+        <v>0</v>
+      </c>
+      <c r="H70" s="5">
+        <v>0</v>
+      </c>
+      <c r="I70" s="5">
+        <v>0</v>
+      </c>
+      <c r="J70" s="5">
+        <v>0</v>
+      </c>
+      <c r="K70" s="5">
+        <v>1</v>
+      </c>
+      <c r="L70" s="5">
+        <v>0</v>
+      </c>
+      <c r="M70" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A65:A68"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="A20:A50"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="A52:A62"/>
-    <mergeCell ref="A7:A18"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B52:B55"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B60:B62"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="A22:A52"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="A54:A64"/>
+    <mergeCell ref="A9:A20"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="B37:B40"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2637,7 +2795,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228FD55C-7A05-4B85-B3F0-CE35E1F4B422}">
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:Q69"/>
   <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="16.625" style="2"/>
@@ -2698,453 +2856,449 @@
         <v>52</v>
       </c>
       <c r="P4" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="Q4" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
+    </row>
+    <row r="5" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="1">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2</v>
+      </c>
+      <c r="K7" s="1">
+        <v>2</v>
+      </c>
+      <c r="L7" s="1">
+        <v>2</v>
+      </c>
+      <c r="M7" s="1">
+        <v>2</v>
+      </c>
+      <c r="N7" s="1">
+        <v>2</v>
+      </c>
+      <c r="O7" s="1">
+        <v>2</v>
+      </c>
+      <c r="P7" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D5" s="1">
-        <v>2</v>
-      </c>
-      <c r="E5" s="1">
-        <v>2</v>
-      </c>
-      <c r="F5" s="1">
-        <v>2</v>
-      </c>
-      <c r="G5" s="1">
-        <v>2</v>
-      </c>
-      <c r="H5" s="1">
-        <v>2</v>
-      </c>
-      <c r="I5" s="1">
-        <v>2</v>
-      </c>
-      <c r="J5" s="1">
-        <v>2</v>
-      </c>
-      <c r="K5" s="1">
-        <v>2</v>
-      </c>
-      <c r="L5" s="1">
-        <v>2</v>
-      </c>
-      <c r="M5" s="1">
-        <v>2</v>
-      </c>
-      <c r="N5" s="1">
-        <v>2</v>
-      </c>
-      <c r="O5" s="1">
-        <v>2</v>
-      </c>
-      <c r="P5" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1">
-        <v>2</v>
-      </c>
-      <c r="I6" s="1">
-        <v>2</v>
-      </c>
-      <c r="J6" s="1">
-        <v>2</v>
-      </c>
-      <c r="K6" s="1">
-        <v>3</v>
-      </c>
-      <c r="L6" s="1">
-        <v>3</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="N6" s="1">
-        <v>3</v>
-      </c>
-      <c r="O6" s="1">
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>2</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2</v>
+      </c>
+      <c r="J8" s="1">
+        <v>2</v>
+      </c>
+      <c r="K8" s="1">
+        <v>3</v>
+      </c>
+      <c r="L8" s="1">
+        <v>3</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="N8" s="1">
+        <v>3</v>
+      </c>
+      <c r="O8" s="1">
         <v>4</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P8" s="1">
         <v>4</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q8" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="18" t="s">
+    <row r="9" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="3">
+        <v>17</v>
+      </c>
+      <c r="E9" s="3">
+        <v>18</v>
+      </c>
+      <c r="F9" s="3">
+        <v>13</v>
+      </c>
+      <c r="G9" s="3">
+        <v>14</v>
+      </c>
+      <c r="H9" s="3">
+        <v>20</v>
+      </c>
+      <c r="I9" s="3">
+        <v>19</v>
+      </c>
+      <c r="J9" s="3">
+        <v>21</v>
+      </c>
+      <c r="K9" s="3">
+        <v>23</v>
+      </c>
+      <c r="L9" s="3">
+        <v>23</v>
+      </c>
+      <c r="M9" s="3">
+        <v>27</v>
+      </c>
+      <c r="N9" s="3">
+        <v>25</v>
+      </c>
+      <c r="O9" s="3">
+        <v>28</v>
+      </c>
+      <c r="P9" s="3">
+        <v>32</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="27"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="3">
+        <v>200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>250</v>
+      </c>
+      <c r="F10" s="3">
+        <v>250</v>
+      </c>
+      <c r="G10" s="3">
+        <v>200</v>
+      </c>
+      <c r="H10" s="3">
+        <v>500</v>
+      </c>
+      <c r="I10" s="3">
+        <v>300</v>
+      </c>
+      <c r="J10" s="3">
+        <v>450</v>
+      </c>
+      <c r="K10" s="3">
+        <v>600</v>
+      </c>
+      <c r="L10" s="3">
+        <v>400</v>
+      </c>
+      <c r="M10" s="3">
+        <v>900</v>
+      </c>
+      <c r="N10" s="3">
+        <v>800</v>
+      </c>
+      <c r="O10" s="3">
+        <v>800</v>
+      </c>
+      <c r="P10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="27"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="3">
+        <v>6</v>
+      </c>
+      <c r="E11" s="3">
+        <v>6</v>
+      </c>
+      <c r="F11" s="3">
+        <v>6</v>
+      </c>
+      <c r="G11" s="3">
+        <v>6</v>
+      </c>
+      <c r="H11" s="3">
+        <v>8</v>
+      </c>
+      <c r="I11" s="3">
+        <v>8</v>
+      </c>
+      <c r="J11" s="3">
+        <v>8</v>
+      </c>
+      <c r="K11" s="3">
+        <v>9</v>
+      </c>
+      <c r="L11" s="3">
+        <v>8</v>
+      </c>
+      <c r="M11" s="3">
+        <v>10</v>
+      </c>
+      <c r="N11" s="3">
+        <v>9</v>
+      </c>
+      <c r="O11" s="3">
+        <v>10</v>
+      </c>
+      <c r="P11" s="3">
+        <v>8</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="27"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M12" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B7" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="3">
-        <v>17</v>
-      </c>
-      <c r="E7" s="3">
-        <v>18</v>
-      </c>
-      <c r="F7" s="3">
-        <v>13</v>
-      </c>
-      <c r="G7" s="3">
-        <v>14</v>
-      </c>
-      <c r="H7" s="3">
-        <v>20</v>
-      </c>
-      <c r="I7" s="3">
-        <v>19</v>
-      </c>
-      <c r="J7" s="3">
-        <v>21</v>
-      </c>
-      <c r="K7" s="3">
-        <v>23</v>
-      </c>
-      <c r="L7" s="3">
-        <v>23</v>
-      </c>
-      <c r="M7" s="3">
-        <v>25</v>
-      </c>
-      <c r="N7" s="3">
-        <v>24</v>
-      </c>
-      <c r="O7" s="3">
-        <v>28</v>
-      </c>
-      <c r="P7" s="3">
-        <v>32</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="3">
-        <v>200</v>
-      </c>
-      <c r="E8" s="3">
-        <v>250</v>
-      </c>
-      <c r="F8" s="3">
-        <v>250</v>
-      </c>
-      <c r="G8" s="3">
-        <v>200</v>
-      </c>
-      <c r="H8" s="3">
-        <v>500</v>
-      </c>
-      <c r="I8" s="3">
-        <v>300</v>
-      </c>
-      <c r="J8" s="3">
-        <v>450</v>
-      </c>
-      <c r="K8" s="3">
-        <v>600</v>
-      </c>
-      <c r="L8" s="3">
-        <v>400</v>
-      </c>
-      <c r="M8" s="3">
-        <v>900</v>
-      </c>
-      <c r="N8" s="3">
-        <v>800</v>
-      </c>
-      <c r="O8" s="3">
-        <v>800</v>
-      </c>
-      <c r="P8" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="18"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3">
-        <v>6</v>
-      </c>
-      <c r="E9" s="3">
-        <v>6</v>
-      </c>
-      <c r="F9" s="3">
-        <v>6</v>
-      </c>
-      <c r="G9" s="3">
-        <v>6</v>
-      </c>
-      <c r="H9" s="3">
-        <v>8</v>
-      </c>
-      <c r="I9" s="3">
-        <v>8</v>
-      </c>
-      <c r="J9" s="3">
-        <v>8</v>
-      </c>
-      <c r="K9" s="3">
-        <v>9</v>
-      </c>
-      <c r="L9" s="3">
-        <v>8</v>
-      </c>
-      <c r="M9" s="3">
-        <v>10</v>
-      </c>
-      <c r="N9" s="3">
-        <v>9</v>
-      </c>
-      <c r="O9" s="3">
-        <v>10</v>
-      </c>
-      <c r="P9" s="3">
-        <v>8</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="18"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="16" t="s">
+      <c r="N12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="27"/>
+      <c r="B13" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="18"/>
-      <c r="B13" s="16"/>
       <c r="C13" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="18"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="27"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="15" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="18"/>
-      <c r="B15" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="3">
+      <c r="A15" s="27"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="27"/>
+    </row>
+    <row r="17" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="27"/>
+      <c r="B17" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="3">
         <v>0.1</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E17" s="3">
         <v>-0.3</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
         <v>0.1</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>-0.2</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="O15" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="18"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E16" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="F16" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G16" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="H16" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="I16" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="J16" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="K16" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="L16" s="3">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="N16" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="O16" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="P16" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="Q16" s="3">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="18"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="3">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G17" s="3">
-        <v>0</v>
       </c>
       <c r="H17" s="3">
         <v>0.1</v>
@@ -3153,1404 +3307,1622 @@
         <v>0</v>
       </c>
       <c r="J17" s="3">
+        <v>-0.2</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="P17" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="27"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="N18" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="P18" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="27"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3">
         <v>0.05</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K19" s="3">
         <v>0.05</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L19" s="3">
         <v>-0.2</v>
       </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="M19" s="3">
+        <v>0</v>
+      </c>
+      <c r="N19" s="3">
         <v>0.1</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O19" s="3">
         <v>0.05</v>
       </c>
-      <c r="P17" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="P19" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="18"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="3" t="s">
+    <row r="20" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="27"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="3">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3">
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>0.2</v>
       </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>0.3</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H20" s="3">
         <v>0.15</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I20" s="3">
         <v>0.3</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J20" s="3">
         <v>0.1</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K20" s="3">
         <v>0.2</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L20" s="3">
         <v>0.4</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M20" s="3">
         <v>0.2</v>
       </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>0.3</v>
       </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>0.35</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-    </row>
-    <row r="20" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="B20" s="34" t="s">
+    <row r="21" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+    </row>
+    <row r="22" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C22" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="4">
-        <v>3</v>
-      </c>
-      <c r="E20" s="4">
-        <v>3</v>
-      </c>
-      <c r="F20" s="4">
+      <c r="D22" s="4">
+        <v>3</v>
+      </c>
+      <c r="E22" s="4">
+        <v>3</v>
+      </c>
+      <c r="F22" s="4">
         <v>4</v>
       </c>
-      <c r="G20" s="4">
-        <v>3</v>
-      </c>
-      <c r="H20" s="4">
+      <c r="G22" s="4">
+        <v>3</v>
+      </c>
+      <c r="H22" s="4">
         <v>4</v>
       </c>
-      <c r="I20" s="4">
+      <c r="I22" s="4">
         <v>4</v>
       </c>
-      <c r="J20" s="4">
-        <v>3</v>
-      </c>
-      <c r="K20" s="4">
+      <c r="J22" s="4">
+        <v>3</v>
+      </c>
+      <c r="K22" s="4">
         <v>4</v>
       </c>
-      <c r="L20" s="4">
+      <c r="L22" s="4">
         <v>4</v>
       </c>
-      <c r="M20" s="4">
+      <c r="M22" s="4">
         <v>5</v>
       </c>
-      <c r="N20" s="4">
+      <c r="N22" s="4">
         <v>4</v>
       </c>
-      <c r="O20" s="4">
+      <c r="O22" s="4">
         <v>5</v>
       </c>
-      <c r="P20" s="4">
+      <c r="P22" s="4">
         <v>5</v>
       </c>
-      <c r="Q20" s="4">
+      <c r="Q22" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="19"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="4" t="s">
+    <row r="23" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="28"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="4">
-        <f>0.7*D26</f>
+      <c r="D23" s="4">
+        <f>0.7*D28</f>
         <v>140</v>
       </c>
-      <c r="E21" s="4">
-        <f t="shared" ref="E21:Q21" si="0">0.7*E26</f>
+      <c r="E23" s="4">
+        <f t="shared" ref="E23:Q23" si="0">0.7*E28</f>
         <v>175</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F23" s="4">
         <f t="shared" si="0"/>
         <v>175</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G23" s="4">
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H23" s="4">
         <f t="shared" si="0"/>
         <v>350</v>
       </c>
-      <c r="I21" s="4">
+      <c r="I23" s="4">
         <f t="shared" si="0"/>
         <v>210</v>
       </c>
-      <c r="J21" s="4">
+      <c r="J23" s="4">
         <f t="shared" si="0"/>
         <v>315</v>
       </c>
-      <c r="K21" s="4">
+      <c r="K23" s="4">
         <f t="shared" si="0"/>
         <v>420</v>
       </c>
-      <c r="L21" s="4">
+      <c r="L23" s="4">
         <f t="shared" si="0"/>
         <v>280</v>
       </c>
-      <c r="M21" s="4">
+      <c r="M23" s="4">
         <f t="shared" si="0"/>
         <v>630</v>
       </c>
-      <c r="N21" s="4">
+      <c r="N23" s="4">
         <f t="shared" si="0"/>
         <v>560</v>
       </c>
-      <c r="O21" s="4">
+      <c r="O23" s="4">
         <f t="shared" si="0"/>
         <v>560</v>
       </c>
-      <c r="P21" s="4">
+      <c r="P23" s="4">
         <f t="shared" si="0"/>
         <v>700</v>
       </c>
-      <c r="Q21" s="4">
+      <c r="Q23" s="4">
         <f t="shared" si="0"/>
         <v>489.99999999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="19"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="4" t="s">
+    <row r="24" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="28"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="4">
-        <v>1</v>
-      </c>
-      <c r="E22" s="4">
-        <v>1</v>
-      </c>
-      <c r="F22" s="4">
-        <v>1</v>
-      </c>
-      <c r="G22" s="4">
-        <v>1</v>
-      </c>
-      <c r="H22" s="4">
-        <v>1</v>
-      </c>
-      <c r="I22" s="4">
-        <v>2</v>
-      </c>
-      <c r="J22" s="4">
-        <v>1</v>
-      </c>
-      <c r="K22" s="4">
-        <v>2</v>
-      </c>
-      <c r="L22" s="4">
-        <v>2</v>
-      </c>
-      <c r="M22" s="4">
-        <v>2</v>
-      </c>
-      <c r="N22" s="4">
-        <v>2</v>
-      </c>
-      <c r="O22" s="4">
-        <v>2</v>
-      </c>
-      <c r="P22" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q22" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="19"/>
-      <c r="B23" s="34"/>
-      <c r="C23" s="4" t="s">
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="4">
+        <v>1</v>
+      </c>
+      <c r="F24" s="4">
+        <v>1</v>
+      </c>
+      <c r="G24" s="4">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4">
+        <v>1</v>
+      </c>
+      <c r="I24" s="4">
+        <v>2</v>
+      </c>
+      <c r="J24" s="4">
+        <v>1</v>
+      </c>
+      <c r="K24" s="4">
+        <v>2</v>
+      </c>
+      <c r="L24" s="4">
+        <v>2</v>
+      </c>
+      <c r="M24" s="4">
+        <v>2</v>
+      </c>
+      <c r="N24" s="4">
+        <v>2</v>
+      </c>
+      <c r="O24" s="4">
+        <v>2</v>
+      </c>
+      <c r="P24" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="28"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="19"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-    </row>
-    <row r="25" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="19"/>
-      <c r="B25" s="34" t="s">
+      <c r="J25" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="K25" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="L25" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="M25" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="N25" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="O25" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="P25" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="Q25" s="4">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="28"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+    </row>
+    <row r="27" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="28"/>
+      <c r="B27" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C27" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D27" s="4">
         <v>4</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E27" s="4">
         <v>4</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F27" s="4">
         <v>4</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G27" s="4">
         <v>4</v>
       </c>
-      <c r="H25" s="4">
+      <c r="H27" s="4">
         <v>6</v>
       </c>
-      <c r="I25" s="4">
+      <c r="I27" s="4">
         <v>5</v>
       </c>
-      <c r="J25" s="4">
+      <c r="J27" s="4">
         <v>6</v>
       </c>
-      <c r="K25" s="4">
+      <c r="K27" s="4">
         <v>6</v>
       </c>
-      <c r="L25" s="4">
+      <c r="L27" s="4">
         <v>6</v>
       </c>
-      <c r="M25" s="4">
+      <c r="M27" s="4">
         <v>7</v>
       </c>
-      <c r="N25" s="4">
+      <c r="N27" s="4">
         <v>6</v>
       </c>
-      <c r="O25" s="4">
+      <c r="O27" s="4">
         <v>7</v>
       </c>
-      <c r="P25" s="4">
+      <c r="P27" s="4">
         <v>8</v>
       </c>
-      <c r="Q25" s="4">
+      <c r="Q27" s="4">
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="19"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="4" t="s">
+    <row r="28" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="28"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="4">
-        <f t="shared" ref="D26:Q26" si="1">D8</f>
+      <c r="D28" s="4">
+        <f t="shared" ref="D28:Q28" si="1">D10</f>
         <v>200</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E28" s="4">
         <f t="shared" si="1"/>
         <v>250</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F28" s="4">
         <f t="shared" si="1"/>
         <v>250</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G28" s="4">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="H26" s="4">
+      <c r="H28" s="4">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="I26" s="4">
+      <c r="I28" s="4">
         <f t="shared" si="1"/>
         <v>300</v>
       </c>
-      <c r="J26" s="4">
+      <c r="J28" s="4">
         <f t="shared" si="1"/>
         <v>450</v>
       </c>
-      <c r="K26" s="4">
+      <c r="K28" s="4">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="L26" s="4">
+      <c r="L28" s="4">
         <f t="shared" si="1"/>
         <v>400</v>
       </c>
-      <c r="M26" s="4">
+      <c r="M28" s="4">
         <f t="shared" si="1"/>
         <v>900</v>
       </c>
-      <c r="N26" s="4">
+      <c r="N28" s="4">
         <f t="shared" si="1"/>
         <v>800</v>
       </c>
-      <c r="O26" s="4">
+      <c r="O28" s="4">
         <f t="shared" si="1"/>
         <v>800</v>
       </c>
-      <c r="P26" s="4">
+      <c r="P28" s="4">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="Q26" s="4">
+      <c r="Q28" s="4">
         <f t="shared" si="1"/>
         <v>700</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="19"/>
-      <c r="B27" s="34"/>
-      <c r="C27" s="4" t="s">
+    <row r="29" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="28"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-      <c r="E27" s="4">
-        <v>1</v>
-      </c>
-      <c r="F27" s="4">
-        <v>1</v>
-      </c>
-      <c r="G27" s="4">
-        <v>1</v>
-      </c>
-      <c r="H27" s="4">
-        <v>1</v>
-      </c>
-      <c r="I27" s="4">
-        <v>1</v>
-      </c>
-      <c r="J27" s="4">
-        <v>1</v>
-      </c>
-      <c r="K27" s="4">
-        <v>2</v>
-      </c>
-      <c r="L27" s="4">
-        <v>2</v>
-      </c>
-      <c r="M27" s="4">
-        <v>2</v>
-      </c>
-      <c r="N27" s="4">
-        <v>2</v>
-      </c>
-      <c r="O27" s="4">
-        <v>2</v>
-      </c>
-      <c r="P27" s="4">
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="4">
+        <v>1</v>
+      </c>
+      <c r="F29" s="4">
+        <v>1</v>
+      </c>
+      <c r="G29" s="4">
+        <v>1</v>
+      </c>
+      <c r="H29" s="4">
+        <v>1</v>
+      </c>
+      <c r="I29" s="4">
+        <v>1</v>
+      </c>
+      <c r="J29" s="4">
+        <v>1</v>
+      </c>
+      <c r="K29" s="4">
+        <v>2</v>
+      </c>
+      <c r="L29" s="4">
+        <v>2</v>
+      </c>
+      <c r="M29" s="4">
+        <v>2</v>
+      </c>
+      <c r="N29" s="4">
+        <v>2</v>
+      </c>
+      <c r="O29" s="4">
+        <v>2</v>
+      </c>
+      <c r="P29" s="4">
         <v>4</v>
       </c>
-      <c r="Q27" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="19"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="4" t="s">
+      <c r="Q29" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="28"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="19"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-    </row>
-    <row r="30" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="19"/>
-      <c r="B30" s="35" t="s">
+      <c r="J30" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="K30" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="L30" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="M30" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="N30" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="O30" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="P30" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="Q30" s="4">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="28"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+    </row>
+    <row r="32" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="28"/>
+      <c r="B32" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C32" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D32" s="4">
         <v>4</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E32" s="4">
         <v>4</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F32" s="4">
         <v>4</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G32" s="4">
         <v>4</v>
       </c>
-      <c r="H30" s="4">
+      <c r="H32" s="4">
         <v>5</v>
       </c>
-      <c r="I30" s="4">
+      <c r="I32" s="4">
         <v>4</v>
       </c>
-      <c r="J30" s="4">
+      <c r="J32" s="4">
         <v>5</v>
       </c>
-      <c r="K30" s="4">
+      <c r="K32" s="4">
         <v>5</v>
       </c>
-      <c r="L30" s="4">
+      <c r="L32" s="4">
         <v>5</v>
       </c>
-      <c r="M30" s="4">
+      <c r="M32" s="4">
         <v>6</v>
       </c>
-      <c r="N30" s="4">
+      <c r="N32" s="4">
         <v>5</v>
       </c>
-      <c r="O30" s="4">
+      <c r="O32" s="4">
         <v>6</v>
       </c>
-      <c r="P30" s="4">
+      <c r="P32" s="4">
         <v>6</v>
       </c>
-      <c r="Q30" s="4">
+      <c r="Q32" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="19"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="4" t="s">
+    <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="28"/>
+      <c r="B33" s="35"/>
+      <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="4">
-        <f>0.9*D26</f>
+      <c r="D33" s="4">
+        <f>0.9*D28</f>
         <v>180</v>
       </c>
-      <c r="E31" s="4">
-        <f t="shared" ref="E31:Q31" si="2">0.9*E26</f>
+      <c r="E33" s="4">
+        <f t="shared" ref="E33:Q33" si="2">0.9*E28</f>
         <v>225</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F33" s="4">
         <f t="shared" si="2"/>
         <v>225</v>
       </c>
-      <c r="G31" s="4">
+      <c r="G33" s="4">
         <f t="shared" si="2"/>
         <v>180</v>
       </c>
-      <c r="H31" s="4">
+      <c r="H33" s="4">
         <f t="shared" si="2"/>
         <v>450</v>
       </c>
-      <c r="I31" s="4">
+      <c r="I33" s="4">
         <f t="shared" si="2"/>
         <v>270</v>
       </c>
-      <c r="J31" s="4">
+      <c r="J33" s="4">
         <f t="shared" si="2"/>
         <v>405</v>
       </c>
-      <c r="K31" s="4">
+      <c r="K33" s="4">
         <f t="shared" si="2"/>
         <v>540</v>
       </c>
-      <c r="L31" s="4">
+      <c r="L33" s="4">
         <f t="shared" si="2"/>
         <v>360</v>
       </c>
-      <c r="M31" s="4">
+      <c r="M33" s="4">
         <f t="shared" si="2"/>
         <v>810</v>
       </c>
-      <c r="N31" s="4">
+      <c r="N33" s="4">
         <f t="shared" si="2"/>
         <v>720</v>
       </c>
-      <c r="O31" s="4">
+      <c r="O33" s="4">
         <f t="shared" si="2"/>
         <v>720</v>
       </c>
-      <c r="P31" s="4">
+      <c r="P33" s="4">
         <f t="shared" si="2"/>
         <v>900</v>
       </c>
-      <c r="Q31" s="4">
+      <c r="Q33" s="4">
         <f t="shared" si="2"/>
         <v>630</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="19"/>
-      <c r="B32" s="36"/>
-      <c r="C32" s="4" t="s">
+    <row r="34" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="28"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="4">
-        <v>1</v>
-      </c>
-      <c r="E32" s="4">
-        <v>1</v>
-      </c>
-      <c r="F32" s="4">
-        <v>1</v>
-      </c>
-      <c r="G32" s="4">
-        <v>1</v>
-      </c>
-      <c r="H32" s="4">
-        <v>1</v>
-      </c>
-      <c r="I32" s="4">
-        <v>1</v>
-      </c>
-      <c r="J32" s="4">
-        <v>1</v>
-      </c>
-      <c r="K32" s="4">
-        <v>2</v>
-      </c>
-      <c r="L32" s="4">
-        <v>2</v>
-      </c>
-      <c r="M32" s="4">
-        <v>2</v>
-      </c>
-      <c r="N32" s="4">
-        <v>2</v>
-      </c>
-      <c r="O32" s="4">
-        <v>2</v>
-      </c>
-      <c r="P32" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q32" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="19"/>
-      <c r="B33" s="37"/>
-      <c r="C33" s="4" t="s">
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+      <c r="E34" s="4">
+        <v>1</v>
+      </c>
+      <c r="F34" s="4">
+        <v>1</v>
+      </c>
+      <c r="G34" s="4">
+        <v>1</v>
+      </c>
+      <c r="H34" s="4">
+        <v>1</v>
+      </c>
+      <c r="I34" s="4">
+        <v>1</v>
+      </c>
+      <c r="J34" s="4">
+        <v>1</v>
+      </c>
+      <c r="K34" s="4">
+        <v>2</v>
+      </c>
+      <c r="L34" s="4">
+        <v>2</v>
+      </c>
+      <c r="M34" s="4">
+        <v>2</v>
+      </c>
+      <c r="N34" s="4">
+        <v>2</v>
+      </c>
+      <c r="O34" s="4">
+        <v>2</v>
+      </c>
+      <c r="P34" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q34" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="28"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="19"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="19"/>
-      <c r="B35" s="35" t="s">
+      <c r="J35" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="K35" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="L35" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="M35" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="N35" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="O35" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="P35" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="Q35" s="4">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="28"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="28"/>
+      <c r="B37" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C37" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="4">
-        <v>2</v>
-      </c>
-      <c r="E35" s="4">
-        <v>2</v>
-      </c>
-      <c r="F35" s="4">
-        <v>2</v>
-      </c>
-      <c r="G35" s="4">
-        <v>3</v>
-      </c>
-      <c r="H35" s="4">
-        <v>3</v>
-      </c>
-      <c r="I35" s="4">
-        <v>3</v>
-      </c>
-      <c r="J35" s="4">
-        <v>2</v>
-      </c>
-      <c r="K35" s="4">
-        <v>3</v>
-      </c>
-      <c r="L35" s="4">
-        <v>3</v>
-      </c>
-      <c r="M35" s="4">
+      <c r="D37" s="4">
+        <v>2</v>
+      </c>
+      <c r="E37" s="4">
+        <v>2</v>
+      </c>
+      <c r="F37" s="4">
+        <v>2</v>
+      </c>
+      <c r="G37" s="4">
+        <v>3</v>
+      </c>
+      <c r="H37" s="4">
+        <v>3</v>
+      </c>
+      <c r="I37" s="4">
+        <v>3</v>
+      </c>
+      <c r="J37" s="4">
+        <v>2</v>
+      </c>
+      <c r="K37" s="4">
+        <v>3</v>
+      </c>
+      <c r="L37" s="4">
+        <v>3</v>
+      </c>
+      <c r="M37" s="4">
         <v>4</v>
       </c>
-      <c r="N35" s="4">
-        <v>3</v>
-      </c>
-      <c r="O35" s="4">
+      <c r="N37" s="4">
+        <v>3</v>
+      </c>
+      <c r="O37" s="4">
         <v>4</v>
       </c>
-      <c r="P35" s="4">
+      <c r="P37" s="4">
         <v>4</v>
       </c>
-      <c r="Q35" s="4">
+      <c r="Q37" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="19"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="4" t="s">
+    <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="28"/>
+      <c r="B38" s="35"/>
+      <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D36" s="4">
-        <f>0.6*D26</f>
+      <c r="D38" s="4">
+        <f>0.6*D28</f>
         <v>120</v>
       </c>
-      <c r="E36" s="4">
-        <f t="shared" ref="E36:Q36" si="3">0.6*E26</f>
+      <c r="E38" s="4">
+        <f t="shared" ref="E38:Q38" si="3">0.6*E28</f>
         <v>150</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F38" s="4">
         <f t="shared" si="3"/>
         <v>150</v>
       </c>
-      <c r="G36" s="4">
+      <c r="G38" s="4">
         <f t="shared" si="3"/>
         <v>120</v>
       </c>
-      <c r="H36" s="4">
+      <c r="H38" s="4">
         <f t="shared" si="3"/>
         <v>300</v>
       </c>
-      <c r="I36" s="4">
+      <c r="I38" s="4">
         <f t="shared" si="3"/>
         <v>180</v>
       </c>
-      <c r="J36" s="4">
+      <c r="J38" s="4">
         <f t="shared" si="3"/>
         <v>270</v>
       </c>
-      <c r="K36" s="4">
+      <c r="K38" s="4">
         <f t="shared" si="3"/>
         <v>360</v>
       </c>
-      <c r="L36" s="4">
+      <c r="L38" s="4">
         <f t="shared" si="3"/>
         <v>240</v>
       </c>
-      <c r="M36" s="4">
+      <c r="M38" s="4">
         <f t="shared" si="3"/>
         <v>540</v>
       </c>
-      <c r="N36" s="4">
+      <c r="N38" s="4">
         <f t="shared" si="3"/>
         <v>480</v>
       </c>
-      <c r="O36" s="4">
+      <c r="O38" s="4">
         <f t="shared" si="3"/>
         <v>480</v>
       </c>
-      <c r="P36" s="4">
+      <c r="P38" s="4">
         <f t="shared" si="3"/>
         <v>600</v>
       </c>
-      <c r="Q36" s="4">
+      <c r="Q38" s="4">
         <f t="shared" si="3"/>
         <v>420</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="19"/>
-      <c r="B37" s="36"/>
-      <c r="C37" s="4" t="s">
+    <row r="39" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="28"/>
+      <c r="B39" s="35"/>
+      <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D37" s="4">
-        <v>1</v>
-      </c>
-      <c r="E37" s="4">
-        <v>1</v>
-      </c>
-      <c r="F37" s="4">
-        <v>1</v>
-      </c>
-      <c r="G37" s="4">
-        <v>1</v>
-      </c>
-      <c r="H37" s="4">
-        <v>1</v>
-      </c>
-      <c r="I37" s="4">
-        <v>2</v>
-      </c>
-      <c r="J37" s="4">
-        <v>1</v>
-      </c>
-      <c r="K37" s="4">
-        <v>2</v>
-      </c>
-      <c r="L37" s="4">
-        <v>2</v>
-      </c>
-      <c r="M37" s="4">
-        <v>2</v>
-      </c>
-      <c r="N37" s="4">
-        <v>2</v>
-      </c>
-      <c r="O37" s="4">
-        <v>2</v>
-      </c>
-      <c r="P37" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q37" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="19"/>
-      <c r="B38" s="37"/>
-      <c r="C38" s="4" t="s">
+      <c r="D39" s="4">
+        <v>1</v>
+      </c>
+      <c r="E39" s="4">
+        <v>1</v>
+      </c>
+      <c r="F39" s="4">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4">
+        <v>1</v>
+      </c>
+      <c r="H39" s="4">
+        <v>1</v>
+      </c>
+      <c r="I39" s="4">
+        <v>2</v>
+      </c>
+      <c r="J39" s="4">
+        <v>1</v>
+      </c>
+      <c r="K39" s="4">
+        <v>2</v>
+      </c>
+      <c r="L39" s="4">
+        <v>2</v>
+      </c>
+      <c r="M39" s="4">
+        <v>2</v>
+      </c>
+      <c r="N39" s="4">
+        <v>2</v>
+      </c>
+      <c r="O39" s="4">
+        <v>2</v>
+      </c>
+      <c r="P39" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q39" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="28"/>
+      <c r="B40" s="36"/>
+      <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="39" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="19"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-    </row>
-    <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="19"/>
-      <c r="B40" s="35" t="s">
+      <c r="J40" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="K40" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="L40" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="M40" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="N40" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="O40" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="P40" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="Q40" s="4">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="28"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+    </row>
+    <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="28"/>
+      <c r="B42" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C42" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D40" s="4">
-        <f>0.9*D26</f>
+      <c r="D42" s="4">
+        <f>0.9*D28</f>
         <v>180</v>
       </c>
-      <c r="E40" s="4">
-        <f t="shared" ref="E40:Q40" si="4">0.9*E26</f>
+      <c r="E42" s="4">
+        <f t="shared" ref="E42:Q42" si="4">0.9*E28</f>
         <v>225</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F42" s="4">
         <f t="shared" si="4"/>
         <v>225</v>
       </c>
-      <c r="G40" s="4">
+      <c r="G42" s="4">
         <f t="shared" si="4"/>
         <v>180</v>
       </c>
-      <c r="H40" s="4">
+      <c r="H42" s="4">
         <f t="shared" si="4"/>
         <v>450</v>
       </c>
-      <c r="I40" s="4">
+      <c r="I42" s="4">
         <f t="shared" si="4"/>
         <v>270</v>
       </c>
-      <c r="J40" s="4">
+      <c r="J42" s="4">
         <f t="shared" si="4"/>
         <v>405</v>
       </c>
-      <c r="K40" s="4">
+      <c r="K42" s="4">
         <f t="shared" si="4"/>
         <v>540</v>
       </c>
-      <c r="L40" s="4">
+      <c r="L42" s="4">
         <f t="shared" si="4"/>
         <v>360</v>
       </c>
-      <c r="M40" s="4">
+      <c r="M42" s="4">
         <f t="shared" si="4"/>
         <v>810</v>
       </c>
-      <c r="N40" s="4">
+      <c r="N42" s="4">
         <f t="shared" si="4"/>
         <v>720</v>
       </c>
-      <c r="O40" s="4">
+      <c r="O42" s="4">
         <f t="shared" si="4"/>
         <v>720</v>
       </c>
-      <c r="P40" s="4">
+      <c r="P42" s="4">
         <f t="shared" si="4"/>
         <v>900</v>
       </c>
-      <c r="Q40" s="4">
+      <c r="Q42" s="4">
         <f t="shared" si="4"/>
         <v>630</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="19"/>
-      <c r="B41" s="36"/>
-      <c r="C41" s="4" t="s">
+    <row r="43" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="28"/>
+      <c r="B43" s="35"/>
+      <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D41" s="4">
-        <v>1</v>
-      </c>
-      <c r="E41" s="4">
-        <v>1</v>
-      </c>
-      <c r="F41" s="4">
-        <v>1</v>
-      </c>
-      <c r="G41" s="4">
-        <v>1</v>
-      </c>
-      <c r="H41" s="4">
-        <v>1</v>
-      </c>
-      <c r="I41" s="4">
-        <v>1</v>
-      </c>
-      <c r="J41" s="4">
-        <v>1</v>
-      </c>
-      <c r="K41" s="4">
-        <v>2</v>
-      </c>
-      <c r="L41" s="4">
-        <v>2</v>
-      </c>
-      <c r="M41" s="4">
-        <v>2</v>
-      </c>
-      <c r="N41" s="4">
-        <v>2</v>
-      </c>
-      <c r="O41" s="4">
-        <v>2</v>
-      </c>
-      <c r="P41" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q41" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="19"/>
-      <c r="B42" s="37"/>
-      <c r="C42" s="4" t="s">
+      <c r="D43" s="4">
+        <v>1</v>
+      </c>
+      <c r="E43" s="4">
+        <v>1</v>
+      </c>
+      <c r="F43" s="4">
+        <v>1</v>
+      </c>
+      <c r="G43" s="4">
+        <v>1</v>
+      </c>
+      <c r="H43" s="4">
+        <v>1</v>
+      </c>
+      <c r="I43" s="4">
+        <v>1</v>
+      </c>
+      <c r="J43" s="4">
+        <v>1</v>
+      </c>
+      <c r="K43" s="4">
+        <v>2</v>
+      </c>
+      <c r="L43" s="4">
+        <v>2</v>
+      </c>
+      <c r="M43" s="4">
+        <v>2</v>
+      </c>
+      <c r="N43" s="4">
+        <v>2</v>
+      </c>
+      <c r="O43" s="4">
+        <v>2</v>
+      </c>
+      <c r="P43" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q43" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="28"/>
+      <c r="B44" s="36"/>
+      <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="43" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="19"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-    </row>
-    <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="19"/>
-      <c r="B44" s="35" t="s">
+      <c r="J44" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="K44" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="L44" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="M44" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="N44" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="O44" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="P44" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="Q44" s="4">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="28"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+    </row>
+    <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="28"/>
+      <c r="B46" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="C44" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="19"/>
-      <c r="B45" s="36"/>
-      <c r="C45" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="19"/>
-      <c r="B46" s="37"/>
       <c r="C46" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="19"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="28"/>
+      <c r="B47" s="35"/>
+      <c r="C47" s="4">
+        <v>2</v>
+      </c>
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="19"/>
-      <c r="B48" s="35" t="s">
+      <c r="A48" s="28"/>
+      <c r="B48" s="36"/>
+      <c r="C48" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="28"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+    </row>
+    <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="28"/>
+      <c r="B50" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C50" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D48" s="4">
-        <f t="shared" ref="D48:Q48" si="5">D20+D25+D30+D35</f>
+      <c r="D50" s="4">
+        <f t="shared" ref="D50:Q50" si="5">D22+D27+D32+D37</f>
         <v>13</v>
       </c>
-      <c r="E48" s="4">
+      <c r="E50" s="4">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="F48" s="4">
+      <c r="F50" s="4">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
-      <c r="G48" s="4">
+      <c r="G50" s="4">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
-      <c r="H48" s="4">
+      <c r="H50" s="4">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="I48" s="4">
+      <c r="I50" s="4">
         <f t="shared" si="5"/>
         <v>16</v>
       </c>
-      <c r="J48" s="4">
+      <c r="J50" s="4">
         <f t="shared" si="5"/>
         <v>16</v>
       </c>
-      <c r="K48" s="4">
+      <c r="K50" s="4">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="L48" s="4">
+      <c r="L50" s="4">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="M48" s="4">
+      <c r="M50" s="4">
         <f t="shared" si="5"/>
         <v>22</v>
       </c>
-      <c r="N48" s="4">
+      <c r="N50" s="4">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="O48" s="4">
+      <c r="O50" s="4">
         <f t="shared" si="5"/>
         <v>22</v>
       </c>
-      <c r="P48" s="4">
+      <c r="P50" s="4">
         <f t="shared" si="5"/>
         <v>23</v>
       </c>
-      <c r="Q48" s="4">
+      <c r="Q50" s="4">
         <f t="shared" si="5"/>
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="19"/>
-      <c r="B49" s="36"/>
-      <c r="C49" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D49" s="4">
-        <f t="shared" ref="D49:Q49" si="6">D22+D27+D32+D37+D41</f>
+    <row r="51" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="28"/>
+      <c r="B51" s="35"/>
+      <c r="C51" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D51" s="4">
+        <f t="shared" ref="D51:Q51" si="6">D24+D29+D34+D39+D43</f>
         <v>5</v>
       </c>
-      <c r="E49" s="4">
+      <c r="E51" s="4">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="F49" s="4">
+      <c r="F51" s="4">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="G49" s="4">
+      <c r="G51" s="4">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="H49" s="4">
+      <c r="H51" s="4">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="I49" s="4">
+      <c r="I51" s="4">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="J49" s="4">
+      <c r="J51" s="4">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="K49" s="4">
+      <c r="K51" s="4">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="L49" s="4">
+      <c r="L51" s="4">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="M49" s="4">
+      <c r="M51" s="4">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="N49" s="4">
+      <c r="N51" s="4">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="O49" s="4">
+      <c r="O51" s="4">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="P49" s="4">
+      <c r="P51" s="4">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="Q49" s="4">
+      <c r="Q51" s="4">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="19"/>
-      <c r="B50" s="37"/>
-      <c r="C50" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D50" s="4">
-        <f>D48*(1+D49*0.02)</f>
+    <row r="52" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="28"/>
+      <c r="B52" s="36"/>
+      <c r="C52" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D52" s="4">
+        <f>D50*(1+D51*0.02)</f>
         <v>14.3</v>
       </c>
-      <c r="E50" s="4">
-        <f>E48*(1+E49*0.02)</f>
+      <c r="E52" s="4">
+        <f>E50*(1+E51*0.02)</f>
         <v>14.3</v>
       </c>
-      <c r="F50" s="4">
-        <f t="shared" ref="F50:M50" si="7">F48*(1+F49*0.02)</f>
+      <c r="F52" s="4">
+        <f t="shared" ref="F52:M52" si="7">F50*(1+F51*0.02)</f>
         <v>15.400000000000002</v>
       </c>
-      <c r="G50" s="4">
+      <c r="G52" s="4">
         <f t="shared" si="7"/>
         <v>15.400000000000002</v>
       </c>
-      <c r="H50" s="4">
+      <c r="H52" s="4">
         <f t="shared" si="7"/>
         <v>19.8</v>
       </c>
-      <c r="I50" s="4">
+      <c r="I52" s="4">
         <f t="shared" si="7"/>
         <v>18.240000000000002</v>
       </c>
-      <c r="J50" s="4">
+      <c r="J52" s="4">
         <f t="shared" si="7"/>
         <v>17.600000000000001</v>
       </c>
-      <c r="K50" s="4">
+      <c r="K52" s="4">
         <f t="shared" si="7"/>
         <v>21.599999999999998</v>
       </c>
-      <c r="L50" s="4">
+      <c r="L52" s="4">
         <f t="shared" si="7"/>
         <v>21.599999999999998</v>
       </c>
-      <c r="M50" s="4">
+      <c r="M52" s="4">
         <f t="shared" si="7"/>
         <v>26.4</v>
       </c>
-      <c r="N50" s="4">
-        <f t="shared" ref="N50" si="8">N48*(1+N49*0.02)</f>
+      <c r="N52" s="4">
+        <f t="shared" ref="N52" si="8">N50*(1+N51*0.02)</f>
         <v>21.599999999999998</v>
       </c>
-      <c r="O50" s="4">
-        <f t="shared" ref="O50" si="9">O48*(1+O49*0.02)</f>
+      <c r="O52" s="4">
+        <f t="shared" ref="O52" si="9">O50*(1+O51*0.02)</f>
         <v>26.4</v>
       </c>
-      <c r="P50" s="4">
-        <f t="shared" ref="P50" si="10">P48*(1+P49*0.02)</f>
+      <c r="P52" s="4">
+        <f t="shared" ref="P52" si="10">P50*(1+P51*0.02)</f>
         <v>28.52</v>
       </c>
-      <c r="Q50" s="4">
-        <f t="shared" ref="Q50" si="11">Q48*(1+Q49*0.02)</f>
+      <c r="Q52" s="4">
+        <f t="shared" ref="Q52" si="11">Q50*(1+Q51*0.02)</f>
         <v>26.4</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="2"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-    </row>
-    <row r="52" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="B52" s="33" t="s">
+    <row r="53" spans="1:17" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="2"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+    </row>
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="B54" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C54" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="20"/>
-      <c r="B53" s="20"/>
-      <c r="C53" s="5" t="s">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="29"/>
+      <c r="B55" s="29"/>
+      <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="20"/>
-      <c r="B54" s="20"/>
-      <c r="C54" s="5" t="s">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="29"/>
+      <c r="B56" s="29"/>
+      <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="20"/>
-      <c r="B55" s="21"/>
-      <c r="C55" s="5" t="s">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="29"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="20"/>
-      <c r="B56" s="33" t="s">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="29"/>
+      <c r="B58" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="C56" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="20"/>
-      <c r="B57" s="20"/>
-      <c r="C57" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="20"/>
-      <c r="B58" s="21"/>
       <c r="C58" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="20"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="29"/>
+      <c r="B59" s="29"/>
+      <c r="C59" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="20"/>
-      <c r="B60" s="33" t="s">
+      <c r="A60" s="29"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="29"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+    </row>
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="29"/>
+      <c r="B62" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="20"/>
-      <c r="B61" s="20"/>
-      <c r="C61" s="5" t="s">
+      <c r="C62" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="29"/>
+      <c r="B63" s="29"/>
+      <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="21"/>
-      <c r="B62" s="21"/>
-      <c r="C62" s="5" t="s">
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="30"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="28" t="s">
+    <row r="65" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B66" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C66" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D64" s="6">
-        <v>1</v>
-      </c>
-      <c r="E64" s="6">
-        <v>1</v>
-      </c>
-      <c r="F64" s="6">
-        <v>1</v>
-      </c>
-      <c r="G64" s="6">
-        <v>1</v>
-      </c>
-      <c r="H64" s="6">
-        <v>1</v>
-      </c>
-      <c r="I64" s="6">
-        <v>1</v>
-      </c>
-      <c r="J64" s="6">
-        <v>1</v>
-      </c>
-      <c r="K64" s="6">
-        <v>1</v>
-      </c>
-      <c r="L64" s="6">
-        <v>1</v>
-      </c>
-      <c r="M64" s="6">
-        <v>1</v>
-      </c>
-      <c r="N64" s="6">
-        <v>1</v>
-      </c>
-      <c r="O64" s="6">
-        <v>1</v>
-      </c>
-      <c r="P64" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q64" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="29"/>
-      <c r="B65" s="4" t="s">
+      <c r="D66" s="6">
+        <v>1</v>
+      </c>
+      <c r="E66" s="6">
+        <v>1</v>
+      </c>
+      <c r="F66" s="6">
+        <v>1</v>
+      </c>
+      <c r="G66" s="6">
+        <v>1</v>
+      </c>
+      <c r="H66" s="6">
+        <v>1</v>
+      </c>
+      <c r="I66" s="6">
+        <v>1</v>
+      </c>
+      <c r="J66" s="6">
+        <v>1</v>
+      </c>
+      <c r="K66" s="6">
+        <v>1</v>
+      </c>
+      <c r="L66" s="6">
+        <v>1</v>
+      </c>
+      <c r="M66" s="6">
+        <v>1</v>
+      </c>
+      <c r="N66" s="6">
+        <v>1</v>
+      </c>
+      <c r="O66" s="6">
+        <v>1</v>
+      </c>
+      <c r="P66" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q66" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="21"/>
+      <c r="B67" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F67" s="4">
+        <v>1</v>
+      </c>
+      <c r="G67" s="4">
+        <v>1</v>
+      </c>
+      <c r="H67" s="4">
+        <v>1</v>
+      </c>
+      <c r="I67" s="4">
+        <v>1</v>
+      </c>
+      <c r="J67" s="4">
+        <v>1</v>
+      </c>
+      <c r="K67" s="4">
+        <v>1</v>
+      </c>
+      <c r="L67" s="4">
+        <v>0</v>
+      </c>
+      <c r="M67" s="4">
+        <v>1</v>
+      </c>
+      <c r="N67" s="4">
+        <v>1</v>
+      </c>
+      <c r="O67" s="4">
+        <v>1</v>
+      </c>
+      <c r="P67" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q67" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="21"/>
+      <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C65" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F65" s="4">
-        <v>1</v>
-      </c>
-      <c r="G65" s="4">
-        <v>1</v>
-      </c>
-      <c r="H65" s="4">
-        <v>1</v>
-      </c>
-      <c r="I65" s="4">
-        <v>1</v>
-      </c>
-      <c r="J65" s="4">
-        <v>1</v>
-      </c>
-      <c r="K65" s="4">
-        <v>1</v>
-      </c>
-      <c r="L65" s="4">
-        <v>0</v>
-      </c>
-      <c r="M65" s="4">
-        <v>1</v>
-      </c>
-      <c r="N65" s="4">
-        <v>1</v>
-      </c>
-      <c r="O65" s="4">
-        <v>1</v>
-      </c>
-      <c r="P65" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q65" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="29"/>
-      <c r="B66" s="4" t="s">
+      <c r="C68" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F68" s="4">
+        <v>1</v>
+      </c>
+      <c r="G68" s="4">
+        <v>1</v>
+      </c>
+      <c r="H68" s="4">
+        <v>1</v>
+      </c>
+      <c r="I68" s="4">
+        <v>1</v>
+      </c>
+      <c r="J68" s="4">
+        <v>1</v>
+      </c>
+      <c r="K68" s="4">
+        <v>1</v>
+      </c>
+      <c r="L68" s="4">
+        <v>0</v>
+      </c>
+      <c r="M68" s="4">
+        <v>1</v>
+      </c>
+      <c r="N68" s="4">
+        <v>1</v>
+      </c>
+      <c r="O68" s="4">
+        <v>1</v>
+      </c>
+      <c r="P68" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q68" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="22"/>
+      <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C66" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F66" s="4">
-        <v>1</v>
-      </c>
-      <c r="G66" s="4">
-        <v>1</v>
-      </c>
-      <c r="H66" s="4">
-        <v>1</v>
-      </c>
-      <c r="I66" s="4">
-        <v>1</v>
-      </c>
-      <c r="J66" s="4">
-        <v>1</v>
-      </c>
-      <c r="K66" s="4">
-        <v>1</v>
-      </c>
-      <c r="L66" s="4">
-        <v>0</v>
-      </c>
-      <c r="M66" s="4">
-        <v>1</v>
-      </c>
-      <c r="N66" s="4">
-        <v>1</v>
-      </c>
-      <c r="O66" s="4">
-        <v>1</v>
-      </c>
-      <c r="P66" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q66" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="30"/>
-      <c r="B67" s="5" t="s">
+      <c r="C69" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>136</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="A7:A18"/>
-    <mergeCell ref="B60:B62"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="A20:A50"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="A52:A62"/>
-    <mergeCell ref="B52:B55"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A9:A20"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="A22:A52"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="A54:A64"/>
+    <mergeCell ref="B54:B57"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4585,98 +4957,98 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="U4" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="V4" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="AA4" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="AA4" s="1" t="s">
+      <c r="AB4" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="AB4" s="1" t="s">
+      <c r="AC4" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="AC4" s="1" t="s">
+      <c r="AD4" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="AD4" s="1" t="s">
+      <c r="AE4" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="AE4" s="1" t="s">
+      <c r="AF4" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="AF4" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:32" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -4770,7 +5142,7 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -4861,10 +5233,10 @@
       </c>
     </row>
     <row r="7" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="B7" s="16" t="s">
+      <c r="A7" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" s="25" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -4875,8 +5247,8 @@
       </c>
     </row>
     <row r="8" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18"/>
-      <c r="B8" s="16"/>
+      <c r="A8" s="27"/>
+      <c r="B8" s="25"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
@@ -4885,8 +5257,8 @@
       </c>
     </row>
     <row r="9" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="18"/>
-      <c r="B9" s="16"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="25"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
@@ -4895,8 +5267,8 @@
       </c>
     </row>
     <row r="10" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="18"/>
-      <c r="B10" s="16"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="25"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -4905,8 +5277,8 @@
       </c>
     </row>
     <row r="11" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="16" t="s">
+      <c r="A11" s="27"/>
+      <c r="B11" s="25" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
@@ -4914,25 +5286,25 @@
       </c>
     </row>
     <row r="12" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
-      <c r="B12" s="16"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="25"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="18"/>
-      <c r="B13" s="16"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="25"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:32" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="18"/>
+      <c r="A14" s="27"/>
     </row>
     <row r="15" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="18"/>
-      <c r="B15" s="22" t="s">
+      <c r="A15" s="27"/>
+      <c r="B15" s="31" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -4943,8 +5315,8 @@
       </c>
     </row>
     <row r="16" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="18"/>
-      <c r="B16" s="23"/>
+      <c r="A16" s="27"/>
+      <c r="B16" s="32"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
@@ -4953,8 +5325,8 @@
       </c>
     </row>
     <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="18"/>
-      <c r="B17" s="23"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="32"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
@@ -4963,8 +5335,8 @@
       </c>
     </row>
     <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="18"/>
-      <c r="B18" s="24"/>
+      <c r="A18" s="27"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
@@ -4979,10 +5351,10 @@
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="B20" s="34" t="s">
+      <c r="A20" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" s="38" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -4990,36 +5362,36 @@
       </c>
     </row>
     <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="19"/>
-      <c r="B21" s="34"/>
+      <c r="A21" s="28"/>
+      <c r="B21" s="38"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="19"/>
-      <c r="B22" s="34"/>
+      <c r="A22" s="28"/>
+      <c r="B22" s="38"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="19"/>
-      <c r="B23" s="34"/>
+      <c r="A23" s="28"/>
+      <c r="B23" s="38"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="19"/>
+      <c r="A24" s="28"/>
       <c r="B24" s="12"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="19"/>
-      <c r="B25" s="34" t="s">
+      <c r="A25" s="28"/>
+      <c r="B25" s="38" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="4" t="s">
@@ -5027,36 +5399,36 @@
       </c>
     </row>
     <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="19"/>
-      <c r="B26" s="34"/>
+      <c r="A26" s="28"/>
+      <c r="B26" s="38"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="19"/>
-      <c r="B27" s="34"/>
+      <c r="A27" s="28"/>
+      <c r="B27" s="38"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="19"/>
-      <c r="B28" s="34"/>
+      <c r="A28" s="28"/>
+      <c r="B28" s="38"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="19"/>
+      <c r="A29" s="28"/>
       <c r="B29" s="13"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="19"/>
-      <c r="B30" s="35" t="s">
+      <c r="A30" s="28"/>
+      <c r="B30" s="34" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -5064,36 +5436,36 @@
       </c>
     </row>
     <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="19"/>
-      <c r="B31" s="36"/>
+      <c r="A31" s="28"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="19"/>
-      <c r="B32" s="36"/>
+      <c r="A32" s="28"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="19"/>
-      <c r="B33" s="37"/>
+      <c r="A33" s="28"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="19"/>
+      <c r="A34" s="28"/>
       <c r="B34" s="14"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="19"/>
-      <c r="B35" s="35" t="s">
+      <c r="A35" s="28"/>
+      <c r="B35" s="34" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -5101,36 +5473,36 @@
       </c>
     </row>
     <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="19"/>
-      <c r="B36" s="36"/>
+      <c r="A36" s="28"/>
+      <c r="B36" s="35"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="19"/>
-      <c r="B37" s="36"/>
+      <c r="A37" s="28"/>
+      <c r="B37" s="35"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="19"/>
-      <c r="B38" s="37"/>
+      <c r="A38" s="28"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="19"/>
+      <c r="A39" s="28"/>
       <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="19"/>
-      <c r="B40" s="35" t="s">
+      <c r="A40" s="28"/>
+      <c r="B40" s="34" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
@@ -5138,27 +5510,27 @@
       </c>
     </row>
     <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="19"/>
-      <c r="B41" s="36"/>
+      <c r="A41" s="28"/>
+      <c r="B41" s="35"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="19"/>
-      <c r="B42" s="37"/>
+      <c r="A42" s="28"/>
+      <c r="B42" s="36"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="19"/>
+      <c r="A43" s="28"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="19"/>
-      <c r="B44" s="35" t="s">
+      <c r="A44" s="28"/>
+      <c r="B44" s="34" t="s">
         <v>30</v>
       </c>
       <c r="C44" s="4">
@@ -5166,29 +5538,29 @@
       </c>
     </row>
     <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="19"/>
-      <c r="B45" s="36"/>
+      <c r="A45" s="28"/>
+      <c r="B45" s="35"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="19"/>
-      <c r="B46" s="37"/>
+      <c r="A46" s="28"/>
+      <c r="B46" s="36"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="19"/>
+      <c r="A47" s="28"/>
       <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="19"/>
-      <c r="B48" s="35" t="s">
+      <c r="A48" s="28"/>
+      <c r="B48" s="34" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="4" t="s">
@@ -5252,10 +5624,10 @@
       </c>
     </row>
     <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="19"/>
-      <c r="B49" s="36"/>
+      <c r="A49" s="28"/>
+      <c r="B49" s="35"/>
       <c r="C49" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D49" s="4">
         <f t="shared" ref="D49:Q49" si="1">D22+D27+D32+D37+D41</f>
@@ -5315,10 +5687,10 @@
       </c>
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="19"/>
-      <c r="B50" s="37"/>
+      <c r="A50" s="28"/>
+      <c r="B50" s="36"/>
       <c r="C50" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D50" s="4">
         <f>D48*(1+D49*0.02)</f>
@@ -5383,10 +5755,10 @@
       <c r="C51" s="8"/>
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="B52" s="33" t="s">
+      <c r="A52" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="B52" s="37" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="5" t="s">
@@ -5394,29 +5766,29 @@
       </c>
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="20"/>
-      <c r="B53" s="20"/>
+      <c r="A53" s="29"/>
+      <c r="B53" s="29"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="20"/>
-      <c r="B54" s="20"/>
+      <c r="A54" s="29"/>
+      <c r="B54" s="29"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="20"/>
-      <c r="B55" s="21"/>
+      <c r="A55" s="29"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="20"/>
-      <c r="B56" s="33" t="s">
+      <c r="A56" s="29"/>
+      <c r="B56" s="37" t="s">
         <v>30</v>
       </c>
       <c r="C56" s="5">
@@ -5424,29 +5796,29 @@
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="20"/>
-      <c r="B57" s="20"/>
+      <c r="A57" s="29"/>
+      <c r="B57" s="29"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="20"/>
-      <c r="B58" s="21"/>
+      <c r="A58" s="29"/>
+      <c r="B58" s="30"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="20"/>
+      <c r="A59" s="29"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="20"/>
-      <c r="B60" s="33" t="s">
+      <c r="A60" s="29"/>
+      <c r="B60" s="37" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
@@ -5454,22 +5826,22 @@
       </c>
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="20"/>
-      <c r="B61" s="20"/>
+      <c r="A61" s="29"/>
+      <c r="B61" s="29"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="21"/>
-      <c r="B62" s="21"/>
+      <c r="A62" s="30"/>
+      <c r="B62" s="30"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="28" t="s">
+      <c r="A64" s="20" t="s">
         <v>26</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -5480,38 +5852,34 @@
       </c>
     </row>
     <row r="65" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="29"/>
+      <c r="A65" s="21"/>
       <c r="B65" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="21"/>
+      <c r="B66" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C65" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="29"/>
-      <c r="B66" s="4" t="s">
+      <c r="C66" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="22"/>
+      <c r="B67" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C66" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="30"/>
-      <c r="B67" s="5" t="s">
+      <c r="C67" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>136</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A64:A67"/>
     <mergeCell ref="A7:A18"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B7:B10"/>
@@ -5525,6 +5893,10 @@
     <mergeCell ref="B52:B55"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A64:A67"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5533,6 +5905,824 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC6F473E-E8F6-46BD-8C8C-636A58FA8F6F}">
+  <dimension ref="A1:AF67"/>
+  <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="3" width="16.625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:32" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
+      <c r="AE4" s="1"/>
+      <c r="AF4" s="1"/>
+    </row>
+    <row r="5" spans="1:32" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="1">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
+      <c r="AD5" s="1"/>
+      <c r="AE5" s="1"/>
+      <c r="AF5" s="1"/>
+    </row>
+    <row r="6" spans="1:32" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1">
+        <v>3</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="1"/>
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="1"/>
+    </row>
+    <row r="7" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="27"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="27"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="27"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="27"/>
+      <c r="B11" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="27"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="27"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="27"/>
+    </row>
+    <row r="15" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="27"/>
+      <c r="B15" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="27"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="27"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="27"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+    </row>
+    <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="28"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="28"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="28"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="28"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+    </row>
+    <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="28"/>
+      <c r="B25" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="28"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="28"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="28"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="28"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+    </row>
+    <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="28"/>
+      <c r="B30" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="28"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="28"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="28"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="28"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="28"/>
+      <c r="B35" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="28"/>
+      <c r="B36" s="35"/>
+      <c r="C36" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="28"/>
+      <c r="B37" s="35"/>
+      <c r="C37" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="28"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="28"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+    </row>
+    <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="28"/>
+      <c r="B40" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="28"/>
+      <c r="B41" s="35"/>
+      <c r="C41" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="28"/>
+      <c r="B42" s="36"/>
+      <c r="C42" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="28"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+    </row>
+    <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="28"/>
+      <c r="B44" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="28"/>
+      <c r="B45" s="35"/>
+      <c r="C45" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="28"/>
+      <c r="B46" s="36"/>
+      <c r="C46" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="28"/>
+      <c r="B47" s="15"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+    </row>
+    <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="28"/>
+      <c r="B48" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D48" s="4">
+        <f t="shared" ref="D48:Q48" si="0">D20+D25+D30+D35</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="28"/>
+      <c r="B49" s="35"/>
+      <c r="C49" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D49" s="4">
+        <f t="shared" ref="D49:Q49" si="1">D22+D27+D32+D37+D41</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="28"/>
+      <c r="B50" s="36"/>
+      <c r="C50" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D50" s="4">
+        <f>D48*(1+D49*0.02)</f>
+        <v>0</v>
+      </c>
+      <c r="E50" s="4">
+        <f>E48*(1+E49*0.02)</f>
+        <v>0</v>
+      </c>
+      <c r="F50" s="4">
+        <f t="shared" ref="F50:Q50" si="2">F48*(1+F49*0.02)</f>
+        <v>0</v>
+      </c>
+      <c r="G50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="2"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+    </row>
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="B52" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="29"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="29"/>
+      <c r="B54" s="29"/>
+      <c r="C54" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="29"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="29"/>
+      <c r="B56" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="29"/>
+      <c r="B57" s="29"/>
+      <c r="C57" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="29"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="29"/>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+    </row>
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="29"/>
+      <c r="B60" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="29"/>
+      <c r="B61" s="29"/>
+      <c r="C61" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="30"/>
+      <c r="B62" s="30"/>
+      <c r="C62" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="21"/>
+      <c r="B65" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="21"/>
+      <c r="B66" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="22"/>
+      <c r="B67" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A7:A18"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="A20:A50"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="A64:A67"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A52:A62"/>
+    <mergeCell ref="B52:B55"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="B60:B62"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C5AF949-03E5-4E6E-B7CB-0D2F8A5AE350}">
   <dimension ref="A1:Q67"/>
   <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5559,44 +6749,44 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:14" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -5636,7 +6826,7 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -5673,10 +6863,10 @@
       </c>
     </row>
     <row r="7" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="B7" s="16" t="s">
+      <c r="A7" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" s="25" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -5687,8 +6877,8 @@
       </c>
     </row>
     <row r="8" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18"/>
-      <c r="B8" s="16"/>
+      <c r="A8" s="27"/>
+      <c r="B8" s="25"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
@@ -5697,8 +6887,8 @@
       </c>
     </row>
     <row r="9" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="18"/>
-      <c r="B9" s="16"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="25"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
@@ -5707,8 +6897,8 @@
       </c>
     </row>
     <row r="10" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="18"/>
-      <c r="B10" s="16"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="25"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -5717,8 +6907,8 @@
       </c>
     </row>
     <row r="11" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="16" t="s">
+      <c r="A11" s="27"/>
+      <c r="B11" s="25" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
@@ -5726,25 +6916,25 @@
       </c>
     </row>
     <row r="12" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
-      <c r="B12" s="16"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="25"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="18"/>
-      <c r="B13" s="16"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="25"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="18"/>
+      <c r="A14" s="27"/>
     </row>
     <row r="15" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="18"/>
-      <c r="B15" s="22" t="s">
+      <c r="A15" s="27"/>
+      <c r="B15" s="31" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -5755,8 +6945,8 @@
       </c>
     </row>
     <row r="16" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="18"/>
-      <c r="B16" s="23"/>
+      <c r="A16" s="27"/>
+      <c r="B16" s="32"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
@@ -5765,8 +6955,8 @@
       </c>
     </row>
     <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="18"/>
-      <c r="B17" s="23"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="32"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
@@ -5775,8 +6965,8 @@
       </c>
     </row>
     <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="18"/>
-      <c r="B18" s="24"/>
+      <c r="A18" s="27"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
@@ -5791,10 +6981,10 @@
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="B20" s="34" t="s">
+      <c r="A20" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" s="38" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -5802,36 +6992,36 @@
       </c>
     </row>
     <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="19"/>
-      <c r="B21" s="34"/>
+      <c r="A21" s="28"/>
+      <c r="B21" s="38"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="19"/>
-      <c r="B22" s="34"/>
+      <c r="A22" s="28"/>
+      <c r="B22" s="38"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="19"/>
-      <c r="B23" s="34"/>
+      <c r="A23" s="28"/>
+      <c r="B23" s="38"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="19"/>
+      <c r="A24" s="28"/>
       <c r="B24" s="12"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="19"/>
-      <c r="B25" s="34" t="s">
+      <c r="A25" s="28"/>
+      <c r="B25" s="38" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="4" t="s">
@@ -5839,36 +7029,36 @@
       </c>
     </row>
     <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="19"/>
-      <c r="B26" s="34"/>
+      <c r="A26" s="28"/>
+      <c r="B26" s="38"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="19"/>
-      <c r="B27" s="34"/>
+      <c r="A27" s="28"/>
+      <c r="B27" s="38"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="19"/>
-      <c r="B28" s="34"/>
+      <c r="A28" s="28"/>
+      <c r="B28" s="38"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="19"/>
+      <c r="A29" s="28"/>
       <c r="B29" s="13"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="19"/>
-      <c r="B30" s="35" t="s">
+      <c r="A30" s="28"/>
+      <c r="B30" s="34" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -5876,36 +7066,36 @@
       </c>
     </row>
     <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="19"/>
-      <c r="B31" s="36"/>
+      <c r="A31" s="28"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="19"/>
-      <c r="B32" s="36"/>
+      <c r="A32" s="28"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="19"/>
-      <c r="B33" s="37"/>
+      <c r="A33" s="28"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="19"/>
+      <c r="A34" s="28"/>
       <c r="B34" s="14"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="19"/>
-      <c r="B35" s="35" t="s">
+      <c r="A35" s="28"/>
+      <c r="B35" s="34" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -5913,36 +7103,36 @@
       </c>
     </row>
     <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="19"/>
-      <c r="B36" s="36"/>
+      <c r="A36" s="28"/>
+      <c r="B36" s="35"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="19"/>
-      <c r="B37" s="36"/>
+      <c r="A37" s="28"/>
+      <c r="B37" s="35"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="19"/>
-      <c r="B38" s="37"/>
+      <c r="A38" s="28"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="19"/>
+      <c r="A39" s="28"/>
       <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="19"/>
-      <c r="B40" s="35" t="s">
+      <c r="A40" s="28"/>
+      <c r="B40" s="34" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
@@ -5950,27 +7140,27 @@
       </c>
     </row>
     <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="19"/>
-      <c r="B41" s="36"/>
+      <c r="A41" s="28"/>
+      <c r="B41" s="35"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="19"/>
-      <c r="B42" s="37"/>
+      <c r="A42" s="28"/>
+      <c r="B42" s="36"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="19"/>
+      <c r="A43" s="28"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="19"/>
-      <c r="B44" s="35" t="s">
+      <c r="A44" s="28"/>
+      <c r="B44" s="34" t="s">
         <v>30</v>
       </c>
       <c r="C44" s="4">
@@ -5978,29 +7168,29 @@
       </c>
     </row>
     <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="19"/>
-      <c r="B45" s="36"/>
+      <c r="A45" s="28"/>
+      <c r="B45" s="35"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="19"/>
-      <c r="B46" s="37"/>
+      <c r="A46" s="28"/>
+      <c r="B46" s="36"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="19"/>
+      <c r="A47" s="28"/>
       <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="19"/>
-      <c r="B48" s="35" t="s">
+      <c r="A48" s="28"/>
+      <c r="B48" s="34" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="4" t="s">
@@ -6064,10 +7254,10 @@
       </c>
     </row>
     <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="19"/>
-      <c r="B49" s="36"/>
+      <c r="A49" s="28"/>
+      <c r="B49" s="35"/>
       <c r="C49" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D49" s="4">
         <f t="shared" ref="D49:Q49" si="1">D22+D27+D32+D37+D41</f>
@@ -6127,10 +7317,10 @@
       </c>
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="19"/>
-      <c r="B50" s="37"/>
+      <c r="A50" s="28"/>
+      <c r="B50" s="36"/>
       <c r="C50" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D50" s="4">
         <f>D48*(1+D49*0.02)</f>
@@ -6195,10 +7385,10 @@
       <c r="C51" s="8"/>
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="B52" s="33" t="s">
+      <c r="A52" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="B52" s="37" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="5" t="s">
@@ -6206,29 +7396,29 @@
       </c>
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="20"/>
-      <c r="B53" s="20"/>
+      <c r="A53" s="29"/>
+      <c r="B53" s="29"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="20"/>
-      <c r="B54" s="20"/>
+      <c r="A54" s="29"/>
+      <c r="B54" s="29"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="20"/>
-      <c r="B55" s="21"/>
+      <c r="A55" s="29"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="20"/>
-      <c r="B56" s="33" t="s">
+      <c r="A56" s="29"/>
+      <c r="B56" s="37" t="s">
         <v>30</v>
       </c>
       <c r="C56" s="5">
@@ -6236,29 +7426,29 @@
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="20"/>
-      <c r="B57" s="20"/>
+      <c r="A57" s="29"/>
+      <c r="B57" s="29"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="20"/>
-      <c r="B58" s="21"/>
+      <c r="A58" s="29"/>
+      <c r="B58" s="30"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="20"/>
+      <c r="A59" s="29"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="20"/>
-      <c r="B60" s="33" t="s">
+      <c r="A60" s="29"/>
+      <c r="B60" s="37" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
@@ -6266,22 +7456,22 @@
       </c>
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="20"/>
-      <c r="B61" s="20"/>
+      <c r="A61" s="29"/>
+      <c r="B61" s="29"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="21"/>
-      <c r="B62" s="21"/>
+      <c r="A62" s="30"/>
+      <c r="B62" s="30"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="28" t="s">
+      <c r="A64" s="20" t="s">
         <v>26</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -6292,38 +7482,34 @@
       </c>
     </row>
     <row r="65" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="29"/>
+      <c r="A65" s="21"/>
       <c r="B65" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="21"/>
+      <c r="B66" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C65" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="29"/>
-      <c r="B66" s="4" t="s">
+      <c r="C66" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="22"/>
+      <c r="B67" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C66" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="30"/>
-      <c r="B67" s="5" t="s">
+      <c r="C67" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>136</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A64:A67"/>
     <mergeCell ref="A7:A18"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B7:B10"/>
@@ -6337,6 +7523,10 @@
     <mergeCell ref="B52:B55"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A64:A67"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6344,7 +7534,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB9C480B-7650-4DE9-B7AF-42C282E029C5}">
   <dimension ref="A1:AB67"/>
   <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -6371,73 +7561,73 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="U4" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="V4" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="AB4" s="1"/>
     </row>
@@ -6445,7 +7635,7 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D5" s="1">
         <v>5</v>
@@ -6522,7 +7712,7 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -6596,10 +7786,10 @@
       <c r="AB6" s="1"/>
     </row>
     <row r="7" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="B7" s="16" t="s">
+      <c r="A7" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" s="25" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -6610,8 +7800,8 @@
       </c>
     </row>
     <row r="8" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18"/>
-      <c r="B8" s="16"/>
+      <c r="A8" s="27"/>
+      <c r="B8" s="25"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
@@ -6620,8 +7810,8 @@
       </c>
     </row>
     <row r="9" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="18"/>
-      <c r="B9" s="16"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="25"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
@@ -6630,8 +7820,8 @@
       </c>
     </row>
     <row r="10" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="18"/>
-      <c r="B10" s="16"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="25"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -6640,8 +7830,8 @@
       </c>
     </row>
     <row r="11" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="16" t="s">
+      <c r="A11" s="27"/>
+      <c r="B11" s="25" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
@@ -6649,25 +7839,25 @@
       </c>
     </row>
     <row r="12" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
-      <c r="B12" s="16"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="25"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="18"/>
-      <c r="B13" s="16"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="25"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="18"/>
+      <c r="A14" s="27"/>
     </row>
     <row r="15" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="18"/>
-      <c r="B15" s="22" t="s">
+      <c r="A15" s="27"/>
+      <c r="B15" s="31" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -6678,8 +7868,8 @@
       </c>
     </row>
     <row r="16" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="18"/>
-      <c r="B16" s="23"/>
+      <c r="A16" s="27"/>
+      <c r="B16" s="32"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
@@ -6688,8 +7878,8 @@
       </c>
     </row>
     <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="18"/>
-      <c r="B17" s="23"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="32"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
@@ -6698,8 +7888,8 @@
       </c>
     </row>
     <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="18"/>
-      <c r="B18" s="24"/>
+      <c r="A18" s="27"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
@@ -6714,10 +7904,10 @@
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="B20" s="34" t="s">
+      <c r="A20" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" s="38" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -6725,36 +7915,36 @@
       </c>
     </row>
     <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="19"/>
-      <c r="B21" s="34"/>
+      <c r="A21" s="28"/>
+      <c r="B21" s="38"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="19"/>
-      <c r="B22" s="34"/>
+      <c r="A22" s="28"/>
+      <c r="B22" s="38"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="19"/>
-      <c r="B23" s="34"/>
+      <c r="A23" s="28"/>
+      <c r="B23" s="38"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="19"/>
+      <c r="A24" s="28"/>
       <c r="B24" s="12"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="19"/>
-      <c r="B25" s="34" t="s">
+      <c r="A25" s="28"/>
+      <c r="B25" s="38" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="4" t="s">
@@ -6762,36 +7952,36 @@
       </c>
     </row>
     <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="19"/>
-      <c r="B26" s="34"/>
+      <c r="A26" s="28"/>
+      <c r="B26" s="38"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="19"/>
-      <c r="B27" s="34"/>
+      <c r="A27" s="28"/>
+      <c r="B27" s="38"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="19"/>
-      <c r="B28" s="34"/>
+      <c r="A28" s="28"/>
+      <c r="B28" s="38"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="19"/>
+      <c r="A29" s="28"/>
       <c r="B29" s="13"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="19"/>
-      <c r="B30" s="35" t="s">
+      <c r="A30" s="28"/>
+      <c r="B30" s="34" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -6799,36 +7989,36 @@
       </c>
     </row>
     <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="19"/>
-      <c r="B31" s="36"/>
+      <c r="A31" s="28"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="19"/>
-      <c r="B32" s="36"/>
+      <c r="A32" s="28"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="19"/>
-      <c r="B33" s="37"/>
+      <c r="A33" s="28"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="19"/>
+      <c r="A34" s="28"/>
       <c r="B34" s="14"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="19"/>
-      <c r="B35" s="35" t="s">
+      <c r="A35" s="28"/>
+      <c r="B35" s="34" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -6836,36 +8026,36 @@
       </c>
     </row>
     <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="19"/>
-      <c r="B36" s="36"/>
+      <c r="A36" s="28"/>
+      <c r="B36" s="35"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="19"/>
-      <c r="B37" s="36"/>
+      <c r="A37" s="28"/>
+      <c r="B37" s="35"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="19"/>
-      <c r="B38" s="37"/>
+      <c r="A38" s="28"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="19"/>
+      <c r="A39" s="28"/>
       <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="19"/>
-      <c r="B40" s="35" t="s">
+      <c r="A40" s="28"/>
+      <c r="B40" s="34" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
@@ -6873,27 +8063,27 @@
       </c>
     </row>
     <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="19"/>
-      <c r="B41" s="36"/>
+      <c r="A41" s="28"/>
+      <c r="B41" s="35"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="19"/>
-      <c r="B42" s="37"/>
+      <c r="A42" s="28"/>
+      <c r="B42" s="36"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="19"/>
+      <c r="A43" s="28"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="19"/>
-      <c r="B44" s="35" t="s">
+      <c r="A44" s="28"/>
+      <c r="B44" s="34" t="s">
         <v>30</v>
       </c>
       <c r="C44" s="4">
@@ -6901,29 +8091,29 @@
       </c>
     </row>
     <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="19"/>
-      <c r="B45" s="36"/>
+      <c r="A45" s="28"/>
+      <c r="B45" s="35"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="19"/>
-      <c r="B46" s="37"/>
+      <c r="A46" s="28"/>
+      <c r="B46" s="36"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="19"/>
+      <c r="A47" s="28"/>
       <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="19"/>
-      <c r="B48" s="35" t="s">
+      <c r="A48" s="28"/>
+      <c r="B48" s="34" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="4" t="s">
@@ -6987,10 +8177,10 @@
       </c>
     </row>
     <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="19"/>
-      <c r="B49" s="36"/>
+      <c r="A49" s="28"/>
+      <c r="B49" s="35"/>
       <c r="C49" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D49" s="4">
         <f t="shared" ref="D49:Q49" si="1">D22+D27+D32+D37+D41</f>
@@ -7050,10 +8240,10 @@
       </c>
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="19"/>
-      <c r="B50" s="37"/>
+      <c r="A50" s="28"/>
+      <c r="B50" s="36"/>
       <c r="C50" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D50" s="4">
         <f>D48*(1+D49*0.02)</f>
@@ -7118,10 +8308,10 @@
       <c r="C51" s="8"/>
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="B52" s="33" t="s">
+      <c r="A52" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="B52" s="37" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="5" t="s">
@@ -7129,29 +8319,29 @@
       </c>
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="20"/>
-      <c r="B53" s="20"/>
+      <c r="A53" s="29"/>
+      <c r="B53" s="29"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="20"/>
-      <c r="B54" s="20"/>
+      <c r="A54" s="29"/>
+      <c r="B54" s="29"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="20"/>
-      <c r="B55" s="21"/>
+      <c r="A55" s="29"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="20"/>
-      <c r="B56" s="33" t="s">
+      <c r="A56" s="29"/>
+      <c r="B56" s="37" t="s">
         <v>30</v>
       </c>
       <c r="C56" s="5">
@@ -7159,29 +8349,29 @@
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="20"/>
-      <c r="B57" s="20"/>
+      <c r="A57" s="29"/>
+      <c r="B57" s="29"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="20"/>
-      <c r="B58" s="21"/>
+      <c r="A58" s="29"/>
+      <c r="B58" s="30"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="20"/>
+      <c r="A59" s="29"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="20"/>
-      <c r="B60" s="33" t="s">
+      <c r="A60" s="29"/>
+      <c r="B60" s="37" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
@@ -7189,22 +8379,22 @@
       </c>
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="20"/>
-      <c r="B61" s="20"/>
+      <c r="A61" s="29"/>
+      <c r="B61" s="29"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="21"/>
-      <c r="B62" s="21"/>
+      <c r="A62" s="30"/>
+      <c r="B62" s="30"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="28" t="s">
+      <c r="A64" s="20" t="s">
         <v>26</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -7215,38 +8405,34 @@
       </c>
     </row>
     <row r="65" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="29"/>
+      <c r="A65" s="21"/>
       <c r="B65" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="21"/>
+      <c r="B66" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C65" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="29"/>
-      <c r="B66" s="4" t="s">
+      <c r="C66" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="22"/>
+      <c r="B67" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C66" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="30"/>
-      <c r="B67" s="5" t="s">
+      <c r="C67" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>136</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A64:A67"/>
     <mergeCell ref="A7:A18"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B7:B10"/>
@@ -7260,6 +8446,10 @@
     <mergeCell ref="B52:B55"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A64:A67"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7267,7 +8457,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21A46B60-4F3A-4D99-AC29-6361CD3DE12A}">
   <dimension ref="A1:Q67"/>
   <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -7294,32 +8484,32 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D5" s="1">
         <v>6</v>
@@ -7347,7 +8537,7 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -7372,10 +8562,10 @@
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="B7" s="16" t="s">
+      <c r="A7" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" s="25" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -7386,8 +8576,8 @@
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18"/>
-      <c r="B8" s="16"/>
+      <c r="A8" s="27"/>
+      <c r="B8" s="25"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
@@ -7396,8 +8586,8 @@
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="18"/>
-      <c r="B9" s="16"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="25"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
@@ -7406,8 +8596,8 @@
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="18"/>
-      <c r="B10" s="16"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="25"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -7416,8 +8606,8 @@
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="16" t="s">
+      <c r="A11" s="27"/>
+      <c r="B11" s="25" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
@@ -7425,25 +8615,25 @@
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
-      <c r="B12" s="16"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="25"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="18"/>
-      <c r="B13" s="16"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="25"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="18"/>
+      <c r="A14" s="27"/>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="18"/>
-      <c r="B15" s="22" t="s">
+      <c r="A15" s="27"/>
+      <c r="B15" s="31" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -7454,8 +8644,8 @@
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="18"/>
-      <c r="B16" s="23"/>
+      <c r="A16" s="27"/>
+      <c r="B16" s="32"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
@@ -7464,8 +8654,8 @@
       </c>
     </row>
     <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="18"/>
-      <c r="B17" s="23"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="32"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
@@ -7474,8 +8664,8 @@
       </c>
     </row>
     <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="18"/>
-      <c r="B18" s="24"/>
+      <c r="A18" s="27"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
@@ -7490,10 +8680,10 @@
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="B20" s="34" t="s">
+      <c r="A20" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" s="38" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -7501,36 +8691,36 @@
       </c>
     </row>
     <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="19"/>
-      <c r="B21" s="34"/>
+      <c r="A21" s="28"/>
+      <c r="B21" s="38"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="19"/>
-      <c r="B22" s="34"/>
+      <c r="A22" s="28"/>
+      <c r="B22" s="38"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="19"/>
-      <c r="B23" s="34"/>
+      <c r="A23" s="28"/>
+      <c r="B23" s="38"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="19"/>
+      <c r="A24" s="28"/>
       <c r="B24" s="12"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="19"/>
-      <c r="B25" s="34" t="s">
+      <c r="A25" s="28"/>
+      <c r="B25" s="38" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="4" t="s">
@@ -7538,36 +8728,36 @@
       </c>
     </row>
     <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="19"/>
-      <c r="B26" s="34"/>
+      <c r="A26" s="28"/>
+      <c r="B26" s="38"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="19"/>
-      <c r="B27" s="34"/>
+      <c r="A27" s="28"/>
+      <c r="B27" s="38"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="19"/>
-      <c r="B28" s="34"/>
+      <c r="A28" s="28"/>
+      <c r="B28" s="38"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="19"/>
+      <c r="A29" s="28"/>
       <c r="B29" s="13"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="19"/>
-      <c r="B30" s="35" t="s">
+      <c r="A30" s="28"/>
+      <c r="B30" s="34" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -7575,36 +8765,36 @@
       </c>
     </row>
     <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="19"/>
-      <c r="B31" s="36"/>
+      <c r="A31" s="28"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="19"/>
-      <c r="B32" s="36"/>
+      <c r="A32" s="28"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="19"/>
-      <c r="B33" s="37"/>
+      <c r="A33" s="28"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="19"/>
+      <c r="A34" s="28"/>
       <c r="B34" s="14"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="19"/>
-      <c r="B35" s="35" t="s">
+      <c r="A35" s="28"/>
+      <c r="B35" s="34" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -7612,36 +8802,36 @@
       </c>
     </row>
     <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="19"/>
-      <c r="B36" s="36"/>
+      <c r="A36" s="28"/>
+      <c r="B36" s="35"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="19"/>
-      <c r="B37" s="36"/>
+      <c r="A37" s="28"/>
+      <c r="B37" s="35"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="19"/>
-      <c r="B38" s="37"/>
+      <c r="A38" s="28"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="19"/>
+      <c r="A39" s="28"/>
       <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="19"/>
-      <c r="B40" s="35" t="s">
+      <c r="A40" s="28"/>
+      <c r="B40" s="34" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
@@ -7649,27 +8839,27 @@
       </c>
     </row>
     <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="19"/>
-      <c r="B41" s="36"/>
+      <c r="A41" s="28"/>
+      <c r="B41" s="35"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="19"/>
-      <c r="B42" s="37"/>
+      <c r="A42" s="28"/>
+      <c r="B42" s="36"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="19"/>
+      <c r="A43" s="28"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="19"/>
-      <c r="B44" s="35" t="s">
+      <c r="A44" s="28"/>
+      <c r="B44" s="34" t="s">
         <v>30</v>
       </c>
       <c r="C44" s="4">
@@ -7677,29 +8867,29 @@
       </c>
     </row>
     <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="19"/>
-      <c r="B45" s="36"/>
+      <c r="A45" s="28"/>
+      <c r="B45" s="35"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="19"/>
-      <c r="B46" s="37"/>
+      <c r="A46" s="28"/>
+      <c r="B46" s="36"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="19"/>
+      <c r="A47" s="28"/>
       <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="19"/>
-      <c r="B48" s="35" t="s">
+      <c r="A48" s="28"/>
+      <c r="B48" s="34" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="4" t="s">
@@ -7763,10 +8953,10 @@
       </c>
     </row>
     <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="19"/>
-      <c r="B49" s="36"/>
+      <c r="A49" s="28"/>
+      <c r="B49" s="35"/>
       <c r="C49" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D49" s="4">
         <f t="shared" ref="D49:Q49" si="1">D22+D27+D32+D37+D41</f>
@@ -7826,10 +9016,10 @@
       </c>
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="19"/>
-      <c r="B50" s="37"/>
+      <c r="A50" s="28"/>
+      <c r="B50" s="36"/>
       <c r="C50" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D50" s="4">
         <f>D48*(1+D49*0.02)</f>
@@ -7894,10 +9084,10 @@
       <c r="C51" s="8"/>
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="B52" s="33" t="s">
+      <c r="A52" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="B52" s="37" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="5" t="s">
@@ -7905,29 +9095,29 @@
       </c>
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="20"/>
-      <c r="B53" s="20"/>
+      <c r="A53" s="29"/>
+      <c r="B53" s="29"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="20"/>
-      <c r="B54" s="20"/>
+      <c r="A54" s="29"/>
+      <c r="B54" s="29"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="20"/>
-      <c r="B55" s="21"/>
+      <c r="A55" s="29"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="20"/>
-      <c r="B56" s="33" t="s">
+      <c r="A56" s="29"/>
+      <c r="B56" s="37" t="s">
         <v>30</v>
       </c>
       <c r="C56" s="5">
@@ -7935,29 +9125,29 @@
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="20"/>
-      <c r="B57" s="20"/>
+      <c r="A57" s="29"/>
+      <c r="B57" s="29"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="20"/>
-      <c r="B58" s="21"/>
+      <c r="A58" s="29"/>
+      <c r="B58" s="30"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="20"/>
+      <c r="A59" s="29"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="20"/>
-      <c r="B60" s="33" t="s">
+      <c r="A60" s="29"/>
+      <c r="B60" s="37" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
@@ -7965,22 +9155,22 @@
       </c>
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="20"/>
-      <c r="B61" s="20"/>
+      <c r="A61" s="29"/>
+      <c r="B61" s="29"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="21"/>
-      <c r="B62" s="21"/>
+      <c r="A62" s="30"/>
+      <c r="B62" s="30"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="28" t="s">
+      <c r="A64" s="20" t="s">
         <v>26</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -7991,38 +9181,34 @@
       </c>
     </row>
     <row r="65" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="29"/>
+      <c r="A65" s="21"/>
       <c r="B65" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="21"/>
+      <c r="B66" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C65" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="29"/>
-      <c r="B66" s="4" t="s">
+      <c r="C66" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="22"/>
+      <c r="B67" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C66" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="30"/>
-      <c r="B67" s="5" t="s">
+      <c r="C67" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>136</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A64:A67"/>
     <mergeCell ref="A7:A18"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B7:B10"/>
@@ -8036,6 +9222,10 @@
     <mergeCell ref="B52:B55"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A64:A67"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dev_stuffs/3匠魂.xlsx
+++ b/dev_stuffs/3匠魂.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\Palmon\dev_stuffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CFBC585-03CD-42C1-A412-2C6A19A2C44B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B99E0B-9F2B-4B3D-B387-6F12821B5B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13035" yWindow="5265" windowWidth="23940" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="阶段1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="181">
   <si>
     <t>材料名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -596,6 +596,38 @@
   </si>
   <si>
     <t>'#forge:gems/certus_quartz'</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>原体合金</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>'kubejs:end_steel'</t>
+  </si>
+  <si>
+    <t>'kubejs:collapse_prediction'</t>
+  </si>
+  <si>
+    <t>'deeperdarker:sculk_tendrils'</t>
+  </si>
+  <si>
+    <t>'deeperdarker:sculk_gleam'</t>
+  </si>
+  <si>
+    <t>'kubejs:iridescent'</t>
+  </si>
+  <si>
+    <t>whitestone</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>'nuclearcraft:fusion_reactor_casing'</t>
+  </si>
+  <si>
+    <t>'#forge:ingots/titanium'</t>
   </si>
 </sst>
 </file>
@@ -794,7 +826,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -842,30 +874,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -893,6 +901,33 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -902,10 +937,13 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1366,10 +1404,10 @@
       </c>
     </row>
     <row r="9" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="17" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -1407,8 +1445,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="27"/>
-      <c r="B10" s="25"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -1444,8 +1482,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="27"/>
-      <c r="B11" s="25"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -1481,8 +1519,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="27"/>
-      <c r="B12" s="25"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -1518,8 +1556,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="27"/>
-      <c r="B13" s="25" t="s">
+      <c r="A13" s="19"/>
+      <c r="B13" s="17" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -1527,25 +1565,25 @@
       </c>
     </row>
     <row r="14" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="27"/>
-      <c r="B14" s="25"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="17"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="27"/>
-      <c r="B15" s="25"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="27"/>
+      <c r="A16" s="19"/>
     </row>
     <row r="17" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="27"/>
-      <c r="B17" s="31" t="s">
+      <c r="A17" s="19"/>
+      <c r="B17" s="23" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -1583,8 +1621,8 @@
       </c>
     </row>
     <row r="18" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="27"/>
-      <c r="B18" s="32"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="24"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1620,8 +1658,8 @@
       </c>
     </row>
     <row r="19" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="27"/>
-      <c r="B19" s="32"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="24"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -1657,8 +1695,8 @@
       </c>
     </row>
     <row r="20" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="27"/>
-      <c r="B20" s="33"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="25"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1700,10 +1738,10 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="20" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -1741,8 +1779,8 @@
       </c>
     </row>
     <row r="23" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="24"/>
-      <c r="B23" s="28"/>
+      <c r="A23" s="33"/>
+      <c r="B23" s="20"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
       </c>
@@ -1788,8 +1826,8 @@
       </c>
     </row>
     <row r="24" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="24"/>
-      <c r="B24" s="28"/>
+      <c r="A24" s="33"/>
+      <c r="B24" s="20"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
       </c>
@@ -1825,22 +1863,22 @@
       </c>
     </row>
     <row r="25" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="24"/>
-      <c r="B25" s="28"/>
+      <c r="A25" s="33"/>
+      <c r="B25" s="20"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="24"/>
+      <c r="A26" s="33"/>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="24"/>
-      <c r="B27" s="28" t="s">
+      <c r="A27" s="33"/>
+      <c r="B27" s="20" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="4" t="s">
@@ -1878,8 +1916,8 @@
       </c>
     </row>
     <row r="28" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="24"/>
-      <c r="B28" s="28"/>
+      <c r="A28" s="33"/>
+      <c r="B28" s="20"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
       </c>
@@ -1925,8 +1963,8 @@
       </c>
     </row>
     <row r="29" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="24"/>
-      <c r="B29" s="28"/>
+      <c r="A29" s="33"/>
+      <c r="B29" s="20"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
       </c>
@@ -1962,22 +2000,22 @@
       </c>
     </row>
     <row r="30" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="24"/>
-      <c r="B30" s="28"/>
+      <c r="A30" s="33"/>
+      <c r="B30" s="20"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="24"/>
+      <c r="A31" s="33"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="24"/>
-      <c r="B32" s="17" t="s">
+      <c r="A32" s="33"/>
+      <c r="B32" s="26" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -2015,8 +2053,8 @@
       </c>
     </row>
     <row r="33" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="24"/>
-      <c r="B33" s="18"/>
+      <c r="A33" s="33"/>
+      <c r="B33" s="27"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -2062,8 +2100,8 @@
       </c>
     </row>
     <row r="34" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="24"/>
-      <c r="B34" s="18"/>
+      <c r="A34" s="33"/>
+      <c r="B34" s="27"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -2099,22 +2137,22 @@
       </c>
     </row>
     <row r="35" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="24"/>
-      <c r="B35" s="19"/>
+      <c r="A35" s="33"/>
+      <c r="B35" s="28"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="24"/>
+      <c r="A36" s="33"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="24"/>
-      <c r="B37" s="17" t="s">
+      <c r="A37" s="33"/>
+      <c r="B37" s="26" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -2152,8 +2190,8 @@
       </c>
     </row>
     <row r="38" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="24"/>
-      <c r="B38" s="18"/>
+      <c r="A38" s="33"/>
+      <c r="B38" s="27"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -2199,8 +2237,8 @@
       </c>
     </row>
     <row r="39" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="24"/>
-      <c r="B39" s="18"/>
+      <c r="A39" s="33"/>
+      <c r="B39" s="27"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -2236,22 +2274,22 @@
       </c>
     </row>
     <row r="40" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="24"/>
-      <c r="B40" s="19"/>
+      <c r="A40" s="33"/>
+      <c r="B40" s="28"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="24"/>
+      <c r="A41" s="33"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="24"/>
-      <c r="B42" s="17" t="s">
+      <c r="A42" s="33"/>
+      <c r="B42" s="26" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -2299,8 +2337,8 @@
       </c>
     </row>
     <row r="43" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="24"/>
-      <c r="B43" s="18"/>
+      <c r="A43" s="33"/>
+      <c r="B43" s="27"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -2336,18 +2374,18 @@
       </c>
     </row>
     <row r="44" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="24"/>
-      <c r="B44" s="19"/>
+      <c r="A44" s="33"/>
+      <c r="B44" s="28"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="24"/>
+      <c r="A45" s="33"/>
     </row>
     <row r="46" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="24"/>
-      <c r="B46" s="17" t="s">
+      <c r="A46" s="33"/>
+      <c r="B46" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -2355,29 +2393,29 @@
       </c>
     </row>
     <row r="47" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="24"/>
-      <c r="B47" s="18"/>
+      <c r="A47" s="33"/>
+      <c r="B47" s="27"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="24"/>
-      <c r="B48" s="19"/>
+      <c r="A48" s="33"/>
+      <c r="B48" s="28"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="24"/>
+      <c r="A49" s="33"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
     </row>
     <row r="50" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="24"/>
-      <c r="B50" s="17" t="s">
+      <c r="A50" s="33"/>
+      <c r="B50" s="26" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -2425,8 +2463,8 @@
       </c>
     </row>
     <row r="51" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="24"/>
-      <c r="B51" s="18"/>
+      <c r="A51" s="33"/>
+      <c r="B51" s="27"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -2472,8 +2510,8 @@
       </c>
     </row>
     <row r="52" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="24"/>
-      <c r="B52" s="19"/>
+      <c r="A52" s="33"/>
+      <c r="B52" s="28"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -2525,10 +2563,10 @@
       <c r="E53" s="8"/>
     </row>
     <row r="54" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="26" t="s">
+      <c r="A54" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="26" t="s">
+      <c r="B54" s="18" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -2536,29 +2574,29 @@
       </c>
     </row>
     <row r="55" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="26"/>
-      <c r="B55" s="26"/>
+      <c r="A55" s="18"/>
+      <c r="B55" s="18"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="26"/>
-      <c r="B56" s="26"/>
+      <c r="A56" s="18"/>
+      <c r="B56" s="18"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="26"/>
-      <c r="B57" s="26"/>
+      <c r="A57" s="18"/>
+      <c r="B57" s="18"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="26"/>
-      <c r="B58" s="26" t="s">
+      <c r="A58" s="18"/>
+      <c r="B58" s="18" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -2566,29 +2604,29 @@
       </c>
     </row>
     <row r="59" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="26"/>
-      <c r="B59" s="29"/>
+      <c r="A59" s="18"/>
+      <c r="B59" s="21"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="26"/>
-      <c r="B60" s="30"/>
+      <c r="A60" s="18"/>
+      <c r="B60" s="22"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="26"/>
+      <c r="A61" s="18"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="26"/>
-      <c r="B62" s="26" t="s">
+      <c r="A62" s="18"/>
+      <c r="B62" s="18" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -2596,21 +2634,21 @@
       </c>
     </row>
     <row r="63" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="26"/>
-      <c r="B63" s="29"/>
+      <c r="A63" s="18"/>
+      <c r="B63" s="21"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="26"/>
-      <c r="B64" s="30"/>
+      <c r="A64" s="18"/>
+      <c r="B64" s="22"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="20" t="s">
+      <c r="A67" s="29" t="s">
         <v>26</v>
       </c>
       <c r="B67" s="6" t="s">
@@ -2651,7 +2689,7 @@
       </c>
     </row>
     <row r="68" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="21"/>
+      <c r="A68" s="30"/>
       <c r="B68" s="4" t="s">
         <v>132</v>
       </c>
@@ -2690,7 +2728,7 @@
       </c>
     </row>
     <row r="69" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="21"/>
+      <c r="A69" s="30"/>
       <c r="B69" s="4" t="s">
         <v>133</v>
       </c>
@@ -2729,7 +2767,7 @@
       </c>
     </row>
     <row r="70" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="22"/>
+      <c r="A70" s="31"/>
       <c r="B70" s="5" t="s">
         <v>134</v>
       </c>
@@ -2769,8 +2807,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B50:B52"/>
     <mergeCell ref="A67:A70"/>
     <mergeCell ref="B46:B48"/>
     <mergeCell ref="A22:A52"/>
@@ -2786,6 +2822,8 @@
     <mergeCell ref="B62:B64"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B50:B52"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3055,10 +3093,10 @@
       </c>
     </row>
     <row r="9" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="17" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -3108,8 +3146,8 @@
       </c>
     </row>
     <row r="10" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="27"/>
-      <c r="B10" s="25"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -3157,8 +3195,8 @@
       </c>
     </row>
     <row r="11" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="27"/>
-      <c r="B11" s="25"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -3206,8 +3244,8 @@
       </c>
     </row>
     <row r="12" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="27"/>
-      <c r="B12" s="25"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -3255,8 +3293,8 @@
       </c>
     </row>
     <row r="13" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="27"/>
-      <c r="B13" s="25" t="s">
+      <c r="A13" s="19"/>
+      <c r="B13" s="17" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -3264,25 +3302,25 @@
       </c>
     </row>
     <row r="14" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="27"/>
-      <c r="B14" s="25"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="17"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="27"/>
-      <c r="B15" s="25"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="27"/>
+      <c r="A16" s="19"/>
     </row>
     <row r="17" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="27"/>
-      <c r="B17" s="31" t="s">
+      <c r="A17" s="19"/>
+      <c r="B17" s="23" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -3332,8 +3370,8 @@
       </c>
     </row>
     <row r="18" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="27"/>
-      <c r="B18" s="32"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="24"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -3381,8 +3419,8 @@
       </c>
     </row>
     <row r="19" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="27"/>
-      <c r="B19" s="32"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="24"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -3430,8 +3468,8 @@
       </c>
     </row>
     <row r="20" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="27"/>
-      <c r="B20" s="33"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="25"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -3485,7 +3523,7 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="20" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="38" t="s">
@@ -3538,7 +3576,7 @@
       </c>
     </row>
     <row r="23" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="28"/>
+      <c r="A23" s="20"/>
       <c r="B23" s="38"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -3601,7 +3639,7 @@
       </c>
     </row>
     <row r="24" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="28"/>
+      <c r="A24" s="20"/>
       <c r="B24" s="38"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -3650,7 +3688,7 @@
       </c>
     </row>
     <row r="25" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="28"/>
+      <c r="A25" s="20"/>
       <c r="B25" s="38"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -3681,14 +3719,14 @@
       </c>
     </row>
     <row r="26" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="28"/>
+      <c r="A26" s="20"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="28"/>
+      <c r="A27" s="20"/>
       <c r="B27" s="38" t="s">
         <v>16</v>
       </c>
@@ -3739,7 +3777,7 @@
       </c>
     </row>
     <row r="28" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="28"/>
+      <c r="A28" s="20"/>
       <c r="B28" s="38"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -3802,7 +3840,7 @@
       </c>
     </row>
     <row r="29" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="28"/>
+      <c r="A29" s="20"/>
       <c r="B29" s="38"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -3851,7 +3889,7 @@
       </c>
     </row>
     <row r="30" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="28"/>
+      <c r="A30" s="20"/>
       <c r="B30" s="38"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -3882,15 +3920,15 @@
       </c>
     </row>
     <row r="31" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="28"/>
+      <c r="A31" s="20"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="28"/>
-      <c r="B32" s="34" t="s">
+      <c r="A32" s="20"/>
+      <c r="B32" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -3940,8 +3978,8 @@
       </c>
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="28"/>
-      <c r="B33" s="35"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -4003,8 +4041,8 @@
       </c>
     </row>
     <row r="34" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="28"/>
-      <c r="B34" s="35"/>
+      <c r="A34" s="20"/>
+      <c r="B34" s="36"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -4052,8 +4090,8 @@
       </c>
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="28"/>
-      <c r="B35" s="36"/>
+      <c r="A35" s="20"/>
+      <c r="B35" s="37"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
@@ -4083,15 +4121,15 @@
       </c>
     </row>
     <row r="36" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="28"/>
+      <c r="A36" s="20"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="28"/>
-      <c r="B37" s="34" t="s">
+      <c r="A37" s="20"/>
+      <c r="B37" s="35" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -4141,8 +4179,8 @@
       </c>
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="28"/>
-      <c r="B38" s="35"/>
+      <c r="A38" s="20"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -4204,8 +4242,8 @@
       </c>
     </row>
     <row r="39" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="28"/>
-      <c r="B39" s="35"/>
+      <c r="A39" s="20"/>
+      <c r="B39" s="36"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -4253,8 +4291,8 @@
       </c>
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="28"/>
-      <c r="B40" s="36"/>
+      <c r="A40" s="20"/>
+      <c r="B40" s="37"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
@@ -4284,15 +4322,15 @@
       </c>
     </row>
     <row r="41" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="28"/>
+      <c r="A41" s="20"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="28"/>
-      <c r="B42" s="34" t="s">
+      <c r="A42" s="20"/>
+      <c r="B42" s="35" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -4356,8 +4394,8 @@
       </c>
     </row>
     <row r="43" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="28"/>
-      <c r="B43" s="35"/>
+      <c r="A43" s="20"/>
+      <c r="B43" s="36"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -4405,8 +4443,8 @@
       </c>
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="28"/>
-      <c r="B44" s="36"/>
+      <c r="A44" s="20"/>
+      <c r="B44" s="37"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
@@ -4436,13 +4474,13 @@
       </c>
     </row>
     <row r="45" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="28"/>
+      <c r="A45" s="20"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="28"/>
-      <c r="B46" s="34" t="s">
+      <c r="A46" s="20"/>
+      <c r="B46" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -4450,29 +4488,29 @@
       </c>
     </row>
     <row r="47" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="28"/>
-      <c r="B47" s="35"/>
+      <c r="A47" s="20"/>
+      <c r="B47" s="36"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="28"/>
-      <c r="B48" s="36"/>
+      <c r="A48" s="20"/>
+      <c r="B48" s="37"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="28"/>
+      <c r="A49" s="20"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="28"/>
-      <c r="B50" s="34" t="s">
+      <c r="A50" s="20"/>
+      <c r="B50" s="35" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -4536,8 +4574,8 @@
       </c>
     </row>
     <row r="51" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="28"/>
-      <c r="B51" s="35"/>
+      <c r="A51" s="20"/>
+      <c r="B51" s="36"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -4599,8 +4637,8 @@
       </c>
     </row>
     <row r="52" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="28"/>
-      <c r="B52" s="36"/>
+      <c r="A52" s="20"/>
+      <c r="B52" s="37"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -4667,10 +4705,10 @@
       <c r="C53" s="8"/>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="37" t="s">
+      <c r="A54" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="37" t="s">
+      <c r="B54" s="34" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -4678,29 +4716,29 @@
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="29"/>
-      <c r="B55" s="29"/>
+      <c r="A55" s="21"/>
+      <c r="B55" s="21"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="29"/>
-      <c r="B56" s="29"/>
+      <c r="A56" s="21"/>
+      <c r="B56" s="21"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="29"/>
-      <c r="B57" s="30"/>
+      <c r="A57" s="21"/>
+      <c r="B57" s="22"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="29"/>
-      <c r="B58" s="37" t="s">
+      <c r="A58" s="21"/>
+      <c r="B58" s="34" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -4708,29 +4746,29 @@
       </c>
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="29"/>
-      <c r="B59" s="29"/>
+      <c r="A59" s="21"/>
+      <c r="B59" s="21"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="29"/>
-      <c r="B60" s="30"/>
+      <c r="A60" s="21"/>
+      <c r="B60" s="22"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="29"/>
+      <c r="A61" s="21"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="29"/>
-      <c r="B62" s="37" t="s">
+      <c r="A62" s="21"/>
+      <c r="B62" s="34" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -4738,22 +4776,22 @@
       </c>
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="29"/>
-      <c r="B63" s="29"/>
+      <c r="A63" s="21"/>
+      <c r="B63" s="21"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="30"/>
-      <c r="B64" s="30"/>
+      <c r="A64" s="22"/>
+      <c r="B64" s="22"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="20" t="s">
+      <c r="A66" s="29" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -4806,7 +4844,7 @@
       </c>
     </row>
     <row r="67" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="21"/>
+      <c r="A67" s="30"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -4851,7 +4889,7 @@
       </c>
     </row>
     <row r="68" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="21"/>
+      <c r="A68" s="30"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -4896,7 +4934,7 @@
       </c>
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="22"/>
+      <c r="A69" s="31"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -4906,6 +4944,8 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A54:A64"/>
+    <mergeCell ref="B54:B57"/>
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="B50:B52"/>
     <mergeCell ref="A66:A69"/>
@@ -4921,8 +4961,6 @@
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="B42:B44"/>
-    <mergeCell ref="A54:A64"/>
-    <mergeCell ref="B54:B57"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4932,27 +4970,27 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15BE3A64-1223-4346-9F98-17294D0E7928}">
-  <dimension ref="A1:AF67"/>
+  <dimension ref="A1:AE67"/>
   <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="16.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="2"/>
     </row>
-    <row r="4" spans="1:32" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -4975,76 +5013,73 @@
         <v>59</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AC4" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD4" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF4" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:32" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
@@ -5134,11 +5169,8 @@
       <c r="AE5" s="1">
         <v>3</v>
       </c>
-      <c r="AF5" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:31" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
@@ -5163,7 +5195,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" s="1">
         <v>2</v>
@@ -5184,7 +5216,7 @@
         <v>2</v>
       </c>
       <c r="Q6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R6" s="1">
         <v>3</v>
@@ -5196,7 +5228,7 @@
         <v>3</v>
       </c>
       <c r="U6" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V6" s="1">
         <v>4</v>
@@ -5205,7 +5237,7 @@
         <v>4</v>
       </c>
       <c r="X6" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y6" s="1">
         <v>5</v>
@@ -5220,7 +5252,7 @@
         <v>5</v>
       </c>
       <c r="AC6" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD6" s="1">
         <v>6</v>
@@ -5228,15 +5260,12 @@
       <c r="AE6" s="1">
         <v>6</v>
       </c>
-      <c r="AF6" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="27" t="s">
+    </row>
+    <row r="7" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="17" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -5246,9 +5275,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="27"/>
-      <c r="B8" s="25"/>
+    <row r="8" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="19"/>
+      <c r="B8" s="17"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
@@ -5256,9 +5285,9 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="25"/>
+    <row r="9" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="19"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
@@ -5266,9 +5295,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="27"/>
-      <c r="B10" s="25"/>
+    <row r="10" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="19"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -5276,35 +5305,35 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="27"/>
-      <c r="B11" s="25" t="s">
+    <row r="11" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="19"/>
+      <c r="B11" s="17" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="27"/>
-      <c r="B12" s="25"/>
+    <row r="12" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="19"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="27"/>
-      <c r="B13" s="25"/>
+    <row r="13" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="19"/>
+      <c r="B13" s="17"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:32" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="27"/>
-    </row>
-    <row r="15" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="27"/>
-      <c r="B15" s="31" t="s">
+    <row r="14" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="19"/>
+    </row>
+    <row r="15" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="19"/>
+      <c r="B15" s="23" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -5314,9 +5343,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="27"/>
-      <c r="B16" s="32"/>
+    <row r="16" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="19"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
@@ -5325,8 +5354,8 @@
       </c>
     </row>
     <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="27"/>
-      <c r="B17" s="32"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="24"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
@@ -5335,8 +5364,8 @@
       </c>
     </row>
     <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="27"/>
-      <c r="B18" s="33"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
@@ -5351,7 +5380,7 @@
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="20" t="s">
         <v>131</v>
       </c>
       <c r="B20" s="38" t="s">
@@ -5362,35 +5391,35 @@
       </c>
     </row>
     <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="28"/>
+      <c r="A21" s="20"/>
       <c r="B21" s="38"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="28"/>
+      <c r="A22" s="20"/>
       <c r="B22" s="38"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="28"/>
+      <c r="A23" s="20"/>
       <c r="B23" s="38"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="28"/>
+      <c r="A24" s="20"/>
       <c r="B24" s="12"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="28"/>
+      <c r="A25" s="20"/>
       <c r="B25" s="38" t="s">
         <v>16</v>
       </c>
@@ -5399,36 +5428,36 @@
       </c>
     </row>
     <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="28"/>
+      <c r="A26" s="20"/>
       <c r="B26" s="38"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="28"/>
+      <c r="A27" s="20"/>
       <c r="B27" s="38"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="28"/>
+      <c r="A28" s="20"/>
       <c r="B28" s="38"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="28"/>
+      <c r="A29" s="20"/>
       <c r="B29" s="13"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="28"/>
-      <c r="B30" s="34" t="s">
+      <c r="A30" s="20"/>
+      <c r="B30" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -5436,138 +5465,138 @@
       </c>
     </row>
     <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="28"/>
-      <c r="B31" s="35"/>
+      <c r="A31" s="20"/>
+      <c r="B31" s="36"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="28"/>
-      <c r="B32" s="35"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="36"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="28"/>
-      <c r="B33" s="36"/>
+    <row r="33" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="20"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="28"/>
+    <row r="34" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="20"/>
       <c r="B34" s="14"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="28"/>
-      <c r="B35" s="34" t="s">
+    <row r="35" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="20"/>
+      <c r="B35" s="35" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="28"/>
-      <c r="B36" s="35"/>
+    <row r="36" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="20"/>
+      <c r="B36" s="36"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="28"/>
-      <c r="B37" s="35"/>
+    <row r="37" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="20"/>
+      <c r="B37" s="36"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="28"/>
-      <c r="B38" s="36"/>
+    <row r="38" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="20"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="28"/>
+    <row r="39" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="20"/>
       <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="28"/>
-      <c r="B40" s="34" t="s">
+    <row r="40" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="20"/>
+      <c r="B40" s="35" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="28"/>
-      <c r="B41" s="35"/>
+    <row r="41" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="20"/>
+      <c r="B41" s="36"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="28"/>
-      <c r="B42" s="36"/>
+    <row r="42" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="20"/>
+      <c r="B42" s="37"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="28"/>
+    <row r="43" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="20"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
     </row>
-    <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="28"/>
-      <c r="B44" s="34" t="s">
+    <row r="44" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="20"/>
+      <c r="B44" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C44" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="28"/>
-      <c r="B45" s="35"/>
+    <row r="45" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="20"/>
+      <c r="B45" s="36"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="28"/>
-      <c r="B46" s="36"/>
+    <row r="46" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="20"/>
+      <c r="B46" s="37"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="28"/>
+    <row r="47" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="20"/>
       <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
-    <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="28"/>
-      <c r="B48" s="34" t="s">
+    <row r="48" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="20"/>
+      <c r="B48" s="35" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>29</v>
       </c>
       <c r="D48" s="4">
-        <f t="shared" ref="D48:Q48" si="0">D20+D25+D30+D35</f>
+        <f t="shared" ref="D48:P48" si="0">D20+D25+D30+D35</f>
         <v>0</v>
       </c>
       <c r="E48" s="4">
@@ -5618,19 +5647,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="28"/>
-      <c r="B49" s="35"/>
+    </row>
+    <row r="49" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="20"/>
+      <c r="B49" s="36"/>
       <c r="C49" s="4" t="s">
         <v>129</v>
       </c>
       <c r="D49" s="4">
-        <f t="shared" ref="D49:Q49" si="1">D22+D27+D32+D37+D41</f>
+        <f t="shared" ref="D49:P49" si="1">D22+D27+D32+D37+D41</f>
         <v>0</v>
       </c>
       <c r="E49" s="4">
@@ -5681,14 +5706,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="28"/>
-      <c r="B50" s="36"/>
+    </row>
+    <row r="50" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="20"/>
+      <c r="B50" s="37"/>
       <c r="C50" s="4" t="s">
         <v>130</v>
       </c>
@@ -5701,7 +5722,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="4">
-        <f t="shared" ref="F50:Q50" si="2">F48*(1+F49*0.02)</f>
+        <f t="shared" ref="F50:P50" si="2">F48*(1+F49*0.02)</f>
         <v>0</v>
       </c>
       <c r="G50" s="4">
@@ -5744,104 +5765,100 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:16" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="37" t="s">
+    <row r="52" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="B52" s="37" t="s">
+      <c r="B52" s="34" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="29"/>
-      <c r="B53" s="29"/>
+    <row r="53" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="21"/>
+      <c r="B53" s="21"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="29"/>
-      <c r="B54" s="29"/>
+    <row r="54" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="21"/>
+      <c r="B54" s="21"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="29"/>
-      <c r="B55" s="30"/>
+    <row r="55" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="21"/>
+      <c r="B55" s="22"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="29"/>
-      <c r="B56" s="37" t="s">
+    <row r="56" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="21"/>
+      <c r="B56" s="34" t="s">
         <v>30</v>
       </c>
       <c r="C56" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="29"/>
-      <c r="B57" s="29"/>
+    <row r="57" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="21"/>
+      <c r="B57" s="21"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="29"/>
-      <c r="B58" s="30"/>
+    <row r="58" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="21"/>
+      <c r="B58" s="22"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="29"/>
+    <row r="59" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="21"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="29"/>
-      <c r="B60" s="37" t="s">
+    <row r="60" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="21"/>
+      <c r="B60" s="34" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="29"/>
-      <c r="B61" s="29"/>
+    <row r="61" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="21"/>
+      <c r="B61" s="21"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="30"/>
-      <c r="B62" s="30"/>
+    <row r="62" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="22"/>
+      <c r="B62" s="22"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="20" t="s">
+    <row r="63" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="29" t="s">
         <v>26</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -5852,7 +5869,7 @@
       </c>
     </row>
     <row r="65" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="21"/>
+      <c r="A65" s="30"/>
       <c r="B65" s="4" t="s">
         <v>132</v>
       </c>
@@ -5861,7 +5878,7 @@
       </c>
     </row>
     <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="21"/>
+      <c r="A66" s="30"/>
       <c r="B66" s="4" t="s">
         <v>133</v>
       </c>
@@ -5870,7 +5887,7 @@
       </c>
     </row>
     <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="22"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="5" t="s">
         <v>134</v>
       </c>
@@ -5880,6 +5897,8 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A64:A67"/>
     <mergeCell ref="A7:A18"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B7:B10"/>
@@ -5895,8 +5914,6 @@
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="B35:B38"/>
     <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A64:A67"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6051,10 +6068,10 @@
       <c r="AF6" s="1"/>
     </row>
     <row r="7" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="17" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -6065,8 +6082,8 @@
       </c>
     </row>
     <row r="8" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="27"/>
-      <c r="B8" s="25"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="17"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
@@ -6075,8 +6092,8 @@
       </c>
     </row>
     <row r="9" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="25"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
@@ -6085,8 +6102,8 @@
       </c>
     </row>
     <row r="10" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="27"/>
-      <c r="B10" s="25"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -6095,8 +6112,8 @@
       </c>
     </row>
     <row r="11" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="27"/>
-      <c r="B11" s="25" t="s">
+      <c r="A11" s="19"/>
+      <c r="B11" s="17" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
@@ -6104,25 +6121,25 @@
       </c>
     </row>
     <row r="12" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="27"/>
-      <c r="B12" s="25"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="27"/>
-      <c r="B13" s="25"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="17"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:32" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="27"/>
+      <c r="A14" s="19"/>
     </row>
     <row r="15" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="27"/>
-      <c r="B15" s="31" t="s">
+      <c r="A15" s="19"/>
+      <c r="B15" s="23" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -6133,8 +6150,8 @@
       </c>
     </row>
     <row r="16" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="27"/>
-      <c r="B16" s="32"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
@@ -6143,8 +6160,8 @@
       </c>
     </row>
     <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="27"/>
-      <c r="B17" s="32"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="24"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
@@ -6153,8 +6170,8 @@
       </c>
     </row>
     <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="27"/>
-      <c r="B18" s="33"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
@@ -6169,7 +6186,7 @@
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="20" t="s">
         <v>131</v>
       </c>
       <c r="B20" s="38" t="s">
@@ -6180,35 +6197,35 @@
       </c>
     </row>
     <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="28"/>
+      <c r="A21" s="20"/>
       <c r="B21" s="38"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="28"/>
+      <c r="A22" s="20"/>
       <c r="B22" s="38"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="28"/>
+      <c r="A23" s="20"/>
       <c r="B23" s="38"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="28"/>
+      <c r="A24" s="20"/>
       <c r="B24" s="12"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="28"/>
+      <c r="A25" s="20"/>
       <c r="B25" s="38" t="s">
         <v>16</v>
       </c>
@@ -6217,36 +6234,36 @@
       </c>
     </row>
     <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="28"/>
+      <c r="A26" s="20"/>
       <c r="B26" s="38"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="28"/>
+      <c r="A27" s="20"/>
       <c r="B27" s="38"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="28"/>
+      <c r="A28" s="20"/>
       <c r="B28" s="38"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="28"/>
+      <c r="A29" s="20"/>
       <c r="B29" s="13"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="28"/>
-      <c r="B30" s="34" t="s">
+      <c r="A30" s="20"/>
+      <c r="B30" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -6254,36 +6271,36 @@
       </c>
     </row>
     <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="28"/>
-      <c r="B31" s="35"/>
+      <c r="A31" s="20"/>
+      <c r="B31" s="36"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="28"/>
-      <c r="B32" s="35"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="36"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="28"/>
-      <c r="B33" s="36"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="28"/>
+      <c r="A34" s="20"/>
       <c r="B34" s="14"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="28"/>
-      <c r="B35" s="34" t="s">
+      <c r="A35" s="20"/>
+      <c r="B35" s="35" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -6291,36 +6308,36 @@
       </c>
     </row>
     <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="28"/>
-      <c r="B36" s="35"/>
+      <c r="A36" s="20"/>
+      <c r="B36" s="36"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="28"/>
-      <c r="B37" s="35"/>
+      <c r="A37" s="20"/>
+      <c r="B37" s="36"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="28"/>
-      <c r="B38" s="36"/>
+      <c r="A38" s="20"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="28"/>
+      <c r="A39" s="20"/>
       <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="28"/>
-      <c r="B40" s="34" t="s">
+      <c r="A40" s="20"/>
+      <c r="B40" s="35" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
@@ -6328,27 +6345,27 @@
       </c>
     </row>
     <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="28"/>
-      <c r="B41" s="35"/>
+      <c r="A41" s="20"/>
+      <c r="B41" s="36"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="28"/>
-      <c r="B42" s="36"/>
+      <c r="A42" s="20"/>
+      <c r="B42" s="37"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="28"/>
+      <c r="A43" s="20"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="28"/>
-      <c r="B44" s="34" t="s">
+      <c r="A44" s="20"/>
+      <c r="B44" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C44" s="4">
@@ -6356,29 +6373,29 @@
       </c>
     </row>
     <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="28"/>
-      <c r="B45" s="35"/>
+      <c r="A45" s="20"/>
+      <c r="B45" s="36"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="28"/>
-      <c r="B46" s="36"/>
+      <c r="A46" s="20"/>
+      <c r="B46" s="37"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="28"/>
+      <c r="A47" s="20"/>
       <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="28"/>
-      <c r="B48" s="34" t="s">
+      <c r="A48" s="20"/>
+      <c r="B48" s="35" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="4" t="s">
@@ -6442,8 +6459,8 @@
       </c>
     </row>
     <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="28"/>
-      <c r="B49" s="35"/>
+      <c r="A49" s="20"/>
+      <c r="B49" s="36"/>
       <c r="C49" s="4" t="s">
         <v>129</v>
       </c>
@@ -6505,8 +6522,8 @@
       </c>
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="28"/>
-      <c r="B50" s="36"/>
+      <c r="A50" s="20"/>
+      <c r="B50" s="37"/>
       <c r="C50" s="4" t="s">
         <v>130</v>
       </c>
@@ -6573,10 +6590,10 @@
       <c r="C51" s="8"/>
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="37" t="s">
+      <c r="A52" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="B52" s="37" t="s">
+      <c r="B52" s="34" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="5" t="s">
@@ -6584,29 +6601,29 @@
       </c>
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="29"/>
-      <c r="B53" s="29"/>
+      <c r="A53" s="21"/>
+      <c r="B53" s="21"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="29"/>
-      <c r="B54" s="29"/>
+      <c r="A54" s="21"/>
+      <c r="B54" s="21"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="29"/>
-      <c r="B55" s="30"/>
+      <c r="A55" s="21"/>
+      <c r="B55" s="22"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="29"/>
-      <c r="B56" s="37" t="s">
+      <c r="A56" s="21"/>
+      <c r="B56" s="34" t="s">
         <v>30</v>
       </c>
       <c r="C56" s="5">
@@ -6614,29 +6631,29 @@
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="29"/>
-      <c r="B57" s="29"/>
+      <c r="A57" s="21"/>
+      <c r="B57" s="21"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="29"/>
-      <c r="B58" s="30"/>
+      <c r="A58" s="21"/>
+      <c r="B58" s="22"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="29"/>
+      <c r="A59" s="21"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="29"/>
-      <c r="B60" s="37" t="s">
+      <c r="A60" s="21"/>
+      <c r="B60" s="34" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
@@ -6644,22 +6661,22 @@
       </c>
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="29"/>
-      <c r="B61" s="29"/>
+      <c r="A61" s="21"/>
+      <c r="B61" s="21"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="30"/>
-      <c r="B62" s="30"/>
+      <c r="A62" s="22"/>
+      <c r="B62" s="22"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="20" t="s">
+      <c r="A64" s="29" t="s">
         <v>26</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -6670,7 +6687,7 @@
       </c>
     </row>
     <row r="65" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="21"/>
+      <c r="A65" s="30"/>
       <c r="B65" s="4" t="s">
         <v>132</v>
       </c>
@@ -6679,7 +6696,7 @@
       </c>
     </row>
     <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="21"/>
+      <c r="A66" s="30"/>
       <c r="B66" s="4" t="s">
         <v>133</v>
       </c>
@@ -6688,7 +6705,7 @@
       </c>
     </row>
     <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="22"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="5" t="s">
         <v>134</v>
       </c>
@@ -6724,27 +6741,30 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C5AF949-03E5-4E6E-B7CB-0D2F8A5AE350}">
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:R67"/>
   <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="16.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
-    </row>
-    <row r="2" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:14" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -6755,34 +6775,37 @@
         <v>84</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
@@ -6795,7 +6818,7 @@
         <v>4</v>
       </c>
       <c r="F5" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
@@ -6821,8 +6844,11 @@
       <c r="N5" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O5" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
@@ -6835,25 +6861,25 @@
         <v>1</v>
       </c>
       <c r="F6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
         <v>2</v>
       </c>
       <c r="H6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" s="1">
         <v>3</v>
       </c>
       <c r="J6" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" s="1">
         <v>4</v>
       </c>
       <c r="L6" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M6" s="1">
         <v>5</v>
@@ -6861,12 +6887,15 @@
       <c r="N6" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="27" t="s">
+      <c r="O6" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="17" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -6876,9 +6905,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="27"/>
-      <c r="B8" s="25"/>
+    <row r="8" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="19"/>
+      <c r="B8" s="17"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
@@ -6886,9 +6915,9 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="25"/>
+    <row r="9" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="19"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
@@ -6896,9 +6925,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="27"/>
-      <c r="B10" s="25"/>
+    <row r="10" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="19"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -6906,35 +6935,35 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="27"/>
-      <c r="B11" s="25" t="s">
+    <row r="11" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="19"/>
+      <c r="B11" s="17" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="27"/>
-      <c r="B12" s="25"/>
+    <row r="12" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="19"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="27"/>
-      <c r="B13" s="25"/>
+    <row r="13" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="19"/>
+      <c r="B13" s="17"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="27"/>
-    </row>
-    <row r="15" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="27"/>
-      <c r="B15" s="31" t="s">
+    <row r="14" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="19"/>
+    </row>
+    <row r="15" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="19"/>
+      <c r="B15" s="23" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -6944,9 +6973,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="27"/>
-      <c r="B16" s="32"/>
+    <row r="16" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="19"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
@@ -6954,9 +6983,9 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="27"/>
-      <c r="B17" s="32"/>
+    <row r="17" spans="1:6" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="19"/>
+      <c r="B17" s="24"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
@@ -6964,9 +6993,9 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="27"/>
-      <c r="B18" s="33"/>
+    <row r="18" spans="1:6" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="19"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
@@ -6974,14 +7003,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
-    </row>
-    <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28" t="s">
+      <c r="F19" s="39"/>
+    </row>
+    <row r="20" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="20" t="s">
         <v>131</v>
       </c>
       <c r="B20" s="38" t="s">
@@ -6991,36 +7021,37 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="28"/>
+    <row r="21" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="20"/>
       <c r="B21" s="38"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="28"/>
+    <row r="22" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="20"/>
       <c r="B22" s="38"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="28"/>
+    <row r="23" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="20"/>
       <c r="B23" s="38"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="28"/>
+    <row r="24" spans="1:6" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="20"/>
       <c r="B24" s="12"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
-    </row>
-    <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="28"/>
+      <c r="F24" s="39"/>
+    </row>
+    <row r="25" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="20"/>
       <c r="B25" s="38" t="s">
         <v>16</v>
       </c>
@@ -7028,186 +7059,187 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="28"/>
+    <row r="26" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="20"/>
       <c r="B26" s="38"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="28"/>
+    <row r="27" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="20"/>
       <c r="B27" s="38"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="28"/>
+    <row r="28" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="20"/>
       <c r="B28" s="38"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="28"/>
+    <row r="29" spans="1:6" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="20"/>
       <c r="B29" s="13"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
-    </row>
-    <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="28"/>
-      <c r="B30" s="34" t="s">
+      <c r="F29" s="39"/>
+    </row>
+    <row r="30" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="20"/>
+      <c r="B30" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="28"/>
-      <c r="B31" s="35"/>
+    <row r="31" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="20"/>
+      <c r="B31" s="36"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="28"/>
-      <c r="B32" s="35"/>
+    <row r="32" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="20"/>
+      <c r="B32" s="36"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="28"/>
-      <c r="B33" s="36"/>
+    <row r="33" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="20"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="28"/>
+    <row r="34" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="20"/>
       <c r="B34" s="14"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="28"/>
-      <c r="B35" s="34" t="s">
+      <c r="F34" s="39"/>
+    </row>
+    <row r="35" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="20"/>
+      <c r="B35" s="35" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="28"/>
-      <c r="B36" s="35"/>
+    <row r="36" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="20"/>
+      <c r="B36" s="36"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="28"/>
-      <c r="B37" s="35"/>
+    <row r="37" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="20"/>
+      <c r="B37" s="36"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="28"/>
-      <c r="B38" s="36"/>
+    <row r="38" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="20"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="28"/>
+    <row r="39" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="20"/>
       <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
-    </row>
-    <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="28"/>
-      <c r="B40" s="34" t="s">
+      <c r="F39" s="39"/>
+    </row>
+    <row r="40" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="20"/>
+      <c r="B40" s="35" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="28"/>
-      <c r="B41" s="35"/>
+    <row r="41" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="20"/>
+      <c r="B41" s="36"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="28"/>
-      <c r="B42" s="36"/>
+    <row r="42" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="20"/>
+      <c r="B42" s="37"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="28"/>
+    <row r="43" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="20"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
-    </row>
-    <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="28"/>
-      <c r="B44" s="34" t="s">
+      <c r="F43" s="40"/>
+    </row>
+    <row r="44" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="20"/>
+      <c r="B44" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C44" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="28"/>
-      <c r="B45" s="35"/>
+    <row r="45" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="20"/>
+      <c r="B45" s="36"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="28"/>
-      <c r="B46" s="36"/>
+    <row r="46" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="20"/>
+      <c r="B46" s="37"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="28"/>
+    <row r="47" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="20"/>
       <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
-    </row>
-    <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="28"/>
-      <c r="B48" s="34" t="s">
+      <c r="F47" s="39"/>
+    </row>
+    <row r="48" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="20"/>
+      <c r="B48" s="35" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>29</v>
       </c>
       <c r="D48" s="4">
-        <f t="shared" ref="D48:Q48" si="0">D20+D25+D30+D35</f>
+        <f t="shared" ref="D48:R48" si="0">D20+D25+D30+D35</f>
         <v>0</v>
       </c>
       <c r="E48" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="G48" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7252,25 +7284,25 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="28"/>
-      <c r="B49" s="35"/>
+      <c r="R48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="20"/>
+      <c r="B49" s="36"/>
       <c r="C49" s="4" t="s">
         <v>129</v>
       </c>
       <c r="D49" s="4">
-        <f t="shared" ref="D49:Q49" si="1">D22+D27+D32+D37+D41</f>
+        <f t="shared" ref="D49:R49" si="1">D22+D27+D32+D37+D41</f>
         <v>0</v>
       </c>
       <c r="E49" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="G49" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -7315,10 +7347,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="28"/>
-      <c r="B50" s="36"/>
+      <c r="R49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="20"/>
+      <c r="B50" s="37"/>
       <c r="C50" s="4" t="s">
         <v>130</v>
       </c>
@@ -7330,12 +7366,8 @@
         <f>E48*(1+E49*0.02)</f>
         <v>0</v>
       </c>
-      <c r="F50" s="4">
-        <f t="shared" ref="F50:Q50" si="2">F48*(1+F49*0.02)</f>
-        <v>0</v>
-      </c>
       <c r="G50" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="G50:R50" si="2">G48*(1+G49*0.02)</f>
         <v>0</v>
       </c>
       <c r="H50" s="4">
@@ -7378,100 +7410,105 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:17" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="37" t="s">
+    <row r="52" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="B52" s="37" t="s">
+      <c r="B52" s="34" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="29"/>
-      <c r="B53" s="29"/>
+    <row r="53" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="21"/>
+      <c r="B53" s="21"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="29"/>
-      <c r="B54" s="29"/>
+    <row r="54" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="21"/>
+      <c r="B54" s="21"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="29"/>
-      <c r="B55" s="30"/>
+    <row r="55" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="21"/>
+      <c r="B55" s="22"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="29"/>
-      <c r="B56" s="37" t="s">
+    <row r="56" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="21"/>
+      <c r="B56" s="34" t="s">
         <v>30</v>
       </c>
       <c r="C56" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="29"/>
-      <c r="B57" s="29"/>
+    <row r="57" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="21"/>
+      <c r="B57" s="21"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="29"/>
-      <c r="B58" s="30"/>
+    <row r="58" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="21"/>
+      <c r="B58" s="22"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="29"/>
+    <row r="59" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="21"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
-    </row>
-    <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="29"/>
-      <c r="B60" s="37" t="s">
+      <c r="F59" s="39"/>
+    </row>
+    <row r="60" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="21"/>
+      <c r="B60" s="34" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="29"/>
-      <c r="B61" s="29"/>
+    <row r="61" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="21"/>
+      <c r="B61" s="21"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="30"/>
-      <c r="B62" s="30"/>
+    <row r="62" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="22"/>
+      <c r="B62" s="22"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="20" t="s">
+    <row r="63" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="29" t="s">
         <v>26</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -7480,36 +7517,50 @@
       <c r="C64" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="21"/>
+      <c r="F64" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="30"/>
       <c r="B65" s="4" t="s">
         <v>132</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="21"/>
+      <c r="F65" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="30"/>
       <c r="B66" s="4" t="s">
         <v>133</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="22"/>
+      <c r="F66" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="31"/>
       <c r="B67" s="5" t="s">
         <v>134</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>135</v>
       </c>
+      <c r="F67" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A64:A67"/>
     <mergeCell ref="A7:A18"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B7:B10"/>
@@ -7525,8 +7576,6 @@
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="B35:B38"/>
     <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A64:A67"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7536,27 +7585,49 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB9C480B-7650-4DE9-B7AF-42C282E029C5}">
-  <dimension ref="A1:AB67"/>
+  <dimension ref="A1:AA69"/>
   <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="16.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1</v>
+      </c>
+      <c r="K2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="2"/>
     </row>
-    <row r="4" spans="1:28" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -7585,130 +7656,3286 @@
         <v>101</v>
       </c>
       <c r="L4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA4" s="1"/>
+    </row>
+    <row r="5" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="1">
+        <v>5</v>
+      </c>
+      <c r="E7" s="1">
+        <v>5</v>
+      </c>
+      <c r="F7" s="1">
+        <v>5</v>
+      </c>
+      <c r="G7" s="1">
+        <v>5</v>
+      </c>
+      <c r="H7" s="1">
+        <v>5</v>
+      </c>
+      <c r="I7" s="1">
+        <v>5</v>
+      </c>
+      <c r="J7" s="1">
+        <v>5</v>
+      </c>
+      <c r="K7" s="1">
+        <v>5</v>
+      </c>
+      <c r="L7" s="1">
+        <v>5</v>
+      </c>
+      <c r="M7" s="1">
+        <v>5</v>
+      </c>
+      <c r="N7" s="1">
+        <v>5</v>
+      </c>
+      <c r="O7" s="1">
+        <v>5</v>
+      </c>
+      <c r="P7" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>5</v>
+      </c>
+      <c r="R7" s="1">
+        <v>5</v>
+      </c>
+      <c r="S7" s="1">
+        <v>5</v>
+      </c>
+      <c r="T7" s="1">
+        <v>5</v>
+      </c>
+      <c r="U7" s="1">
+        <v>5</v>
+      </c>
+      <c r="V7" s="1">
+        <v>5</v>
+      </c>
+      <c r="W7" s="1">
+        <v>5</v>
+      </c>
+      <c r="X7" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AA7" s="1"/>
+    </row>
+    <row r="8" spans="1:27" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1">
+        <v>2</v>
+      </c>
+      <c r="K8" s="1">
+        <v>2</v>
+      </c>
+      <c r="L8" s="1">
+        <v>3</v>
+      </c>
+      <c r="M8" s="1">
+        <v>3</v>
+      </c>
+      <c r="N8" s="1">
+        <v>3</v>
+      </c>
+      <c r="O8" s="1">
+        <v>3</v>
+      </c>
+      <c r="P8" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>4</v>
+      </c>
+      <c r="R8" s="1">
+        <v>5</v>
+      </c>
+      <c r="S8" s="1">
+        <v>5</v>
+      </c>
+      <c r="T8" s="1">
+        <v>5</v>
+      </c>
+      <c r="U8" s="1">
+        <v>5</v>
+      </c>
+      <c r="V8" s="1">
+        <v>6</v>
+      </c>
+      <c r="W8" s="1">
+        <v>6</v>
+      </c>
+      <c r="X8" s="1">
+        <v>6</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>6</v>
+      </c>
+      <c r="AA8" s="1"/>
+    </row>
+    <row r="9" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="3">
+        <v>155</v>
+      </c>
+      <c r="E9" s="3">
+        <v>130</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G9" s="3">
+        <v>72</v>
+      </c>
+      <c r="H9" s="3">
+        <v>175</v>
+      </c>
+      <c r="I9" s="3">
+        <v>64</v>
+      </c>
+      <c r="J9" s="3">
+        <v>200</v>
+      </c>
+      <c r="K9" s="3">
+        <v>250</v>
+      </c>
+      <c r="L9" s="3">
+        <v>270</v>
+      </c>
+      <c r="M9" s="3">
+        <v>290</v>
+      </c>
+      <c r="N9" s="3">
+        <v>275</v>
+      </c>
+      <c r="O9" s="3">
+        <v>280</v>
+      </c>
+      <c r="P9" s="3">
+        <v>290</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>295</v>
+      </c>
+      <c r="R9" s="3">
+        <v>325</v>
+      </c>
+      <c r="S9" s="3">
+        <v>350</v>
+      </c>
+      <c r="T9" s="3">
+        <v>345</v>
+      </c>
+      <c r="U9" s="3">
+        <v>340</v>
+      </c>
+      <c r="V9" s="3">
+        <v>350</v>
+      </c>
+      <c r="W9" s="3">
+        <v>365</v>
+      </c>
+      <c r="X9" s="3">
+        <v>370</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="19"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>800</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G10" s="3">
+        <v>500</v>
+      </c>
+      <c r="H10" s="3">
+        <v>900</v>
+      </c>
+      <c r="I10" s="3">
+        <v>500</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L10" s="3">
+        <v>900</v>
+      </c>
+      <c r="M10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O10" s="3">
+        <v>900</v>
+      </c>
+      <c r="P10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>800</v>
+      </c>
+      <c r="R10" s="3">
+        <v>950</v>
+      </c>
+      <c r="S10" s="3">
+        <v>1050</v>
+      </c>
+      <c r="T10" s="3">
+        <v>2000</v>
+      </c>
+      <c r="U10" s="3">
+        <v>1550</v>
+      </c>
+      <c r="V10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X10" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="19"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="3">
+        <v>14</v>
+      </c>
+      <c r="E11" s="3">
+        <v>15</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G11" s="3">
+        <v>14</v>
+      </c>
+      <c r="H11" s="3">
+        <v>14</v>
+      </c>
+      <c r="I11" s="3">
+        <v>10</v>
+      </c>
+      <c r="J11" s="3">
+        <v>13</v>
+      </c>
+      <c r="K11" s="3">
+        <v>14</v>
+      </c>
+      <c r="L11" s="3">
+        <v>12</v>
+      </c>
+      <c r="M11" s="3">
+        <v>14</v>
+      </c>
+      <c r="N11" s="3">
+        <v>14</v>
+      </c>
+      <c r="O11" s="3">
+        <v>14</v>
+      </c>
+      <c r="P11" s="3">
+        <v>15</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>15</v>
+      </c>
+      <c r="R11" s="3">
+        <v>17</v>
+      </c>
+      <c r="S11" s="3">
+        <v>16</v>
+      </c>
+      <c r="T11" s="3">
+        <v>14</v>
+      </c>
+      <c r="U11" s="3">
+        <v>21</v>
+      </c>
+      <c r="V11" s="3">
+        <v>19</v>
+      </c>
+      <c r="W11" s="3">
+        <v>18</v>
+      </c>
+      <c r="X11" s="3">
+        <v>18</v>
+      </c>
+      <c r="Y11" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="19"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="19"/>
+      <c r="B13" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="19"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="19"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="19"/>
+    </row>
+    <row r="17" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="19"/>
+      <c r="B17" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="N17" s="3">
+        <v>-0.1</v>
+      </c>
+      <c r="O17" s="3">
+        <v>-0.2</v>
+      </c>
+      <c r="P17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>-0.1</v>
+      </c>
+      <c r="R17" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="S17" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="T17" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="U17" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V17" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="W17" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="X17" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="19"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0.65</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="N18" s="3">
+        <v>0.85</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="P18" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="R18" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="S18" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="T18" s="3">
+        <v>1</v>
+      </c>
+      <c r="U18" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="V18" s="3">
+        <v>1</v>
+      </c>
+      <c r="W18" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="X18" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="19"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="K19" s="3">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="M19" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="N19" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="O19" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="P19" s="3">
+        <v>-0.2</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="R19" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="S19" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="T19" s="3">
+        <v>0</v>
+      </c>
+      <c r="U19" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V19" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="W19" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="X19" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="Y19" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="19"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-0.2</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>-0.2</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="V20" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+    </row>
+    <row r="22" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="4">
+        <v>12</v>
+      </c>
+      <c r="E22" s="4">
+        <v>12</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G22" s="4">
+        <v>6</v>
+      </c>
+      <c r="H22" s="4">
+        <v>12</v>
+      </c>
+      <c r="I22" s="4">
+        <v>6</v>
+      </c>
+      <c r="J22" s="4">
+        <v>13</v>
+      </c>
+      <c r="K22" s="4">
+        <v>13</v>
+      </c>
+      <c r="L22" s="4">
+        <v>13</v>
+      </c>
+      <c r="M22" s="4">
+        <v>13</v>
+      </c>
+      <c r="N22" s="4">
+        <v>13</v>
+      </c>
+      <c r="O22" s="4">
+        <v>13</v>
+      </c>
+      <c r="P22" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>14</v>
+      </c>
+      <c r="R22" s="4">
+        <v>15</v>
+      </c>
+      <c r="S22" s="4">
+        <v>15</v>
+      </c>
+      <c r="T22" s="4">
+        <v>16</v>
+      </c>
+      <c r="U22" s="4">
+        <v>15</v>
+      </c>
+      <c r="V22" s="4">
+        <v>15</v>
+      </c>
+      <c r="W22" s="4">
+        <v>15</v>
+      </c>
+      <c r="X22" s="4">
+        <v>15</v>
+      </c>
+      <c r="Y22" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="20"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="4">
+        <f>0.7*D28</f>
+        <v>909.99999999999989</v>
+      </c>
+      <c r="E23" s="4">
+        <f>0.7*E28</f>
+        <v>560</v>
+      </c>
+      <c r="F23" s="4" t="e">
+        <f>0.7*F28</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G23" s="4">
+        <f>0.7*G28</f>
+        <v>350</v>
+      </c>
+      <c r="H23" s="4">
+        <f>0.7*H28</f>
+        <v>630</v>
+      </c>
+      <c r="I23" s="4">
+        <f>0.7*I28</f>
+        <v>350</v>
+      </c>
+      <c r="J23" s="4">
+        <f>0.7*J28</f>
+        <v>840</v>
+      </c>
+      <c r="K23" s="4">
+        <f>0.7*K28</f>
+        <v>1050</v>
+      </c>
+      <c r="L23" s="4">
+        <f>0.7*L28</f>
+        <v>630</v>
+      </c>
+      <c r="M23" s="4">
+        <f>0.7*M28</f>
+        <v>840</v>
+      </c>
+      <c r="N23" s="4">
+        <f>0.7*N28</f>
+        <v>700</v>
+      </c>
+      <c r="O23" s="4">
+        <f>0.7*O28</f>
+        <v>630</v>
+      </c>
+      <c r="P23" s="4">
+        <f>0.7*P28</f>
+        <v>1050</v>
+      </c>
+      <c r="Q23" s="4">
+        <f>0.7*Q28</f>
+        <v>560</v>
+      </c>
+      <c r="R23" s="4">
+        <f>0.7*R28</f>
+        <v>665</v>
+      </c>
+      <c r="S23" s="4">
+        <f>0.7*S28</f>
+        <v>735</v>
+      </c>
+      <c r="T23" s="4">
+        <f>0.7*T28</f>
+        <v>1400</v>
+      </c>
+      <c r="U23" s="4">
+        <f>0.7*U28</f>
+        <v>1085</v>
+      </c>
+      <c r="V23" s="4">
+        <f>0.7*V28</f>
+        <v>979.99999999999989</v>
+      </c>
+      <c r="W23" s="4">
+        <f>0.7*W28</f>
+        <v>700</v>
+      </c>
+      <c r="X23" s="4">
+        <f>0.7*X28</f>
+        <v>770</v>
+      </c>
+      <c r="Y23" s="4">
+        <f>0.7*Y28</f>
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="20"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="4">
+        <v>6</v>
+      </c>
+      <c r="E24" s="4">
+        <v>6</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G24" s="4">
+        <v>5</v>
+      </c>
+      <c r="H24" s="4">
+        <v>7</v>
+      </c>
+      <c r="I24" s="4">
+        <v>5</v>
+      </c>
+      <c r="J24" s="4">
+        <v>6</v>
+      </c>
+      <c r="K24" s="4">
+        <v>6</v>
+      </c>
+      <c r="L24" s="4">
+        <v>7</v>
+      </c>
+      <c r="M24" s="4">
+        <v>7</v>
+      </c>
+      <c r="N24" s="4">
+        <v>7</v>
+      </c>
+      <c r="O24" s="4">
+        <v>7</v>
+      </c>
+      <c r="P24" s="4">
+        <v>7</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>8</v>
+      </c>
+      <c r="R24" s="4">
+        <v>9</v>
+      </c>
+      <c r="S24" s="4">
+        <v>9</v>
+      </c>
+      <c r="T24" s="4">
+        <v>9</v>
+      </c>
+      <c r="U24" s="4">
+        <v>10</v>
+      </c>
+      <c r="V24" s="4">
+        <v>10</v>
+      </c>
+      <c r="W24" s="4">
+        <v>11</v>
+      </c>
+      <c r="X24" s="4">
+        <v>10</v>
+      </c>
+      <c r="Y24" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="20"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="E25" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="F25" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="G25" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="H25" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I25" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="J25" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="K25" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="L25" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="M25" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="N25" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="O25" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="P25" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="Q25" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="R25" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="S25" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="T25" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="U25" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="V25" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="W25" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="X25" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="Y25" s="4">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="20"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+    </row>
+    <row r="27" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="20"/>
+      <c r="B27" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="4">
+        <v>19</v>
+      </c>
+      <c r="E27" s="4">
+        <v>19</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G27" s="4">
+        <v>8</v>
+      </c>
+      <c r="H27" s="4">
+        <v>20</v>
+      </c>
+      <c r="I27" s="4">
+        <v>8</v>
+      </c>
+      <c r="J27" s="4">
+        <v>20</v>
+      </c>
+      <c r="K27" s="4">
+        <v>20</v>
+      </c>
+      <c r="L27" s="4">
+        <v>20</v>
+      </c>
+      <c r="M27" s="4">
+        <v>20</v>
+      </c>
+      <c r="N27" s="4">
+        <v>20</v>
+      </c>
+      <c r="O27" s="4">
+        <v>20</v>
+      </c>
+      <c r="P27" s="4">
+        <v>20</v>
+      </c>
+      <c r="Q27" s="4">
+        <v>22</v>
+      </c>
+      <c r="R27" s="4">
+        <v>23</v>
+      </c>
+      <c r="S27" s="4">
+        <v>23</v>
+      </c>
+      <c r="T27" s="4">
+        <v>24</v>
+      </c>
+      <c r="U27" s="4">
+        <v>23</v>
+      </c>
+      <c r="V27" s="4">
+        <v>24</v>
+      </c>
+      <c r="W27" s="4">
+        <v>24</v>
+      </c>
+      <c r="X27" s="4">
+        <v>24</v>
+      </c>
+      <c r="Y27" s="4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="20"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="4">
+        <f>D10</f>
+        <v>1300</v>
+      </c>
+      <c r="E28" s="4">
+        <f>E10</f>
+        <v>800</v>
+      </c>
+      <c r="F28" s="4" t="str">
+        <f>F10</f>
+        <v>null</v>
+      </c>
+      <c r="G28" s="4">
+        <f>G10</f>
+        <v>500</v>
+      </c>
+      <c r="H28" s="4">
+        <f>H10</f>
+        <v>900</v>
+      </c>
+      <c r="I28" s="4">
+        <f>I10</f>
+        <v>500</v>
+      </c>
+      <c r="J28" s="4">
+        <f>J10</f>
+        <v>1200</v>
+      </c>
+      <c r="K28" s="4">
+        <f>K10</f>
+        <v>1500</v>
+      </c>
+      <c r="L28" s="4">
+        <f>L10</f>
+        <v>900</v>
+      </c>
+      <c r="M28" s="4">
+        <f>M10</f>
+        <v>1200</v>
+      </c>
+      <c r="N28" s="4">
+        <f>N10</f>
+        <v>1000</v>
+      </c>
+      <c r="O28" s="4">
+        <f>O10</f>
+        <v>900</v>
+      </c>
+      <c r="P28" s="4">
+        <f>P10</f>
+        <v>1500</v>
+      </c>
+      <c r="Q28" s="4">
+        <f>Q10</f>
+        <v>800</v>
+      </c>
+      <c r="R28" s="4">
+        <f>R10</f>
+        <v>950</v>
+      </c>
+      <c r="S28" s="4">
+        <f>S10</f>
+        <v>1050</v>
+      </c>
+      <c r="T28" s="4">
+        <f>T10</f>
+        <v>2000</v>
+      </c>
+      <c r="U28" s="4">
+        <f>U10</f>
+        <v>1550</v>
+      </c>
+      <c r="V28" s="4">
+        <f>V10</f>
+        <v>1400</v>
+      </c>
+      <c r="W28" s="4">
+        <f>W10</f>
+        <v>1000</v>
+      </c>
+      <c r="X28" s="4">
+        <f>X10</f>
+        <v>1100</v>
+      </c>
+      <c r="Y28" s="4">
+        <f>Y10</f>
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="20"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="4">
+        <v>6</v>
+      </c>
+      <c r="E29" s="4">
+        <v>6</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G29" s="4">
+        <v>5</v>
+      </c>
+      <c r="H29" s="4">
+        <v>6</v>
+      </c>
+      <c r="I29" s="4">
+        <v>5</v>
+      </c>
+      <c r="J29" s="4">
+        <v>6</v>
+      </c>
+      <c r="K29" s="4">
+        <v>6</v>
+      </c>
+      <c r="L29" s="4">
+        <v>7</v>
+      </c>
+      <c r="M29" s="4">
+        <v>7</v>
+      </c>
+      <c r="N29" s="4">
+        <v>7</v>
+      </c>
+      <c r="O29" s="4">
+        <v>8</v>
+      </c>
+      <c r="P29" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="4">
+        <v>8</v>
+      </c>
+      <c r="R29" s="4">
+        <v>9</v>
+      </c>
+      <c r="S29" s="4">
+        <v>9</v>
+      </c>
+      <c r="T29" s="4">
+        <v>9</v>
+      </c>
+      <c r="U29" s="4">
+        <v>10</v>
+      </c>
+      <c r="V29" s="4">
+        <v>10</v>
+      </c>
+      <c r="W29" s="4">
+        <v>11</v>
+      </c>
+      <c r="X29" s="4">
+        <v>10</v>
+      </c>
+      <c r="Y29" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="20"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="E30" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="F30" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="G30" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="H30" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I30" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="J30" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="K30" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="L30" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="M30" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="N30" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="O30" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="P30" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="Q30" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="R30" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="S30" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="T30" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="U30" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="V30" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="W30" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="X30" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="Y30" s="4">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="20"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+    </row>
+    <row r="32" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="20"/>
+      <c r="B32" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="4">
+        <v>17</v>
+      </c>
+      <c r="E32" s="4">
+        <v>17</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G32" s="4">
+        <v>7</v>
+      </c>
+      <c r="H32" s="4">
+        <v>18</v>
+      </c>
+      <c r="I32" s="4">
+        <v>7</v>
+      </c>
+      <c r="J32" s="4">
+        <v>18</v>
+      </c>
+      <c r="K32" s="4">
+        <v>19</v>
+      </c>
+      <c r="L32" s="4">
+        <v>18</v>
+      </c>
+      <c r="M32" s="4">
+        <v>18</v>
+      </c>
+      <c r="N32" s="4">
+        <v>18</v>
+      </c>
+      <c r="O32" s="4">
+        <v>18</v>
+      </c>
+      <c r="P32" s="4">
+        <v>18</v>
+      </c>
+      <c r="Q32" s="4">
+        <v>19</v>
+      </c>
+      <c r="R32" s="4">
+        <v>20</v>
+      </c>
+      <c r="S32" s="4">
+        <v>20</v>
+      </c>
+      <c r="T32" s="4">
+        <v>21</v>
+      </c>
+      <c r="U32" s="4">
+        <v>20</v>
+      </c>
+      <c r="V32" s="4">
+        <v>21</v>
+      </c>
+      <c r="W32" s="4">
+        <v>21</v>
+      </c>
+      <c r="X32" s="4">
+        <v>21</v>
+      </c>
+      <c r="Y32" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="20"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="4">
+        <f>0.9*D28</f>
+        <v>1170</v>
+      </c>
+      <c r="E33" s="4">
+        <f>0.9*E28</f>
+        <v>720</v>
+      </c>
+      <c r="F33" s="4" t="e">
+        <f>0.9*F28</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G33" s="4">
+        <f>0.9*G28</f>
+        <v>450</v>
+      </c>
+      <c r="H33" s="4">
+        <f>0.9*H28</f>
+        <v>810</v>
+      </c>
+      <c r="I33" s="4">
+        <f>0.9*I28</f>
+        <v>450</v>
+      </c>
+      <c r="J33" s="4">
+        <f>0.9*J28</f>
+        <v>1080</v>
+      </c>
+      <c r="K33" s="4">
+        <f>0.9*K28</f>
+        <v>1350</v>
+      </c>
+      <c r="L33" s="4">
+        <f>0.9*L28</f>
+        <v>810</v>
+      </c>
+      <c r="M33" s="4">
+        <f>0.9*M28</f>
+        <v>1080</v>
+      </c>
+      <c r="N33" s="4">
+        <f>0.9*N28</f>
+        <v>900</v>
+      </c>
+      <c r="O33" s="4">
+        <f>0.9*O28</f>
+        <v>810</v>
+      </c>
+      <c r="P33" s="4">
+        <f>0.9*P28</f>
+        <v>1350</v>
+      </c>
+      <c r="Q33" s="4">
+        <f>0.9*Q28</f>
+        <v>720</v>
+      </c>
+      <c r="R33" s="4">
+        <f>0.9*R28</f>
+        <v>855</v>
+      </c>
+      <c r="S33" s="4">
+        <f>0.9*S28</f>
+        <v>945</v>
+      </c>
+      <c r="T33" s="4">
+        <f>0.9*T28</f>
+        <v>1800</v>
+      </c>
+      <c r="U33" s="4">
+        <f>0.9*U28</f>
+        <v>1395</v>
+      </c>
+      <c r="V33" s="4">
+        <f>0.9*V28</f>
+        <v>1260</v>
+      </c>
+      <c r="W33" s="4">
+        <f>0.9*W28</f>
+        <v>900</v>
+      </c>
+      <c r="X33" s="4">
+        <f>0.9*X28</f>
+        <v>990</v>
+      </c>
+      <c r="Y33" s="4">
+        <f>0.9*Y28</f>
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="20"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" s="4">
+        <v>6</v>
+      </c>
+      <c r="E34" s="4">
+        <v>6</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G34" s="4">
+        <v>5</v>
+      </c>
+      <c r="H34" s="4">
+        <v>6</v>
+      </c>
+      <c r="I34" s="4">
+        <v>5</v>
+      </c>
+      <c r="J34" s="4">
+        <v>6</v>
+      </c>
+      <c r="K34" s="4">
+        <v>6</v>
+      </c>
+      <c r="L34" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="M34" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="N34" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="O34" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="P34" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="Q34" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="R34" s="4">
+        <v>9</v>
+      </c>
+      <c r="S34" s="4">
+        <v>9</v>
+      </c>
+      <c r="T34" s="4">
+        <v>9</v>
+      </c>
+      <c r="U34" s="4">
+        <v>10</v>
+      </c>
+      <c r="V34" s="4">
+        <v>10</v>
+      </c>
+      <c r="W34" s="4">
+        <v>11</v>
+      </c>
+      <c r="X34" s="4">
+        <v>10</v>
+      </c>
+      <c r="Y34" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="20"/>
+      <c r="B35" s="37"/>
+      <c r="C35" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="E35" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="F35" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="G35" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="H35" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I35" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="J35" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="K35" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="L35" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="M35" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="N35" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="O35" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="P35" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="Q35" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="R35" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="S35" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="T35" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="U35" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="V35" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="W35" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="X35" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="Y35" s="4">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="20"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="20"/>
+      <c r="B37" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="4">
+        <v>10</v>
+      </c>
+      <c r="E37" s="4">
+        <v>10</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G37" s="4">
+        <v>6</v>
+      </c>
+      <c r="H37" s="4">
+        <v>10</v>
+      </c>
+      <c r="I37" s="4">
+        <v>5</v>
+      </c>
+      <c r="J37" s="4">
+        <v>10</v>
+      </c>
+      <c r="K37" s="4">
+        <v>10</v>
+      </c>
+      <c r="L37" s="4">
+        <v>10</v>
+      </c>
+      <c r="M37" s="4">
+        <v>10</v>
+      </c>
+      <c r="N37" s="4">
+        <v>10</v>
+      </c>
+      <c r="O37" s="4">
+        <v>10</v>
+      </c>
+      <c r="P37" s="4">
+        <v>10</v>
+      </c>
+      <c r="Q37" s="4">
+        <v>11</v>
+      </c>
+      <c r="R37" s="4">
+        <v>12</v>
+      </c>
+      <c r="S37" s="4">
+        <v>12</v>
+      </c>
+      <c r="T37" s="4">
+        <v>13</v>
+      </c>
+      <c r="U37" s="4">
+        <v>12</v>
+      </c>
+      <c r="V37" s="4">
+        <v>12</v>
+      </c>
+      <c r="W37" s="4">
+        <v>12</v>
+      </c>
+      <c r="X37" s="4">
+        <v>12</v>
+      </c>
+      <c r="Y37" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="20"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="4">
+        <f>0.6*D28</f>
+        <v>780</v>
+      </c>
+      <c r="E38" s="4">
+        <f>0.6*E28</f>
+        <v>480</v>
+      </c>
+      <c r="F38" s="4" t="e">
+        <f>0.6*F28</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G38" s="4">
+        <f>0.6*G28</f>
+        <v>300</v>
+      </c>
+      <c r="H38" s="4">
+        <f>0.6*H28</f>
+        <v>540</v>
+      </c>
+      <c r="I38" s="4">
+        <f>0.6*I28</f>
+        <v>300</v>
+      </c>
+      <c r="J38" s="4">
+        <f>0.6*J28</f>
+        <v>720</v>
+      </c>
+      <c r="K38" s="4">
+        <f>0.6*K28</f>
+        <v>900</v>
+      </c>
+      <c r="L38" s="4">
+        <f>0.6*L28</f>
+        <v>540</v>
+      </c>
+      <c r="M38" s="4">
+        <f>0.6*M28</f>
+        <v>720</v>
+      </c>
+      <c r="N38" s="4">
+        <f>0.6*N28</f>
+        <v>600</v>
+      </c>
+      <c r="O38" s="4">
+        <f>0.6*O28</f>
+        <v>540</v>
+      </c>
+      <c r="P38" s="4">
+        <f>0.6*P28</f>
+        <v>900</v>
+      </c>
+      <c r="Q38" s="4">
+        <f>0.6*Q28</f>
+        <v>480</v>
+      </c>
+      <c r="R38" s="4">
+        <f>0.6*R28</f>
+        <v>570</v>
+      </c>
+      <c r="S38" s="4">
+        <f>0.6*S28</f>
+        <v>630</v>
+      </c>
+      <c r="T38" s="4">
+        <f>0.6*T28</f>
+        <v>1200</v>
+      </c>
+      <c r="U38" s="4">
+        <f>0.6*U28</f>
+        <v>930</v>
+      </c>
+      <c r="V38" s="4">
+        <f>0.6*V28</f>
+        <v>840</v>
+      </c>
+      <c r="W38" s="4">
+        <f>0.6*W28</f>
+        <v>600</v>
+      </c>
+      <c r="X38" s="4">
+        <f>0.6*X28</f>
+        <v>660</v>
+      </c>
+      <c r="Y38" s="4">
+        <f>0.6*Y28</f>
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="20"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="4">
+        <v>6</v>
+      </c>
+      <c r="E39" s="4">
+        <v>6</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G39" s="4">
+        <v>5</v>
+      </c>
+      <c r="H39" s="4">
+        <v>7</v>
+      </c>
+      <c r="I39" s="4">
+        <v>5</v>
+      </c>
+      <c r="J39" s="4">
+        <v>6</v>
+      </c>
+      <c r="K39" s="4">
+        <v>6</v>
+      </c>
+      <c r="L39" s="4">
+        <v>7</v>
+      </c>
+      <c r="M39" s="4">
+        <v>7</v>
+      </c>
+      <c r="N39" s="4">
+        <v>7</v>
+      </c>
+      <c r="O39" s="4">
+        <v>7</v>
+      </c>
+      <c r="P39" s="4">
+        <v>7</v>
+      </c>
+      <c r="Q39" s="4">
+        <v>8</v>
+      </c>
+      <c r="R39" s="4">
+        <v>9</v>
+      </c>
+      <c r="S39" s="4">
+        <v>9</v>
+      </c>
+      <c r="T39" s="4">
+        <v>9</v>
+      </c>
+      <c r="U39" s="4">
+        <v>10</v>
+      </c>
+      <c r="V39" s="4">
+        <v>10</v>
+      </c>
+      <c r="W39" s="4">
+        <v>11</v>
+      </c>
+      <c r="X39" s="4">
+        <v>10</v>
+      </c>
+      <c r="Y39" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="20"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="E40" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="F40" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="G40" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="H40" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I40" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="J40" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="K40" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="L40" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="M40" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="N40" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="O40" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="P40" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="Q40" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="R40" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="S40" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="T40" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="U40" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="V40" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="W40" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="X40" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="Y40" s="4">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="20"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+    </row>
+    <row r="42" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="20"/>
+      <c r="B42" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="4">
+        <f>0.9*D28</f>
+        <v>1170</v>
+      </c>
+      <c r="E42" s="4">
+        <f>0.9*E28</f>
+        <v>720</v>
+      </c>
+      <c r="F42" s="4" t="e">
+        <f>0.9*F28</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G42" s="4">
+        <f>0.9*G28</f>
+        <v>450</v>
+      </c>
+      <c r="H42" s="4">
+        <f>0.9*H28</f>
+        <v>810</v>
+      </c>
+      <c r="I42" s="4">
+        <f>0.9*I28</f>
+        <v>450</v>
+      </c>
+      <c r="J42" s="4">
+        <f>0.9*J28</f>
+        <v>1080</v>
+      </c>
+      <c r="K42" s="4">
+        <f>0.9*K28</f>
+        <v>1350</v>
+      </c>
+      <c r="L42" s="4">
+        <f>0.9*L28</f>
+        <v>810</v>
+      </c>
+      <c r="M42" s="4">
+        <f>0.9*M28</f>
+        <v>1080</v>
+      </c>
+      <c r="N42" s="4">
+        <f>0.9*N28</f>
+        <v>900</v>
+      </c>
+      <c r="O42" s="4">
+        <f>0.9*O28</f>
+        <v>810</v>
+      </c>
+      <c r="P42" s="4">
+        <f>0.9*P28</f>
+        <v>1350</v>
+      </c>
+      <c r="Q42" s="4">
+        <f>0.9*Q28</f>
+        <v>720</v>
+      </c>
+      <c r="R42" s="4">
+        <f>0.9*R28</f>
+        <v>855</v>
+      </c>
+      <c r="S42" s="4">
+        <f>0.9*S28</f>
+        <v>945</v>
+      </c>
+      <c r="T42" s="4">
+        <f>0.9*T28</f>
+        <v>1800</v>
+      </c>
+      <c r="U42" s="4">
+        <f>0.9*U28</f>
+        <v>1395</v>
+      </c>
+      <c r="V42" s="4">
+        <f>0.9*V28</f>
+        <v>1260</v>
+      </c>
+      <c r="W42" s="4">
+        <f>0.9*W28</f>
+        <v>900</v>
+      </c>
+      <c r="X42" s="4">
+        <f>0.9*X28</f>
+        <v>990</v>
+      </c>
+      <c r="Y42" s="4">
+        <f>0.9*Y28</f>
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="20"/>
+      <c r="B43" s="36"/>
+      <c r="C43" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" s="4">
+        <v>6</v>
+      </c>
+      <c r="E43" s="4">
+        <v>6</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G43" s="4">
+        <v>5</v>
+      </c>
+      <c r="H43" s="4">
+        <v>5</v>
+      </c>
+      <c r="I43" s="4">
+        <v>5</v>
+      </c>
+      <c r="J43" s="4">
+        <v>6</v>
+      </c>
+      <c r="K43" s="4">
+        <v>6</v>
+      </c>
+      <c r="L43" s="4">
+        <v>7</v>
+      </c>
+      <c r="M43" s="4">
+        <v>7</v>
+      </c>
+      <c r="N43" s="4">
+        <v>7</v>
+      </c>
+      <c r="O43" s="4">
+        <v>7</v>
+      </c>
+      <c r="P43" s="4">
+        <v>7</v>
+      </c>
+      <c r="Q43" s="4">
+        <v>8</v>
+      </c>
+      <c r="R43" s="4">
+        <v>9</v>
+      </c>
+      <c r="S43" s="4">
+        <v>9</v>
+      </c>
+      <c r="T43" s="4">
+        <v>9</v>
+      </c>
+      <c r="U43" s="4">
+        <v>10</v>
+      </c>
+      <c r="V43" s="4">
+        <v>10</v>
+      </c>
+      <c r="W43" s="4">
+        <v>11</v>
+      </c>
+      <c r="X43" s="4">
+        <v>10</v>
+      </c>
+      <c r="Y43" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="20"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="E44" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="F44" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="G44" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="H44" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I44" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="J44" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="K44" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="L44" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="M44" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="N44" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="O44" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="P44" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="Q44" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="R44" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="S44" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="T44" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="U44" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="V44" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="W44" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="X44" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="Y44" s="4">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="20"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+    </row>
+    <row r="46" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="20"/>
+      <c r="B46" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="C46" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="20"/>
+      <c r="B47" s="36"/>
+      <c r="C47" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="20"/>
+      <c r="B48" s="37"/>
+      <c r="C48" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="20"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+    </row>
+    <row r="50" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="20"/>
+      <c r="B50" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D50" s="4">
+        <f>D22+D27+D32+D37</f>
+        <v>58</v>
+      </c>
+      <c r="E50" s="4">
+        <f>E22+E27+E32+E37</f>
+        <v>58</v>
+      </c>
+      <c r="F50" s="4" t="e">
+        <f>F22+F27+F32+F37</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G50" s="4">
+        <f>G22+G27+G32+G37</f>
+        <v>27</v>
+      </c>
+      <c r="H50" s="4">
+        <f>H22+H27+H32+H37</f>
+        <v>60</v>
+      </c>
+      <c r="I50" s="4">
+        <f>I22+I27+I32+I37</f>
+        <v>26</v>
+      </c>
+      <c r="J50" s="4">
+        <f>J22+J27+J32+J37</f>
+        <v>61</v>
+      </c>
+      <c r="K50" s="4">
+        <f>K22+K27+K32+K37</f>
+        <v>62</v>
+      </c>
+      <c r="L50" s="4">
+        <f>L22+L27+L32+L37</f>
+        <v>61</v>
+      </c>
+      <c r="M50" s="4">
+        <f>M22+M27+M32+M37</f>
+        <v>61</v>
+      </c>
+      <c r="N50" s="4">
+        <f>N22+N27+N32+N37</f>
+        <v>61</v>
+      </c>
+      <c r="O50" s="4">
+        <f>O22+O27+O32+O37</f>
+        <v>61</v>
+      </c>
+      <c r="P50" s="4">
+        <f>P22+P27+P32+P37</f>
+        <v>61</v>
+      </c>
+      <c r="Q50" s="4">
+        <f t="shared" ref="Q50:Y50" si="0">Q22+Q27+Q32+Q37</f>
+        <v>66</v>
+      </c>
+      <c r="R50" s="4">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="S50" s="4">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="T50" s="4">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="U50" s="4">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="V50" s="4">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="W50" s="4">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="X50" s="4">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="Y50" s="4">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="20"/>
+      <c r="B51" s="36"/>
+      <c r="C51" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D51" s="4">
+        <f>D24+D29+D34+D39+D43</f>
+        <v>30</v>
+      </c>
+      <c r="E51" s="4">
+        <f>E24+E29+E34+E39+E43</f>
+        <v>30</v>
+      </c>
+      <c r="F51" s="4" t="e">
+        <f>F24+F29+F34+F39+F43</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G51" s="4">
+        <f>G24+G29+G34+G39+G43</f>
+        <v>25</v>
+      </c>
+      <c r="H51" s="4">
+        <f>H24+H29+H34+H39+H43</f>
+        <v>31</v>
+      </c>
+      <c r="I51" s="4">
+        <f>I24+I29+I34+I39+I43</f>
+        <v>25</v>
+      </c>
+      <c r="J51" s="4">
+        <f>J24+J29+J34+J39+J43</f>
+        <v>30</v>
+      </c>
+      <c r="K51" s="4">
+        <f>K24+K29+K34+K39+K43</f>
+        <v>30</v>
+      </c>
+      <c r="L51" s="4">
+        <f>L24+L29+L34+L39+L43</f>
+        <v>28.15</v>
+      </c>
+      <c r="M51" s="4">
+        <f>M24+M29+M34+M39+M43</f>
+        <v>28.15</v>
+      </c>
+      <c r="N51" s="4">
+        <f>N24+N29+N34+N39+N43</f>
+        <v>28.15</v>
+      </c>
+      <c r="O51" s="4">
+        <f>O24+O29+O34+O39+O43</f>
+        <v>29.15</v>
+      </c>
+      <c r="P51" s="4">
+        <f>P24+P29+P34+P39+P43</f>
+        <v>29.15</v>
+      </c>
+      <c r="Q51" s="4">
+        <f t="shared" ref="Q51:Y51" si="1">Q24+Q29+Q34+Q39+Q43</f>
+        <v>32.15</v>
+      </c>
+      <c r="R51" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="S51" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="T51" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="U51" s="4">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="V51" s="4">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="W51" s="4">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+      <c r="X51" s="4">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="Y51" s="4">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="20"/>
+      <c r="B52" s="37"/>
+      <c r="C52" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D52" s="4">
+        <f>D50*(1+D51*0.02)</f>
+        <v>92.800000000000011</v>
+      </c>
+      <c r="E52" s="4">
+        <f>E50*(1+E51*0.02)</f>
+        <v>92.800000000000011</v>
+      </c>
+      <c r="F52" s="4" t="e">
+        <f>F50*(1+F51*0.02)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G52" s="4">
+        <f>G50*(1+G51*0.02)</f>
+        <v>40.5</v>
+      </c>
+      <c r="H52" s="4">
+        <f>H50*(1+H51*0.02)</f>
+        <v>97.2</v>
+      </c>
+      <c r="I52" s="4">
+        <f>I50*(1+I51*0.02)</f>
+        <v>39</v>
+      </c>
+      <c r="J52" s="4">
+        <f>J50*(1+J51*0.02)</f>
+        <v>97.600000000000009</v>
+      </c>
+      <c r="K52" s="4">
+        <f>K50*(1+K51*0.02)</f>
+        <v>99.2</v>
+      </c>
+      <c r="L52" s="4">
+        <f>L50*(1+L51*0.02)</f>
+        <v>95.343000000000004</v>
+      </c>
+      <c r="M52" s="4">
+        <f>M50*(1+M51*0.02)</f>
+        <v>95.343000000000004</v>
+      </c>
+      <c r="N52" s="4">
+        <f>N50*(1+N51*0.02)</f>
+        <v>95.343000000000004</v>
+      </c>
+      <c r="O52" s="4">
+        <f>O50*(1+O51*0.02)</f>
+        <v>96.563000000000002</v>
+      </c>
+      <c r="P52" s="4">
+        <f>P50*(1+P51*0.02)</f>
+        <v>96.563000000000002</v>
+      </c>
+      <c r="Q52" s="4">
+        <f t="shared" ref="Q52:Y52" si="2">Q50*(1+Q51*0.02)</f>
+        <v>108.438</v>
+      </c>
+      <c r="R52" s="4">
+        <f t="shared" si="2"/>
+        <v>133</v>
+      </c>
+      <c r="S52" s="4">
+        <f t="shared" si="2"/>
+        <v>133</v>
+      </c>
+      <c r="T52" s="4">
+        <f t="shared" si="2"/>
+        <v>140.6</v>
+      </c>
+      <c r="U52" s="4">
+        <f t="shared" si="2"/>
+        <v>140</v>
+      </c>
+      <c r="V52" s="4">
+        <f t="shared" si="2"/>
+        <v>144</v>
+      </c>
+      <c r="W52" s="4">
+        <f t="shared" si="2"/>
+        <v>151.20000000000002</v>
+      </c>
+      <c r="X52" s="4">
+        <f t="shared" si="2"/>
+        <v>144</v>
+      </c>
+      <c r="Y52" s="4">
+        <f t="shared" si="2"/>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="2"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+    </row>
+    <row r="54" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="B54" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="21"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="21"/>
+      <c r="B56" s="21"/>
+      <c r="C56" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="21"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="21"/>
+      <c r="B58" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C58" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="21"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="21"/>
+      <c r="B60" s="22"/>
+      <c r="C60" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="21"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+    </row>
+    <row r="62" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="21"/>
+      <c r="B62" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="21"/>
+      <c r="B63" s="21"/>
+      <c r="C63" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="22"/>
+      <c r="B64" s="22"/>
+      <c r="C64" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D66" s="6">
+        <v>1</v>
+      </c>
+      <c r="E66" s="6">
+        <v>1</v>
+      </c>
+      <c r="F66" s="6">
+        <v>0</v>
+      </c>
+      <c r="G66" s="6">
+        <v>1</v>
+      </c>
+      <c r="H66" s="6">
+        <v>1</v>
+      </c>
+      <c r="I66" s="6">
+        <v>1</v>
+      </c>
+      <c r="J66" s="6">
+        <v>1</v>
+      </c>
+      <c r="K66" s="6">
+        <v>1</v>
+      </c>
+      <c r="L66" s="6">
+        <v>1</v>
+      </c>
+      <c r="M66" s="6">
+        <v>1</v>
+      </c>
+      <c r="N66" s="6">
+        <v>1</v>
+      </c>
+      <c r="O66" s="6">
+        <v>1</v>
+      </c>
+      <c r="P66" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q66" s="6">
+        <v>1</v>
+      </c>
+      <c r="R66" s="6">
+        <v>1</v>
+      </c>
+      <c r="S66" s="6">
+        <v>1</v>
+      </c>
+      <c r="T66" s="6">
+        <v>1</v>
+      </c>
+      <c r="U66" s="6">
+        <v>1</v>
+      </c>
+      <c r="V66" s="6">
+        <v>1</v>
+      </c>
+      <c r="W66" s="6">
+        <v>1</v>
+      </c>
+      <c r="X66" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y66" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="30"/>
+      <c r="B67" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D67" s="4">
+        <v>1</v>
+      </c>
+      <c r="E67" s="4">
+        <v>1</v>
+      </c>
+      <c r="F67" s="4">
+        <v>0</v>
+      </c>
+      <c r="G67" s="4">
+        <v>1</v>
+      </c>
+      <c r="H67" s="4">
+        <v>1</v>
+      </c>
+      <c r="I67" s="4">
+        <v>1</v>
+      </c>
+      <c r="J67" s="4">
+        <v>1</v>
+      </c>
+      <c r="K67" s="4">
+        <v>1</v>
+      </c>
+      <c r="L67" s="4">
+        <v>1</v>
+      </c>
+      <c r="M67" s="4">
+        <v>1</v>
+      </c>
+      <c r="N67" s="4">
+        <v>1</v>
+      </c>
+      <c r="O67" s="4">
+        <v>0</v>
+      </c>
+      <c r="P67" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q67" s="4">
+        <v>1</v>
+      </c>
+      <c r="R67" s="4">
+        <v>1</v>
+      </c>
+      <c r="S67" s="4">
+        <v>1</v>
+      </c>
+      <c r="T67" s="4">
+        <v>1</v>
+      </c>
+      <c r="U67" s="4">
+        <v>1</v>
+      </c>
+      <c r="V67" s="4">
+        <v>1</v>
+      </c>
+      <c r="W67" s="4">
+        <v>1</v>
+      </c>
+      <c r="X67" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y67" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="30"/>
+      <c r="B68" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D68" s="4">
+        <v>1</v>
+      </c>
+      <c r="E68" s="4">
+        <v>0</v>
+      </c>
+      <c r="F68" s="4">
+        <v>0</v>
+      </c>
+      <c r="G68" s="4">
+        <v>0</v>
+      </c>
+      <c r="H68" s="4">
+        <v>0</v>
+      </c>
+      <c r="I68" s="4">
+        <v>0</v>
+      </c>
+      <c r="J68" s="4">
+        <v>0</v>
+      </c>
+      <c r="K68" s="4">
+        <v>1</v>
+      </c>
+      <c r="L68" s="4">
+        <v>0</v>
+      </c>
+      <c r="M68" s="4">
+        <v>0</v>
+      </c>
+      <c r="N68" s="4">
+        <v>0</v>
+      </c>
+      <c r="O68" s="4">
+        <v>0</v>
+      </c>
+      <c r="P68" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="4">
+        <v>0</v>
+      </c>
+      <c r="R68" s="4">
+        <v>0</v>
+      </c>
+      <c r="S68" s="4">
+        <v>0</v>
+      </c>
+      <c r="T68" s="4">
+        <v>0</v>
+      </c>
+      <c r="U68" s="4">
+        <v>0</v>
+      </c>
+      <c r="V68" s="4">
+        <v>0</v>
+      </c>
+      <c r="W68" s="4">
+        <v>0</v>
+      </c>
+      <c r="X68" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="31"/>
+      <c r="B69" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D69" s="5">
+        <v>0</v>
+      </c>
+      <c r="E69" s="5">
+        <v>0</v>
+      </c>
+      <c r="F69" s="5">
+        <v>1</v>
+      </c>
+      <c r="G69" s="5">
+        <v>0</v>
+      </c>
+      <c r="H69" s="5">
+        <v>1</v>
+      </c>
+      <c r="I69" s="5">
+        <v>0</v>
+      </c>
+      <c r="J69" s="5">
+        <v>0</v>
+      </c>
+      <c r="K69" s="5">
+        <v>0</v>
+      </c>
+      <c r="L69" s="5">
+        <v>0</v>
+      </c>
+      <c r="M69" s="5">
+        <v>0</v>
+      </c>
+      <c r="N69" s="5">
+        <v>0</v>
+      </c>
+      <c r="O69" s="5">
+        <v>0</v>
+      </c>
+      <c r="P69" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="5">
+        <v>0</v>
+      </c>
+      <c r="R69" s="5">
+        <v>0</v>
+      </c>
+      <c r="S69" s="5">
+        <v>1</v>
+      </c>
+      <c r="T69" s="5">
+        <v>0</v>
+      </c>
+      <c r="U69" s="5">
+        <v>0</v>
+      </c>
+      <c r="V69" s="5">
+        <v>0</v>
+      </c>
+      <c r="W69" s="5">
+        <v>0</v>
+      </c>
+      <c r="X69" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A9:A20"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="A22:A52"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="A54:A64"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="B42:B44"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21A46B60-4F3A-4D99-AC29-6361CD3DE12A}">
+  <dimension ref="A1:R67"/>
+  <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="3" width="16.625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:12" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AB4" s="1"/>
-    </row>
-    <row r="5" spans="1:28" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G4" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
         <v>124</v>
       </c>
       <c r="D5" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L5" s="1">
-        <v>5</v>
-      </c>
-      <c r="M5" s="1">
-        <v>5</v>
-      </c>
-      <c r="N5" s="1">
-        <v>5</v>
-      </c>
-      <c r="O5" s="1">
-        <v>5</v>
-      </c>
-      <c r="P5" s="1">
-        <v>5</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>5</v>
-      </c>
-      <c r="R5" s="1">
-        <v>5</v>
-      </c>
-      <c r="S5" s="1">
-        <v>5</v>
-      </c>
-      <c r="T5" s="1">
-        <v>5</v>
-      </c>
-      <c r="U5" s="1">
-        <v>5</v>
-      </c>
-      <c r="V5" s="1">
-        <v>5</v>
-      </c>
-      <c r="W5" s="1">
-        <v>5</v>
-      </c>
-      <c r="X5" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y5" s="1">
-        <v>5</v>
-      </c>
-      <c r="Z5" s="1">
-        <v>5</v>
-      </c>
-      <c r="AB5" s="1"/>
-    </row>
-    <row r="6" spans="1:28" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
@@ -7724,72 +10951,29 @@
         <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" s="1">
         <v>2</v>
       </c>
-      <c r="M6" s="1">
-        <v>3</v>
-      </c>
-      <c r="N6" s="1">
-        <v>3</v>
-      </c>
-      <c r="O6" s="1">
-        <v>3</v>
-      </c>
-      <c r="P6" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>3</v>
-      </c>
-      <c r="R6" s="1">
-        <v>4</v>
-      </c>
-      <c r="S6" s="1">
-        <v>5</v>
-      </c>
-      <c r="T6" s="1">
-        <v>5</v>
-      </c>
-      <c r="U6" s="1">
-        <v>5</v>
-      </c>
-      <c r="V6" s="1">
-        <v>5</v>
-      </c>
-      <c r="W6" s="1">
-        <v>6</v>
-      </c>
-      <c r="X6" s="1">
-        <v>6</v>
-      </c>
-      <c r="Y6" s="1">
-        <v>6</v>
-      </c>
-      <c r="Z6" s="1">
-        <v>6</v>
-      </c>
-      <c r="AB6" s="1"/>
-    </row>
-    <row r="7" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="27" t="s">
+    </row>
+    <row r="7" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="17" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -7799,9 +10983,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="27"/>
-      <c r="B8" s="25"/>
+    <row r="8" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="19"/>
+      <c r="B8" s="17"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
@@ -7809,9 +10993,9 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="25"/>
+    <row r="9" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="19"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
@@ -7819,9 +11003,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="27"/>
-      <c r="B10" s="25"/>
+    <row r="10" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="19"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -7829,35 +11013,35 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="27"/>
-      <c r="B11" s="25" t="s">
+    <row r="11" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="19"/>
+      <c r="B11" s="17" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="27"/>
-      <c r="B12" s="25"/>
+    <row r="12" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="19"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="27"/>
-      <c r="B13" s="25"/>
+    <row r="13" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="19"/>
+      <c r="B13" s="17"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="27"/>
-    </row>
-    <row r="15" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="27"/>
-      <c r="B15" s="31" t="s">
+    <row r="14" spans="1:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="19"/>
+    </row>
+    <row r="15" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="19"/>
+      <c r="B15" s="23" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -7867,9 +11051,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="27"/>
-      <c r="B16" s="32"/>
+    <row r="16" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="19"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
@@ -7878,8 +11062,8 @@
       </c>
     </row>
     <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="27"/>
-      <c r="B17" s="32"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="24"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
@@ -7888,8 +11072,8 @@
       </c>
     </row>
     <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="27"/>
-      <c r="B18" s="33"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
@@ -7904,7 +11088,7 @@
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="20" t="s">
         <v>131</v>
       </c>
       <c r="B20" s="38" t="s">
@@ -7915,35 +11099,35 @@
       </c>
     </row>
     <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="28"/>
+      <c r="A21" s="20"/>
       <c r="B21" s="38"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="28"/>
+      <c r="A22" s="20"/>
       <c r="B22" s="38"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="28"/>
+      <c r="A23" s="20"/>
       <c r="B23" s="38"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="28"/>
+      <c r="A24" s="20"/>
       <c r="B24" s="12"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="28"/>
+      <c r="A25" s="20"/>
       <c r="B25" s="38" t="s">
         <v>16</v>
       </c>
@@ -7952,36 +11136,36 @@
       </c>
     </row>
     <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="28"/>
+      <c r="A26" s="20"/>
       <c r="B26" s="38"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="28"/>
+      <c r="A27" s="20"/>
       <c r="B27" s="38"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="28"/>
+      <c r="A28" s="20"/>
       <c r="B28" s="38"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="28"/>
+      <c r="A29" s="20"/>
       <c r="B29" s="13"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="28"/>
-      <c r="B30" s="34" t="s">
+      <c r="A30" s="20"/>
+      <c r="B30" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -7989,138 +11173,138 @@
       </c>
     </row>
     <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="28"/>
-      <c r="B31" s="35"/>
+      <c r="A31" s="20"/>
+      <c r="B31" s="36"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="28"/>
-      <c r="B32" s="35"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="36"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="28"/>
-      <c r="B33" s="36"/>
+    <row r="33" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="20"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="28"/>
+    <row r="34" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="20"/>
       <c r="B34" s="14"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="28"/>
-      <c r="B35" s="34" t="s">
+    <row r="35" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="20"/>
+      <c r="B35" s="35" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="28"/>
-      <c r="B36" s="35"/>
+    <row r="36" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="20"/>
+      <c r="B36" s="36"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="28"/>
-      <c r="B37" s="35"/>
+    <row r="37" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="20"/>
+      <c r="B37" s="36"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="28"/>
-      <c r="B38" s="36"/>
+    <row r="38" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="20"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="28"/>
+    <row r="39" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="20"/>
       <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="28"/>
-      <c r="B40" s="34" t="s">
+    <row r="40" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="20"/>
+      <c r="B40" s="35" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="28"/>
-      <c r="B41" s="35"/>
+    <row r="41" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="20"/>
+      <c r="B41" s="36"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="28"/>
-      <c r="B42" s="36"/>
+    <row r="42" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="20"/>
+      <c r="B42" s="37"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="28"/>
+    <row r="43" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="20"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
     </row>
-    <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="28"/>
-      <c r="B44" s="34" t="s">
+    <row r="44" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="20"/>
+      <c r="B44" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C44" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="28"/>
-      <c r="B45" s="35"/>
+    <row r="45" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="20"/>
+      <c r="B45" s="36"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="28"/>
-      <c r="B46" s="36"/>
+    <row r="46" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="20"/>
+      <c r="B46" s="37"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="28"/>
+    <row r="47" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="20"/>
       <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
-    <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="28"/>
-      <c r="B48" s="34" t="s">
+    <row r="48" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="20"/>
+      <c r="B48" s="35" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>29</v>
       </c>
       <c r="D48" s="4">
-        <f t="shared" ref="D48:Q48" si="0">D20+D25+D30+D35</f>
+        <f t="shared" ref="D48:R48" si="0">D20+D25+D30+D35</f>
         <v>0</v>
       </c>
       <c r="E48" s="4">
@@ -8128,7 +11312,7 @@
         <v>0</v>
       </c>
       <c r="F48" s="4">
-        <f t="shared" si="0"/>
+        <f>F20+F25+F30+F35</f>
         <v>0</v>
       </c>
       <c r="G48" s="4">
@@ -8175,15 +11359,19 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="28"/>
-      <c r="B49" s="35"/>
+      <c r="R48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="20"/>
+      <c r="B49" s="36"/>
       <c r="C49" s="4" t="s">
         <v>129</v>
       </c>
       <c r="D49" s="4">
-        <f t="shared" ref="D49:Q49" si="1">D22+D27+D32+D37+D41</f>
+        <f t="shared" ref="D49:R49" si="1">D22+D27+D32+D37+D41</f>
         <v>0</v>
       </c>
       <c r="E49" s="4">
@@ -8191,7 +11379,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="4">
-        <f t="shared" si="1"/>
+        <f>F22+F27+F32+F37+F41</f>
         <v>0</v>
       </c>
       <c r="G49" s="4">
@@ -8238,10 +11426,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="28"/>
-      <c r="B50" s="36"/>
+      <c r="R49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="20"/>
+      <c r="B50" s="37"/>
       <c r="C50" s="4" t="s">
         <v>130</v>
       </c>
@@ -8254,11 +11446,11 @@
         <v>0</v>
       </c>
       <c r="F50" s="4">
-        <f t="shared" ref="F50:Q50" si="2">F48*(1+F49*0.02)</f>
+        <f>F48*(1+F49*0.02)</f>
         <v>0</v>
       </c>
       <c r="G50" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="G50:R50" si="2">G48*(1+G49*0.02)</f>
         <v>0</v>
       </c>
       <c r="H50" s="4">
@@ -8301,100 +11493,104 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:17" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R50" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="37" t="s">
+    <row r="52" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="B52" s="37" t="s">
+      <c r="B52" s="34" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="29"/>
-      <c r="B53" s="29"/>
+    <row r="53" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="21"/>
+      <c r="B53" s="21"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="29"/>
-      <c r="B54" s="29"/>
+    <row r="54" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="21"/>
+      <c r="B54" s="21"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="29"/>
-      <c r="B55" s="30"/>
+    <row r="55" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="21"/>
+      <c r="B55" s="22"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="29"/>
-      <c r="B56" s="37" t="s">
+    <row r="56" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="21"/>
+      <c r="B56" s="34" t="s">
         <v>30</v>
       </c>
       <c r="C56" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="29"/>
-      <c r="B57" s="29"/>
+    <row r="57" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="21"/>
+      <c r="B57" s="21"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="29"/>
-      <c r="B58" s="30"/>
+    <row r="58" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="21"/>
+      <c r="B58" s="22"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="29"/>
+    <row r="59" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="21"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="29"/>
-      <c r="B60" s="37" t="s">
+    <row r="60" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="21"/>
+      <c r="B60" s="34" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="29"/>
-      <c r="B61" s="29"/>
+    <row r="61" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="21"/>
+      <c r="B61" s="21"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="30"/>
-      <c r="B62" s="30"/>
+    <row r="62" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="22"/>
+      <c r="B62" s="22"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="20" t="s">
+    <row r="63" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="29" t="s">
         <v>26</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -8403,36 +11599,50 @@
       <c r="C64" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="21"/>
+      <c r="F64" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="30"/>
       <c r="B65" s="4" t="s">
         <v>132</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="21"/>
+      <c r="F65" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="30"/>
       <c r="B66" s="4" t="s">
         <v>133</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="22"/>
+      <c r="F66" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="31"/>
       <c r="B67" s="5" t="s">
         <v>134</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>135</v>
       </c>
+      <c r="F67" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A64:A67"/>
     <mergeCell ref="A7:A18"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B7:B10"/>
@@ -8448,784 +11658,6 @@
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="B35:B38"/>
     <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A64:A67"/>
-  </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21A46B60-4F3A-4D99-AC29-6361CD3DE12A}">
-  <dimension ref="A1:Q67"/>
-  <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="3" width="16.625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-    </row>
-    <row r="2" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D5" s="1">
-        <v>6</v>
-      </c>
-      <c r="E5" s="1">
-        <v>6</v>
-      </c>
-      <c r="F5" s="1">
-        <v>6</v>
-      </c>
-      <c r="G5" s="1">
-        <v>6</v>
-      </c>
-      <c r="H5" s="1">
-        <v>6</v>
-      </c>
-      <c r="I5" s="1">
-        <v>7</v>
-      </c>
-      <c r="J5" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <v>2</v>
-      </c>
-      <c r="G6" s="1">
-        <v>2</v>
-      </c>
-      <c r="H6" s="1">
-        <v>3</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1</v>
-      </c>
-      <c r="J6" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="27"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="27"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="27"/>
-      <c r="B11" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="27"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="27"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="27"/>
-    </row>
-    <row r="15" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="27"/>
-      <c r="B15" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="27"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="3">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="27"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="3">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="27"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-    </row>
-    <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="B20" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="28"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="28"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="28"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="28"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-    </row>
-    <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="28"/>
-      <c r="B25" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="28"/>
-      <c r="B26" s="38"/>
-      <c r="C26" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="28"/>
-      <c r="B27" s="38"/>
-      <c r="C27" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="28"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="28"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-    </row>
-    <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="28"/>
-      <c r="B30" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="28"/>
-      <c r="B31" s="35"/>
-      <c r="C31" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="28"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="28"/>
-      <c r="B33" s="36"/>
-      <c r="C33" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="28"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="28"/>
-      <c r="B35" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="28"/>
-      <c r="B36" s="35"/>
-      <c r="C36" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="28"/>
-      <c r="B37" s="35"/>
-      <c r="C37" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="28"/>
-      <c r="B38" s="36"/>
-      <c r="C38" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="28"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-    </row>
-    <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="28"/>
-      <c r="B40" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="28"/>
-      <c r="B41" s="35"/>
-      <c r="C41" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="28"/>
-      <c r="B42" s="36"/>
-      <c r="C42" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="28"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-    </row>
-    <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="28"/>
-      <c r="B44" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="C44" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="28"/>
-      <c r="B45" s="35"/>
-      <c r="C45" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="28"/>
-      <c r="B46" s="36"/>
-      <c r="C46" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="28"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-    </row>
-    <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="28"/>
-      <c r="B48" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D48" s="4">
-        <f t="shared" ref="D48:Q48" si="0">D20+D25+D30+D35</f>
-        <v>0</v>
-      </c>
-      <c r="E48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="28"/>
-      <c r="B49" s="35"/>
-      <c r="C49" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D49" s="4">
-        <f t="shared" ref="D49:Q49" si="1">D22+D27+D32+D37+D41</f>
-        <v>0</v>
-      </c>
-      <c r="E49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="28"/>
-      <c r="B50" s="36"/>
-      <c r="C50" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D50" s="4">
-        <f>D48*(1+D49*0.02)</f>
-        <v>0</v>
-      </c>
-      <c r="E50" s="4">
-        <f>E48*(1+E49*0.02)</f>
-        <v>0</v>
-      </c>
-      <c r="F50" s="4">
-        <f t="shared" ref="F50:Q50" si="2">F48*(1+F49*0.02)</f>
-        <v>0</v>
-      </c>
-      <c r="G50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="2"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-    </row>
-    <row r="52" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="B52" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="29"/>
-      <c r="B53" s="29"/>
-      <c r="C53" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="29"/>
-      <c r="B54" s="29"/>
-      <c r="C54" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="29"/>
-      <c r="B55" s="30"/>
-      <c r="C55" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="29"/>
-      <c r="B56" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="C56" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="29"/>
-      <c r="B57" s="29"/>
-      <c r="C57" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="29"/>
-      <c r="B58" s="30"/>
-      <c r="C58" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="29"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-    </row>
-    <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="29"/>
-      <c r="B60" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="29"/>
-      <c r="B61" s="29"/>
-      <c r="C61" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="30"/>
-      <c r="B62" s="30"/>
-      <c r="C62" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="21"/>
-      <c r="B65" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="21"/>
-      <c r="B66" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="22"/>
-      <c r="B67" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A7:A18"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="A20:A50"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="A52:A62"/>
-    <mergeCell ref="B52:B55"/>
-    <mergeCell ref="B60:B62"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A64:A67"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dev_stuffs/3匠魂.xlsx
+++ b/dev_stuffs/3匠魂.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\Palmon\dev_stuffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B99E0B-9F2B-4B3D-B387-6F12821B5B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85930F6A-8A9A-460C-A30C-EA699DDE6192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10260" yWindow="3390" windowWidth="23940" windowHeight="15435" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="阶段1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="210">
   <si>
     <t>材料名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -628,6 +628,96 @@
   </si>
   <si>
     <t>'#forge:ingots/titanium'</t>
+  </si>
+  <si>
+    <t>'kubejs:otherside_mixture'</t>
+  </si>
+  <si>
+    <t>'deeperdarker:resonarium_plate'</t>
+  </si>
+  <si>
+    <t>'aetherworks:ingot_aether'</t>
+  </si>
+  <si>
+    <t>'aetherworks:gem_aether'</t>
+  </si>
+  <si>
+    <t>'nuclearcraft:niobium_titanium_ingot'</t>
+  </si>
+  <si>
+    <t>'kubejs:helium_3_crystal'</t>
+  </si>
+  <si>
+    <t>'kubejs:light_of_inlixaland'</t>
+  </si>
+  <si>
+    <t>'kubejs:alfheim_iridescent'</t>
+  </si>
+  <si>
+    <t>ex</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>'dustandash:titanium_tungsten_alloy'</t>
+  </si>
+  <si>
+    <t>'dustandash:titanium_aluminum_alloy'</t>
+  </si>
+  <si>
+    <t>'kubejs:epsilon_framework'</t>
+  </si>
+  <si>
+    <t>'kubejs:helium_3_crystal_infinity'</t>
+  </si>
+  <si>
+    <t>'aetherworks:aether_pearl'</t>
+  </si>
+  <si>
+    <t>'kubejs:basepoint_alloy'</t>
+  </si>
+  <si>
+    <t>超导线圈2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>'#forge:ingots/ostrum'</t>
+  </si>
+  <si>
+    <t>'#tinkers_advanced:plastic'</t>
+  </si>
+  <si>
+    <t>'tinkers_advanced:resonance_crystal'</t>
+  </si>
+  <si>
+    <t>'#botania:elementium_ingots'</t>
+  </si>
+  <si>
+    <t>'#forge:ingots/calorite'</t>
+  </si>
+  <si>
+    <t>'mythicbotany:alfsteel_ingot'</t>
+  </si>
+  <si>
+    <t>'kubejs:intelligent_draconium_ingot'</t>
+  </si>
+  <si>
+    <t>'kubejs:superconducting_coil_type_1'</t>
+  </si>
+  <si>
+    <t>'kubejs:unify_essence'</t>
+  </si>
+  <si>
+    <t>'kubejs:delta_framework'</t>
+  </si>
+  <si>
+    <t>'kubejs:marid_binded_gem'</t>
+  </si>
+  <si>
+    <t>'cataclysm:ignitium_ingot'</t>
+  </si>
+  <si>
+    <t>咒魂</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -826,7 +916,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -872,6 +962,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="4" applyBorder="1" applyAlignment="1">
@@ -925,9 +1018,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -937,13 +1027,10 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1404,10 +1491,10 @@
       </c>
     </row>
     <row r="9" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -1445,8 +1532,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="19"/>
-      <c r="B10" s="17"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -1482,8 +1569,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
-      <c r="B11" s="17"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -1519,8 +1606,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="19"/>
-      <c r="B12" s="17"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -1556,8 +1643,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19"/>
-      <c r="B13" s="17" t="s">
+      <c r="A13" s="20"/>
+      <c r="B13" s="18" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -1565,25 +1652,25 @@
       </c>
     </row>
     <row r="14" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="19"/>
-      <c r="B14" s="17"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="18"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19"/>
-      <c r="B15" s="17"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="18"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19"/>
+      <c r="A16" s="20"/>
     </row>
     <row r="17" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="19"/>
-      <c r="B17" s="23" t="s">
+      <c r="A17" s="20"/>
+      <c r="B17" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -1621,8 +1708,8 @@
       </c>
     </row>
     <row r="18" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19"/>
-      <c r="B18" s="24"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1658,8 +1745,8 @@
       </c>
     </row>
     <row r="19" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19"/>
-      <c r="B19" s="24"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="25"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -1695,8 +1782,8 @@
       </c>
     </row>
     <row r="20" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="19"/>
-      <c r="B20" s="25"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1738,10 +1825,10 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="32" t="s">
+      <c r="A22" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="21" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -1779,8 +1866,8 @@
       </c>
     </row>
     <row r="23" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="33"/>
-      <c r="B23" s="20"/>
+      <c r="A23" s="34"/>
+      <c r="B23" s="21"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
       </c>
@@ -1826,8 +1913,8 @@
       </c>
     </row>
     <row r="24" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="33"/>
-      <c r="B24" s="20"/>
+      <c r="A24" s="34"/>
+      <c r="B24" s="21"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
       </c>
@@ -1863,22 +1950,22 @@
       </c>
     </row>
     <row r="25" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="33"/>
-      <c r="B25" s="20"/>
+      <c r="A25" s="34"/>
+      <c r="B25" s="21"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="33"/>
+      <c r="A26" s="34"/>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="33"/>
-      <c r="B27" s="20" t="s">
+      <c r="A27" s="34"/>
+      <c r="B27" s="21" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="4" t="s">
@@ -1916,8 +2003,8 @@
       </c>
     </row>
     <row r="28" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="33"/>
-      <c r="B28" s="20"/>
+      <c r="A28" s="34"/>
+      <c r="B28" s="21"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
       </c>
@@ -1963,8 +2050,8 @@
       </c>
     </row>
     <row r="29" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="33"/>
-      <c r="B29" s="20"/>
+      <c r="A29" s="34"/>
+      <c r="B29" s="21"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
       </c>
@@ -2000,22 +2087,22 @@
       </c>
     </row>
     <row r="30" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="33"/>
-      <c r="B30" s="20"/>
+      <c r="A30" s="34"/>
+      <c r="B30" s="21"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="33"/>
+      <c r="A31" s="34"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="33"/>
-      <c r="B32" s="26" t="s">
+      <c r="A32" s="34"/>
+      <c r="B32" s="27" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -2053,8 +2140,8 @@
       </c>
     </row>
     <row r="33" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="33"/>
-      <c r="B33" s="27"/>
+      <c r="A33" s="34"/>
+      <c r="B33" s="28"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -2100,8 +2187,8 @@
       </c>
     </row>
     <row r="34" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="33"/>
-      <c r="B34" s="27"/>
+      <c r="A34" s="34"/>
+      <c r="B34" s="28"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -2137,22 +2224,22 @@
       </c>
     </row>
     <row r="35" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="33"/>
-      <c r="B35" s="28"/>
+      <c r="A35" s="34"/>
+      <c r="B35" s="29"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="33"/>
+      <c r="A36" s="34"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="33"/>
-      <c r="B37" s="26" t="s">
+      <c r="A37" s="34"/>
+      <c r="B37" s="27" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -2190,8 +2277,8 @@
       </c>
     </row>
     <row r="38" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="33"/>
-      <c r="B38" s="27"/>
+      <c r="A38" s="34"/>
+      <c r="B38" s="28"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -2237,8 +2324,8 @@
       </c>
     </row>
     <row r="39" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="33"/>
-      <c r="B39" s="27"/>
+      <c r="A39" s="34"/>
+      <c r="B39" s="28"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -2274,22 +2361,22 @@
       </c>
     </row>
     <row r="40" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="33"/>
-      <c r="B40" s="28"/>
+      <c r="A40" s="34"/>
+      <c r="B40" s="29"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="33"/>
+      <c r="A41" s="34"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="33"/>
-      <c r="B42" s="26" t="s">
+      <c r="A42" s="34"/>
+      <c r="B42" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -2337,8 +2424,8 @@
       </c>
     </row>
     <row r="43" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="33"/>
-      <c r="B43" s="27"/>
+      <c r="A43" s="34"/>
+      <c r="B43" s="28"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -2374,18 +2461,18 @@
       </c>
     </row>
     <row r="44" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="33"/>
-      <c r="B44" s="28"/>
+      <c r="A44" s="34"/>
+      <c r="B44" s="29"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="33"/>
+      <c r="A45" s="34"/>
     </row>
     <row r="46" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="33"/>
-      <c r="B46" s="26" t="s">
+      <c r="A46" s="34"/>
+      <c r="B46" s="27" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -2393,29 +2480,29 @@
       </c>
     </row>
     <row r="47" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="33"/>
-      <c r="B47" s="27"/>
+      <c r="A47" s="34"/>
+      <c r="B47" s="28"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="33"/>
-      <c r="B48" s="28"/>
+      <c r="A48" s="34"/>
+      <c r="B48" s="29"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="33"/>
+      <c r="A49" s="34"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
     </row>
     <row r="50" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="33"/>
-      <c r="B50" s="26" t="s">
+      <c r="A50" s="34"/>
+      <c r="B50" s="27" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -2463,8 +2550,8 @@
       </c>
     </row>
     <row r="51" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="33"/>
-      <c r="B51" s="27"/>
+      <c r="A51" s="34"/>
+      <c r="B51" s="28"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -2510,8 +2597,8 @@
       </c>
     </row>
     <row r="52" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="33"/>
-      <c r="B52" s="28"/>
+      <c r="A52" s="34"/>
+      <c r="B52" s="29"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -2563,10 +2650,10 @@
       <c r="E53" s="8"/>
     </row>
     <row r="54" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="18" t="s">
+      <c r="A54" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="18" t="s">
+      <c r="B54" s="19" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -2574,29 +2661,29 @@
       </c>
     </row>
     <row r="55" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="18"/>
-      <c r="B55" s="18"/>
+      <c r="A55" s="19"/>
+      <c r="B55" s="19"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="18"/>
-      <c r="B56" s="18"/>
+      <c r="A56" s="19"/>
+      <c r="B56" s="19"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="18"/>
-      <c r="B57" s="18"/>
+      <c r="A57" s="19"/>
+      <c r="B57" s="19"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="18"/>
-      <c r="B58" s="18" t="s">
+      <c r="A58" s="19"/>
+      <c r="B58" s="19" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -2604,29 +2691,29 @@
       </c>
     </row>
     <row r="59" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="18"/>
-      <c r="B59" s="21"/>
+      <c r="A59" s="19"/>
+      <c r="B59" s="22"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="18"/>
-      <c r="B60" s="22"/>
+      <c r="A60" s="19"/>
+      <c r="B60" s="23"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="18"/>
+      <c r="A61" s="19"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="18"/>
-      <c r="B62" s="18" t="s">
+      <c r="A62" s="19"/>
+      <c r="B62" s="19" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -2634,21 +2721,21 @@
       </c>
     </row>
     <row r="63" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="18"/>
-      <c r="B63" s="21"/>
+      <c r="A63" s="19"/>
+      <c r="B63" s="22"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="18"/>
-      <c r="B64" s="22"/>
+      <c r="A64" s="19"/>
+      <c r="B64" s="23"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="29" t="s">
+      <c r="A67" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B67" s="6" t="s">
@@ -2689,7 +2776,7 @@
       </c>
     </row>
     <row r="68" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="30"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="4" t="s">
         <v>132</v>
       </c>
@@ -2728,7 +2815,7 @@
       </c>
     </row>
     <row r="69" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="30"/>
+      <c r="A69" s="31"/>
       <c r="B69" s="4" t="s">
         <v>133</v>
       </c>
@@ -2767,7 +2854,7 @@
       </c>
     </row>
     <row r="70" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="31"/>
+      <c r="A70" s="32"/>
       <c r="B70" s="5" t="s">
         <v>134</v>
       </c>
@@ -3093,10 +3180,10 @@
       </c>
     </row>
     <row r="9" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -3146,8 +3233,8 @@
       </c>
     </row>
     <row r="10" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="19"/>
-      <c r="B10" s="17"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -3195,8 +3282,8 @@
       </c>
     </row>
     <row r="11" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
-      <c r="B11" s="17"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -3244,8 +3331,8 @@
       </c>
     </row>
     <row r="12" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="19"/>
-      <c r="B12" s="17"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -3293,8 +3380,8 @@
       </c>
     </row>
     <row r="13" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19"/>
-      <c r="B13" s="17" t="s">
+      <c r="A13" s="20"/>
+      <c r="B13" s="18" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -3302,25 +3389,25 @@
       </c>
     </row>
     <row r="14" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="19"/>
-      <c r="B14" s="17"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="18"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19"/>
-      <c r="B15" s="17"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="18"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19"/>
+      <c r="A16" s="20"/>
     </row>
     <row r="17" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="19"/>
-      <c r="B17" s="23" t="s">
+      <c r="A17" s="20"/>
+      <c r="B17" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -3370,8 +3457,8 @@
       </c>
     </row>
     <row r="18" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19"/>
-      <c r="B18" s="24"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -3419,8 +3506,8 @@
       </c>
     </row>
     <row r="19" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19"/>
-      <c r="B19" s="24"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="25"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -3468,8 +3555,8 @@
       </c>
     </row>
     <row r="20" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="19"/>
-      <c r="B20" s="25"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -3523,10 +3610,10 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="38" t="s">
+      <c r="B22" s="39" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -3576,8 +3663,8 @@
       </c>
     </row>
     <row r="23" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="20"/>
-      <c r="B23" s="38"/>
+      <c r="A23" s="21"/>
+      <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
       </c>
@@ -3639,8 +3726,8 @@
       </c>
     </row>
     <row r="24" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="20"/>
-      <c r="B24" s="38"/>
+      <c r="A24" s="21"/>
+      <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
       </c>
@@ -3688,8 +3775,8 @@
       </c>
     </row>
     <row r="25" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="20"/>
-      <c r="B25" s="38"/>
+      <c r="A25" s="21"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
       </c>
@@ -3719,15 +3806,15 @@
       </c>
     </row>
     <row r="26" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="20"/>
+      <c r="A26" s="21"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="20"/>
-      <c r="B27" s="38" t="s">
+      <c r="A27" s="21"/>
+      <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="4" t="s">
@@ -3777,8 +3864,8 @@
       </c>
     </row>
     <row r="28" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="20"/>
-      <c r="B28" s="38"/>
+      <c r="A28" s="21"/>
+      <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
       </c>
@@ -3840,8 +3927,8 @@
       </c>
     </row>
     <row r="29" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="20"/>
-      <c r="B29" s="38"/>
+      <c r="A29" s="21"/>
+      <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
       </c>
@@ -3889,8 +3976,8 @@
       </c>
     </row>
     <row r="30" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="20"/>
-      <c r="B30" s="38"/>
+      <c r="A30" s="21"/>
+      <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
       </c>
@@ -3920,14 +4007,14 @@
       </c>
     </row>
     <row r="31" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="20"/>
+      <c r="A31" s="21"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="20"/>
+      <c r="A32" s="21"/>
       <c r="B32" s="35" t="s">
         <v>17</v>
       </c>
@@ -3978,7 +4065,7 @@
       </c>
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="20"/>
+      <c r="A33" s="21"/>
       <c r="B33" s="36"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
@@ -4041,7 +4128,7 @@
       </c>
     </row>
     <row r="34" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="20"/>
+      <c r="A34" s="21"/>
       <c r="B34" s="36"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
@@ -4090,7 +4177,7 @@
       </c>
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="20"/>
+      <c r="A35" s="21"/>
       <c r="B35" s="37"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
@@ -4121,14 +4208,14 @@
       </c>
     </row>
     <row r="36" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="20"/>
+      <c r="A36" s="21"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="20"/>
+      <c r="A37" s="21"/>
       <c r="B37" s="35" t="s">
         <v>18</v>
       </c>
@@ -4179,7 +4266,7 @@
       </c>
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="20"/>
+      <c r="A38" s="21"/>
       <c r="B38" s="36"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
@@ -4242,7 +4329,7 @@
       </c>
     </row>
     <row r="39" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="20"/>
+      <c r="A39" s="21"/>
       <c r="B39" s="36"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
@@ -4291,7 +4378,7 @@
       </c>
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="20"/>
+      <c r="A40" s="21"/>
       <c r="B40" s="37"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
@@ -4322,14 +4409,14 @@
       </c>
     </row>
     <row r="41" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="20"/>
+      <c r="A41" s="21"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="20"/>
+      <c r="A42" s="21"/>
       <c r="B42" s="35" t="s">
         <v>19</v>
       </c>
@@ -4394,7 +4481,7 @@
       </c>
     </row>
     <row r="43" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="20"/>
+      <c r="A43" s="21"/>
       <c r="B43" s="36"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
@@ -4443,7 +4530,7 @@
       </c>
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="20"/>
+      <c r="A44" s="21"/>
       <c r="B44" s="37"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
@@ -4474,12 +4561,12 @@
       </c>
     </row>
     <row r="45" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="20"/>
+      <c r="A45" s="21"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="20"/>
+      <c r="A46" s="21"/>
       <c r="B46" s="35" t="s">
         <v>30</v>
       </c>
@@ -4488,28 +4575,28 @@
       </c>
     </row>
     <row r="47" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="20"/>
+      <c r="A47" s="21"/>
       <c r="B47" s="36"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="20"/>
+      <c r="A48" s="21"/>
       <c r="B48" s="37"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="20"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="20"/>
+      <c r="A50" s="21"/>
       <c r="B50" s="35" t="s">
         <v>28</v>
       </c>
@@ -4574,7 +4661,7 @@
       </c>
     </row>
     <row r="51" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="20"/>
+      <c r="A51" s="21"/>
       <c r="B51" s="36"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
@@ -4637,7 +4724,7 @@
       </c>
     </row>
     <row r="52" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="20"/>
+      <c r="A52" s="21"/>
       <c r="B52" s="37"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
@@ -4705,10 +4792,10 @@
       <c r="C53" s="8"/>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="34" t="s">
+      <c r="A54" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="34" t="s">
+      <c r="B54" s="38" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -4716,29 +4803,29 @@
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="21"/>
-      <c r="B55" s="21"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="21"/>
-      <c r="B56" s="21"/>
+      <c r="A56" s="22"/>
+      <c r="B56" s="22"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="21"/>
-      <c r="B57" s="22"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="23"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="21"/>
-      <c r="B58" s="34" t="s">
+      <c r="A58" s="22"/>
+      <c r="B58" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -4746,29 +4833,29 @@
       </c>
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="21"/>
-      <c r="B59" s="21"/>
+      <c r="A59" s="22"/>
+      <c r="B59" s="22"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="21"/>
-      <c r="B60" s="22"/>
+      <c r="A60" s="22"/>
+      <c r="B60" s="23"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="21"/>
+      <c r="A61" s="22"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="21"/>
-      <c r="B62" s="34" t="s">
+      <c r="A62" s="22"/>
+      <c r="B62" s="38" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -4776,22 +4863,22 @@
       </c>
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="21"/>
-      <c r="B63" s="21"/>
+      <c r="A63" s="22"/>
+      <c r="B63" s="22"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="22"/>
-      <c r="B64" s="22"/>
+      <c r="A64" s="23"/>
+      <c r="B64" s="23"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="29" t="s">
+      <c r="A66" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -4844,7 +4931,7 @@
       </c>
     </row>
     <row r="67" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="30"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -4889,7 +4976,7 @@
       </c>
     </row>
     <row r="68" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="30"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -4934,7 +5021,7 @@
       </c>
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="31"/>
+      <c r="A69" s="32"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -4944,8 +5031,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A54:A64"/>
-    <mergeCell ref="B54:B57"/>
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="B50:B52"/>
     <mergeCell ref="A66:A69"/>
@@ -4961,6 +5046,8 @@
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="B42:B44"/>
+    <mergeCell ref="A54:A64"/>
+    <mergeCell ref="B54:B57"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4970,7 +5057,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15BE3A64-1223-4346-9F98-17294D0E7928}">
-  <dimension ref="A1:AE67"/>
+  <dimension ref="A1:AE69"/>
   <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="16.625" style="2"/>
@@ -5083,837 +5170,947 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D5" s="1">
-        <v>3</v>
-      </c>
-      <c r="E5" s="1">
-        <v>3</v>
-      </c>
-      <c r="F5" s="1">
-        <v>3</v>
-      </c>
-      <c r="G5" s="1">
-        <v>3</v>
-      </c>
-      <c r="H5" s="1">
-        <v>3</v>
-      </c>
-      <c r="I5" s="1">
-        <v>3</v>
-      </c>
-      <c r="J5" s="1">
-        <v>3</v>
-      </c>
-      <c r="K5" s="1">
-        <v>3</v>
-      </c>
-      <c r="L5" s="1">
-        <v>3</v>
-      </c>
-      <c r="M5" s="1">
-        <v>3</v>
-      </c>
-      <c r="N5" s="1">
-        <v>3</v>
-      </c>
-      <c r="O5" s="1">
-        <v>3</v>
-      </c>
-      <c r="P5" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>3</v>
-      </c>
-      <c r="R5" s="1">
-        <v>3</v>
-      </c>
-      <c r="S5" s="1">
-        <v>3</v>
-      </c>
-      <c r="T5" s="1">
-        <v>3</v>
-      </c>
-      <c r="U5" s="1">
-        <v>3</v>
-      </c>
-      <c r="V5" s="1">
-        <v>3</v>
-      </c>
-      <c r="W5" s="1">
-        <v>3</v>
-      </c>
-      <c r="X5" s="1">
-        <v>3</v>
-      </c>
-      <c r="Y5" s="1">
-        <v>3</v>
-      </c>
-      <c r="Z5" s="1">
-        <v>3</v>
-      </c>
-      <c r="AA5" s="1">
-        <v>3</v>
-      </c>
-      <c r="AB5" s="1">
-        <v>3</v>
-      </c>
-      <c r="AC5" s="1">
-        <v>3</v>
-      </c>
-      <c r="AD5" s="1">
-        <v>3</v>
-      </c>
-      <c r="AE5" s="1">
-        <v>3</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:31" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AA6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AB6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AD6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AE6" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1">
+        <v>3</v>
+      </c>
+      <c r="G7" s="1">
+        <v>3</v>
+      </c>
+      <c r="H7" s="1">
+        <v>3</v>
+      </c>
+      <c r="I7" s="1">
+        <v>3</v>
+      </c>
+      <c r="J7" s="1">
+        <v>3</v>
+      </c>
+      <c r="K7" s="1">
+        <v>3</v>
+      </c>
+      <c r="L7" s="1">
+        <v>3</v>
+      </c>
+      <c r="M7" s="1">
+        <v>3</v>
+      </c>
+      <c r="N7" s="1">
+        <v>3</v>
+      </c>
+      <c r="O7" s="1">
+        <v>3</v>
+      </c>
+      <c r="P7" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>3</v>
+      </c>
+      <c r="R7" s="1">
+        <v>3</v>
+      </c>
+      <c r="S7" s="1">
+        <v>3</v>
+      </c>
+      <c r="T7" s="1">
+        <v>3</v>
+      </c>
+      <c r="U7" s="1">
+        <v>3</v>
+      </c>
+      <c r="V7" s="1">
+        <v>3</v>
+      </c>
+      <c r="W7" s="1">
+        <v>3</v>
+      </c>
+      <c r="X7" s="1">
+        <v>3</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>3</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1</v>
-      </c>
-      <c r="J6" s="1">
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1">
         <v>2</v>
       </c>
-      <c r="K6" s="1">
+      <c r="K8" s="1">
         <v>2</v>
       </c>
-      <c r="L6" s="1">
+      <c r="L8" s="1">
         <v>2</v>
       </c>
-      <c r="M6" s="1">
+      <c r="M8" s="1">
         <v>2</v>
       </c>
-      <c r="N6" s="1">
+      <c r="N8" s="1">
         <v>2</v>
       </c>
-      <c r="O6" s="1">
+      <c r="O8" s="1">
         <v>2</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P8" s="1">
         <v>2</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q8" s="1">
         <v>3</v>
       </c>
-      <c r="R6" s="1">
+      <c r="R8" s="1">
         <v>3</v>
       </c>
-      <c r="S6" s="1">
+      <c r="S8" s="1">
         <v>3</v>
       </c>
-      <c r="T6" s="1">
+      <c r="T8" s="1">
         <v>3</v>
       </c>
-      <c r="U6" s="1">
+      <c r="U8" s="1">
         <v>4</v>
       </c>
-      <c r="V6" s="1">
+      <c r="V8" s="1">
         <v>4</v>
       </c>
-      <c r="W6" s="1">
+      <c r="W8" s="1">
         <v>4</v>
       </c>
-      <c r="X6" s="1">
+      <c r="X8" s="1">
         <v>5</v>
       </c>
-      <c r="Y6" s="1">
+      <c r="Y8" s="1">
         <v>5</v>
       </c>
-      <c r="Z6" s="1">
+      <c r="Z8" s="1">
         <v>5</v>
       </c>
-      <c r="AA6" s="1">
+      <c r="AA8" s="1">
         <v>5</v>
       </c>
-      <c r="AB6" s="1">
+      <c r="AB8" s="1">
         <v>5</v>
       </c>
-      <c r="AC6" s="1">
+      <c r="AC8" s="1">
         <v>6</v>
       </c>
-      <c r="AD6" s="1">
+      <c r="AD8" s="1">
         <v>6</v>
       </c>
-      <c r="AE6" s="1">
+      <c r="AE8" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="19" t="s">
+    <row r="9" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B9" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D9" s="3">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="19"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="3" t="s">
+    <row r="10" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="20"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D10" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="19"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="3" t="s">
+    <row r="11" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="20"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D11" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="19"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="3" t="s">
+    <row r="12" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="20"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
-      <c r="B11" s="17" t="s">
+    <row r="13" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="20"/>
+      <c r="B13" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="19"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="3">
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="20"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="3">
+    <row r="15" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="20"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="19"/>
-    </row>
-    <row r="15" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19"/>
-      <c r="B15" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3" t="s">
+    <row r="16" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="20"/>
+    </row>
+    <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="20"/>
+      <c r="B17" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="3">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="19"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="D17" s="3">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19"/>
+      <c r="A18" s="20"/>
       <c r="B18" s="25"/>
       <c r="C18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="20"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="20"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-    </row>
-    <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20" t="s">
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+    </row>
+    <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="B20" s="38" t="s">
+      <c r="B22" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C22" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="20"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="4" t="s">
+    <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="21"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="20"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="4" t="s">
+    <row r="24" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="21"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="20"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="4" t="s">
+    <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="21"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="20"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-    </row>
-    <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="20"/>
-      <c r="B25" s="38" t="s">
+    <row r="26" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="21"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+    </row>
+    <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="21"/>
+      <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C27" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="20"/>
-      <c r="B26" s="38"/>
-      <c r="C26" s="4" t="s">
+    <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="21"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="20"/>
-      <c r="B27" s="38"/>
-      <c r="C27" s="4" t="s">
+    <row r="29" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="21"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="20"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="4" t="s">
+    <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="21"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="20"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-    </row>
-    <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="20"/>
-      <c r="B30" s="35" t="s">
+    <row r="31" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="21"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+    </row>
+    <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="21"/>
+      <c r="B32" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C32" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="20"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="4" t="s">
+    <row r="33" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="21"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="20"/>
-      <c r="B32" s="36"/>
-      <c r="C32" s="4" t="s">
+    <row r="34" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="21"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="20"/>
-      <c r="B33" s="37"/>
-      <c r="C33" s="4" t="s">
+    <row r="35" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="21"/>
+      <c r="B35" s="37"/>
+      <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="20"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="20"/>
-      <c r="B35" s="35" t="s">
+    <row r="36" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="21"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="21"/>
+      <c r="B37" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C37" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="20"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="4" t="s">
+    <row r="38" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="21"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="20"/>
-      <c r="B37" s="36"/>
-      <c r="C37" s="4" t="s">
+    <row r="39" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="21"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="20"/>
-      <c r="B38" s="37"/>
-      <c r="C38" s="4" t="s">
+    <row r="40" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="21"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="20"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-    </row>
-    <row r="40" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="20"/>
-      <c r="B40" s="35" t="s">
+    <row r="41" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="21"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+    </row>
+    <row r="42" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="21"/>
+      <c r="B42" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C42" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="20"/>
-      <c r="B41" s="36"/>
-      <c r="C41" s="4" t="s">
+    <row r="43" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="21"/>
+      <c r="B43" s="36"/>
+      <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="20"/>
-      <c r="B42" s="37"/>
-      <c r="C42" s="4" t="s">
+    <row r="44" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="21"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="20"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-    </row>
-    <row r="44" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="20"/>
-      <c r="B44" s="35" t="s">
+    <row r="45" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="21"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+    </row>
+    <row r="46" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="21"/>
+      <c r="B46" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="C44" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="20"/>
-      <c r="B45" s="36"/>
-      <c r="C45" s="4">
+      <c r="C46" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="21"/>
+      <c r="B47" s="36"/>
+      <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="20"/>
-      <c r="B46" s="37"/>
-      <c r="C46" s="4">
+    <row r="48" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="21"/>
+      <c r="B48" s="37"/>
+      <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="20"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-    </row>
-    <row r="48" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="20"/>
-      <c r="B48" s="35" t="s">
+    <row r="49" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="21"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+    </row>
+    <row r="50" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="21"/>
+      <c r="B50" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C50" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D48" s="4">
-        <f t="shared" ref="D48:P48" si="0">D20+D25+D30+D35</f>
-        <v>0</v>
-      </c>
-      <c r="E48" s="4">
+      <c r="D50" s="4">
+        <f t="shared" ref="D50:P50" si="0">D22+D27+D32+D37</f>
+        <v>0</v>
+      </c>
+      <c r="E50" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F48" s="4">
+      <c r="F50" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G48" s="4">
+      <c r="G50" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H48" s="4">
+      <c r="H50" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I48" s="4">
+      <c r="I50" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J48" s="4">
+      <c r="J50" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K48" s="4">
+      <c r="K50" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L48" s="4">
+      <c r="L50" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M48" s="4">
+      <c r="M50" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N48" s="4">
+      <c r="N50" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O48" s="4">
+      <c r="O50" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P48" s="4">
+      <c r="P50" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="20"/>
-      <c r="B49" s="36"/>
-      <c r="C49" s="4" t="s">
+    <row r="51" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="21"/>
+      <c r="B51" s="36"/>
+      <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D49" s="4">
-        <f t="shared" ref="D49:P49" si="1">D22+D27+D32+D37+D41</f>
-        <v>0</v>
-      </c>
-      <c r="E49" s="4">
+      <c r="D51" s="4">
+        <f t="shared" ref="D51:P51" si="1">D24+D29+D34+D39+D43</f>
+        <v>0</v>
+      </c>
+      <c r="E51" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F49" s="4">
+      <c r="F51" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G49" s="4">
+      <c r="G51" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H49" s="4">
+      <c r="H51" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I49" s="4">
+      <c r="I51" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J49" s="4">
+      <c r="J51" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K49" s="4">
+      <c r="K51" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L49" s="4">
+      <c r="L51" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M49" s="4">
+      <c r="M51" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N49" s="4">
+      <c r="N51" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O49" s="4">
+      <c r="O51" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P49" s="4">
+      <c r="P51" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="20"/>
-      <c r="B50" s="37"/>
-      <c r="C50" s="4" t="s">
+    <row r="52" spans="1:16" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="21"/>
+      <c r="B52" s="37"/>
+      <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="D50" s="4">
-        <f>D48*(1+D49*0.02)</f>
-        <v>0</v>
-      </c>
-      <c r="E50" s="4">
-        <f>E48*(1+E49*0.02)</f>
-        <v>0</v>
-      </c>
-      <c r="F50" s="4">
-        <f t="shared" ref="F50:P50" si="2">F48*(1+F49*0.02)</f>
-        <v>0</v>
-      </c>
-      <c r="G50" s="4">
+      <c r="D52" s="4">
+        <f>D50*(1+D51*0.02)</f>
+        <v>0</v>
+      </c>
+      <c r="E52" s="4">
+        <f>E50*(1+E51*0.02)</f>
+        <v>0</v>
+      </c>
+      <c r="F52" s="4">
+        <f t="shared" ref="F52:P52" si="2">F50*(1+F51*0.02)</f>
+        <v>0</v>
+      </c>
+      <c r="G52" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H50" s="4">
+      <c r="H52" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I50" s="4">
+      <c r="I52" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J50" s="4">
+      <c r="J52" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K50" s="4">
+      <c r="K52" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L50" s="4">
+      <c r="L52" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M50" s="4">
+      <c r="M52" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N50" s="4">
+      <c r="N52" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O50" s="4">
+      <c r="O52" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P50" s="4">
+      <c r="P52" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:16" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="2"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-    </row>
-    <row r="52" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="34" t="s">
+    <row r="53" spans="1:16" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="2"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+    </row>
+    <row r="54" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="B52" s="34" t="s">
+      <c r="B54" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C54" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="21"/>
-      <c r="B53" s="21"/>
-      <c r="C53" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="21"/>
-      <c r="B54" s="21"/>
-      <c r="C54" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="55" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="21"/>
+      <c r="A55" s="22"/>
       <c r="B55" s="22"/>
       <c r="C55" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="22"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="22"/>
+      <c r="B57" s="23"/>
+      <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="21"/>
-      <c r="B56" s="34" t="s">
+    <row r="58" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="22"/>
+      <c r="B58" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C56" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="21"/>
-      <c r="B57" s="21"/>
-      <c r="C57" s="5">
+      <c r="C58" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="22"/>
+      <c r="B59" s="22"/>
+      <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="21"/>
-      <c r="B58" s="22"/>
-      <c r="C58" s="5">
+    <row r="60" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="22"/>
+      <c r="B60" s="23"/>
+      <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="21"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-    </row>
-    <row r="60" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="21"/>
-      <c r="B60" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="21"/>
-      <c r="B61" s="21"/>
-      <c r="C61" s="5" t="s">
-        <v>23</v>
-      </c>
+    <row r="61" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="22"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="22"/>
-      <c r="B62" s="22"/>
+      <c r="B62" s="38" t="s">
+        <v>25</v>
+      </c>
       <c r="C62" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="22"/>
+      <c r="B63" s="22"/>
+      <c r="C63" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="23"/>
+      <c r="B64" s="23"/>
+      <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="29" t="s">
+    <row r="65" spans="1:3" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" spans="1:3" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B66" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C66" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="30"/>
-      <c r="B65" s="4" t="s">
+    <row r="67" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="31"/>
+      <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C67" s="4" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="30"/>
-      <c r="B66" s="4" t="s">
+    <row r="68" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="31"/>
+      <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C68" s="4" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="31"/>
-      <c r="B67" s="5" t="s">
+    <row r="69" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="32"/>
+      <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="C69" s="5" t="s">
         <v>135</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="A7:A18"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="A20:A50"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="A52:A62"/>
-    <mergeCell ref="B52:B55"/>
-    <mergeCell ref="B60:B62"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="A9:A20"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="A22:A52"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="A54:A64"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A66:A69"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6068,10 +6265,10 @@
       <c r="AF6" s="1"/>
     </row>
     <row r="7" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -6082,8 +6279,8 @@
       </c>
     </row>
     <row r="8" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="19"/>
-      <c r="B8" s="17"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="18"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
@@ -6092,8 +6289,8 @@
       </c>
     </row>
     <row r="9" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="19"/>
-      <c r="B9" s="17"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="18"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
@@ -6102,8 +6299,8 @@
       </c>
     </row>
     <row r="10" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="19"/>
-      <c r="B10" s="17"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -6112,8 +6309,8 @@
       </c>
     </row>
     <row r="11" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
-      <c r="B11" s="17" t="s">
+      <c r="A11" s="20"/>
+      <c r="B11" s="18" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
@@ -6121,25 +6318,25 @@
       </c>
     </row>
     <row r="12" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="19"/>
-      <c r="B12" s="17"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19"/>
-      <c r="B13" s="17"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="18"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:32" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="19"/>
+      <c r="A14" s="20"/>
     </row>
     <row r="15" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19"/>
-      <c r="B15" s="23" t="s">
+      <c r="A15" s="20"/>
+      <c r="B15" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -6150,8 +6347,8 @@
       </c>
     </row>
     <row r="16" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19"/>
-      <c r="B16" s="24"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="25"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
@@ -6160,8 +6357,8 @@
       </c>
     </row>
     <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="19"/>
-      <c r="B17" s="24"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="25"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
@@ -6170,8 +6367,8 @@
       </c>
     </row>
     <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19"/>
-      <c r="B18" s="25"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="26"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
@@ -6186,10 +6383,10 @@
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="39" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -6197,36 +6394,36 @@
       </c>
     </row>
     <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="20"/>
-      <c r="B21" s="38"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="39"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="20"/>
-      <c r="B22" s="38"/>
+      <c r="A22" s="21"/>
+      <c r="B22" s="39"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="20"/>
-      <c r="B23" s="38"/>
+      <c r="A23" s="21"/>
+      <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="20"/>
+      <c r="A24" s="21"/>
       <c r="B24" s="12"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="20"/>
-      <c r="B25" s="38" t="s">
+      <c r="A25" s="21"/>
+      <c r="B25" s="39" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="4" t="s">
@@ -6234,35 +6431,35 @@
       </c>
     </row>
     <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="20"/>
-      <c r="B26" s="38"/>
+      <c r="A26" s="21"/>
+      <c r="B26" s="39"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="20"/>
-      <c r="B27" s="38"/>
+      <c r="A27" s="21"/>
+      <c r="B27" s="39"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="20"/>
-      <c r="B28" s="38"/>
+      <c r="A28" s="21"/>
+      <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="20"/>
+      <c r="A29" s="21"/>
       <c r="B29" s="13"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="20"/>
+      <c r="A30" s="21"/>
       <c r="B30" s="35" t="s">
         <v>17</v>
       </c>
@@ -6271,35 +6468,35 @@
       </c>
     </row>
     <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="20"/>
+      <c r="A31" s="21"/>
       <c r="B31" s="36"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="20"/>
+      <c r="A32" s="21"/>
       <c r="B32" s="36"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="20"/>
+      <c r="A33" s="21"/>
       <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="20"/>
+      <c r="A34" s="21"/>
       <c r="B34" s="14"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="20"/>
+      <c r="A35" s="21"/>
       <c r="B35" s="35" t="s">
         <v>18</v>
       </c>
@@ -6308,35 +6505,35 @@
       </c>
     </row>
     <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="20"/>
+      <c r="A36" s="21"/>
       <c r="B36" s="36"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="20"/>
+      <c r="A37" s="21"/>
       <c r="B37" s="36"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="20"/>
+      <c r="A38" s="21"/>
       <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="20"/>
+      <c r="A39" s="21"/>
       <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="20"/>
+      <c r="A40" s="21"/>
       <c r="B40" s="35" t="s">
         <v>19</v>
       </c>
@@ -6345,26 +6542,26 @@
       </c>
     </row>
     <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="20"/>
+      <c r="A41" s="21"/>
       <c r="B41" s="36"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="20"/>
+      <c r="A42" s="21"/>
       <c r="B42" s="37"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="20"/>
+      <c r="A43" s="21"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="20"/>
+      <c r="A44" s="21"/>
       <c r="B44" s="35" t="s">
         <v>30</v>
       </c>
@@ -6373,28 +6570,28 @@
       </c>
     </row>
     <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="20"/>
+      <c r="A45" s="21"/>
       <c r="B45" s="36"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="20"/>
+      <c r="A46" s="21"/>
       <c r="B46" s="37"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="20"/>
+      <c r="A47" s="21"/>
       <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="20"/>
+      <c r="A48" s="21"/>
       <c r="B48" s="35" t="s">
         <v>28</v>
       </c>
@@ -6459,7 +6656,7 @@
       </c>
     </row>
     <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="20"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="36"/>
       <c r="C49" s="4" t="s">
         <v>129</v>
@@ -6522,7 +6719,7 @@
       </c>
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="20"/>
+      <c r="A50" s="21"/>
       <c r="B50" s="37"/>
       <c r="C50" s="4" t="s">
         <v>130</v>
@@ -6590,10 +6787,10 @@
       <c r="C51" s="8"/>
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="34" t="s">
+      <c r="A52" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="B52" s="34" t="s">
+      <c r="B52" s="38" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="5" t="s">
@@ -6601,29 +6798,29 @@
       </c>
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="21"/>
-      <c r="B53" s="21"/>
+      <c r="A53" s="22"/>
+      <c r="B53" s="22"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="21"/>
-      <c r="B54" s="21"/>
+      <c r="A54" s="22"/>
+      <c r="B54" s="22"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="21"/>
-      <c r="B55" s="22"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="23"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="21"/>
-      <c r="B56" s="34" t="s">
+      <c r="A56" s="22"/>
+      <c r="B56" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C56" s="5">
@@ -6631,29 +6828,29 @@
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="21"/>
-      <c r="B57" s="21"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="22"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="21"/>
-      <c r="B58" s="22"/>
+      <c r="A58" s="22"/>
+      <c r="B58" s="23"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="21"/>
+      <c r="A59" s="22"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="21"/>
-      <c r="B60" s="34" t="s">
+      <c r="A60" s="22"/>
+      <c r="B60" s="38" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
@@ -6661,22 +6858,22 @@
       </c>
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="21"/>
-      <c r="B61" s="21"/>
+      <c r="A61" s="22"/>
+      <c r="B61" s="22"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="22"/>
-      <c r="B62" s="22"/>
+      <c r="A62" s="23"/>
+      <c r="B62" s="23"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="29" t="s">
+      <c r="A64" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -6687,7 +6884,7 @@
       </c>
     </row>
     <row r="65" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="30"/>
+      <c r="A65" s="31"/>
       <c r="B65" s="4" t="s">
         <v>132</v>
       </c>
@@ -6696,7 +6893,7 @@
       </c>
     </row>
     <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="30"/>
+      <c r="A66" s="31"/>
       <c r="B66" s="4" t="s">
         <v>133</v>
       </c>
@@ -6705,7 +6902,7 @@
       </c>
     </row>
     <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="31"/>
+      <c r="A67" s="32"/>
       <c r="B67" s="5" t="s">
         <v>134</v>
       </c>
@@ -6741,7 +6938,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C5AF949-03E5-4E6E-B7CB-0D2F8A5AE350}">
-  <dimension ref="A1:R67"/>
+  <dimension ref="A1:O69"/>
   <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="16.625" style="2"/>
@@ -6805,777 +7002,1989 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
+    <row r="5" spans="1:15" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D7" s="1">
         <v>4</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E7" s="1">
         <v>4</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F7" s="1">
         <v>3</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G7" s="1">
         <v>4</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H7" s="1">
         <v>4</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I7" s="1">
         <v>4</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J7" s="1">
         <v>4</v>
       </c>
-      <c r="K5" s="1">
+      <c r="K7" s="1">
         <v>4</v>
       </c>
-      <c r="L5" s="1">
+      <c r="L7" s="1">
         <v>4</v>
       </c>
-      <c r="M5" s="1">
+      <c r="M7" s="1">
         <v>4</v>
       </c>
-      <c r="N5" s="1">
+      <c r="N7" s="1">
         <v>4</v>
       </c>
-      <c r="O5" s="1">
+      <c r="O7" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1" t="s">
+    <row r="8" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1">
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
         <v>2</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H8" s="1">
         <v>2</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I8" s="1">
         <v>3</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J8" s="1">
         <v>3</v>
       </c>
-      <c r="K6" s="1">
+      <c r="K8" s="1">
         <v>4</v>
       </c>
-      <c r="L6" s="1">
+      <c r="L8" s="1">
         <v>4</v>
       </c>
-      <c r="M6" s="1">
+      <c r="M8" s="1">
         <v>5</v>
       </c>
-      <c r="N6" s="1">
+      <c r="N8" s="1">
         <v>5</v>
       </c>
-      <c r="O6" s="1">
+      <c r="O8" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="19" t="s">
+    <row r="9" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B9" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="19"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="3" t="s">
+      <c r="D9" s="3">
+        <v>72</v>
+      </c>
+      <c r="E9" s="3">
+        <v>54</v>
+      </c>
+      <c r="F9" s="3">
+        <v>84</v>
+      </c>
+      <c r="G9" s="3">
+        <v>96</v>
+      </c>
+      <c r="H9" s="3">
+        <v>102</v>
+      </c>
+      <c r="I9" s="3">
+        <v>120</v>
+      </c>
+      <c r="J9" s="3">
+        <v>125</v>
+      </c>
+      <c r="K9" s="3">
+        <v>130</v>
+      </c>
+      <c r="L9" s="3">
+        <v>130</v>
+      </c>
+      <c r="M9" s="3">
+        <v>145</v>
+      </c>
+      <c r="N9" s="3">
+        <v>140</v>
+      </c>
+      <c r="O9" s="3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="20"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="19"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="3" t="s">
+      <c r="D10" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>550</v>
+      </c>
+      <c r="F10" s="3">
+        <v>850</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1150</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1150</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K10" s="3">
+        <v>1150</v>
+      </c>
+      <c r="L10" s="3">
+        <v>900</v>
+      </c>
+      <c r="M10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N10" s="3">
+        <v>900</v>
+      </c>
+      <c r="O10" s="3">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="20"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="19"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="3" t="s">
+      <c r="D11" s="3">
+        <v>12</v>
+      </c>
+      <c r="E11" s="3">
+        <v>10</v>
+      </c>
+      <c r="F11" s="3">
+        <v>12</v>
+      </c>
+      <c r="G11" s="3">
+        <v>12</v>
+      </c>
+      <c r="H11" s="3">
+        <v>13</v>
+      </c>
+      <c r="I11" s="3">
+        <v>13</v>
+      </c>
+      <c r="J11" s="3">
+        <v>12</v>
+      </c>
+      <c r="K11" s="3">
+        <v>13</v>
+      </c>
+      <c r="L11" s="3">
+        <v>15</v>
+      </c>
+      <c r="M11" s="3">
+        <v>14</v>
+      </c>
+      <c r="N11" s="3">
+        <v>15</v>
+      </c>
+      <c r="O11" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="20"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
-      <c r="B11" s="17" t="s">
+      <c r="F12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="20"/>
+      <c r="B13" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="19"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="3">
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="20"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="3">
+    <row r="15" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="20"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="19"/>
-    </row>
-    <row r="15" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19"/>
-      <c r="B15" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3" t="s">
+    <row r="16" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="20"/>
+    </row>
+    <row r="17" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="20"/>
+      <c r="B17" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="3">
+      <c r="D17" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="H17" s="3">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="19"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="3">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19"/>
+      <c r="I17" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3">
+        <v>-0.2</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="20"/>
       <c r="B18" s="25"/>
       <c r="C18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="N18" s="3">
+        <v>0.65</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="20"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="K19" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="L19" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="M19" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="N19" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="O19" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="20"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="39"/>
-    </row>
-    <row r="20" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20" t="s">
+      <c r="D20" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-0.2</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+    </row>
+    <row r="22" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="B20" s="38" t="s">
+      <c r="B22" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C22" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="20"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="4" t="s">
+      <c r="D22" s="4">
+        <v>9</v>
+      </c>
+      <c r="E22" s="4">
+        <v>9</v>
+      </c>
+      <c r="F22" s="4">
+        <v>9</v>
+      </c>
+      <c r="G22" s="4">
+        <v>9</v>
+      </c>
+      <c r="H22" s="4">
+        <v>9</v>
+      </c>
+      <c r="I22" s="4">
+        <v>10</v>
+      </c>
+      <c r="J22" s="4">
+        <v>10</v>
+      </c>
+      <c r="K22" s="4">
+        <v>11</v>
+      </c>
+      <c r="L22" s="4">
+        <v>11</v>
+      </c>
+      <c r="M22" s="4">
+        <v>12</v>
+      </c>
+      <c r="N22" s="4">
+        <v>12</v>
+      </c>
+      <c r="O22" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="21"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="20"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="4" t="s">
+      <c r="D23" s="4">
+        <f t="shared" ref="D23:O23" si="0">0.7*D28</f>
+        <v>770</v>
+      </c>
+      <c r="E23" s="4">
+        <f t="shared" si="0"/>
+        <v>385</v>
+      </c>
+      <c r="F23" s="4">
+        <f t="shared" si="0"/>
+        <v>595</v>
+      </c>
+      <c r="G23" s="4">
+        <f t="shared" si="0"/>
+        <v>770</v>
+      </c>
+      <c r="H23" s="4">
+        <f t="shared" si="0"/>
+        <v>805</v>
+      </c>
+      <c r="I23" s="4">
+        <f t="shared" si="0"/>
+        <v>805</v>
+      </c>
+      <c r="J23" s="4">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="K23" s="4">
+        <f t="shared" si="0"/>
+        <v>805</v>
+      </c>
+      <c r="L23" s="4">
+        <f t="shared" si="0"/>
+        <v>630</v>
+      </c>
+      <c r="M23" s="4">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="N23" s="4">
+        <f t="shared" si="0"/>
+        <v>630</v>
+      </c>
+      <c r="O23" s="4">
+        <f t="shared" si="0"/>
+        <v>909.99999999999989</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="21"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="20"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="4" t="s">
+      <c r="D24" s="4">
+        <v>3</v>
+      </c>
+      <c r="E24" s="4">
+        <v>3</v>
+      </c>
+      <c r="F24" s="4">
+        <v>3</v>
+      </c>
+      <c r="G24" s="4">
+        <v>4</v>
+      </c>
+      <c r="H24" s="4">
+        <v>4</v>
+      </c>
+      <c r="I24" s="4">
+        <v>4</v>
+      </c>
+      <c r="J24" s="4">
+        <v>4</v>
+      </c>
+      <c r="K24" s="4">
+        <v>5</v>
+      </c>
+      <c r="L24" s="4">
+        <v>5</v>
+      </c>
+      <c r="M24" s="4">
+        <v>7</v>
+      </c>
+      <c r="N24" s="4">
+        <v>7</v>
+      </c>
+      <c r="O24" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="21"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="20"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="39"/>
-    </row>
-    <row r="25" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="20"/>
-      <c r="B25" s="38" t="s">
+      <c r="D25" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="E25" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="F25" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="G25" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="H25" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="I25" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="J25" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="K25" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="L25" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="M25" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="N25" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="O25" s="4">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="21"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+    </row>
+    <row r="27" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="21"/>
+      <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C27" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="20"/>
-      <c r="B26" s="38"/>
-      <c r="C26" s="4" t="s">
+      <c r="D27" s="4">
+        <v>14</v>
+      </c>
+      <c r="E27" s="4">
+        <v>14</v>
+      </c>
+      <c r="F27" s="4">
+        <v>14</v>
+      </c>
+      <c r="G27" s="4">
+        <v>14</v>
+      </c>
+      <c r="H27" s="4">
+        <v>14</v>
+      </c>
+      <c r="I27" s="4">
+        <v>15</v>
+      </c>
+      <c r="J27" s="4">
+        <v>16</v>
+      </c>
+      <c r="K27" s="4">
+        <v>18</v>
+      </c>
+      <c r="L27" s="4">
+        <v>18</v>
+      </c>
+      <c r="M27" s="4">
+        <v>19</v>
+      </c>
+      <c r="N27" s="4">
+        <v>19</v>
+      </c>
+      <c r="O27" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="21"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="20"/>
-      <c r="B27" s="38"/>
-      <c r="C27" s="4" t="s">
+      <c r="D28" s="4">
+        <f t="shared" ref="D28:O28" si="1">D10</f>
+        <v>1100</v>
+      </c>
+      <c r="E28" s="4">
+        <f t="shared" si="1"/>
+        <v>550</v>
+      </c>
+      <c r="F28" s="4">
+        <f t="shared" si="1"/>
+        <v>850</v>
+      </c>
+      <c r="G28" s="4">
+        <f t="shared" si="1"/>
+        <v>1100</v>
+      </c>
+      <c r="H28" s="4">
+        <f t="shared" si="1"/>
+        <v>1150</v>
+      </c>
+      <c r="I28" s="4">
+        <f t="shared" si="1"/>
+        <v>1150</v>
+      </c>
+      <c r="J28" s="4">
+        <f t="shared" si="1"/>
+        <v>1200</v>
+      </c>
+      <c r="K28" s="4">
+        <f t="shared" si="1"/>
+        <v>1150</v>
+      </c>
+      <c r="L28" s="4">
+        <f t="shared" si="1"/>
+        <v>900</v>
+      </c>
+      <c r="M28" s="4">
+        <f t="shared" si="1"/>
+        <v>1200</v>
+      </c>
+      <c r="N28" s="4">
+        <f t="shared" si="1"/>
+        <v>900</v>
+      </c>
+      <c r="O28" s="4">
+        <f t="shared" si="1"/>
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="21"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="20"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="4" t="s">
+      <c r="D29" s="4">
+        <v>3</v>
+      </c>
+      <c r="E29" s="4">
+        <v>3</v>
+      </c>
+      <c r="F29" s="4">
+        <v>3</v>
+      </c>
+      <c r="G29" s="4">
+        <v>4</v>
+      </c>
+      <c r="H29" s="4">
+        <v>4</v>
+      </c>
+      <c r="I29" s="4">
+        <v>4</v>
+      </c>
+      <c r="J29" s="4">
+        <v>4</v>
+      </c>
+      <c r="K29" s="4">
+        <v>5</v>
+      </c>
+      <c r="L29" s="4">
+        <v>5</v>
+      </c>
+      <c r="M29" s="4">
+        <v>6</v>
+      </c>
+      <c r="N29" s="4">
+        <v>6</v>
+      </c>
+      <c r="O29" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="21"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="20"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="39"/>
-    </row>
-    <row r="30" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="20"/>
-      <c r="B30" s="35" t="s">
+      <c r="D30" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="E30" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="F30" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="G30" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="H30" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="I30" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="J30" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="K30" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="L30" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="M30" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="N30" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="O30" s="4">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="21"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+    </row>
+    <row r="32" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="21"/>
+      <c r="B32" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C32" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="20"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="4" t="s">
+      <c r="D32" s="4">
+        <v>12</v>
+      </c>
+      <c r="E32" s="4">
+        <v>12</v>
+      </c>
+      <c r="F32" s="4">
+        <v>12</v>
+      </c>
+      <c r="G32" s="4">
+        <v>12</v>
+      </c>
+      <c r="H32" s="4">
+        <v>12</v>
+      </c>
+      <c r="I32" s="4">
+        <v>13</v>
+      </c>
+      <c r="J32" s="4">
+        <v>14</v>
+      </c>
+      <c r="K32" s="4">
+        <v>16</v>
+      </c>
+      <c r="L32" s="4">
+        <v>16</v>
+      </c>
+      <c r="M32" s="4">
+        <v>17</v>
+      </c>
+      <c r="N32" s="4">
+        <v>17</v>
+      </c>
+      <c r="O32" s="4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="21"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="20"/>
-      <c r="B32" s="36"/>
-      <c r="C32" s="4" t="s">
+      <c r="D33" s="4">
+        <f t="shared" ref="D33:O33" si="2">0.9*D28</f>
+        <v>990</v>
+      </c>
+      <c r="E33" s="4">
+        <f t="shared" si="2"/>
+        <v>495</v>
+      </c>
+      <c r="F33" s="4">
+        <f t="shared" si="2"/>
+        <v>765</v>
+      </c>
+      <c r="G33" s="4">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="H33" s="4">
+        <f t="shared" si="2"/>
+        <v>1035</v>
+      </c>
+      <c r="I33" s="4">
+        <f t="shared" si="2"/>
+        <v>1035</v>
+      </c>
+      <c r="J33" s="4">
+        <f t="shared" si="2"/>
+        <v>1080</v>
+      </c>
+      <c r="K33" s="4">
+        <f t="shared" si="2"/>
+        <v>1035</v>
+      </c>
+      <c r="L33" s="4">
+        <f t="shared" si="2"/>
+        <v>810</v>
+      </c>
+      <c r="M33" s="4">
+        <f t="shared" si="2"/>
+        <v>1080</v>
+      </c>
+      <c r="N33" s="4">
+        <f t="shared" si="2"/>
+        <v>810</v>
+      </c>
+      <c r="O33" s="4">
+        <f t="shared" si="2"/>
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="21"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="20"/>
-      <c r="B33" s="37"/>
-      <c r="C33" s="4" t="s">
+      <c r="D34" s="4">
+        <v>3</v>
+      </c>
+      <c r="E34" s="4">
+        <v>3</v>
+      </c>
+      <c r="F34" s="4">
+        <v>3</v>
+      </c>
+      <c r="G34" s="4">
+        <v>4</v>
+      </c>
+      <c r="H34" s="4">
+        <v>4</v>
+      </c>
+      <c r="I34" s="4">
+        <v>4</v>
+      </c>
+      <c r="J34" s="4">
+        <v>4</v>
+      </c>
+      <c r="K34" s="4">
+        <v>5</v>
+      </c>
+      <c r="L34" s="4">
+        <v>5</v>
+      </c>
+      <c r="M34" s="4">
+        <v>6</v>
+      </c>
+      <c r="N34" s="4">
+        <v>6</v>
+      </c>
+      <c r="O34" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="21"/>
+      <c r="B35" s="37"/>
+      <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="20"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="39"/>
-    </row>
-    <row r="35" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="20"/>
-      <c r="B35" s="35" t="s">
+      <c r="D35" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="E35" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="F35" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="G35" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="H35" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="I35" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="J35" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="K35" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="L35" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="M35" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="N35" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="O35" s="4">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="21"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="21"/>
+      <c r="B37" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C37" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="20"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="4" t="s">
+      <c r="D37" s="4">
         <v>7</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="20"/>
-      <c r="B37" s="36"/>
-      <c r="C37" s="4" t="s">
+      <c r="E37" s="4">
+        <v>7</v>
+      </c>
+      <c r="F37" s="4">
+        <v>7</v>
+      </c>
+      <c r="G37" s="4">
+        <v>7</v>
+      </c>
+      <c r="H37" s="4">
+        <v>7</v>
+      </c>
+      <c r="I37" s="4">
+        <v>8</v>
+      </c>
+      <c r="J37" s="4">
+        <v>8</v>
+      </c>
+      <c r="K37" s="4">
+        <v>9</v>
+      </c>
+      <c r="L37" s="4">
+        <v>9</v>
+      </c>
+      <c r="M37" s="4">
+        <v>10</v>
+      </c>
+      <c r="N37" s="4">
+        <v>10</v>
+      </c>
+      <c r="O37" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="21"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="4">
+        <f t="shared" ref="D38:O38" si="3">0.6*D28</f>
+        <v>660</v>
+      </c>
+      <c r="E38" s="4">
+        <f t="shared" si="3"/>
+        <v>330</v>
+      </c>
+      <c r="F38" s="4">
+        <f t="shared" si="3"/>
+        <v>510</v>
+      </c>
+      <c r="G38" s="4">
+        <f t="shared" si="3"/>
+        <v>660</v>
+      </c>
+      <c r="H38" s="4">
+        <f t="shared" si="3"/>
+        <v>690</v>
+      </c>
+      <c r="I38" s="4">
+        <f t="shared" si="3"/>
+        <v>690</v>
+      </c>
+      <c r="J38" s="4">
+        <f t="shared" si="3"/>
+        <v>720</v>
+      </c>
+      <c r="K38" s="4">
+        <f t="shared" si="3"/>
+        <v>690</v>
+      </c>
+      <c r="L38" s="4">
+        <f t="shared" si="3"/>
+        <v>540</v>
+      </c>
+      <c r="M38" s="4">
+        <f t="shared" si="3"/>
+        <v>720</v>
+      </c>
+      <c r="N38" s="4">
+        <f t="shared" si="3"/>
+        <v>540</v>
+      </c>
+      <c r="O38" s="4">
+        <f t="shared" si="3"/>
+        <v>780</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="21"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="38" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="20"/>
-      <c r="B38" s="37"/>
-      <c r="C38" s="4" t="s">
+      <c r="D39" s="4">
+        <v>3</v>
+      </c>
+      <c r="E39" s="4">
+        <v>3</v>
+      </c>
+      <c r="F39" s="4">
+        <v>3</v>
+      </c>
+      <c r="G39" s="4">
+        <v>4</v>
+      </c>
+      <c r="H39" s="4">
+        <v>4</v>
+      </c>
+      <c r="I39" s="4">
+        <v>4</v>
+      </c>
+      <c r="J39" s="4">
+        <v>4</v>
+      </c>
+      <c r="K39" s="4">
+        <v>5</v>
+      </c>
+      <c r="L39" s="4">
+        <v>5</v>
+      </c>
+      <c r="M39" s="4">
+        <v>7</v>
+      </c>
+      <c r="N39" s="4">
+        <v>6</v>
+      </c>
+      <c r="O39" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="21"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="39" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="20"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="39"/>
-    </row>
-    <row r="40" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="20"/>
-      <c r="B40" s="35" t="s">
+      <c r="D40" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="E40" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="F40" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="G40" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="H40" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="I40" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="J40" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="K40" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="L40" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="M40" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="N40" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="O40" s="4">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="21"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+    </row>
+    <row r="42" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="21"/>
+      <c r="B42" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C42" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="41" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="20"/>
-      <c r="B41" s="36"/>
-      <c r="C41" s="4" t="s">
+      <c r="D42" s="4">
+        <f t="shared" ref="D42:O42" si="4">0.9*D28</f>
+        <v>990</v>
+      </c>
+      <c r="E42" s="4">
+        <f t="shared" si="4"/>
+        <v>495</v>
+      </c>
+      <c r="F42" s="4">
+        <f t="shared" si="4"/>
+        <v>765</v>
+      </c>
+      <c r="G42" s="4">
+        <f t="shared" si="4"/>
+        <v>990</v>
+      </c>
+      <c r="H42" s="4">
+        <f t="shared" si="4"/>
+        <v>1035</v>
+      </c>
+      <c r="I42" s="4">
+        <f t="shared" si="4"/>
+        <v>1035</v>
+      </c>
+      <c r="J42" s="4">
+        <f t="shared" si="4"/>
+        <v>1080</v>
+      </c>
+      <c r="K42" s="4">
+        <f t="shared" si="4"/>
+        <v>1035</v>
+      </c>
+      <c r="L42" s="4">
+        <f t="shared" si="4"/>
+        <v>810</v>
+      </c>
+      <c r="M42" s="4">
+        <f t="shared" si="4"/>
+        <v>1080</v>
+      </c>
+      <c r="N42" s="4">
+        <f t="shared" si="4"/>
+        <v>810</v>
+      </c>
+      <c r="O42" s="4">
+        <f t="shared" si="4"/>
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="21"/>
+      <c r="B43" s="36"/>
+      <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="42" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="20"/>
-      <c r="B42" s="37"/>
-      <c r="C42" s="4" t="s">
+      <c r="D43" s="4">
+        <v>3</v>
+      </c>
+      <c r="E43" s="4">
+        <v>3</v>
+      </c>
+      <c r="F43" s="4">
+        <v>3</v>
+      </c>
+      <c r="G43" s="4">
+        <v>4</v>
+      </c>
+      <c r="H43" s="4">
+        <v>4</v>
+      </c>
+      <c r="I43" s="4">
+        <v>4</v>
+      </c>
+      <c r="J43" s="4">
+        <v>4</v>
+      </c>
+      <c r="K43" s="4">
+        <v>5</v>
+      </c>
+      <c r="L43" s="4">
+        <v>5</v>
+      </c>
+      <c r="M43" s="4">
+        <v>7</v>
+      </c>
+      <c r="N43" s="4">
+        <v>6</v>
+      </c>
+      <c r="O43" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="21"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="20"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="40"/>
-    </row>
-    <row r="44" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="20"/>
-      <c r="B44" s="35" t="s">
+      <c r="D44" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="E44" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="F44" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="G44" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="H44" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="I44" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="J44" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="K44" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="L44" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="M44" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="N44" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="O44" s="4">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="21"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="17"/>
+    </row>
+    <row r="46" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="21"/>
+      <c r="B46" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="C44" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="20"/>
-      <c r="B45" s="36"/>
-      <c r="C45" s="4">
+      <c r="C46" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="21"/>
+      <c r="B47" s="36"/>
+      <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="20"/>
-      <c r="B46" s="37"/>
-      <c r="C46" s="4">
+    <row r="48" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="21"/>
+      <c r="B48" s="37"/>
+      <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="20"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="39"/>
-    </row>
-    <row r="48" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="20"/>
-      <c r="B48" s="35" t="s">
+    <row r="49" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="21"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+    </row>
+    <row r="50" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="21"/>
+      <c r="B50" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C50" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D48" s="4">
-        <f t="shared" ref="D48:R48" si="0">D20+D25+D30+D35</f>
-        <v>0</v>
-      </c>
-      <c r="E48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="20"/>
-      <c r="B49" s="36"/>
-      <c r="C49" s="4" t="s">
+      <c r="D50" s="4">
+        <f t="shared" ref="D50:O50" si="5">D22+D27+D32+D37</f>
+        <v>42</v>
+      </c>
+      <c r="E50" s="4">
+        <f t="shared" si="5"/>
+        <v>42</v>
+      </c>
+      <c r="F50" s="4">
+        <f t="shared" ref="F50" si="6">F22+F27+F32+F37</f>
+        <v>42</v>
+      </c>
+      <c r="G50" s="4">
+        <f t="shared" si="5"/>
+        <v>42</v>
+      </c>
+      <c r="H50" s="4">
+        <f t="shared" si="5"/>
+        <v>42</v>
+      </c>
+      <c r="I50" s="4">
+        <f t="shared" si="5"/>
+        <v>46</v>
+      </c>
+      <c r="J50" s="4">
+        <f t="shared" si="5"/>
+        <v>48</v>
+      </c>
+      <c r="K50" s="4">
+        <f t="shared" si="5"/>
+        <v>54</v>
+      </c>
+      <c r="L50" s="4">
+        <f t="shared" si="5"/>
+        <v>54</v>
+      </c>
+      <c r="M50" s="4">
+        <f t="shared" si="5"/>
+        <v>58</v>
+      </c>
+      <c r="N50" s="4">
+        <f t="shared" si="5"/>
+        <v>58</v>
+      </c>
+      <c r="O50" s="4">
+        <f t="shared" si="5"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="21"/>
+      <c r="B51" s="36"/>
+      <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D49" s="4">
-        <f t="shared" ref="D49:R49" si="1">D22+D27+D32+D37+D41</f>
-        <v>0</v>
-      </c>
-      <c r="E49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="20"/>
-      <c r="B50" s="37"/>
-      <c r="C50" s="4" t="s">
+      <c r="D51" s="4">
+        <f t="shared" ref="D51:O51" si="7">D24+D29+D34+D39+D43</f>
+        <v>15</v>
+      </c>
+      <c r="E51" s="4">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="F51" s="4">
+        <f t="shared" ref="F51" si="8">F24+F29+F34+F39+F43</f>
+        <v>15</v>
+      </c>
+      <c r="G51" s="4">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="H51" s="4">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="I51" s="4">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="J51" s="4">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K51" s="4">
+        <f t="shared" si="7"/>
+        <v>25</v>
+      </c>
+      <c r="L51" s="4">
+        <f t="shared" si="7"/>
+        <v>25</v>
+      </c>
+      <c r="M51" s="4">
+        <f t="shared" si="7"/>
+        <v>33</v>
+      </c>
+      <c r="N51" s="4">
+        <f t="shared" si="7"/>
+        <v>31</v>
+      </c>
+      <c r="O51" s="4">
+        <f t="shared" si="7"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="21"/>
+      <c r="B52" s="37"/>
+      <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="D50" s="4">
-        <f>D48*(1+D49*0.02)</f>
-        <v>0</v>
-      </c>
-      <c r="E50" s="4">
-        <f>E48*(1+E49*0.02)</f>
-        <v>0</v>
-      </c>
-      <c r="G50" s="4">
-        <f t="shared" ref="G50:R50" si="2">G48*(1+G49*0.02)</f>
-        <v>0</v>
-      </c>
-      <c r="H50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="2"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-    </row>
-    <row r="52" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="34" t="s">
+      <c r="D52" s="4">
+        <f>D50*(1+D51*0.02)</f>
+        <v>54.6</v>
+      </c>
+      <c r="E52" s="4">
+        <f>E50*(1+E51*0.02)</f>
+        <v>54.6</v>
+      </c>
+      <c r="F52" s="4">
+        <f>F50*(1+F51*0.02)</f>
+        <v>54.6</v>
+      </c>
+      <c r="G52" s="4">
+        <f t="shared" ref="G52:O52" si="9">G50*(1+G51*0.02)</f>
+        <v>58.8</v>
+      </c>
+      <c r="H52" s="4">
+        <f t="shared" si="9"/>
+        <v>58.8</v>
+      </c>
+      <c r="I52" s="4">
+        <f t="shared" si="9"/>
+        <v>64.399999999999991</v>
+      </c>
+      <c r="J52" s="4">
+        <f t="shared" si="9"/>
+        <v>67.199999999999989</v>
+      </c>
+      <c r="K52" s="4">
+        <f t="shared" si="9"/>
+        <v>81</v>
+      </c>
+      <c r="L52" s="4">
+        <f t="shared" si="9"/>
+        <v>81</v>
+      </c>
+      <c r="M52" s="4">
+        <f t="shared" si="9"/>
+        <v>96.28</v>
+      </c>
+      <c r="N52" s="4">
+        <f t="shared" si="9"/>
+        <v>93.960000000000008</v>
+      </c>
+      <c r="O52" s="4">
+        <f t="shared" si="9"/>
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="2"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+    </row>
+    <row r="54" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="B52" s="34" t="s">
+      <c r="B54" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C54" s="5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="53" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="21"/>
-      <c r="B53" s="21"/>
-      <c r="C53" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="21"/>
-      <c r="B54" s="21"/>
-      <c r="C54" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="21"/>
+      <c r="F54" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="22"/>
       <c r="B55" s="22"/>
       <c r="C55" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="22"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="22"/>
+      <c r="B57" s="23"/>
+      <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="56" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="21"/>
-      <c r="B56" s="34" t="s">
+      <c r="F57" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="22"/>
+      <c r="B58" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C56" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="21"/>
-      <c r="B57" s="21"/>
-      <c r="C57" s="5">
+      <c r="C58" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="22"/>
+      <c r="B59" s="22"/>
+      <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="21"/>
-      <c r="B58" s="22"/>
-      <c r="C58" s="5">
+    <row r="60" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="22"/>
+      <c r="B60" s="23"/>
+      <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="21"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="39"/>
-    </row>
-    <row r="60" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="21"/>
-      <c r="B60" s="34" t="s">
+    <row r="61" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="22"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+    </row>
+    <row r="62" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="22"/>
+      <c r="B62" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C62" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="61" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="21"/>
-      <c r="B61" s="21"/>
-      <c r="C61" s="5" t="s">
+      <c r="F62" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="22"/>
+      <c r="B63" s="22"/>
+      <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="62" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="22"/>
-      <c r="B62" s="22"/>
-      <c r="C62" s="5" t="s">
+      <c r="F63" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="23"/>
+      <c r="B64" s="23"/>
+      <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="63" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="29" t="s">
+      <c r="F64" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B66" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C66" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F64" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="30"/>
-      <c r="B65" s="4" t="s">
+      <c r="D66" s="6">
+        <v>1</v>
+      </c>
+      <c r="E66" s="6">
+        <v>1</v>
+      </c>
+      <c r="F66" s="6">
+        <v>1</v>
+      </c>
+      <c r="G66" s="6">
+        <v>1</v>
+      </c>
+      <c r="H66" s="6">
+        <v>1</v>
+      </c>
+      <c r="I66" s="6">
+        <v>1</v>
+      </c>
+      <c r="J66" s="6">
+        <v>1</v>
+      </c>
+      <c r="K66" s="6">
+        <v>1</v>
+      </c>
+      <c r="L66" s="6">
+        <v>1</v>
+      </c>
+      <c r="M66" s="6">
+        <v>1</v>
+      </c>
+      <c r="N66" s="6">
+        <v>1</v>
+      </c>
+      <c r="O66" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="31"/>
+      <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C67" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="F65" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="30"/>
-      <c r="B66" s="4" t="s">
+      <c r="D67" s="4">
+        <v>1</v>
+      </c>
+      <c r="E67" s="4">
+        <v>1</v>
+      </c>
+      <c r="F67" s="4">
+        <v>0</v>
+      </c>
+      <c r="G67" s="4">
+        <v>1</v>
+      </c>
+      <c r="H67" s="4">
+        <v>1</v>
+      </c>
+      <c r="I67" s="4">
+        <v>1</v>
+      </c>
+      <c r="J67" s="4">
+        <v>1</v>
+      </c>
+      <c r="K67" s="4">
+        <v>1</v>
+      </c>
+      <c r="L67" s="4">
+        <v>1</v>
+      </c>
+      <c r="M67" s="4">
+        <v>1</v>
+      </c>
+      <c r="N67" s="4">
+        <v>1</v>
+      </c>
+      <c r="O67" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="31"/>
+      <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C68" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="F66" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="31"/>
-      <c r="B67" s="5" t="s">
+      <c r="D68" s="4">
+        <v>1</v>
+      </c>
+      <c r="E68" s="4">
+        <v>0</v>
+      </c>
+      <c r="F68" s="4">
+        <v>0</v>
+      </c>
+      <c r="G68" s="4">
+        <v>0</v>
+      </c>
+      <c r="H68" s="4">
+        <v>0</v>
+      </c>
+      <c r="I68" s="4">
+        <v>0</v>
+      </c>
+      <c r="J68" s="4">
+        <v>0</v>
+      </c>
+      <c r="K68" s="4">
+        <v>0</v>
+      </c>
+      <c r="L68" s="4">
+        <v>1</v>
+      </c>
+      <c r="M68" s="4">
+        <v>0</v>
+      </c>
+      <c r="N68" s="4">
+        <v>0</v>
+      </c>
+      <c r="O68" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="32"/>
+      <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="C69" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F67" s="5">
+      <c r="D69" s="5">
+        <v>0</v>
+      </c>
+      <c r="E69" s="5">
+        <v>0</v>
+      </c>
+      <c r="F69" s="5">
+        <v>0</v>
+      </c>
+      <c r="G69" s="5">
+        <v>0</v>
+      </c>
+      <c r="H69" s="5">
+        <v>0</v>
+      </c>
+      <c r="I69" s="5">
+        <v>0</v>
+      </c>
+      <c r="J69" s="5">
+        <v>0</v>
+      </c>
+      <c r="K69" s="5">
+        <v>0</v>
+      </c>
+      <c r="L69" s="5">
+        <v>1</v>
+      </c>
+      <c r="M69" s="5">
+        <v>0</v>
+      </c>
+      <c r="N69" s="5">
+        <v>0</v>
+      </c>
+      <c r="O69" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="A7:A18"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="A20:A50"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="A52:A62"/>
-    <mergeCell ref="B52:B55"/>
-    <mergeCell ref="B60:B62"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="A9:A20"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="A22:A52"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="A54:A64"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A66:A69"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7602,7 +9011,7 @@
       <c r="E2" s="2">
         <v>1</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>1</v>
       </c>
       <c r="G2" s="2">
@@ -7618,6 +9027,30 @@
         <v>1</v>
       </c>
       <c r="K2" s="2">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1</v>
+      </c>
+      <c r="M2" s="2">
+        <v>1</v>
+      </c>
+      <c r="N2" s="2">
+        <v>1</v>
+      </c>
+      <c r="O2" s="2">
+        <v>1</v>
+      </c>
+      <c r="P2" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>1</v>
+      </c>
+      <c r="R2" s="2">
+        <v>1</v>
+      </c>
+      <c r="S2" s="2">
         <v>1</v>
       </c>
     </row>
@@ -7727,6 +9160,48 @@
       <c r="K5" s="1" t="s">
         <v>180</v>
       </c>
+      <c r="L5" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="6" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="1" t="s">
@@ -7827,7 +9302,7 @@
         <v>5</v>
       </c>
       <c r="K7" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L7" s="1">
         <v>5</v>
@@ -7842,7 +9317,7 @@
         <v>5</v>
       </c>
       <c r="P7" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q7" s="1">
         <v>5</v>
@@ -7900,8 +9375,8 @@
       <c r="J8" s="1">
         <v>2</v>
       </c>
-      <c r="K8" s="1">
-        <v>2</v>
+      <c r="K8" s="1" t="s">
+        <v>189</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
@@ -7915,8 +9390,8 @@
       <c r="O8" s="1">
         <v>3</v>
       </c>
-      <c r="P8" s="1">
-        <v>3</v>
+      <c r="P8" s="1" t="s">
+        <v>189</v>
       </c>
       <c r="Q8" s="1">
         <v>4</v>
@@ -7948,10 +9423,10 @@
       <c r="AA8" s="1"/>
     </row>
     <row r="9" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -7979,7 +9454,7 @@
         <v>200</v>
       </c>
       <c r="K9" s="3">
-        <v>250</v>
+        <v>88</v>
       </c>
       <c r="L9" s="3">
         <v>270</v>
@@ -7994,16 +9469,16 @@
         <v>280</v>
       </c>
       <c r="P9" s="3">
-        <v>290</v>
+        <v>98</v>
       </c>
       <c r="Q9" s="3">
         <v>295</v>
       </c>
       <c r="R9" s="3">
+        <v>350</v>
+      </c>
+      <c r="S9" s="3">
         <v>325</v>
-      </c>
-      <c r="S9" s="3">
-        <v>350</v>
       </c>
       <c r="T9" s="3">
         <v>345</v>
@@ -8025,8 +9500,8 @@
       </c>
     </row>
     <row r="10" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="19"/>
-      <c r="B10" s="17"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -8052,7 +9527,7 @@
         <v>1200</v>
       </c>
       <c r="K10" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
       <c r="L10" s="3">
         <v>900</v>
@@ -8067,7 +9542,7 @@
         <v>900</v>
       </c>
       <c r="P10" s="3">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="Q10" s="3">
         <v>800</v>
@@ -8098,8 +9573,8 @@
       </c>
     </row>
     <row r="11" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
-      <c r="B11" s="17"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -8171,8 +9646,8 @@
       </c>
     </row>
     <row r="12" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="19"/>
-      <c r="B12" s="17"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -8244,8 +9719,8 @@
       </c>
     </row>
     <row r="13" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19"/>
-      <c r="B13" s="17" t="s">
+      <c r="A13" s="20"/>
+      <c r="B13" s="18" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -8253,25 +9728,25 @@
       </c>
     </row>
     <row r="14" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="19"/>
-      <c r="B14" s="17"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="18"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19"/>
-      <c r="B15" s="17"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="18"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:27" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19"/>
+      <c r="A16" s="20"/>
     </row>
     <row r="17" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="19"/>
-      <c r="B17" s="23" t="s">
+      <c r="A17" s="20"/>
+      <c r="B17" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -8345,8 +9820,8 @@
       </c>
     </row>
     <row r="18" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19"/>
-      <c r="B18" s="24"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -8372,7 +9847,7 @@
         <v>0.7</v>
       </c>
       <c r="K18" s="3">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="L18" s="3">
         <v>0.9</v>
@@ -8387,7 +9862,7 @@
         <v>0.9</v>
       </c>
       <c r="P18" s="3">
-        <v>0.8</v>
+        <v>0.65</v>
       </c>
       <c r="Q18" s="3">
         <v>0.9</v>
@@ -8418,8 +9893,8 @@
       </c>
     </row>
     <row r="19" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19"/>
-      <c r="B19" s="24"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="25"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -8491,8 +9966,8 @@
       </c>
     </row>
     <row r="20" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="19"/>
-      <c r="B20" s="25"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -8533,7 +10008,7 @@
         <v>0.6</v>
       </c>
       <c r="P20" s="3">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="Q20" s="3">
         <v>-0.2</v>
@@ -8570,10 +10045,10 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="38" t="s">
+      <c r="B22" s="39" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -8601,7 +10076,7 @@
         <v>13</v>
       </c>
       <c r="K22" s="4">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L22" s="4">
         <v>13</v>
@@ -8616,7 +10091,7 @@
         <v>13</v>
       </c>
       <c r="P22" s="4">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q22" s="4">
         <v>14</v>
@@ -8647,103 +10122,103 @@
       </c>
     </row>
     <row r="23" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="20"/>
-      <c r="B23" s="38"/>
+      <c r="A23" s="21"/>
+      <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D23" s="4">
-        <f>0.7*D28</f>
+        <f t="shared" ref="D23:Y23" si="0">0.7*D28</f>
         <v>909.99999999999989</v>
       </c>
       <c r="E23" s="4">
-        <f>0.7*E28</f>
+        <f t="shared" si="0"/>
         <v>560</v>
       </c>
       <c r="F23" s="4" t="e">
-        <f>0.7*F28</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="G23" s="4">
-        <f>0.7*G28</f>
+        <f t="shared" si="0"/>
         <v>350</v>
       </c>
       <c r="H23" s="4">
-        <f>0.7*H28</f>
+        <f t="shared" si="0"/>
         <v>630</v>
       </c>
       <c r="I23" s="4">
-        <f>0.7*I28</f>
+        <f t="shared" si="0"/>
         <v>350</v>
       </c>
       <c r="J23" s="4">
-        <f>0.7*J28</f>
+        <f t="shared" si="0"/>
         <v>840</v>
       </c>
       <c r="K23" s="4">
-        <f>0.7*K28</f>
-        <v>1050</v>
+        <f t="shared" si="0"/>
+        <v>770</v>
       </c>
       <c r="L23" s="4">
-        <f>0.7*L28</f>
+        <f t="shared" si="0"/>
         <v>630</v>
       </c>
       <c r="M23" s="4">
-        <f>0.7*M28</f>
+        <f t="shared" si="0"/>
         <v>840</v>
       </c>
       <c r="N23" s="4">
-        <f>0.7*N28</f>
+        <f t="shared" si="0"/>
         <v>700</v>
       </c>
       <c r="O23" s="4">
-        <f>0.7*O28</f>
+        <f t="shared" si="0"/>
         <v>630</v>
       </c>
       <c r="P23" s="4">
-        <f>0.7*P28</f>
-        <v>1050</v>
+        <f t="shared" si="0"/>
+        <v>840</v>
       </c>
       <c r="Q23" s="4">
-        <f>0.7*Q28</f>
+        <f t="shared" si="0"/>
         <v>560</v>
       </c>
       <c r="R23" s="4">
-        <f>0.7*R28</f>
+        <f t="shared" si="0"/>
         <v>665</v>
       </c>
       <c r="S23" s="4">
-        <f>0.7*S28</f>
+        <f t="shared" si="0"/>
         <v>735</v>
       </c>
       <c r="T23" s="4">
-        <f>0.7*T28</f>
+        <f t="shared" si="0"/>
         <v>1400</v>
       </c>
       <c r="U23" s="4">
-        <f>0.7*U28</f>
+        <f t="shared" si="0"/>
         <v>1085</v>
       </c>
       <c r="V23" s="4">
-        <f>0.7*V28</f>
+        <f t="shared" si="0"/>
         <v>979.99999999999989</v>
       </c>
       <c r="W23" s="4">
-        <f>0.7*W28</f>
+        <f t="shared" si="0"/>
         <v>700</v>
       </c>
       <c r="X23" s="4">
-        <f>0.7*X28</f>
+        <f t="shared" si="0"/>
         <v>770</v>
       </c>
       <c r="Y23" s="4">
-        <f>0.7*Y28</f>
+        <f t="shared" si="0"/>
         <v>1470</v>
       </c>
     </row>
     <row r="24" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="20"/>
-      <c r="B24" s="38"/>
+      <c r="A24" s="21"/>
+      <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
       </c>
@@ -8769,7 +10244,7 @@
         <v>6</v>
       </c>
       <c r="K24" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L24" s="4">
         <v>7</v>
@@ -8784,7 +10259,7 @@
         <v>7</v>
       </c>
       <c r="P24" s="4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q24" s="4">
         <v>8</v>
@@ -8815,8 +10290,8 @@
       </c>
     </row>
     <row r="25" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="20"/>
-      <c r="B25" s="38"/>
+      <c r="A25" s="21"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
       </c>
@@ -8888,15 +10363,15 @@
       </c>
     </row>
     <row r="26" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="20"/>
+      <c r="A26" s="21"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="20"/>
-      <c r="B27" s="38" t="s">
+      <c r="A27" s="21"/>
+      <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="4" t="s">
@@ -8924,7 +10399,7 @@
         <v>20</v>
       </c>
       <c r="K27" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L27" s="4">
         <v>20</v>
@@ -8939,7 +10414,7 @@
         <v>20</v>
       </c>
       <c r="P27" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Q27" s="4">
         <v>22</v>
@@ -8970,103 +10445,103 @@
       </c>
     </row>
     <row r="28" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="20"/>
-      <c r="B28" s="38"/>
+      <c r="A28" s="21"/>
+      <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D28" s="4">
-        <f>D10</f>
+        <f t="shared" ref="D28:Y28" si="1">D10</f>
         <v>1300</v>
       </c>
       <c r="E28" s="4">
-        <f>E10</f>
+        <f t="shared" si="1"/>
         <v>800</v>
       </c>
       <c r="F28" s="4" t="str">
-        <f>F10</f>
+        <f t="shared" si="1"/>
         <v>null</v>
       </c>
       <c r="G28" s="4">
-        <f>G10</f>
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="H28" s="4">
-        <f>H10</f>
+        <f t="shared" si="1"/>
         <v>900</v>
       </c>
       <c r="I28" s="4">
-        <f>I10</f>
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J28" s="4">
-        <f>J10</f>
+        <f t="shared" si="1"/>
         <v>1200</v>
       </c>
       <c r="K28" s="4">
-        <f>K10</f>
-        <v>1500</v>
+        <f t="shared" si="1"/>
+        <v>1100</v>
       </c>
       <c r="L28" s="4">
-        <f>L10</f>
+        <f t="shared" si="1"/>
         <v>900</v>
       </c>
       <c r="M28" s="4">
-        <f>M10</f>
+        <f t="shared" si="1"/>
         <v>1200</v>
       </c>
       <c r="N28" s="4">
-        <f>N10</f>
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
       <c r="O28" s="4">
-        <f>O10</f>
+        <f t="shared" si="1"/>
         <v>900</v>
       </c>
       <c r="P28" s="4">
-        <f>P10</f>
-        <v>1500</v>
+        <f t="shared" si="1"/>
+        <v>1200</v>
       </c>
       <c r="Q28" s="4">
-        <f>Q10</f>
+        <f t="shared" si="1"/>
         <v>800</v>
       </c>
       <c r="R28" s="4">
-        <f>R10</f>
+        <f t="shared" si="1"/>
         <v>950</v>
       </c>
       <c r="S28" s="4">
-        <f>S10</f>
+        <f t="shared" si="1"/>
         <v>1050</v>
       </c>
       <c r="T28" s="4">
-        <f>T10</f>
+        <f t="shared" si="1"/>
         <v>2000</v>
       </c>
       <c r="U28" s="4">
-        <f>U10</f>
+        <f t="shared" si="1"/>
         <v>1550</v>
       </c>
       <c r="V28" s="4">
-        <f>V10</f>
+        <f t="shared" si="1"/>
         <v>1400</v>
       </c>
       <c r="W28" s="4">
-        <f>W10</f>
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
       <c r="X28" s="4">
-        <f>X10</f>
+        <f t="shared" si="1"/>
         <v>1100</v>
       </c>
       <c r="Y28" s="4">
-        <f>Y10</f>
+        <f t="shared" si="1"/>
         <v>2100</v>
       </c>
     </row>
     <row r="29" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="20"/>
-      <c r="B29" s="38"/>
+      <c r="A29" s="21"/>
+      <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
       </c>
@@ -9092,7 +10567,7 @@
         <v>6</v>
       </c>
       <c r="K29" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L29" s="4">
         <v>7</v>
@@ -9107,7 +10582,7 @@
         <v>8</v>
       </c>
       <c r="P29" s="4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q29" s="4">
         <v>8</v>
@@ -9138,8 +10613,8 @@
       </c>
     </row>
     <row r="30" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="20"/>
-      <c r="B30" s="38"/>
+      <c r="A30" s="21"/>
+      <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
       </c>
@@ -9211,14 +10686,14 @@
       </c>
     </row>
     <row r="31" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="20"/>
+      <c r="A31" s="21"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="20"/>
+      <c r="A32" s="21"/>
       <c r="B32" s="35" t="s">
         <v>17</v>
       </c>
@@ -9247,7 +10722,7 @@
         <v>18</v>
       </c>
       <c r="K32" s="4">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="L32" s="4">
         <v>18</v>
@@ -9262,7 +10737,7 @@
         <v>18</v>
       </c>
       <c r="P32" s="4">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Q32" s="4">
         <v>19</v>
@@ -9293,102 +10768,102 @@
       </c>
     </row>
     <row r="33" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="20"/>
+      <c r="A33" s="21"/>
       <c r="B33" s="36"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D33" s="4">
-        <f>0.9*D28</f>
+        <f t="shared" ref="D33:Y33" si="2">0.9*D28</f>
         <v>1170</v>
       </c>
       <c r="E33" s="4">
-        <f>0.9*E28</f>
+        <f t="shared" si="2"/>
         <v>720</v>
       </c>
       <c r="F33" s="4" t="e">
-        <f>0.9*F28</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="G33" s="4">
-        <f>0.9*G28</f>
+        <f t="shared" si="2"/>
         <v>450</v>
       </c>
       <c r="H33" s="4">
-        <f>0.9*H28</f>
+        <f t="shared" si="2"/>
         <v>810</v>
       </c>
       <c r="I33" s="4">
-        <f>0.9*I28</f>
+        <f t="shared" si="2"/>
         <v>450</v>
       </c>
       <c r="J33" s="4">
-        <f>0.9*J28</f>
+        <f t="shared" si="2"/>
         <v>1080</v>
       </c>
       <c r="K33" s="4">
-        <f>0.9*K28</f>
-        <v>1350</v>
+        <f t="shared" si="2"/>
+        <v>990</v>
       </c>
       <c r="L33" s="4">
-        <f>0.9*L28</f>
+        <f t="shared" si="2"/>
         <v>810</v>
       </c>
       <c r="M33" s="4">
-        <f>0.9*M28</f>
+        <f t="shared" si="2"/>
         <v>1080</v>
       </c>
       <c r="N33" s="4">
-        <f>0.9*N28</f>
+        <f t="shared" si="2"/>
         <v>900</v>
       </c>
       <c r="O33" s="4">
-        <f>0.9*O28</f>
+        <f t="shared" si="2"/>
         <v>810</v>
       </c>
       <c r="P33" s="4">
-        <f>0.9*P28</f>
-        <v>1350</v>
+        <f t="shared" si="2"/>
+        <v>1080</v>
       </c>
       <c r="Q33" s="4">
-        <f>0.9*Q28</f>
+        <f t="shared" si="2"/>
         <v>720</v>
       </c>
       <c r="R33" s="4">
-        <f>0.9*R28</f>
+        <f t="shared" si="2"/>
         <v>855</v>
       </c>
       <c r="S33" s="4">
-        <f>0.9*S28</f>
+        <f t="shared" si="2"/>
         <v>945</v>
       </c>
       <c r="T33" s="4">
-        <f>0.9*T28</f>
+        <f t="shared" si="2"/>
         <v>1800</v>
       </c>
       <c r="U33" s="4">
-        <f>0.9*U28</f>
+        <f t="shared" si="2"/>
         <v>1395</v>
       </c>
       <c r="V33" s="4">
-        <f>0.9*V28</f>
+        <f t="shared" si="2"/>
         <v>1260</v>
       </c>
       <c r="W33" s="4">
-        <f>0.9*W28</f>
+        <f t="shared" si="2"/>
         <v>900</v>
       </c>
       <c r="X33" s="4">
-        <f>0.9*X28</f>
+        <f t="shared" si="2"/>
         <v>990</v>
       </c>
       <c r="Y33" s="4">
-        <f>0.9*Y28</f>
+        <f t="shared" si="2"/>
         <v>1890</v>
       </c>
     </row>
     <row r="34" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="20"/>
+      <c r="A34" s="21"/>
       <c r="B34" s="36"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
@@ -9415,25 +10890,25 @@
         <v>6</v>
       </c>
       <c r="K34" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L34" s="4">
-        <v>0.15</v>
+        <v>7</v>
       </c>
       <c r="M34" s="4">
-        <v>0.15</v>
+        <v>7</v>
       </c>
       <c r="N34" s="4">
-        <v>0.15</v>
+        <v>7</v>
       </c>
       <c r="O34" s="4">
-        <v>0.15</v>
+        <v>8</v>
       </c>
       <c r="P34" s="4">
-        <v>0.15</v>
+        <v>4</v>
       </c>
       <c r="Q34" s="4">
-        <v>0.15</v>
+        <v>8</v>
       </c>
       <c r="R34" s="4">
         <v>9</v>
@@ -9461,7 +10936,7 @@
       </c>
     </row>
     <row r="35" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="20"/>
+      <c r="A35" s="21"/>
       <c r="B35" s="37"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
@@ -9534,14 +11009,14 @@
       </c>
     </row>
     <row r="36" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="20"/>
+      <c r="A36" s="21"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="20"/>
+      <c r="A37" s="21"/>
       <c r="B37" s="35" t="s">
         <v>18</v>
       </c>
@@ -9570,7 +11045,7 @@
         <v>10</v>
       </c>
       <c r="K37" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L37" s="4">
         <v>10</v>
@@ -9585,7 +11060,7 @@
         <v>10</v>
       </c>
       <c r="P37" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q37" s="4">
         <v>11</v>
@@ -9616,102 +11091,102 @@
       </c>
     </row>
     <row r="38" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="20"/>
+      <c r="A38" s="21"/>
       <c r="B38" s="36"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="4">
-        <f>0.6*D28</f>
+        <f t="shared" ref="D38:Y38" si="3">0.6*D28</f>
         <v>780</v>
       </c>
       <c r="E38" s="4">
-        <f>0.6*E28</f>
+        <f t="shared" si="3"/>
         <v>480</v>
       </c>
       <c r="F38" s="4" t="e">
-        <f>0.6*F28</f>
+        <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
       <c r="G38" s="4">
-        <f>0.6*G28</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="H38" s="4">
-        <f>0.6*H28</f>
+        <f t="shared" si="3"/>
         <v>540</v>
       </c>
       <c r="I38" s="4">
-        <f>0.6*I28</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="J38" s="4">
-        <f>0.6*J28</f>
+        <f t="shared" si="3"/>
         <v>720</v>
       </c>
       <c r="K38" s="4">
-        <f>0.6*K28</f>
-        <v>900</v>
+        <f t="shared" si="3"/>
+        <v>660</v>
       </c>
       <c r="L38" s="4">
-        <f>0.6*L28</f>
+        <f t="shared" si="3"/>
         <v>540</v>
       </c>
       <c r="M38" s="4">
-        <f>0.6*M28</f>
+        <f t="shared" si="3"/>
         <v>720</v>
       </c>
       <c r="N38" s="4">
-        <f>0.6*N28</f>
+        <f t="shared" si="3"/>
         <v>600</v>
       </c>
       <c r="O38" s="4">
-        <f>0.6*O28</f>
+        <f t="shared" si="3"/>
         <v>540</v>
       </c>
       <c r="P38" s="4">
-        <f>0.6*P28</f>
-        <v>900</v>
+        <f t="shared" si="3"/>
+        <v>720</v>
       </c>
       <c r="Q38" s="4">
-        <f>0.6*Q28</f>
+        <f t="shared" si="3"/>
         <v>480</v>
       </c>
       <c r="R38" s="4">
-        <f>0.6*R28</f>
+        <f t="shared" si="3"/>
         <v>570</v>
       </c>
       <c r="S38" s="4">
-        <f>0.6*S28</f>
+        <f t="shared" si="3"/>
         <v>630</v>
       </c>
       <c r="T38" s="4">
-        <f>0.6*T28</f>
+        <f t="shared" si="3"/>
         <v>1200</v>
       </c>
       <c r="U38" s="4">
-        <f>0.6*U28</f>
+        <f t="shared" si="3"/>
         <v>930</v>
       </c>
       <c r="V38" s="4">
-        <f>0.6*V28</f>
+        <f t="shared" si="3"/>
         <v>840</v>
       </c>
       <c r="W38" s="4">
-        <f>0.6*W28</f>
+        <f t="shared" si="3"/>
         <v>600</v>
       </c>
       <c r="X38" s="4">
-        <f>0.6*X28</f>
+        <f t="shared" si="3"/>
         <v>660</v>
       </c>
       <c r="Y38" s="4">
-        <f>0.6*Y28</f>
+        <f t="shared" si="3"/>
         <v>1260</v>
       </c>
     </row>
     <row r="39" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="20"/>
+      <c r="A39" s="21"/>
       <c r="B39" s="36"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
@@ -9738,7 +11213,7 @@
         <v>6</v>
       </c>
       <c r="K39" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L39" s="4">
         <v>7</v>
@@ -9753,7 +11228,7 @@
         <v>7</v>
       </c>
       <c r="P39" s="4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q39" s="4">
         <v>8</v>
@@ -9784,7 +11259,7 @@
       </c>
     </row>
     <row r="40" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="20"/>
+      <c r="A40" s="21"/>
       <c r="B40" s="37"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
@@ -9857,14 +11332,14 @@
       </c>
     </row>
     <row r="41" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="20"/>
+      <c r="A41" s="21"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="20"/>
+      <c r="A42" s="21"/>
       <c r="B42" s="35" t="s">
         <v>19</v>
       </c>
@@ -9872,96 +11347,96 @@
         <v>7</v>
       </c>
       <c r="D42" s="4">
-        <f>0.9*D28</f>
+        <f t="shared" ref="D42:Y42" si="4">0.9*D28</f>
         <v>1170</v>
       </c>
       <c r="E42" s="4">
-        <f>0.9*E28</f>
+        <f t="shared" si="4"/>
         <v>720</v>
       </c>
       <c r="F42" s="4" t="e">
-        <f>0.9*F28</f>
+        <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
       <c r="G42" s="4">
-        <f>0.9*G28</f>
+        <f t="shared" si="4"/>
         <v>450</v>
       </c>
       <c r="H42" s="4">
-        <f>0.9*H28</f>
+        <f t="shared" si="4"/>
         <v>810</v>
       </c>
       <c r="I42" s="4">
-        <f>0.9*I28</f>
+        <f t="shared" si="4"/>
         <v>450</v>
       </c>
       <c r="J42" s="4">
-        <f>0.9*J28</f>
+        <f t="shared" si="4"/>
         <v>1080</v>
       </c>
       <c r="K42" s="4">
-        <f>0.9*K28</f>
-        <v>1350</v>
+        <f t="shared" si="4"/>
+        <v>990</v>
       </c>
       <c r="L42" s="4">
-        <f>0.9*L28</f>
+        <f t="shared" si="4"/>
         <v>810</v>
       </c>
       <c r="M42" s="4">
-        <f>0.9*M28</f>
+        <f t="shared" si="4"/>
         <v>1080</v>
       </c>
       <c r="N42" s="4">
-        <f>0.9*N28</f>
+        <f t="shared" si="4"/>
         <v>900</v>
       </c>
       <c r="O42" s="4">
-        <f>0.9*O28</f>
+        <f t="shared" si="4"/>
         <v>810</v>
       </c>
       <c r="P42" s="4">
-        <f>0.9*P28</f>
-        <v>1350</v>
+        <f t="shared" si="4"/>
+        <v>1080</v>
       </c>
       <c r="Q42" s="4">
-        <f>0.9*Q28</f>
+        <f t="shared" si="4"/>
         <v>720</v>
       </c>
       <c r="R42" s="4">
-        <f>0.9*R28</f>
+        <f t="shared" si="4"/>
         <v>855</v>
       </c>
       <c r="S42" s="4">
-        <f>0.9*S28</f>
+        <f t="shared" si="4"/>
         <v>945</v>
       </c>
       <c r="T42" s="4">
-        <f>0.9*T28</f>
+        <f t="shared" si="4"/>
         <v>1800</v>
       </c>
       <c r="U42" s="4">
-        <f>0.9*U28</f>
+        <f t="shared" si="4"/>
         <v>1395</v>
       </c>
       <c r="V42" s="4">
-        <f>0.9*V28</f>
+        <f t="shared" si="4"/>
         <v>1260</v>
       </c>
       <c r="W42" s="4">
-        <f>0.9*W28</f>
+        <f t="shared" si="4"/>
         <v>900</v>
       </c>
       <c r="X42" s="4">
-        <f>0.9*X28</f>
+        <f t="shared" si="4"/>
         <v>990</v>
       </c>
       <c r="Y42" s="4">
-        <f>0.9*Y28</f>
+        <f t="shared" si="4"/>
         <v>1890</v>
       </c>
     </row>
     <row r="43" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="20"/>
+      <c r="A43" s="21"/>
       <c r="B43" s="36"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
@@ -10003,7 +11478,7 @@
         <v>7</v>
       </c>
       <c r="P43" s="4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q43" s="4">
         <v>8</v>
@@ -10034,7 +11509,7 @@
       </c>
     </row>
     <row r="44" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="20"/>
+      <c r="A44" s="21"/>
       <c r="B44" s="37"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
@@ -10107,12 +11582,12 @@
       </c>
     </row>
     <row r="45" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="20"/>
+      <c r="A45" s="21"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
     </row>
     <row r="46" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="20"/>
+      <c r="A46" s="21"/>
       <c r="B46" s="35" t="s">
         <v>30</v>
       </c>
@@ -10121,28 +11596,28 @@
       </c>
     </row>
     <row r="47" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="20"/>
+      <c r="A47" s="21"/>
       <c r="B47" s="36"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="20"/>
+      <c r="A48" s="21"/>
       <c r="B48" s="37"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="20"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="20"/>
+      <c r="A50" s="21"/>
       <c r="B50" s="35" t="s">
         <v>28</v>
       </c>
@@ -10150,281 +11625,281 @@
         <v>29</v>
       </c>
       <c r="D50" s="4">
-        <f>D22+D27+D32+D37</f>
+        <f t="shared" ref="D50:P50" si="5">D22+D27+D32+D37</f>
         <v>58</v>
       </c>
       <c r="E50" s="4">
-        <f>E22+E27+E32+E37</f>
+        <f t="shared" si="5"/>
         <v>58</v>
       </c>
       <c r="F50" s="4" t="e">
-        <f>F22+F27+F32+F37</f>
+        <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="G50" s="4">
-        <f>G22+G27+G32+G37</f>
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="H50" s="4">
-        <f>H22+H27+H32+H37</f>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="I50" s="4">
-        <f>I22+I27+I32+I37</f>
+        <f t="shared" si="5"/>
         <v>26</v>
       </c>
       <c r="J50" s="4">
-        <f>J22+J27+J32+J37</f>
+        <f t="shared" si="5"/>
         <v>61</v>
       </c>
       <c r="K50" s="4">
-        <f>K22+K27+K32+K37</f>
-        <v>62</v>
+        <f t="shared" si="5"/>
+        <v>45</v>
       </c>
       <c r="L50" s="4">
-        <f>L22+L27+L32+L37</f>
+        <f t="shared" si="5"/>
         <v>61</v>
       </c>
       <c r="M50" s="4">
-        <f>M22+M27+M32+M37</f>
+        <f t="shared" si="5"/>
         <v>61</v>
       </c>
       <c r="N50" s="4">
-        <f>N22+N27+N32+N37</f>
+        <f t="shared" si="5"/>
         <v>61</v>
       </c>
       <c r="O50" s="4">
-        <f>O22+O27+O32+O37</f>
+        <f t="shared" si="5"/>
         <v>61</v>
       </c>
       <c r="P50" s="4">
-        <f>P22+P27+P32+P37</f>
-        <v>61</v>
+        <f t="shared" si="5"/>
+        <v>46</v>
       </c>
       <c r="Q50" s="4">
-        <f t="shared" ref="Q50:Y50" si="0">Q22+Q27+Q32+Q37</f>
+        <f t="shared" ref="Q50:Y50" si="6">Q22+Q27+Q32+Q37</f>
         <v>66</v>
       </c>
       <c r="R50" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>70</v>
       </c>
       <c r="S50" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>70</v>
       </c>
       <c r="T50" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>74</v>
       </c>
       <c r="U50" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>70</v>
       </c>
       <c r="V50" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>72</v>
       </c>
       <c r="W50" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>72</v>
       </c>
       <c r="X50" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>72</v>
       </c>
       <c r="Y50" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="20"/>
+      <c r="A51" s="21"/>
       <c r="B51" s="36"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
       <c r="D51" s="4">
-        <f>D24+D29+D34+D39+D43</f>
+        <f t="shared" ref="D51:P51" si="7">D24+D29+D34+D39+D43</f>
         <v>30</v>
       </c>
       <c r="E51" s="4">
-        <f>E24+E29+E34+E39+E43</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="F51" s="4" t="e">
-        <f>F24+F29+F34+F39+F43</f>
+        <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
       <c r="G51" s="4">
-        <f>G24+G29+G34+G39+G43</f>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
       <c r="H51" s="4">
-        <f>H24+H29+H34+H39+H43</f>
+        <f t="shared" si="7"/>
         <v>31</v>
       </c>
       <c r="I51" s="4">
-        <f>I24+I29+I34+I39+I43</f>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
       <c r="J51" s="4">
-        <f>J24+J29+J34+J39+J43</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="K51" s="4">
-        <f>K24+K29+K34+K39+K43</f>
-        <v>30</v>
+        <f t="shared" si="7"/>
+        <v>22</v>
       </c>
       <c r="L51" s="4">
-        <f>L24+L29+L34+L39+L43</f>
-        <v>28.15</v>
+        <f t="shared" si="7"/>
+        <v>35</v>
       </c>
       <c r="M51" s="4">
-        <f>M24+M29+M34+M39+M43</f>
-        <v>28.15</v>
+        <f t="shared" si="7"/>
+        <v>35</v>
       </c>
       <c r="N51" s="4">
-        <f>N24+N29+N34+N39+N43</f>
-        <v>28.15</v>
+        <f t="shared" si="7"/>
+        <v>35</v>
       </c>
       <c r="O51" s="4">
-        <f>O24+O29+O34+O39+O43</f>
-        <v>29.15</v>
+        <f t="shared" si="7"/>
+        <v>37</v>
       </c>
       <c r="P51" s="4">
-        <f>P24+P29+P34+P39+P43</f>
-        <v>29.15</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="Q51" s="4">
-        <f t="shared" ref="Q51:Y51" si="1">Q24+Q29+Q34+Q39+Q43</f>
-        <v>32.15</v>
+        <f t="shared" ref="Q51:Y51" si="8">Q24+Q29+Q34+Q39+Q43</f>
+        <v>40</v>
       </c>
       <c r="R51" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>45</v>
       </c>
       <c r="S51" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>45</v>
       </c>
       <c r="T51" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>45</v>
       </c>
       <c r="U51" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>50</v>
       </c>
       <c r="V51" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>50</v>
       </c>
       <c r="W51" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>55</v>
       </c>
       <c r="X51" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>50</v>
       </c>
       <c r="Y51" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="20"/>
+      <c r="A52" s="21"/>
       <c r="B52" s="37"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
       <c r="D52" s="4">
-        <f>D50*(1+D51*0.02)</f>
+        <f t="shared" ref="D52:P52" si="9">D50*(1+D51*0.02)</f>
         <v>92.800000000000011</v>
       </c>
       <c r="E52" s="4">
-        <f>E50*(1+E51*0.02)</f>
+        <f t="shared" si="9"/>
         <v>92.800000000000011</v>
       </c>
       <c r="F52" s="4" t="e">
-        <f>F50*(1+F51*0.02)</f>
+        <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
       <c r="G52" s="4">
-        <f>G50*(1+G51*0.02)</f>
+        <f t="shared" si="9"/>
         <v>40.5</v>
       </c>
       <c r="H52" s="4">
-        <f>H50*(1+H51*0.02)</f>
+        <f t="shared" si="9"/>
         <v>97.2</v>
       </c>
       <c r="I52" s="4">
-        <f>I50*(1+I51*0.02)</f>
+        <f t="shared" si="9"/>
         <v>39</v>
       </c>
       <c r="J52" s="4">
-        <f>J50*(1+J51*0.02)</f>
+        <f t="shared" si="9"/>
         <v>97.600000000000009</v>
       </c>
       <c r="K52" s="4">
-        <f>K50*(1+K51*0.02)</f>
-        <v>99.2</v>
+        <f t="shared" si="9"/>
+        <v>64.8</v>
       </c>
       <c r="L52" s="4">
-        <f>L50*(1+L51*0.02)</f>
-        <v>95.343000000000004</v>
+        <f t="shared" si="9"/>
+        <v>103.70000000000002</v>
       </c>
       <c r="M52" s="4">
-        <f>M50*(1+M51*0.02)</f>
-        <v>95.343000000000004</v>
+        <f t="shared" si="9"/>
+        <v>103.70000000000002</v>
       </c>
       <c r="N52" s="4">
-        <f>N50*(1+N51*0.02)</f>
-        <v>95.343000000000004</v>
+        <f t="shared" si="9"/>
+        <v>103.70000000000002</v>
       </c>
       <c r="O52" s="4">
-        <f>O50*(1+O51*0.02)</f>
-        <v>96.563000000000002</v>
+        <f t="shared" si="9"/>
+        <v>106.14</v>
       </c>
       <c r="P52" s="4">
-        <f>P50*(1+P51*0.02)</f>
-        <v>96.563000000000002</v>
+        <f t="shared" si="9"/>
+        <v>64.399999999999991</v>
       </c>
       <c r="Q52" s="4">
-        <f t="shared" ref="Q52:Y52" si="2">Q50*(1+Q51*0.02)</f>
-        <v>108.438</v>
+        <f t="shared" ref="Q52:Y52" si="10">Q50*(1+Q51*0.02)</f>
+        <v>118.8</v>
       </c>
       <c r="R52" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>133</v>
       </c>
       <c r="S52" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>133</v>
       </c>
       <c r="T52" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>140.6</v>
       </c>
       <c r="U52" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>140</v>
       </c>
       <c r="V52" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>144</v>
       </c>
       <c r="W52" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>151.20000000000002</v>
       </c>
       <c r="X52" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>144</v>
       </c>
       <c r="Y52" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>152</v>
       </c>
     </row>
@@ -10434,10 +11909,10 @@
       <c r="C53" s="8"/>
     </row>
     <row r="54" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="34" t="s">
+      <c r="A54" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="34" t="s">
+      <c r="B54" s="38" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -10445,29 +11920,29 @@
       </c>
     </row>
     <row r="55" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="21"/>
-      <c r="B55" s="21"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="21"/>
-      <c r="B56" s="21"/>
+      <c r="A56" s="22"/>
+      <c r="B56" s="22"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="21"/>
-      <c r="B57" s="22"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="23"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="21"/>
-      <c r="B58" s="34" t="s">
+      <c r="A58" s="22"/>
+      <c r="B58" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -10475,29 +11950,29 @@
       </c>
     </row>
     <row r="59" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="21"/>
-      <c r="B59" s="21"/>
+      <c r="A59" s="22"/>
+      <c r="B59" s="22"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="21"/>
-      <c r="B60" s="22"/>
+      <c r="A60" s="22"/>
+      <c r="B60" s="23"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="21"/>
+      <c r="A61" s="22"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="21"/>
-      <c r="B62" s="34" t="s">
+      <c r="A62" s="22"/>
+      <c r="B62" s="38" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -10505,22 +11980,22 @@
       </c>
     </row>
     <row r="63" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="21"/>
-      <c r="B63" s="21"/>
+      <c r="A63" s="22"/>
+      <c r="B63" s="22"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="22"/>
-      <c r="B64" s="22"/>
+      <c r="A64" s="23"/>
+      <c r="B64" s="23"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="29" t="s">
+      <c r="A66" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -10597,7 +12072,7 @@
       </c>
     </row>
     <row r="67" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="30"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -10672,7 +12147,7 @@
       </c>
     </row>
     <row r="68" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="30"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -10747,7 +12222,7 @@
       </c>
     </row>
     <row r="69" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="31"/>
+      <c r="A69" s="32"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -10823,8 +12298,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="B9:B12"/>
@@ -10840,6 +12313,8 @@
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A66:A69"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10855,53 +12330,59 @@
     <col min="1" max="3" width="16.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="2"/>
     </row>
-    <row r="4" spans="1:12" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N4" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
@@ -10929,13 +12410,19 @@
         <v>6</v>
       </c>
       <c r="K5" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L5" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M5" s="1">
+        <v>7</v>
+      </c>
+      <c r="N5" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
@@ -10951,29 +12438,35 @@
         <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="1">
         <v>2</v>
       </c>
       <c r="I6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J6" s="1">
         <v>3</v>
       </c>
       <c r="K6" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="19" t="s">
+      <c r="N6" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -10983,9 +12476,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="19"/>
-      <c r="B8" s="17"/>
+    <row r="8" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="20"/>
+      <c r="B8" s="18"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
@@ -10993,9 +12486,9 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="19"/>
-      <c r="B9" s="17"/>
+    <row r="9" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="20"/>
+      <c r="B9" s="18"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
@@ -11003,9 +12496,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="19"/>
-      <c r="B10" s="17"/>
+    <row r="10" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="20"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -11013,35 +12506,35 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
-      <c r="B11" s="17" t="s">
+    <row r="11" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="20"/>
+      <c r="B11" s="18" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="19"/>
-      <c r="B12" s="17"/>
+    <row r="12" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="20"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19"/>
-      <c r="B13" s="17"/>
+    <row r="13" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="20"/>
+      <c r="B13" s="18"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="19"/>
-    </row>
-    <row r="15" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19"/>
-      <c r="B15" s="23" t="s">
+    <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="20"/>
+    </row>
+    <row r="15" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="20"/>
+      <c r="B15" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -11051,9 +12544,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19"/>
-      <c r="B16" s="24"/>
+    <row r="16" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="20"/>
+      <c r="B16" s="25"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
@@ -11062,8 +12555,8 @@
       </c>
     </row>
     <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="19"/>
-      <c r="B17" s="24"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="25"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
@@ -11072,8 +12565,8 @@
       </c>
     </row>
     <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19"/>
-      <c r="B18" s="25"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="26"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
@@ -11088,10 +12581,10 @@
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="39" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -11099,36 +12592,36 @@
       </c>
     </row>
     <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="20"/>
-      <c r="B21" s="38"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="39"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="20"/>
-      <c r="B22" s="38"/>
+      <c r="A22" s="21"/>
+      <c r="B22" s="39"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="20"/>
-      <c r="B23" s="38"/>
+      <c r="A23" s="21"/>
+      <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="20"/>
+      <c r="A24" s="21"/>
       <c r="B24" s="12"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="20"/>
-      <c r="B25" s="38" t="s">
+      <c r="A25" s="21"/>
+      <c r="B25" s="39" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="4" t="s">
@@ -11136,35 +12629,35 @@
       </c>
     </row>
     <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="20"/>
-      <c r="B26" s="38"/>
+      <c r="A26" s="21"/>
+      <c r="B26" s="39"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="20"/>
-      <c r="B27" s="38"/>
+      <c r="A27" s="21"/>
+      <c r="B27" s="39"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="20"/>
-      <c r="B28" s="38"/>
+      <c r="A28" s="21"/>
+      <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="20"/>
+      <c r="A29" s="21"/>
       <c r="B29" s="13"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="20"/>
+      <c r="A30" s="21"/>
       <c r="B30" s="35" t="s">
         <v>17</v>
       </c>
@@ -11173,35 +12666,35 @@
       </c>
     </row>
     <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="20"/>
+      <c r="A31" s="21"/>
       <c r="B31" s="36"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="20"/>
+      <c r="A32" s="21"/>
       <c r="B32" s="36"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="20"/>
+      <c r="A33" s="21"/>
       <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="20"/>
+      <c r="A34" s="21"/>
       <c r="B34" s="14"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
     <row r="35" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="20"/>
+      <c r="A35" s="21"/>
       <c r="B35" s="35" t="s">
         <v>18</v>
       </c>
@@ -11210,35 +12703,35 @@
       </c>
     </row>
     <row r="36" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="20"/>
+      <c r="A36" s="21"/>
       <c r="B36" s="36"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="20"/>
+      <c r="A37" s="21"/>
       <c r="B37" s="36"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="20"/>
+      <c r="A38" s="21"/>
       <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="20"/>
+      <c r="A39" s="21"/>
       <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
     <row r="40" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="20"/>
+      <c r="A40" s="21"/>
       <c r="B40" s="35" t="s">
         <v>19</v>
       </c>
@@ -11247,26 +12740,26 @@
       </c>
     </row>
     <row r="41" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="20"/>
+      <c r="A41" s="21"/>
       <c r="B41" s="36"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="20"/>
+      <c r="A42" s="21"/>
       <c r="B42" s="37"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="20"/>
+      <c r="A43" s="21"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
     </row>
     <row r="44" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="20"/>
+      <c r="A44" s="21"/>
       <c r="B44" s="35" t="s">
         <v>30</v>
       </c>
@@ -11275,28 +12768,28 @@
       </c>
     </row>
     <row r="45" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="20"/>
+      <c r="A45" s="21"/>
       <c r="B45" s="36"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="20"/>
+      <c r="A46" s="21"/>
       <c r="B46" s="37"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="20"/>
+      <c r="A47" s="21"/>
       <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
     <row r="48" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="20"/>
+      <c r="A48" s="21"/>
       <c r="B48" s="35" t="s">
         <v>28</v>
       </c>
@@ -11365,7 +12858,7 @@
       </c>
     </row>
     <row r="49" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="20"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="36"/>
       <c r="C49" s="4" t="s">
         <v>129</v>
@@ -11432,7 +12925,7 @@
       </c>
     </row>
     <row r="50" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="20"/>
+      <c r="A50" s="21"/>
       <c r="B50" s="37"/>
       <c r="C50" s="4" t="s">
         <v>130</v>
@@ -11504,10 +12997,10 @@
       <c r="C51" s="8"/>
     </row>
     <row r="52" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="34" t="s">
+      <c r="A52" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="B52" s="34" t="s">
+      <c r="B52" s="38" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="5" t="s">
@@ -11515,29 +13008,29 @@
       </c>
     </row>
     <row r="53" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="21"/>
-      <c r="B53" s="21"/>
+      <c r="A53" s="22"/>
+      <c r="B53" s="22"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="21"/>
-      <c r="B54" s="21"/>
+      <c r="A54" s="22"/>
+      <c r="B54" s="22"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="21"/>
-      <c r="B55" s="22"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="23"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="21"/>
-      <c r="B56" s="34" t="s">
+      <c r="A56" s="22"/>
+      <c r="B56" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C56" s="5">
@@ -11545,29 +13038,29 @@
       </c>
     </row>
     <row r="57" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="21"/>
-      <c r="B57" s="21"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="22"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="21"/>
-      <c r="B58" s="22"/>
+      <c r="A58" s="22"/>
+      <c r="B58" s="23"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="21"/>
+      <c r="A59" s="22"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
     </row>
     <row r="60" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="21"/>
-      <c r="B60" s="34" t="s">
+      <c r="A60" s="22"/>
+      <c r="B60" s="38" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
@@ -11575,22 +13068,22 @@
       </c>
     </row>
     <row r="61" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="21"/>
-      <c r="B61" s="21"/>
+      <c r="A61" s="22"/>
+      <c r="B61" s="22"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="22"/>
-      <c r="B62" s="22"/>
+      <c r="A62" s="23"/>
+      <c r="B62" s="23"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="64" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="29" t="s">
+      <c r="A64" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -11604,7 +13097,7 @@
       </c>
     </row>
     <row r="65" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="30"/>
+      <c r="A65" s="31"/>
       <c r="B65" s="4" t="s">
         <v>132</v>
       </c>
@@ -11616,7 +13109,7 @@
       </c>
     </row>
     <row r="66" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="30"/>
+      <c r="A66" s="31"/>
       <c r="B66" s="4" t="s">
         <v>133</v>
       </c>
@@ -11628,7 +13121,7 @@
       </c>
     </row>
     <row r="67" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="31"/>
+      <c r="A67" s="32"/>
       <c r="B67" s="5" t="s">
         <v>134</v>
       </c>
@@ -11641,8 +13134,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A64:A67"/>
     <mergeCell ref="A7:A18"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B7:B10"/>
@@ -11658,6 +13149,8 @@
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="B35:B38"/>
     <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A64:A67"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dev_stuffs/3匠魂.xlsx
+++ b/dev_stuffs/3匠魂.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\Palmon\dev_stuffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48F62108-F622-429A-B187-A3C46E9369C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597351A4-5E82-43B7-B465-3823897B6F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15960" yWindow="2250" windowWidth="23940" windowHeight="15435" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6090" yWindow="2715" windowWidth="23940" windowHeight="15435" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="阶段1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="242">
   <si>
     <t>材料名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -789,6 +789,36 @@
   </si>
   <si>
     <t>'kubejs:stable_desh_ingot'</t>
+  </si>
+  <si>
+    <t>'kubejs:hallowed_soul_steel_ingot'</t>
+  </si>
+  <si>
+    <t>'aquamirae:ship_graveyard_echo'</t>
+  </si>
+  <si>
+    <t>'kubejs:gamma_framework'</t>
+  </si>
+  <si>
+    <t>'#forge:ingots/thermoconducting'</t>
+  </si>
+  <si>
+    <t>'malum:void_tablet'</t>
+  </si>
+  <si>
+    <t>'aquamirae:abyssal_amethyst'</t>
+  </si>
+  <si>
+    <t>'tinkers_advanced:activated_chromatic_steel'</t>
+  </si>
+  <si>
+    <t>'#forge:gems/boron_nitride'</t>
+  </si>
+  <si>
+    <t>'malum:malignant_pewter_ingot'</t>
+  </si>
+  <si>
+    <t>'kubejs:ember_profile'</t>
   </si>
 </sst>
 </file>
@@ -1038,6 +1068,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1063,30 +1117,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
@@ -1562,10 +1592,10 @@
       </c>
     </row>
     <row r="9" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -1603,8 +1633,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="18"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -1640,8 +1670,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="18"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -1677,8 +1707,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="18"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -1714,8 +1744,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="18" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -1723,25 +1753,25 @@
       </c>
     </row>
     <row r="14" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="18"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="18"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
+      <c r="A16" s="28"/>
     </row>
     <row r="17" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="24" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -1779,8 +1809,8 @@
       </c>
     </row>
     <row r="18" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="25"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1816,8 +1846,8 @@
       </c>
     </row>
     <row r="19" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="25"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -1853,8 +1883,8 @@
       </c>
     </row>
     <row r="20" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20"/>
-      <c r="B20" s="26"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1896,10 +1926,10 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="33" t="s">
+      <c r="A22" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="29" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -1937,8 +1967,8 @@
       </c>
     </row>
     <row r="23" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="34"/>
-      <c r="B23" s="21"/>
+      <c r="A23" s="25"/>
+      <c r="B23" s="29"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
       </c>
@@ -1984,8 +2014,8 @@
       </c>
     </row>
     <row r="24" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="34"/>
-      <c r="B24" s="21"/>
+      <c r="A24" s="25"/>
+      <c r="B24" s="29"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
       </c>
@@ -2021,22 +2051,22 @@
       </c>
     </row>
     <row r="25" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="34"/>
-      <c r="B25" s="21"/>
+      <c r="A25" s="25"/>
+      <c r="B25" s="29"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="34"/>
+      <c r="A26" s="25"/>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="34"/>
-      <c r="B27" s="21" t="s">
+      <c r="A27" s="25"/>
+      <c r="B27" s="29" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="4" t="s">
@@ -2074,8 +2104,8 @@
       </c>
     </row>
     <row r="28" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="34"/>
-      <c r="B28" s="21"/>
+      <c r="A28" s="25"/>
+      <c r="B28" s="29"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
       </c>
@@ -2121,8 +2151,8 @@
       </c>
     </row>
     <row r="29" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="34"/>
-      <c r="B29" s="21"/>
+      <c r="A29" s="25"/>
+      <c r="B29" s="29"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
       </c>
@@ -2158,22 +2188,22 @@
       </c>
     </row>
     <row r="30" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="34"/>
-      <c r="B30" s="21"/>
+      <c r="A30" s="25"/>
+      <c r="B30" s="29"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="34"/>
+      <c r="A31" s="25"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="34"/>
-      <c r="B32" s="27" t="s">
+      <c r="A32" s="25"/>
+      <c r="B32" s="21" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -2211,8 +2241,8 @@
       </c>
     </row>
     <row r="33" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="34"/>
-      <c r="B33" s="28"/>
+      <c r="A33" s="25"/>
+      <c r="B33" s="22"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -2258,8 +2288,8 @@
       </c>
     </row>
     <row r="34" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="34"/>
-      <c r="B34" s="28"/>
+      <c r="A34" s="25"/>
+      <c r="B34" s="22"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -2295,22 +2325,22 @@
       </c>
     </row>
     <row r="35" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="34"/>
-      <c r="B35" s="29"/>
+      <c r="A35" s="25"/>
+      <c r="B35" s="23"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="34"/>
+      <c r="A36" s="25"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="34"/>
-      <c r="B37" s="27" t="s">
+      <c r="A37" s="25"/>
+      <c r="B37" s="21" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -2348,8 +2378,8 @@
       </c>
     </row>
     <row r="38" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="34"/>
-      <c r="B38" s="28"/>
+      <c r="A38" s="25"/>
+      <c r="B38" s="22"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -2395,8 +2425,8 @@
       </c>
     </row>
     <row r="39" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="34"/>
-      <c r="B39" s="28"/>
+      <c r="A39" s="25"/>
+      <c r="B39" s="22"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -2432,22 +2462,22 @@
       </c>
     </row>
     <row r="40" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="34"/>
-      <c r="B40" s="29"/>
+      <c r="A40" s="25"/>
+      <c r="B40" s="23"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="34"/>
+      <c r="A41" s="25"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="34"/>
-      <c r="B42" s="27" t="s">
+      <c r="A42" s="25"/>
+      <c r="B42" s="21" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -2495,8 +2525,8 @@
       </c>
     </row>
     <row r="43" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="34"/>
-      <c r="B43" s="28"/>
+      <c r="A43" s="25"/>
+      <c r="B43" s="22"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -2532,18 +2562,18 @@
       </c>
     </row>
     <row r="44" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="34"/>
-      <c r="B44" s="29"/>
+      <c r="A44" s="25"/>
+      <c r="B44" s="23"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="34"/>
+      <c r="A45" s="25"/>
     </row>
     <row r="46" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="34"/>
-      <c r="B46" s="27" t="s">
+      <c r="A46" s="25"/>
+      <c r="B46" s="21" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -2551,29 +2581,29 @@
       </c>
     </row>
     <row r="47" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="34"/>
-      <c r="B47" s="28"/>
+      <c r="A47" s="25"/>
+      <c r="B47" s="22"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="34"/>
-      <c r="B48" s="29"/>
+      <c r="A48" s="25"/>
+      <c r="B48" s="23"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="34"/>
+      <c r="A49" s="25"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
     </row>
     <row r="50" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="34"/>
-      <c r="B50" s="27" t="s">
+      <c r="A50" s="25"/>
+      <c r="B50" s="21" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -2621,8 +2651,8 @@
       </c>
     </row>
     <row r="51" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="34"/>
-      <c r="B51" s="28"/>
+      <c r="A51" s="25"/>
+      <c r="B51" s="22"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -2668,8 +2698,8 @@
       </c>
     </row>
     <row r="52" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="34"/>
-      <c r="B52" s="29"/>
+      <c r="A52" s="25"/>
+      <c r="B52" s="23"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -2721,10 +2751,10 @@
       <c r="E53" s="8"/>
     </row>
     <row r="54" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="19" t="s">
+      <c r="A54" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="19" t="s">
+      <c r="B54" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -2732,29 +2762,29 @@
       </c>
     </row>
     <row r="55" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="19"/>
-      <c r="B55" s="19"/>
+      <c r="A55" s="27"/>
+      <c r="B55" s="27"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="19"/>
-      <c r="B56" s="19"/>
+      <c r="A56" s="27"/>
+      <c r="B56" s="27"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="19"/>
-      <c r="B57" s="19"/>
+      <c r="A57" s="27"/>
+      <c r="B57" s="27"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="19"/>
-      <c r="B58" s="19" t="s">
+      <c r="A58" s="27"/>
+      <c r="B58" s="27" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -2762,29 +2792,29 @@
       </c>
     </row>
     <row r="59" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="19"/>
-      <c r="B59" s="22"/>
+      <c r="A59" s="27"/>
+      <c r="B59" s="30"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="19"/>
-      <c r="B60" s="23"/>
+      <c r="A60" s="27"/>
+      <c r="B60" s="31"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="19"/>
+      <c r="A61" s="27"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="19"/>
-      <c r="B62" s="19" t="s">
+      <c r="A62" s="27"/>
+      <c r="B62" s="27" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -2792,21 +2822,21 @@
       </c>
     </row>
     <row r="63" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="19"/>
-      <c r="B63" s="22"/>
+      <c r="A63" s="27"/>
+      <c r="B63" s="30"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="19"/>
-      <c r="B64" s="23"/>
+      <c r="A64" s="27"/>
+      <c r="B64" s="31"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="30" t="s">
+      <c r="A67" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B67" s="6" t="s">
@@ -2847,7 +2877,7 @@
       </c>
     </row>
     <row r="68" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="31"/>
+      <c r="A68" s="19"/>
       <c r="B68" s="4" t="s">
         <v>132</v>
       </c>
@@ -2886,7 +2916,7 @@
       </c>
     </row>
     <row r="69" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="31"/>
+      <c r="A69" s="19"/>
       <c r="B69" s="4" t="s">
         <v>133</v>
       </c>
@@ -2925,7 +2955,7 @@
       </c>
     </row>
     <row r="70" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="32"/>
+      <c r="A70" s="20"/>
       <c r="B70" s="5" t="s">
         <v>134</v>
       </c>
@@ -2965,6 +2995,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B50:B52"/>
     <mergeCell ref="A67:A70"/>
     <mergeCell ref="B46:B48"/>
     <mergeCell ref="A22:A52"/>
@@ -2981,7 +3012,6 @@
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B50:B52"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3251,10 +3281,10 @@
       </c>
     </row>
     <row r="9" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -3304,8 +3334,8 @@
       </c>
     </row>
     <row r="10" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="18"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -3353,8 +3383,8 @@
       </c>
     </row>
     <row r="11" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="18"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -3402,8 +3432,8 @@
       </c>
     </row>
     <row r="12" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="18"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -3451,8 +3481,8 @@
       </c>
     </row>
     <row r="13" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="18" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -3460,25 +3490,25 @@
       </c>
     </row>
     <row r="14" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="18"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="18"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
+      <c r="A16" s="28"/>
     </row>
     <row r="17" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="24" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -3528,8 +3558,8 @@
       </c>
     </row>
     <row r="18" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="25"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -3577,8 +3607,8 @@
       </c>
     </row>
     <row r="19" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="25"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -3626,8 +3656,8 @@
       </c>
     </row>
     <row r="20" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20"/>
-      <c r="B20" s="26"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -3681,7 +3711,7 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="29" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="36" t="s">
@@ -3734,7 +3764,7 @@
       </c>
     </row>
     <row r="23" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="36"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -3797,7 +3827,7 @@
       </c>
     </row>
     <row r="24" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="36"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -3846,7 +3876,7 @@
       </c>
     </row>
     <row r="25" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="36"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -3877,14 +3907,14 @@
       </c>
     </row>
     <row r="26" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
+      <c r="A27" s="29"/>
       <c r="B27" s="36" t="s">
         <v>16</v>
       </c>
@@ -3935,7 +3965,7 @@
       </c>
     </row>
     <row r="28" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="36"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -3998,7 +4028,7 @@
       </c>
     </row>
     <row r="29" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="36"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -4047,7 +4077,7 @@
       </c>
     </row>
     <row r="30" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="36"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -4078,14 +4108,14 @@
       </c>
     </row>
     <row r="31" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
+      <c r="A32" s="29"/>
       <c r="B32" s="37" t="s">
         <v>17</v>
       </c>
@@ -4136,7 +4166,7 @@
       </c>
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
+      <c r="A33" s="29"/>
       <c r="B33" s="38"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
@@ -4199,7 +4229,7 @@
       </c>
     </row>
     <row r="34" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
+      <c r="A34" s="29"/>
       <c r="B34" s="38"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
@@ -4248,7 +4278,7 @@
       </c>
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
+      <c r="A35" s="29"/>
       <c r="B35" s="39"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
@@ -4279,14 +4309,14 @@
       </c>
     </row>
     <row r="36" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
+      <c r="A37" s="29"/>
       <c r="B37" s="37" t="s">
         <v>18</v>
       </c>
@@ -4337,7 +4367,7 @@
       </c>
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
+      <c r="A38" s="29"/>
       <c r="B38" s="38"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
@@ -4400,7 +4430,7 @@
       </c>
     </row>
     <row r="39" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
+      <c r="A39" s="29"/>
       <c r="B39" s="38"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
@@ -4449,7 +4479,7 @@
       </c>
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
+      <c r="A40" s="29"/>
       <c r="B40" s="39"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
@@ -4480,14 +4510,14 @@
       </c>
     </row>
     <row r="41" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
+      <c r="A41" s="29"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
+      <c r="A42" s="29"/>
       <c r="B42" s="37" t="s">
         <v>19</v>
       </c>
@@ -4552,7 +4582,7 @@
       </c>
     </row>
     <row r="43" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="21"/>
+      <c r="A43" s="29"/>
       <c r="B43" s="38"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
@@ -4601,7 +4631,7 @@
       </c>
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="21"/>
+      <c r="A44" s="29"/>
       <c r="B44" s="39"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
@@ -4632,12 +4662,12 @@
       </c>
     </row>
     <row r="45" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="21"/>
+      <c r="A45" s="29"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="21"/>
+      <c r="A46" s="29"/>
       <c r="B46" s="37" t="s">
         <v>30</v>
       </c>
@@ -4646,28 +4676,28 @@
       </c>
     </row>
     <row r="47" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="21"/>
+      <c r="A47" s="29"/>
       <c r="B47" s="38"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="21"/>
+      <c r="A48" s="29"/>
       <c r="B48" s="39"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="21"/>
+      <c r="A49" s="29"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="21"/>
+      <c r="A50" s="29"/>
       <c r="B50" s="37" t="s">
         <v>28</v>
       </c>
@@ -4732,7 +4762,7 @@
       </c>
     </row>
     <row r="51" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="21"/>
+      <c r="A51" s="29"/>
       <c r="B51" s="38"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
@@ -4795,7 +4825,7 @@
       </c>
     </row>
     <row r="52" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="21"/>
+      <c r="A52" s="29"/>
       <c r="B52" s="39"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
@@ -4874,28 +4904,28 @@
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="22"/>
-      <c r="B55" s="22"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="22"/>
-      <c r="B56" s="22"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="30"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="22"/>
-      <c r="B57" s="23"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="31"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="22"/>
+      <c r="A58" s="30"/>
       <c r="B58" s="35" t="s">
         <v>30</v>
       </c>
@@ -4904,28 +4934,28 @@
       </c>
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="22"/>
-      <c r="B59" s="22"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="22"/>
-      <c r="B60" s="23"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="31"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="22"/>
+      <c r="A61" s="30"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="22"/>
+      <c r="A62" s="30"/>
       <c r="B62" s="35" t="s">
         <v>25</v>
       </c>
@@ -4934,22 +4964,22 @@
       </c>
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="22"/>
-      <c r="B63" s="22"/>
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="23"/>
-      <c r="B64" s="23"/>
+      <c r="A64" s="31"/>
+      <c r="B64" s="31"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -5002,7 +5032,7 @@
       </c>
     </row>
     <row r="67" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="31"/>
+      <c r="A67" s="19"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -5047,7 +5077,7 @@
       </c>
     </row>
     <row r="68" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="31"/>
+      <c r="A68" s="19"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -5092,7 +5122,7 @@
       </c>
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="32"/>
+      <c r="A69" s="20"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -5102,6 +5132,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B50:B52"/>
     <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="B62:B64"/>
@@ -5118,7 +5149,6 @@
     <mergeCell ref="A54:A64"/>
     <mergeCell ref="B54:B57"/>
     <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B50:B52"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5297,6 +5327,36 @@
       <c r="U5" s="11" t="s">
         <v>231</v>
       </c>
+      <c r="V5" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="W5" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="X5" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="Y5" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="Z5" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="AA5" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="AB5" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="AC5" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="AD5" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AE5" s="11" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="6" spans="1:31" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
@@ -5572,10 +5632,10 @@
       </c>
     </row>
     <row r="9" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -5667,8 +5727,8 @@
       </c>
     </row>
     <row r="10" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="18"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -5758,8 +5818,8 @@
       </c>
     </row>
     <row r="11" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="18"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -5849,8 +5909,8 @@
       </c>
     </row>
     <row r="12" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="18"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -5940,8 +6000,8 @@
       </c>
     </row>
     <row r="13" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="18" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -5949,25 +6009,25 @@
       </c>
     </row>
     <row r="14" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="18"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="18"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
+      <c r="A16" s="28"/>
     </row>
     <row r="17" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="24" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -6059,8 +6119,8 @@
       </c>
     </row>
     <row r="18" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="25"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -6150,8 +6210,8 @@
       </c>
     </row>
     <row r="19" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="25"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -6241,8 +6301,8 @@
       </c>
     </row>
     <row r="20" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20"/>
-      <c r="B20" s="26"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -6341,7 +6401,7 @@
       </c>
     </row>
     <row r="22" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="29" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="36" t="s">
@@ -6436,7 +6496,7 @@
       </c>
     </row>
     <row r="23" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="36"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -6555,7 +6615,7 @@
       </c>
     </row>
     <row r="24" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="36"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -6646,7 +6706,7 @@
       </c>
     </row>
     <row r="25" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="36"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -6737,14 +6797,14 @@
       </c>
     </row>
     <row r="26" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
+      <c r="A27" s="29"/>
       <c r="B27" s="36" t="s">
         <v>16</v>
       </c>
@@ -6837,7 +6897,7 @@
       </c>
     </row>
     <row r="28" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="36"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -6956,7 +7016,7 @@
       </c>
     </row>
     <row r="29" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="36"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -7047,7 +7107,7 @@
       </c>
     </row>
     <row r="30" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="36"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -7138,14 +7198,14 @@
       </c>
     </row>
     <row r="31" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
+      <c r="A32" s="29"/>
       <c r="B32" s="37" t="s">
         <v>17</v>
       </c>
@@ -7238,7 +7298,7 @@
       </c>
     </row>
     <row r="33" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
+      <c r="A33" s="29"/>
       <c r="B33" s="38"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
@@ -7357,7 +7417,7 @@
       </c>
     </row>
     <row r="34" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
+      <c r="A34" s="29"/>
       <c r="B34" s="38"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
@@ -7448,7 +7508,7 @@
       </c>
     </row>
     <row r="35" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
+      <c r="A35" s="29"/>
       <c r="B35" s="39"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
@@ -7539,14 +7599,14 @@
       </c>
     </row>
     <row r="36" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
+      <c r="A37" s="29"/>
       <c r="B37" s="37" t="s">
         <v>18</v>
       </c>
@@ -7639,7 +7699,7 @@
       </c>
     </row>
     <row r="38" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
+      <c r="A38" s="29"/>
       <c r="B38" s="38"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
@@ -7758,7 +7818,7 @@
       </c>
     </row>
     <row r="39" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
+      <c r="A39" s="29"/>
       <c r="B39" s="38"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
@@ -7849,7 +7909,7 @@
       </c>
     </row>
     <row r="40" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
+      <c r="A40" s="29"/>
       <c r="B40" s="39"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
@@ -7940,14 +8000,14 @@
       </c>
     </row>
     <row r="41" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
+      <c r="A41" s="29"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
+      <c r="A42" s="29"/>
       <c r="B42" s="37" t="s">
         <v>19</v>
       </c>
@@ -7956,7 +8016,7 @@
       </c>
     </row>
     <row r="43" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="21"/>
+      <c r="A43" s="29"/>
       <c r="B43" s="38"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
@@ -8047,7 +8107,7 @@
       </c>
     </row>
     <row r="44" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="21"/>
+      <c r="A44" s="29"/>
       <c r="B44" s="39"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
@@ -8138,12 +8198,12 @@
       </c>
     </row>
     <row r="45" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="21"/>
+      <c r="A45" s="29"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
     </row>
     <row r="46" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="21"/>
+      <c r="A46" s="29"/>
       <c r="B46" s="37" t="s">
         <v>30</v>
       </c>
@@ -8152,28 +8212,28 @@
       </c>
     </row>
     <row r="47" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="21"/>
+      <c r="A47" s="29"/>
       <c r="B47" s="38"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="21"/>
+      <c r="A48" s="29"/>
       <c r="B48" s="39"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="21"/>
+      <c r="A49" s="29"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="21"/>
+      <c r="A50" s="29"/>
       <c r="B50" s="37" t="s">
         <v>28</v>
       </c>
@@ -8294,7 +8354,7 @@
       </c>
     </row>
     <row r="51" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="21"/>
+      <c r="A51" s="29"/>
       <c r="B51" s="38"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
@@ -8413,7 +8473,7 @@
       </c>
     </row>
     <row r="52" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="21"/>
+      <c r="A52" s="29"/>
       <c r="B52" s="39"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
@@ -8548,28 +8608,28 @@
       </c>
     </row>
     <row r="55" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="22"/>
-      <c r="B55" s="22"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="22"/>
-      <c r="B56" s="22"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="30"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="22"/>
-      <c r="B57" s="23"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="31"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="22"/>
+      <c r="A58" s="30"/>
       <c r="B58" s="35" t="s">
         <v>30</v>
       </c>
@@ -8578,28 +8638,28 @@
       </c>
     </row>
     <row r="59" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="22"/>
-      <c r="B59" s="22"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="22"/>
-      <c r="B60" s="23"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="31"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="22"/>
+      <c r="A61" s="30"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="22"/>
+      <c r="A62" s="30"/>
       <c r="B62" s="35" t="s">
         <v>25</v>
       </c>
@@ -8608,22 +8668,22 @@
       </c>
     </row>
     <row r="63" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="22"/>
-      <c r="B63" s="22"/>
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="23"/>
-      <c r="B64" s="23"/>
+      <c r="A64" s="31"/>
+      <c r="B64" s="31"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:31" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -8718,7 +8778,7 @@
       </c>
     </row>
     <row r="67" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="31"/>
+      <c r="A67" s="19"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -8811,7 +8871,7 @@
       </c>
     </row>
     <row r="68" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="31"/>
+      <c r="A68" s="19"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -8904,7 +8964,7 @@
       </c>
     </row>
     <row r="69" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="32"/>
+      <c r="A69" s="20"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -8998,6 +9058,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="B50:B52"/>
@@ -9014,7 +9075,6 @@
     <mergeCell ref="A54:A64"/>
     <mergeCell ref="B54:B57"/>
     <mergeCell ref="B62:B64"/>
-    <mergeCell ref="B32:B35"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9257,10 +9317,10 @@
       </c>
     </row>
     <row r="9" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -9304,8 +9364,8 @@
       </c>
     </row>
     <row r="10" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="18"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -9347,8 +9407,8 @@
       </c>
     </row>
     <row r="11" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="18"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -9390,8 +9450,8 @@
       </c>
     </row>
     <row r="12" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="18"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -9433,8 +9493,8 @@
       </c>
     </row>
     <row r="13" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="18" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -9442,25 +9502,25 @@
       </c>
     </row>
     <row r="14" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="18"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="18"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
+      <c r="A16" s="28"/>
     </row>
     <row r="17" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="24" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -9504,8 +9564,8 @@
       </c>
     </row>
     <row r="18" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="25"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -9547,8 +9607,8 @@
       </c>
     </row>
     <row r="19" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="25"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -9590,8 +9650,8 @@
       </c>
     </row>
     <row r="20" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20"/>
-      <c r="B20" s="26"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -9639,7 +9699,7 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="29" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="36" t="s">
@@ -9686,7 +9746,7 @@
       </c>
     </row>
     <row r="23" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="36"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -9741,7 +9801,7 @@
       </c>
     </row>
     <row r="24" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="36"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -9784,7 +9844,7 @@
       </c>
     </row>
     <row r="25" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="36"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -9827,14 +9887,14 @@
       </c>
     </row>
     <row r="26" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
+      <c r="A27" s="29"/>
       <c r="B27" s="36" t="s">
         <v>16</v>
       </c>
@@ -9879,7 +9939,7 @@
       </c>
     </row>
     <row r="28" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="36"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -9934,7 +9994,7 @@
       </c>
     </row>
     <row r="29" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="36"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -9977,7 +10037,7 @@
       </c>
     </row>
     <row r="30" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="36"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -10020,14 +10080,14 @@
       </c>
     </row>
     <row r="31" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
+      <c r="A32" s="29"/>
       <c r="B32" s="37" t="s">
         <v>17</v>
       </c>
@@ -10072,7 +10132,7 @@
       </c>
     </row>
     <row r="33" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
+      <c r="A33" s="29"/>
       <c r="B33" s="38"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
@@ -10127,7 +10187,7 @@
       </c>
     </row>
     <row r="34" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
+      <c r="A34" s="29"/>
       <c r="B34" s="38"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
@@ -10170,7 +10230,7 @@
       </c>
     </row>
     <row r="35" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
+      <c r="A35" s="29"/>
       <c r="B35" s="39"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
@@ -10213,14 +10273,14 @@
       </c>
     </row>
     <row r="36" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
+      <c r="A37" s="29"/>
       <c r="B37" s="37" t="s">
         <v>18</v>
       </c>
@@ -10265,7 +10325,7 @@
       </c>
     </row>
     <row r="38" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
+      <c r="A38" s="29"/>
       <c r="B38" s="38"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
@@ -10320,7 +10380,7 @@
       </c>
     </row>
     <row r="39" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
+      <c r="A39" s="29"/>
       <c r="B39" s="38"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
@@ -10363,7 +10423,7 @@
       </c>
     </row>
     <row r="40" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
+      <c r="A40" s="29"/>
       <c r="B40" s="39"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
@@ -10406,14 +10466,14 @@
       </c>
     </row>
     <row r="41" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
+      <c r="A41" s="29"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
+      <c r="A42" s="29"/>
       <c r="B42" s="37" t="s">
         <v>19</v>
       </c>
@@ -10470,7 +10530,7 @@
       </c>
     </row>
     <row r="43" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="21"/>
+      <c r="A43" s="29"/>
       <c r="B43" s="38"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
@@ -10513,7 +10573,7 @@
       </c>
     </row>
     <row r="44" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="21"/>
+      <c r="A44" s="29"/>
       <c r="B44" s="39"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
@@ -10556,13 +10616,13 @@
       </c>
     </row>
     <row r="45" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="21"/>
+      <c r="A45" s="29"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
       <c r="F45" s="17"/>
     </row>
     <row r="46" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="21"/>
+      <c r="A46" s="29"/>
       <c r="B46" s="37" t="s">
         <v>30</v>
       </c>
@@ -10571,28 +10631,28 @@
       </c>
     </row>
     <row r="47" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="21"/>
+      <c r="A47" s="29"/>
       <c r="B47" s="38"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="21"/>
+      <c r="A48" s="29"/>
       <c r="B48" s="39"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="21"/>
+      <c r="A49" s="29"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="21"/>
+      <c r="A50" s="29"/>
       <c r="B50" s="37" t="s">
         <v>28</v>
       </c>
@@ -10649,7 +10709,7 @@
       </c>
     </row>
     <row r="51" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="21"/>
+      <c r="A51" s="29"/>
       <c r="B51" s="38"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
@@ -10704,7 +10764,7 @@
       </c>
     </row>
     <row r="52" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="21"/>
+      <c r="A52" s="29"/>
       <c r="B52" s="39"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
@@ -10778,8 +10838,8 @@
       </c>
     </row>
     <row r="55" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="22"/>
-      <c r="B55" s="22"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
@@ -10788,8 +10848,8 @@
       </c>
     </row>
     <row r="56" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="22"/>
-      <c r="B56" s="22"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="30"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
@@ -10798,8 +10858,8 @@
       </c>
     </row>
     <row r="57" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="22"/>
-      <c r="B57" s="23"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="31"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
@@ -10808,7 +10868,7 @@
       </c>
     </row>
     <row r="58" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="22"/>
+      <c r="A58" s="30"/>
       <c r="B58" s="35" t="s">
         <v>30</v>
       </c>
@@ -10817,28 +10877,28 @@
       </c>
     </row>
     <row r="59" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="22"/>
-      <c r="B59" s="22"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="22"/>
-      <c r="B60" s="23"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="31"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="22"/>
+      <c r="A61" s="30"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="22"/>
+      <c r="A62" s="30"/>
       <c r="B62" s="35" t="s">
         <v>25</v>
       </c>
@@ -10850,8 +10910,8 @@
       </c>
     </row>
     <row r="63" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="22"/>
-      <c r="B63" s="22"/>
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
@@ -10860,8 +10920,8 @@
       </c>
     </row>
     <row r="64" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="23"/>
-      <c r="B64" s="23"/>
+      <c r="A64" s="31"/>
+      <c r="B64" s="31"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
@@ -10871,7 +10931,7 @@
     </row>
     <row r="65" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -10918,7 +10978,7 @@
       </c>
     </row>
     <row r="67" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="31"/>
+      <c r="A67" s="19"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -10963,7 +11023,7 @@
       </c>
     </row>
     <row r="68" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="31"/>
+      <c r="A68" s="19"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -11008,7 +11068,7 @@
       </c>
     </row>
     <row r="69" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="32"/>
+      <c r="A69" s="20"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -11054,6 +11114,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="B50:B52"/>
@@ -11070,7 +11131,6 @@
     <mergeCell ref="A54:A64"/>
     <mergeCell ref="B54:B57"/>
     <mergeCell ref="B62:B64"/>
-    <mergeCell ref="B32:B35"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11509,10 +11569,10 @@
       <c r="AA8" s="1"/>
     </row>
     <row r="9" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -11586,8 +11646,8 @@
       </c>
     </row>
     <row r="10" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="18"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -11659,8 +11719,8 @@
       </c>
     </row>
     <row r="11" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="18"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -11732,8 +11792,8 @@
       </c>
     </row>
     <row r="12" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="18"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -11805,8 +11865,8 @@
       </c>
     </row>
     <row r="13" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="18" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -11814,25 +11874,25 @@
       </c>
     </row>
     <row r="14" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="18"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="18"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:27" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
+      <c r="A16" s="28"/>
     </row>
     <row r="17" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="24" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -11906,8 +11966,8 @@
       </c>
     </row>
     <row r="18" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="25"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -11979,8 +12039,8 @@
       </c>
     </row>
     <row r="19" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="25"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -12052,8 +12112,8 @@
       </c>
     </row>
     <row r="20" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20"/>
-      <c r="B20" s="26"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -12131,7 +12191,7 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="29" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="36" t="s">
@@ -12208,7 +12268,7 @@
       </c>
     </row>
     <row r="23" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="36"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -12303,7 +12363,7 @@
       </c>
     </row>
     <row r="24" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="36"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -12376,7 +12436,7 @@
       </c>
     </row>
     <row r="25" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="36"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -12449,14 +12509,14 @@
       </c>
     </row>
     <row r="26" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
+      <c r="A27" s="29"/>
       <c r="B27" s="36" t="s">
         <v>16</v>
       </c>
@@ -12531,7 +12591,7 @@
       </c>
     </row>
     <row r="28" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="36"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -12626,7 +12686,7 @@
       </c>
     </row>
     <row r="29" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="36"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -12699,7 +12759,7 @@
       </c>
     </row>
     <row r="30" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="36"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -12772,14 +12832,14 @@
       </c>
     </row>
     <row r="31" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
+      <c r="A32" s="29"/>
       <c r="B32" s="37" t="s">
         <v>17</v>
       </c>
@@ -12854,7 +12914,7 @@
       </c>
     </row>
     <row r="33" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
+      <c r="A33" s="29"/>
       <c r="B33" s="38"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
@@ -12949,7 +13009,7 @@
       </c>
     </row>
     <row r="34" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
+      <c r="A34" s="29"/>
       <c r="B34" s="38"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
@@ -13022,7 +13082,7 @@
       </c>
     </row>
     <row r="35" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
+      <c r="A35" s="29"/>
       <c r="B35" s="39"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
@@ -13095,14 +13155,14 @@
       </c>
     </row>
     <row r="36" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
+      <c r="A37" s="29"/>
       <c r="B37" s="37" t="s">
         <v>18</v>
       </c>
@@ -13177,7 +13237,7 @@
       </c>
     </row>
     <row r="38" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
+      <c r="A38" s="29"/>
       <c r="B38" s="38"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
@@ -13272,7 +13332,7 @@
       </c>
     </row>
     <row r="39" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
+      <c r="A39" s="29"/>
       <c r="B39" s="38"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
@@ -13345,7 +13405,7 @@
       </c>
     </row>
     <row r="40" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
+      <c r="A40" s="29"/>
       <c r="B40" s="39"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
@@ -13418,14 +13478,14 @@
       </c>
     </row>
     <row r="41" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
+      <c r="A41" s="29"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
+      <c r="A42" s="29"/>
       <c r="B42" s="37" t="s">
         <v>19</v>
       </c>
@@ -13522,7 +13582,7 @@
       </c>
     </row>
     <row r="43" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="21"/>
+      <c r="A43" s="29"/>
       <c r="B43" s="38"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
@@ -13595,7 +13655,7 @@
       </c>
     </row>
     <row r="44" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="21"/>
+      <c r="A44" s="29"/>
       <c r="B44" s="39"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
@@ -13668,12 +13728,12 @@
       </c>
     </row>
     <row r="45" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="21"/>
+      <c r="A45" s="29"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
     </row>
     <row r="46" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="21"/>
+      <c r="A46" s="29"/>
       <c r="B46" s="37" t="s">
         <v>30</v>
       </c>
@@ -13682,28 +13742,28 @@
       </c>
     </row>
     <row r="47" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="21"/>
+      <c r="A47" s="29"/>
       <c r="B47" s="38"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="21"/>
+      <c r="A48" s="29"/>
       <c r="B48" s="39"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="21"/>
+      <c r="A49" s="29"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="21"/>
+      <c r="A50" s="29"/>
       <c r="B50" s="37" t="s">
         <v>28</v>
       </c>
@@ -13800,7 +13860,7 @@
       </c>
     </row>
     <row r="51" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="21"/>
+      <c r="A51" s="29"/>
       <c r="B51" s="38"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
@@ -13895,7 +13955,7 @@
       </c>
     </row>
     <row r="52" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="21"/>
+      <c r="A52" s="29"/>
       <c r="B52" s="39"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
@@ -14006,28 +14066,28 @@
       </c>
     </row>
     <row r="55" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="22"/>
-      <c r="B55" s="22"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="22"/>
-      <c r="B56" s="22"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="30"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="22"/>
-      <c r="B57" s="23"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="31"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="22"/>
+      <c r="A58" s="30"/>
       <c r="B58" s="35" t="s">
         <v>30</v>
       </c>
@@ -14036,28 +14096,28 @@
       </c>
     </row>
     <row r="59" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="22"/>
-      <c r="B59" s="22"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="22"/>
-      <c r="B60" s="23"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="31"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="22"/>
+      <c r="A61" s="30"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="22"/>
+      <c r="A62" s="30"/>
       <c r="B62" s="35" t="s">
         <v>25</v>
       </c>
@@ -14066,22 +14126,22 @@
       </c>
     </row>
     <row r="63" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="22"/>
-      <c r="B63" s="22"/>
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="23"/>
-      <c r="B64" s="23"/>
+      <c r="A64" s="31"/>
+      <c r="B64" s="31"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -14158,7 +14218,7 @@
       </c>
     </row>
     <row r="67" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="31"/>
+      <c r="A67" s="19"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -14233,7 +14293,7 @@
       </c>
     </row>
     <row r="68" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="31"/>
+      <c r="A68" s="19"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -14308,7 +14368,7 @@
       </c>
     </row>
     <row r="69" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="32"/>
+      <c r="A69" s="20"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -14384,6 +14444,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="B50:B52"/>
@@ -14400,7 +14461,6 @@
     <mergeCell ref="A54:A64"/>
     <mergeCell ref="B54:B57"/>
     <mergeCell ref="B62:B64"/>
-    <mergeCell ref="B32:B35"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14549,10 +14609,10 @@
       </c>
     </row>
     <row r="7" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -14563,8 +14623,8 @@
       </c>
     </row>
     <row r="8" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="20"/>
-      <c r="B8" s="18"/>
+      <c r="A8" s="28"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
@@ -14573,8 +14633,8 @@
       </c>
     </row>
     <row r="9" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20"/>
-      <c r="B9" s="18"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="26"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
@@ -14583,8 +14643,8 @@
       </c>
     </row>
     <row r="10" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="18"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -14593,8 +14653,8 @@
       </c>
     </row>
     <row r="11" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="18" t="s">
+      <c r="A11" s="28"/>
+      <c r="B11" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
@@ -14602,25 +14662,25 @@
       </c>
     </row>
     <row r="12" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="18"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="18"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="26"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
+      <c r="A14" s="28"/>
     </row>
     <row r="15" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="24" t="s">
+      <c r="A15" s="28"/>
+      <c r="B15" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -14631,8 +14691,8 @@
       </c>
     </row>
     <row r="16" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
-      <c r="B16" s="25"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="33"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
@@ -14641,8 +14701,8 @@
       </c>
     </row>
     <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="25"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="33"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
@@ -14651,8 +14711,8 @@
       </c>
     </row>
     <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="26"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="34"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
@@ -14667,7 +14727,7 @@
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="29" t="s">
         <v>131</v>
       </c>
       <c r="B20" s="36" t="s">
@@ -14678,35 +14738,35 @@
       </c>
     </row>
     <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="21"/>
+      <c r="A21" s="29"/>
       <c r="B21" s="36"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="21"/>
+      <c r="A22" s="29"/>
       <c r="B22" s="36"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="36"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="12"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="36" t="s">
         <v>16</v>
       </c>
@@ -14715,35 +14775,35 @@
       </c>
     </row>
     <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="36"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
+      <c r="A27" s="29"/>
       <c r="B27" s="36"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="36"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="13"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="37" t="s">
         <v>17</v>
       </c>
@@ -14752,35 +14812,35 @@
       </c>
     </row>
     <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="38"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
+      <c r="A32" s="29"/>
       <c r="B32" s="38"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
+      <c r="A33" s="29"/>
       <c r="B33" s="39"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
+      <c r="A34" s="29"/>
       <c r="B34" s="14"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
     <row r="35" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
+      <c r="A35" s="29"/>
       <c r="B35" s="37" t="s">
         <v>18</v>
       </c>
@@ -14789,35 +14849,35 @@
       </c>
     </row>
     <row r="36" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="38"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
+      <c r="A37" s="29"/>
       <c r="B37" s="38"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
+      <c r="A38" s="29"/>
       <c r="B38" s="39"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
+      <c r="A39" s="29"/>
       <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
     <row r="40" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
+      <c r="A40" s="29"/>
       <c r="B40" s="37" t="s">
         <v>19</v>
       </c>
@@ -14826,26 +14886,26 @@
       </c>
     </row>
     <row r="41" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
+      <c r="A41" s="29"/>
       <c r="B41" s="38"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
+      <c r="A42" s="29"/>
       <c r="B42" s="39"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="21"/>
+      <c r="A43" s="29"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
     </row>
     <row r="44" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="21"/>
+      <c r="A44" s="29"/>
       <c r="B44" s="37" t="s">
         <v>30</v>
       </c>
@@ -14854,28 +14914,28 @@
       </c>
     </row>
     <row r="45" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="21"/>
+      <c r="A45" s="29"/>
       <c r="B45" s="38"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="21"/>
+      <c r="A46" s="29"/>
       <c r="B46" s="39"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="21"/>
+      <c r="A47" s="29"/>
       <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
     <row r="48" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="21"/>
+      <c r="A48" s="29"/>
       <c r="B48" s="37" t="s">
         <v>28</v>
       </c>
@@ -14944,7 +15004,7 @@
       </c>
     </row>
     <row r="49" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="21"/>
+      <c r="A49" s="29"/>
       <c r="B49" s="38"/>
       <c r="C49" s="4" t="s">
         <v>129</v>
@@ -15011,7 +15071,7 @@
       </c>
     </row>
     <row r="50" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="21"/>
+      <c r="A50" s="29"/>
       <c r="B50" s="39"/>
       <c r="C50" s="4" t="s">
         <v>130</v>
@@ -15094,28 +15154,28 @@
       </c>
     </row>
     <row r="53" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="22"/>
-      <c r="B53" s="22"/>
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="22"/>
-      <c r="B54" s="22"/>
+      <c r="A54" s="30"/>
+      <c r="B54" s="30"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="22"/>
-      <c r="B55" s="23"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="31"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="22"/>
+      <c r="A56" s="30"/>
       <c r="B56" s="35" t="s">
         <v>30</v>
       </c>
@@ -15124,28 +15184,28 @@
       </c>
     </row>
     <row r="57" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="22"/>
-      <c r="B57" s="22"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="30"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="22"/>
-      <c r="B58" s="23"/>
+      <c r="A58" s="30"/>
+      <c r="B58" s="31"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="22"/>
+      <c r="A59" s="30"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
     </row>
     <row r="60" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="22"/>
+      <c r="A60" s="30"/>
       <c r="B60" s="35" t="s">
         <v>25</v>
       </c>
@@ -15154,22 +15214,22 @@
       </c>
     </row>
     <row r="61" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="22"/>
-      <c r="B61" s="22"/>
+      <c r="A61" s="30"/>
+      <c r="B61" s="30"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="23"/>
-      <c r="B62" s="23"/>
+      <c r="A62" s="31"/>
+      <c r="B62" s="31"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="64" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="30" t="s">
+      <c r="A64" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -15183,7 +15243,7 @@
       </c>
     </row>
     <row r="65" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="31"/>
+      <c r="A65" s="19"/>
       <c r="B65" s="4" t="s">
         <v>132</v>
       </c>
@@ -15195,7 +15255,7 @@
       </c>
     </row>
     <row r="66" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="31"/>
+      <c r="A66" s="19"/>
       <c r="B66" s="4" t="s">
         <v>133</v>
       </c>
@@ -15207,7 +15267,7 @@
       </c>
     </row>
     <row r="67" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="32"/>
+      <c r="A67" s="20"/>
       <c r="B67" s="5" t="s">
         <v>134</v>
       </c>
@@ -15220,6 +15280,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B30:B33"/>
     <mergeCell ref="B35:B38"/>
     <mergeCell ref="B40:B42"/>
     <mergeCell ref="B48:B50"/>
@@ -15236,7 +15297,6 @@
     <mergeCell ref="A52:A62"/>
     <mergeCell ref="B52:B55"/>
     <mergeCell ref="B60:B62"/>
-    <mergeCell ref="B30:B33"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15409,10 +15469,10 @@
       <c r="AF6" s="1"/>
     </row>
     <row r="7" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -15420,29 +15480,29 @@
       </c>
     </row>
     <row r="8" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="20"/>
-      <c r="B8" s="18"/>
+      <c r="A8" s="28"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20"/>
-      <c r="B9" s="18"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="26"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="18"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="18" t="s">
+      <c r="A11" s="28"/>
+      <c r="B11" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
@@ -15450,25 +15510,25 @@
       </c>
     </row>
     <row r="12" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="18"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="18"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="26"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:32" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
+      <c r="A14" s="28"/>
     </row>
     <row r="15" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="24" t="s">
+      <c r="A15" s="28"/>
+      <c r="B15" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -15476,22 +15536,22 @@
       </c>
     </row>
     <row r="16" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
-      <c r="B16" s="25"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="33"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="25"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="33"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="26"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="34"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
@@ -15503,7 +15563,7 @@
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="29" t="s">
         <v>131</v>
       </c>
       <c r="B20" s="36" t="s">
@@ -15514,35 +15574,35 @@
       </c>
     </row>
     <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="21"/>
+      <c r="A21" s="29"/>
       <c r="B21" s="36"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="21"/>
+      <c r="A22" s="29"/>
       <c r="B22" s="36"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="36"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="12"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="36" t="s">
         <v>16</v>
       </c>
@@ -15551,35 +15611,35 @@
       </c>
     </row>
     <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="36"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
+      <c r="A27" s="29"/>
       <c r="B27" s="36"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="36"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="13"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="37" t="s">
         <v>17</v>
       </c>
@@ -15588,35 +15648,35 @@
       </c>
     </row>
     <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="38"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
+      <c r="A32" s="29"/>
       <c r="B32" s="38"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
+      <c r="A33" s="29"/>
       <c r="B33" s="39"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
+      <c r="A34" s="29"/>
       <c r="B34" s="14"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
+      <c r="A35" s="29"/>
       <c r="B35" s="37" t="s">
         <v>18</v>
       </c>
@@ -15625,35 +15685,35 @@
       </c>
     </row>
     <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="38"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
+      <c r="A37" s="29"/>
       <c r="B37" s="38"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
+      <c r="A38" s="29"/>
       <c r="B38" s="39"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
+      <c r="A39" s="29"/>
       <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
+      <c r="A40" s="29"/>
       <c r="B40" s="37" t="s">
         <v>19</v>
       </c>
@@ -15662,26 +15722,26 @@
       </c>
     </row>
     <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
+      <c r="A41" s="29"/>
       <c r="B41" s="38"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
+      <c r="A42" s="29"/>
       <c r="B42" s="39"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="21"/>
+      <c r="A43" s="29"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="21"/>
+      <c r="A44" s="29"/>
       <c r="B44" s="37" t="s">
         <v>30</v>
       </c>
@@ -15690,28 +15750,28 @@
       </c>
     </row>
     <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="21"/>
+      <c r="A45" s="29"/>
       <c r="B45" s="38"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="21"/>
+      <c r="A46" s="29"/>
       <c r="B46" s="39"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="21"/>
+      <c r="A47" s="29"/>
       <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="21"/>
+      <c r="A48" s="29"/>
       <c r="B48" s="37" t="s">
         <v>28</v>
       </c>
@@ -15776,7 +15836,7 @@
       </c>
     </row>
     <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="21"/>
+      <c r="A49" s="29"/>
       <c r="B49" s="38"/>
       <c r="C49" s="4" t="s">
         <v>129</v>
@@ -15839,7 +15899,7 @@
       </c>
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="21"/>
+      <c r="A50" s="29"/>
       <c r="B50" s="39"/>
       <c r="C50" s="4" t="s">
         <v>130</v>
@@ -15918,28 +15978,28 @@
       </c>
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="22"/>
-      <c r="B53" s="22"/>
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="22"/>
-      <c r="B54" s="22"/>
+      <c r="A54" s="30"/>
+      <c r="B54" s="30"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="22"/>
-      <c r="B55" s="23"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="31"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="22"/>
+      <c r="A56" s="30"/>
       <c r="B56" s="35" t="s">
         <v>30</v>
       </c>
@@ -15948,28 +16008,28 @@
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="22"/>
-      <c r="B57" s="22"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="30"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="22"/>
-      <c r="B58" s="23"/>
+      <c r="A58" s="30"/>
+      <c r="B58" s="31"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="22"/>
+      <c r="A59" s="30"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="22"/>
+      <c r="A60" s="30"/>
       <c r="B60" s="35" t="s">
         <v>25</v>
       </c>
@@ -15978,22 +16038,22 @@
       </c>
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="22"/>
-      <c r="B61" s="22"/>
+      <c r="A61" s="30"/>
+      <c r="B61" s="30"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="23"/>
-      <c r="B62" s="23"/>
+      <c r="A62" s="31"/>
+      <c r="B62" s="31"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="30" t="s">
+      <c r="A64" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -16004,7 +16064,7 @@
       </c>
     </row>
     <row r="65" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="31"/>
+      <c r="A65" s="19"/>
       <c r="B65" s="4" t="s">
         <v>132</v>
       </c>
@@ -16013,7 +16073,7 @@
       </c>
     </row>
     <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="31"/>
+      <c r="A66" s="19"/>
       <c r="B66" s="4" t="s">
         <v>133</v>
       </c>
@@ -16022,7 +16082,7 @@
       </c>
     </row>
     <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="32"/>
+      <c r="A67" s="20"/>
       <c r="B67" s="5" t="s">
         <v>134</v>
       </c>
@@ -16032,6 +16092,13 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A64:A67"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A52:A62"/>
+    <mergeCell ref="B52:B55"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="B60:B62"/>
     <mergeCell ref="A7:A18"/>
     <mergeCell ref="B7:B10"/>
     <mergeCell ref="B11:B13"/>
@@ -16042,13 +16109,6 @@
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="B35:B38"/>
     <mergeCell ref="B40:B42"/>
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A52:A62"/>
-    <mergeCell ref="B52:B55"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B60:B62"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dev_stuffs/3匠魂.xlsx
+++ b/dev_stuffs/3匠魂.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\Palmon\dev_stuffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597351A4-5E82-43B7-B465-3823897B6F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D843C7-4B06-4A22-97E5-F1D4B14EB213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6090" yWindow="2715" windowWidth="23940" windowHeight="15435" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="21105" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="阶段1" sheetId="1" r:id="rId1"/>
@@ -1068,6 +1068,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1075,15 +1084,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
@@ -1119,12 +1119,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1132,6 +1126,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2203,7 +2203,7 @@
     </row>
     <row r="32" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="25"/>
-      <c r="B32" s="21" t="s">
+      <c r="B32" s="18" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -2242,7 +2242,7 @@
     </row>
     <row r="33" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="25"/>
-      <c r="B33" s="22"/>
+      <c r="B33" s="19"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -2289,7 +2289,7 @@
     </row>
     <row r="34" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="25"/>
-      <c r="B34" s="22"/>
+      <c r="B34" s="19"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -2326,7 +2326,7 @@
     </row>
     <row r="35" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="25"/>
-      <c r="B35" s="23"/>
+      <c r="B35" s="20"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="37" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="25"/>
-      <c r="B37" s="21" t="s">
+      <c r="B37" s="18" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -2379,7 +2379,7 @@
     </row>
     <row r="38" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="25"/>
-      <c r="B38" s="22"/>
+      <c r="B38" s="19"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -2426,7 +2426,7 @@
     </row>
     <row r="39" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="25"/>
-      <c r="B39" s="22"/>
+      <c r="B39" s="19"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -2463,7 +2463,7 @@
     </row>
     <row r="40" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="25"/>
-      <c r="B40" s="23"/>
+      <c r="B40" s="20"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="42" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="25"/>
-      <c r="B42" s="21" t="s">
+      <c r="B42" s="18" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -2526,7 +2526,7 @@
     </row>
     <row r="43" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="25"/>
-      <c r="B43" s="22"/>
+      <c r="B43" s="19"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -2563,7 +2563,7 @@
     </row>
     <row r="44" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="25"/>
-      <c r="B44" s="23"/>
+      <c r="B44" s="20"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
@@ -2573,7 +2573,7 @@
     </row>
     <row r="46" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="25"/>
-      <c r="B46" s="21" t="s">
+      <c r="B46" s="18" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -2582,14 +2582,14 @@
     </row>
     <row r="47" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="25"/>
-      <c r="B47" s="22"/>
+      <c r="B47" s="19"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="25"/>
-      <c r="B48" s="23"/>
+      <c r="B48" s="20"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="50" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="25"/>
-      <c r="B50" s="21" t="s">
+      <c r="B50" s="18" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -2652,7 +2652,7 @@
     </row>
     <row r="51" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="25"/>
-      <c r="B51" s="22"/>
+      <c r="B51" s="19"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -2699,7 +2699,7 @@
     </row>
     <row r="52" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="25"/>
-      <c r="B52" s="23"/>
+      <c r="B52" s="20"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -2836,7 +2836,7 @@
       </c>
     </row>
     <row r="67" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="18" t="s">
+      <c r="A67" s="21" t="s">
         <v>26</v>
       </c>
       <c r="B67" s="6" t="s">
@@ -2877,7 +2877,7 @@
       </c>
     </row>
     <row r="68" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="19"/>
+      <c r="A68" s="22"/>
       <c r="B68" s="4" t="s">
         <v>132</v>
       </c>
@@ -2916,7 +2916,7 @@
       </c>
     </row>
     <row r="69" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="19"/>
+      <c r="A69" s="22"/>
       <c r="B69" s="4" t="s">
         <v>133</v>
       </c>
@@ -2955,7 +2955,7 @@
       </c>
     </row>
     <row r="70" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="20"/>
+      <c r="A70" s="23"/>
       <c r="B70" s="5" t="s">
         <v>134</v>
       </c>
@@ -2995,6 +2995,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B42:B44"/>
     <mergeCell ref="B50:B52"/>
     <mergeCell ref="A67:A70"/>
     <mergeCell ref="B46:B48"/>
@@ -3011,7 +3012,6 @@
     <mergeCell ref="B62:B64"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
-    <mergeCell ref="B42:B44"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3714,7 +3714,7 @@
       <c r="A22" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="36" t="s">
+      <c r="B22" s="39" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -3765,7 +3765,7 @@
     </row>
     <row r="23" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="29"/>
-      <c r="B23" s="36"/>
+      <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
       </c>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="24" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="29"/>
-      <c r="B24" s="36"/>
+      <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
       </c>
@@ -3877,7 +3877,7 @@
     </row>
     <row r="25" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="29"/>
-      <c r="B25" s="36"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
       </c>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="27" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="29"/>
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="4" t="s">
@@ -3966,7 +3966,7 @@
     </row>
     <row r="28" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="29"/>
-      <c r="B28" s="36"/>
+      <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
       </c>
@@ -4029,7 +4029,7 @@
     </row>
     <row r="29" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="29"/>
-      <c r="B29" s="36"/>
+      <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
       </c>
@@ -4078,7 +4078,7 @@
     </row>
     <row r="30" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="29"/>
-      <c r="B30" s="36"/>
+      <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
       </c>
@@ -4116,7 +4116,7 @@
     </row>
     <row r="32" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="29"/>
-      <c r="B32" s="37" t="s">
+      <c r="B32" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -4167,7 +4167,7 @@
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="29"/>
-      <c r="B33" s="38"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -4230,7 +4230,7 @@
     </row>
     <row r="34" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="29"/>
-      <c r="B34" s="38"/>
+      <c r="B34" s="36"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="29"/>
-      <c r="B35" s="39"/>
+      <c r="B35" s="37"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="29"/>
-      <c r="B37" s="37" t="s">
+      <c r="B37" s="35" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -4368,7 +4368,7 @@
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="38"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="39" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="29"/>
-      <c r="B39" s="38"/>
+      <c r="B39" s="36"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -4480,7 +4480,7 @@
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="29"/>
-      <c r="B40" s="39"/>
+      <c r="B40" s="37"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="29"/>
-      <c r="B42" s="37" t="s">
+      <c r="B42" s="35" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -4583,7 +4583,7 @@
     </row>
     <row r="43" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="29"/>
-      <c r="B43" s="38"/>
+      <c r="B43" s="36"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -4632,7 +4632,7 @@
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="29"/>
-      <c r="B44" s="39"/>
+      <c r="B44" s="37"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
@@ -4668,7 +4668,7 @@
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="29"/>
-      <c r="B46" s="37" t="s">
+      <c r="B46" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -4677,14 +4677,14 @@
     </row>
     <row r="47" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="29"/>
-      <c r="B47" s="38"/>
+      <c r="B47" s="36"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="29"/>
-      <c r="B48" s="39"/>
+      <c r="B48" s="37"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
@@ -4698,7 +4698,7 @@
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="29"/>
-      <c r="B50" s="37" t="s">
+      <c r="B50" s="35" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -4763,7 +4763,7 @@
     </row>
     <row r="51" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="29"/>
-      <c r="B51" s="38"/>
+      <c r="B51" s="36"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -4826,7 +4826,7 @@
     </row>
     <row r="52" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="29"/>
-      <c r="B52" s="39"/>
+      <c r="B52" s="37"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -4893,10 +4893,10 @@
       <c r="C53" s="8"/>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="35" t="s">
+      <c r="A54" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="35" t="s">
+      <c r="B54" s="38" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -4926,7 +4926,7 @@
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="30"/>
-      <c r="B58" s="35" t="s">
+      <c r="B58" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -4956,7 +4956,7 @@
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="30"/>
-      <c r="B62" s="35" t="s">
+      <c r="B62" s="38" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -4979,7 +4979,7 @@
     </row>
     <row r="65" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="18" t="s">
+      <c r="A66" s="21" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -5032,7 +5032,7 @@
       </c>
     </row>
     <row r="67" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="19"/>
+      <c r="A67" s="22"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -5077,7 +5077,7 @@
       </c>
     </row>
     <row r="68" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="19"/>
+      <c r="A68" s="22"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -5122,7 +5122,7 @@
       </c>
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="20"/>
+      <c r="A69" s="23"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -5132,6 +5132,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B58:B60"/>
     <mergeCell ref="B50:B52"/>
     <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
@@ -5148,7 +5149,6 @@
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="A54:A64"/>
     <mergeCell ref="B54:B57"/>
-    <mergeCell ref="B58:B60"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6404,7 +6404,7 @@
       <c r="A22" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="36" t="s">
+      <c r="B22" s="39" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -6497,7 +6497,7 @@
     </row>
     <row r="23" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="29"/>
-      <c r="B23" s="36"/>
+      <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
       </c>
@@ -6616,7 +6616,7 @@
     </row>
     <row r="24" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="29"/>
-      <c r="B24" s="36"/>
+      <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
       </c>
@@ -6707,7 +6707,7 @@
     </row>
     <row r="25" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="29"/>
-      <c r="B25" s="36"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
       </c>
@@ -6805,7 +6805,7 @@
     </row>
     <row r="27" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="29"/>
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="4" t="s">
@@ -6898,7 +6898,7 @@
     </row>
     <row r="28" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="29"/>
-      <c r="B28" s="36"/>
+      <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
       </c>
@@ -7017,7 +7017,7 @@
     </row>
     <row r="29" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="29"/>
-      <c r="B29" s="36"/>
+      <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
       </c>
@@ -7108,7 +7108,7 @@
     </row>
     <row r="30" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="29"/>
-      <c r="B30" s="36"/>
+      <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
       </c>
@@ -7206,7 +7206,7 @@
     </row>
     <row r="32" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="29"/>
-      <c r="B32" s="37" t="s">
+      <c r="B32" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -7299,7 +7299,7 @@
     </row>
     <row r="33" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="29"/>
-      <c r="B33" s="38"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -7418,7 +7418,7 @@
     </row>
     <row r="34" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="29"/>
-      <c r="B34" s="38"/>
+      <c r="B34" s="36"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -7509,7 +7509,7 @@
     </row>
     <row r="35" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="29"/>
-      <c r="B35" s="39"/>
+      <c r="B35" s="37"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
@@ -7607,7 +7607,7 @@
     </row>
     <row r="37" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="29"/>
-      <c r="B37" s="37" t="s">
+      <c r="B37" s="35" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -7700,7 +7700,7 @@
     </row>
     <row r="38" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="38"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -7819,7 +7819,7 @@
     </row>
     <row r="39" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="29"/>
-      <c r="B39" s="38"/>
+      <c r="B39" s="36"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -7910,7 +7910,7 @@
     </row>
     <row r="40" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="29"/>
-      <c r="B40" s="39"/>
+      <c r="B40" s="37"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
@@ -8008,7 +8008,7 @@
     </row>
     <row r="42" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="29"/>
-      <c r="B42" s="37" t="s">
+      <c r="B42" s="35" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -8017,7 +8017,7 @@
     </row>
     <row r="43" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="29"/>
-      <c r="B43" s="38"/>
+      <c r="B43" s="36"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -8108,7 +8108,7 @@
     </row>
     <row r="44" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="29"/>
-      <c r="B44" s="39"/>
+      <c r="B44" s="37"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
@@ -8204,7 +8204,7 @@
     </row>
     <row r="46" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="29"/>
-      <c r="B46" s="37" t="s">
+      <c r="B46" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -8213,14 +8213,14 @@
     </row>
     <row r="47" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="29"/>
-      <c r="B47" s="38"/>
+      <c r="B47" s="36"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="29"/>
-      <c r="B48" s="39"/>
+      <c r="B48" s="37"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
@@ -8234,7 +8234,7 @@
     </row>
     <row r="50" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="29"/>
-      <c r="B50" s="37" t="s">
+      <c r="B50" s="35" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -8355,7 +8355,7 @@
     </row>
     <row r="51" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="29"/>
-      <c r="B51" s="38"/>
+      <c r="B51" s="36"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -8474,7 +8474,7 @@
     </row>
     <row r="52" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="29"/>
-      <c r="B52" s="39"/>
+      <c r="B52" s="37"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -8597,10 +8597,10 @@
       <c r="C53" s="8"/>
     </row>
     <row r="54" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="35" t="s">
+      <c r="A54" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="35" t="s">
+      <c r="B54" s="38" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -8630,7 +8630,7 @@
     </row>
     <row r="58" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="30"/>
-      <c r="B58" s="35" t="s">
+      <c r="B58" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -8660,7 +8660,7 @@
     </row>
     <row r="62" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="30"/>
-      <c r="B62" s="35" t="s">
+      <c r="B62" s="38" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -8683,7 +8683,7 @@
     </row>
     <row r="65" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:31" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="18" t="s">
+      <c r="A66" s="21" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -8778,7 +8778,7 @@
       </c>
     </row>
     <row r="67" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="19"/>
+      <c r="A67" s="22"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -8871,7 +8871,7 @@
       </c>
     </row>
     <row r="68" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="19"/>
+      <c r="A68" s="22"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -8964,7 +8964,7 @@
       </c>
     </row>
     <row r="69" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="20"/>
+      <c r="A69" s="23"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -9058,11 +9058,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="B37:B40"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="B9:B12"/>
@@ -9075,6 +9070,11 @@
     <mergeCell ref="A54:A64"/>
     <mergeCell ref="B54:B57"/>
     <mergeCell ref="B62:B64"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A66:A69"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9702,7 +9702,7 @@
       <c r="A22" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="36" t="s">
+      <c r="B22" s="39" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -9747,7 +9747,7 @@
     </row>
     <row r="23" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="29"/>
-      <c r="B23" s="36"/>
+      <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
       </c>
@@ -9802,7 +9802,7 @@
     </row>
     <row r="24" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="29"/>
-      <c r="B24" s="36"/>
+      <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
       </c>
@@ -9845,7 +9845,7 @@
     </row>
     <row r="25" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="29"/>
-      <c r="B25" s="36"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
       </c>
@@ -9895,7 +9895,7 @@
     </row>
     <row r="27" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="29"/>
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="4" t="s">
@@ -9940,7 +9940,7 @@
     </row>
     <row r="28" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="29"/>
-      <c r="B28" s="36"/>
+      <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
       </c>
@@ -9995,7 +9995,7 @@
     </row>
     <row r="29" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="29"/>
-      <c r="B29" s="36"/>
+      <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
       </c>
@@ -10038,7 +10038,7 @@
     </row>
     <row r="30" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="29"/>
-      <c r="B30" s="36"/>
+      <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
       </c>
@@ -10088,7 +10088,7 @@
     </row>
     <row r="32" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="29"/>
-      <c r="B32" s="37" t="s">
+      <c r="B32" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -10133,7 +10133,7 @@
     </row>
     <row r="33" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="29"/>
-      <c r="B33" s="38"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -10188,7 +10188,7 @@
     </row>
     <row r="34" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="29"/>
-      <c r="B34" s="38"/>
+      <c r="B34" s="36"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -10231,7 +10231,7 @@
     </row>
     <row r="35" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="29"/>
-      <c r="B35" s="39"/>
+      <c r="B35" s="37"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
@@ -10281,7 +10281,7 @@
     </row>
     <row r="37" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="29"/>
-      <c r="B37" s="37" t="s">
+      <c r="B37" s="35" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -10326,7 +10326,7 @@
     </row>
     <row r="38" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="38"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -10381,7 +10381,7 @@
     </row>
     <row r="39" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="29"/>
-      <c r="B39" s="38"/>
+      <c r="B39" s="36"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -10424,7 +10424,7 @@
     </row>
     <row r="40" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="29"/>
-      <c r="B40" s="39"/>
+      <c r="B40" s="37"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
@@ -10474,7 +10474,7 @@
     </row>
     <row r="42" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="29"/>
-      <c r="B42" s="37" t="s">
+      <c r="B42" s="35" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -10531,7 +10531,7 @@
     </row>
     <row r="43" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="29"/>
-      <c r="B43" s="38"/>
+      <c r="B43" s="36"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -10574,7 +10574,7 @@
     </row>
     <row r="44" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="29"/>
-      <c r="B44" s="39"/>
+      <c r="B44" s="37"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
@@ -10623,7 +10623,7 @@
     </row>
     <row r="46" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="29"/>
-      <c r="B46" s="37" t="s">
+      <c r="B46" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -10632,14 +10632,14 @@
     </row>
     <row r="47" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="29"/>
-      <c r="B47" s="38"/>
+      <c r="B47" s="36"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="29"/>
-      <c r="B48" s="39"/>
+      <c r="B48" s="37"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
@@ -10653,7 +10653,7 @@
     </row>
     <row r="50" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="29"/>
-      <c r="B50" s="37" t="s">
+      <c r="B50" s="35" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -10710,7 +10710,7 @@
     </row>
     <row r="51" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="29"/>
-      <c r="B51" s="38"/>
+      <c r="B51" s="36"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -10765,7 +10765,7 @@
     </row>
     <row r="52" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="29"/>
-      <c r="B52" s="39"/>
+      <c r="B52" s="37"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -10824,10 +10824,10 @@
       <c r="C53" s="8"/>
     </row>
     <row r="54" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="35" t="s">
+      <c r="A54" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="35" t="s">
+      <c r="B54" s="38" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -10869,7 +10869,7 @@
     </row>
     <row r="58" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="30"/>
-      <c r="B58" s="35" t="s">
+      <c r="B58" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -10899,7 +10899,7 @@
     </row>
     <row r="62" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="30"/>
-      <c r="B62" s="35" t="s">
+      <c r="B62" s="38" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -10931,7 +10931,7 @@
     </row>
     <row r="65" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="18" t="s">
+      <c r="A66" s="21" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -10978,7 +10978,7 @@
       </c>
     </row>
     <row r="67" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="19"/>
+      <c r="A67" s="22"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -11023,7 +11023,7 @@
       </c>
     </row>
     <row r="68" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="19"/>
+      <c r="A68" s="22"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -11068,7 +11068,7 @@
       </c>
     </row>
     <row r="69" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="20"/>
+      <c r="A69" s="23"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -11114,11 +11114,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="B37:B40"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="B9:B12"/>
@@ -11131,6 +11126,11 @@
     <mergeCell ref="A54:A64"/>
     <mergeCell ref="B54:B57"/>
     <mergeCell ref="B62:B64"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A66:A69"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12194,7 +12194,7 @@
       <c r="A22" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="36" t="s">
+      <c r="B22" s="39" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -12269,7 +12269,7 @@
     </row>
     <row r="23" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="29"/>
-      <c r="B23" s="36"/>
+      <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
       </c>
@@ -12364,7 +12364,7 @@
     </row>
     <row r="24" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="29"/>
-      <c r="B24" s="36"/>
+      <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
       </c>
@@ -12437,7 +12437,7 @@
     </row>
     <row r="25" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="29"/>
-      <c r="B25" s="36"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
       </c>
@@ -12517,7 +12517,7 @@
     </row>
     <row r="27" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="29"/>
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="4" t="s">
@@ -12592,7 +12592,7 @@
     </row>
     <row r="28" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="29"/>
-      <c r="B28" s="36"/>
+      <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
       </c>
@@ -12687,7 +12687,7 @@
     </row>
     <row r="29" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="29"/>
-      <c r="B29" s="36"/>
+      <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
       </c>
@@ -12760,7 +12760,7 @@
     </row>
     <row r="30" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="29"/>
-      <c r="B30" s="36"/>
+      <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
       </c>
@@ -12840,7 +12840,7 @@
     </row>
     <row r="32" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="29"/>
-      <c r="B32" s="37" t="s">
+      <c r="B32" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -12915,7 +12915,7 @@
     </row>
     <row r="33" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="29"/>
-      <c r="B33" s="38"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -13010,7 +13010,7 @@
     </row>
     <row r="34" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="29"/>
-      <c r="B34" s="38"/>
+      <c r="B34" s="36"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -13083,7 +13083,7 @@
     </row>
     <row r="35" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="29"/>
-      <c r="B35" s="39"/>
+      <c r="B35" s="37"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
@@ -13163,7 +13163,7 @@
     </row>
     <row r="37" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="29"/>
-      <c r="B37" s="37" t="s">
+      <c r="B37" s="35" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -13238,7 +13238,7 @@
     </row>
     <row r="38" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="38"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -13333,7 +13333,7 @@
     </row>
     <row r="39" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="29"/>
-      <c r="B39" s="38"/>
+      <c r="B39" s="36"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -13406,7 +13406,7 @@
     </row>
     <row r="40" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="29"/>
-      <c r="B40" s="39"/>
+      <c r="B40" s="37"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
@@ -13486,7 +13486,7 @@
     </row>
     <row r="42" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="29"/>
-      <c r="B42" s="37" t="s">
+      <c r="B42" s="35" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -13583,7 +13583,7 @@
     </row>
     <row r="43" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="29"/>
-      <c r="B43" s="38"/>
+      <c r="B43" s="36"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -13656,7 +13656,7 @@
     </row>
     <row r="44" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="29"/>
-      <c r="B44" s="39"/>
+      <c r="B44" s="37"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
@@ -13734,7 +13734,7 @@
     </row>
     <row r="46" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="29"/>
-      <c r="B46" s="37" t="s">
+      <c r="B46" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -13743,14 +13743,14 @@
     </row>
     <row r="47" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="29"/>
-      <c r="B47" s="38"/>
+      <c r="B47" s="36"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="29"/>
-      <c r="B48" s="39"/>
+      <c r="B48" s="37"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
@@ -13764,7 +13764,7 @@
     </row>
     <row r="50" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="29"/>
-      <c r="B50" s="37" t="s">
+      <c r="B50" s="35" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -13861,7 +13861,7 @@
     </row>
     <row r="51" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="29"/>
-      <c r="B51" s="38"/>
+      <c r="B51" s="36"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -13956,7 +13956,7 @@
     </row>
     <row r="52" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="29"/>
-      <c r="B52" s="39"/>
+      <c r="B52" s="37"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -14055,10 +14055,10 @@
       <c r="C53" s="8"/>
     </row>
     <row r="54" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="35" t="s">
+      <c r="A54" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="35" t="s">
+      <c r="B54" s="38" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -14088,7 +14088,7 @@
     </row>
     <row r="58" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="30"/>
-      <c r="B58" s="35" t="s">
+      <c r="B58" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -14118,7 +14118,7 @@
     </row>
     <row r="62" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="30"/>
-      <c r="B62" s="35" t="s">
+      <c r="B62" s="38" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -14141,7 +14141,7 @@
     </row>
     <row r="65" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="18" t="s">
+      <c r="A66" s="21" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -14218,7 +14218,7 @@
       </c>
     </row>
     <row r="67" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="19"/>
+      <c r="A67" s="22"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -14293,7 +14293,7 @@
       </c>
     </row>
     <row r="68" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="19"/>
+      <c r="A68" s="22"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -14368,7 +14368,7 @@
       </c>
     </row>
     <row r="69" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="20"/>
+      <c r="A69" s="23"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -14444,11 +14444,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="B37:B40"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="B9:B12"/>
@@ -14461,6 +14456,11 @@
     <mergeCell ref="A54:A64"/>
     <mergeCell ref="B54:B57"/>
     <mergeCell ref="B62:B64"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A66:A69"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14730,7 +14730,7 @@
       <c r="A20" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="39" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -14739,21 +14739,21 @@
     </row>
     <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="29"/>
-      <c r="B21" s="36"/>
+      <c r="B21" s="39"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="29"/>
-      <c r="B22" s="36"/>
+      <c r="B22" s="39"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="29"/>
-      <c r="B23" s="36"/>
+      <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
@@ -14767,7 +14767,7 @@
     </row>
     <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="29"/>
-      <c r="B25" s="36" t="s">
+      <c r="B25" s="39" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="4" t="s">
@@ -14776,21 +14776,21 @@
     </row>
     <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="29"/>
-      <c r="B26" s="36"/>
+      <c r="B26" s="39"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="29"/>
-      <c r="B27" s="36"/>
+      <c r="B27" s="39"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="29"/>
-      <c r="B28" s="36"/>
+      <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
@@ -14804,7 +14804,7 @@
     </row>
     <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="29"/>
-      <c r="B30" s="37" t="s">
+      <c r="B30" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -14813,21 +14813,21 @@
     </row>
     <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="29"/>
-      <c r="B31" s="38"/>
+      <c r="B31" s="36"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="29"/>
-      <c r="B32" s="38"/>
+      <c r="B32" s="36"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="29"/>
-      <c r="B33" s="39"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
@@ -14841,7 +14841,7 @@
     </row>
     <row r="35" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="29"/>
-      <c r="B35" s="37" t="s">
+      <c r="B35" s="35" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -14850,21 +14850,21 @@
     </row>
     <row r="36" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="29"/>
-      <c r="B36" s="38"/>
+      <c r="B36" s="36"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="29"/>
-      <c r="B37" s="38"/>
+      <c r="B37" s="36"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="39"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
@@ -14878,7 +14878,7 @@
     </row>
     <row r="40" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="29"/>
-      <c r="B40" s="37" t="s">
+      <c r="B40" s="35" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
@@ -14887,14 +14887,14 @@
     </row>
     <row r="41" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="29"/>
-      <c r="B41" s="38"/>
+      <c r="B41" s="36"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="29"/>
-      <c r="B42" s="39"/>
+      <c r="B42" s="37"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
@@ -14906,7 +14906,7 @@
     </row>
     <row r="44" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="29"/>
-      <c r="B44" s="37" t="s">
+      <c r="B44" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C44" s="4">
@@ -14915,14 +14915,14 @@
     </row>
     <row r="45" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="29"/>
-      <c r="B45" s="38"/>
+      <c r="B45" s="36"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="29"/>
-      <c r="B46" s="39"/>
+      <c r="B46" s="37"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
@@ -14936,7 +14936,7 @@
     </row>
     <row r="48" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="29"/>
-      <c r="B48" s="37" t="s">
+      <c r="B48" s="35" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="4" t="s">
@@ -15005,7 +15005,7 @@
     </row>
     <row r="49" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="29"/>
-      <c r="B49" s="38"/>
+      <c r="B49" s="36"/>
       <c r="C49" s="4" t="s">
         <v>129</v>
       </c>
@@ -15072,7 +15072,7 @@
     </row>
     <row r="50" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="29"/>
-      <c r="B50" s="39"/>
+      <c r="B50" s="37"/>
       <c r="C50" s="4" t="s">
         <v>130</v>
       </c>
@@ -15143,10 +15143,10 @@
       <c r="C51" s="8"/>
     </row>
     <row r="52" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="35" t="s">
+      <c r="A52" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="B52" s="35" t="s">
+      <c r="B52" s="38" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="5" t="s">
@@ -15176,7 +15176,7 @@
     </row>
     <row r="56" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="30"/>
-      <c r="B56" s="35" t="s">
+      <c r="B56" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C56" s="5">
@@ -15206,7 +15206,7 @@
     </row>
     <row r="60" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="30"/>
-      <c r="B60" s="35" t="s">
+      <c r="B60" s="38" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
@@ -15229,7 +15229,7 @@
     </row>
     <row r="63" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="64" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="18" t="s">
+      <c r="A64" s="21" t="s">
         <v>26</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -15243,7 +15243,7 @@
       </c>
     </row>
     <row r="65" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="19"/>
+      <c r="A65" s="22"/>
       <c r="B65" s="4" t="s">
         <v>132</v>
       </c>
@@ -15255,7 +15255,7 @@
       </c>
     </row>
     <row r="66" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="19"/>
+      <c r="A66" s="22"/>
       <c r="B66" s="4" t="s">
         <v>133</v>
       </c>
@@ -15267,7 +15267,7 @@
       </c>
     </row>
     <row r="67" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="20"/>
+      <c r="A67" s="23"/>
       <c r="B67" s="5" t="s">
         <v>134</v>
       </c>
@@ -15280,11 +15280,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A64:A67"/>
     <mergeCell ref="A7:A18"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B7:B10"/>
@@ -15297,6 +15292,11 @@
     <mergeCell ref="A52:A62"/>
     <mergeCell ref="B52:B55"/>
     <mergeCell ref="B60:B62"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A64:A67"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15566,7 +15566,7 @@
       <c r="A20" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="39" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -15575,21 +15575,21 @@
     </row>
     <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="29"/>
-      <c r="B21" s="36"/>
+      <c r="B21" s="39"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="29"/>
-      <c r="B22" s="36"/>
+      <c r="B22" s="39"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="29"/>
-      <c r="B23" s="36"/>
+      <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
@@ -15603,7 +15603,7 @@
     </row>
     <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="29"/>
-      <c r="B25" s="36" t="s">
+      <c r="B25" s="39" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="4" t="s">
@@ -15612,21 +15612,21 @@
     </row>
     <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="29"/>
-      <c r="B26" s="36"/>
+      <c r="B26" s="39"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="29"/>
-      <c r="B27" s="36"/>
+      <c r="B27" s="39"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="29"/>
-      <c r="B28" s="36"/>
+      <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
@@ -15640,7 +15640,7 @@
     </row>
     <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="29"/>
-      <c r="B30" s="37" t="s">
+      <c r="B30" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -15649,21 +15649,21 @@
     </row>
     <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="29"/>
-      <c r="B31" s="38"/>
+      <c r="B31" s="36"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="29"/>
-      <c r="B32" s="38"/>
+      <c r="B32" s="36"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="29"/>
-      <c r="B33" s="39"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
@@ -15677,7 +15677,7 @@
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="29"/>
-      <c r="B35" s="37" t="s">
+      <c r="B35" s="35" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -15686,21 +15686,21 @@
     </row>
     <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="29"/>
-      <c r="B36" s="38"/>
+      <c r="B36" s="36"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="29"/>
-      <c r="B37" s="38"/>
+      <c r="B37" s="36"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="39"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
@@ -15714,7 +15714,7 @@
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="29"/>
-      <c r="B40" s="37" t="s">
+      <c r="B40" s="35" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
@@ -15723,14 +15723,14 @@
     </row>
     <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="29"/>
-      <c r="B41" s="38"/>
+      <c r="B41" s="36"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="29"/>
-      <c r="B42" s="39"/>
+      <c r="B42" s="37"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
@@ -15742,7 +15742,7 @@
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="29"/>
-      <c r="B44" s="37" t="s">
+      <c r="B44" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C44" s="4">
@@ -15751,14 +15751,14 @@
     </row>
     <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="29"/>
-      <c r="B45" s="38"/>
+      <c r="B45" s="36"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="29"/>
-      <c r="B46" s="39"/>
+      <c r="B46" s="37"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
@@ -15772,7 +15772,7 @@
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="29"/>
-      <c r="B48" s="37" t="s">
+      <c r="B48" s="35" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="4" t="s">
@@ -15837,7 +15837,7 @@
     </row>
     <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="29"/>
-      <c r="B49" s="38"/>
+      <c r="B49" s="36"/>
       <c r="C49" s="4" t="s">
         <v>129</v>
       </c>
@@ -15900,7 +15900,7 @@
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="29"/>
-      <c r="B50" s="39"/>
+      <c r="B50" s="37"/>
       <c r="C50" s="4" t="s">
         <v>130</v>
       </c>
@@ -15967,10 +15967,10 @@
       <c r="C51" s="8"/>
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="35" t="s">
+      <c r="A52" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="B52" s="35" t="s">
+      <c r="B52" s="38" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="5" t="s">
@@ -16000,7 +16000,7 @@
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="30"/>
-      <c r="B56" s="35" t="s">
+      <c r="B56" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C56" s="5">
@@ -16030,7 +16030,7 @@
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="30"/>
-      <c r="B60" s="35" t="s">
+      <c r="B60" s="38" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
@@ -16053,7 +16053,7 @@
     </row>
     <row r="63" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="18" t="s">
+      <c r="A64" s="21" t="s">
         <v>26</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -16064,7 +16064,7 @@
       </c>
     </row>
     <row r="65" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="19"/>
+      <c r="A65" s="22"/>
       <c r="B65" s="4" t="s">
         <v>132</v>
       </c>
@@ -16073,7 +16073,7 @@
       </c>
     </row>
     <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="19"/>
+      <c r="A66" s="22"/>
       <c r="B66" s="4" t="s">
         <v>133</v>
       </c>
@@ -16082,7 +16082,7 @@
       </c>
     </row>
     <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="20"/>
+      <c r="A67" s="23"/>
       <c r="B67" s="5" t="s">
         <v>134</v>
       </c>
@@ -16092,13 +16092,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A52:A62"/>
-    <mergeCell ref="B52:B55"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B60:B62"/>
     <mergeCell ref="A7:A18"/>
     <mergeCell ref="B7:B10"/>
     <mergeCell ref="B11:B13"/>
@@ -16109,6 +16102,13 @@
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="B35:B38"/>
     <mergeCell ref="B40:B42"/>
+    <mergeCell ref="A64:A67"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A52:A62"/>
+    <mergeCell ref="B52:B55"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="B60:B62"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dev_stuffs/3匠魂.xlsx
+++ b/dev_stuffs/3匠魂.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\Palmon\dev_stuffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D843C7-4B06-4A22-97E5-F1D4B14EB213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02BEAED1-B2FD-4C4E-B9CE-1AC3EB85EEF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="21105" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13185" yWindow="2595" windowWidth="23940" windowHeight="15435" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="阶段1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="268">
   <si>
     <t>材料名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -819,6 +819,110 @@
   </si>
   <si>
     <t>'kubejs:ember_profile'</t>
+  </si>
+  <si>
+    <t>铁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒之骨</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>粘木</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>锇</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>防腐木</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>铅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>银</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>粘钢</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫水晶青铜</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>纳瓦</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生铁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玫瑰金</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>青铜</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>康铜</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>殷钢</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>琥珀金</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>黏液浸钢</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>粉色史莱姆金属</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>复合粘木</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>钴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>钢</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄铜</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>余烬黏液</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>皇后史莱姆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑色青铜</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>锑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1119,6 +1223,9 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1126,9 +1233,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
@@ -2995,11 +3099,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="A22:A52"/>
     <mergeCell ref="B13:B15"/>
     <mergeCell ref="A54:A64"/>
     <mergeCell ref="A9:A20"/>
@@ -3012,6 +3111,11 @@
     <mergeCell ref="B62:B64"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="A22:A52"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4116,7 +4220,7 @@
     </row>
     <row r="32" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="29"/>
-      <c r="B32" s="35" t="s">
+      <c r="B32" s="36" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -4167,7 +4271,7 @@
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="29"/>
-      <c r="B33" s="36"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -4230,7 +4334,7 @@
     </row>
     <row r="34" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="29"/>
-      <c r="B34" s="36"/>
+      <c r="B34" s="37"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -4279,7 +4383,7 @@
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="29"/>
-      <c r="B35" s="37"/>
+      <c r="B35" s="38"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
@@ -4317,7 +4421,7 @@
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="29"/>
-      <c r="B37" s="35" t="s">
+      <c r="B37" s="36" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -4368,7 +4472,7 @@
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="36"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -4431,7 +4535,7 @@
     </row>
     <row r="39" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="29"/>
-      <c r="B39" s="36"/>
+      <c r="B39" s="37"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -4480,7 +4584,7 @@
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="29"/>
-      <c r="B40" s="37"/>
+      <c r="B40" s="38"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
@@ -4518,7 +4622,7 @@
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="29"/>
-      <c r="B42" s="35" t="s">
+      <c r="B42" s="36" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -4583,7 +4687,7 @@
     </row>
     <row r="43" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="29"/>
-      <c r="B43" s="36"/>
+      <c r="B43" s="37"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -4632,7 +4736,7 @@
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="29"/>
-      <c r="B44" s="37"/>
+      <c r="B44" s="38"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
@@ -4668,7 +4772,7 @@
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="29"/>
-      <c r="B46" s="35" t="s">
+      <c r="B46" s="36" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -4677,14 +4781,14 @@
     </row>
     <row r="47" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="29"/>
-      <c r="B47" s="36"/>
+      <c r="B47" s="37"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="29"/>
-      <c r="B48" s="37"/>
+      <c r="B48" s="38"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
@@ -4698,7 +4802,7 @@
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="29"/>
-      <c r="B50" s="35" t="s">
+      <c r="B50" s="36" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -4763,7 +4867,7 @@
     </row>
     <row r="51" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="29"/>
-      <c r="B51" s="36"/>
+      <c r="B51" s="37"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -4826,7 +4930,7 @@
     </row>
     <row r="52" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="29"/>
-      <c r="B52" s="37"/>
+      <c r="B52" s="38"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -4893,10 +4997,10 @@
       <c r="C53" s="8"/>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="38" t="s">
+      <c r="A54" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="38" t="s">
+      <c r="B54" s="35" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -4926,7 +5030,7 @@
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="30"/>
-      <c r="B58" s="38" t="s">
+      <c r="B58" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -4956,7 +5060,7 @@
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="30"/>
-      <c r="B62" s="38" t="s">
+      <c r="B62" s="35" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -5132,6 +5236,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B54:B57"/>
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="B50:B52"/>
     <mergeCell ref="A66:A69"/>
@@ -5148,7 +5253,6 @@
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="A54:A64"/>
-    <mergeCell ref="B54:B57"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7206,7 +7310,7 @@
     </row>
     <row r="32" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="29"/>
-      <c r="B32" s="35" t="s">
+      <c r="B32" s="36" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -7299,7 +7403,7 @@
     </row>
     <row r="33" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="29"/>
-      <c r="B33" s="36"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -7418,7 +7522,7 @@
     </row>
     <row r="34" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="29"/>
-      <c r="B34" s="36"/>
+      <c r="B34" s="37"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -7509,7 +7613,7 @@
     </row>
     <row r="35" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="29"/>
-      <c r="B35" s="37"/>
+      <c r="B35" s="38"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
@@ -7607,7 +7711,7 @@
     </row>
     <row r="37" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="29"/>
-      <c r="B37" s="35" t="s">
+      <c r="B37" s="36" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -7700,7 +7804,7 @@
     </row>
     <row r="38" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="36"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -7819,7 +7923,7 @@
     </row>
     <row r="39" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="29"/>
-      <c r="B39" s="36"/>
+      <c r="B39" s="37"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -7910,7 +8014,7 @@
     </row>
     <row r="40" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="29"/>
-      <c r="B40" s="37"/>
+      <c r="B40" s="38"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
@@ -8008,7 +8112,7 @@
     </row>
     <row r="42" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="29"/>
-      <c r="B42" s="35" t="s">
+      <c r="B42" s="36" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -8017,7 +8121,7 @@
     </row>
     <row r="43" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="29"/>
-      <c r="B43" s="36"/>
+      <c r="B43" s="37"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -8108,7 +8212,7 @@
     </row>
     <row r="44" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="29"/>
-      <c r="B44" s="37"/>
+      <c r="B44" s="38"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
@@ -8204,7 +8308,7 @@
     </row>
     <row r="46" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="29"/>
-      <c r="B46" s="35" t="s">
+      <c r="B46" s="36" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -8213,14 +8317,14 @@
     </row>
     <row r="47" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="29"/>
-      <c r="B47" s="36"/>
+      <c r="B47" s="37"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="29"/>
-      <c r="B48" s="37"/>
+      <c r="B48" s="38"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
@@ -8234,7 +8338,7 @@
     </row>
     <row r="50" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="29"/>
-      <c r="B50" s="35" t="s">
+      <c r="B50" s="36" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -8355,7 +8459,7 @@
     </row>
     <row r="51" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="29"/>
-      <c r="B51" s="36"/>
+      <c r="B51" s="37"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -8474,7 +8578,7 @@
     </row>
     <row r="52" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="29"/>
-      <c r="B52" s="37"/>
+      <c r="B52" s="38"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -8597,10 +8701,10 @@
       <c r="C53" s="8"/>
     </row>
     <row r="54" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="38" t="s">
+      <c r="A54" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="38" t="s">
+      <c r="B54" s="35" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -8630,7 +8734,7 @@
     </row>
     <row r="58" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="30"/>
-      <c r="B58" s="38" t="s">
+      <c r="B58" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -8660,7 +8764,7 @@
     </row>
     <row r="62" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="30"/>
-      <c r="B62" s="38" t="s">
+      <c r="B62" s="35" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -9058,6 +9162,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="B9:B12"/>
@@ -9074,7 +9179,6 @@
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="B50:B52"/>
-    <mergeCell ref="A66:A69"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10088,7 +10192,7 @@
     </row>
     <row r="32" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="29"/>
-      <c r="B32" s="35" t="s">
+      <c r="B32" s="36" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -10133,7 +10237,7 @@
     </row>
     <row r="33" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="29"/>
-      <c r="B33" s="36"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -10188,7 +10292,7 @@
     </row>
     <row r="34" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="29"/>
-      <c r="B34" s="36"/>
+      <c r="B34" s="37"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -10231,7 +10335,7 @@
     </row>
     <row r="35" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="29"/>
-      <c r="B35" s="37"/>
+      <c r="B35" s="38"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
@@ -10281,7 +10385,7 @@
     </row>
     <row r="37" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="29"/>
-      <c r="B37" s="35" t="s">
+      <c r="B37" s="36" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -10326,7 +10430,7 @@
     </row>
     <row r="38" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="36"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -10381,7 +10485,7 @@
     </row>
     <row r="39" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="29"/>
-      <c r="B39" s="36"/>
+      <c r="B39" s="37"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -10424,7 +10528,7 @@
     </row>
     <row r="40" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="29"/>
-      <c r="B40" s="37"/>
+      <c r="B40" s="38"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
@@ -10474,7 +10578,7 @@
     </row>
     <row r="42" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="29"/>
-      <c r="B42" s="35" t="s">
+      <c r="B42" s="36" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -10531,7 +10635,7 @@
     </row>
     <row r="43" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="29"/>
-      <c r="B43" s="36"/>
+      <c r="B43" s="37"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -10574,7 +10678,7 @@
     </row>
     <row r="44" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="29"/>
-      <c r="B44" s="37"/>
+      <c r="B44" s="38"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
@@ -10623,7 +10727,7 @@
     </row>
     <row r="46" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="29"/>
-      <c r="B46" s="35" t="s">
+      <c r="B46" s="36" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -10632,14 +10736,14 @@
     </row>
     <row r="47" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="29"/>
-      <c r="B47" s="36"/>
+      <c r="B47" s="37"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="29"/>
-      <c r="B48" s="37"/>
+      <c r="B48" s="38"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
@@ -10653,7 +10757,7 @@
     </row>
     <row r="50" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="29"/>
-      <c r="B50" s="35" t="s">
+      <c r="B50" s="36" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -10710,7 +10814,7 @@
     </row>
     <row r="51" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="29"/>
-      <c r="B51" s="36"/>
+      <c r="B51" s="37"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -10765,7 +10869,7 @@
     </row>
     <row r="52" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="29"/>
-      <c r="B52" s="37"/>
+      <c r="B52" s="38"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -10824,10 +10928,10 @@
       <c r="C53" s="8"/>
     </row>
     <row r="54" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="38" t="s">
+      <c r="A54" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="38" t="s">
+      <c r="B54" s="35" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -10869,7 +10973,7 @@
     </row>
     <row r="58" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="30"/>
-      <c r="B58" s="38" t="s">
+      <c r="B58" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -10899,7 +11003,7 @@
     </row>
     <row r="62" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="30"/>
-      <c r="B62" s="38" t="s">
+      <c r="B62" s="35" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -11114,6 +11218,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="B9:B12"/>
@@ -11130,7 +11235,6 @@
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="B50:B52"/>
-    <mergeCell ref="A66:A69"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12840,7 +12944,7 @@
     </row>
     <row r="32" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="29"/>
-      <c r="B32" s="35" t="s">
+      <c r="B32" s="36" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -12915,7 +13019,7 @@
     </row>
     <row r="33" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="29"/>
-      <c r="B33" s="36"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -13010,7 +13114,7 @@
     </row>
     <row r="34" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="29"/>
-      <c r="B34" s="36"/>
+      <c r="B34" s="37"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -13083,7 +13187,7 @@
     </row>
     <row r="35" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="29"/>
-      <c r="B35" s="37"/>
+      <c r="B35" s="38"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
@@ -13163,7 +13267,7 @@
     </row>
     <row r="37" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="29"/>
-      <c r="B37" s="35" t="s">
+      <c r="B37" s="36" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -13238,7 +13342,7 @@
     </row>
     <row r="38" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="36"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -13333,7 +13437,7 @@
     </row>
     <row r="39" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="29"/>
-      <c r="B39" s="36"/>
+      <c r="B39" s="37"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -13406,7 +13510,7 @@
     </row>
     <row r="40" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="29"/>
-      <c r="B40" s="37"/>
+      <c r="B40" s="38"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
@@ -13486,7 +13590,7 @@
     </row>
     <row r="42" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="29"/>
-      <c r="B42" s="35" t="s">
+      <c r="B42" s="36" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -13583,7 +13687,7 @@
     </row>
     <row r="43" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="29"/>
-      <c r="B43" s="36"/>
+      <c r="B43" s="37"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -13656,7 +13760,7 @@
     </row>
     <row r="44" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="29"/>
-      <c r="B44" s="37"/>
+      <c r="B44" s="38"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
@@ -13734,7 +13838,7 @@
     </row>
     <row r="46" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="29"/>
-      <c r="B46" s="35" t="s">
+      <c r="B46" s="36" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -13743,14 +13847,14 @@
     </row>
     <row r="47" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="29"/>
-      <c r="B47" s="36"/>
+      <c r="B47" s="37"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="29"/>
-      <c r="B48" s="37"/>
+      <c r="B48" s="38"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
@@ -13764,7 +13868,7 @@
     </row>
     <row r="50" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="29"/>
-      <c r="B50" s="35" t="s">
+      <c r="B50" s="36" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -13861,7 +13965,7 @@
     </row>
     <row r="51" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="29"/>
-      <c r="B51" s="36"/>
+      <c r="B51" s="37"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -13956,7 +14060,7 @@
     </row>
     <row r="52" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="29"/>
-      <c r="B52" s="37"/>
+      <c r="B52" s="38"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -14055,10 +14159,10 @@
       <c r="C53" s="8"/>
     </row>
     <row r="54" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="38" t="s">
+      <c r="A54" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="38" t="s">
+      <c r="B54" s="35" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -14088,7 +14192,7 @@
     </row>
     <row r="58" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="30"/>
-      <c r="B58" s="38" t="s">
+      <c r="B58" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -14118,7 +14222,7 @@
     </row>
     <row r="62" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="30"/>
-      <c r="B62" s="38" t="s">
+      <c r="B62" s="35" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -14444,6 +14548,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="B9:B12"/>
@@ -14460,7 +14565,6 @@
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="B50:B52"/>
-    <mergeCell ref="A66:A69"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14804,7 +14908,7 @@
     </row>
     <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="29"/>
-      <c r="B30" s="35" t="s">
+      <c r="B30" s="36" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -14813,21 +14917,21 @@
     </row>
     <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="29"/>
-      <c r="B31" s="36"/>
+      <c r="B31" s="37"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="29"/>
-      <c r="B32" s="36"/>
+      <c r="B32" s="37"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="29"/>
-      <c r="B33" s="37"/>
+      <c r="B33" s="38"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
@@ -14841,7 +14945,7 @@
     </row>
     <row r="35" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="29"/>
-      <c r="B35" s="35" t="s">
+      <c r="B35" s="36" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -14850,21 +14954,21 @@
     </row>
     <row r="36" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="29"/>
-      <c r="B36" s="36"/>
+      <c r="B36" s="37"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="29"/>
-      <c r="B37" s="36"/>
+      <c r="B37" s="37"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="37"/>
+      <c r="B38" s="38"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
@@ -14878,7 +14982,7 @@
     </row>
     <row r="40" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="29"/>
-      <c r="B40" s="35" t="s">
+      <c r="B40" s="36" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
@@ -14887,14 +14991,14 @@
     </row>
     <row r="41" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="29"/>
-      <c r="B41" s="36"/>
+      <c r="B41" s="37"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="29"/>
-      <c r="B42" s="37"/>
+      <c r="B42" s="38"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
@@ -14906,7 +15010,7 @@
     </row>
     <row r="44" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="29"/>
-      <c r="B44" s="35" t="s">
+      <c r="B44" s="36" t="s">
         <v>30</v>
       </c>
       <c r="C44" s="4">
@@ -14915,14 +15019,14 @@
     </row>
     <row r="45" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="29"/>
-      <c r="B45" s="36"/>
+      <c r="B45" s="37"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="29"/>
-      <c r="B46" s="37"/>
+      <c r="B46" s="38"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
@@ -14936,7 +15040,7 @@
     </row>
     <row r="48" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="29"/>
-      <c r="B48" s="35" t="s">
+      <c r="B48" s="36" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="4" t="s">
@@ -15005,7 +15109,7 @@
     </row>
     <row r="49" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="29"/>
-      <c r="B49" s="36"/>
+      <c r="B49" s="37"/>
       <c r="C49" s="4" t="s">
         <v>129</v>
       </c>
@@ -15072,7 +15176,7 @@
     </row>
     <row r="50" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="29"/>
-      <c r="B50" s="37"/>
+      <c r="B50" s="38"/>
       <c r="C50" s="4" t="s">
         <v>130</v>
       </c>
@@ -15143,10 +15247,10 @@
       <c r="C51" s="8"/>
     </row>
     <row r="52" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="38" t="s">
+      <c r="A52" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="B52" s="38" t="s">
+      <c r="B52" s="35" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="5" t="s">
@@ -15176,7 +15280,7 @@
     </row>
     <row r="56" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="30"/>
-      <c r="B56" s="38" t="s">
+      <c r="B56" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C56" s="5">
@@ -15206,7 +15310,7 @@
     </row>
     <row r="60" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="30"/>
-      <c r="B60" s="38" t="s">
+      <c r="B60" s="35" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
@@ -15280,6 +15384,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A64:A67"/>
     <mergeCell ref="A7:A18"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B7:B10"/>
@@ -15296,7 +15401,6 @@
     <mergeCell ref="B35:B38"/>
     <mergeCell ref="B40:B42"/>
     <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A64:A67"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15306,27 +15410,27 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC6F473E-E8F6-46BD-8C8C-636A58FA8F6F}">
-  <dimension ref="A1:AF67"/>
+  <dimension ref="A1:AI67"/>
   <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="16.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="2"/>
     </row>
-    <row r="4" spans="1:32" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:35" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -15348,31 +15452,86 @@
       <c r="I4" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="1"/>
-      <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
-      <c r="AF4" s="1"/>
-    </row>
-    <row r="5" spans="1:32" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J4" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="AG4" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="AH4" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="AI4" s="11" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
@@ -15396,7 +15555,6 @@
       <c r="I5" s="1">
         <v>3</v>
       </c>
-      <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -15420,7 +15578,7 @@
       <c r="AE5" s="1"/>
       <c r="AF5" s="1"/>
     </row>
-    <row r="6" spans="1:32" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
@@ -15468,7 +15626,7 @@
       <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
     </row>
-    <row r="7" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="28" t="s">
         <v>137</v>
       </c>
@@ -15479,28 +15637,28 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="28"/>
       <c r="B8" s="26"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="28"/>
       <c r="B9" s="26"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="28"/>
       <c r="B10" s="26"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="28"/>
       <c r="B11" s="26" t="s">
         <v>30</v>
@@ -15509,24 +15667,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="28"/>
       <c r="B12" s="26"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="28"/>
       <c r="B13" s="26"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:32" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="28"/>
     </row>
-    <row r="15" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="28"/>
       <c r="B15" s="32" t="s">
         <v>1</v>
@@ -15535,7 +15693,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="28"/>
       <c r="B16" s="33"/>
       <c r="C16" s="3" t="s">
@@ -15640,7 +15798,7 @@
     </row>
     <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="29"/>
-      <c r="B30" s="35" t="s">
+      <c r="B30" s="36" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -15649,21 +15807,21 @@
     </row>
     <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="29"/>
-      <c r="B31" s="36"/>
+      <c r="B31" s="37"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="29"/>
-      <c r="B32" s="36"/>
+      <c r="B32" s="37"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="29"/>
-      <c r="B33" s="37"/>
+      <c r="B33" s="38"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
@@ -15677,7 +15835,7 @@
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="29"/>
-      <c r="B35" s="35" t="s">
+      <c r="B35" s="36" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -15686,21 +15844,21 @@
     </row>
     <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="29"/>
-      <c r="B36" s="36"/>
+      <c r="B36" s="37"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="29"/>
-      <c r="B37" s="36"/>
+      <c r="B37" s="37"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="37"/>
+      <c r="B38" s="38"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
@@ -15714,7 +15872,7 @@
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="29"/>
-      <c r="B40" s="35" t="s">
+      <c r="B40" s="36" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
@@ -15723,14 +15881,14 @@
     </row>
     <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="29"/>
-      <c r="B41" s="36"/>
+      <c r="B41" s="37"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="29"/>
-      <c r="B42" s="37"/>
+      <c r="B42" s="38"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
@@ -15742,7 +15900,7 @@
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="29"/>
-      <c r="B44" s="35" t="s">
+      <c r="B44" s="36" t="s">
         <v>30</v>
       </c>
       <c r="C44" s="4">
@@ -15751,14 +15909,14 @@
     </row>
     <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="29"/>
-      <c r="B45" s="36"/>
+      <c r="B45" s="37"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="29"/>
-      <c r="B46" s="37"/>
+      <c r="B46" s="38"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
@@ -15772,7 +15930,7 @@
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="29"/>
-      <c r="B48" s="35" t="s">
+      <c r="B48" s="36" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="4" t="s">
@@ -15837,7 +15995,7 @@
     </row>
     <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="29"/>
-      <c r="B49" s="36"/>
+      <c r="B49" s="37"/>
       <c r="C49" s="4" t="s">
         <v>129</v>
       </c>
@@ -15900,7 +16058,7 @@
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="29"/>
-      <c r="B50" s="37"/>
+      <c r="B50" s="38"/>
       <c r="C50" s="4" t="s">
         <v>130</v>
       </c>
@@ -15967,10 +16125,10 @@
       <c r="C51" s="8"/>
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="38" t="s">
+      <c r="A52" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="B52" s="38" t="s">
+      <c r="B52" s="35" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="5" t="s">
@@ -16000,7 +16158,7 @@
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="30"/>
-      <c r="B56" s="38" t="s">
+      <c r="B56" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C56" s="5">
@@ -16030,7 +16188,7 @@
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="30"/>
-      <c r="B60" s="38" t="s">
+      <c r="B60" s="35" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
@@ -16092,6 +16250,13 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A64:A67"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A52:A62"/>
+    <mergeCell ref="B52:B55"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="B60:B62"/>
     <mergeCell ref="A7:A18"/>
     <mergeCell ref="B7:B10"/>
     <mergeCell ref="B11:B13"/>
@@ -16102,13 +16267,6 @@
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="B35:B38"/>
     <mergeCell ref="B40:B42"/>
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A52:A62"/>
-    <mergeCell ref="B52:B55"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B60:B62"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dev_stuffs/3匠魂.xlsx
+++ b/dev_stuffs/3匠魂.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\Palmon\dev_stuffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02BEAED1-B2FD-4C4E-B9CE-1AC3EB85EEF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9BC20B-B2EB-4868-9BB6-0EE3697DEB84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13185" yWindow="2595" windowWidth="23940" windowHeight="15435" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8685" yWindow="2400" windowWidth="24015" windowHeight="15435" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="阶段1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="274">
   <si>
     <t>材料名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -922,6 +922,30 @@
   </si>
   <si>
     <t>锑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>木</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>岩石</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>燧石</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>骨头</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>铜</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫菘</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1172,30 +1196,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1221,6 +1221,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
@@ -1696,10 +1720,10 @@
       </c>
     </row>
     <row r="9" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -1737,8 +1761,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="26"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -1774,8 +1798,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="26"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -1811,8 +1835,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="26"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -1848,8 +1872,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="26" t="s">
+      <c r="A13" s="20"/>
+      <c r="B13" s="18" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -1857,25 +1881,25 @@
       </c>
     </row>
     <row r="14" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-      <c r="B14" s="26"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="18"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="26"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="18"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
+      <c r="A16" s="20"/>
     </row>
     <row r="17" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28"/>
-      <c r="B17" s="32" t="s">
+      <c r="A17" s="20"/>
+      <c r="B17" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -1913,8 +1937,8 @@
       </c>
     </row>
     <row r="18" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28"/>
-      <c r="B18" s="33"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1950,8 +1974,8 @@
       </c>
     </row>
     <row r="19" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="28"/>
-      <c r="B19" s="33"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="25"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -1987,8 +2011,8 @@
       </c>
     </row>
     <row r="20" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28"/>
-      <c r="B20" s="34"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -2030,10 +2054,10 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="21" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -2071,8 +2095,8 @@
       </c>
     </row>
     <row r="23" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="25"/>
-      <c r="B23" s="29"/>
+      <c r="A23" s="34"/>
+      <c r="B23" s="21"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
       </c>
@@ -2118,8 +2142,8 @@
       </c>
     </row>
     <row r="24" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="25"/>
-      <c r="B24" s="29"/>
+      <c r="A24" s="34"/>
+      <c r="B24" s="21"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
       </c>
@@ -2155,22 +2179,22 @@
       </c>
     </row>
     <row r="25" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="25"/>
-      <c r="B25" s="29"/>
+      <c r="A25" s="34"/>
+      <c r="B25" s="21"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="25"/>
+      <c r="A26" s="34"/>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="25"/>
-      <c r="B27" s="29" t="s">
+      <c r="A27" s="34"/>
+      <c r="B27" s="21" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="4" t="s">
@@ -2208,8 +2232,8 @@
       </c>
     </row>
     <row r="28" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="25"/>
-      <c r="B28" s="29"/>
+      <c r="A28" s="34"/>
+      <c r="B28" s="21"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
       </c>
@@ -2255,8 +2279,8 @@
       </c>
     </row>
     <row r="29" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="25"/>
-      <c r="B29" s="29"/>
+      <c r="A29" s="34"/>
+      <c r="B29" s="21"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
       </c>
@@ -2292,22 +2316,22 @@
       </c>
     </row>
     <row r="30" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="25"/>
-      <c r="B30" s="29"/>
+      <c r="A30" s="34"/>
+      <c r="B30" s="21"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="25"/>
+      <c r="A31" s="34"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="25"/>
-      <c r="B32" s="18" t="s">
+      <c r="A32" s="34"/>
+      <c r="B32" s="27" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -2345,8 +2369,8 @@
       </c>
     </row>
     <row r="33" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="25"/>
-      <c r="B33" s="19"/>
+      <c r="A33" s="34"/>
+      <c r="B33" s="28"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -2392,8 +2416,8 @@
       </c>
     </row>
     <row r="34" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="25"/>
-      <c r="B34" s="19"/>
+      <c r="A34" s="34"/>
+      <c r="B34" s="28"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -2429,22 +2453,22 @@
       </c>
     </row>
     <row r="35" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="25"/>
-      <c r="B35" s="20"/>
+      <c r="A35" s="34"/>
+      <c r="B35" s="29"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="25"/>
+      <c r="A36" s="34"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="25"/>
-      <c r="B37" s="18" t="s">
+      <c r="A37" s="34"/>
+      <c r="B37" s="27" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -2482,8 +2506,8 @@
       </c>
     </row>
     <row r="38" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="25"/>
-      <c r="B38" s="19"/>
+      <c r="A38" s="34"/>
+      <c r="B38" s="28"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -2529,8 +2553,8 @@
       </c>
     </row>
     <row r="39" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="25"/>
-      <c r="B39" s="19"/>
+      <c r="A39" s="34"/>
+      <c r="B39" s="28"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -2566,22 +2590,22 @@
       </c>
     </row>
     <row r="40" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="25"/>
-      <c r="B40" s="20"/>
+      <c r="A40" s="34"/>
+      <c r="B40" s="29"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="25"/>
+      <c r="A41" s="34"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="25"/>
-      <c r="B42" s="18" t="s">
+      <c r="A42" s="34"/>
+      <c r="B42" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -2629,8 +2653,8 @@
       </c>
     </row>
     <row r="43" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="25"/>
-      <c r="B43" s="19"/>
+      <c r="A43" s="34"/>
+      <c r="B43" s="28"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -2666,18 +2690,18 @@
       </c>
     </row>
     <row r="44" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="25"/>
-      <c r="B44" s="20"/>
+      <c r="A44" s="34"/>
+      <c r="B44" s="29"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="25"/>
+      <c r="A45" s="34"/>
     </row>
     <row r="46" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="25"/>
-      <c r="B46" s="18" t="s">
+      <c r="A46" s="34"/>
+      <c r="B46" s="27" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -2685,29 +2709,29 @@
       </c>
     </row>
     <row r="47" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="25"/>
-      <c r="B47" s="19"/>
+      <c r="A47" s="34"/>
+      <c r="B47" s="28"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="25"/>
-      <c r="B48" s="20"/>
+      <c r="A48" s="34"/>
+      <c r="B48" s="29"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="25"/>
+      <c r="A49" s="34"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
     </row>
     <row r="50" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="25"/>
-      <c r="B50" s="18" t="s">
+      <c r="A50" s="34"/>
+      <c r="B50" s="27" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -2755,8 +2779,8 @@
       </c>
     </row>
     <row r="51" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="25"/>
-      <c r="B51" s="19"/>
+      <c r="A51" s="34"/>
+      <c r="B51" s="28"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -2802,8 +2826,8 @@
       </c>
     </row>
     <row r="52" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="25"/>
-      <c r="B52" s="20"/>
+      <c r="A52" s="34"/>
+      <c r="B52" s="29"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -2855,10 +2879,10 @@
       <c r="E53" s="8"/>
     </row>
     <row r="54" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="27" t="s">
+      <c r="A54" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="27" t="s">
+      <c r="B54" s="19" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -2866,29 +2890,29 @@
       </c>
     </row>
     <row r="55" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="27"/>
-      <c r="B55" s="27"/>
+      <c r="A55" s="19"/>
+      <c r="B55" s="19"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="27"/>
-      <c r="B56" s="27"/>
+      <c r="A56" s="19"/>
+      <c r="B56" s="19"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="27"/>
-      <c r="B57" s="27"/>
+      <c r="A57" s="19"/>
+      <c r="B57" s="19"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="27"/>
-      <c r="B58" s="27" t="s">
+      <c r="A58" s="19"/>
+      <c r="B58" s="19" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -2896,29 +2920,29 @@
       </c>
     </row>
     <row r="59" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="27"/>
-      <c r="B59" s="30"/>
+      <c r="A59" s="19"/>
+      <c r="B59" s="22"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="27"/>
-      <c r="B60" s="31"/>
+      <c r="A60" s="19"/>
+      <c r="B60" s="23"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="27"/>
+      <c r="A61" s="19"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="27"/>
-      <c r="B62" s="27" t="s">
+      <c r="A62" s="19"/>
+      <c r="B62" s="19" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -2926,21 +2950,21 @@
       </c>
     </row>
     <row r="63" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="27"/>
-      <c r="B63" s="30"/>
+      <c r="A63" s="19"/>
+      <c r="B63" s="22"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="27"/>
-      <c r="B64" s="31"/>
+      <c r="A64" s="19"/>
+      <c r="B64" s="23"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="21" t="s">
+      <c r="A67" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B67" s="6" t="s">
@@ -2981,7 +3005,7 @@
       </c>
     </row>
     <row r="68" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="22"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="4" t="s">
         <v>132</v>
       </c>
@@ -3020,7 +3044,7 @@
       </c>
     </row>
     <row r="69" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="22"/>
+      <c r="A69" s="31"/>
       <c r="B69" s="4" t="s">
         <v>133</v>
       </c>
@@ -3059,7 +3083,7 @@
       </c>
     </row>
     <row r="70" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="23"/>
+      <c r="A70" s="32"/>
       <c r="B70" s="5" t="s">
         <v>134</v>
       </c>
@@ -3099,6 +3123,9 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="A22:A52"/>
     <mergeCell ref="B13:B15"/>
     <mergeCell ref="A54:A64"/>
     <mergeCell ref="A9:A20"/>
@@ -3113,9 +3140,6 @@
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="B50:B52"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="A22:A52"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3385,10 +3409,10 @@
       </c>
     </row>
     <row r="9" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -3438,8 +3462,8 @@
       </c>
     </row>
     <row r="10" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="26"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -3487,8 +3511,8 @@
       </c>
     </row>
     <row r="11" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="26"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -3536,8 +3560,8 @@
       </c>
     </row>
     <row r="12" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="26"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -3585,8 +3609,8 @@
       </c>
     </row>
     <row r="13" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="26" t="s">
+      <c r="A13" s="20"/>
+      <c r="B13" s="18" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -3594,25 +3618,25 @@
       </c>
     </row>
     <row r="14" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-      <c r="B14" s="26"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="18"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="26"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="18"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
+      <c r="A16" s="20"/>
     </row>
     <row r="17" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28"/>
-      <c r="B17" s="32" t="s">
+      <c r="A17" s="20"/>
+      <c r="B17" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -3662,8 +3686,8 @@
       </c>
     </row>
     <row r="18" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28"/>
-      <c r="B18" s="33"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -3711,8 +3735,8 @@
       </c>
     </row>
     <row r="19" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="28"/>
-      <c r="B19" s="33"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="25"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -3760,8 +3784,8 @@
       </c>
     </row>
     <row r="20" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28"/>
-      <c r="B20" s="34"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -3815,7 +3839,7 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="21" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="39" t="s">
@@ -3868,7 +3892,7 @@
       </c>
     </row>
     <row r="23" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="29"/>
+      <c r="A23" s="21"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -3931,7 +3955,7 @@
       </c>
     </row>
     <row r="24" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="29"/>
+      <c r="A24" s="21"/>
       <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -3980,7 +4004,7 @@
       </c>
     </row>
     <row r="25" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="29"/>
+      <c r="A25" s="21"/>
       <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -4011,14 +4035,14 @@
       </c>
     </row>
     <row r="26" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="29"/>
+      <c r="A26" s="21"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="29"/>
+      <c r="A27" s="21"/>
       <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
@@ -4069,7 +4093,7 @@
       </c>
     </row>
     <row r="28" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="29"/>
+      <c r="A28" s="21"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -4132,7 +4156,7 @@
       </c>
     </row>
     <row r="29" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="29"/>
+      <c r="A29" s="21"/>
       <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -4181,7 +4205,7 @@
       </c>
     </row>
     <row r="30" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="29"/>
+      <c r="A30" s="21"/>
       <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -4212,14 +4236,14 @@
       </c>
     </row>
     <row r="31" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="29"/>
+      <c r="A31" s="21"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="29"/>
+      <c r="A32" s="21"/>
       <c r="B32" s="36" t="s">
         <v>17</v>
       </c>
@@ -4270,7 +4294,7 @@
       </c>
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="29"/>
+      <c r="A33" s="21"/>
       <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
@@ -4333,7 +4357,7 @@
       </c>
     </row>
     <row r="34" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="29"/>
+      <c r="A34" s="21"/>
       <c r="B34" s="37"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
@@ -4382,7 +4406,7 @@
       </c>
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="29"/>
+      <c r="A35" s="21"/>
       <c r="B35" s="38"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
@@ -4413,14 +4437,14 @@
       </c>
     </row>
     <row r="36" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="29"/>
+      <c r="A36" s="21"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="29"/>
+      <c r="A37" s="21"/>
       <c r="B37" s="36" t="s">
         <v>18</v>
       </c>
@@ -4471,7 +4495,7 @@
       </c>
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="29"/>
+      <c r="A38" s="21"/>
       <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
@@ -4534,7 +4558,7 @@
       </c>
     </row>
     <row r="39" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="29"/>
+      <c r="A39" s="21"/>
       <c r="B39" s="37"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
@@ -4583,7 +4607,7 @@
       </c>
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="29"/>
+      <c r="A40" s="21"/>
       <c r="B40" s="38"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
@@ -4614,14 +4638,14 @@
       </c>
     </row>
     <row r="41" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="29"/>
+      <c r="A41" s="21"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="29"/>
+      <c r="A42" s="21"/>
       <c r="B42" s="36" t="s">
         <v>19</v>
       </c>
@@ -4686,7 +4710,7 @@
       </c>
     </row>
     <row r="43" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="29"/>
+      <c r="A43" s="21"/>
       <c r="B43" s="37"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
@@ -4735,7 +4759,7 @@
       </c>
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="29"/>
+      <c r="A44" s="21"/>
       <c r="B44" s="38"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
@@ -4766,12 +4790,12 @@
       </c>
     </row>
     <row r="45" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="29"/>
+      <c r="A45" s="21"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="29"/>
+      <c r="A46" s="21"/>
       <c r="B46" s="36" t="s">
         <v>30</v>
       </c>
@@ -4780,28 +4804,28 @@
       </c>
     </row>
     <row r="47" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="29"/>
+      <c r="A47" s="21"/>
       <c r="B47" s="37"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="29"/>
+      <c r="A48" s="21"/>
       <c r="B48" s="38"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="29"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="29"/>
+      <c r="A50" s="21"/>
       <c r="B50" s="36" t="s">
         <v>28</v>
       </c>
@@ -4866,7 +4890,7 @@
       </c>
     </row>
     <row r="51" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="29"/>
+      <c r="A51" s="21"/>
       <c r="B51" s="37"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
@@ -4929,7 +4953,7 @@
       </c>
     </row>
     <row r="52" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="29"/>
+      <c r="A52" s="21"/>
       <c r="B52" s="38"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
@@ -5008,28 +5032,28 @@
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="30"/>
-      <c r="B55" s="30"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="30"/>
-      <c r="B56" s="30"/>
+      <c r="A56" s="22"/>
+      <c r="B56" s="22"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="30"/>
-      <c r="B57" s="31"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="23"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="30"/>
+      <c r="A58" s="22"/>
       <c r="B58" s="35" t="s">
         <v>30</v>
       </c>
@@ -5038,28 +5062,28 @@
       </c>
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="30"/>
-      <c r="B59" s="30"/>
+      <c r="A59" s="22"/>
+      <c r="B59" s="22"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="30"/>
-      <c r="B60" s="31"/>
+      <c r="A60" s="22"/>
+      <c r="B60" s="23"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="30"/>
+      <c r="A61" s="22"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="30"/>
+      <c r="A62" s="22"/>
       <c r="B62" s="35" t="s">
         <v>25</v>
       </c>
@@ -5068,22 +5092,22 @@
       </c>
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="30"/>
-      <c r="B63" s="30"/>
+      <c r="A63" s="22"/>
+      <c r="B63" s="22"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="31"/>
-      <c r="B64" s="31"/>
+      <c r="A64" s="23"/>
+      <c r="B64" s="23"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="21" t="s">
+      <c r="A66" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -5136,7 +5160,7 @@
       </c>
     </row>
     <row r="67" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="22"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -5181,7 +5205,7 @@
       </c>
     </row>
     <row r="68" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="22"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -5226,7 +5250,7 @@
       </c>
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="23"/>
+      <c r="A69" s="32"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -5236,6 +5260,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A54:A64"/>
     <mergeCell ref="B54:B57"/>
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="B50:B52"/>
@@ -5252,7 +5277,6 @@
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="B42:B44"/>
-    <mergeCell ref="A54:A64"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5736,10 +5760,10 @@
       </c>
     </row>
     <row r="9" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -5831,8 +5855,8 @@
       </c>
     </row>
     <row r="10" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="26"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -5922,8 +5946,8 @@
       </c>
     </row>
     <row r="11" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="26"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -6013,8 +6037,8 @@
       </c>
     </row>
     <row r="12" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="26"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -6104,8 +6128,8 @@
       </c>
     </row>
     <row r="13" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="26" t="s">
+      <c r="A13" s="20"/>
+      <c r="B13" s="18" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -6113,25 +6137,25 @@
       </c>
     </row>
     <row r="14" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-      <c r="B14" s="26"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="18"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="26"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="18"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
+      <c r="A16" s="20"/>
     </row>
     <row r="17" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28"/>
-      <c r="B17" s="32" t="s">
+      <c r="A17" s="20"/>
+      <c r="B17" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -6223,8 +6247,8 @@
       </c>
     </row>
     <row r="18" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28"/>
-      <c r="B18" s="33"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -6314,8 +6338,8 @@
       </c>
     </row>
     <row r="19" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="28"/>
-      <c r="B19" s="33"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="25"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -6405,8 +6429,8 @@
       </c>
     </row>
     <row r="20" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28"/>
-      <c r="B20" s="34"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -6505,7 +6529,7 @@
       </c>
     </row>
     <row r="22" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="21" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="39" t="s">
@@ -6600,7 +6624,7 @@
       </c>
     </row>
     <row r="23" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="29"/>
+      <c r="A23" s="21"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -6719,7 +6743,7 @@
       </c>
     </row>
     <row r="24" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="29"/>
+      <c r="A24" s="21"/>
       <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -6810,7 +6834,7 @@
       </c>
     </row>
     <row r="25" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="29"/>
+      <c r="A25" s="21"/>
       <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -6901,14 +6925,14 @@
       </c>
     </row>
     <row r="26" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="29"/>
+      <c r="A26" s="21"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="29"/>
+      <c r="A27" s="21"/>
       <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
@@ -7001,7 +7025,7 @@
       </c>
     </row>
     <row r="28" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="29"/>
+      <c r="A28" s="21"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -7120,7 +7144,7 @@
       </c>
     </row>
     <row r="29" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="29"/>
+      <c r="A29" s="21"/>
       <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -7211,7 +7235,7 @@
       </c>
     </row>
     <row r="30" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="29"/>
+      <c r="A30" s="21"/>
       <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -7302,14 +7326,14 @@
       </c>
     </row>
     <row r="31" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="29"/>
+      <c r="A31" s="21"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="29"/>
+      <c r="A32" s="21"/>
       <c r="B32" s="36" t="s">
         <v>17</v>
       </c>
@@ -7402,7 +7426,7 @@
       </c>
     </row>
     <row r="33" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="29"/>
+      <c r="A33" s="21"/>
       <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
@@ -7521,7 +7545,7 @@
       </c>
     </row>
     <row r="34" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="29"/>
+      <c r="A34" s="21"/>
       <c r="B34" s="37"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
@@ -7612,7 +7636,7 @@
       </c>
     </row>
     <row r="35" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="29"/>
+      <c r="A35" s="21"/>
       <c r="B35" s="38"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
@@ -7703,14 +7727,14 @@
       </c>
     </row>
     <row r="36" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="29"/>
+      <c r="A36" s="21"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="29"/>
+      <c r="A37" s="21"/>
       <c r="B37" s="36" t="s">
         <v>18</v>
       </c>
@@ -7803,7 +7827,7 @@
       </c>
     </row>
     <row r="38" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="29"/>
+      <c r="A38" s="21"/>
       <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
@@ -7922,7 +7946,7 @@
       </c>
     </row>
     <row r="39" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="29"/>
+      <c r="A39" s="21"/>
       <c r="B39" s="37"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
@@ -8013,7 +8037,7 @@
       </c>
     </row>
     <row r="40" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="29"/>
+      <c r="A40" s="21"/>
       <c r="B40" s="38"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
@@ -8104,14 +8128,14 @@
       </c>
     </row>
     <row r="41" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="29"/>
+      <c r="A41" s="21"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="29"/>
+      <c r="A42" s="21"/>
       <c r="B42" s="36" t="s">
         <v>19</v>
       </c>
@@ -8120,7 +8144,7 @@
       </c>
     </row>
     <row r="43" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="29"/>
+      <c r="A43" s="21"/>
       <c r="B43" s="37"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
@@ -8211,7 +8235,7 @@
       </c>
     </row>
     <row r="44" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="29"/>
+      <c r="A44" s="21"/>
       <c r="B44" s="38"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
@@ -8302,12 +8326,12 @@
       </c>
     </row>
     <row r="45" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="29"/>
+      <c r="A45" s="21"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
     </row>
     <row r="46" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="29"/>
+      <c r="A46" s="21"/>
       <c r="B46" s="36" t="s">
         <v>30</v>
       </c>
@@ -8316,28 +8340,28 @@
       </c>
     </row>
     <row r="47" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="29"/>
+      <c r="A47" s="21"/>
       <c r="B47" s="37"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="29"/>
+      <c r="A48" s="21"/>
       <c r="B48" s="38"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="29"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="29"/>
+      <c r="A50" s="21"/>
       <c r="B50" s="36" t="s">
         <v>28</v>
       </c>
@@ -8458,7 +8482,7 @@
       </c>
     </row>
     <row r="51" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="29"/>
+      <c r="A51" s="21"/>
       <c r="B51" s="37"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
@@ -8577,7 +8601,7 @@
       </c>
     </row>
     <row r="52" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="29"/>
+      <c r="A52" s="21"/>
       <c r="B52" s="38"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
@@ -8712,28 +8736,28 @@
       </c>
     </row>
     <row r="55" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="30"/>
-      <c r="B55" s="30"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="30"/>
-      <c r="B56" s="30"/>
+      <c r="A56" s="22"/>
+      <c r="B56" s="22"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="30"/>
-      <c r="B57" s="31"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="23"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="30"/>
+      <c r="A58" s="22"/>
       <c r="B58" s="35" t="s">
         <v>30</v>
       </c>
@@ -8742,28 +8766,28 @@
       </c>
     </row>
     <row r="59" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="30"/>
-      <c r="B59" s="30"/>
+      <c r="A59" s="22"/>
+      <c r="B59" s="22"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="30"/>
-      <c r="B60" s="31"/>
+      <c r="A60" s="22"/>
+      <c r="B60" s="23"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="30"/>
+      <c r="A61" s="22"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="30"/>
+      <c r="A62" s="22"/>
       <c r="B62" s="35" t="s">
         <v>25</v>
       </c>
@@ -8772,22 +8796,22 @@
       </c>
     </row>
     <row r="63" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="30"/>
-      <c r="B63" s="30"/>
+      <c r="A63" s="22"/>
+      <c r="B63" s="22"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="31"/>
-      <c r="B64" s="31"/>
+      <c r="A64" s="23"/>
+      <c r="B64" s="23"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:31" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="21" t="s">
+      <c r="A66" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -8882,7 +8906,7 @@
       </c>
     </row>
     <row r="67" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="22"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -8975,7 +8999,7 @@
       </c>
     </row>
     <row r="68" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="22"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -9068,7 +9092,7 @@
       </c>
     </row>
     <row r="69" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="23"/>
+      <c r="A69" s="32"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -9162,6 +9186,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B50:B52"/>
     <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="B58:B60"/>
@@ -9178,7 +9203,6 @@
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B50:B52"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9421,10 +9445,10 @@
       </c>
     </row>
     <row r="9" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -9468,8 +9492,8 @@
       </c>
     </row>
     <row r="10" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="26"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -9511,8 +9535,8 @@
       </c>
     </row>
     <row r="11" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="26"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -9554,8 +9578,8 @@
       </c>
     </row>
     <row r="12" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="26"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -9597,8 +9621,8 @@
       </c>
     </row>
     <row r="13" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="26" t="s">
+      <c r="A13" s="20"/>
+      <c r="B13" s="18" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -9606,25 +9630,25 @@
       </c>
     </row>
     <row r="14" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-      <c r="B14" s="26"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="18"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="26"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="18"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
+      <c r="A16" s="20"/>
     </row>
     <row r="17" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28"/>
-      <c r="B17" s="32" t="s">
+      <c r="A17" s="20"/>
+      <c r="B17" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -9668,8 +9692,8 @@
       </c>
     </row>
     <row r="18" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28"/>
-      <c r="B18" s="33"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -9711,8 +9735,8 @@
       </c>
     </row>
     <row r="19" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="28"/>
-      <c r="B19" s="33"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="25"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -9754,8 +9778,8 @@
       </c>
     </row>
     <row r="20" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28"/>
-      <c r="B20" s="34"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -9803,7 +9827,7 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="21" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="39" t="s">
@@ -9850,7 +9874,7 @@
       </c>
     </row>
     <row r="23" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="29"/>
+      <c r="A23" s="21"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -9905,7 +9929,7 @@
       </c>
     </row>
     <row r="24" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="29"/>
+      <c r="A24" s="21"/>
       <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -9948,7 +9972,7 @@
       </c>
     </row>
     <row r="25" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="29"/>
+      <c r="A25" s="21"/>
       <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -9991,14 +10015,14 @@
       </c>
     </row>
     <row r="26" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="29"/>
+      <c r="A26" s="21"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="29"/>
+      <c r="A27" s="21"/>
       <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
@@ -10043,7 +10067,7 @@
       </c>
     </row>
     <row r="28" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="29"/>
+      <c r="A28" s="21"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -10098,7 +10122,7 @@
       </c>
     </row>
     <row r="29" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="29"/>
+      <c r="A29" s="21"/>
       <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -10141,7 +10165,7 @@
       </c>
     </row>
     <row r="30" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="29"/>
+      <c r="A30" s="21"/>
       <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -10184,14 +10208,14 @@
       </c>
     </row>
     <row r="31" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="29"/>
+      <c r="A31" s="21"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="29"/>
+      <c r="A32" s="21"/>
       <c r="B32" s="36" t="s">
         <v>17</v>
       </c>
@@ -10236,7 +10260,7 @@
       </c>
     </row>
     <row r="33" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="29"/>
+      <c r="A33" s="21"/>
       <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
@@ -10291,7 +10315,7 @@
       </c>
     </row>
     <row r="34" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="29"/>
+      <c r="A34" s="21"/>
       <c r="B34" s="37"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
@@ -10334,7 +10358,7 @@
       </c>
     </row>
     <row r="35" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="29"/>
+      <c r="A35" s="21"/>
       <c r="B35" s="38"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
@@ -10377,14 +10401,14 @@
       </c>
     </row>
     <row r="36" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="29"/>
+      <c r="A36" s="21"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="29"/>
+      <c r="A37" s="21"/>
       <c r="B37" s="36" t="s">
         <v>18</v>
       </c>
@@ -10429,7 +10453,7 @@
       </c>
     </row>
     <row r="38" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="29"/>
+      <c r="A38" s="21"/>
       <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
@@ -10484,7 +10508,7 @@
       </c>
     </row>
     <row r="39" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="29"/>
+      <c r="A39" s="21"/>
       <c r="B39" s="37"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
@@ -10527,7 +10551,7 @@
       </c>
     </row>
     <row r="40" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="29"/>
+      <c r="A40" s="21"/>
       <c r="B40" s="38"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
@@ -10570,14 +10594,14 @@
       </c>
     </row>
     <row r="41" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="29"/>
+      <c r="A41" s="21"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="29"/>
+      <c r="A42" s="21"/>
       <c r="B42" s="36" t="s">
         <v>19</v>
       </c>
@@ -10634,7 +10658,7 @@
       </c>
     </row>
     <row r="43" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="29"/>
+      <c r="A43" s="21"/>
       <c r="B43" s="37"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
@@ -10677,7 +10701,7 @@
       </c>
     </row>
     <row r="44" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="29"/>
+      <c r="A44" s="21"/>
       <c r="B44" s="38"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
@@ -10720,13 +10744,13 @@
       </c>
     </row>
     <row r="45" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="29"/>
+      <c r="A45" s="21"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
       <c r="F45" s="17"/>
     </row>
     <row r="46" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="29"/>
+      <c r="A46" s="21"/>
       <c r="B46" s="36" t="s">
         <v>30</v>
       </c>
@@ -10735,28 +10759,28 @@
       </c>
     </row>
     <row r="47" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="29"/>
+      <c r="A47" s="21"/>
       <c r="B47" s="37"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="29"/>
+      <c r="A48" s="21"/>
       <c r="B48" s="38"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="29"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="29"/>
+      <c r="A50" s="21"/>
       <c r="B50" s="36" t="s">
         <v>28</v>
       </c>
@@ -10813,7 +10837,7 @@
       </c>
     </row>
     <row r="51" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="29"/>
+      <c r="A51" s="21"/>
       <c r="B51" s="37"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
@@ -10868,7 +10892,7 @@
       </c>
     </row>
     <row r="52" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="29"/>
+      <c r="A52" s="21"/>
       <c r="B52" s="38"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
@@ -10942,8 +10966,8 @@
       </c>
     </row>
     <row r="55" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="30"/>
-      <c r="B55" s="30"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
@@ -10952,8 +10976,8 @@
       </c>
     </row>
     <row r="56" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="30"/>
-      <c r="B56" s="30"/>
+      <c r="A56" s="22"/>
+      <c r="B56" s="22"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
@@ -10962,8 +10986,8 @@
       </c>
     </row>
     <row r="57" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="30"/>
-      <c r="B57" s="31"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="23"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
@@ -10972,7 +10996,7 @@
       </c>
     </row>
     <row r="58" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="30"/>
+      <c r="A58" s="22"/>
       <c r="B58" s="35" t="s">
         <v>30</v>
       </c>
@@ -10981,28 +11005,28 @@
       </c>
     </row>
     <row r="59" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="30"/>
-      <c r="B59" s="30"/>
+      <c r="A59" s="22"/>
+      <c r="B59" s="22"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="30"/>
-      <c r="B60" s="31"/>
+      <c r="A60" s="22"/>
+      <c r="B60" s="23"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="30"/>
+      <c r="A61" s="22"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="30"/>
+      <c r="A62" s="22"/>
       <c r="B62" s="35" t="s">
         <v>25</v>
       </c>
@@ -11014,8 +11038,8 @@
       </c>
     </row>
     <row r="63" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="30"/>
-      <c r="B63" s="30"/>
+      <c r="A63" s="22"/>
+      <c r="B63" s="22"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
@@ -11024,8 +11048,8 @@
       </c>
     </row>
     <row r="64" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="31"/>
-      <c r="B64" s="31"/>
+      <c r="A64" s="23"/>
+      <c r="B64" s="23"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
@@ -11035,7 +11059,7 @@
     </row>
     <row r="65" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="21" t="s">
+      <c r="A66" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -11082,7 +11106,7 @@
       </c>
     </row>
     <row r="67" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="22"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -11127,7 +11151,7 @@
       </c>
     </row>
     <row r="68" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="22"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -11172,7 +11196,7 @@
       </c>
     </row>
     <row r="69" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="23"/>
+      <c r="A69" s="32"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -11218,6 +11242,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B50:B52"/>
     <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="B58:B60"/>
@@ -11234,7 +11259,6 @@
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B50:B52"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11673,10 +11697,10 @@
       <c r="AA8" s="1"/>
     </row>
     <row r="9" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -11750,8 +11774,8 @@
       </c>
     </row>
     <row r="10" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="26"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -11823,8 +11847,8 @@
       </c>
     </row>
     <row r="11" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="26"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -11896,8 +11920,8 @@
       </c>
     </row>
     <row r="12" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="26"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -11969,8 +11993,8 @@
       </c>
     </row>
     <row r="13" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="26" t="s">
+      <c r="A13" s="20"/>
+      <c r="B13" s="18" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -11978,25 +12002,25 @@
       </c>
     </row>
     <row r="14" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-      <c r="B14" s="26"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="18"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="26"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="18"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:27" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
+      <c r="A16" s="20"/>
     </row>
     <row r="17" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28"/>
-      <c r="B17" s="32" t="s">
+      <c r="A17" s="20"/>
+      <c r="B17" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -12070,8 +12094,8 @@
       </c>
     </row>
     <row r="18" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28"/>
-      <c r="B18" s="33"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -12143,8 +12167,8 @@
       </c>
     </row>
     <row r="19" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="28"/>
-      <c r="B19" s="33"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="25"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -12216,8 +12240,8 @@
       </c>
     </row>
     <row r="20" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28"/>
-      <c r="B20" s="34"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -12295,7 +12319,7 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="21" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="39" t="s">
@@ -12372,7 +12396,7 @@
       </c>
     </row>
     <row r="23" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="29"/>
+      <c r="A23" s="21"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -12467,7 +12491,7 @@
       </c>
     </row>
     <row r="24" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="29"/>
+      <c r="A24" s="21"/>
       <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -12540,7 +12564,7 @@
       </c>
     </row>
     <row r="25" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="29"/>
+      <c r="A25" s="21"/>
       <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -12613,14 +12637,14 @@
       </c>
     </row>
     <row r="26" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="29"/>
+      <c r="A26" s="21"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="29"/>
+      <c r="A27" s="21"/>
       <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
@@ -12695,7 +12719,7 @@
       </c>
     </row>
     <row r="28" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="29"/>
+      <c r="A28" s="21"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -12790,7 +12814,7 @@
       </c>
     </row>
     <row r="29" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="29"/>
+      <c r="A29" s="21"/>
       <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -12863,7 +12887,7 @@
       </c>
     </row>
     <row r="30" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="29"/>
+      <c r="A30" s="21"/>
       <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -12936,14 +12960,14 @@
       </c>
     </row>
     <row r="31" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="29"/>
+      <c r="A31" s="21"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="29"/>
+      <c r="A32" s="21"/>
       <c r="B32" s="36" t="s">
         <v>17</v>
       </c>
@@ -13018,7 +13042,7 @@
       </c>
     </row>
     <row r="33" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="29"/>
+      <c r="A33" s="21"/>
       <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
@@ -13113,7 +13137,7 @@
       </c>
     </row>
     <row r="34" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="29"/>
+      <c r="A34" s="21"/>
       <c r="B34" s="37"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
@@ -13186,7 +13210,7 @@
       </c>
     </row>
     <row r="35" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="29"/>
+      <c r="A35" s="21"/>
       <c r="B35" s="38"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
@@ -13259,14 +13283,14 @@
       </c>
     </row>
     <row r="36" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="29"/>
+      <c r="A36" s="21"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="29"/>
+      <c r="A37" s="21"/>
       <c r="B37" s="36" t="s">
         <v>18</v>
       </c>
@@ -13341,7 +13365,7 @@
       </c>
     </row>
     <row r="38" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="29"/>
+      <c r="A38" s="21"/>
       <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
@@ -13436,7 +13460,7 @@
       </c>
     </row>
     <row r="39" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="29"/>
+      <c r="A39" s="21"/>
       <c r="B39" s="37"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
@@ -13509,7 +13533,7 @@
       </c>
     </row>
     <row r="40" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="29"/>
+      <c r="A40" s="21"/>
       <c r="B40" s="38"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
@@ -13582,14 +13606,14 @@
       </c>
     </row>
     <row r="41" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="29"/>
+      <c r="A41" s="21"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="29"/>
+      <c r="A42" s="21"/>
       <c r="B42" s="36" t="s">
         <v>19</v>
       </c>
@@ -13686,7 +13710,7 @@
       </c>
     </row>
     <row r="43" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="29"/>
+      <c r="A43" s="21"/>
       <c r="B43" s="37"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
@@ -13759,7 +13783,7 @@
       </c>
     </row>
     <row r="44" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="29"/>
+      <c r="A44" s="21"/>
       <c r="B44" s="38"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
@@ -13832,12 +13856,12 @@
       </c>
     </row>
     <row r="45" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="29"/>
+      <c r="A45" s="21"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
     </row>
     <row r="46" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="29"/>
+      <c r="A46" s="21"/>
       <c r="B46" s="36" t="s">
         <v>30</v>
       </c>
@@ -13846,28 +13870,28 @@
       </c>
     </row>
     <row r="47" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="29"/>
+      <c r="A47" s="21"/>
       <c r="B47" s="37"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="29"/>
+      <c r="A48" s="21"/>
       <c r="B48" s="38"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="29"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="29"/>
+      <c r="A50" s="21"/>
       <c r="B50" s="36" t="s">
         <v>28</v>
       </c>
@@ -13964,7 +13988,7 @@
       </c>
     </row>
     <row r="51" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="29"/>
+      <c r="A51" s="21"/>
       <c r="B51" s="37"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
@@ -14059,7 +14083,7 @@
       </c>
     </row>
     <row r="52" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="29"/>
+      <c r="A52" s="21"/>
       <c r="B52" s="38"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
@@ -14170,28 +14194,28 @@
       </c>
     </row>
     <row r="55" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="30"/>
-      <c r="B55" s="30"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="30"/>
-      <c r="B56" s="30"/>
+      <c r="A56" s="22"/>
+      <c r="B56" s="22"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="30"/>
-      <c r="B57" s="31"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="23"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="30"/>
+      <c r="A58" s="22"/>
       <c r="B58" s="35" t="s">
         <v>30</v>
       </c>
@@ -14200,28 +14224,28 @@
       </c>
     </row>
     <row r="59" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="30"/>
-      <c r="B59" s="30"/>
+      <c r="A59" s="22"/>
+      <c r="B59" s="22"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="30"/>
-      <c r="B60" s="31"/>
+      <c r="A60" s="22"/>
+      <c r="B60" s="23"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="30"/>
+      <c r="A61" s="22"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="30"/>
+      <c r="A62" s="22"/>
       <c r="B62" s="35" t="s">
         <v>25</v>
       </c>
@@ -14230,22 +14254,22 @@
       </c>
     </row>
     <row r="63" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="30"/>
-      <c r="B63" s="30"/>
+      <c r="A63" s="22"/>
+      <c r="B63" s="22"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="31"/>
-      <c r="B64" s="31"/>
+      <c r="A64" s="23"/>
+      <c r="B64" s="23"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="21" t="s">
+      <c r="A66" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -14322,7 +14346,7 @@
       </c>
     </row>
     <row r="67" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="22"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -14397,7 +14421,7 @@
       </c>
     </row>
     <row r="68" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="22"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -14472,7 +14496,7 @@
       </c>
     </row>
     <row r="69" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="23"/>
+      <c r="A69" s="32"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -14548,6 +14572,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B50:B52"/>
     <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="B58:B60"/>
@@ -14564,7 +14589,6 @@
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B50:B52"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14713,10 +14737,10 @@
       </c>
     </row>
     <row r="7" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -14727,8 +14751,8 @@
       </c>
     </row>
     <row r="8" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="28"/>
-      <c r="B8" s="26"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="18"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
@@ -14737,8 +14761,8 @@
       </c>
     </row>
     <row r="9" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28"/>
-      <c r="B9" s="26"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="18"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
@@ -14747,8 +14771,8 @@
       </c>
     </row>
     <row r="10" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="26"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -14757,8 +14781,8 @@
       </c>
     </row>
     <row r="11" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="26" t="s">
+      <c r="A11" s="20"/>
+      <c r="B11" s="18" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
@@ -14766,25 +14790,25 @@
       </c>
     </row>
     <row r="12" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="26"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="26"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="18"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
+      <c r="A14" s="20"/>
     </row>
     <row r="15" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="32" t="s">
+      <c r="A15" s="20"/>
+      <c r="B15" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -14795,8 +14819,8 @@
       </c>
     </row>
     <row r="16" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
-      <c r="B16" s="33"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="25"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
@@ -14805,8 +14829,8 @@
       </c>
     </row>
     <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28"/>
-      <c r="B17" s="33"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="25"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
@@ -14815,8 +14839,8 @@
       </c>
     </row>
     <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28"/>
-      <c r="B18" s="34"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="26"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
@@ -14831,7 +14855,7 @@
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="21" t="s">
         <v>131</v>
       </c>
       <c r="B20" s="39" t="s">
@@ -14842,35 +14866,35 @@
       </c>
     </row>
     <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="29"/>
+      <c r="A21" s="21"/>
       <c r="B21" s="39"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="29"/>
+      <c r="A22" s="21"/>
       <c r="B22" s="39"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="29"/>
+      <c r="A23" s="21"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="29"/>
+      <c r="A24" s="21"/>
       <c r="B24" s="12"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="29"/>
+      <c r="A25" s="21"/>
       <c r="B25" s="39" t="s">
         <v>16</v>
       </c>
@@ -14879,35 +14903,35 @@
       </c>
     </row>
     <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="29"/>
+      <c r="A26" s="21"/>
       <c r="B26" s="39"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="29"/>
+      <c r="A27" s="21"/>
       <c r="B27" s="39"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="29"/>
+      <c r="A28" s="21"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="29"/>
+      <c r="A29" s="21"/>
       <c r="B29" s="13"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="29"/>
+      <c r="A30" s="21"/>
       <c r="B30" s="36" t="s">
         <v>17</v>
       </c>
@@ -14916,35 +14940,35 @@
       </c>
     </row>
     <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="29"/>
+      <c r="A31" s="21"/>
       <c r="B31" s="37"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="29"/>
+      <c r="A32" s="21"/>
       <c r="B32" s="37"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="29"/>
+      <c r="A33" s="21"/>
       <c r="B33" s="38"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="29"/>
+      <c r="A34" s="21"/>
       <c r="B34" s="14"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
     <row r="35" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="29"/>
+      <c r="A35" s="21"/>
       <c r="B35" s="36" t="s">
         <v>18</v>
       </c>
@@ -14953,35 +14977,35 @@
       </c>
     </row>
     <row r="36" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="29"/>
+      <c r="A36" s="21"/>
       <c r="B36" s="37"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="29"/>
+      <c r="A37" s="21"/>
       <c r="B37" s="37"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="29"/>
+      <c r="A38" s="21"/>
       <c r="B38" s="38"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="29"/>
+      <c r="A39" s="21"/>
       <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
     <row r="40" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="29"/>
+      <c r="A40" s="21"/>
       <c r="B40" s="36" t="s">
         <v>19</v>
       </c>
@@ -14990,26 +15014,26 @@
       </c>
     </row>
     <row r="41" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="29"/>
+      <c r="A41" s="21"/>
       <c r="B41" s="37"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="29"/>
+      <c r="A42" s="21"/>
       <c r="B42" s="38"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="29"/>
+      <c r="A43" s="21"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
     </row>
     <row r="44" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="29"/>
+      <c r="A44" s="21"/>
       <c r="B44" s="36" t="s">
         <v>30</v>
       </c>
@@ -15018,28 +15042,28 @@
       </c>
     </row>
     <row r="45" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="29"/>
+      <c r="A45" s="21"/>
       <c r="B45" s="37"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="29"/>
+      <c r="A46" s="21"/>
       <c r="B46" s="38"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="29"/>
+      <c r="A47" s="21"/>
       <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
     <row r="48" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="29"/>
+      <c r="A48" s="21"/>
       <c r="B48" s="36" t="s">
         <v>28</v>
       </c>
@@ -15108,7 +15132,7 @@
       </c>
     </row>
     <row r="49" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="29"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="37"/>
       <c r="C49" s="4" t="s">
         <v>129</v>
@@ -15175,7 +15199,7 @@
       </c>
     </row>
     <row r="50" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="29"/>
+      <c r="A50" s="21"/>
       <c r="B50" s="38"/>
       <c r="C50" s="4" t="s">
         <v>130</v>
@@ -15258,28 +15282,28 @@
       </c>
     </row>
     <row r="53" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="30"/>
-      <c r="B53" s="30"/>
+      <c r="A53" s="22"/>
+      <c r="B53" s="22"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="30"/>
-      <c r="B54" s="30"/>
+      <c r="A54" s="22"/>
+      <c r="B54" s="22"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="30"/>
-      <c r="B55" s="31"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="23"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="30"/>
+      <c r="A56" s="22"/>
       <c r="B56" s="35" t="s">
         <v>30</v>
       </c>
@@ -15288,28 +15312,28 @@
       </c>
     </row>
     <row r="57" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="30"/>
-      <c r="B57" s="30"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="22"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="30"/>
-      <c r="B58" s="31"/>
+      <c r="A58" s="22"/>
+      <c r="B58" s="23"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="30"/>
+      <c r="A59" s="22"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
     </row>
     <row r="60" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="30"/>
+      <c r="A60" s="22"/>
       <c r="B60" s="35" t="s">
         <v>25</v>
       </c>
@@ -15318,22 +15342,22 @@
       </c>
     </row>
     <row r="61" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="30"/>
-      <c r="B61" s="30"/>
+      <c r="A61" s="22"/>
+      <c r="B61" s="22"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="31"/>
-      <c r="B62" s="31"/>
+      <c r="A62" s="23"/>
+      <c r="B62" s="23"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="64" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="21" t="s">
+      <c r="A64" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -15347,7 +15371,7 @@
       </c>
     </row>
     <row r="65" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="22"/>
+      <c r="A65" s="31"/>
       <c r="B65" s="4" t="s">
         <v>132</v>
       </c>
@@ -15359,7 +15383,7 @@
       </c>
     </row>
     <row r="66" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="22"/>
+      <c r="A66" s="31"/>
       <c r="B66" s="4" t="s">
         <v>133</v>
       </c>
@@ -15371,7 +15395,7 @@
       </c>
     </row>
     <row r="67" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="23"/>
+      <c r="A67" s="32"/>
       <c r="B67" s="5" t="s">
         <v>134</v>
       </c>
@@ -15384,6 +15408,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B48:B50"/>
     <mergeCell ref="A64:A67"/>
     <mergeCell ref="A7:A18"/>
     <mergeCell ref="B56:B58"/>
@@ -15400,7 +15425,6 @@
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="B35:B38"/>
     <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B48:B50"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15410,318 +15434,371 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC6F473E-E8F6-46BD-8C8C-636A58FA8F6F}">
-  <dimension ref="A1:AI67"/>
+  <dimension ref="A3:AO67"/>
   <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="16.625" style="2"/>
+    <col min="1" max="16384" width="16.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-    </row>
-    <row r="2" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:41" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:35" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
+    </row>
+    <row r="4" spans="1:41" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D4" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="AC4" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="AD4" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="AE4" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="AF4" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="AG4" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="AH4" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="AI4" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="AK4" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AL4" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="AM4" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="AN4" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="AO4" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="AC4" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="AD4" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="AE4" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="AF4" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="AG4" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="AH4" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="AI4" s="11" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="5" spans="1:35" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
+    </row>
+    <row r="5" spans="1:41" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="1" t="s">
         <v>124</v>
       </c>
       <c r="D5" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1">
+        <v>1</v>
+      </c>
+      <c r="P5" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>1</v>
+      </c>
+      <c r="R5" s="1">
+        <v>1</v>
+      </c>
+      <c r="S5" s="1">
+        <v>1</v>
+      </c>
+      <c r="T5" s="1">
+        <v>1</v>
+      </c>
+      <c r="U5" s="1">
+        <v>2</v>
+      </c>
+      <c r="V5" s="1">
+        <v>2</v>
+      </c>
+      <c r="W5" s="1">
+        <v>2</v>
+      </c>
+      <c r="X5" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>2</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>2</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>2</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>3</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>3</v>
+      </c>
+      <c r="AF5" s="1">
+        <v>3</v>
+      </c>
+      <c r="AG5" s="1">
+        <v>3</v>
+      </c>
+      <c r="AH5" s="1">
+        <v>3</v>
+      </c>
+      <c r="AI5" s="1">
+        <v>3</v>
+      </c>
+      <c r="AJ5" s="1">
+        <v>3</v>
+      </c>
+      <c r="AK5" s="1">
+        <v>3</v>
+      </c>
+      <c r="AL5" s="1">
+        <v>3</v>
+      </c>
+      <c r="AM5" s="1">
+        <v>3</v>
+      </c>
+      <c r="AN5" s="1">
         <v>4</v>
       </c>
-      <c r="H5" s="1">
+      <c r="AO5" s="1">
         <v>4</v>
       </c>
-      <c r="I5" s="1">
-        <v>3</v>
-      </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
-      <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
-      <c r="AB5" s="1"/>
-      <c r="AC5" s="1"/>
-      <c r="AD5" s="1"/>
-      <c r="AE5" s="1"/>
-      <c r="AF5" s="1"/>
-    </row>
-    <row r="6" spans="1:35" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
+    </row>
+    <row r="6" spans="1:41" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D6" s="1">
+      <c r="AC6" s="1">
         <v>2</v>
       </c>
-      <c r="E6" s="1">
-        <v>3</v>
-      </c>
-      <c r="F6" s="1">
-        <v>3</v>
-      </c>
-      <c r="G6" s="1">
+      <c r="AD6" s="1">
+        <v>3</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>3</v>
+      </c>
+      <c r="AF6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AN6" s="1">
         <v>4</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="AO6" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I6" s="1">
-        <v>5</v>
-      </c>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
-      <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
-      <c r="AB6" s="1"/>
-      <c r="AC6" s="1"/>
-      <c r="AD6" s="1"/>
-      <c r="AE6" s="1"/>
-      <c r="AF6" s="1"/>
-    </row>
-    <row r="7" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="28" t="s">
+    </row>
+    <row r="7" spans="1:41" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="28"/>
-      <c r="B8" s="26"/>
+    <row r="8" spans="1:41" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="20"/>
+      <c r="B8" s="18"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28"/>
-      <c r="B9" s="26"/>
+    <row r="9" spans="1:41" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="20"/>
+      <c r="B9" s="18"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="26"/>
+    <row r="10" spans="1:41" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="20"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="26" t="s">
+    <row r="11" spans="1:41" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="20"/>
+      <c r="B11" s="18" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="26"/>
+    <row r="12" spans="1:41" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="20"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="26"/>
+    <row r="13" spans="1:41" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="20"/>
+      <c r="B13" s="18"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-    </row>
-    <row r="15" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="32" t="s">
+    <row r="14" spans="1:41" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="20"/>
+    </row>
+    <row r="15" spans="1:41" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="20"/>
+      <c r="B15" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
-      <c r="B16" s="33"/>
+    <row r="16" spans="1:41" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="20"/>
+      <c r="B16" s="25"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28"/>
-      <c r="B17" s="33"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="25"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28"/>
-      <c r="B18" s="34"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="26"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="21" t="s">
         <v>131</v>
       </c>
       <c r="B20" s="39" t="s">
@@ -15732,35 +15809,35 @@
       </c>
     </row>
     <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="29"/>
+      <c r="A21" s="21"/>
       <c r="B21" s="39"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="29"/>
+      <c r="A22" s="21"/>
       <c r="B22" s="39"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="29"/>
+      <c r="A23" s="21"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="29"/>
+    <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="21"/>
       <c r="B24" s="12"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="29"/>
+      <c r="A25" s="21"/>
       <c r="B25" s="39" t="s">
         <v>16</v>
       </c>
@@ -15769,35 +15846,35 @@
       </c>
     </row>
     <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="29"/>
+      <c r="A26" s="21"/>
       <c r="B26" s="39"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="29"/>
+      <c r="A27" s="21"/>
       <c r="B27" s="39"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="29"/>
+      <c r="A28" s="21"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="29"/>
+    <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="21"/>
       <c r="B29" s="13"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="29"/>
+      <c r="A30" s="21"/>
       <c r="B30" s="36" t="s">
         <v>17</v>
       </c>
@@ -15806,35 +15883,35 @@
       </c>
     </row>
     <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="29"/>
+      <c r="A31" s="21"/>
       <c r="B31" s="37"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="29"/>
+      <c r="A32" s="21"/>
       <c r="B32" s="37"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="29"/>
+      <c r="A33" s="21"/>
       <c r="B33" s="38"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="29"/>
+    <row r="34" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="21"/>
       <c r="B34" s="14"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="29"/>
+      <c r="A35" s="21"/>
       <c r="B35" s="36" t="s">
         <v>18</v>
       </c>
@@ -15843,35 +15920,35 @@
       </c>
     </row>
     <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="29"/>
+      <c r="A36" s="21"/>
       <c r="B36" s="37"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="29"/>
+      <c r="A37" s="21"/>
       <c r="B37" s="37"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="29"/>
+      <c r="A38" s="21"/>
       <c r="B38" s="38"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="29"/>
+    <row r="39" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="21"/>
       <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="29"/>
+      <c r="A40" s="21"/>
       <c r="B40" s="36" t="s">
         <v>19</v>
       </c>
@@ -15880,26 +15957,26 @@
       </c>
     </row>
     <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="29"/>
+      <c r="A41" s="21"/>
       <c r="B41" s="37"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="29"/>
+      <c r="A42" s="21"/>
       <c r="B42" s="38"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="29"/>
+    <row r="43" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="21"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="29"/>
+      <c r="A44" s="21"/>
       <c r="B44" s="36" t="s">
         <v>30</v>
       </c>
@@ -15908,28 +15985,28 @@
       </c>
     </row>
     <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="29"/>
+      <c r="A45" s="21"/>
       <c r="B45" s="37"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="29"/>
+      <c r="A46" s="21"/>
       <c r="B46" s="38"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="29"/>
+    <row r="47" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="21"/>
       <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="29"/>
+      <c r="A48" s="21"/>
       <c r="B48" s="36" t="s">
         <v>28</v>
       </c>
@@ -15994,7 +16071,7 @@
       </c>
     </row>
     <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="29"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="37"/>
       <c r="C49" s="4" t="s">
         <v>129</v>
@@ -16057,7 +16134,7 @@
       </c>
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="29"/>
+      <c r="A50" s="21"/>
       <c r="B50" s="38"/>
       <c r="C50" s="4" t="s">
         <v>130</v>
@@ -16136,28 +16213,28 @@
       </c>
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="30"/>
-      <c r="B53" s="30"/>
+      <c r="A53" s="22"/>
+      <c r="B53" s="22"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="30"/>
-      <c r="B54" s="30"/>
+      <c r="A54" s="22"/>
+      <c r="B54" s="22"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="30"/>
-      <c r="B55" s="31"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="23"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="30"/>
+      <c r="A56" s="22"/>
       <c r="B56" s="35" t="s">
         <v>30</v>
       </c>
@@ -16166,28 +16243,28 @@
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="30"/>
-      <c r="B57" s="30"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="22"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="30"/>
-      <c r="B58" s="31"/>
+      <c r="A58" s="22"/>
+      <c r="B58" s="23"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="30"/>
+    <row r="59" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="22"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="30"/>
+      <c r="A60" s="22"/>
       <c r="B60" s="35" t="s">
         <v>25</v>
       </c>
@@ -16196,22 +16273,21 @@
       </c>
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="30"/>
-      <c r="B61" s="30"/>
+      <c r="A61" s="22"/>
+      <c r="B61" s="22"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="31"/>
-      <c r="B62" s="31"/>
+      <c r="A62" s="23"/>
+      <c r="B62" s="23"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="21" t="s">
+      <c r="A64" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -16222,7 +16298,7 @@
       </c>
     </row>
     <row r="65" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="22"/>
+      <c r="A65" s="31"/>
       <c r="B65" s="4" t="s">
         <v>132</v>
       </c>
@@ -16231,7 +16307,7 @@
       </c>
     </row>
     <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="22"/>
+      <c r="A66" s="31"/>
       <c r="B66" s="4" t="s">
         <v>133</v>
       </c>
@@ -16240,7 +16316,7 @@
       </c>
     </row>
     <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="23"/>
+      <c r="A67" s="32"/>
       <c r="B67" s="5" t="s">
         <v>134</v>
       </c>
@@ -16249,14 +16325,11 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="C4:AO6">
+    <sortCondition ref="C5:AO5"/>
+    <sortCondition ref="C6:AO6"/>
+  </sortState>
   <mergeCells count="17">
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A52:A62"/>
-    <mergeCell ref="B52:B55"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B60:B62"/>
     <mergeCell ref="A7:A18"/>
     <mergeCell ref="B7:B10"/>
     <mergeCell ref="B11:B13"/>
@@ -16267,6 +16340,13 @@
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="B35:B38"/>
     <mergeCell ref="B40:B42"/>
+    <mergeCell ref="A64:A67"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A52:A62"/>
+    <mergeCell ref="B52:B55"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="B60:B62"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dev_stuffs/3匠魂.xlsx
+++ b/dev_stuffs/3匠魂.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\Palmon\dev_stuffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9BC20B-B2EB-4868-9BB6-0EE3697DEB84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B5BA7F6-3061-4923-BE90-217653DE11A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8685" yWindow="2400" windowWidth="24015" windowHeight="15435" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2880" yWindow="2895" windowWidth="24015" windowHeight="15435" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="阶段1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="276">
   <si>
     <t>材料名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -759,10 +759,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>5?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>凋零</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -946,6 +942,18 @@
   </si>
   <si>
     <t>紫菘</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>热核</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>光谱</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1196,6 +1204,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1221,30 +1253,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
@@ -1720,10 +1728,10 @@
       </c>
     </row>
     <row r="9" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -1761,8 +1769,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="18"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -1798,8 +1806,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="18"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -1835,8 +1843,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="18"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -1872,8 +1880,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="18" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -1881,25 +1889,25 @@
       </c>
     </row>
     <row r="14" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="18"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="18"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
+      <c r="A16" s="28"/>
     </row>
     <row r="17" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="24" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -1937,8 +1945,8 @@
       </c>
     </row>
     <row r="18" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="25"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1974,8 +1982,8 @@
       </c>
     </row>
     <row r="19" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="25"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -2011,8 +2019,8 @@
       </c>
     </row>
     <row r="20" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20"/>
-      <c r="B20" s="26"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -2054,10 +2062,10 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="33" t="s">
+      <c r="A22" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="29" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -2095,8 +2103,8 @@
       </c>
     </row>
     <row r="23" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="34"/>
-      <c r="B23" s="21"/>
+      <c r="A23" s="25"/>
+      <c r="B23" s="29"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
       </c>
@@ -2142,8 +2150,8 @@
       </c>
     </row>
     <row r="24" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="34"/>
-      <c r="B24" s="21"/>
+      <c r="A24" s="25"/>
+      <c r="B24" s="29"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
       </c>
@@ -2179,22 +2187,22 @@
       </c>
     </row>
     <row r="25" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="34"/>
-      <c r="B25" s="21"/>
+      <c r="A25" s="25"/>
+      <c r="B25" s="29"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="34"/>
+      <c r="A26" s="25"/>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="34"/>
-      <c r="B27" s="21" t="s">
+      <c r="A27" s="25"/>
+      <c r="B27" s="29" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="4" t="s">
@@ -2232,8 +2240,8 @@
       </c>
     </row>
     <row r="28" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="34"/>
-      <c r="B28" s="21"/>
+      <c r="A28" s="25"/>
+      <c r="B28" s="29"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
       </c>
@@ -2279,8 +2287,8 @@
       </c>
     </row>
     <row r="29" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="34"/>
-      <c r="B29" s="21"/>
+      <c r="A29" s="25"/>
+      <c r="B29" s="29"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
       </c>
@@ -2316,22 +2324,22 @@
       </c>
     </row>
     <row r="30" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="34"/>
-      <c r="B30" s="21"/>
+      <c r="A30" s="25"/>
+      <c r="B30" s="29"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="34"/>
+      <c r="A31" s="25"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="34"/>
-      <c r="B32" s="27" t="s">
+      <c r="A32" s="25"/>
+      <c r="B32" s="21" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -2369,8 +2377,8 @@
       </c>
     </row>
     <row r="33" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="34"/>
-      <c r="B33" s="28"/>
+      <c r="A33" s="25"/>
+      <c r="B33" s="22"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -2416,8 +2424,8 @@
       </c>
     </row>
     <row r="34" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="34"/>
-      <c r="B34" s="28"/>
+      <c r="A34" s="25"/>
+      <c r="B34" s="22"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -2453,22 +2461,22 @@
       </c>
     </row>
     <row r="35" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="34"/>
-      <c r="B35" s="29"/>
+      <c r="A35" s="25"/>
+      <c r="B35" s="23"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="34"/>
+      <c r="A36" s="25"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="34"/>
-      <c r="B37" s="27" t="s">
+      <c r="A37" s="25"/>
+      <c r="B37" s="21" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -2506,8 +2514,8 @@
       </c>
     </row>
     <row r="38" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="34"/>
-      <c r="B38" s="28"/>
+      <c r="A38" s="25"/>
+      <c r="B38" s="22"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -2553,8 +2561,8 @@
       </c>
     </row>
     <row r="39" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="34"/>
-      <c r="B39" s="28"/>
+      <c r="A39" s="25"/>
+      <c r="B39" s="22"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -2590,22 +2598,22 @@
       </c>
     </row>
     <row r="40" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="34"/>
-      <c r="B40" s="29"/>
+      <c r="A40" s="25"/>
+      <c r="B40" s="23"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="34"/>
+      <c r="A41" s="25"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="34"/>
-      <c r="B42" s="27" t="s">
+      <c r="A42" s="25"/>
+      <c r="B42" s="21" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -2653,8 +2661,8 @@
       </c>
     </row>
     <row r="43" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="34"/>
-      <c r="B43" s="28"/>
+      <c r="A43" s="25"/>
+      <c r="B43" s="22"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -2690,18 +2698,18 @@
       </c>
     </row>
     <row r="44" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="34"/>
-      <c r="B44" s="29"/>
+      <c r="A44" s="25"/>
+      <c r="B44" s="23"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="34"/>
+      <c r="A45" s="25"/>
     </row>
     <row r="46" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="34"/>
-      <c r="B46" s="27" t="s">
+      <c r="A46" s="25"/>
+      <c r="B46" s="21" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -2709,29 +2717,29 @@
       </c>
     </row>
     <row r="47" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="34"/>
-      <c r="B47" s="28"/>
+      <c r="A47" s="25"/>
+      <c r="B47" s="22"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="34"/>
-      <c r="B48" s="29"/>
+      <c r="A48" s="25"/>
+      <c r="B48" s="23"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="34"/>
+      <c r="A49" s="25"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
     </row>
     <row r="50" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="34"/>
-      <c r="B50" s="27" t="s">
+      <c r="A50" s="25"/>
+      <c r="B50" s="21" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -2779,8 +2787,8 @@
       </c>
     </row>
     <row r="51" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="34"/>
-      <c r="B51" s="28"/>
+      <c r="A51" s="25"/>
+      <c r="B51" s="22"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -2826,8 +2834,8 @@
       </c>
     </row>
     <row r="52" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="34"/>
-      <c r="B52" s="29"/>
+      <c r="A52" s="25"/>
+      <c r="B52" s="23"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -2879,10 +2887,10 @@
       <c r="E53" s="8"/>
     </row>
     <row r="54" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="19" t="s">
+      <c r="A54" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="19" t="s">
+      <c r="B54" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -2890,29 +2898,29 @@
       </c>
     </row>
     <row r="55" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="19"/>
-      <c r="B55" s="19"/>
+      <c r="A55" s="27"/>
+      <c r="B55" s="27"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="19"/>
-      <c r="B56" s="19"/>
+      <c r="A56" s="27"/>
+      <c r="B56" s="27"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="19"/>
-      <c r="B57" s="19"/>
+      <c r="A57" s="27"/>
+      <c r="B57" s="27"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="19"/>
-      <c r="B58" s="19" t="s">
+      <c r="A58" s="27"/>
+      <c r="B58" s="27" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -2920,29 +2928,29 @@
       </c>
     </row>
     <row r="59" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="19"/>
-      <c r="B59" s="22"/>
+      <c r="A59" s="27"/>
+      <c r="B59" s="30"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="19"/>
-      <c r="B60" s="23"/>
+      <c r="A60" s="27"/>
+      <c r="B60" s="31"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="19"/>
+      <c r="A61" s="27"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="19"/>
-      <c r="B62" s="19" t="s">
+      <c r="A62" s="27"/>
+      <c r="B62" s="27" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -2950,21 +2958,21 @@
       </c>
     </row>
     <row r="63" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="19"/>
-      <c r="B63" s="22"/>
+      <c r="A63" s="27"/>
+      <c r="B63" s="30"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="19"/>
-      <c r="B64" s="23"/>
+      <c r="A64" s="27"/>
+      <c r="B64" s="31"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="30" t="s">
+      <c r="A67" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B67" s="6" t="s">
@@ -3005,7 +3013,7 @@
       </c>
     </row>
     <row r="68" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="31"/>
+      <c r="A68" s="19"/>
       <c r="B68" s="4" t="s">
         <v>132</v>
       </c>
@@ -3044,7 +3052,7 @@
       </c>
     </row>
     <row r="69" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="31"/>
+      <c r="A69" s="19"/>
       <c r="B69" s="4" t="s">
         <v>133</v>
       </c>
@@ -3083,7 +3091,7 @@
       </c>
     </row>
     <row r="70" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="32"/>
+      <c r="A70" s="20"/>
       <c r="B70" s="5" t="s">
         <v>134</v>
       </c>
@@ -3123,6 +3131,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B50:B52"/>
     <mergeCell ref="A67:A70"/>
     <mergeCell ref="B46:B48"/>
     <mergeCell ref="A22:A52"/>
@@ -3139,7 +3148,6 @@
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B50:B52"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3409,10 +3417,10 @@
       </c>
     </row>
     <row r="9" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -3462,8 +3470,8 @@
       </c>
     </row>
     <row r="10" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="18"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -3511,8 +3519,8 @@
       </c>
     </row>
     <row r="11" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="18"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -3560,8 +3568,8 @@
       </c>
     </row>
     <row r="12" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="18"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -3609,8 +3617,8 @@
       </c>
     </row>
     <row r="13" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="18" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -3618,25 +3626,25 @@
       </c>
     </row>
     <row r="14" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="18"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="18"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
+      <c r="A16" s="28"/>
     </row>
     <row r="17" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="24" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -3686,8 +3694,8 @@
       </c>
     </row>
     <row r="18" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="25"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -3735,8 +3743,8 @@
       </c>
     </row>
     <row r="19" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="25"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -3784,8 +3792,8 @@
       </c>
     </row>
     <row r="20" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20"/>
-      <c r="B20" s="26"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -3839,7 +3847,7 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="29" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="39" t="s">
@@ -3892,7 +3900,7 @@
       </c>
     </row>
     <row r="23" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -3955,7 +3963,7 @@
       </c>
     </row>
     <row r="24" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -4004,7 +4012,7 @@
       </c>
     </row>
     <row r="25" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -4035,14 +4043,14 @@
       </c>
     </row>
     <row r="26" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
+      <c r="A27" s="29"/>
       <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
@@ -4093,7 +4101,7 @@
       </c>
     </row>
     <row r="28" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -4156,7 +4164,7 @@
       </c>
     </row>
     <row r="29" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -4205,7 +4213,7 @@
       </c>
     </row>
     <row r="30" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -4236,14 +4244,14 @@
       </c>
     </row>
     <row r="31" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
+      <c r="A32" s="29"/>
       <c r="B32" s="36" t="s">
         <v>17</v>
       </c>
@@ -4294,7 +4302,7 @@
       </c>
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
+      <c r="A33" s="29"/>
       <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
@@ -4357,7 +4365,7 @@
       </c>
     </row>
     <row r="34" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
+      <c r="A34" s="29"/>
       <c r="B34" s="37"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
@@ -4406,7 +4414,7 @@
       </c>
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
+      <c r="A35" s="29"/>
       <c r="B35" s="38"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
@@ -4437,14 +4445,14 @@
       </c>
     </row>
     <row r="36" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
+      <c r="A37" s="29"/>
       <c r="B37" s="36" t="s">
         <v>18</v>
       </c>
@@ -4495,7 +4503,7 @@
       </c>
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
+      <c r="A38" s="29"/>
       <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
@@ -4558,7 +4566,7 @@
       </c>
     </row>
     <row r="39" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
+      <c r="A39" s="29"/>
       <c r="B39" s="37"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
@@ -4607,7 +4615,7 @@
       </c>
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
+      <c r="A40" s="29"/>
       <c r="B40" s="38"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
@@ -4638,14 +4646,14 @@
       </c>
     </row>
     <row r="41" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
+      <c r="A41" s="29"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
+      <c r="A42" s="29"/>
       <c r="B42" s="36" t="s">
         <v>19</v>
       </c>
@@ -4710,7 +4718,7 @@
       </c>
     </row>
     <row r="43" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="21"/>
+      <c r="A43" s="29"/>
       <c r="B43" s="37"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
@@ -4759,7 +4767,7 @@
       </c>
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="21"/>
+      <c r="A44" s="29"/>
       <c r="B44" s="38"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
@@ -4790,12 +4798,12 @@
       </c>
     </row>
     <row r="45" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="21"/>
+      <c r="A45" s="29"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="21"/>
+      <c r="A46" s="29"/>
       <c r="B46" s="36" t="s">
         <v>30</v>
       </c>
@@ -4804,28 +4812,28 @@
       </c>
     </row>
     <row r="47" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="21"/>
+      <c r="A47" s="29"/>
       <c r="B47" s="37"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="21"/>
+      <c r="A48" s="29"/>
       <c r="B48" s="38"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="21"/>
+      <c r="A49" s="29"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="21"/>
+      <c r="A50" s="29"/>
       <c r="B50" s="36" t="s">
         <v>28</v>
       </c>
@@ -4890,7 +4898,7 @@
       </c>
     </row>
     <row r="51" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="21"/>
+      <c r="A51" s="29"/>
       <c r="B51" s="37"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
@@ -4953,7 +4961,7 @@
       </c>
     </row>
     <row r="52" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="21"/>
+      <c r="A52" s="29"/>
       <c r="B52" s="38"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
@@ -5032,28 +5040,28 @@
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="22"/>
-      <c r="B55" s="22"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="22"/>
-      <c r="B56" s="22"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="30"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="22"/>
-      <c r="B57" s="23"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="31"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="22"/>
+      <c r="A58" s="30"/>
       <c r="B58" s="35" t="s">
         <v>30</v>
       </c>
@@ -5062,28 +5070,28 @@
       </c>
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="22"/>
-      <c r="B59" s="22"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="22"/>
-      <c r="B60" s="23"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="31"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="22"/>
+      <c r="A61" s="30"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="22"/>
+      <c r="A62" s="30"/>
       <c r="B62" s="35" t="s">
         <v>25</v>
       </c>
@@ -5092,22 +5100,22 @@
       </c>
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="22"/>
-      <c r="B63" s="22"/>
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="23"/>
-      <c r="B64" s="23"/>
+      <c r="A64" s="31"/>
+      <c r="B64" s="31"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -5160,7 +5168,7 @@
       </c>
     </row>
     <row r="67" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="31"/>
+      <c r="A67" s="19"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -5205,7 +5213,7 @@
       </c>
     </row>
     <row r="68" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="31"/>
+      <c r="A68" s="19"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -5250,7 +5258,7 @@
       </c>
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="32"/>
+      <c r="A69" s="20"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -5260,11 +5268,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A54:A64"/>
-    <mergeCell ref="B54:B57"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="B62:B64"/>
     <mergeCell ref="B9:B12"/>
@@ -5277,6 +5280,11 @@
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="B42:B44"/>
+    <mergeCell ref="A54:A64"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A66:A69"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5429,61 +5437,61 @@
         <v>219</v>
       </c>
       <c r="M5" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="N5" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="P5" s="11" t="s">
+      <c r="Q5" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="Q5" s="11" t="s">
+      <c r="R5" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="R5" s="11" t="s">
+      <c r="S5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="S5" s="11" t="s">
+      <c r="T5" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="T5" s="11" t="s">
+      <c r="U5" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="U5" s="11" t="s">
+      <c r="V5" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="V5" s="11" t="s">
+      <c r="W5" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="W5" s="11" t="s">
+      <c r="X5" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="X5" s="11" t="s">
+      <c r="Y5" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="Y5" s="11" t="s">
+      <c r="Z5" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="Z5" s="11" t="s">
+      <c r="AA5" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="AA5" s="11" t="s">
+      <c r="AB5" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="AB5" s="11" t="s">
+      <c r="AC5" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="AC5" s="11" t="s">
+      <c r="AD5" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="AD5" s="11" t="s">
+      <c r="AE5" s="11" t="s">
         <v>240</v>
-      </c>
-      <c r="AE5" s="11" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="6" spans="1:31" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -5760,10 +5768,10 @@
       </c>
     </row>
     <row r="9" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -5855,8 +5863,8 @@
       </c>
     </row>
     <row r="10" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="18"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -5946,8 +5954,8 @@
       </c>
     </row>
     <row r="11" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="18"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -6037,8 +6045,8 @@
       </c>
     </row>
     <row r="12" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="18"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -6128,8 +6136,8 @@
       </c>
     </row>
     <row r="13" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="18" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -6137,25 +6145,25 @@
       </c>
     </row>
     <row r="14" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="18"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="18"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
+      <c r="A16" s="28"/>
     </row>
     <row r="17" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="24" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -6247,8 +6255,8 @@
       </c>
     </row>
     <row r="18" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="25"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -6338,8 +6346,8 @@
       </c>
     </row>
     <row r="19" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="25"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -6429,8 +6437,8 @@
       </c>
     </row>
     <row r="20" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20"/>
-      <c r="B20" s="26"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -6529,7 +6537,7 @@
       </c>
     </row>
     <row r="22" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="29" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="39" t="s">
@@ -6624,7 +6632,7 @@
       </c>
     </row>
     <row r="23" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -6743,7 +6751,7 @@
       </c>
     </row>
     <row r="24" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -6834,7 +6842,7 @@
       </c>
     </row>
     <row r="25" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -6925,14 +6933,14 @@
       </c>
     </row>
     <row r="26" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
+      <c r="A27" s="29"/>
       <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
@@ -7025,7 +7033,7 @@
       </c>
     </row>
     <row r="28" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -7144,7 +7152,7 @@
       </c>
     </row>
     <row r="29" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -7235,7 +7243,7 @@
       </c>
     </row>
     <row r="30" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -7326,14 +7334,14 @@
       </c>
     </row>
     <row r="31" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
+      <c r="A32" s="29"/>
       <c r="B32" s="36" t="s">
         <v>17</v>
       </c>
@@ -7426,7 +7434,7 @@
       </c>
     </row>
     <row r="33" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
+      <c r="A33" s="29"/>
       <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
@@ -7545,7 +7553,7 @@
       </c>
     </row>
     <row r="34" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
+      <c r="A34" s="29"/>
       <c r="B34" s="37"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
@@ -7636,7 +7644,7 @@
       </c>
     </row>
     <row r="35" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
+      <c r="A35" s="29"/>
       <c r="B35" s="38"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
@@ -7727,14 +7735,14 @@
       </c>
     </row>
     <row r="36" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
+      <c r="A37" s="29"/>
       <c r="B37" s="36" t="s">
         <v>18</v>
       </c>
@@ -7827,7 +7835,7 @@
       </c>
     </row>
     <row r="38" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
+      <c r="A38" s="29"/>
       <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
@@ -7946,7 +7954,7 @@
       </c>
     </row>
     <row r="39" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
+      <c r="A39" s="29"/>
       <c r="B39" s="37"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
@@ -8037,7 +8045,7 @@
       </c>
     </row>
     <row r="40" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
+      <c r="A40" s="29"/>
       <c r="B40" s="38"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
@@ -8128,14 +8136,14 @@
       </c>
     </row>
     <row r="41" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
+      <c r="A41" s="29"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
+      <c r="A42" s="29"/>
       <c r="B42" s="36" t="s">
         <v>19</v>
       </c>
@@ -8144,7 +8152,7 @@
       </c>
     </row>
     <row r="43" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="21"/>
+      <c r="A43" s="29"/>
       <c r="B43" s="37"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
@@ -8235,7 +8243,7 @@
       </c>
     </row>
     <row r="44" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="21"/>
+      <c r="A44" s="29"/>
       <c r="B44" s="38"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
@@ -8326,12 +8334,12 @@
       </c>
     </row>
     <row r="45" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="21"/>
+      <c r="A45" s="29"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
     </row>
     <row r="46" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="21"/>
+      <c r="A46" s="29"/>
       <c r="B46" s="36" t="s">
         <v>30</v>
       </c>
@@ -8340,28 +8348,28 @@
       </c>
     </row>
     <row r="47" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="21"/>
+      <c r="A47" s="29"/>
       <c r="B47" s="37"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="21"/>
+      <c r="A48" s="29"/>
       <c r="B48" s="38"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="21"/>
+      <c r="A49" s="29"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="21"/>
+      <c r="A50" s="29"/>
       <c r="B50" s="36" t="s">
         <v>28</v>
       </c>
@@ -8482,7 +8490,7 @@
       </c>
     </row>
     <row r="51" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="21"/>
+      <c r="A51" s="29"/>
       <c r="B51" s="37"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
@@ -8601,7 +8609,7 @@
       </c>
     </row>
     <row r="52" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="21"/>
+      <c r="A52" s="29"/>
       <c r="B52" s="38"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
@@ -8736,28 +8744,28 @@
       </c>
     </row>
     <row r="55" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="22"/>
-      <c r="B55" s="22"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="22"/>
-      <c r="B56" s="22"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="30"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="22"/>
-      <c r="B57" s="23"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="31"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="22"/>
+      <c r="A58" s="30"/>
       <c r="B58" s="35" t="s">
         <v>30</v>
       </c>
@@ -8766,28 +8774,28 @@
       </c>
     </row>
     <row r="59" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="22"/>
-      <c r="B59" s="22"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="22"/>
-      <c r="B60" s="23"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="31"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="22"/>
+      <c r="A61" s="30"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="22"/>
+      <c r="A62" s="30"/>
       <c r="B62" s="35" t="s">
         <v>25</v>
       </c>
@@ -8796,22 +8804,22 @@
       </c>
     </row>
     <row r="63" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="22"/>
-      <c r="B63" s="22"/>
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="23"/>
-      <c r="B64" s="23"/>
+      <c r="A64" s="31"/>
+      <c r="B64" s="31"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:31" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -8906,7 +8914,7 @@
       </c>
     </row>
     <row r="67" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="31"/>
+      <c r="A67" s="19"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -8999,7 +9007,7 @@
       </c>
     </row>
     <row r="68" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="31"/>
+      <c r="A68" s="19"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -9092,7 +9100,7 @@
       </c>
     </row>
     <row r="69" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="32"/>
+      <c r="A69" s="20"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -9186,6 +9194,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B42:B44"/>
     <mergeCell ref="B50:B52"/>
     <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
@@ -9202,7 +9211,6 @@
     <mergeCell ref="B62:B64"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
-    <mergeCell ref="B42:B44"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9445,10 +9453,10 @@
       </c>
     </row>
     <row r="9" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -9492,8 +9500,8 @@
       </c>
     </row>
     <row r="10" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="18"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -9535,8 +9543,8 @@
       </c>
     </row>
     <row r="11" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="18"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -9578,8 +9586,8 @@
       </c>
     </row>
     <row r="12" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="18"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -9621,8 +9629,8 @@
       </c>
     </row>
     <row r="13" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="18" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -9630,25 +9638,25 @@
       </c>
     </row>
     <row r="14" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="18"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="18"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
+      <c r="A16" s="28"/>
     </row>
     <row r="17" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="24" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -9692,8 +9700,8 @@
       </c>
     </row>
     <row r="18" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="25"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -9735,8 +9743,8 @@
       </c>
     </row>
     <row r="19" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="25"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -9778,8 +9786,8 @@
       </c>
     </row>
     <row r="20" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20"/>
-      <c r="B20" s="26"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -9827,7 +9835,7 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="29" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="39" t="s">
@@ -9874,7 +9882,7 @@
       </c>
     </row>
     <row r="23" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -9929,7 +9937,7 @@
       </c>
     </row>
     <row r="24" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -9972,7 +9980,7 @@
       </c>
     </row>
     <row r="25" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -10015,14 +10023,14 @@
       </c>
     </row>
     <row r="26" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
+      <c r="A27" s="29"/>
       <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
@@ -10067,7 +10075,7 @@
       </c>
     </row>
     <row r="28" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -10122,7 +10130,7 @@
       </c>
     </row>
     <row r="29" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -10165,7 +10173,7 @@
       </c>
     </row>
     <row r="30" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -10208,14 +10216,14 @@
       </c>
     </row>
     <row r="31" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
+      <c r="A32" s="29"/>
       <c r="B32" s="36" t="s">
         <v>17</v>
       </c>
@@ -10260,7 +10268,7 @@
       </c>
     </row>
     <row r="33" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
+      <c r="A33" s="29"/>
       <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
@@ -10315,7 +10323,7 @@
       </c>
     </row>
     <row r="34" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
+      <c r="A34" s="29"/>
       <c r="B34" s="37"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
@@ -10358,7 +10366,7 @@
       </c>
     </row>
     <row r="35" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
+      <c r="A35" s="29"/>
       <c r="B35" s="38"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
@@ -10401,14 +10409,14 @@
       </c>
     </row>
     <row r="36" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
+      <c r="A37" s="29"/>
       <c r="B37" s="36" t="s">
         <v>18</v>
       </c>
@@ -10453,7 +10461,7 @@
       </c>
     </row>
     <row r="38" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
+      <c r="A38" s="29"/>
       <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
@@ -10508,7 +10516,7 @@
       </c>
     </row>
     <row r="39" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
+      <c r="A39" s="29"/>
       <c r="B39" s="37"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
@@ -10551,7 +10559,7 @@
       </c>
     </row>
     <row r="40" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
+      <c r="A40" s="29"/>
       <c r="B40" s="38"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
@@ -10594,14 +10602,14 @@
       </c>
     </row>
     <row r="41" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
+      <c r="A41" s="29"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
+      <c r="A42" s="29"/>
       <c r="B42" s="36" t="s">
         <v>19</v>
       </c>
@@ -10658,7 +10666,7 @@
       </c>
     </row>
     <row r="43" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="21"/>
+      <c r="A43" s="29"/>
       <c r="B43" s="37"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
@@ -10701,7 +10709,7 @@
       </c>
     </row>
     <row r="44" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="21"/>
+      <c r="A44" s="29"/>
       <c r="B44" s="38"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
@@ -10744,13 +10752,13 @@
       </c>
     </row>
     <row r="45" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="21"/>
+      <c r="A45" s="29"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
       <c r="F45" s="17"/>
     </row>
     <row r="46" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="21"/>
+      <c r="A46" s="29"/>
       <c r="B46" s="36" t="s">
         <v>30</v>
       </c>
@@ -10759,28 +10767,28 @@
       </c>
     </row>
     <row r="47" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="21"/>
+      <c r="A47" s="29"/>
       <c r="B47" s="37"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="21"/>
+      <c r="A48" s="29"/>
       <c r="B48" s="38"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="21"/>
+      <c r="A49" s="29"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="21"/>
+      <c r="A50" s="29"/>
       <c r="B50" s="36" t="s">
         <v>28</v>
       </c>
@@ -10837,7 +10845,7 @@
       </c>
     </row>
     <row r="51" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="21"/>
+      <c r="A51" s="29"/>
       <c r="B51" s="37"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
@@ -10892,7 +10900,7 @@
       </c>
     </row>
     <row r="52" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="21"/>
+      <c r="A52" s="29"/>
       <c r="B52" s="38"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
@@ -10966,8 +10974,8 @@
       </c>
     </row>
     <row r="55" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="22"/>
-      <c r="B55" s="22"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
@@ -10976,8 +10984,8 @@
       </c>
     </row>
     <row r="56" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="22"/>
-      <c r="B56" s="22"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="30"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
@@ -10986,8 +10994,8 @@
       </c>
     </row>
     <row r="57" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="22"/>
-      <c r="B57" s="23"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="31"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
@@ -10996,7 +11004,7 @@
       </c>
     </row>
     <row r="58" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="22"/>
+      <c r="A58" s="30"/>
       <c r="B58" s="35" t="s">
         <v>30</v>
       </c>
@@ -11005,28 +11013,28 @@
       </c>
     </row>
     <row r="59" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="22"/>
-      <c r="B59" s="22"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="22"/>
-      <c r="B60" s="23"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="31"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="22"/>
+      <c r="A61" s="30"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="22"/>
+      <c r="A62" s="30"/>
       <c r="B62" s="35" t="s">
         <v>25</v>
       </c>
@@ -11038,8 +11046,8 @@
       </c>
     </row>
     <row r="63" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="22"/>
-      <c r="B63" s="22"/>
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
@@ -11048,8 +11056,8 @@
       </c>
     </row>
     <row r="64" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="23"/>
-      <c r="B64" s="23"/>
+      <c r="A64" s="31"/>
+      <c r="B64" s="31"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
@@ -11059,7 +11067,7 @@
     </row>
     <row r="65" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -11106,7 +11114,7 @@
       </c>
     </row>
     <row r="67" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="31"/>
+      <c r="A67" s="19"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -11151,7 +11159,7 @@
       </c>
     </row>
     <row r="68" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="31"/>
+      <c r="A68" s="19"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -11196,7 +11204,7 @@
       </c>
     </row>
     <row r="69" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="32"/>
+      <c r="A69" s="20"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -11242,6 +11250,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B42:B44"/>
     <mergeCell ref="B50:B52"/>
     <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
@@ -11258,7 +11267,6 @@
     <mergeCell ref="B62:B64"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
-    <mergeCell ref="B42:B44"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11697,10 +11705,10 @@
       <c r="AA8" s="1"/>
     </row>
     <row r="9" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -11774,8 +11782,8 @@
       </c>
     </row>
     <row r="10" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="18"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -11847,8 +11855,8 @@
       </c>
     </row>
     <row r="11" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="18"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -11920,8 +11928,8 @@
       </c>
     </row>
     <row r="12" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="18"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -11993,8 +12001,8 @@
       </c>
     </row>
     <row r="13" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="18" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -12002,25 +12010,25 @@
       </c>
     </row>
     <row r="14" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="18"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="18"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:27" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
+      <c r="A16" s="28"/>
     </row>
     <row r="17" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="24" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -12094,8 +12102,8 @@
       </c>
     </row>
     <row r="18" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="25"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -12167,8 +12175,8 @@
       </c>
     </row>
     <row r="19" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="25"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -12240,8 +12248,8 @@
       </c>
     </row>
     <row r="20" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20"/>
-      <c r="B20" s="26"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -12319,7 +12327,7 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="29" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="39" t="s">
@@ -12396,7 +12404,7 @@
       </c>
     </row>
     <row r="23" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -12491,7 +12499,7 @@
       </c>
     </row>
     <row r="24" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -12564,7 +12572,7 @@
       </c>
     </row>
     <row r="25" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -12637,14 +12645,14 @@
       </c>
     </row>
     <row r="26" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
+      <c r="A27" s="29"/>
       <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
@@ -12719,7 +12727,7 @@
       </c>
     </row>
     <row r="28" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -12814,7 +12822,7 @@
       </c>
     </row>
     <row r="29" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -12887,7 +12895,7 @@
       </c>
     </row>
     <row r="30" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -12960,14 +12968,14 @@
       </c>
     </row>
     <row r="31" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
+      <c r="A32" s="29"/>
       <c r="B32" s="36" t="s">
         <v>17</v>
       </c>
@@ -13042,7 +13050,7 @@
       </c>
     </row>
     <row r="33" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
+      <c r="A33" s="29"/>
       <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
@@ -13137,7 +13145,7 @@
       </c>
     </row>
     <row r="34" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
+      <c r="A34" s="29"/>
       <c r="B34" s="37"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
@@ -13210,7 +13218,7 @@
       </c>
     </row>
     <row r="35" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
+      <c r="A35" s="29"/>
       <c r="B35" s="38"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
@@ -13283,14 +13291,14 @@
       </c>
     </row>
     <row r="36" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
+      <c r="A37" s="29"/>
       <c r="B37" s="36" t="s">
         <v>18</v>
       </c>
@@ -13365,7 +13373,7 @@
       </c>
     </row>
     <row r="38" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
+      <c r="A38" s="29"/>
       <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
@@ -13460,7 +13468,7 @@
       </c>
     </row>
     <row r="39" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
+      <c r="A39" s="29"/>
       <c r="B39" s="37"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
@@ -13533,7 +13541,7 @@
       </c>
     </row>
     <row r="40" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
+      <c r="A40" s="29"/>
       <c r="B40" s="38"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
@@ -13606,14 +13614,14 @@
       </c>
     </row>
     <row r="41" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
+      <c r="A41" s="29"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
+      <c r="A42" s="29"/>
       <c r="B42" s="36" t="s">
         <v>19</v>
       </c>
@@ -13710,7 +13718,7 @@
       </c>
     </row>
     <row r="43" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="21"/>
+      <c r="A43" s="29"/>
       <c r="B43" s="37"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
@@ -13783,7 +13791,7 @@
       </c>
     </row>
     <row r="44" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="21"/>
+      <c r="A44" s="29"/>
       <c r="B44" s="38"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
@@ -13856,12 +13864,12 @@
       </c>
     </row>
     <row r="45" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="21"/>
+      <c r="A45" s="29"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
     </row>
     <row r="46" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="21"/>
+      <c r="A46" s="29"/>
       <c r="B46" s="36" t="s">
         <v>30</v>
       </c>
@@ -13870,28 +13878,28 @@
       </c>
     </row>
     <row r="47" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="21"/>
+      <c r="A47" s="29"/>
       <c r="B47" s="37"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="21"/>
+      <c r="A48" s="29"/>
       <c r="B48" s="38"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="21"/>
+      <c r="A49" s="29"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="21"/>
+      <c r="A50" s="29"/>
       <c r="B50" s="36" t="s">
         <v>28</v>
       </c>
@@ -13988,7 +13996,7 @@
       </c>
     </row>
     <row r="51" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="21"/>
+      <c r="A51" s="29"/>
       <c r="B51" s="37"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
@@ -14083,7 +14091,7 @@
       </c>
     </row>
     <row r="52" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="21"/>
+      <c r="A52" s="29"/>
       <c r="B52" s="38"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
@@ -14194,28 +14202,28 @@
       </c>
     </row>
     <row r="55" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="22"/>
-      <c r="B55" s="22"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="22"/>
-      <c r="B56" s="22"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="30"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="22"/>
-      <c r="B57" s="23"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="31"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="22"/>
+      <c r="A58" s="30"/>
       <c r="B58" s="35" t="s">
         <v>30</v>
       </c>
@@ -14224,28 +14232,28 @@
       </c>
     </row>
     <row r="59" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="22"/>
-      <c r="B59" s="22"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="22"/>
-      <c r="B60" s="23"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="31"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="22"/>
+      <c r="A61" s="30"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="22"/>
+      <c r="A62" s="30"/>
       <c r="B62" s="35" t="s">
         <v>25</v>
       </c>
@@ -14254,22 +14262,22 @@
       </c>
     </row>
     <row r="63" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="22"/>
-      <c r="B63" s="22"/>
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="23"/>
-      <c r="B64" s="23"/>
+      <c r="A64" s="31"/>
+      <c r="B64" s="31"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -14346,7 +14354,7 @@
       </c>
     </row>
     <row r="67" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="31"/>
+      <c r="A67" s="19"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -14421,7 +14429,7 @@
       </c>
     </row>
     <row r="68" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="31"/>
+      <c r="A68" s="19"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -14496,7 +14504,7 @@
       </c>
     </row>
     <row r="69" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="32"/>
+      <c r="A69" s="20"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -14572,6 +14580,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B42:B44"/>
     <mergeCell ref="B50:B52"/>
     <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
@@ -14588,7 +14597,6 @@
     <mergeCell ref="B62:B64"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
-    <mergeCell ref="B42:B44"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14737,10 +14745,10 @@
       </c>
     </row>
     <row r="7" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -14751,8 +14759,8 @@
       </c>
     </row>
     <row r="8" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="20"/>
-      <c r="B8" s="18"/>
+      <c r="A8" s="28"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
@@ -14761,8 +14769,8 @@
       </c>
     </row>
     <row r="9" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20"/>
-      <c r="B9" s="18"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="26"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
@@ -14771,8 +14779,8 @@
       </c>
     </row>
     <row r="10" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="18"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -14781,8 +14789,8 @@
       </c>
     </row>
     <row r="11" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="18" t="s">
+      <c r="A11" s="28"/>
+      <c r="B11" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
@@ -14790,25 +14798,25 @@
       </c>
     </row>
     <row r="12" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="18"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="18"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="26"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
+      <c r="A14" s="28"/>
     </row>
     <row r="15" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="24" t="s">
+      <c r="A15" s="28"/>
+      <c r="B15" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -14819,8 +14827,8 @@
       </c>
     </row>
     <row r="16" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
-      <c r="B16" s="25"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="33"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
@@ -14829,8 +14837,8 @@
       </c>
     </row>
     <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="25"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="33"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
@@ -14839,8 +14847,8 @@
       </c>
     </row>
     <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="26"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="34"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
@@ -14855,7 +14863,7 @@
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="29" t="s">
         <v>131</v>
       </c>
       <c r="B20" s="39" t="s">
@@ -14866,35 +14874,35 @@
       </c>
     </row>
     <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="21"/>
+      <c r="A21" s="29"/>
       <c r="B21" s="39"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="21"/>
+      <c r="A22" s="29"/>
       <c r="B22" s="39"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="12"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="39" t="s">
         <v>16</v>
       </c>
@@ -14903,35 +14911,35 @@
       </c>
     </row>
     <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="39"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
+      <c r="A27" s="29"/>
       <c r="B27" s="39"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="13"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="36" t="s">
         <v>17</v>
       </c>
@@ -14940,35 +14948,35 @@
       </c>
     </row>
     <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="37"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
+      <c r="A32" s="29"/>
       <c r="B32" s="37"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
+      <c r="A33" s="29"/>
       <c r="B33" s="38"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
+      <c r="A34" s="29"/>
       <c r="B34" s="14"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
     <row r="35" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
+      <c r="A35" s="29"/>
       <c r="B35" s="36" t="s">
         <v>18</v>
       </c>
@@ -14977,35 +14985,35 @@
       </c>
     </row>
     <row r="36" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="37"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
+      <c r="A37" s="29"/>
       <c r="B37" s="37"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
+      <c r="A38" s="29"/>
       <c r="B38" s="38"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
+      <c r="A39" s="29"/>
       <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
     <row r="40" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
+      <c r="A40" s="29"/>
       <c r="B40" s="36" t="s">
         <v>19</v>
       </c>
@@ -15014,26 +15022,26 @@
       </c>
     </row>
     <row r="41" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
+      <c r="A41" s="29"/>
       <c r="B41" s="37"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
+      <c r="A42" s="29"/>
       <c r="B42" s="38"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="21"/>
+      <c r="A43" s="29"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
     </row>
     <row r="44" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="21"/>
+      <c r="A44" s="29"/>
       <c r="B44" s="36" t="s">
         <v>30</v>
       </c>
@@ -15042,28 +15050,28 @@
       </c>
     </row>
     <row r="45" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="21"/>
+      <c r="A45" s="29"/>
       <c r="B45" s="37"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="21"/>
+      <c r="A46" s="29"/>
       <c r="B46" s="38"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="21"/>
+      <c r="A47" s="29"/>
       <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
     <row r="48" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="21"/>
+      <c r="A48" s="29"/>
       <c r="B48" s="36" t="s">
         <v>28</v>
       </c>
@@ -15132,7 +15140,7 @@
       </c>
     </row>
     <row r="49" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="21"/>
+      <c r="A49" s="29"/>
       <c r="B49" s="37"/>
       <c r="C49" s="4" t="s">
         <v>129</v>
@@ -15199,7 +15207,7 @@
       </c>
     </row>
     <row r="50" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="21"/>
+      <c r="A50" s="29"/>
       <c r="B50" s="38"/>
       <c r="C50" s="4" t="s">
         <v>130</v>
@@ -15282,28 +15290,28 @@
       </c>
     </row>
     <row r="53" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="22"/>
-      <c r="B53" s="22"/>
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="22"/>
-      <c r="B54" s="22"/>
+      <c r="A54" s="30"/>
+      <c r="B54" s="30"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="22"/>
-      <c r="B55" s="23"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="31"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="22"/>
+      <c r="A56" s="30"/>
       <c r="B56" s="35" t="s">
         <v>30</v>
       </c>
@@ -15312,28 +15320,28 @@
       </c>
     </row>
     <row r="57" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="22"/>
-      <c r="B57" s="22"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="30"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="22"/>
-      <c r="B58" s="23"/>
+      <c r="A58" s="30"/>
+      <c r="B58" s="31"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="22"/>
+      <c r="A59" s="30"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
     </row>
     <row r="60" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="22"/>
+      <c r="A60" s="30"/>
       <c r="B60" s="35" t="s">
         <v>25</v>
       </c>
@@ -15342,22 +15350,22 @@
       </c>
     </row>
     <row r="61" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="22"/>
-      <c r="B61" s="22"/>
+      <c r="A61" s="30"/>
+      <c r="B61" s="30"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="23"/>
-      <c r="B62" s="23"/>
+      <c r="A62" s="31"/>
+      <c r="B62" s="31"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="64" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="30" t="s">
+      <c r="A64" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -15371,7 +15379,7 @@
       </c>
     </row>
     <row r="65" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="31"/>
+      <c r="A65" s="19"/>
       <c r="B65" s="4" t="s">
         <v>132</v>
       </c>
@@ -15383,7 +15391,7 @@
       </c>
     </row>
     <row r="66" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="31"/>
+      <c r="A66" s="19"/>
       <c r="B66" s="4" t="s">
         <v>133</v>
       </c>
@@ -15395,7 +15403,7 @@
       </c>
     </row>
     <row r="67" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="32"/>
+      <c r="A67" s="20"/>
       <c r="B67" s="5" t="s">
         <v>134</v>
       </c>
@@ -15408,6 +15416,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B40:B42"/>
     <mergeCell ref="B48:B50"/>
     <mergeCell ref="A64:A67"/>
     <mergeCell ref="A7:A18"/>
@@ -15424,7 +15433,6 @@
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="B35:B38"/>
-    <mergeCell ref="B40:B42"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15434,92 +15442,92 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC6F473E-E8F6-46BD-8C8C-636A58FA8F6F}">
-  <dimension ref="A3:AO67"/>
+  <dimension ref="A3:AR67"/>
   <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="16.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:41" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:41" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:44" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D4" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="U4" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="O4" s="1" t="s">
+      <c r="V4" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="Z4" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="P4" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="T4" s="1" t="s">
+      <c r="AA4" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="AB4" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="AC4" s="1" t="s">
         <v>149</v>
@@ -15531,37 +15539,46 @@
         <v>151</v>
       </c>
       <c r="AF4" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG4" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AH4" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AI4" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="AJ4" s="1" t="s">
+      <c r="AK4" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="AK4" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="AL4" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="AM4" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="AM4" s="1" t="s">
-        <v>266</v>
       </c>
       <c r="AN4" s="1" t="s">
         <v>220</v>
       </c>
       <c r="AO4" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="AP4" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="AQ4" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="AR4" s="1" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="5" spans="1:41" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:44" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="1" t="s">
         <v>124</v>
       </c>
@@ -15677,10 +15694,19 @@
         <v>4</v>
       </c>
       <c r="AO5" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:41" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="AP5" s="1">
+        <v>7</v>
+      </c>
+      <c r="AQ5" s="1">
+        <v>7</v>
+      </c>
+      <c r="AR5" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:44" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="1" t="s">
         <v>125</v>
       </c>
@@ -15699,94 +15725,103 @@
       <c r="AN6" s="1">
         <v>4</v>
       </c>
-      <c r="AO6" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="7" spans="1:41" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="20" t="s">
+      <c r="AO6" s="1">
+        <v>1</v>
+      </c>
+      <c r="AP6" s="1">
+        <v>2</v>
+      </c>
+      <c r="AQ6" s="1">
+        <v>3</v>
+      </c>
+      <c r="AR6" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:44" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:41" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="20"/>
-      <c r="B8" s="18"/>
+    <row r="8" spans="1:44" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="28"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:41" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20"/>
-      <c r="B9" s="18"/>
+    <row r="9" spans="1:44" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="28"/>
+      <c r="B9" s="26"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:41" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="18"/>
+    <row r="10" spans="1:44" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:41" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="18" t="s">
+    <row r="11" spans="1:44" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="28"/>
+      <c r="B11" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:41" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="18"/>
+    <row r="12" spans="1:44" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="28"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:41" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="18"/>
+    <row r="13" spans="1:44" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="28"/>
+      <c r="B13" s="26"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:41" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-    </row>
-    <row r="15" spans="1:41" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="24" t="s">
+    <row r="14" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="28"/>
+    </row>
+    <row r="15" spans="1:44" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="28"/>
+      <c r="B15" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:41" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
-      <c r="B16" s="25"/>
+    <row r="16" spans="1:44" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="28"/>
+      <c r="B16" s="33"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="25"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="33"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="26"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="34"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
@@ -15798,7 +15833,7 @@
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="29" t="s">
         <v>131</v>
       </c>
       <c r="B20" s="39" t="s">
@@ -15809,35 +15844,35 @@
       </c>
     </row>
     <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="21"/>
+      <c r="A21" s="29"/>
       <c r="B21" s="39"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="21"/>
+      <c r="A22" s="29"/>
       <c r="B22" s="39"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="12"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="39" t="s">
         <v>16</v>
       </c>
@@ -15846,35 +15881,35 @@
       </c>
     </row>
     <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="39"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
+      <c r="A27" s="29"/>
       <c r="B27" s="39"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="13"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="36" t="s">
         <v>17</v>
       </c>
@@ -15883,35 +15918,35 @@
       </c>
     </row>
     <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="37"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
+      <c r="A32" s="29"/>
       <c r="B32" s="37"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
+      <c r="A33" s="29"/>
       <c r="B33" s="38"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
+      <c r="A34" s="29"/>
       <c r="B34" s="14"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
+      <c r="A35" s="29"/>
       <c r="B35" s="36" t="s">
         <v>18</v>
       </c>
@@ -15920,35 +15955,35 @@
       </c>
     </row>
     <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="37"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
+      <c r="A37" s="29"/>
       <c r="B37" s="37"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
+      <c r="A38" s="29"/>
       <c r="B38" s="38"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
+      <c r="A39" s="29"/>
       <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
+      <c r="A40" s="29"/>
       <c r="B40" s="36" t="s">
         <v>19</v>
       </c>
@@ -15957,26 +15992,26 @@
       </c>
     </row>
     <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
+      <c r="A41" s="29"/>
       <c r="B41" s="37"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
+      <c r="A42" s="29"/>
       <c r="B42" s="38"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="21"/>
+      <c r="A43" s="29"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="21"/>
+      <c r="A44" s="29"/>
       <c r="B44" s="36" t="s">
         <v>30</v>
       </c>
@@ -15985,28 +16020,28 @@
       </c>
     </row>
     <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="21"/>
+      <c r="A45" s="29"/>
       <c r="B45" s="37"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="21"/>
+      <c r="A46" s="29"/>
       <c r="B46" s="38"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="21"/>
+      <c r="A47" s="29"/>
       <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="21"/>
+      <c r="A48" s="29"/>
       <c r="B48" s="36" t="s">
         <v>28</v>
       </c>
@@ -16071,7 +16106,7 @@
       </c>
     </row>
     <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="21"/>
+      <c r="A49" s="29"/>
       <c r="B49" s="37"/>
       <c r="C49" s="4" t="s">
         <v>129</v>
@@ -16134,7 +16169,7 @@
       </c>
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="21"/>
+      <c r="A50" s="29"/>
       <c r="B50" s="38"/>
       <c r="C50" s="4" t="s">
         <v>130</v>
@@ -16213,28 +16248,28 @@
       </c>
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="22"/>
-      <c r="B53" s="22"/>
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="22"/>
-      <c r="B54" s="22"/>
+      <c r="A54" s="30"/>
+      <c r="B54" s="30"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="22"/>
-      <c r="B55" s="23"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="31"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="22"/>
+      <c r="A56" s="30"/>
       <c r="B56" s="35" t="s">
         <v>30</v>
       </c>
@@ -16243,28 +16278,28 @@
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="22"/>
-      <c r="B57" s="22"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="30"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="22"/>
-      <c r="B58" s="23"/>
+      <c r="A58" s="30"/>
+      <c r="B58" s="31"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="22"/>
+      <c r="A59" s="30"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="22"/>
+      <c r="A60" s="30"/>
       <c r="B60" s="35" t="s">
         <v>25</v>
       </c>
@@ -16273,21 +16308,21 @@
       </c>
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="22"/>
-      <c r="B61" s="22"/>
+      <c r="A61" s="30"/>
+      <c r="B61" s="30"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="23"/>
-      <c r="B62" s="23"/>
+      <c r="A62" s="31"/>
+      <c r="B62" s="31"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="30" t="s">
+      <c r="A64" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -16298,7 +16333,7 @@
       </c>
     </row>
     <row r="65" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="31"/>
+      <c r="A65" s="19"/>
       <c r="B65" s="4" t="s">
         <v>132</v>
       </c>
@@ -16307,7 +16342,7 @@
       </c>
     </row>
     <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="31"/>
+      <c r="A66" s="19"/>
       <c r="B66" s="4" t="s">
         <v>133</v>
       </c>
@@ -16316,7 +16351,7 @@
       </c>
     </row>
     <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="32"/>
+      <c r="A67" s="20"/>
       <c r="B67" s="5" t="s">
         <v>134</v>
       </c>
@@ -16330,6 +16365,13 @@
     <sortCondition ref="C6:AO6"/>
   </sortState>
   <mergeCells count="17">
+    <mergeCell ref="A64:A67"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A52:A62"/>
+    <mergeCell ref="B52:B55"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="B60:B62"/>
     <mergeCell ref="A7:A18"/>
     <mergeCell ref="B7:B10"/>
     <mergeCell ref="B11:B13"/>
@@ -16340,13 +16382,6 @@
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="B35:B38"/>
     <mergeCell ref="B40:B42"/>
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A52:A62"/>
-    <mergeCell ref="B52:B55"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B60:B62"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dev_stuffs/3匠魂.xlsx
+++ b/dev_stuffs/3匠魂.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\Palmon\dev_stuffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B5BA7F6-3061-4923-BE90-217653DE11A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489C3C0D-92FB-465A-BAA7-DE219658F5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2880" yWindow="2895" windowWidth="24015" windowHeight="15435" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="阶段1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="阶段4" sheetId="9" r:id="rId4"/>
     <sheet name="阶段5" sheetId="10" r:id="rId5"/>
     <sheet name="阶段EX" sheetId="11" r:id="rId6"/>
-    <sheet name="追加" sheetId="12" r:id="rId7"/>
+    <sheet name="追加1" sheetId="12" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="304">
   <si>
     <t>材料名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -817,70 +817,14 @@
     <t>'kubejs:ember_profile'</t>
   </si>
   <si>
-    <t>铁</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>毒之骨</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>粘木</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>锇</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>防腐木</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>铅</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>银</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>粘钢</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>紫水晶青铜</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>纳瓦</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>生铁</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>玫瑰金</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>青铜</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>康铜</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>殷钢</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>琥珀金</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>黏液浸钢</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -893,22 +837,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>钴</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>钢</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄铜</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>余烬黏液</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>皇后史莱姆</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -917,43 +845,206 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>锑</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>木</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>岩石</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>燧石</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>骨头</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>铜</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>紫菘</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中子</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>热核</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>光谱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>minecraft:iron</t>
+  </si>
+  <si>
+    <t>minecraft:wood</t>
+  </si>
+  <si>
+    <t>minecraft:stone</t>
+  </si>
+  <si>
+    <t>minecraft:gold</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>minecraft:diamond</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>防腐木*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>木*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>minecraft:stone</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>岩石*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>燧石*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>骨头*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>铅*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>银*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生铁*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玫瑰金*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>青铜*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>康铜*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>殷钢*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>琥珀金*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>钢*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄铜*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>铜*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>粘木*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫水晶青铜*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>纳瓦*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>钴*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>余烬黏液*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>锑*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫菘*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>techreborn:lead_ingot</t>
+  </si>
+  <si>
+    <t>techreborn:silver_ingot</t>
+  </si>
+  <si>
+    <t>tfc:metal/ingot/pig_iron</t>
+  </si>
+  <si>
+    <t>tconstruct:rose_gold_ingot</t>
+  </si>
+  <si>
+    <t>tfc:metal/ingot/bronze</t>
+  </si>
+  <si>
+    <t>thermal:constantan_ingot</t>
+  </si>
+  <si>
+    <t>thermal:invar_ingot</t>
+  </si>
+  <si>
+    <t>thermal:electrum_ingot</t>
+  </si>
+  <si>
+    <t>tfc:metal/ingot/steel</t>
+  </si>
+  <si>
+    <t>tfc:metal/ingot/brass</t>
+  </si>
+  <si>
+    <t>minecraft:copper_ingot</t>
+  </si>
+  <si>
+    <t>tconstruct:stripped_greenheart_log</t>
+  </si>
+  <si>
+    <t>tconstruct:amethyst_bronze_ingot</t>
+  </si>
+  <si>
+    <t>tconstruct:nahuatl</t>
+  </si>
+  <si>
+    <t>tconstruct:cobalt_ingot</t>
+  </si>
+  <si>
+    <t>tconstruct:cinderslime_ingot</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:antimony_ingot</t>
+  </si>
+  <si>
+    <t>minecraft:chorus_fruit</t>
+  </si>
+  <si>
+    <t>treated_wood</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wood</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rock</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>flint</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bone</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>iron</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1204,30 +1295,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1255,7 +1322,28 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
@@ -1265,6 +1353,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
@@ -1728,10 +1819,10 @@
       </c>
     </row>
     <row r="9" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -1769,8 +1860,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="26"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -1806,8 +1897,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="26"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -1843,8 +1934,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="26"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -1880,8 +1971,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="26" t="s">
+      <c r="A13" s="20"/>
+      <c r="B13" s="18" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -1889,25 +1980,25 @@
       </c>
     </row>
     <row r="14" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-      <c r="B14" s="26"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="18"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="26"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="18"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
+      <c r="A16" s="20"/>
     </row>
     <row r="17" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28"/>
-      <c r="B17" s="32" t="s">
+      <c r="A17" s="20"/>
+      <c r="B17" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -1945,8 +2036,8 @@
       </c>
     </row>
     <row r="18" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28"/>
-      <c r="B18" s="33"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1982,8 +2073,8 @@
       </c>
     </row>
     <row r="19" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="28"/>
-      <c r="B19" s="33"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="25"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -2019,8 +2110,8 @@
       </c>
     </row>
     <row r="20" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28"/>
-      <c r="B20" s="34"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -2062,10 +2153,10 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="21" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -2103,8 +2194,8 @@
       </c>
     </row>
     <row r="23" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="25"/>
-      <c r="B23" s="29"/>
+      <c r="A23" s="34"/>
+      <c r="B23" s="21"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
       </c>
@@ -2150,8 +2241,8 @@
       </c>
     </row>
     <row r="24" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="25"/>
-      <c r="B24" s="29"/>
+      <c r="A24" s="34"/>
+      <c r="B24" s="21"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
       </c>
@@ -2187,22 +2278,22 @@
       </c>
     </row>
     <row r="25" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="25"/>
-      <c r="B25" s="29"/>
+      <c r="A25" s="34"/>
+      <c r="B25" s="21"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="25"/>
+      <c r="A26" s="34"/>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="25"/>
-      <c r="B27" s="29" t="s">
+      <c r="A27" s="34"/>
+      <c r="B27" s="21" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="4" t="s">
@@ -2240,8 +2331,8 @@
       </c>
     </row>
     <row r="28" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="25"/>
-      <c r="B28" s="29"/>
+      <c r="A28" s="34"/>
+      <c r="B28" s="21"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
       </c>
@@ -2287,8 +2378,8 @@
       </c>
     </row>
     <row r="29" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="25"/>
-      <c r="B29" s="29"/>
+      <c r="A29" s="34"/>
+      <c r="B29" s="21"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
       </c>
@@ -2324,22 +2415,22 @@
       </c>
     </row>
     <row r="30" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="25"/>
-      <c r="B30" s="29"/>
+      <c r="A30" s="34"/>
+      <c r="B30" s="21"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="25"/>
+      <c r="A31" s="34"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="25"/>
-      <c r="B32" s="21" t="s">
+      <c r="A32" s="34"/>
+      <c r="B32" s="27" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -2377,8 +2468,8 @@
       </c>
     </row>
     <row r="33" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="25"/>
-      <c r="B33" s="22"/>
+      <c r="A33" s="34"/>
+      <c r="B33" s="28"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -2424,8 +2515,8 @@
       </c>
     </row>
     <row r="34" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="25"/>
-      <c r="B34" s="22"/>
+      <c r="A34" s="34"/>
+      <c r="B34" s="28"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -2461,22 +2552,22 @@
       </c>
     </row>
     <row r="35" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="25"/>
-      <c r="B35" s="23"/>
+      <c r="A35" s="34"/>
+      <c r="B35" s="29"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="25"/>
+      <c r="A36" s="34"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="25"/>
-      <c r="B37" s="21" t="s">
+      <c r="A37" s="34"/>
+      <c r="B37" s="27" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -2514,8 +2605,8 @@
       </c>
     </row>
     <row r="38" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="25"/>
-      <c r="B38" s="22"/>
+      <c r="A38" s="34"/>
+      <c r="B38" s="28"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -2561,8 +2652,8 @@
       </c>
     </row>
     <row r="39" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="25"/>
-      <c r="B39" s="22"/>
+      <c r="A39" s="34"/>
+      <c r="B39" s="28"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -2598,22 +2689,22 @@
       </c>
     </row>
     <row r="40" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="25"/>
-      <c r="B40" s="23"/>
+      <c r="A40" s="34"/>
+      <c r="B40" s="29"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="25"/>
+      <c r="A41" s="34"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="25"/>
-      <c r="B42" s="21" t="s">
+      <c r="A42" s="34"/>
+      <c r="B42" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -2661,8 +2752,8 @@
       </c>
     </row>
     <row r="43" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="25"/>
-      <c r="B43" s="22"/>
+      <c r="A43" s="34"/>
+      <c r="B43" s="28"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -2698,18 +2789,18 @@
       </c>
     </row>
     <row r="44" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="25"/>
-      <c r="B44" s="23"/>
+      <c r="A44" s="34"/>
+      <c r="B44" s="29"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="25"/>
+      <c r="A45" s="34"/>
     </row>
     <row r="46" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="25"/>
-      <c r="B46" s="21" t="s">
+      <c r="A46" s="34"/>
+      <c r="B46" s="27" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -2717,29 +2808,29 @@
       </c>
     </row>
     <row r="47" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="25"/>
-      <c r="B47" s="22"/>
+      <c r="A47" s="34"/>
+      <c r="B47" s="28"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="25"/>
-      <c r="B48" s="23"/>
+      <c r="A48" s="34"/>
+      <c r="B48" s="29"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="25"/>
+      <c r="A49" s="34"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
     </row>
     <row r="50" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="25"/>
-      <c r="B50" s="21" t="s">
+      <c r="A50" s="34"/>
+      <c r="B50" s="27" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -2787,8 +2878,8 @@
       </c>
     </row>
     <row r="51" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="25"/>
-      <c r="B51" s="22"/>
+      <c r="A51" s="34"/>
+      <c r="B51" s="28"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -2834,8 +2925,8 @@
       </c>
     </row>
     <row r="52" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="25"/>
-      <c r="B52" s="23"/>
+      <c r="A52" s="34"/>
+      <c r="B52" s="29"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -2887,10 +2978,10 @@
       <c r="E53" s="8"/>
     </row>
     <row r="54" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="27" t="s">
+      <c r="A54" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="27" t="s">
+      <c r="B54" s="19" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -2898,29 +2989,29 @@
       </c>
     </row>
     <row r="55" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="27"/>
-      <c r="B55" s="27"/>
+      <c r="A55" s="19"/>
+      <c r="B55" s="19"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="27"/>
-      <c r="B56" s="27"/>
+      <c r="A56" s="19"/>
+      <c r="B56" s="19"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="27"/>
-      <c r="B57" s="27"/>
+      <c r="A57" s="19"/>
+      <c r="B57" s="19"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="27"/>
-      <c r="B58" s="27" t="s">
+      <c r="A58" s="19"/>
+      <c r="B58" s="19" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -2928,29 +3019,29 @@
       </c>
     </row>
     <row r="59" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="27"/>
-      <c r="B59" s="30"/>
+      <c r="A59" s="19"/>
+      <c r="B59" s="22"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="27"/>
-      <c r="B60" s="31"/>
+      <c r="A60" s="19"/>
+      <c r="B60" s="23"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="27"/>
+      <c r="A61" s="19"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="27"/>
-      <c r="B62" s="27" t="s">
+      <c r="A62" s="19"/>
+      <c r="B62" s="19" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -2958,21 +3049,21 @@
       </c>
     </row>
     <row r="63" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="27"/>
-      <c r="B63" s="30"/>
+      <c r="A63" s="19"/>
+      <c r="B63" s="22"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="27"/>
-      <c r="B64" s="31"/>
+      <c r="A64" s="19"/>
+      <c r="B64" s="23"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="18" t="s">
+      <c r="A67" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B67" s="6" t="s">
@@ -3013,7 +3104,7 @@
       </c>
     </row>
     <row r="68" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="19"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="4" t="s">
         <v>132</v>
       </c>
@@ -3052,7 +3143,7 @@
       </c>
     </row>
     <row r="69" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="19"/>
+      <c r="A69" s="31"/>
       <c r="B69" s="4" t="s">
         <v>133</v>
       </c>
@@ -3091,7 +3182,7 @@
       </c>
     </row>
     <row r="70" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="20"/>
+      <c r="A70" s="32"/>
       <c r="B70" s="5" t="s">
         <v>134</v>
       </c>
@@ -3131,7 +3222,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B50:B52"/>
     <mergeCell ref="A67:A70"/>
     <mergeCell ref="B46:B48"/>
     <mergeCell ref="A22:A52"/>
@@ -3148,6 +3238,7 @@
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B50:B52"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3417,10 +3508,10 @@
       </c>
     </row>
     <row r="9" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -3470,8 +3561,8 @@
       </c>
     </row>
     <row r="10" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="26"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -3519,8 +3610,8 @@
       </c>
     </row>
     <row r="11" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="26"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -3568,8 +3659,8 @@
       </c>
     </row>
     <row r="12" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="26"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -3617,8 +3708,8 @@
       </c>
     </row>
     <row r="13" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="26" t="s">
+      <c r="A13" s="20"/>
+      <c r="B13" s="18" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -3626,25 +3717,25 @@
       </c>
     </row>
     <row r="14" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-      <c r="B14" s="26"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="18"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="26"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="18"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
+      <c r="A16" s="20"/>
     </row>
     <row r="17" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28"/>
-      <c r="B17" s="32" t="s">
+      <c r="A17" s="20"/>
+      <c r="B17" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -3694,8 +3785,8 @@
       </c>
     </row>
     <row r="18" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28"/>
-      <c r="B18" s="33"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -3743,8 +3834,8 @@
       </c>
     </row>
     <row r="19" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="28"/>
-      <c r="B19" s="33"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="25"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -3792,8 +3883,8 @@
       </c>
     </row>
     <row r="20" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28"/>
-      <c r="B20" s="34"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -3847,7 +3938,7 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="21" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="39" t="s">
@@ -3900,7 +3991,7 @@
       </c>
     </row>
     <row r="23" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="29"/>
+      <c r="A23" s="21"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -3963,7 +4054,7 @@
       </c>
     </row>
     <row r="24" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="29"/>
+      <c r="A24" s="21"/>
       <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -4012,7 +4103,7 @@
       </c>
     </row>
     <row r="25" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="29"/>
+      <c r="A25" s="21"/>
       <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -4043,14 +4134,14 @@
       </c>
     </row>
     <row r="26" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="29"/>
+      <c r="A26" s="21"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="29"/>
+      <c r="A27" s="21"/>
       <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
@@ -4101,7 +4192,7 @@
       </c>
     </row>
     <row r="28" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="29"/>
+      <c r="A28" s="21"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -4164,7 +4255,7 @@
       </c>
     </row>
     <row r="29" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="29"/>
+      <c r="A29" s="21"/>
       <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -4213,7 +4304,7 @@
       </c>
     </row>
     <row r="30" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="29"/>
+      <c r="A30" s="21"/>
       <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -4244,15 +4335,15 @@
       </c>
     </row>
     <row r="31" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="29"/>
+      <c r="A31" s="21"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="29"/>
-      <c r="B32" s="36" t="s">
+      <c r="A32" s="21"/>
+      <c r="B32" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -4302,8 +4393,8 @@
       </c>
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="29"/>
-      <c r="B33" s="37"/>
+      <c r="A33" s="21"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -4365,8 +4456,8 @@
       </c>
     </row>
     <row r="34" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="29"/>
-      <c r="B34" s="37"/>
+      <c r="A34" s="21"/>
+      <c r="B34" s="36"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -4414,8 +4505,8 @@
       </c>
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="29"/>
-      <c r="B35" s="38"/>
+      <c r="A35" s="21"/>
+      <c r="B35" s="37"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
@@ -4445,15 +4536,15 @@
       </c>
     </row>
     <row r="36" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="29"/>
+      <c r="A36" s="21"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="29"/>
-      <c r="B37" s="36" t="s">
+      <c r="A37" s="21"/>
+      <c r="B37" s="35" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -4503,8 +4594,8 @@
       </c>
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="29"/>
-      <c r="B38" s="37"/>
+      <c r="A38" s="21"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -4566,8 +4657,8 @@
       </c>
     </row>
     <row r="39" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="29"/>
-      <c r="B39" s="37"/>
+      <c r="A39" s="21"/>
+      <c r="B39" s="36"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -4615,8 +4706,8 @@
       </c>
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="29"/>
-      <c r="B40" s="38"/>
+      <c r="A40" s="21"/>
+      <c r="B40" s="37"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
@@ -4646,15 +4737,15 @@
       </c>
     </row>
     <row r="41" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="29"/>
+      <c r="A41" s="21"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="29"/>
-      <c r="B42" s="36" t="s">
+      <c r="A42" s="21"/>
+      <c r="B42" s="35" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -4718,8 +4809,8 @@
       </c>
     </row>
     <row r="43" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="29"/>
-      <c r="B43" s="37"/>
+      <c r="A43" s="21"/>
+      <c r="B43" s="36"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -4767,8 +4858,8 @@
       </c>
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="29"/>
-      <c r="B44" s="38"/>
+      <c r="A44" s="21"/>
+      <c r="B44" s="37"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
@@ -4798,13 +4889,13 @@
       </c>
     </row>
     <row r="45" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="29"/>
+      <c r="A45" s="21"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="29"/>
-      <c r="B46" s="36" t="s">
+      <c r="A46" s="21"/>
+      <c r="B46" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -4812,29 +4903,29 @@
       </c>
     </row>
     <row r="47" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="29"/>
-      <c r="B47" s="37"/>
+      <c r="A47" s="21"/>
+      <c r="B47" s="36"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="29"/>
-      <c r="B48" s="38"/>
+      <c r="A48" s="21"/>
+      <c r="B48" s="37"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="29"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="29"/>
-      <c r="B50" s="36" t="s">
+      <c r="A50" s="21"/>
+      <c r="B50" s="35" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -4898,8 +4989,8 @@
       </c>
     </row>
     <row r="51" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="29"/>
-      <c r="B51" s="37"/>
+      <c r="A51" s="21"/>
+      <c r="B51" s="36"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -4961,8 +5052,8 @@
       </c>
     </row>
     <row r="52" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="29"/>
-      <c r="B52" s="38"/>
+      <c r="A52" s="21"/>
+      <c r="B52" s="37"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -5029,10 +5120,10 @@
       <c r="C53" s="8"/>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="35" t="s">
+      <c r="A54" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="35" t="s">
+      <c r="B54" s="38" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -5040,29 +5131,29 @@
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="30"/>
-      <c r="B55" s="30"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="30"/>
-      <c r="B56" s="30"/>
+      <c r="A56" s="22"/>
+      <c r="B56" s="22"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="30"/>
-      <c r="B57" s="31"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="23"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="30"/>
-      <c r="B58" s="35" t="s">
+      <c r="A58" s="22"/>
+      <c r="B58" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -5070,29 +5161,29 @@
       </c>
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="30"/>
-      <c r="B59" s="30"/>
+      <c r="A59" s="22"/>
+      <c r="B59" s="22"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="30"/>
-      <c r="B60" s="31"/>
+      <c r="A60" s="22"/>
+      <c r="B60" s="23"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="30"/>
+      <c r="A61" s="22"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="30"/>
-      <c r="B62" s="35" t="s">
+      <c r="A62" s="22"/>
+      <c r="B62" s="38" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -5100,22 +5191,22 @@
       </c>
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="30"/>
-      <c r="B63" s="30"/>
+      <c r="A63" s="22"/>
+      <c r="B63" s="22"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="31"/>
-      <c r="B64" s="31"/>
+      <c r="A64" s="23"/>
+      <c r="B64" s="23"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="18" t="s">
+      <c r="A66" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -5168,7 +5259,7 @@
       </c>
     </row>
     <row r="67" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="19"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -5213,7 +5304,7 @@
       </c>
     </row>
     <row r="68" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="19"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -5258,7 +5349,7 @@
       </c>
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="20"/>
+      <c r="A69" s="32"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -5268,6 +5359,9 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="B62:B64"/>
     <mergeCell ref="B9:B12"/>
@@ -5282,9 +5376,6 @@
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="A54:A64"/>
     <mergeCell ref="B54:B57"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="A66:A69"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5768,10 +5859,10 @@
       </c>
     </row>
     <row r="9" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -5863,8 +5954,8 @@
       </c>
     </row>
     <row r="10" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="26"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -5954,8 +6045,8 @@
       </c>
     </row>
     <row r="11" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="26"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -6045,8 +6136,8 @@
       </c>
     </row>
     <row r="12" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="26"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -6136,8 +6227,8 @@
       </c>
     </row>
     <row r="13" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="26" t="s">
+      <c r="A13" s="20"/>
+      <c r="B13" s="18" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -6145,25 +6236,25 @@
       </c>
     </row>
     <row r="14" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-      <c r="B14" s="26"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="18"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="26"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="18"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
+      <c r="A16" s="20"/>
     </row>
     <row r="17" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28"/>
-      <c r="B17" s="32" t="s">
+      <c r="A17" s="20"/>
+      <c r="B17" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -6255,8 +6346,8 @@
       </c>
     </row>
     <row r="18" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28"/>
-      <c r="B18" s="33"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -6346,8 +6437,8 @@
       </c>
     </row>
     <row r="19" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="28"/>
-      <c r="B19" s="33"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="25"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -6437,8 +6528,8 @@
       </c>
     </row>
     <row r="20" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28"/>
-      <c r="B20" s="34"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -6537,7 +6628,7 @@
       </c>
     </row>
     <row r="22" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="21" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="39" t="s">
@@ -6632,7 +6723,7 @@
       </c>
     </row>
     <row r="23" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="29"/>
+      <c r="A23" s="21"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -6751,7 +6842,7 @@
       </c>
     </row>
     <row r="24" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="29"/>
+      <c r="A24" s="21"/>
       <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -6842,7 +6933,7 @@
       </c>
     </row>
     <row r="25" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="29"/>
+      <c r="A25" s="21"/>
       <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -6933,14 +7024,14 @@
       </c>
     </row>
     <row r="26" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="29"/>
+      <c r="A26" s="21"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="29"/>
+      <c r="A27" s="21"/>
       <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
@@ -7033,7 +7124,7 @@
       </c>
     </row>
     <row r="28" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="29"/>
+      <c r="A28" s="21"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -7152,7 +7243,7 @@
       </c>
     </row>
     <row r="29" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="29"/>
+      <c r="A29" s="21"/>
       <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -7243,7 +7334,7 @@
       </c>
     </row>
     <row r="30" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="29"/>
+      <c r="A30" s="21"/>
       <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -7334,15 +7425,15 @@
       </c>
     </row>
     <row r="31" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="29"/>
+      <c r="A31" s="21"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="29"/>
-      <c r="B32" s="36" t="s">
+      <c r="A32" s="21"/>
+      <c r="B32" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -7434,8 +7525,8 @@
       </c>
     </row>
     <row r="33" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="29"/>
-      <c r="B33" s="37"/>
+      <c r="A33" s="21"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -7553,8 +7644,8 @@
       </c>
     </row>
     <row r="34" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="29"/>
-      <c r="B34" s="37"/>
+      <c r="A34" s="21"/>
+      <c r="B34" s="36"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -7644,8 +7735,8 @@
       </c>
     </row>
     <row r="35" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="29"/>
-      <c r="B35" s="38"/>
+      <c r="A35" s="21"/>
+      <c r="B35" s="37"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
@@ -7735,15 +7826,15 @@
       </c>
     </row>
     <row r="36" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="29"/>
+      <c r="A36" s="21"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="29"/>
-      <c r="B37" s="36" t="s">
+      <c r="A37" s="21"/>
+      <c r="B37" s="35" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -7835,8 +7926,8 @@
       </c>
     </row>
     <row r="38" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="29"/>
-      <c r="B38" s="37"/>
+      <c r="A38" s="21"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -7954,8 +8045,8 @@
       </c>
     </row>
     <row r="39" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="29"/>
-      <c r="B39" s="37"/>
+      <c r="A39" s="21"/>
+      <c r="B39" s="36"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -8045,8 +8136,8 @@
       </c>
     </row>
     <row r="40" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="29"/>
-      <c r="B40" s="38"/>
+      <c r="A40" s="21"/>
+      <c r="B40" s="37"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
@@ -8136,15 +8227,15 @@
       </c>
     </row>
     <row r="41" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="29"/>
+      <c r="A41" s="21"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="29"/>
-      <c r="B42" s="36" t="s">
+      <c r="A42" s="21"/>
+      <c r="B42" s="35" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -8152,8 +8243,8 @@
       </c>
     </row>
     <row r="43" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="29"/>
-      <c r="B43" s="37"/>
+      <c r="A43" s="21"/>
+      <c r="B43" s="36"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -8243,8 +8334,8 @@
       </c>
     </row>
     <row r="44" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="29"/>
-      <c r="B44" s="38"/>
+      <c r="A44" s="21"/>
+      <c r="B44" s="37"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
@@ -8334,13 +8425,13 @@
       </c>
     </row>
     <row r="45" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="29"/>
+      <c r="A45" s="21"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
     </row>
     <row r="46" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="29"/>
-      <c r="B46" s="36" t="s">
+      <c r="A46" s="21"/>
+      <c r="B46" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -8348,29 +8439,29 @@
       </c>
     </row>
     <row r="47" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="29"/>
-      <c r="B47" s="37"/>
+      <c r="A47" s="21"/>
+      <c r="B47" s="36"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="29"/>
-      <c r="B48" s="38"/>
+      <c r="A48" s="21"/>
+      <c r="B48" s="37"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="29"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="29"/>
-      <c r="B50" s="36" t="s">
+      <c r="A50" s="21"/>
+      <c r="B50" s="35" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -8490,8 +8581,8 @@
       </c>
     </row>
     <row r="51" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="29"/>
-      <c r="B51" s="37"/>
+      <c r="A51" s="21"/>
+      <c r="B51" s="36"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -8609,8 +8700,8 @@
       </c>
     </row>
     <row r="52" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="29"/>
-      <c r="B52" s="38"/>
+      <c r="A52" s="21"/>
+      <c r="B52" s="37"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -8733,10 +8824,10 @@
       <c r="C53" s="8"/>
     </row>
     <row r="54" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="35" t="s">
+      <c r="A54" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="35" t="s">
+      <c r="B54" s="38" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -8744,29 +8835,29 @@
       </c>
     </row>
     <row r="55" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="30"/>
-      <c r="B55" s="30"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="30"/>
-      <c r="B56" s="30"/>
+      <c r="A56" s="22"/>
+      <c r="B56" s="22"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="30"/>
-      <c r="B57" s="31"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="23"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="30"/>
-      <c r="B58" s="35" t="s">
+      <c r="A58" s="22"/>
+      <c r="B58" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -8774,29 +8865,29 @@
       </c>
     </row>
     <row r="59" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="30"/>
-      <c r="B59" s="30"/>
+      <c r="A59" s="22"/>
+      <c r="B59" s="22"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="30"/>
-      <c r="B60" s="31"/>
+      <c r="A60" s="22"/>
+      <c r="B60" s="23"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="30"/>
+      <c r="A61" s="22"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="30"/>
-      <c r="B62" s="35" t="s">
+      <c r="A62" s="22"/>
+      <c r="B62" s="38" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -8804,22 +8895,22 @@
       </c>
     </row>
     <row r="63" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="30"/>
-      <c r="B63" s="30"/>
+      <c r="A63" s="22"/>
+      <c r="B63" s="22"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="31"/>
-      <c r="B64" s="31"/>
+      <c r="A64" s="23"/>
+      <c r="B64" s="23"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:31" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="18" t="s">
+      <c r="A66" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -8914,7 +9005,7 @@
       </c>
     </row>
     <row r="67" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="19"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -9007,7 +9098,7 @@
       </c>
     </row>
     <row r="68" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="19"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -9100,7 +9191,7 @@
       </c>
     </row>
     <row r="69" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="20"/>
+      <c r="A69" s="32"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -9194,9 +9285,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="B9:B12"/>
@@ -9211,6 +9299,9 @@
     <mergeCell ref="B62:B64"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A66:A69"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9453,10 +9544,10 @@
       </c>
     </row>
     <row r="9" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -9500,8 +9591,8 @@
       </c>
     </row>
     <row r="10" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="26"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -9543,8 +9634,8 @@
       </c>
     </row>
     <row r="11" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="26"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -9586,8 +9677,8 @@
       </c>
     </row>
     <row r="12" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="26"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -9629,8 +9720,8 @@
       </c>
     </row>
     <row r="13" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="26" t="s">
+      <c r="A13" s="20"/>
+      <c r="B13" s="18" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -9638,25 +9729,25 @@
       </c>
     </row>
     <row r="14" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-      <c r="B14" s="26"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="18"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="26"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="18"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
+      <c r="A16" s="20"/>
     </row>
     <row r="17" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28"/>
-      <c r="B17" s="32" t="s">
+      <c r="A17" s="20"/>
+      <c r="B17" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -9700,8 +9791,8 @@
       </c>
     </row>
     <row r="18" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28"/>
-      <c r="B18" s="33"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -9743,8 +9834,8 @@
       </c>
     </row>
     <row r="19" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="28"/>
-      <c r="B19" s="33"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="25"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -9786,8 +9877,8 @@
       </c>
     </row>
     <row r="20" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28"/>
-      <c r="B20" s="34"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -9835,7 +9926,7 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="21" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="39" t="s">
@@ -9882,7 +9973,7 @@
       </c>
     </row>
     <row r="23" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="29"/>
+      <c r="A23" s="21"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -9937,7 +10028,7 @@
       </c>
     </row>
     <row r="24" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="29"/>
+      <c r="A24" s="21"/>
       <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -9980,7 +10071,7 @@
       </c>
     </row>
     <row r="25" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="29"/>
+      <c r="A25" s="21"/>
       <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -10023,14 +10114,14 @@
       </c>
     </row>
     <row r="26" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="29"/>
+      <c r="A26" s="21"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="29"/>
+      <c r="A27" s="21"/>
       <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
@@ -10075,7 +10166,7 @@
       </c>
     </row>
     <row r="28" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="29"/>
+      <c r="A28" s="21"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -10130,7 +10221,7 @@
       </c>
     </row>
     <row r="29" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="29"/>
+      <c r="A29" s="21"/>
       <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -10173,7 +10264,7 @@
       </c>
     </row>
     <row r="30" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="29"/>
+      <c r="A30" s="21"/>
       <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -10216,15 +10307,15 @@
       </c>
     </row>
     <row r="31" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="29"/>
+      <c r="A31" s="21"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="29"/>
-      <c r="B32" s="36" t="s">
+      <c r="A32" s="21"/>
+      <c r="B32" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -10268,8 +10359,8 @@
       </c>
     </row>
     <row r="33" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="29"/>
-      <c r="B33" s="37"/>
+      <c r="A33" s="21"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -10323,8 +10414,8 @@
       </c>
     </row>
     <row r="34" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="29"/>
-      <c r="B34" s="37"/>
+      <c r="A34" s="21"/>
+      <c r="B34" s="36"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -10366,8 +10457,8 @@
       </c>
     </row>
     <row r="35" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="29"/>
-      <c r="B35" s="38"/>
+      <c r="A35" s="21"/>
+      <c r="B35" s="37"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
@@ -10409,15 +10500,15 @@
       </c>
     </row>
     <row r="36" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="29"/>
+      <c r="A36" s="21"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="29"/>
-      <c r="B37" s="36" t="s">
+      <c r="A37" s="21"/>
+      <c r="B37" s="35" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -10461,8 +10552,8 @@
       </c>
     </row>
     <row r="38" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="29"/>
-      <c r="B38" s="37"/>
+      <c r="A38" s="21"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -10516,8 +10607,8 @@
       </c>
     </row>
     <row r="39" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="29"/>
-      <c r="B39" s="37"/>
+      <c r="A39" s="21"/>
+      <c r="B39" s="36"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -10559,8 +10650,8 @@
       </c>
     </row>
     <row r="40" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="29"/>
-      <c r="B40" s="38"/>
+      <c r="A40" s="21"/>
+      <c r="B40" s="37"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
@@ -10602,15 +10693,15 @@
       </c>
     </row>
     <row r="41" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="29"/>
+      <c r="A41" s="21"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="29"/>
-      <c r="B42" s="36" t="s">
+      <c r="A42" s="21"/>
+      <c r="B42" s="35" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -10666,8 +10757,8 @@
       </c>
     </row>
     <row r="43" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="29"/>
-      <c r="B43" s="37"/>
+      <c r="A43" s="21"/>
+      <c r="B43" s="36"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -10709,8 +10800,8 @@
       </c>
     </row>
     <row r="44" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="29"/>
-      <c r="B44" s="38"/>
+      <c r="A44" s="21"/>
+      <c r="B44" s="37"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
@@ -10752,14 +10843,14 @@
       </c>
     </row>
     <row r="45" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="29"/>
+      <c r="A45" s="21"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
       <c r="F45" s="17"/>
     </row>
     <row r="46" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="29"/>
-      <c r="B46" s="36" t="s">
+      <c r="A46" s="21"/>
+      <c r="B46" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -10767,29 +10858,29 @@
       </c>
     </row>
     <row r="47" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="29"/>
-      <c r="B47" s="37"/>
+      <c r="A47" s="21"/>
+      <c r="B47" s="36"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="29"/>
-      <c r="B48" s="38"/>
+      <c r="A48" s="21"/>
+      <c r="B48" s="37"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="29"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="29"/>
-      <c r="B50" s="36" t="s">
+      <c r="A50" s="21"/>
+      <c r="B50" s="35" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -10845,8 +10936,8 @@
       </c>
     </row>
     <row r="51" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="29"/>
-      <c r="B51" s="37"/>
+      <c r="A51" s="21"/>
+      <c r="B51" s="36"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -10900,8 +10991,8 @@
       </c>
     </row>
     <row r="52" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="29"/>
-      <c r="B52" s="38"/>
+      <c r="A52" s="21"/>
+      <c r="B52" s="37"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -10960,10 +11051,10 @@
       <c r="C53" s="8"/>
     </row>
     <row r="54" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="35" t="s">
+      <c r="A54" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="35" t="s">
+      <c r="B54" s="38" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -10974,8 +11065,8 @@
       </c>
     </row>
     <row r="55" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="30"/>
-      <c r="B55" s="30"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
@@ -10984,8 +11075,8 @@
       </c>
     </row>
     <row r="56" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="30"/>
-      <c r="B56" s="30"/>
+      <c r="A56" s="22"/>
+      <c r="B56" s="22"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
@@ -10994,8 +11085,8 @@
       </c>
     </row>
     <row r="57" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="30"/>
-      <c r="B57" s="31"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="23"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
@@ -11004,8 +11095,8 @@
       </c>
     </row>
     <row r="58" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="30"/>
-      <c r="B58" s="35" t="s">
+      <c r="A58" s="22"/>
+      <c r="B58" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -11013,29 +11104,29 @@
       </c>
     </row>
     <row r="59" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="30"/>
-      <c r="B59" s="30"/>
+      <c r="A59" s="22"/>
+      <c r="B59" s="22"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="30"/>
-      <c r="B60" s="31"/>
+      <c r="A60" s="22"/>
+      <c r="B60" s="23"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="30"/>
+      <c r="A61" s="22"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="30"/>
-      <c r="B62" s="35" t="s">
+      <c r="A62" s="22"/>
+      <c r="B62" s="38" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -11046,8 +11137,8 @@
       </c>
     </row>
     <row r="63" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="30"/>
-      <c r="B63" s="30"/>
+      <c r="A63" s="22"/>
+      <c r="B63" s="22"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
@@ -11056,8 +11147,8 @@
       </c>
     </row>
     <row r="64" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="31"/>
-      <c r="B64" s="31"/>
+      <c r="A64" s="23"/>
+      <c r="B64" s="23"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
@@ -11067,7 +11158,7 @@
     </row>
     <row r="65" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="18" t="s">
+      <c r="A66" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -11114,7 +11205,7 @@
       </c>
     </row>
     <row r="67" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="19"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -11159,7 +11250,7 @@
       </c>
     </row>
     <row r="68" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="19"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -11204,7 +11295,7 @@
       </c>
     </row>
     <row r="69" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="20"/>
+      <c r="A69" s="32"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -11250,9 +11341,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="B9:B12"/>
@@ -11267,6 +11355,9 @@
     <mergeCell ref="B62:B64"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A66:A69"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11705,10 +11796,10 @@
       <c r="AA8" s="1"/>
     </row>
     <row r="9" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -11782,8 +11873,8 @@
       </c>
     </row>
     <row r="10" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="26"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -11855,8 +11946,8 @@
       </c>
     </row>
     <row r="11" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="26"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -11928,8 +12019,8 @@
       </c>
     </row>
     <row r="12" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="26"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -12001,8 +12092,8 @@
       </c>
     </row>
     <row r="13" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="26" t="s">
+      <c r="A13" s="20"/>
+      <c r="B13" s="18" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -12010,25 +12101,25 @@
       </c>
     </row>
     <row r="14" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-      <c r="B14" s="26"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="18"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="26"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="18"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:27" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
+      <c r="A16" s="20"/>
     </row>
     <row r="17" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28"/>
-      <c r="B17" s="32" t="s">
+      <c r="A17" s="20"/>
+      <c r="B17" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -12102,8 +12193,8 @@
       </c>
     </row>
     <row r="18" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28"/>
-      <c r="B18" s="33"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -12175,8 +12266,8 @@
       </c>
     </row>
     <row r="19" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="28"/>
-      <c r="B19" s="33"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="25"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -12248,8 +12339,8 @@
       </c>
     </row>
     <row r="20" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28"/>
-      <c r="B20" s="34"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -12327,7 +12418,7 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="21" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="39" t="s">
@@ -12404,7 +12495,7 @@
       </c>
     </row>
     <row r="23" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="29"/>
+      <c r="A23" s="21"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -12499,7 +12590,7 @@
       </c>
     </row>
     <row r="24" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="29"/>
+      <c r="A24" s="21"/>
       <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -12572,7 +12663,7 @@
       </c>
     </row>
     <row r="25" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="29"/>
+      <c r="A25" s="21"/>
       <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -12645,14 +12736,14 @@
       </c>
     </row>
     <row r="26" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="29"/>
+      <c r="A26" s="21"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="29"/>
+      <c r="A27" s="21"/>
       <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
@@ -12727,7 +12818,7 @@
       </c>
     </row>
     <row r="28" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="29"/>
+      <c r="A28" s="21"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -12822,7 +12913,7 @@
       </c>
     </row>
     <row r="29" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="29"/>
+      <c r="A29" s="21"/>
       <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -12895,7 +12986,7 @@
       </c>
     </row>
     <row r="30" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="29"/>
+      <c r="A30" s="21"/>
       <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -12968,15 +13059,15 @@
       </c>
     </row>
     <row r="31" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="29"/>
+      <c r="A31" s="21"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="29"/>
-      <c r="B32" s="36" t="s">
+      <c r="A32" s="21"/>
+      <c r="B32" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -13050,8 +13141,8 @@
       </c>
     </row>
     <row r="33" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="29"/>
-      <c r="B33" s="37"/>
+      <c r="A33" s="21"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -13145,8 +13236,8 @@
       </c>
     </row>
     <row r="34" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="29"/>
-      <c r="B34" s="37"/>
+      <c r="A34" s="21"/>
+      <c r="B34" s="36"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -13218,8 +13309,8 @@
       </c>
     </row>
     <row r="35" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="29"/>
-      <c r="B35" s="38"/>
+      <c r="A35" s="21"/>
+      <c r="B35" s="37"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
@@ -13291,15 +13382,15 @@
       </c>
     </row>
     <row r="36" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="29"/>
+      <c r="A36" s="21"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="29"/>
-      <c r="B37" s="36" t="s">
+      <c r="A37" s="21"/>
+      <c r="B37" s="35" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -13373,8 +13464,8 @@
       </c>
     </row>
     <row r="38" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="29"/>
-      <c r="B38" s="37"/>
+      <c r="A38" s="21"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -13468,8 +13559,8 @@
       </c>
     </row>
     <row r="39" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="29"/>
-      <c r="B39" s="37"/>
+      <c r="A39" s="21"/>
+      <c r="B39" s="36"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -13541,8 +13632,8 @@
       </c>
     </row>
     <row r="40" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="29"/>
-      <c r="B40" s="38"/>
+      <c r="A40" s="21"/>
+      <c r="B40" s="37"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
@@ -13614,15 +13705,15 @@
       </c>
     </row>
     <row r="41" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="29"/>
+      <c r="A41" s="21"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="29"/>
-      <c r="B42" s="36" t="s">
+      <c r="A42" s="21"/>
+      <c r="B42" s="35" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -13718,8 +13809,8 @@
       </c>
     </row>
     <row r="43" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="29"/>
-      <c r="B43" s="37"/>
+      <c r="A43" s="21"/>
+      <c r="B43" s="36"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -13791,8 +13882,8 @@
       </c>
     </row>
     <row r="44" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="29"/>
-      <c r="B44" s="38"/>
+      <c r="A44" s="21"/>
+      <c r="B44" s="37"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
@@ -13864,13 +13955,13 @@
       </c>
     </row>
     <row r="45" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="29"/>
+      <c r="A45" s="21"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
     </row>
     <row r="46" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="29"/>
-      <c r="B46" s="36" t="s">
+      <c r="A46" s="21"/>
+      <c r="B46" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -13878,29 +13969,29 @@
       </c>
     </row>
     <row r="47" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="29"/>
-      <c r="B47" s="37"/>
+      <c r="A47" s="21"/>
+      <c r="B47" s="36"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="29"/>
-      <c r="B48" s="38"/>
+      <c r="A48" s="21"/>
+      <c r="B48" s="37"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="29"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="29"/>
-      <c r="B50" s="36" t="s">
+      <c r="A50" s="21"/>
+      <c r="B50" s="35" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -13996,8 +14087,8 @@
       </c>
     </row>
     <row r="51" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="29"/>
-      <c r="B51" s="37"/>
+      <c r="A51" s="21"/>
+      <c r="B51" s="36"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -14091,8 +14182,8 @@
       </c>
     </row>
     <row r="52" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="29"/>
-      <c r="B52" s="38"/>
+      <c r="A52" s="21"/>
+      <c r="B52" s="37"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -14191,10 +14282,10 @@
       <c r="C53" s="8"/>
     </row>
     <row r="54" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="35" t="s">
+      <c r="A54" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="35" t="s">
+      <c r="B54" s="38" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -14202,29 +14293,29 @@
       </c>
     </row>
     <row r="55" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="30"/>
-      <c r="B55" s="30"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="30"/>
-      <c r="B56" s="30"/>
+      <c r="A56" s="22"/>
+      <c r="B56" s="22"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="30"/>
-      <c r="B57" s="31"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="23"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="30"/>
-      <c r="B58" s="35" t="s">
+      <c r="A58" s="22"/>
+      <c r="B58" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -14232,29 +14323,29 @@
       </c>
     </row>
     <row r="59" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="30"/>
-      <c r="B59" s="30"/>
+      <c r="A59" s="22"/>
+      <c r="B59" s="22"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="30"/>
-      <c r="B60" s="31"/>
+      <c r="A60" s="22"/>
+      <c r="B60" s="23"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="30"/>
+      <c r="A61" s="22"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="30"/>
-      <c r="B62" s="35" t="s">
+      <c r="A62" s="22"/>
+      <c r="B62" s="38" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -14262,22 +14353,22 @@
       </c>
     </row>
     <row r="63" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="30"/>
-      <c r="B63" s="30"/>
+      <c r="A63" s="22"/>
+      <c r="B63" s="22"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="31"/>
-      <c r="B64" s="31"/>
+      <c r="A64" s="23"/>
+      <c r="B64" s="23"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="18" t="s">
+      <c r="A66" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -14354,7 +14445,7 @@
       </c>
     </row>
     <row r="67" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="19"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -14429,7 +14520,7 @@
       </c>
     </row>
     <row r="68" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="19"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -14504,7 +14595,7 @@
       </c>
     </row>
     <row r="69" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="20"/>
+      <c r="A69" s="32"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -14580,9 +14671,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="B9:B12"/>
@@ -14597,6 +14685,9 @@
     <mergeCell ref="B62:B64"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A66:A69"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14612,21 +14703,21 @@
     <col min="1" max="3" width="16.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="2"/>
     </row>
-    <row r="4" spans="1:14" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -14663,8 +14754,17 @@
       <c r="N4" s="1" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O4" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
@@ -14703,8 +14803,17 @@
       <c r="N5" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O5" s="1">
+        <v>7</v>
+      </c>
+      <c r="P5" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
@@ -14743,12 +14852,21 @@
       <c r="N6" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="28" t="s">
+      <c r="O6" s="1">
+        <v>2</v>
+      </c>
+      <c r="P6" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -14758,9 +14876,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="28"/>
-      <c r="B8" s="26"/>
+    <row r="8" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="20"/>
+      <c r="B8" s="18"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
@@ -14768,9 +14886,9 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28"/>
-      <c r="B9" s="26"/>
+    <row r="9" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="20"/>
+      <c r="B9" s="18"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
@@ -14778,9 +14896,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="26"/>
+    <row r="10" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="20"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -14788,35 +14906,35 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="26" t="s">
+    <row r="11" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="20"/>
+      <c r="B11" s="18" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="26"/>
+    <row r="12" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="20"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="26"/>
+    <row r="13" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="20"/>
+      <c r="B13" s="18"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-    </row>
-    <row r="15" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="32" t="s">
+    <row r="14" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="20"/>
+    </row>
+    <row r="15" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="20"/>
+      <c r="B15" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -14826,9 +14944,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
-      <c r="B16" s="33"/>
+    <row r="16" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="20"/>
+      <c r="B16" s="25"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
@@ -14837,8 +14955,8 @@
       </c>
     </row>
     <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28"/>
-      <c r="B17" s="33"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="25"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
@@ -14847,8 +14965,8 @@
       </c>
     </row>
     <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28"/>
-      <c r="B18" s="34"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="26"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
@@ -14863,7 +14981,7 @@
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="21" t="s">
         <v>131</v>
       </c>
       <c r="B20" s="39" t="s">
@@ -14874,35 +14992,35 @@
       </c>
     </row>
     <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="29"/>
+      <c r="A21" s="21"/>
       <c r="B21" s="39"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="29"/>
+      <c r="A22" s="21"/>
       <c r="B22" s="39"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="29"/>
+      <c r="A23" s="21"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="29"/>
+      <c r="A24" s="21"/>
       <c r="B24" s="12"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="29"/>
+      <c r="A25" s="21"/>
       <c r="B25" s="39" t="s">
         <v>16</v>
       </c>
@@ -14911,36 +15029,36 @@
       </c>
     </row>
     <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="29"/>
+      <c r="A26" s="21"/>
       <c r="B26" s="39"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="29"/>
+      <c r="A27" s="21"/>
       <c r="B27" s="39"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="29"/>
+      <c r="A28" s="21"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="29"/>
+      <c r="A29" s="21"/>
       <c r="B29" s="13"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="29"/>
-      <c r="B30" s="36" t="s">
+      <c r="A30" s="21"/>
+      <c r="B30" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -14948,36 +15066,36 @@
       </c>
     </row>
     <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="29"/>
-      <c r="B31" s="37"/>
+      <c r="A31" s="21"/>
+      <c r="B31" s="36"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="29"/>
-      <c r="B32" s="37"/>
+      <c r="A32" s="21"/>
+      <c r="B32" s="36"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="29"/>
-      <c r="B33" s="38"/>
+      <c r="A33" s="21"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="29"/>
+      <c r="A34" s="21"/>
       <c r="B34" s="14"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
     <row r="35" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="29"/>
-      <c r="B35" s="36" t="s">
+      <c r="A35" s="21"/>
+      <c r="B35" s="35" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -14985,36 +15103,36 @@
       </c>
     </row>
     <row r="36" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="29"/>
-      <c r="B36" s="37"/>
+      <c r="A36" s="21"/>
+      <c r="B36" s="36"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="29"/>
-      <c r="B37" s="37"/>
+      <c r="A37" s="21"/>
+      <c r="B37" s="36"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="29"/>
-      <c r="B38" s="38"/>
+      <c r="A38" s="21"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="29"/>
+      <c r="A39" s="21"/>
       <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
     <row r="40" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="29"/>
-      <c r="B40" s="36" t="s">
+      <c r="A40" s="21"/>
+      <c r="B40" s="35" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
@@ -15022,27 +15140,27 @@
       </c>
     </row>
     <row r="41" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="29"/>
-      <c r="B41" s="37"/>
+      <c r="A41" s="21"/>
+      <c r="B41" s="36"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="29"/>
-      <c r="B42" s="38"/>
+      <c r="A42" s="21"/>
+      <c r="B42" s="37"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="29"/>
+      <c r="A43" s="21"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
     </row>
     <row r="44" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="29"/>
-      <c r="B44" s="36" t="s">
+      <c r="A44" s="21"/>
+      <c r="B44" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C44" s="4">
@@ -15050,29 +15168,29 @@
       </c>
     </row>
     <row r="45" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="29"/>
-      <c r="B45" s="37"/>
+      <c r="A45" s="21"/>
+      <c r="B45" s="36"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="29"/>
-      <c r="B46" s="38"/>
+      <c r="A46" s="21"/>
+      <c r="B46" s="37"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="29"/>
+      <c r="A47" s="21"/>
       <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
     <row r="48" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="29"/>
-      <c r="B48" s="36" t="s">
+      <c r="A48" s="21"/>
+      <c r="B48" s="35" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="4" t="s">
@@ -15140,8 +15258,8 @@
       </c>
     </row>
     <row r="49" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="29"/>
-      <c r="B49" s="37"/>
+      <c r="A49" s="21"/>
+      <c r="B49" s="36"/>
       <c r="C49" s="4" t="s">
         <v>129</v>
       </c>
@@ -15207,8 +15325,8 @@
       </c>
     </row>
     <row r="50" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="29"/>
-      <c r="B50" s="38"/>
+      <c r="A50" s="21"/>
+      <c r="B50" s="37"/>
       <c r="C50" s="4" t="s">
         <v>130</v>
       </c>
@@ -15279,10 +15397,10 @@
       <c r="C51" s="8"/>
     </row>
     <row r="52" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="35" t="s">
+      <c r="A52" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="B52" s="35" t="s">
+      <c r="B52" s="38" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="5" t="s">
@@ -15290,29 +15408,29 @@
       </c>
     </row>
     <row r="53" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="30"/>
-      <c r="B53" s="30"/>
+      <c r="A53" s="22"/>
+      <c r="B53" s="22"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="30"/>
-      <c r="B54" s="30"/>
+      <c r="A54" s="22"/>
+      <c r="B54" s="22"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="30"/>
-      <c r="B55" s="31"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="23"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="30"/>
-      <c r="B56" s="35" t="s">
+      <c r="A56" s="22"/>
+      <c r="B56" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C56" s="5">
@@ -15320,29 +15438,29 @@
       </c>
     </row>
     <row r="57" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="30"/>
-      <c r="B57" s="30"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="22"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="30"/>
-      <c r="B58" s="31"/>
+      <c r="A58" s="22"/>
+      <c r="B58" s="23"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="30"/>
+      <c r="A59" s="22"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
     </row>
     <row r="60" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="30"/>
-      <c r="B60" s="35" t="s">
+      <c r="A60" s="22"/>
+      <c r="B60" s="38" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
@@ -15350,22 +15468,22 @@
       </c>
     </row>
     <row r="61" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="30"/>
-      <c r="B61" s="30"/>
+      <c r="A61" s="22"/>
+      <c r="B61" s="22"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="31"/>
-      <c r="B62" s="31"/>
+      <c r="A62" s="23"/>
+      <c r="B62" s="23"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="64" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="18" t="s">
+      <c r="A64" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -15379,7 +15497,7 @@
       </c>
     </row>
     <row r="65" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="19"/>
+      <c r="A65" s="31"/>
       <c r="B65" s="4" t="s">
         <v>132</v>
       </c>
@@ -15391,7 +15509,7 @@
       </c>
     </row>
     <row r="66" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="19"/>
+      <c r="A66" s="31"/>
       <c r="B66" s="4" t="s">
         <v>133</v>
       </c>
@@ -15403,7 +15521,7 @@
       </c>
     </row>
     <row r="67" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="20"/>
+      <c r="A67" s="32"/>
       <c r="B67" s="5" t="s">
         <v>134</v>
       </c>
@@ -15416,9 +15534,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A64:A67"/>
     <mergeCell ref="A7:A18"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B7:B10"/>
@@ -15433,6 +15548,9 @@
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="B35:B38"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A64:A67"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15442,946 +15560,3244 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC6F473E-E8F6-46BD-8C8C-636A58FA8F6F}">
-  <dimension ref="A3:AR67"/>
+  <dimension ref="A3:AQ69"/>
   <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="16.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:44" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:39" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D4" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="AF4" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="AG4" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="AH4" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="AI4" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="AK4" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="AL4" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="AM4" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="6" spans="1:39" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="7" spans="1:39" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1">
+        <v>1</v>
+      </c>
+      <c r="N7" s="1">
+        <v>1</v>
+      </c>
+      <c r="O7" s="1">
+        <v>1</v>
+      </c>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>1</v>
+      </c>
+      <c r="R7" s="1">
+        <v>1</v>
+      </c>
+      <c r="S7" s="1">
+        <v>1</v>
+      </c>
+      <c r="T7" s="1">
+        <v>1</v>
+      </c>
+      <c r="U7" s="1">
+        <v>2</v>
+      </c>
+      <c r="V7" s="1">
+        <v>2</v>
+      </c>
+      <c r="W7" s="1">
+        <v>2</v>
+      </c>
+      <c r="X7" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>2</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>2</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AG7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AH7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AI7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AJ7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AK7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AL7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AM7" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:39" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C8" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1">
+        <v>1</v>
+      </c>
+      <c r="N8" s="1">
+        <v>1</v>
+      </c>
+      <c r="O8" s="1">
+        <v>1</v>
+      </c>
+      <c r="P8" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>1</v>
+      </c>
+      <c r="R8" s="1">
+        <v>1</v>
+      </c>
+      <c r="S8" s="1">
+        <v>1</v>
+      </c>
+      <c r="T8" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>2</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>3</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="3">
+        <v>4</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4</v>
+      </c>
+      <c r="F9" s="3">
+        <v>5</v>
+      </c>
+      <c r="G9" s="3">
+        <v>5</v>
+      </c>
+      <c r="H9" s="3">
+        <v>4</v>
+      </c>
+      <c r="I9" s="3">
+        <v>9</v>
+      </c>
+      <c r="J9" s="3">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
+        <v>8</v>
+      </c>
+      <c r="L9" s="3">
+        <v>7</v>
+      </c>
+      <c r="M9" s="3">
+        <v>6</v>
+      </c>
+      <c r="N9" s="3">
+        <v>7</v>
+      </c>
+      <c r="O9" s="3">
+        <v>6</v>
+      </c>
+      <c r="P9" s="3">
+        <v>9</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>6</v>
+      </c>
+      <c r="R9" s="3">
+        <v>10</v>
+      </c>
+      <c r="S9" s="3">
+        <v>7</v>
+      </c>
+      <c r="T9" s="3">
+        <v>6</v>
+      </c>
+      <c r="U9" s="3">
+        <v>15</v>
+      </c>
+      <c r="V9" s="3">
+        <v>17</v>
+      </c>
+      <c r="W9" s="3">
+        <v>17</v>
+      </c>
+      <c r="X9" s="3">
+        <v>19</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>21</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>20</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="20"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="3">
+        <v>150</v>
+      </c>
+      <c r="E10" s="3">
+        <v>100</v>
+      </c>
+      <c r="F10" s="3">
+        <v>100</v>
+      </c>
+      <c r="G10" s="3">
+        <v>150</v>
+      </c>
+      <c r="H10" s="3">
+        <v>150</v>
+      </c>
+      <c r="I10" s="3">
+        <v>450</v>
+      </c>
+      <c r="J10" s="3">
+        <v>350</v>
+      </c>
+      <c r="K10" s="3">
+        <v>400</v>
+      </c>
+      <c r="L10" s="3">
+        <v>500</v>
+      </c>
+      <c r="M10" s="3">
+        <v>350</v>
+      </c>
+      <c r="N10" s="3">
+        <v>400</v>
+      </c>
+      <c r="O10" s="3">
+        <v>350</v>
+      </c>
+      <c r="P10" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>350</v>
+      </c>
+      <c r="R10" s="3">
+        <v>500</v>
+      </c>
+      <c r="S10" s="3">
+        <v>300</v>
+      </c>
+      <c r="T10" s="3">
+        <v>300</v>
+      </c>
+      <c r="U10" s="3">
+        <v>300</v>
+      </c>
+      <c r="V10" s="3">
+        <v>700</v>
+      </c>
+      <c r="W10" s="3">
+        <v>500</v>
+      </c>
+      <c r="X10" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>650</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>550</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="11" spans="1:39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="20"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3</v>
+      </c>
+      <c r="F11" s="3">
+        <v>3</v>
+      </c>
+      <c r="G11" s="3">
+        <v>4</v>
+      </c>
+      <c r="H11" s="3">
+        <v>3</v>
+      </c>
+      <c r="I11" s="3">
+        <v>5</v>
+      </c>
+      <c r="J11" s="3">
+        <v>4</v>
+      </c>
+      <c r="K11" s="3">
+        <v>4</v>
+      </c>
+      <c r="L11" s="3">
+        <v>5</v>
+      </c>
+      <c r="M11" s="3">
+        <v>6</v>
+      </c>
+      <c r="N11" s="3">
+        <v>5</v>
+      </c>
+      <c r="O11" s="3">
+        <v>5</v>
+      </c>
+      <c r="P11" s="3">
+        <v>6</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>6</v>
+      </c>
+      <c r="R11" s="3">
+        <v>6</v>
+      </c>
+      <c r="S11" s="3">
+        <v>5</v>
+      </c>
+      <c r="T11" s="3">
+        <v>5</v>
+      </c>
+      <c r="U11" s="3">
+        <v>6</v>
+      </c>
+      <c r="V11" s="3">
+        <v>10</v>
+      </c>
+      <c r="W11" s="3">
+        <v>7</v>
+      </c>
+      <c r="X11" s="3">
+        <v>9</v>
+      </c>
+      <c r="Y11" s="3">
+        <v>9</v>
+      </c>
+      <c r="Z11" s="3">
+        <v>7</v>
+      </c>
+      <c r="AA11" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="20"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="E12" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="H12" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K12" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="R12" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="X4" s="1" t="s">
+      <c r="S12" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="U12" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="Y4" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="AC4" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="AD4" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="AE4" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="AF4" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="AG4" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="AH4" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="AI4" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="AJ4" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="AK4" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="AL4" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="AM4" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="AN4" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="AO4" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="AP4" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="AQ4" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="AR4" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" spans="1:44" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C5" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1">
-        <v>1</v>
-      </c>
-      <c r="L5" s="1">
-        <v>1</v>
-      </c>
-      <c r="M5" s="1">
-        <v>1</v>
-      </c>
-      <c r="N5" s="1">
-        <v>1</v>
-      </c>
-      <c r="O5" s="1">
-        <v>1</v>
-      </c>
-      <c r="P5" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>1</v>
-      </c>
-      <c r="R5" s="1">
-        <v>1</v>
-      </c>
-      <c r="S5" s="1">
-        <v>1</v>
-      </c>
-      <c r="T5" s="1">
-        <v>1</v>
-      </c>
-      <c r="U5" s="1">
-        <v>2</v>
-      </c>
-      <c r="V5" s="1">
-        <v>2</v>
-      </c>
-      <c r="W5" s="1">
-        <v>2</v>
-      </c>
-      <c r="X5" s="1">
-        <v>2</v>
-      </c>
-      <c r="Y5" s="1">
-        <v>2</v>
-      </c>
-      <c r="Z5" s="1">
-        <v>2</v>
-      </c>
-      <c r="AA5" s="1">
-        <v>2</v>
-      </c>
-      <c r="AB5" s="1">
-        <v>2</v>
-      </c>
-      <c r="AC5" s="1">
-        <v>3</v>
-      </c>
-      <c r="AD5" s="1">
-        <v>3</v>
-      </c>
-      <c r="AE5" s="1">
-        <v>3</v>
-      </c>
-      <c r="AF5" s="1">
-        <v>3</v>
-      </c>
-      <c r="AG5" s="1">
-        <v>3</v>
-      </c>
-      <c r="AH5" s="1">
-        <v>3</v>
-      </c>
-      <c r="AI5" s="1">
-        <v>3</v>
-      </c>
-      <c r="AJ5" s="1">
-        <v>3</v>
-      </c>
-      <c r="AK5" s="1">
-        <v>3</v>
-      </c>
-      <c r="AL5" s="1">
-        <v>3</v>
-      </c>
-      <c r="AM5" s="1">
-        <v>3</v>
-      </c>
-      <c r="AN5" s="1">
+      <c r="V12" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="13" spans="1:39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="20"/>
+      <c r="B13" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="20"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="20"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="20"/>
+    </row>
+    <row r="17" spans="1:39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="20"/>
+      <c r="B17" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
+        <v>-0.2</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="M17" s="3">
+        <v>-0.1</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="P17" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>0</v>
+      </c>
+      <c r="R17" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="S17" s="3">
+        <v>0</v>
+      </c>
+      <c r="T17" s="3">
+        <v>0</v>
+      </c>
+      <c r="U17" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="V17" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="W17" s="3">
+        <v>0</v>
+      </c>
+      <c r="X17" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="20"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="R18" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="S18" s="3">
+        <v>-0.1</v>
+      </c>
+      <c r="T18" s="3">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="V18" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="W18" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="X18" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="20"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AO5" s="1">
-        <v>7</v>
-      </c>
-      <c r="AP5" s="1">
-        <v>7</v>
-      </c>
-      <c r="AQ5" s="1">
-        <v>7</v>
-      </c>
-      <c r="AR5" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:44" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C6" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC6" s="1">
-        <v>2</v>
-      </c>
-      <c r="AD6" s="1">
-        <v>3</v>
-      </c>
-      <c r="AE6" s="1">
-        <v>3</v>
-      </c>
-      <c r="AF6" s="1">
+      <c r="D19" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F19" s="3">
+        <v>-0.2</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3">
+        <v>-0.1</v>
+      </c>
+      <c r="K19" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="L19" s="3">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="N19" s="3">
+        <v>0</v>
+      </c>
+      <c r="O19" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="P19" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="R19" s="3">
+        <v>0</v>
+      </c>
+      <c r="S19" s="3">
+        <v>0</v>
+      </c>
+      <c r="T19" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="U19" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="V19" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="W19" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="X19" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="Y19" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="AA19" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="20"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AN6" s="1">
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-0.2</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+    </row>
+    <row r="22" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4">
+        <v>1</v>
+      </c>
+      <c r="F22" s="4">
+        <v>1</v>
+      </c>
+      <c r="G22" s="4">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4">
+        <v>1</v>
+      </c>
+      <c r="I22" s="4">
+        <v>2</v>
+      </c>
+      <c r="J22" s="4">
+        <v>2</v>
+      </c>
+      <c r="K22" s="4">
+        <v>2</v>
+      </c>
+      <c r="L22" s="4">
+        <v>2</v>
+      </c>
+      <c r="M22" s="4">
+        <v>2</v>
+      </c>
+      <c r="N22" s="4">
+        <v>2</v>
+      </c>
+      <c r="O22" s="4">
+        <v>2</v>
+      </c>
+      <c r="P22" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>2</v>
+      </c>
+      <c r="R22" s="4">
+        <v>2</v>
+      </c>
+      <c r="S22" s="4">
+        <v>2</v>
+      </c>
+      <c r="T22" s="4">
+        <v>2</v>
+      </c>
+      <c r="U22" s="4">
+        <v>3</v>
+      </c>
+      <c r="V22" s="4">
+        <v>3</v>
+      </c>
+      <c r="W22" s="4">
+        <v>3</v>
+      </c>
+      <c r="X22" s="4">
         <v>4</v>
       </c>
-      <c r="AO6" s="1">
-        <v>1</v>
-      </c>
-      <c r="AP6" s="1">
-        <v>2</v>
-      </c>
-      <c r="AQ6" s="1">
-        <v>3</v>
-      </c>
-      <c r="AR6" s="1">
+      <c r="Y22" s="4">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:44" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:44" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="28"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:44" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:44" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:44" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:44" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:44" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-    </row>
-    <row r="15" spans="1:44" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:44" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-    </row>
-    <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="29" t="s">
-        <v>131</v>
-      </c>
-      <c r="B20" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="29"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="29"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="29"/>
+      <c r="Z22" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="21"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="4">
+        <f t="shared" ref="D23:AM23" si="0">0.7*D28</f>
+        <v>105</v>
+      </c>
+      <c r="E23" s="4">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="F23" s="4">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="G23" s="4">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+      <c r="H23" s="4">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+      <c r="I23" s="4">
+        <f t="shared" ref="I23" si="1">0.7*I28</f>
+        <v>315</v>
+      </c>
+      <c r="J23" s="4">
+        <f t="shared" si="0"/>
+        <v>244.99999999999997</v>
+      </c>
+      <c r="K23" s="4">
+        <f t="shared" si="0"/>
+        <v>280</v>
+      </c>
+      <c r="L23" s="4">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="M23" s="4">
+        <f t="shared" si="0"/>
+        <v>244.99999999999997</v>
+      </c>
+      <c r="N23" s="4">
+        <f t="shared" si="0"/>
+        <v>280</v>
+      </c>
+      <c r="O23" s="4">
+        <f t="shared" si="0"/>
+        <v>244.99999999999997</v>
+      </c>
+      <c r="P23" s="4">
+        <f t="shared" si="0"/>
+        <v>280</v>
+      </c>
+      <c r="Q23" s="4">
+        <f t="shared" si="0"/>
+        <v>244.99999999999997</v>
+      </c>
+      <c r="R23" s="4">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="S23" s="4">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="T23" s="4">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="U23" s="4">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="V23" s="4">
+        <f t="shared" si="0"/>
+        <v>489.99999999999994</v>
+      </c>
+      <c r="W23" s="4">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="X23" s="4">
+        <f t="shared" si="0"/>
+        <v>489.99999999999994</v>
+      </c>
+      <c r="Y23" s="4">
+        <f t="shared" si="0"/>
+        <v>454.99999999999994</v>
+      </c>
+      <c r="Z23" s="4">
+        <f t="shared" si="0"/>
+        <v>385</v>
+      </c>
+      <c r="AB23" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC23" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD23" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE23" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AF23" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AG23" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH23" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI23" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK23" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL23" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM23" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="21"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <v>1</v>
+      </c>
+      <c r="I24" s="4">
+        <v>1</v>
+      </c>
+      <c r="J24" s="4">
+        <v>0</v>
+      </c>
+      <c r="K24" s="4">
+        <v>0</v>
+      </c>
+      <c r="L24" s="4">
+        <v>1</v>
+      </c>
+      <c r="M24" s="4">
+        <v>0</v>
+      </c>
+      <c r="N24" s="4">
+        <v>1</v>
+      </c>
+      <c r="O24" s="4">
+        <v>1</v>
+      </c>
+      <c r="P24" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>0</v>
+      </c>
+      <c r="R24" s="4">
+        <v>1</v>
+      </c>
+      <c r="S24" s="4">
+        <v>1</v>
+      </c>
+      <c r="T24" s="4">
+        <v>1</v>
+      </c>
+      <c r="U24" s="4">
+        <v>1</v>
+      </c>
+      <c r="V24" s="4">
+        <v>2</v>
+      </c>
+      <c r="W24" s="4">
+        <v>1</v>
+      </c>
+      <c r="X24" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y24" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z24" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="21"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="29"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-    </row>
-    <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="29"/>
-      <c r="B25" s="39" t="s">
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4">
+        <v>0</v>
+      </c>
+      <c r="J25" s="4">
+        <v>0</v>
+      </c>
+      <c r="K25" s="4">
+        <v>0</v>
+      </c>
+      <c r="L25" s="4">
+        <v>0</v>
+      </c>
+      <c r="M25" s="4">
+        <v>0</v>
+      </c>
+      <c r="N25" s="4">
+        <v>0</v>
+      </c>
+      <c r="O25" s="4">
+        <v>0</v>
+      </c>
+      <c r="P25" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="4">
+        <v>0</v>
+      </c>
+      <c r="R25" s="4">
+        <v>0</v>
+      </c>
+      <c r="S25" s="4">
+        <v>0</v>
+      </c>
+      <c r="T25" s="4">
+        <v>0</v>
+      </c>
+      <c r="U25" s="4">
+        <v>0</v>
+      </c>
+      <c r="V25" s="4">
+        <v>0</v>
+      </c>
+      <c r="W25" s="4">
+        <v>0</v>
+      </c>
+      <c r="X25" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="21"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+    </row>
+    <row r="27" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="21"/>
+      <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C27" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="29"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="29"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="29"/>
+      <c r="D27" s="4">
+        <v>2</v>
+      </c>
+      <c r="E27" s="4">
+        <v>2</v>
+      </c>
+      <c r="F27" s="4">
+        <v>2</v>
+      </c>
+      <c r="G27" s="4">
+        <v>2</v>
+      </c>
+      <c r="H27" s="4">
+        <v>2</v>
+      </c>
+      <c r="I27" s="4">
+        <v>3</v>
+      </c>
+      <c r="J27" s="4">
+        <v>3</v>
+      </c>
+      <c r="K27" s="4">
+        <v>3</v>
+      </c>
+      <c r="L27" s="4">
+        <v>3</v>
+      </c>
+      <c r="M27" s="4">
+        <v>3</v>
+      </c>
+      <c r="N27" s="4">
+        <v>3</v>
+      </c>
+      <c r="O27" s="4">
+        <v>3</v>
+      </c>
+      <c r="P27" s="4">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="4">
+        <v>3</v>
+      </c>
+      <c r="R27" s="4">
+        <v>3</v>
+      </c>
+      <c r="S27" s="4">
+        <v>3</v>
+      </c>
+      <c r="T27" s="4">
+        <v>3</v>
+      </c>
+      <c r="U27" s="4">
+        <v>4</v>
+      </c>
+      <c r="V27" s="4">
+        <v>4</v>
+      </c>
+      <c r="W27" s="4">
+        <v>4</v>
+      </c>
+      <c r="X27" s="4">
+        <v>5</v>
+      </c>
+      <c r="Y27" s="4">
+        <v>6</v>
+      </c>
+      <c r="Z27" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="21"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="4">
+        <f t="shared" ref="D28:AM28" si="2">D10</f>
+        <v>150</v>
+      </c>
+      <c r="E28" s="4">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="F28" s="4">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="G28" s="4">
+        <f t="shared" si="2"/>
+        <v>150</v>
+      </c>
+      <c r="H28" s="4">
+        <f t="shared" si="2"/>
+        <v>150</v>
+      </c>
+      <c r="I28" s="4">
+        <f t="shared" ref="I28" si="3">I10</f>
+        <v>450</v>
+      </c>
+      <c r="J28" s="4">
+        <f t="shared" si="2"/>
+        <v>350</v>
+      </c>
+      <c r="K28" s="4">
+        <f t="shared" si="2"/>
+        <v>400</v>
+      </c>
+      <c r="L28" s="4">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M28" s="4">
+        <f t="shared" si="2"/>
+        <v>350</v>
+      </c>
+      <c r="N28" s="4">
+        <f t="shared" si="2"/>
+        <v>400</v>
+      </c>
+      <c r="O28" s="4">
+        <f t="shared" si="2"/>
+        <v>350</v>
+      </c>
+      <c r="P28" s="4">
+        <f t="shared" si="2"/>
+        <v>400</v>
+      </c>
+      <c r="Q28" s="4">
+        <f t="shared" si="2"/>
+        <v>350</v>
+      </c>
+      <c r="R28" s="4">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="S28" s="4">
+        <f t="shared" si="2"/>
+        <v>300</v>
+      </c>
+      <c r="T28" s="4">
+        <f t="shared" si="2"/>
+        <v>300</v>
+      </c>
+      <c r="U28" s="4">
+        <f t="shared" si="2"/>
+        <v>300</v>
+      </c>
+      <c r="V28" s="4">
+        <f t="shared" si="2"/>
+        <v>700</v>
+      </c>
+      <c r="W28" s="4">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="X28" s="4">
+        <f t="shared" si="2"/>
+        <v>700</v>
+      </c>
+      <c r="Y28" s="4">
+        <f t="shared" si="2"/>
+        <v>650</v>
+      </c>
+      <c r="Z28" s="4">
+        <f t="shared" si="2"/>
+        <v>550</v>
+      </c>
+      <c r="AB28" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC28" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD28" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE28" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AF28" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AG28" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AH28" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI28" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK28" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AL28" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM28" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="21"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4">
+        <v>1</v>
+      </c>
+      <c r="I29" s="4">
+        <v>1</v>
+      </c>
+      <c r="J29" s="4">
+        <v>0</v>
+      </c>
+      <c r="K29" s="4">
+        <v>0</v>
+      </c>
+      <c r="L29" s="4">
+        <v>1</v>
+      </c>
+      <c r="M29" s="4">
+        <v>0</v>
+      </c>
+      <c r="N29" s="4">
+        <v>1</v>
+      </c>
+      <c r="O29" s="4">
+        <v>1</v>
+      </c>
+      <c r="P29" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="4">
+        <v>0</v>
+      </c>
+      <c r="R29" s="4">
+        <v>1</v>
+      </c>
+      <c r="S29" s="4">
+        <v>1</v>
+      </c>
+      <c r="T29" s="4">
+        <v>1</v>
+      </c>
+      <c r="U29" s="4">
+        <v>1</v>
+      </c>
+      <c r="V29" s="4">
+        <v>2</v>
+      </c>
+      <c r="W29" s="4">
+        <v>1</v>
+      </c>
+      <c r="X29" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y29" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z29" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="21"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="29"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-    </row>
-    <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="29"/>
-      <c r="B30" s="36" t="s">
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
+      <c r="E30" s="4">
+        <v>0</v>
+      </c>
+      <c r="F30" s="4">
+        <v>0</v>
+      </c>
+      <c r="G30" s="4">
+        <v>0</v>
+      </c>
+      <c r="H30" s="4">
+        <v>0</v>
+      </c>
+      <c r="I30" s="4">
+        <v>0</v>
+      </c>
+      <c r="J30" s="4">
+        <v>0</v>
+      </c>
+      <c r="K30" s="4">
+        <v>0</v>
+      </c>
+      <c r="L30" s="4">
+        <v>0</v>
+      </c>
+      <c r="M30" s="4">
+        <v>0</v>
+      </c>
+      <c r="N30" s="4">
+        <v>0</v>
+      </c>
+      <c r="O30" s="4">
+        <v>0</v>
+      </c>
+      <c r="P30" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="4">
+        <v>0</v>
+      </c>
+      <c r="R30" s="4">
+        <v>0</v>
+      </c>
+      <c r="S30" s="4">
+        <v>0</v>
+      </c>
+      <c r="T30" s="4">
+        <v>0</v>
+      </c>
+      <c r="U30" s="4">
+        <v>0</v>
+      </c>
+      <c r="V30" s="4">
+        <v>0</v>
+      </c>
+      <c r="W30" s="4">
+        <v>0</v>
+      </c>
+      <c r="X30" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="21"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+    </row>
+    <row r="32" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="21"/>
+      <c r="B32" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C32" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="29"/>
-      <c r="B31" s="37"/>
-      <c r="C31" s="4" t="s">
+      <c r="D32" s="4">
+        <v>2</v>
+      </c>
+      <c r="E32" s="4">
+        <v>2</v>
+      </c>
+      <c r="F32" s="4">
+        <v>2</v>
+      </c>
+      <c r="G32" s="4">
+        <v>2</v>
+      </c>
+      <c r="H32" s="4">
+        <v>2</v>
+      </c>
+      <c r="I32" s="4">
+        <v>3</v>
+      </c>
+      <c r="J32" s="4">
+        <v>3</v>
+      </c>
+      <c r="K32" s="4">
+        <v>3</v>
+      </c>
+      <c r="L32" s="4">
+        <v>3</v>
+      </c>
+      <c r="M32" s="4">
+        <v>3</v>
+      </c>
+      <c r="N32" s="4">
+        <v>3</v>
+      </c>
+      <c r="O32" s="4">
+        <v>3</v>
+      </c>
+      <c r="P32" s="4">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="4">
+        <v>3</v>
+      </c>
+      <c r="R32" s="4">
+        <v>3</v>
+      </c>
+      <c r="S32" s="4">
+        <v>3</v>
+      </c>
+      <c r="T32" s="4">
+        <v>3</v>
+      </c>
+      <c r="U32" s="4">
+        <v>4</v>
+      </c>
+      <c r="V32" s="4">
+        <v>4</v>
+      </c>
+      <c r="W32" s="4">
+        <v>4</v>
+      </c>
+      <c r="X32" s="4">
+        <v>5</v>
+      </c>
+      <c r="Y32" s="4">
+        <v>5</v>
+      </c>
+      <c r="Z32" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="21"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="29"/>
-      <c r="B32" s="37"/>
-      <c r="C32" s="4" t="s">
+      <c r="D33" s="4">
+        <f t="shared" ref="D33:AM33" si="4">0.9*D28</f>
+        <v>135</v>
+      </c>
+      <c r="E33" s="4">
+        <f t="shared" si="4"/>
+        <v>90</v>
+      </c>
+      <c r="F33" s="4">
+        <f t="shared" si="4"/>
+        <v>90</v>
+      </c>
+      <c r="G33" s="4">
+        <f t="shared" si="4"/>
+        <v>135</v>
+      </c>
+      <c r="H33" s="4">
+        <f t="shared" si="4"/>
+        <v>135</v>
+      </c>
+      <c r="I33" s="4">
+        <f t="shared" ref="I33" si="5">0.9*I28</f>
+        <v>405</v>
+      </c>
+      <c r="J33" s="4">
+        <f t="shared" si="4"/>
+        <v>315</v>
+      </c>
+      <c r="K33" s="4">
+        <f t="shared" si="4"/>
+        <v>360</v>
+      </c>
+      <c r="L33" s="4">
+        <f t="shared" si="4"/>
+        <v>450</v>
+      </c>
+      <c r="M33" s="4">
+        <f t="shared" si="4"/>
+        <v>315</v>
+      </c>
+      <c r="N33" s="4">
+        <f t="shared" si="4"/>
+        <v>360</v>
+      </c>
+      <c r="O33" s="4">
+        <f t="shared" si="4"/>
+        <v>315</v>
+      </c>
+      <c r="P33" s="4">
+        <f t="shared" si="4"/>
+        <v>360</v>
+      </c>
+      <c r="Q33" s="4">
+        <f t="shared" si="4"/>
+        <v>315</v>
+      </c>
+      <c r="R33" s="4">
+        <f t="shared" si="4"/>
+        <v>450</v>
+      </c>
+      <c r="S33" s="4">
+        <f t="shared" si="4"/>
+        <v>270</v>
+      </c>
+      <c r="T33" s="4">
+        <f t="shared" si="4"/>
+        <v>270</v>
+      </c>
+      <c r="U33" s="4">
+        <f t="shared" si="4"/>
+        <v>270</v>
+      </c>
+      <c r="V33" s="4">
+        <f t="shared" si="4"/>
+        <v>630</v>
+      </c>
+      <c r="W33" s="4">
+        <f t="shared" si="4"/>
+        <v>450</v>
+      </c>
+      <c r="X33" s="4">
+        <f t="shared" si="4"/>
+        <v>630</v>
+      </c>
+      <c r="Y33" s="4">
+        <f t="shared" si="4"/>
+        <v>585</v>
+      </c>
+      <c r="Z33" s="4">
+        <f t="shared" si="4"/>
+        <v>495</v>
+      </c>
+      <c r="AB33" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AC33" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AD33" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AE33" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AF33" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AG33" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AH33" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AI33" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AK33" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AL33" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AM33" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="21"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="29"/>
-      <c r="B33" s="38"/>
-      <c r="C33" s="4" t="s">
+      <c r="D34" s="4">
+        <v>0</v>
+      </c>
+      <c r="E34" s="4">
+        <v>0</v>
+      </c>
+      <c r="F34" s="4">
+        <v>0</v>
+      </c>
+      <c r="G34" s="4">
+        <v>0</v>
+      </c>
+      <c r="H34" s="4">
+        <v>1</v>
+      </c>
+      <c r="I34" s="4">
+        <v>1</v>
+      </c>
+      <c r="J34" s="4">
+        <v>0</v>
+      </c>
+      <c r="K34" s="4">
+        <v>0</v>
+      </c>
+      <c r="L34" s="4">
+        <v>1</v>
+      </c>
+      <c r="M34" s="4">
+        <v>0</v>
+      </c>
+      <c r="N34" s="4">
+        <v>1</v>
+      </c>
+      <c r="O34" s="4">
+        <v>1</v>
+      </c>
+      <c r="P34" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="4">
+        <v>0</v>
+      </c>
+      <c r="R34" s="4">
+        <v>1</v>
+      </c>
+      <c r="S34" s="4">
+        <v>1</v>
+      </c>
+      <c r="T34" s="4">
+        <v>1</v>
+      </c>
+      <c r="U34" s="4">
+        <v>1</v>
+      </c>
+      <c r="V34" s="4">
+        <v>2</v>
+      </c>
+      <c r="W34" s="4">
+        <v>1</v>
+      </c>
+      <c r="X34" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y34" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z34" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="21"/>
+      <c r="B35" s="37"/>
+      <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="29"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="29"/>
-      <c r="B35" s="36" t="s">
+      <c r="D35" s="4">
+        <v>0</v>
+      </c>
+      <c r="E35" s="4">
+        <v>0</v>
+      </c>
+      <c r="F35" s="4">
+        <v>0</v>
+      </c>
+      <c r="G35" s="4">
+        <v>0</v>
+      </c>
+      <c r="H35" s="4">
+        <v>0</v>
+      </c>
+      <c r="I35" s="4">
+        <v>0</v>
+      </c>
+      <c r="J35" s="4">
+        <v>0</v>
+      </c>
+      <c r="K35" s="4">
+        <v>0</v>
+      </c>
+      <c r="L35" s="4">
+        <v>0</v>
+      </c>
+      <c r="M35" s="4">
+        <v>0</v>
+      </c>
+      <c r="N35" s="4">
+        <v>0</v>
+      </c>
+      <c r="O35" s="4">
+        <v>0</v>
+      </c>
+      <c r="P35" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="4">
+        <v>0</v>
+      </c>
+      <c r="R35" s="4">
+        <v>0</v>
+      </c>
+      <c r="S35" s="4">
+        <v>0</v>
+      </c>
+      <c r="T35" s="4">
+        <v>0</v>
+      </c>
+      <c r="U35" s="4">
+        <v>0</v>
+      </c>
+      <c r="V35" s="4">
+        <v>0</v>
+      </c>
+      <c r="W35" s="4">
+        <v>0</v>
+      </c>
+      <c r="X35" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="21"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="21"/>
+      <c r="B37" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C37" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="29"/>
-      <c r="B36" s="37"/>
-      <c r="C36" s="4" t="s">
+      <c r="D37" s="4">
+        <v>1</v>
+      </c>
+      <c r="E37" s="4">
+        <v>1</v>
+      </c>
+      <c r="F37" s="4">
+        <v>1</v>
+      </c>
+      <c r="G37" s="4">
+        <v>1</v>
+      </c>
+      <c r="H37" s="4">
+        <v>1</v>
+      </c>
+      <c r="I37" s="4">
+        <v>2</v>
+      </c>
+      <c r="J37" s="4">
+        <v>2</v>
+      </c>
+      <c r="K37" s="4">
+        <v>2</v>
+      </c>
+      <c r="L37" s="4">
+        <v>2</v>
+      </c>
+      <c r="M37" s="4">
+        <v>2</v>
+      </c>
+      <c r="N37" s="4">
+        <v>2</v>
+      </c>
+      <c r="O37" s="4">
+        <v>2</v>
+      </c>
+      <c r="P37" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q37" s="4">
+        <v>2</v>
+      </c>
+      <c r="R37" s="4">
+        <v>2</v>
+      </c>
+      <c r="S37" s="4">
+        <v>2</v>
+      </c>
+      <c r="T37" s="4">
+        <v>2</v>
+      </c>
+      <c r="U37" s="4">
+        <v>2</v>
+      </c>
+      <c r="V37" s="4">
+        <v>3</v>
+      </c>
+      <c r="W37" s="4">
+        <v>3</v>
+      </c>
+      <c r="X37" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y37" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z37" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="21"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="29"/>
-      <c r="B37" s="37"/>
-      <c r="C37" s="4" t="s">
+      <c r="D38" s="4">
+        <f t="shared" ref="D38:AM38" si="6">0.6*D28</f>
+        <v>90</v>
+      </c>
+      <c r="E38" s="4">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="F38" s="4">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="G38" s="4">
+        <f t="shared" si="6"/>
+        <v>90</v>
+      </c>
+      <c r="H38" s="4">
+        <f t="shared" si="6"/>
+        <v>90</v>
+      </c>
+      <c r="I38" s="4">
+        <f t="shared" ref="I38" si="7">0.6*I28</f>
+        <v>270</v>
+      </c>
+      <c r="J38" s="4">
+        <f t="shared" si="6"/>
+        <v>210</v>
+      </c>
+      <c r="K38" s="4">
+        <f t="shared" si="6"/>
+        <v>240</v>
+      </c>
+      <c r="L38" s="4">
+        <f t="shared" si="6"/>
+        <v>300</v>
+      </c>
+      <c r="M38" s="4">
+        <f t="shared" si="6"/>
+        <v>210</v>
+      </c>
+      <c r="N38" s="4">
+        <f t="shared" si="6"/>
+        <v>240</v>
+      </c>
+      <c r="O38" s="4">
+        <f t="shared" si="6"/>
+        <v>210</v>
+      </c>
+      <c r="P38" s="4">
+        <f t="shared" si="6"/>
+        <v>240</v>
+      </c>
+      <c r="Q38" s="4">
+        <f t="shared" si="6"/>
+        <v>210</v>
+      </c>
+      <c r="R38" s="4">
+        <f t="shared" si="6"/>
+        <v>300</v>
+      </c>
+      <c r="S38" s="4">
+        <f t="shared" si="6"/>
+        <v>180</v>
+      </c>
+      <c r="T38" s="4">
+        <f t="shared" si="6"/>
+        <v>180</v>
+      </c>
+      <c r="U38" s="4">
+        <f t="shared" si="6"/>
+        <v>180</v>
+      </c>
+      <c r="V38" s="4">
+        <f t="shared" si="6"/>
+        <v>420</v>
+      </c>
+      <c r="W38" s="4">
+        <f t="shared" si="6"/>
+        <v>300</v>
+      </c>
+      <c r="X38" s="4">
+        <f t="shared" si="6"/>
+        <v>420</v>
+      </c>
+      <c r="Y38" s="4">
+        <f t="shared" si="6"/>
+        <v>390</v>
+      </c>
+      <c r="Z38" s="4">
+        <f t="shared" si="6"/>
+        <v>330</v>
+      </c>
+      <c r="AB38" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AC38" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD38" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AE38" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AF38" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AG38" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AH38" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AI38" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AK38" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AL38" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AM38" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="21"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="29"/>
-      <c r="B38" s="38"/>
-      <c r="C38" s="4" t="s">
+      <c r="D39" s="4">
+        <v>0</v>
+      </c>
+      <c r="E39" s="4">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4">
+        <v>0</v>
+      </c>
+      <c r="G39" s="4">
+        <v>0</v>
+      </c>
+      <c r="H39" s="4">
+        <v>1</v>
+      </c>
+      <c r="I39" s="4">
+        <v>1</v>
+      </c>
+      <c r="J39" s="4">
+        <v>0</v>
+      </c>
+      <c r="K39" s="4">
+        <v>0</v>
+      </c>
+      <c r="L39" s="4">
+        <v>1</v>
+      </c>
+      <c r="M39" s="4">
+        <v>0</v>
+      </c>
+      <c r="N39" s="4">
+        <v>1</v>
+      </c>
+      <c r="O39" s="4">
+        <v>1</v>
+      </c>
+      <c r="P39" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="4">
+        <v>0</v>
+      </c>
+      <c r="R39" s="4">
+        <v>1</v>
+      </c>
+      <c r="S39" s="4">
+        <v>1</v>
+      </c>
+      <c r="T39" s="4">
+        <v>1</v>
+      </c>
+      <c r="U39" s="4">
+        <v>1</v>
+      </c>
+      <c r="V39" s="4">
+        <v>2</v>
+      </c>
+      <c r="W39" s="4">
+        <v>1</v>
+      </c>
+      <c r="X39" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y39" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z39" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="21"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="39" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="29"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-    </row>
-    <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="29"/>
-      <c r="B40" s="36" t="s">
+      <c r="D40" s="4">
+        <v>0</v>
+      </c>
+      <c r="E40" s="4">
+        <v>0</v>
+      </c>
+      <c r="F40" s="4">
+        <v>0</v>
+      </c>
+      <c r="G40" s="4">
+        <v>0</v>
+      </c>
+      <c r="H40" s="4">
+        <v>0</v>
+      </c>
+      <c r="I40" s="4">
+        <v>0</v>
+      </c>
+      <c r="J40" s="4">
+        <v>0</v>
+      </c>
+      <c r="K40" s="4">
+        <v>0</v>
+      </c>
+      <c r="L40" s="4">
+        <v>0</v>
+      </c>
+      <c r="M40" s="4">
+        <v>0</v>
+      </c>
+      <c r="N40" s="4">
+        <v>0</v>
+      </c>
+      <c r="O40" s="4">
+        <v>0</v>
+      </c>
+      <c r="P40" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="4">
+        <v>0</v>
+      </c>
+      <c r="R40" s="4">
+        <v>0</v>
+      </c>
+      <c r="S40" s="4">
+        <v>0</v>
+      </c>
+      <c r="T40" s="4">
+        <v>0</v>
+      </c>
+      <c r="U40" s="4">
+        <v>0</v>
+      </c>
+      <c r="V40" s="4">
+        <v>0</v>
+      </c>
+      <c r="W40" s="4">
+        <v>0</v>
+      </c>
+      <c r="X40" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="21"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+    </row>
+    <row r="42" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="21"/>
+      <c r="B42" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C42" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="29"/>
-      <c r="B41" s="37"/>
-      <c r="C41" s="4" t="s">
+    <row r="43" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="21"/>
+      <c r="B43" s="36"/>
+      <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="29"/>
-      <c r="B42" s="38"/>
-      <c r="C42" s="4" t="s">
+    <row r="44" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="21"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="29"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-    </row>
-    <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="29"/>
-      <c r="B44" s="36" t="s">
+    <row r="45" spans="1:39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="21"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+    </row>
+    <row r="46" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="21"/>
+      <c r="B46" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="C44" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="29"/>
-      <c r="B45" s="37"/>
-      <c r="C45" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="29"/>
-      <c r="B46" s="38"/>
       <c r="C46" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="29"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-    </row>
-    <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="29"/>
-      <c r="B48" s="36" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="21"/>
+      <c r="B47" s="36"/>
+      <c r="C47" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="21"/>
+      <c r="B48" s="37"/>
+      <c r="C48" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="21"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+    </row>
+    <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="21"/>
+      <c r="B50" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C50" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D48" s="4">
-        <f t="shared" ref="D48:Q48" si="0">D20+D25+D30+D35</f>
-        <v>0</v>
-      </c>
-      <c r="E48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="29"/>
-      <c r="B49" s="37"/>
-      <c r="C49" s="4" t="s">
+      <c r="D50" s="4">
+        <f t="shared" ref="D50:Q50" si="8">D22+D27+D32+D37</f>
+        <v>6</v>
+      </c>
+      <c r="E50" s="4">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+      <c r="F50" s="4">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+      <c r="G50" s="4">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+      <c r="H50" s="4">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+      <c r="I50" s="4">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="J50" s="4">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="K50" s="4">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="L50" s="4">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="M50" s="4">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="N50" s="4">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="O50" s="4">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="P50" s="4">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="Q50" s="4">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="21"/>
+      <c r="B51" s="36"/>
+      <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D49" s="4">
-        <f t="shared" ref="D49:Q49" si="1">D22+D27+D32+D37+D41</f>
-        <v>0</v>
-      </c>
-      <c r="E49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="29"/>
-      <c r="B50" s="38"/>
-      <c r="C50" s="4" t="s">
+      <c r="D51" s="4">
+        <f t="shared" ref="D51:Q51" si="9">D24+D29+D34+D39+D43</f>
+        <v>0</v>
+      </c>
+      <c r="E51" s="4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F51" s="4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G51" s="4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H51" s="4">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="I51" s="4">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="J51" s="4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L51" s="4">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="M51" s="4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="N51" s="4">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="O51" s="4">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="P51" s="4">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="Q51" s="4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="21"/>
+      <c r="B52" s="37"/>
+      <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="D50" s="4">
-        <f>D48*(1+D49*0.02)</f>
-        <v>0</v>
-      </c>
-      <c r="E50" s="4">
-        <f>E48*(1+E49*0.02)</f>
-        <v>0</v>
-      </c>
-      <c r="F50" s="4">
-        <f t="shared" ref="F50:Q50" si="2">F48*(1+F49*0.02)</f>
-        <v>0</v>
-      </c>
-      <c r="G50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="2"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-    </row>
-    <row r="52" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="35" t="s">
+      <c r="D52" s="4">
+        <f>D50*(1+D51*0.02)</f>
+        <v>6</v>
+      </c>
+      <c r="E52" s="4">
+        <f>E50*(1+E51*0.02)</f>
+        <v>6</v>
+      </c>
+      <c r="F52" s="4">
+        <f t="shared" ref="F52:Q52" si="10">F50*(1+F51*0.02)</f>
+        <v>6</v>
+      </c>
+      <c r="G52" s="4">
+        <f t="shared" si="10"/>
+        <v>6</v>
+      </c>
+      <c r="H52" s="4">
+        <f t="shared" si="10"/>
+        <v>6.48</v>
+      </c>
+      <c r="I52" s="4">
+        <f t="shared" si="10"/>
+        <v>10.8</v>
+      </c>
+      <c r="J52" s="4">
+        <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="K52" s="4">
+        <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="L52" s="4">
+        <f t="shared" si="10"/>
+        <v>10.8</v>
+      </c>
+      <c r="M52" s="4">
+        <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="N52" s="4">
+        <f t="shared" si="10"/>
+        <v>10.8</v>
+      </c>
+      <c r="O52" s="4">
+        <f t="shared" si="10"/>
+        <v>10.8</v>
+      </c>
+      <c r="P52" s="4">
+        <f t="shared" si="10"/>
+        <v>10.8</v>
+      </c>
+      <c r="Q52" s="4">
+        <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="2"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+    </row>
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="B52" s="35" t="s">
+      <c r="B54" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C54" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="30"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="5" t="s">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
+      <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="30"/>
-      <c r="B54" s="30"/>
-      <c r="C54" s="5" t="s">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="22"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="30"/>
-      <c r="B55" s="31"/>
-      <c r="C55" s="5" t="s">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="22"/>
+      <c r="B57" s="23"/>
+      <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="30"/>
-      <c r="B56" s="35" t="s">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="22"/>
+      <c r="B58" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C56" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="30"/>
-      <c r="B57" s="30"/>
-      <c r="C57" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="30"/>
-      <c r="B58" s="31"/>
       <c r="C58" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="30"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="22"/>
+      <c r="B59" s="22"/>
+      <c r="C59" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="30"/>
-      <c r="B60" s="35" t="s">
+      <c r="A60" s="22"/>
+      <c r="B60" s="23"/>
+      <c r="C60" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="22"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+    </row>
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="22"/>
+      <c r="B62" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="30"/>
-      <c r="B61" s="30"/>
-      <c r="C61" s="5" t="s">
+      <c r="C62" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="22"/>
+      <c r="B63" s="22"/>
+      <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="31"/>
-      <c r="B62" s="31"/>
-      <c r="C62" s="5" t="s">
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="23"/>
+      <c r="B64" s="23"/>
+      <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="18" t="s">
+    <row r="66" spans="1:43" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B66" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C66" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="19"/>
-      <c r="B65" s="4" t="s">
+      <c r="D66" s="6">
+        <v>1</v>
+      </c>
+      <c r="E66" s="6">
+        <v>1</v>
+      </c>
+      <c r="F66" s="6">
+        <v>1</v>
+      </c>
+      <c r="G66" s="6">
+        <v>1</v>
+      </c>
+      <c r="H66" s="6">
+        <v>1</v>
+      </c>
+      <c r="I66" s="6">
+        <v>1</v>
+      </c>
+      <c r="J66" s="6">
+        <v>1</v>
+      </c>
+      <c r="K66" s="6">
+        <v>1</v>
+      </c>
+      <c r="L66" s="6">
+        <v>1</v>
+      </c>
+      <c r="M66" s="6">
+        <v>1</v>
+      </c>
+      <c r="N66" s="6">
+        <v>1</v>
+      </c>
+      <c r="O66" s="6">
+        <v>1</v>
+      </c>
+      <c r="P66" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q66" s="6">
+        <v>1</v>
+      </c>
+      <c r="R66" s="6">
+        <v>1</v>
+      </c>
+      <c r="S66" s="6">
+        <v>1</v>
+      </c>
+      <c r="T66" s="6">
+        <v>1</v>
+      </c>
+      <c r="U66" s="6">
+        <v>1</v>
+      </c>
+      <c r="V66" s="6">
+        <v>1</v>
+      </c>
+      <c r="W66" s="6">
+        <v>1</v>
+      </c>
+      <c r="X66" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y66" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z66" s="6">
+        <v>1</v>
+      </c>
+      <c r="AA66" s="6">
+        <v>1</v>
+      </c>
+      <c r="AB66" s="6">
+        <v>1</v>
+      </c>
+      <c r="AC66" s="6">
+        <v>1</v>
+      </c>
+      <c r="AD66" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE66" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF66" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG66" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH66" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI66" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ66" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK66" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL66" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM66" s="6">
+        <v>1</v>
+      </c>
+      <c r="AN66" s="6">
+        <v>1</v>
+      </c>
+      <c r="AO66" s="6">
+        <v>1</v>
+      </c>
+      <c r="AP66" s="6">
+        <v>1</v>
+      </c>
+      <c r="AQ66" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:43" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="31"/>
+      <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C67" s="4" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="19"/>
-      <c r="B66" s="4" t="s">
+      <c r="D67" s="4">
+        <v>1</v>
+      </c>
+      <c r="E67" s="4">
+        <v>1</v>
+      </c>
+      <c r="F67" s="4">
+        <v>1</v>
+      </c>
+      <c r="G67" s="4">
+        <v>1</v>
+      </c>
+      <c r="H67" s="4">
+        <v>1</v>
+      </c>
+      <c r="I67" s="4">
+        <v>1</v>
+      </c>
+      <c r="J67" s="4">
+        <v>1</v>
+      </c>
+      <c r="K67" s="4">
+        <v>1</v>
+      </c>
+      <c r="L67" s="4">
+        <v>1</v>
+      </c>
+      <c r="M67" s="4">
+        <v>1</v>
+      </c>
+      <c r="N67" s="4">
+        <v>1</v>
+      </c>
+      <c r="O67" s="4">
+        <v>1</v>
+      </c>
+      <c r="P67" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q67" s="4">
+        <v>1</v>
+      </c>
+      <c r="R67" s="4">
+        <v>1</v>
+      </c>
+      <c r="S67" s="4">
+        <v>1</v>
+      </c>
+      <c r="T67" s="4">
+        <v>1</v>
+      </c>
+      <c r="U67" s="4">
+        <v>1</v>
+      </c>
+      <c r="V67" s="4">
+        <v>1</v>
+      </c>
+      <c r="W67" s="4">
+        <v>1</v>
+      </c>
+      <c r="X67" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y67" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z67" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA67" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB67" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC67" s="4">
+        <v>1</v>
+      </c>
+      <c r="AD67" s="4">
+        <v>1</v>
+      </c>
+      <c r="AE67" s="4">
+        <v>1</v>
+      </c>
+      <c r="AF67" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG67" s="4">
+        <v>1</v>
+      </c>
+      <c r="AH67" s="4">
+        <v>1</v>
+      </c>
+      <c r="AI67" s="4">
+        <v>1</v>
+      </c>
+      <c r="AJ67" s="4">
+        <v>1</v>
+      </c>
+      <c r="AK67" s="4">
+        <v>1</v>
+      </c>
+      <c r="AL67" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM67" s="4">
+        <v>1</v>
+      </c>
+      <c r="AN67" s="4">
+        <v>1</v>
+      </c>
+      <c r="AO67" s="4">
+        <v>1</v>
+      </c>
+      <c r="AP67" s="4">
+        <v>1</v>
+      </c>
+      <c r="AQ67" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:43" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="31"/>
+      <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C68" s="4" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="20"/>
-      <c r="B67" s="5" t="s">
+      <c r="E68" s="4">
+        <v>1</v>
+      </c>
+      <c r="F68" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:43" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="32"/>
+      <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="C69" s="5" t="s">
         <v>135</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="C4:AO6">
-    <sortCondition ref="C5:AO5"/>
-    <sortCondition ref="C6:AO6"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="D4:T9">
+    <sortCondition ref="D7:T7"/>
+    <sortCondition ref="D8:T8"/>
   </sortState>
   <mergeCells count="17">
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A52:A62"/>
-    <mergeCell ref="B52:B55"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B60:B62"/>
-    <mergeCell ref="A7:A18"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="A20:A50"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="A9:A20"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="A22:A52"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A54:A64"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B62:B64"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dev_stuffs/3匠魂.xlsx
+++ b/dev_stuffs/3匠魂.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\Palmon\dev_stuffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489C3C0D-92FB-465A-BAA7-DE219658F5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BBE0BB4-6479-41E2-9AEB-13FC084D154F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="3855" windowWidth="24015" windowHeight="15435" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="阶段1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="阶段EX" sheetId="11" r:id="rId6"/>
     <sheet name="追加1" sheetId="12" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="303">
   <si>
     <t>材料名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -601,10 +601,6 @@
     <t>null</t>
   </si>
   <si>
-    <t>原体合金</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>'kubejs:end_steel'</t>
   </si>
   <si>
@@ -676,10 +672,6 @@
     <t>'kubejs:basepoint_alloy'</t>
   </si>
   <si>
-    <t>超导线圈2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>'#forge:ingots/ostrum'</t>
   </si>
   <si>
@@ -1045,6 +1037,10 @@
   </si>
   <si>
     <t>iron</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>原体合金*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1295,6 +1291,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1322,28 +1342,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
@@ -1353,9 +1352,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
@@ -1819,10 +1815,10 @@
       </c>
     </row>
     <row r="9" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -1860,8 +1856,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="18"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -1897,8 +1893,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="18"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -1934,8 +1930,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="18"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -1971,8 +1967,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="18" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -1980,25 +1976,25 @@
       </c>
     </row>
     <row r="14" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="18"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="18"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
+      <c r="A16" s="28"/>
     </row>
     <row r="17" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="24" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -2036,8 +2032,8 @@
       </c>
     </row>
     <row r="18" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="25"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -2073,8 +2069,8 @@
       </c>
     </row>
     <row r="19" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="25"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -2110,8 +2106,8 @@
       </c>
     </row>
     <row r="20" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20"/>
-      <c r="B20" s="26"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -2153,10 +2149,10 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="33" t="s">
+      <c r="A22" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="29" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -2194,8 +2190,8 @@
       </c>
     </row>
     <row r="23" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="34"/>
-      <c r="B23" s="21"/>
+      <c r="A23" s="25"/>
+      <c r="B23" s="29"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
       </c>
@@ -2241,8 +2237,8 @@
       </c>
     </row>
     <row r="24" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="34"/>
-      <c r="B24" s="21"/>
+      <c r="A24" s="25"/>
+      <c r="B24" s="29"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
       </c>
@@ -2278,22 +2274,22 @@
       </c>
     </row>
     <row r="25" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="34"/>
-      <c r="B25" s="21"/>
+      <c r="A25" s="25"/>
+      <c r="B25" s="29"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="34"/>
+      <c r="A26" s="25"/>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="34"/>
-      <c r="B27" s="21" t="s">
+      <c r="A27" s="25"/>
+      <c r="B27" s="29" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="4" t="s">
@@ -2331,8 +2327,8 @@
       </c>
     </row>
     <row r="28" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="34"/>
-      <c r="B28" s="21"/>
+      <c r="A28" s="25"/>
+      <c r="B28" s="29"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
       </c>
@@ -2378,8 +2374,8 @@
       </c>
     </row>
     <row r="29" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="34"/>
-      <c r="B29" s="21"/>
+      <c r="A29" s="25"/>
+      <c r="B29" s="29"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
       </c>
@@ -2415,22 +2411,22 @@
       </c>
     </row>
     <row r="30" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="34"/>
-      <c r="B30" s="21"/>
+      <c r="A30" s="25"/>
+      <c r="B30" s="29"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="34"/>
+      <c r="A31" s="25"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="34"/>
-      <c r="B32" s="27" t="s">
+      <c r="A32" s="25"/>
+      <c r="B32" s="18" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -2468,8 +2464,8 @@
       </c>
     </row>
     <row r="33" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="34"/>
-      <c r="B33" s="28"/>
+      <c r="A33" s="25"/>
+      <c r="B33" s="19"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -2515,8 +2511,8 @@
       </c>
     </row>
     <row r="34" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="34"/>
-      <c r="B34" s="28"/>
+      <c r="A34" s="25"/>
+      <c r="B34" s="19"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -2552,22 +2548,22 @@
       </c>
     </row>
     <row r="35" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="34"/>
-      <c r="B35" s="29"/>
+      <c r="A35" s="25"/>
+      <c r="B35" s="20"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="34"/>
+      <c r="A36" s="25"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="34"/>
-      <c r="B37" s="27" t="s">
+      <c r="A37" s="25"/>
+      <c r="B37" s="18" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -2605,8 +2601,8 @@
       </c>
     </row>
     <row r="38" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="34"/>
-      <c r="B38" s="28"/>
+      <c r="A38" s="25"/>
+      <c r="B38" s="19"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -2652,8 +2648,8 @@
       </c>
     </row>
     <row r="39" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="34"/>
-      <c r="B39" s="28"/>
+      <c r="A39" s="25"/>
+      <c r="B39" s="19"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -2689,22 +2685,22 @@
       </c>
     </row>
     <row r="40" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="34"/>
-      <c r="B40" s="29"/>
+      <c r="A40" s="25"/>
+      <c r="B40" s="20"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="34"/>
+      <c r="A41" s="25"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="34"/>
-      <c r="B42" s="27" t="s">
+      <c r="A42" s="25"/>
+      <c r="B42" s="18" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -2752,8 +2748,8 @@
       </c>
     </row>
     <row r="43" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="34"/>
-      <c r="B43" s="28"/>
+      <c r="A43" s="25"/>
+      <c r="B43" s="19"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -2789,18 +2785,18 @@
       </c>
     </row>
     <row r="44" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="34"/>
-      <c r="B44" s="29"/>
+      <c r="A44" s="25"/>
+      <c r="B44" s="20"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="34"/>
+      <c r="A45" s="25"/>
     </row>
     <row r="46" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="34"/>
-      <c r="B46" s="27" t="s">
+      <c r="A46" s="25"/>
+      <c r="B46" s="18" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -2808,29 +2804,29 @@
       </c>
     </row>
     <row r="47" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="34"/>
-      <c r="B47" s="28"/>
+      <c r="A47" s="25"/>
+      <c r="B47" s="19"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="34"/>
-      <c r="B48" s="29"/>
+      <c r="A48" s="25"/>
+      <c r="B48" s="20"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="34"/>
+      <c r="A49" s="25"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
     </row>
     <row r="50" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="34"/>
-      <c r="B50" s="27" t="s">
+      <c r="A50" s="25"/>
+      <c r="B50" s="18" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -2878,8 +2874,8 @@
       </c>
     </row>
     <row r="51" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="34"/>
-      <c r="B51" s="28"/>
+      <c r="A51" s="25"/>
+      <c r="B51" s="19"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -2925,8 +2921,8 @@
       </c>
     </row>
     <row r="52" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="34"/>
-      <c r="B52" s="29"/>
+      <c r="A52" s="25"/>
+      <c r="B52" s="20"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -2978,40 +2974,130 @@
       <c r="E53" s="8"/>
     </row>
     <row r="54" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="19" t="s">
+      <c r="A54" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="19" t="s">
+      <c r="B54" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>21</v>
       </c>
+      <c r="D54" s="5">
+        <v>2</v>
+      </c>
+      <c r="E54" s="5">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F54" s="5">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G54" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="H54" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="I54" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="J54" s="5">
+        <v>2.6</v>
+      </c>
+      <c r="K54" s="5">
+        <v>2.6</v>
+      </c>
+      <c r="L54" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="M54" s="5">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="55" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="19"/>
-      <c r="B55" s="19"/>
+      <c r="A55" s="27"/>
+      <c r="B55" s="27"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="19"/>
-      <c r="B56" s="19"/>
+      <c r="A56" s="27"/>
+      <c r="B56" s="27"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
+      <c r="D56" s="5">
+        <v>-0.3</v>
+      </c>
+      <c r="E56" s="5">
+        <v>-0.3</v>
+      </c>
+      <c r="F56" s="5">
+        <v>-0.3</v>
+      </c>
+      <c r="G56" s="5">
+        <v>-0.3</v>
+      </c>
+      <c r="H56" s="5">
+        <v>-0.3</v>
+      </c>
+      <c r="I56" s="5">
+        <v>-0.3</v>
+      </c>
+      <c r="J56" s="5">
+        <v>-0.25</v>
+      </c>
+      <c r="K56" s="5">
+        <v>-0.25</v>
+      </c>
+      <c r="L56" s="5">
+        <v>-0.25</v>
+      </c>
+      <c r="M56" s="5">
+        <v>-0.2</v>
+      </c>
     </row>
     <row r="57" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="19"/>
-      <c r="B57" s="19"/>
+      <c r="A57" s="27"/>
+      <c r="B57" s="27"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
+      <c r="D57" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="E57" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="F57" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G57" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="H57" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="I57" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="J57" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="K57" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="L57" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="M57" s="5">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="58" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="19"/>
-      <c r="B58" s="19" t="s">
+      <c r="A58" s="27"/>
+      <c r="B58" s="27" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -3019,29 +3105,29 @@
       </c>
     </row>
     <row r="59" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="19"/>
-      <c r="B59" s="22"/>
+      <c r="A59" s="27"/>
+      <c r="B59" s="30"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="19"/>
-      <c r="B60" s="23"/>
+      <c r="A60" s="27"/>
+      <c r="B60" s="31"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="19"/>
+      <c r="A61" s="27"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="19"/>
-      <c r="B62" s="19" t="s">
+      <c r="A62" s="27"/>
+      <c r="B62" s="27" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -3049,21 +3135,81 @@
       </c>
     </row>
     <row r="63" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="19"/>
-      <c r="B63" s="22"/>
+      <c r="A63" s="27"/>
+      <c r="B63" s="30"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
+      <c r="D63" s="5">
+        <v>-0.1</v>
+      </c>
+      <c r="E63" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="F63" s="5">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5">
+        <v>-0.1</v>
+      </c>
+      <c r="H63" s="5">
+        <v>-0.1</v>
+      </c>
+      <c r="I63" s="5">
+        <v>-0.15</v>
+      </c>
+      <c r="J63" s="5">
+        <v>0</v>
+      </c>
+      <c r="K63" s="5">
+        <v>0</v>
+      </c>
+      <c r="L63" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="M63" s="5">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="64" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="19"/>
-      <c r="B64" s="23"/>
+      <c r="A64" s="27"/>
+      <c r="B64" s="31"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
+      <c r="D64" s="5">
+        <v>5</v>
+      </c>
+      <c r="E64" s="5">
+        <v>7</v>
+      </c>
+      <c r="F64" s="5">
+        <v>6</v>
+      </c>
+      <c r="G64" s="5">
+        <v>4</v>
+      </c>
+      <c r="H64" s="5">
+        <v>8</v>
+      </c>
+      <c r="I64" s="5">
+        <v>7</v>
+      </c>
+      <c r="J64" s="5">
+        <v>9</v>
+      </c>
+      <c r="K64" s="5">
+        <v>9</v>
+      </c>
+      <c r="L64" s="5">
+        <v>10</v>
+      </c>
+      <c r="M64" s="5">
+        <v>12</v>
+      </c>
     </row>
     <row r="67" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="30" t="s">
+      <c r="A67" s="21" t="s">
         <v>26</v>
       </c>
       <c r="B67" s="6" t="s">
@@ -3104,7 +3250,7 @@
       </c>
     </row>
     <row r="68" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="31"/>
+      <c r="A68" s="22"/>
       <c r="B68" s="4" t="s">
         <v>132</v>
       </c>
@@ -3143,7 +3289,7 @@
       </c>
     </row>
     <row r="69" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="31"/>
+      <c r="A69" s="22"/>
       <c r="B69" s="4" t="s">
         <v>133</v>
       </c>
@@ -3182,7 +3328,7 @@
       </c>
     </row>
     <row r="70" spans="1:13" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="32"/>
+      <c r="A70" s="23"/>
       <c r="B70" s="5" t="s">
         <v>134</v>
       </c>
@@ -3222,9 +3368,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="A22:A52"/>
     <mergeCell ref="B13:B15"/>
     <mergeCell ref="A54:A64"/>
     <mergeCell ref="A9:A20"/>
@@ -3239,6 +3382,9 @@
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="A22:A52"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3508,10 +3654,10 @@
       </c>
     </row>
     <row r="9" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -3561,8 +3707,8 @@
       </c>
     </row>
     <row r="10" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="18"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -3610,8 +3756,8 @@
       </c>
     </row>
     <row r="11" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="18"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -3659,8 +3805,8 @@
       </c>
     </row>
     <row r="12" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="18"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -3708,8 +3854,8 @@
       </c>
     </row>
     <row r="13" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="18" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -3717,25 +3863,25 @@
       </c>
     </row>
     <row r="14" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="18"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="18"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
+      <c r="A16" s="28"/>
     </row>
     <row r="17" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="24" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -3785,8 +3931,8 @@
       </c>
     </row>
     <row r="18" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="25"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -3834,8 +3980,8 @@
       </c>
     </row>
     <row r="19" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="25"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -3883,8 +4029,8 @@
       </c>
     </row>
     <row r="20" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20"/>
-      <c r="B20" s="26"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -3938,7 +4084,7 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="29" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="39" t="s">
@@ -3991,7 +4137,7 @@
       </c>
     </row>
     <row r="23" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -4054,7 +4200,7 @@
       </c>
     </row>
     <row r="24" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -4103,7 +4249,7 @@
       </c>
     </row>
     <row r="25" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -4134,14 +4280,14 @@
       </c>
     </row>
     <row r="26" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
+      <c r="A27" s="29"/>
       <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
@@ -4192,7 +4338,7 @@
       </c>
     </row>
     <row r="28" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -4255,7 +4401,7 @@
       </c>
     </row>
     <row r="29" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -4304,7 +4450,7 @@
       </c>
     </row>
     <row r="30" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -4335,15 +4481,15 @@
       </c>
     </row>
     <row r="31" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
-      <c r="B32" s="35" t="s">
+      <c r="A32" s="29"/>
+      <c r="B32" s="36" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -4393,8 +4539,8 @@
       </c>
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
-      <c r="B33" s="36"/>
+      <c r="A33" s="29"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -4456,8 +4602,8 @@
       </c>
     </row>
     <row r="34" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
-      <c r="B34" s="36"/>
+      <c r="A34" s="29"/>
+      <c r="B34" s="37"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -4505,8 +4651,8 @@
       </c>
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
-      <c r="B35" s="37"/>
+      <c r="A35" s="29"/>
+      <c r="B35" s="38"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
@@ -4536,15 +4682,15 @@
       </c>
     </row>
     <row r="36" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
-      <c r="B37" s="35" t="s">
+      <c r="A37" s="29"/>
+      <c r="B37" s="36" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -4594,8 +4740,8 @@
       </c>
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
-      <c r="B38" s="36"/>
+      <c r="A38" s="29"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -4657,8 +4803,8 @@
       </c>
     </row>
     <row r="39" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
-      <c r="B39" s="36"/>
+      <c r="A39" s="29"/>
+      <c r="B39" s="37"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -4706,8 +4852,8 @@
       </c>
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
-      <c r="B40" s="37"/>
+      <c r="A40" s="29"/>
+      <c r="B40" s="38"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
@@ -4737,15 +4883,15 @@
       </c>
     </row>
     <row r="41" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
+      <c r="A41" s="29"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
-      <c r="B42" s="35" t="s">
+      <c r="A42" s="29"/>
+      <c r="B42" s="36" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -4809,8 +4955,8 @@
       </c>
     </row>
     <row r="43" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="21"/>
-      <c r="B43" s="36"/>
+      <c r="A43" s="29"/>
+      <c r="B43" s="37"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -4858,8 +5004,8 @@
       </c>
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="21"/>
-      <c r="B44" s="37"/>
+      <c r="A44" s="29"/>
+      <c r="B44" s="38"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
@@ -4889,13 +5035,13 @@
       </c>
     </row>
     <row r="45" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="21"/>
+      <c r="A45" s="29"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="21"/>
-      <c r="B46" s="35" t="s">
+      <c r="A46" s="29"/>
+      <c r="B46" s="36" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -4903,29 +5049,29 @@
       </c>
     </row>
     <row r="47" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="21"/>
-      <c r="B47" s="36"/>
+      <c r="A47" s="29"/>
+      <c r="B47" s="37"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="21"/>
-      <c r="B48" s="37"/>
+      <c r="A48" s="29"/>
+      <c r="B48" s="38"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="21"/>
+      <c r="A49" s="29"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="21"/>
-      <c r="B50" s="35" t="s">
+      <c r="A50" s="29"/>
+      <c r="B50" s="36" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -4989,8 +5135,8 @@
       </c>
     </row>
     <row r="51" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="21"/>
-      <c r="B51" s="36"/>
+      <c r="A51" s="29"/>
+      <c r="B51" s="37"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -5052,8 +5198,8 @@
       </c>
     </row>
     <row r="52" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="21"/>
-      <c r="B52" s="37"/>
+      <c r="A52" s="29"/>
+      <c r="B52" s="38"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -5120,40 +5266,166 @@
       <c r="C53" s="8"/>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="38" t="s">
+      <c r="A54" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="38" t="s">
+      <c r="B54" s="35" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>21</v>
       </c>
+      <c r="D54" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="E54" s="5">
+        <v>5</v>
+      </c>
+      <c r="F54" s="5">
+        <v>4</v>
+      </c>
+      <c r="G54" s="5">
+        <v>4.5</v>
+      </c>
+      <c r="H54" s="5">
+        <v>5.5</v>
+      </c>
+      <c r="I54" s="5">
+        <v>5</v>
+      </c>
+      <c r="J54" s="5">
+        <v>7.5</v>
+      </c>
+      <c r="K54" s="5">
+        <v>6.5</v>
+      </c>
+      <c r="L54" s="5">
+        <v>6</v>
+      </c>
+      <c r="M54" s="5">
+        <v>7.5</v>
+      </c>
+      <c r="N54" s="5">
+        <v>8</v>
+      </c>
+      <c r="O54" s="5">
+        <v>16</v>
+      </c>
+      <c r="P54" s="5">
+        <v>16</v>
+      </c>
+      <c r="Q54" s="5">
+        <v>13</v>
+      </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="22"/>
-      <c r="B55" s="22"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="22"/>
-      <c r="B56" s="22"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="30"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
+      <c r="D56" s="5">
+        <v>-0.1</v>
+      </c>
+      <c r="E56" s="5">
+        <v>-0.4</v>
+      </c>
+      <c r="F56" s="5">
+        <v>-0.15</v>
+      </c>
+      <c r="G56" s="5">
+        <v>-0.3</v>
+      </c>
+      <c r="H56" s="5">
+        <v>-0.3</v>
+      </c>
+      <c r="I56" s="5">
+        <v>-0.1</v>
+      </c>
+      <c r="J56" s="5">
+        <v>-0.45</v>
+      </c>
+      <c r="K56" s="5">
+        <v>-0.3</v>
+      </c>
+      <c r="L56" s="5">
+        <v>-0.15</v>
+      </c>
+      <c r="M56" s="5">
+        <v>-0.3</v>
+      </c>
+      <c r="N56" s="5">
+        <v>-0.35</v>
+      </c>
+      <c r="O56" s="5">
+        <v>-0.3</v>
+      </c>
+      <c r="P56" s="5">
+        <v>-0.5</v>
+      </c>
+      <c r="Q56" s="5">
+        <v>-0.2</v>
+      </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="22"/>
-      <c r="B57" s="23"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="31"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
+      <c r="D57" s="5">
+        <v>0</v>
+      </c>
+      <c r="E57" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="F57" s="5">
+        <v>-0.1</v>
+      </c>
+      <c r="G57" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="H57" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="I57" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="J57" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="K57" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="L57" s="5">
+        <v>-0.1</v>
+      </c>
+      <c r="M57" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="N57" s="5">
+        <v>-0.1</v>
+      </c>
+      <c r="O57" s="5">
+        <v>0</v>
+      </c>
+      <c r="P57" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="Q57" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="22"/>
-      <c r="B58" s="38" t="s">
+      <c r="A58" s="30"/>
+      <c r="B58" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -5161,29 +5433,29 @@
       </c>
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="22"/>
-      <c r="B59" s="22"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="22"/>
-      <c r="B60" s="23"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="31"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="22"/>
+      <c r="A61" s="30"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="22"/>
-      <c r="B62" s="38" t="s">
+      <c r="A62" s="30"/>
+      <c r="B62" s="35" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -5191,22 +5463,106 @@
       </c>
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="22"/>
-      <c r="B63" s="22"/>
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
+      <c r="D63" s="5">
+        <v>-0.15</v>
+      </c>
+      <c r="E63" s="5">
+        <v>0</v>
+      </c>
+      <c r="F63" s="5">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="H63" s="5">
+        <v>0</v>
+      </c>
+      <c r="I63" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="J63" s="5">
+        <v>0</v>
+      </c>
+      <c r="K63" s="5">
+        <v>-0.15</v>
+      </c>
+      <c r="L63" s="5">
+        <v>0</v>
+      </c>
+      <c r="M63" s="5">
+        <v>-0.3</v>
+      </c>
+      <c r="N63" s="5">
+        <v>0</v>
+      </c>
+      <c r="O63" s="5">
+        <v>-0.1</v>
+      </c>
+      <c r="P63" s="5">
+        <v>-0.1</v>
+      </c>
+      <c r="Q63" s="5">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="23"/>
-      <c r="B64" s="23"/>
+      <c r="A64" s="31"/>
+      <c r="B64" s="31"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
+      <c r="D64" s="5">
+        <v>8</v>
+      </c>
+      <c r="E64" s="5">
+        <v>9</v>
+      </c>
+      <c r="F64" s="5">
+        <v>6</v>
+      </c>
+      <c r="G64" s="5">
+        <v>7</v>
+      </c>
+      <c r="H64" s="5">
+        <v>10</v>
+      </c>
+      <c r="I64" s="5">
+        <v>9</v>
+      </c>
+      <c r="J64" s="5">
+        <v>11</v>
+      </c>
+      <c r="K64" s="5">
+        <v>11</v>
+      </c>
+      <c r="L64" s="5">
+        <v>11</v>
+      </c>
+      <c r="M64" s="5">
+        <v>14</v>
+      </c>
+      <c r="N64" s="5">
+        <v>13</v>
+      </c>
+      <c r="O64" s="5">
+        <v>14</v>
+      </c>
+      <c r="P64" s="5">
+        <v>16</v>
+      </c>
+      <c r="Q64" s="5">
+        <v>13</v>
+      </c>
     </row>
     <row r="65" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="21" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -5259,7 +5615,7 @@
       </c>
     </row>
     <row r="67" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="31"/>
+      <c r="A67" s="22"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -5304,7 +5660,7 @@
       </c>
     </row>
     <row r="68" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="31"/>
+      <c r="A68" s="22"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -5349,7 +5705,7 @@
       </c>
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="32"/>
+      <c r="A69" s="23"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -5359,9 +5715,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="B62:B64"/>
     <mergeCell ref="B9:B12"/>
@@ -5376,6 +5729,9 @@
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="A54:A64"/>
     <mergeCell ref="B54:B57"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A66:A69"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5501,88 +5857,88 @@
         <v>139</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="M5" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="P5" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="N5" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="O5" s="1" t="s">
+      <c r="Q5" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="P5" s="11" t="s">
+      <c r="R5" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="Q5" s="11" t="s">
+      <c r="S5" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="R5" s="11" t="s">
+      <c r="T5" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="S5" s="11" t="s">
+      <c r="U5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="T5" s="11" t="s">
+      <c r="V5" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="U5" s="11" t="s">
+      <c r="W5" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="V5" s="11" t="s">
+      <c r="X5" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="W5" s="11" t="s">
+      <c r="Y5" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="X5" s="11" t="s">
+      <c r="Z5" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="Y5" s="11" t="s">
+      <c r="AA5" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="Z5" s="11" t="s">
+      <c r="AB5" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="AA5" s="11" t="s">
+      <c r="AC5" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="AB5" s="11" t="s">
+      <c r="AD5" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="AC5" s="11" t="s">
+      <c r="AE5" s="11" t="s">
         <v>238</v>
-      </c>
-      <c r="AD5" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="AE5" s="11" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:31" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -5859,10 +6215,10 @@
       </c>
     </row>
     <row r="9" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -5954,8 +6310,8 @@
       </c>
     </row>
     <row r="10" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="18"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -6045,8 +6401,8 @@
       </c>
     </row>
     <row r="11" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="18"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -6136,8 +6492,8 @@
       </c>
     </row>
     <row r="12" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="18"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -6227,8 +6583,8 @@
       </c>
     </row>
     <row r="13" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="18" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -6236,25 +6592,25 @@
       </c>
     </row>
     <row r="14" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="18"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="18"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
+      <c r="A16" s="28"/>
     </row>
     <row r="17" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="24" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -6346,8 +6702,8 @@
       </c>
     </row>
     <row r="18" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="25"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -6437,8 +6793,8 @@
       </c>
     </row>
     <row r="19" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="25"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -6528,8 +6884,8 @@
       </c>
     </row>
     <row r="20" spans="1:31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20"/>
-      <c r="B20" s="26"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -6624,11 +6980,11 @@
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
       <c r="R21" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="22" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="29" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="39" t="s">
@@ -6723,7 +7079,7 @@
       </c>
     </row>
     <row r="23" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -6842,7 +7198,7 @@
       </c>
     </row>
     <row r="24" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -6933,7 +7289,7 @@
       </c>
     </row>
     <row r="25" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -7024,14 +7380,14 @@
       </c>
     </row>
     <row r="26" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
+      <c r="A27" s="29"/>
       <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
@@ -7124,7 +7480,7 @@
       </c>
     </row>
     <row r="28" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -7243,7 +7599,7 @@
       </c>
     </row>
     <row r="29" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -7334,7 +7690,7 @@
       </c>
     </row>
     <row r="30" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -7425,15 +7781,15 @@
       </c>
     </row>
     <row r="31" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
-      <c r="B32" s="35" t="s">
+      <c r="A32" s="29"/>
+      <c r="B32" s="36" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -7525,8 +7881,8 @@
       </c>
     </row>
     <row r="33" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
-      <c r="B33" s="36"/>
+      <c r="A33" s="29"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -7644,8 +8000,8 @@
       </c>
     </row>
     <row r="34" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
-      <c r="B34" s="36"/>
+      <c r="A34" s="29"/>
+      <c r="B34" s="37"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -7735,8 +8091,8 @@
       </c>
     </row>
     <row r="35" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
-      <c r="B35" s="37"/>
+      <c r="A35" s="29"/>
+      <c r="B35" s="38"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
@@ -7826,15 +8182,15 @@
       </c>
     </row>
     <row r="36" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
-      <c r="B37" s="35" t="s">
+      <c r="A37" s="29"/>
+      <c r="B37" s="36" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -7926,8 +8282,8 @@
       </c>
     </row>
     <row r="38" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
-      <c r="B38" s="36"/>
+      <c r="A38" s="29"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -8045,8 +8401,8 @@
       </c>
     </row>
     <row r="39" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
-      <c r="B39" s="36"/>
+      <c r="A39" s="29"/>
+      <c r="B39" s="37"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -8136,8 +8492,8 @@
       </c>
     </row>
     <row r="40" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
-      <c r="B40" s="37"/>
+      <c r="A40" s="29"/>
+      <c r="B40" s="38"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
@@ -8227,15 +8583,15 @@
       </c>
     </row>
     <row r="41" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
+      <c r="A41" s="29"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
-      <c r="B42" s="35" t="s">
+      <c r="A42" s="29"/>
+      <c r="B42" s="36" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -8243,8 +8599,8 @@
       </c>
     </row>
     <row r="43" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="21"/>
-      <c r="B43" s="36"/>
+      <c r="A43" s="29"/>
+      <c r="B43" s="37"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -8334,8 +8690,8 @@
       </c>
     </row>
     <row r="44" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="21"/>
-      <c r="B44" s="37"/>
+      <c r="A44" s="29"/>
+      <c r="B44" s="38"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
@@ -8425,13 +8781,13 @@
       </c>
     </row>
     <row r="45" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="21"/>
+      <c r="A45" s="29"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
     </row>
     <row r="46" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="21"/>
-      <c r="B46" s="35" t="s">
+      <c r="A46" s="29"/>
+      <c r="B46" s="36" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -8439,29 +8795,29 @@
       </c>
     </row>
     <row r="47" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="21"/>
-      <c r="B47" s="36"/>
+      <c r="A47" s="29"/>
+      <c r="B47" s="37"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="21"/>
-      <c r="B48" s="37"/>
+      <c r="A48" s="29"/>
+      <c r="B48" s="38"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="21"/>
+      <c r="A49" s="29"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="21"/>
-      <c r="B50" s="35" t="s">
+      <c r="A50" s="29"/>
+      <c r="B50" s="36" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -8581,8 +8937,8 @@
       </c>
     </row>
     <row r="51" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="21"/>
-      <c r="B51" s="36"/>
+      <c r="A51" s="29"/>
+      <c r="B51" s="37"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -8700,8 +9056,8 @@
       </c>
     </row>
     <row r="52" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="21"/>
-      <c r="B52" s="37"/>
+      <c r="A52" s="29"/>
+      <c r="B52" s="38"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -8824,40 +9180,190 @@
       <c r="C53" s="8"/>
     </row>
     <row r="54" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="38" t="s">
+      <c r="A54" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="38" t="s">
+      <c r="B54" s="35" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>21</v>
       </c>
+      <c r="D54" s="5">
+        <v>13</v>
+      </c>
+      <c r="E54" s="5">
+        <v>12</v>
+      </c>
+      <c r="F54" s="5">
+        <v>15</v>
+      </c>
+      <c r="G54" s="5">
+        <v>14</v>
+      </c>
+      <c r="H54" s="5">
+        <v>11</v>
+      </c>
+      <c r="I54" s="5">
+        <v>17</v>
+      </c>
+      <c r="J54" s="5">
+        <v>15</v>
+      </c>
+      <c r="K54" s="5">
+        <v>14</v>
+      </c>
+      <c r="L54" s="5">
+        <v>17</v>
+      </c>
+      <c r="M54" s="5">
+        <v>12</v>
+      </c>
+      <c r="N54" s="5">
+        <v>16</v>
+      </c>
+      <c r="O54" s="5">
+        <v>22</v>
+      </c>
+      <c r="P54" s="5">
+        <v>16</v>
+      </c>
+      <c r="Q54" s="5">
+        <v>16</v>
+      </c>
+      <c r="R54" s="5">
+        <v>17</v>
+      </c>
+      <c r="S54" s="5">
+        <v>19</v>
+      </c>
+      <c r="T54" s="5">
+        <v>22</v>
+      </c>
+      <c r="U54" s="5">
+        <v>18</v>
+      </c>
+      <c r="V54" s="5">
+        <v>14</v>
+      </c>
+      <c r="W54" s="5">
+        <v>16</v>
+      </c>
+      <c r="X54" s="5">
+        <v>20</v>
+      </c>
+      <c r="AA54" s="5">
+        <v>22</v>
+      </c>
+      <c r="AB54" s="5">
+        <v>20</v>
+      </c>
+      <c r="AC54" s="5">
+        <v>22</v>
+      </c>
+      <c r="AE54" s="5">
+        <v>34</v>
+      </c>
     </row>
     <row r="55" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="22"/>
-      <c r="B55" s="22"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="22"/>
-      <c r="B56" s="22"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="30"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
+      <c r="D56" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="E56" s="5">
+        <v>-0.1</v>
+      </c>
+      <c r="F56" s="5">
+        <v>-0.35</v>
+      </c>
+      <c r="G56" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="H56" s="5">
+        <v>0</v>
+      </c>
+      <c r="I56" s="5">
+        <v>-0.4</v>
+      </c>
+      <c r="J56" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="K56" s="5">
+        <v>-0.1</v>
+      </c>
+      <c r="L56" s="5">
+        <v>-0.3</v>
+      </c>
+      <c r="M56" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="N56" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="O56" s="5">
+        <v>-0.5</v>
+      </c>
+      <c r="P56" s="5">
+        <v>-0.25</v>
+      </c>
+      <c r="Q56" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="R56" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="S56" s="5">
+        <v>-0.35</v>
+      </c>
+      <c r="T56" s="5">
+        <v>-0.35</v>
+      </c>
+      <c r="U56" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="V56" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="W56" s="5">
+        <v>0</v>
+      </c>
+      <c r="X56" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="AA56" s="5">
+        <v>-0.25</v>
+      </c>
+      <c r="AB56" s="5">
+        <v>-0.25</v>
+      </c>
+      <c r="AC56" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="AE56" s="5">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="57" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="22"/>
-      <c r="B57" s="23"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="31"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="22"/>
-      <c r="B58" s="38" t="s">
+      <c r="A58" s="30"/>
+      <c r="B58" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -8865,29 +9371,29 @@
       </c>
     </row>
     <row r="59" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="22"/>
-      <c r="B59" s="22"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="22"/>
-      <c r="B60" s="23"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="31"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="22"/>
+      <c r="A61" s="30"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="22"/>
-      <c r="B62" s="38" t="s">
+      <c r="A62" s="30"/>
+      <c r="B62" s="35" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -8895,22 +9401,22 @@
       </c>
     </row>
     <row r="63" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="22"/>
-      <c r="B63" s="22"/>
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="23"/>
-      <c r="B64" s="23"/>
+      <c r="A64" s="31"/>
+      <c r="B64" s="31"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:31" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:31" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="21" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -9005,7 +9511,7 @@
       </c>
     </row>
     <row r="67" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="31"/>
+      <c r="A67" s="22"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -9098,7 +9604,7 @@
       </c>
     </row>
     <row r="68" spans="1:31" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="31"/>
+      <c r="A68" s="22"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -9191,7 +9697,7 @@
       </c>
     </row>
     <row r="69" spans="1:31" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="32"/>
+      <c r="A69" s="23"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -9285,6 +9791,9 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="B9:B12"/>
@@ -9299,9 +9808,6 @@
     <mergeCell ref="B62:B64"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="A66:A69"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9380,40 +9886,40 @@
         <v>139</v>
       </c>
       <c r="D5" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="G5" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:15" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -9544,10 +10050,10 @@
       </c>
     </row>
     <row r="9" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -9591,8 +10097,8 @@
       </c>
     </row>
     <row r="10" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="18"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -9634,8 +10140,8 @@
       </c>
     </row>
     <row r="11" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="18"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -9677,8 +10183,8 @@
       </c>
     </row>
     <row r="12" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="18"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -9720,8 +10226,8 @@
       </c>
     </row>
     <row r="13" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="18" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -9729,25 +10235,25 @@
       </c>
     </row>
     <row r="14" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="18"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="18"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
+      <c r="A16" s="28"/>
     </row>
     <row r="17" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="24" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -9791,8 +10297,8 @@
       </c>
     </row>
     <row r="18" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="25"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -9834,8 +10340,8 @@
       </c>
     </row>
     <row r="19" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="25"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -9877,8 +10383,8 @@
       </c>
     </row>
     <row r="20" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20"/>
-      <c r="B20" s="26"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -9926,7 +10432,7 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="29" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="39" t="s">
@@ -9973,7 +10479,7 @@
       </c>
     </row>
     <row r="23" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -10028,7 +10534,7 @@
       </c>
     </row>
     <row r="24" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -10071,7 +10577,7 @@
       </c>
     </row>
     <row r="25" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -10114,14 +10620,14 @@
       </c>
     </row>
     <row r="26" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
+      <c r="A27" s="29"/>
       <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
@@ -10166,7 +10672,7 @@
       </c>
     </row>
     <row r="28" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -10221,7 +10727,7 @@
       </c>
     </row>
     <row r="29" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -10264,7 +10770,7 @@
       </c>
     </row>
     <row r="30" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -10307,15 +10813,15 @@
       </c>
     </row>
     <row r="31" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
-      <c r="B32" s="35" t="s">
+      <c r="A32" s="29"/>
+      <c r="B32" s="36" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -10359,8 +10865,8 @@
       </c>
     </row>
     <row r="33" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
-      <c r="B33" s="36"/>
+      <c r="A33" s="29"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -10414,8 +10920,8 @@
       </c>
     </row>
     <row r="34" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
-      <c r="B34" s="36"/>
+      <c r="A34" s="29"/>
+      <c r="B34" s="37"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -10457,8 +10963,8 @@
       </c>
     </row>
     <row r="35" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
-      <c r="B35" s="37"/>
+      <c r="A35" s="29"/>
+      <c r="B35" s="38"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
@@ -10500,15 +11006,15 @@
       </c>
     </row>
     <row r="36" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
-      <c r="B37" s="35" t="s">
+      <c r="A37" s="29"/>
+      <c r="B37" s="36" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -10552,8 +11058,8 @@
       </c>
     </row>
     <row r="38" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
-      <c r="B38" s="36"/>
+      <c r="A38" s="29"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -10607,8 +11113,8 @@
       </c>
     </row>
     <row r="39" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
-      <c r="B39" s="36"/>
+      <c r="A39" s="29"/>
+      <c r="B39" s="37"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -10650,8 +11156,8 @@
       </c>
     </row>
     <row r="40" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
-      <c r="B40" s="37"/>
+      <c r="A40" s="29"/>
+      <c r="B40" s="38"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
@@ -10693,15 +11199,15 @@
       </c>
     </row>
     <row r="41" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
+      <c r="A41" s="29"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
-      <c r="B42" s="35" t="s">
+      <c r="A42" s="29"/>
+      <c r="B42" s="36" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -10757,8 +11263,8 @@
       </c>
     </row>
     <row r="43" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="21"/>
-      <c r="B43" s="36"/>
+      <c r="A43" s="29"/>
+      <c r="B43" s="37"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -10800,8 +11306,8 @@
       </c>
     </row>
     <row r="44" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="21"/>
-      <c r="B44" s="37"/>
+      <c r="A44" s="29"/>
+      <c r="B44" s="38"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
@@ -10843,14 +11349,14 @@
       </c>
     </row>
     <row r="45" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="21"/>
+      <c r="A45" s="29"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
       <c r="F45" s="17"/>
     </row>
     <row r="46" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="21"/>
-      <c r="B46" s="35" t="s">
+      <c r="A46" s="29"/>
+      <c r="B46" s="36" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -10858,29 +11364,29 @@
       </c>
     </row>
     <row r="47" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="21"/>
-      <c r="B47" s="36"/>
+      <c r="A47" s="29"/>
+      <c r="B47" s="37"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="21"/>
-      <c r="B48" s="37"/>
+      <c r="A48" s="29"/>
+      <c r="B48" s="38"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="21"/>
+      <c r="A49" s="29"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="21"/>
-      <c r="B50" s="35" t="s">
+      <c r="A50" s="29"/>
+      <c r="B50" s="36" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -10936,8 +11442,8 @@
       </c>
     </row>
     <row r="51" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="21"/>
-      <c r="B51" s="36"/>
+      <c r="A51" s="29"/>
+      <c r="B51" s="37"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -10991,8 +11497,8 @@
       </c>
     </row>
     <row r="52" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="21"/>
-      <c r="B52" s="37"/>
+      <c r="A52" s="29"/>
+      <c r="B52" s="38"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -11051,22 +11557,55 @@
       <c r="C53" s="8"/>
     </row>
     <row r="54" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="38" t="s">
+      <c r="A54" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="38" t="s">
+      <c r="B54" s="35" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>21</v>
       </c>
+      <c r="D54" s="5">
+        <v>30</v>
+      </c>
+      <c r="E54" s="5">
+        <v>22</v>
+      </c>
       <c r="F54" s="5" t="s">
         <v>156</v>
       </c>
+      <c r="G54" s="5">
+        <v>32</v>
+      </c>
+      <c r="H54" s="5">
+        <v>36</v>
+      </c>
+      <c r="I54" s="5">
+        <v>34</v>
+      </c>
+      <c r="J54" s="5">
+        <v>44</v>
+      </c>
+      <c r="K54" s="5">
+        <v>35</v>
+      </c>
+      <c r="L54" s="5">
+        <v>32</v>
+      </c>
+      <c r="M54" s="5">
+        <v>52</v>
+      </c>
+      <c r="N54" s="5">
+        <v>49</v>
+      </c>
+      <c r="O54" s="5">
+        <v>50</v>
+      </c>
     </row>
     <row r="55" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="22"/>
-      <c r="B55" s="22"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
@@ -11075,18 +11614,51 @@
       </c>
     </row>
     <row r="56" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="22"/>
-      <c r="B56" s="22"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="30"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
+      <c r="D56" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="E56" s="5">
+        <v>0</v>
+      </c>
       <c r="F56" s="5" t="s">
         <v>156</v>
       </c>
+      <c r="G56" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="H56" s="5">
+        <v>-0.4</v>
+      </c>
+      <c r="I56" s="5">
+        <v>-0.3</v>
+      </c>
+      <c r="J56" s="5">
+        <v>-0.4</v>
+      </c>
+      <c r="K56" s="5">
+        <v>-0.25</v>
+      </c>
+      <c r="L56" s="5">
+        <v>-0.1</v>
+      </c>
+      <c r="M56" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="N56" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="O56" s="5">
+        <v>-0.45</v>
+      </c>
     </row>
     <row r="57" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="22"/>
-      <c r="B57" s="23"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="31"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
@@ -11095,8 +11667,8 @@
       </c>
     </row>
     <row r="58" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="22"/>
-      <c r="B58" s="38" t="s">
+      <c r="A58" s="30"/>
+      <c r="B58" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -11104,29 +11676,29 @@
       </c>
     </row>
     <row r="59" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="22"/>
-      <c r="B59" s="22"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="22"/>
-      <c r="B60" s="23"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="31"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="22"/>
+      <c r="A61" s="30"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="22"/>
-      <c r="B62" s="38" t="s">
+      <c r="A62" s="30"/>
+      <c r="B62" s="35" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -11137,8 +11709,8 @@
       </c>
     </row>
     <row r="63" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="22"/>
-      <c r="B63" s="22"/>
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
@@ -11147,8 +11719,8 @@
       </c>
     </row>
     <row r="64" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="23"/>
-      <c r="B64" s="23"/>
+      <c r="A64" s="31"/>
+      <c r="B64" s="31"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
@@ -11158,7 +11730,7 @@
     </row>
     <row r="65" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="21" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -11205,7 +11777,7 @@
       </c>
     </row>
     <row r="67" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="31"/>
+      <c r="A67" s="22"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -11250,7 +11822,7 @@
       </c>
     </row>
     <row r="68" spans="1:15" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="31"/>
+      <c r="A68" s="22"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -11295,7 +11867,7 @@
       </c>
     </row>
     <row r="69" spans="1:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="32"/>
+      <c r="A69" s="23"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -11341,6 +11913,9 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="B9:B12"/>
@@ -11355,9 +11930,6 @@
     <mergeCell ref="B62:B64"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="A66:A69"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11510,70 +12082,70 @@
         <v>139</v>
       </c>
       <c r="D5" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="E5" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="F5" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="Q5" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="R5" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="S5" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="S5" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="T5" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="U5" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="U5" s="1" t="s">
+      <c r="V5" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="V5" s="1" t="s">
+      <c r="W5" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="W5" s="1" t="s">
+      <c r="X5" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="X5" s="1" t="s">
+      <c r="Y5" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="Y5" s="1" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -11749,7 +12321,7 @@
         <v>2</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
@@ -11764,7 +12336,7 @@
         <v>3</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q8" s="1">
         <v>4</v>
@@ -11796,10 +12368,10 @@
       <c r="AA8" s="1"/>
     </row>
     <row r="9" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -11860,7 +12432,7 @@
         <v>340</v>
       </c>
       <c r="V9" s="3">
-        <v>350</v>
+        <v>485</v>
       </c>
       <c r="W9" s="3">
         <v>365</v>
@@ -11873,8 +12445,8 @@
       </c>
     </row>
     <row r="10" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="18"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -11946,8 +12518,8 @@
       </c>
     </row>
     <row r="11" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="18"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -12019,8 +12591,8 @@
       </c>
     </row>
     <row r="12" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="18"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -12092,8 +12664,8 @@
       </c>
     </row>
     <row r="13" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="18" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -12101,25 +12673,25 @@
       </c>
     </row>
     <row r="14" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="18"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="18"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:27" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
+      <c r="A16" s="28"/>
     </row>
     <row r="17" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="24" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -12193,8 +12765,8 @@
       </c>
     </row>
     <row r="18" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="25"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -12266,8 +12838,8 @@
       </c>
     </row>
     <row r="19" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="25"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -12339,8 +12911,8 @@
       </c>
     </row>
     <row r="20" spans="1:25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20"/>
-      <c r="B20" s="26"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -12418,7 +12990,7 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="29" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="39" t="s">
@@ -12482,7 +13054,7 @@
         <v>15</v>
       </c>
       <c r="V22" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W22" s="4">
         <v>15</v>
@@ -12495,7 +13067,7 @@
       </c>
     </row>
     <row r="23" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -12590,7 +13162,7 @@
       </c>
     </row>
     <row r="24" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -12650,7 +13222,7 @@
         <v>10</v>
       </c>
       <c r="V24" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W24" s="4">
         <v>11</v>
@@ -12663,7 +13235,7 @@
       </c>
     </row>
     <row r="25" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -12736,14 +13308,14 @@
       </c>
     </row>
     <row r="26" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
+      <c r="A27" s="29"/>
       <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
@@ -12805,7 +13377,7 @@
         <v>23</v>
       </c>
       <c r="V27" s="4">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="W27" s="4">
         <v>24</v>
@@ -12818,7 +13390,7 @@
       </c>
     </row>
     <row r="28" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -12913,7 +13485,7 @@
       </c>
     </row>
     <row r="29" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -12973,7 +13545,7 @@
         <v>10</v>
       </c>
       <c r="V29" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W29" s="4">
         <v>11</v>
@@ -12986,7 +13558,7 @@
       </c>
     </row>
     <row r="30" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -13059,15 +13631,15 @@
       </c>
     </row>
     <row r="31" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
-      <c r="B32" s="35" t="s">
+      <c r="A32" s="29"/>
+      <c r="B32" s="36" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -13128,7 +13700,7 @@
         <v>20</v>
       </c>
       <c r="V32" s="4">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="W32" s="4">
         <v>21</v>
@@ -13141,8 +13713,8 @@
       </c>
     </row>
     <row r="33" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
-      <c r="B33" s="36"/>
+      <c r="A33" s="29"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -13236,8 +13808,8 @@
       </c>
     </row>
     <row r="34" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
-      <c r="B34" s="36"/>
+      <c r="A34" s="29"/>
+      <c r="B34" s="37"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -13296,7 +13868,7 @@
         <v>10</v>
       </c>
       <c r="V34" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W34" s="4">
         <v>11</v>
@@ -13309,8 +13881,8 @@
       </c>
     </row>
     <row r="35" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
-      <c r="B35" s="37"/>
+      <c r="A35" s="29"/>
+      <c r="B35" s="38"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
@@ -13382,15 +13954,15 @@
       </c>
     </row>
     <row r="36" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
-      <c r="B37" s="35" t="s">
+      <c r="A37" s="29"/>
+      <c r="B37" s="36" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -13451,7 +14023,7 @@
         <v>12</v>
       </c>
       <c r="V37" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W37" s="4">
         <v>12</v>
@@ -13464,8 +14036,8 @@
       </c>
     </row>
     <row r="38" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
-      <c r="B38" s="36"/>
+      <c r="A38" s="29"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -13559,8 +14131,8 @@
       </c>
     </row>
     <row r="39" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
-      <c r="B39" s="36"/>
+      <c r="A39" s="29"/>
+      <c r="B39" s="37"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -13619,7 +14191,7 @@
         <v>10</v>
       </c>
       <c r="V39" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W39" s="4">
         <v>11</v>
@@ -13632,8 +14204,8 @@
       </c>
     </row>
     <row r="40" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
-      <c r="B40" s="37"/>
+      <c r="A40" s="29"/>
+      <c r="B40" s="38"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
@@ -13705,15 +14277,15 @@
       </c>
     </row>
     <row r="41" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
+      <c r="A41" s="29"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
-      <c r="B42" s="35" t="s">
+      <c r="A42" s="29"/>
+      <c r="B42" s="36" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -13809,8 +14381,8 @@
       </c>
     </row>
     <row r="43" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="21"/>
-      <c r="B43" s="36"/>
+      <c r="A43" s="29"/>
+      <c r="B43" s="37"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
@@ -13869,7 +14441,7 @@
         <v>10</v>
       </c>
       <c r="V43" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W43" s="4">
         <v>11</v>
@@ -13882,8 +14454,8 @@
       </c>
     </row>
     <row r="44" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="21"/>
-      <c r="B44" s="37"/>
+      <c r="A44" s="29"/>
+      <c r="B44" s="38"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
@@ -13955,13 +14527,13 @@
       </c>
     </row>
     <row r="45" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="21"/>
+      <c r="A45" s="29"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
     </row>
     <row r="46" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="21"/>
-      <c r="B46" s="35" t="s">
+      <c r="A46" s="29"/>
+      <c r="B46" s="36" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -13969,29 +14541,29 @@
       </c>
     </row>
     <row r="47" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="21"/>
-      <c r="B47" s="36"/>
+      <c r="A47" s="29"/>
+      <c r="B47" s="37"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="21"/>
-      <c r="B48" s="37"/>
+      <c r="A48" s="29"/>
+      <c r="B48" s="38"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="21"/>
+      <c r="A49" s="29"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="21"/>
-      <c r="B50" s="35" t="s">
+      <c r="A50" s="29"/>
+      <c r="B50" s="36" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -14071,7 +14643,7 @@
       </c>
       <c r="V50" s="4">
         <f t="shared" si="6"/>
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="W50" s="4">
         <f t="shared" si="6"/>
@@ -14087,8 +14659,8 @@
       </c>
     </row>
     <row r="51" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="21"/>
-      <c r="B51" s="36"/>
+      <c r="A51" s="29"/>
+      <c r="B51" s="37"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -14166,7 +14738,7 @@
       </c>
       <c r="V51" s="4">
         <f t="shared" si="8"/>
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="W51" s="4">
         <f t="shared" si="8"/>
@@ -14182,8 +14754,8 @@
       </c>
     </row>
     <row r="52" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="21"/>
-      <c r="B52" s="37"/>
+      <c r="A52" s="29"/>
+      <c r="B52" s="38"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -14261,7 +14833,7 @@
       </c>
       <c r="V52" s="4">
         <f t="shared" si="10"/>
-        <v>144</v>
+        <v>184.8</v>
       </c>
       <c r="W52" s="4">
         <f t="shared" si="10"/>
@@ -14282,40 +14854,202 @@
       <c r="C53" s="8"/>
     </row>
     <row r="54" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="38" t="s">
+      <c r="A54" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="38" t="s">
+      <c r="B54" s="35" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>21</v>
       </c>
+      <c r="D54" s="5">
+        <v>50</v>
+      </c>
+      <c r="E54" s="5">
+        <v>58</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="H54" s="5">
+        <v>48</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="J54" s="5">
+        <v>55</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="L54" s="5">
+        <v>62</v>
+      </c>
+      <c r="M54" s="5">
+        <v>73</v>
+      </c>
+      <c r="N54" s="5">
+        <v>64</v>
+      </c>
+      <c r="O54" s="5">
+        <v>66</v>
+      </c>
+      <c r="P54" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q54" s="5">
+        <v>66</v>
+      </c>
+      <c r="R54" s="5">
+        <v>70</v>
+      </c>
+      <c r="S54" s="5">
+        <v>64</v>
+      </c>
+      <c r="T54" s="5">
+        <v>79</v>
+      </c>
+      <c r="U54" s="5">
+        <v>73</v>
+      </c>
+      <c r="V54" s="5">
+        <v>100</v>
+      </c>
+      <c r="W54" s="5">
+        <v>69</v>
+      </c>
+      <c r="X54" s="5">
+        <v>80</v>
+      </c>
+      <c r="Y54" s="5">
+        <v>79</v>
+      </c>
     </row>
     <row r="55" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="22"/>
-      <c r="B55" s="22"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="F55" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="P55" s="5" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="56" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="22"/>
-      <c r="B56" s="22"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="30"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
+      <c r="D56" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="E56" s="5">
+        <v>-0.45</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="H56" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="J56" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="K56" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="L56" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="M56" s="5">
+        <v>-0.55000000000000004</v>
+      </c>
+      <c r="N56" s="5">
+        <v>-0.25</v>
+      </c>
+      <c r="O56" s="5">
+        <v>-0.35</v>
+      </c>
+      <c r="P56" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q56" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="R56" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="S56" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="T56" s="5">
+        <v>-0.65</v>
+      </c>
+      <c r="U56" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="V56" s="5">
+        <v>-0.15</v>
+      </c>
+      <c r="W56" s="5">
+        <v>-0.15</v>
+      </c>
+      <c r="X56" s="5">
+        <v>-0.25</v>
+      </c>
+      <c r="Y56" s="5">
+        <v>-0.3</v>
+      </c>
     </row>
     <row r="57" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="22"/>
-      <c r="B57" s="23"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="31"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
+      <c r="F57" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="P57" s="5" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="58" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="22"/>
-      <c r="B58" s="38" t="s">
+      <c r="A58" s="30"/>
+      <c r="B58" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -14323,29 +15057,29 @@
       </c>
     </row>
     <row r="59" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="22"/>
-      <c r="B59" s="22"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="22"/>
-      <c r="B60" s="23"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="31"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="22"/>
+      <c r="A61" s="30"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="22"/>
-      <c r="B62" s="38" t="s">
+      <c r="A62" s="30"/>
+      <c r="B62" s="35" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -14353,22 +15087,22 @@
       </c>
     </row>
     <row r="63" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="22"/>
-      <c r="B63" s="22"/>
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="23"/>
-      <c r="B64" s="23"/>
+      <c r="A64" s="31"/>
+      <c r="B64" s="31"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="21" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -14445,7 +15179,7 @@
       </c>
     </row>
     <row r="67" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="31"/>
+      <c r="A67" s="22"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -14520,7 +15254,7 @@
       </c>
     </row>
     <row r="68" spans="1:25" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="31"/>
+      <c r="A68" s="22"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -14595,7 +15329,7 @@
       </c>
     </row>
     <row r="69" spans="1:25" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="32"/>
+      <c r="A69" s="23"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -14671,6 +15405,9 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A66:A69"/>
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="B9:B12"/>
@@ -14685,9 +15422,6 @@
     <mergeCell ref="B62:B64"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="A66:A69"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14697,53 +15431,48 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21A46B60-4F3A-4D99-AC29-6361CD3DE12A}">
-  <dimension ref="A1:R67"/>
+  <dimension ref="A1:Q67"/>
   <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="16.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-    </row>
-    <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:17" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:16" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>196</v>
+        <v>117</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>121</v>
+        <v>302</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>122</v>
@@ -14752,19 +15481,16 @@
         <v>123</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
@@ -14809,11 +15535,8 @@
       <c r="P5" s="1">
         <v>7</v>
       </c>
-      <c r="Q5" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:16" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
@@ -14829,13 +15552,13 @@
         <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="1">
         <v>2</v>
       </c>
       <c r="I6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" s="1">
         <v>3</v>
@@ -14853,135 +15576,296 @@
         <v>2</v>
       </c>
       <c r="O6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P6" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q6" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="20" t="s">
+    <row r="7" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="20"/>
-      <c r="B8" s="18"/>
+        <v>390</v>
+      </c>
+      <c r="E7" s="3">
+        <v>380</v>
+      </c>
+      <c r="F7" s="3">
+        <v>395</v>
+      </c>
+      <c r="G7" s="3">
+        <v>420</v>
+      </c>
+      <c r="H7" s="3">
+        <v>425</v>
+      </c>
+      <c r="I7" s="3">
+        <v>475</v>
+      </c>
+      <c r="J7" s="3">
+        <v>475</v>
+      </c>
+      <c r="L7" s="3">
+        <v>550</v>
+      </c>
+      <c r="M7" s="3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="28"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20"/>
-      <c r="B9" s="18"/>
+        <v>1100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>900</v>
+      </c>
+      <c r="F8" s="3">
+        <v>850</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1050</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M8" s="3">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="28"/>
+      <c r="B9" s="26"/>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="3">
+        <v>16</v>
+      </c>
+      <c r="E9" s="3">
+        <v>18</v>
+      </c>
+      <c r="F9" s="3">
+        <v>17</v>
+      </c>
+      <c r="G9" s="3">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="18"/>
+      <c r="H9" s="3">
+        <v>17</v>
+      </c>
+      <c r="I9" s="3">
+        <v>18</v>
+      </c>
+      <c r="J9" s="3">
+        <v>20</v>
+      </c>
+      <c r="L9" s="3">
+        <v>20</v>
+      </c>
+      <c r="M9" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="18" t="s">
+    </row>
+    <row r="11" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="28"/>
+      <c r="B11" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="18"/>
+    <row r="12" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="28"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="18"/>
+    <row r="13" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="28"/>
+      <c r="B13" s="26"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-    </row>
-    <row r="15" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="24" t="s">
+    <row r="14" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="28"/>
+    </row>
+    <row r="15" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="28"/>
+      <c r="B15" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
-      <c r="B16" s="25"/>
+        <v>0.3</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="I15" s="3">
+        <v>-0.2</v>
+      </c>
+      <c r="J15" s="3">
+        <v>-0.3</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="28"/>
+      <c r="B16" s="33"/>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="3">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="25"/>
+        <v>1</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I16" s="3">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J16" s="3">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L16" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="M16" s="3">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="28"/>
+      <c r="B17" s="33"/>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D17" s="3">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="26"/>
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="G17" s="3">
+        <v>-0.3</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="28"/>
+      <c r="B18" s="34"/>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.1</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-    </row>
-    <row r="20" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="21" t="s">
+    </row>
+    <row r="20" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="29" t="s">
         <v>131</v>
       </c>
       <c r="B20" s="39" t="s">
@@ -14990,251 +15874,473 @@
       <c r="C20" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="21"/>
+      <c r="D20" s="4">
+        <v>16</v>
+      </c>
+      <c r="E20" s="4">
+        <v>16</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G20" s="4">
+        <v>18</v>
+      </c>
+      <c r="H20" s="4">
+        <v>18</v>
+      </c>
+      <c r="I20" s="4">
+        <v>19</v>
+      </c>
+      <c r="J20" s="4">
+        <v>19</v>
+      </c>
+      <c r="L20" s="4">
+        <v>21</v>
+      </c>
+      <c r="M20" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="29"/>
       <c r="B21" s="39"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="21"/>
+    <row r="22" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="29"/>
       <c r="B22" s="39"/>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
+      <c r="D22" s="4">
+        <v>10</v>
+      </c>
+      <c r="E22" s="4">
+        <v>9</v>
+      </c>
+      <c r="G22" s="4">
+        <v>10</v>
+      </c>
+      <c r="H22" s="4">
+        <v>9</v>
+      </c>
+      <c r="I22" s="4">
+        <v>10</v>
+      </c>
+      <c r="J22" s="4">
+        <v>10</v>
+      </c>
+      <c r="L22" s="4">
+        <v>13</v>
+      </c>
+      <c r="M22" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="29"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+    <row r="24" spans="1:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="29"/>
       <c r="B24" s="12"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-    </row>
-    <row r="25" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+    </row>
+    <row r="25" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="29"/>
       <c r="B25" s="39" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="D25" s="4">
+        <v>25</v>
+      </c>
+      <c r="E25" s="4">
+        <v>25</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G25" s="4">
+        <v>27</v>
+      </c>
+      <c r="H25" s="4">
+        <v>27</v>
+      </c>
+      <c r="I25" s="4">
+        <v>28</v>
+      </c>
+      <c r="J25" s="4">
+        <v>28</v>
+      </c>
+      <c r="L25" s="4">
+        <v>32</v>
+      </c>
+      <c r="M25" s="4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="29"/>
       <c r="B26" s="39"/>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
+    <row r="27" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="29"/>
       <c r="B27" s="39"/>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
+      <c r="D27" s="4">
+        <v>10</v>
+      </c>
+      <c r="E27" s="4">
+        <v>9</v>
+      </c>
+      <c r="G27" s="4">
+        <v>10</v>
+      </c>
+      <c r="H27" s="4">
+        <v>9</v>
+      </c>
+      <c r="I27" s="4">
+        <v>10</v>
+      </c>
+      <c r="J27" s="4">
+        <v>10</v>
+      </c>
+      <c r="L27" s="4">
+        <v>13</v>
+      </c>
+      <c r="M27" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="29"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+    <row r="29" spans="1:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="29"/>
       <c r="B29" s="13"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-    </row>
-    <row r="30" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
-      <c r="B30" s="35" t="s">
+    </row>
+    <row r="30" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="29"/>
+      <c r="B30" s="36" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
-      <c r="B31" s="36"/>
+      <c r="D30" s="4">
+        <v>22</v>
+      </c>
+      <c r="E30" s="4">
+        <v>22</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G30" s="4">
+        <v>24</v>
+      </c>
+      <c r="H30" s="4">
+        <v>24</v>
+      </c>
+      <c r="I30" s="4">
+        <v>25</v>
+      </c>
+      <c r="J30" s="4">
+        <v>25</v>
+      </c>
+      <c r="L30" s="4">
+        <v>28</v>
+      </c>
+      <c r="M30" s="4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="29"/>
+      <c r="B31" s="37"/>
       <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
-      <c r="B32" s="36"/>
+    <row r="32" spans="1:13" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="29"/>
+      <c r="B32" s="37"/>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
-      <c r="B33" s="37"/>
+      <c r="D32" s="4">
+        <v>10</v>
+      </c>
+      <c r="E32" s="4">
+        <v>9</v>
+      </c>
+      <c r="G32" s="4">
+        <v>10</v>
+      </c>
+      <c r="H32" s="4">
+        <v>9</v>
+      </c>
+      <c r="I32" s="4">
+        <v>10</v>
+      </c>
+      <c r="J32" s="4">
+        <v>10</v>
+      </c>
+      <c r="L32" s="4">
+        <v>13</v>
+      </c>
+      <c r="M32" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="29"/>
+      <c r="B33" s="38"/>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
+    <row r="34" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="29"/>
       <c r="B34" s="14"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
-      <c r="B35" s="35" t="s">
+    </row>
+    <row r="35" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="29"/>
+      <c r="B35" s="36" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
-      <c r="B36" s="36"/>
+      <c r="D35" s="4">
+        <v>13</v>
+      </c>
+      <c r="E35" s="4">
+        <v>13</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G35" s="4">
+        <v>15</v>
+      </c>
+      <c r="H35" s="4">
+        <v>15</v>
+      </c>
+      <c r="I35" s="4">
+        <v>16</v>
+      </c>
+      <c r="J35" s="4">
+        <v>16</v>
+      </c>
+      <c r="L35" s="4">
+        <v>18</v>
+      </c>
+      <c r="M35" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="29"/>
+      <c r="B36" s="37"/>
       <c r="C36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
-      <c r="B37" s="36"/>
+    <row r="37" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="29"/>
+      <c r="B37" s="37"/>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="38" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
-      <c r="B38" s="37"/>
+      <c r="D37" s="4">
+        <v>10</v>
+      </c>
+      <c r="E37" s="4">
+        <v>9</v>
+      </c>
+      <c r="G37" s="4">
+        <v>10</v>
+      </c>
+      <c r="H37" s="4">
+        <v>9</v>
+      </c>
+      <c r="I37" s="4">
+        <v>10</v>
+      </c>
+      <c r="J37" s="4">
+        <v>10</v>
+      </c>
+      <c r="L37" s="4">
+        <v>13</v>
+      </c>
+      <c r="M37" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="29"/>
+      <c r="B38" s="38"/>
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
+    <row r="39" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="29"/>
       <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-    </row>
-    <row r="40" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
-      <c r="B40" s="35" t="s">
+    </row>
+    <row r="40" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="29"/>
+      <c r="B40" s="36" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
-      <c r="B41" s="36"/>
+    <row r="41" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="29"/>
+      <c r="B41" s="37"/>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="42" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
-      <c r="B42" s="37"/>
+      <c r="D41" s="4">
+        <v>10</v>
+      </c>
+      <c r="E41" s="4">
+        <v>9</v>
+      </c>
+      <c r="G41" s="4">
+        <v>10</v>
+      </c>
+      <c r="H41" s="4">
+        <v>9</v>
+      </c>
+      <c r="I41" s="4">
+        <v>10</v>
+      </c>
+      <c r="J41" s="4">
+        <v>10</v>
+      </c>
+      <c r="L41" s="4">
+        <v>13</v>
+      </c>
+      <c r="M41" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="29"/>
+      <c r="B42" s="38"/>
       <c r="C42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="21"/>
+    <row r="43" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="29"/>
       <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-    </row>
-    <row r="44" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="21"/>
-      <c r="B44" s="35" t="s">
+    </row>
+    <row r="44" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="29"/>
+      <c r="B44" s="36" t="s">
         <v>30</v>
       </c>
       <c r="C44" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="21"/>
-      <c r="B45" s="36"/>
+    <row r="45" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="29"/>
+      <c r="B45" s="37"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="21"/>
-      <c r="B46" s="37"/>
+    <row r="46" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="29"/>
+      <c r="B46" s="38"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="21"/>
+    <row r="47" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="29"/>
       <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-    </row>
-    <row r="48" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="21"/>
-      <c r="B48" s="35" t="s">
+    </row>
+    <row r="48" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="29"/>
+      <c r="B48" s="36" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>29</v>
       </c>
       <c r="D48" s="4">
-        <f t="shared" ref="D48:R48" si="0">D20+D25+D30+D35</f>
-        <v>0</v>
+        <f t="shared" ref="D48:Q48" si="0">D20+D25+D30+D35</f>
+        <v>76</v>
       </c>
       <c r="E48" s="4">
+        <f>E20+E25+E30+E35</f>
+        <v>76</v>
+      </c>
+      <c r="F48" s="4" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F48" s="4">
-        <f>F20+F25+F30+F35</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G48" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H48" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="I48" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="J48" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="K48" s="4">
-        <f t="shared" si="0"/>
+        <f>K20+K25+K30+K35</f>
         <v>0</v>
       </c>
       <c r="L48" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="M48" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="N48" s="4">
         <f t="shared" si="0"/>
@@ -15252,56 +16358,52 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="21"/>
-      <c r="B49" s="36"/>
+    </row>
+    <row r="49" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="29"/>
+      <c r="B49" s="37"/>
       <c r="C49" s="4" t="s">
         <v>129</v>
       </c>
       <c r="D49" s="4">
-        <f t="shared" ref="D49:R49" si="1">D22+D27+D32+D37+D41</f>
-        <v>0</v>
+        <f t="shared" ref="D49:Q49" si="1">D22+D27+D32+D37+D41</f>
+        <v>50</v>
       </c>
       <c r="E49" s="4">
+        <f>E22+E27+E32+E37+E41</f>
+        <v>45</v>
+      </c>
+      <c r="F49" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F49" s="4">
-        <f>F22+F27+F32+F37+F41</f>
         <v>0</v>
       </c>
       <c r="G49" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H49" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I49" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J49" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K49" s="4">
-        <f t="shared" si="1"/>
+        <f>K22+K27+K32+K37+K41</f>
         <v>0</v>
       </c>
       <c r="L49" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M49" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="N49" s="4">
         <f t="shared" si="1"/>
@@ -15319,56 +16421,52 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="21"/>
-      <c r="B50" s="37"/>
+    </row>
+    <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="29"/>
+      <c r="B50" s="38"/>
       <c r="C50" s="4" t="s">
         <v>130</v>
       </c>
       <c r="D50" s="4">
         <f>D48*(1+D49*0.02)</f>
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="E50" s="4">
         <f>E48*(1+E49*0.02)</f>
-        <v>0</v>
-      </c>
-      <c r="F50" s="4">
-        <f>F48*(1+F49*0.02)</f>
-        <v>0</v>
+        <v>144.4</v>
+      </c>
+      <c r="F50" s="4" t="e">
+        <f t="shared" ref="F50:Q50" si="2">F48*(1+F49*0.02)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="G50" s="4">
-        <f t="shared" ref="G50:R50" si="2">G48*(1+G49*0.02)</f>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>168</v>
       </c>
       <c r="H50" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>159.6</v>
       </c>
       <c r="I50" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="J50" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="K50" s="4">
-        <f t="shared" si="2"/>
+        <f>K48*(1+K49*0.02)</f>
         <v>0</v>
       </c>
       <c r="L50" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>227.7</v>
       </c>
       <c r="M50" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>264.00000000000006</v>
       </c>
       <c r="N50" s="4">
         <f t="shared" si="2"/>
@@ -15386,104 +16484,153 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:17" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
     </row>
-    <row r="52" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="38" t="s">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="B52" s="38" t="s">
+      <c r="B52" s="35" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="53" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="22"/>
-      <c r="B53" s="22"/>
+      <c r="D52" s="5">
+        <v>75</v>
+      </c>
+      <c r="E52" s="5">
+        <v>70</v>
+      </c>
+      <c r="F52" s="5">
+        <v>65</v>
+      </c>
+      <c r="G52" s="5">
+        <v>100</v>
+      </c>
+      <c r="H52" s="5">
+        <v>90</v>
+      </c>
+      <c r="I52" s="5">
+        <v>110</v>
+      </c>
+      <c r="J52" s="5">
+        <v>120</v>
+      </c>
+      <c r="L52" s="5">
+        <v>150</v>
+      </c>
+      <c r="M52" s="5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="22"/>
-      <c r="B54" s="22"/>
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="30"/>
+      <c r="B54" s="30"/>
       <c r="C54" s="5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="55" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="22"/>
-      <c r="B55" s="23"/>
+      <c r="D54" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="E54" s="5">
+        <v>-0.05</v>
+      </c>
+      <c r="F54" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="G54" s="5">
+        <v>-0.5</v>
+      </c>
+      <c r="H54" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="I54" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="J54" s="5">
+        <v>-0.35</v>
+      </c>
+      <c r="L54" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="M54" s="5">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="30"/>
+      <c r="B55" s="31"/>
       <c r="C55" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="22"/>
-      <c r="B56" s="38" t="s">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="30"/>
+      <c r="B56" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C56" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="22"/>
-      <c r="B57" s="22"/>
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="30"/>
+      <c r="B57" s="30"/>
       <c r="C57" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="22"/>
-      <c r="B58" s="23"/>
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="30"/>
+      <c r="B58" s="31"/>
       <c r="C58" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="22"/>
+    <row r="59" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="30"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-    </row>
-    <row r="60" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="22"/>
-      <c r="B60" s="38" t="s">
+    </row>
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="30"/>
+      <c r="B60" s="35" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="22"/>
-      <c r="B61" s="22"/>
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="30"/>
+      <c r="B61" s="30"/>
       <c r="C61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="23"/>
-      <c r="B62" s="23"/>
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="31"/>
+      <c r="B62" s="31"/>
       <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="30" t="s">
+    <row r="63" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="21" t="s">
         <v>26</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -15492,48 +16639,51 @@
       <c r="C64" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F64" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="31"/>
+      <c r="E64" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="22"/>
       <c r="B65" s="4" t="s">
         <v>132</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="F65" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="31"/>
+      <c r="E65" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="22"/>
       <c r="B66" s="4" t="s">
         <v>133</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="F66" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="32"/>
+      <c r="E66" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="23"/>
       <c r="B67" s="5" t="s">
         <v>134</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F67" s="5">
+      <c r="E67" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A64:A67"/>
     <mergeCell ref="A7:A18"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B7:B10"/>
@@ -15548,9 +16698,6 @@
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="B35:B38"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A64:A67"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15573,76 +16720,76 @@
     </row>
     <row r="4" spans="1:39" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D4" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="U4" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="V4" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="AA4" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>279</v>
       </c>
       <c r="AB4" s="1" t="s">
         <v>149</v>
@@ -15654,31 +16801,31 @@
         <v>151</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AF4" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="AG4" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="AH4" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="AG4" s="1" t="s">
+      <c r="AI4" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="AH4" s="1" t="s">
+      <c r="AJ4" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="AI4" s="1" t="s">
+      <c r="AK4" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="AJ4" s="1" t="s">
+      <c r="AL4" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="AK4" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="AL4" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="AM4" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:39" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -15686,76 +16833,76 @@
         <v>139</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="J5" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="P5" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="Q5" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="R5" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="S5" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="T5" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="U5" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="V5" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="U5" s="1" t="s">
+      <c r="W5" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="V5" s="1" t="s">
+      <c r="X5" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="W5" s="1" t="s">
+      <c r="Y5" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="X5" s="1" t="s">
+      <c r="Z5" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="Y5" s="1" t="s">
+      <c r="AA5" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="Z5" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="AA5" s="1" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:39" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -15945,10 +17092,10 @@
       </c>
     </row>
     <row r="9" spans="1:39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -16028,8 +17175,8 @@
       </c>
     </row>
     <row r="10" spans="1:39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="18"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -16107,8 +17254,8 @@
       </c>
     </row>
     <row r="11" spans="1:39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="18"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
@@ -16186,87 +17333,87 @@
       </c>
     </row>
     <row r="12" spans="1:39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="18"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="K12" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="L12" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="R12" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="S12" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="V12" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>254</v>
-      </c>
       <c r="W12" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y12" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Z12" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AA12" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="1:39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="18" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="3">
@@ -16274,25 +17421,25 @@
       </c>
     </row>
     <row r="14" spans="1:39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="18"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="18"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
+      <c r="A16" s="28"/>
     </row>
     <row r="17" spans="1:39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="24" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -16372,8 +17519,8 @@
       </c>
     </row>
     <row r="18" spans="1:39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="25"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
@@ -16451,8 +17598,8 @@
       </c>
     </row>
     <row r="19" spans="1:39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="25"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
@@ -16530,8 +17677,8 @@
       </c>
     </row>
     <row r="20" spans="1:39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20"/>
-      <c r="B20" s="26"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -16615,7 +17762,7 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="29" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="39" t="s">
@@ -16695,7 +17842,7 @@
       </c>
     </row>
     <row r="23" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="39"/>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -16842,7 +17989,7 @@
       </c>
     </row>
     <row r="24" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="39"/>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -16918,7 +18065,7 @@
       </c>
     </row>
     <row r="25" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="39"/>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -16994,14 +18141,14 @@
       </c>
     </row>
     <row r="26" spans="1:39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
+      <c r="A27" s="29"/>
       <c r="B27" s="39" t="s">
         <v>16</v>
       </c>
@@ -17079,7 +18226,7 @@
       </c>
     </row>
     <row r="28" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="39"/>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -17226,7 +18373,7 @@
       </c>
     </row>
     <row r="29" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="39"/>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -17302,7 +18449,7 @@
       </c>
     </row>
     <row r="30" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="39"/>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -17378,15 +18525,15 @@
       </c>
     </row>
     <row r="31" spans="1:39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
-      <c r="B32" s="35" t="s">
+      <c r="A32" s="29"/>
+      <c r="B32" s="36" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -17463,8 +18610,8 @@
       </c>
     </row>
     <row r="33" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
-      <c r="B33" s="36"/>
+      <c r="A33" s="29"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="4" t="s">
         <v>7</v>
       </c>
@@ -17610,8 +18757,8 @@
       </c>
     </row>
     <row r="34" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
-      <c r="B34" s="36"/>
+      <c r="A34" s="29"/>
+      <c r="B34" s="37"/>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
@@ -17686,8 +18833,8 @@
       </c>
     </row>
     <row r="35" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
-      <c r="B35" s="37"/>
+      <c r="A35" s="29"/>
+      <c r="B35" s="38"/>
       <c r="C35" s="4" t="s">
         <v>15</v>
       </c>
@@ -17762,15 +18909,15 @@
       </c>
     </row>
     <row r="36" spans="1:39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="14"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
-      <c r="B37" s="35" t="s">
+      <c r="A37" s="29"/>
+      <c r="B37" s="36" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -17847,8 +18994,8 @@
       </c>
     </row>
     <row r="38" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
-      <c r="B38" s="36"/>
+      <c r="A38" s="29"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="4" t="s">
         <v>7</v>
       </c>
@@ -17994,8 +19141,8 @@
       </c>
     </row>
     <row r="39" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
-      <c r="B39" s="36"/>
+      <c r="A39" s="29"/>
+      <c r="B39" s="37"/>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
@@ -18070,8 +19217,8 @@
       </c>
     </row>
     <row r="40" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
-      <c r="B40" s="37"/>
+      <c r="A40" s="29"/>
+      <c r="B40" s="38"/>
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
@@ -18146,15 +19293,15 @@
       </c>
     </row>
     <row r="41" spans="1:39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
+      <c r="A41" s="29"/>
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
-      <c r="B42" s="35" t="s">
+      <c r="A42" s="29"/>
+      <c r="B42" s="36" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -18162,27 +19309,27 @@
       </c>
     </row>
     <row r="43" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="21"/>
-      <c r="B43" s="36"/>
+      <c r="A43" s="29"/>
+      <c r="B43" s="37"/>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="44" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="21"/>
-      <c r="B44" s="37"/>
+      <c r="A44" s="29"/>
+      <c r="B44" s="38"/>
       <c r="C44" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="21"/>
+      <c r="A45" s="29"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
     </row>
     <row r="46" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="21"/>
-      <c r="B46" s="35" t="s">
+      <c r="A46" s="29"/>
+      <c r="B46" s="36" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="4">
@@ -18190,29 +19337,29 @@
       </c>
     </row>
     <row r="47" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="21"/>
-      <c r="B47" s="36"/>
+      <c r="A47" s="29"/>
+      <c r="B47" s="37"/>
       <c r="C47" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:39" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="21"/>
-      <c r="B48" s="37"/>
+      <c r="A48" s="29"/>
+      <c r="B48" s="38"/>
       <c r="C48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="21"/>
+      <c r="A49" s="29"/>
       <c r="B49" s="15"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="21"/>
-      <c r="B50" s="35" t="s">
+      <c r="A50" s="29"/>
+      <c r="B50" s="36" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -18276,8 +19423,8 @@
       </c>
     </row>
     <row r="51" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="21"/>
-      <c r="B51" s="36"/>
+      <c r="A51" s="29"/>
+      <c r="B51" s="37"/>
       <c r="C51" s="4" t="s">
         <v>129</v>
       </c>
@@ -18339,8 +19486,8 @@
       </c>
     </row>
     <row r="52" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="21"/>
-      <c r="B52" s="37"/>
+      <c r="A52" s="29"/>
+      <c r="B52" s="38"/>
       <c r="C52" s="4" t="s">
         <v>130</v>
       </c>
@@ -18407,10 +19554,10 @@
       <c r="C53" s="8"/>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="38" t="s">
+      <c r="A54" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="38" t="s">
+      <c r="B54" s="35" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -18418,29 +19565,29 @@
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="22"/>
-      <c r="B55" s="22"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="22"/>
-      <c r="B56" s="22"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="30"/>
       <c r="C56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="22"/>
-      <c r="B57" s="23"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="31"/>
       <c r="C57" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="22"/>
-      <c r="B58" s="38" t="s">
+      <c r="A58" s="30"/>
+      <c r="B58" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C58" s="5">
@@ -18448,29 +19595,29 @@
       </c>
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="22"/>
-      <c r="B59" s="22"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
       <c r="C59" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="22"/>
-      <c r="B60" s="23"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="31"/>
       <c r="C60" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="22"/>
+      <c r="A61" s="30"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="22"/>
-      <c r="B62" s="38" t="s">
+      <c r="A62" s="30"/>
+      <c r="B62" s="35" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -18478,21 +19625,21 @@
       </c>
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="22"/>
-      <c r="B63" s="22"/>
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
       <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="23"/>
-      <c r="B64" s="23"/>
+      <c r="A64" s="31"/>
+      <c r="B64" s="31"/>
       <c r="C64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:43" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="21" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -18623,7 +19770,7 @@
       </c>
     </row>
     <row r="67" spans="1:43" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="31"/>
+      <c r="A67" s="22"/>
       <c r="B67" s="4" t="s">
         <v>132</v>
       </c>
@@ -18752,7 +19899,7 @@
       </c>
     </row>
     <row r="68" spans="1:43" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="31"/>
+      <c r="A68" s="22"/>
       <c r="B68" s="4" t="s">
         <v>133</v>
       </c>
@@ -18767,7 +19914,7 @@
       </c>
     </row>
     <row r="69" spans="1:43" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="32"/>
+      <c r="A69" s="23"/>
       <c r="B69" s="5" t="s">
         <v>134</v>
       </c>
@@ -18781,6 +19928,13 @@
     <sortCondition ref="D8:T8"/>
   </sortState>
   <mergeCells count="17">
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A54:A64"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B62:B64"/>
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="B9:B12"/>
     <mergeCell ref="B13:B15"/>
@@ -18791,13 +19945,6 @@
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="B42:B44"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="A54:A64"/>
-    <mergeCell ref="B54:B57"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B62:B64"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dev_stuffs/3匠魂.xlsx
+++ b/dev_stuffs/3匠魂.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requi